--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-24.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="90">
   <si>
     <t>League</t>
   </si>
@@ -254,6 +254,36 @@
   </si>
   <si>
     <t>SnapshotTS</t>
+  </si>
+  <si>
+    <t>Colombian Primera A</t>
+  </si>
+  <si>
+    <t>US MLS</t>
+  </si>
+  <si>
+    <t>2026-09-24</t>
+  </si>
+  <si>
+    <t>00:30:00</t>
+  </si>
+  <si>
+    <t>01:30:00</t>
+  </si>
+  <si>
+    <t>America de Cali S.A</t>
+  </si>
+  <si>
+    <t>Seattle Sounders</t>
+  </si>
+  <si>
+    <t>Aguilas Doradas</t>
+  </si>
+  <si>
+    <t>Real Salt Lake</t>
+  </si>
+  <si>
+    <t>2026-09-22 01:49:03</t>
   </si>
 </sst>
 </file>
@@ -585,7 +615,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB1"/>
+  <dimension ref="A1:CB3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -830,6 +860,490 @@
         <v>79</v>
       </c>
     </row>
+    <row r="2" spans="1:80">
+      <c r="A2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F2">
+        <v>1.69</v>
+      </c>
+      <c r="G2">
+        <v>1.76</v>
+      </c>
+      <c r="H2">
+        <v>5.9</v>
+      </c>
+      <c r="I2">
+        <v>6.6</v>
+      </c>
+      <c r="J2">
+        <v>3.7</v>
+      </c>
+      <c r="K2">
+        <v>4</v>
+      </c>
+      <c r="L2">
+        <v>1.02</v>
+      </c>
+      <c r="M2">
+        <v>1.08</v>
+      </c>
+      <c r="N2">
+        <v>3.35</v>
+      </c>
+      <c r="O2">
+        <v>1.38</v>
+      </c>
+      <c r="P2">
+        <v>1.8</v>
+      </c>
+      <c r="Q2">
+        <v>2.12</v>
+      </c>
+      <c r="R2">
+        <v>1.3</v>
+      </c>
+      <c r="S2">
+        <v>3.9</v>
+      </c>
+      <c r="T2">
+        <v>2.04</v>
+      </c>
+      <c r="U2">
+        <v>1.87</v>
+      </c>
+      <c r="V2">
+        <v>1.17</v>
+      </c>
+      <c r="W2">
+        <v>2.3</v>
+      </c>
+      <c r="X2">
+        <v>13</v>
+      </c>
+      <c r="Y2">
+        <v>22</v>
+      </c>
+      <c r="Z2">
+        <v>60</v>
+      </c>
+      <c r="AA2">
+        <v>220</v>
+      </c>
+      <c r="AB2">
+        <v>8.6</v>
+      </c>
+      <c r="AC2">
+        <v>8.6</v>
+      </c>
+      <c r="AD2">
+        <v>34</v>
+      </c>
+      <c r="AE2">
+        <v>120</v>
+      </c>
+      <c r="AF2">
+        <v>9.6</v>
+      </c>
+      <c r="AG2">
+        <v>10.5</v>
+      </c>
+      <c r="AH2">
+        <v>34</v>
+      </c>
+      <c r="AI2">
+        <v>120</v>
+      </c>
+      <c r="AJ2">
+        <v>18</v>
+      </c>
+      <c r="AK2">
+        <v>29</v>
+      </c>
+      <c r="AL2">
+        <v>55</v>
+      </c>
+      <c r="AM2">
+        <v>190</v>
+      </c>
+      <c r="AN2">
+        <v>13</v>
+      </c>
+      <c r="AO2">
+        <v>180</v>
+      </c>
+      <c r="AP2">
+        <v>11</v>
+      </c>
+      <c r="AQ2">
+        <v>15.5</v>
+      </c>
+      <c r="AR2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS2">
+        <v>8.6</v>
+      </c>
+      <c r="AT2">
+        <v>6.6</v>
+      </c>
+      <c r="AU2">
+        <v>7.8</v>
+      </c>
+      <c r="AV2">
+        <v>6.8</v>
+      </c>
+      <c r="AW2">
+        <v>8.4</v>
+      </c>
+      <c r="AX2">
+        <v>8.6</v>
+      </c>
+      <c r="AY2">
+        <v>9</v>
+      </c>
+      <c r="AZ2">
+        <v>14</v>
+      </c>
+      <c r="BA2">
+        <v>8.4</v>
+      </c>
+      <c r="BB2">
+        <v>14.5</v>
+      </c>
+      <c r="BC2">
+        <v>16.5</v>
+      </c>
+      <c r="BD2">
+        <v>8</v>
+      </c>
+      <c r="BE2">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF2">
+        <v>11.5</v>
+      </c>
+      <c r="BG2">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BH2">
+        <v>3.7</v>
+      </c>
+      <c r="BI2">
+        <v>2.58</v>
+      </c>
+      <c r="BJ2">
+        <v>13.5</v>
+      </c>
+      <c r="BK2">
+        <v>4</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>5.6</v>
+      </c>
+      <c r="BN2">
+        <v>4.2</v>
+      </c>
+      <c r="BO2">
+        <v>3.7</v>
+      </c>
+      <c r="BP2">
+        <v>14.5</v>
+      </c>
+      <c r="BQ2">
+        <v>4.1</v>
+      </c>
+      <c r="BR2">
+        <v>38</v>
+      </c>
+      <c r="BS2">
+        <v>5</v>
+      </c>
+      <c r="BT2">
+        <v>11.5</v>
+      </c>
+      <c r="BU2">
+        <v>3.85</v>
+      </c>
+      <c r="BV2">
+        <v>85</v>
+      </c>
+      <c r="BW2">
+        <v>5.3</v>
+      </c>
+      <c r="BX2">
+        <v>85</v>
+      </c>
+      <c r="BY2">
+        <v>5.4</v>
+      </c>
+      <c r="BZ2">
+        <v>32</v>
+      </c>
+      <c r="CA2">
+        <v>4.9</v>
+      </c>
+      <c r="CB2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3" spans="1:80">
+      <c r="A3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E3" t="s">
+        <v>88</v>
+      </c>
+      <c r="F3">
+        <v>1.98</v>
+      </c>
+      <c r="G3">
+        <v>2.02</v>
+      </c>
+      <c r="H3">
+        <v>3.85</v>
+      </c>
+      <c r="I3">
+        <v>4.1</v>
+      </c>
+      <c r="J3">
+        <v>4</v>
+      </c>
+      <c r="K3">
+        <v>4.1</v>
+      </c>
+      <c r="L3">
+        <v>1.31</v>
+      </c>
+      <c r="M3">
+        <v>1.04</v>
+      </c>
+      <c r="N3">
+        <v>5.3</v>
+      </c>
+      <c r="O3">
+        <v>1.22</v>
+      </c>
+      <c r="P3">
+        <v>2.46</v>
+      </c>
+      <c r="Q3">
+        <v>1.64</v>
+      </c>
+      <c r="R3">
+        <v>1.59</v>
+      </c>
+      <c r="S3">
+        <v>2.6</v>
+      </c>
+      <c r="T3">
+        <v>1.59</v>
+      </c>
+      <c r="U3">
+        <v>2.56</v>
+      </c>
+      <c r="V3">
+        <v>1.32</v>
+      </c>
+      <c r="W3">
+        <v>1.98</v>
+      </c>
+      <c r="X3">
+        <v>22</v>
+      </c>
+      <c r="Y3">
+        <v>21</v>
+      </c>
+      <c r="Z3">
+        <v>36</v>
+      </c>
+      <c r="AA3">
+        <v>80</v>
+      </c>
+      <c r="AB3">
+        <v>13</v>
+      </c>
+      <c r="AC3">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD3">
+        <v>16.5</v>
+      </c>
+      <c r="AE3">
+        <v>42</v>
+      </c>
+      <c r="AF3">
+        <v>15.5</v>
+      </c>
+      <c r="AG3">
+        <v>11</v>
+      </c>
+      <c r="AH3">
+        <v>16</v>
+      </c>
+      <c r="AI3">
+        <v>46</v>
+      </c>
+      <c r="AJ3">
+        <v>26</v>
+      </c>
+      <c r="AK3">
+        <v>18.5</v>
+      </c>
+      <c r="AL3">
+        <v>26</v>
+      </c>
+      <c r="AM3">
+        <v>70</v>
+      </c>
+      <c r="AN3">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AO3">
+        <v>34</v>
+      </c>
+      <c r="AP3">
+        <v>16.5</v>
+      </c>
+      <c r="AQ3">
+        <v>18</v>
+      </c>
+      <c r="AR3">
+        <v>28</v>
+      </c>
+      <c r="AS3">
+        <v>34</v>
+      </c>
+      <c r="AT3">
+        <v>11.5</v>
+      </c>
+      <c r="AU3">
+        <v>8.6</v>
+      </c>
+      <c r="AV3">
+        <v>14.5</v>
+      </c>
+      <c r="AW3">
+        <v>34</v>
+      </c>
+      <c r="AX3">
+        <v>13</v>
+      </c>
+      <c r="AY3">
+        <v>10</v>
+      </c>
+      <c r="AZ3">
+        <v>14</v>
+      </c>
+      <c r="BA3">
+        <v>36</v>
+      </c>
+      <c r="BB3">
+        <v>22</v>
+      </c>
+      <c r="BC3">
+        <v>16.5</v>
+      </c>
+      <c r="BD3">
+        <v>24</v>
+      </c>
+      <c r="BE3">
+        <v>50</v>
+      </c>
+      <c r="BF3">
+        <v>9</v>
+      </c>
+      <c r="BG3">
+        <v>23</v>
+      </c>
+      <c r="BH3">
+        <v>1000</v>
+      </c>
+      <c r="BI3">
+        <v>3.45</v>
+      </c>
+      <c r="BJ3">
+        <v>10.5</v>
+      </c>
+      <c r="BK3">
+        <v>5.6</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
+        <v>21</v>
+      </c>
+      <c r="BN3">
+        <v>6</v>
+      </c>
+      <c r="BO3">
+        <v>3.4</v>
+      </c>
+      <c r="BP3">
+        <v>18</v>
+      </c>
+      <c r="BQ3">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BR3">
+        <v>32</v>
+      </c>
+      <c r="BS3">
+        <v>13.5</v>
+      </c>
+      <c r="BT3">
+        <v>9</v>
+      </c>
+      <c r="BU3">
+        <v>4.9</v>
+      </c>
+      <c r="BV3">
+        <v>40</v>
+      </c>
+      <c r="BW3">
+        <v>16.5</v>
+      </c>
+      <c r="BX3">
+        <v>48</v>
+      </c>
+      <c r="BY3">
+        <v>19</v>
+      </c>
+      <c r="BZ3">
+        <v>23</v>
+      </c>
+      <c r="CA3">
+        <v>9.6</v>
+      </c>
+      <c r="CB3" t="s">
+        <v>89</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-24.xlsx
@@ -283,7 +283,7 @@
     <t>Real Salt Lake</t>
   </si>
   <si>
-    <t>2026-09-22 01:49:03</t>
+    <t>2026-09-22 03:59:47</t>
   </si>
 </sst>
 </file>
@@ -895,13 +895,13 @@
         <v>4</v>
       </c>
       <c r="L2">
-        <v>1.02</v>
+        <v>1.37</v>
       </c>
       <c r="M2">
         <v>1.08</v>
       </c>
       <c r="N2">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O2">
         <v>1.38</v>
@@ -919,7 +919,7 @@
         <v>3.9</v>
       </c>
       <c r="T2">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U2">
         <v>1.87</v>
@@ -967,7 +967,7 @@
         <v>120</v>
       </c>
       <c r="AJ2">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AK2">
         <v>29</v>
@@ -991,7 +991,7 @@
         <v>15.5</v>
       </c>
       <c r="AR2">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AS2">
         <v>8.6</v>
@@ -1000,10 +1000,10 @@
         <v>6.6</v>
       </c>
       <c r="AU2">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV2">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AW2">
         <v>8.4</v>
@@ -1021,10 +1021,10 @@
         <v>8.4</v>
       </c>
       <c r="BB2">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BC2">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BD2">
         <v>8</v>
@@ -1048,13 +1048,13 @@
         <v>13.5</v>
       </c>
       <c r="BK2">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BN2">
         <v>4.2</v>
@@ -1066,16 +1066,16 @@
         <v>14.5</v>
       </c>
       <c r="BQ2">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BR2">
         <v>38</v>
       </c>
       <c r="BS2">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BT2">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BU2">
         <v>3.85</v>
@@ -1084,19 +1084,19 @@
         <v>85</v>
       </c>
       <c r="BW2">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BX2">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="BY2">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BZ2">
         <v>32</v>
       </c>
       <c r="CA2">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="CB2" t="s">
         <v>89</v>
@@ -1119,22 +1119,22 @@
         <v>88</v>
       </c>
       <c r="F3">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="G3">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="H3">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="I3">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="J3">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K3">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L3">
         <v>1.31</v>
@@ -1164,16 +1164,16 @@
         <v>1.59</v>
       </c>
       <c r="U3">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="V3">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W3">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="X3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y3">
         <v>21</v>
@@ -1182,22 +1182,22 @@
         <v>36</v>
       </c>
       <c r="AA3">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AB3">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC3">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AD3">
         <v>16.5</v>
       </c>
       <c r="AE3">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AF3">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG3">
         <v>11</v>
@@ -1206,10 +1206,10 @@
         <v>16</v>
       </c>
       <c r="AI3">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ3">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AK3">
         <v>18.5</v>
@@ -1221,19 +1221,19 @@
         <v>70</v>
       </c>
       <c r="AN3">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AO3">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AP3">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AQ3">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AR3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AS3">
         <v>34</v>
@@ -1245,28 +1245,28 @@
         <v>8.6</v>
       </c>
       <c r="AV3">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AW3">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AX3">
         <v>13</v>
       </c>
       <c r="AY3">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AZ3">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA3">
         <v>36</v>
       </c>
       <c r="BB3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC3">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BD3">
         <v>24</v>
@@ -1275,37 +1275,37 @@
         <v>50</v>
       </c>
       <c r="BF3">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BG3">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="BH3">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BI3">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="BJ3">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK3">
-        <v>5.6</v>
+        <v>7.8</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>21</v>
+        <v>13.5</v>
       </c>
       <c r="BN3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BO3">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="BP3">
-        <v>18</v>
+        <v>12.5</v>
       </c>
       <c r="BQ3">
         <v>9.199999999999999</v>
@@ -1314,31 +1314,31 @@
         <v>32</v>
       </c>
       <c r="BS3">
-        <v>13.5</v>
+        <v>9</v>
       </c>
       <c r="BT3">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="BU3">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="BV3">
         <v>40</v>
       </c>
       <c r="BW3">
-        <v>16.5</v>
+        <v>10</v>
       </c>
       <c r="BX3">
         <v>48</v>
       </c>
       <c r="BY3">
-        <v>19</v>
+        <v>10.5</v>
       </c>
       <c r="BZ3">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="CA3">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB3" t="s">
         <v>89</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-24.xlsx
@@ -283,7 +283,7 @@
     <t>Real Salt Lake</t>
   </si>
   <si>
-    <t>2026-09-22 03:59:47</t>
+    <t>2026-09-22 06:10:38</t>
   </si>
 </sst>
 </file>
@@ -895,13 +895,13 @@
         <v>4</v>
       </c>
       <c r="L2">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="M2">
         <v>1.08</v>
       </c>
       <c r="N2">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="O2">
         <v>1.38</v>
@@ -919,7 +919,7 @@
         <v>3.9</v>
       </c>
       <c r="T2">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="U2">
         <v>1.87</v>
@@ -1000,7 +1000,7 @@
         <v>6.6</v>
       </c>
       <c r="AU2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV2">
         <v>6.6</v>
@@ -1021,7 +1021,7 @@
         <v>8.4</v>
       </c>
       <c r="BB2">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BC2">
         <v>17</v>
@@ -1048,13 +1048,13 @@
         <v>13.5</v>
       </c>
       <c r="BK2">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="BN2">
         <v>4.2</v>
@@ -1066,16 +1066,16 @@
         <v>14.5</v>
       </c>
       <c r="BQ2">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BR2">
         <v>38</v>
       </c>
       <c r="BS2">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="BT2">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BU2">
         <v>3.85</v>
@@ -1084,19 +1084,19 @@
         <v>85</v>
       </c>
       <c r="BW2">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="BX2">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="BY2">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="BZ2">
         <v>32</v>
       </c>
       <c r="CA2">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="CB2" t="s">
         <v>89</v>
@@ -1122,7 +1122,7 @@
         <v>1.93</v>
       </c>
       <c r="G3">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="H3">
         <v>4</v>
@@ -1131,7 +1131,7 @@
         <v>4.3</v>
       </c>
       <c r="J3">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K3">
         <v>4.2</v>
@@ -1161,37 +1161,37 @@
         <v>2.6</v>
       </c>
       <c r="T3">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="U3">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="V3">
         <v>1.3</v>
       </c>
       <c r="W3">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="X3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y3">
         <v>21</v>
       </c>
       <c r="Z3">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA3">
         <v>85</v>
       </c>
       <c r="AB3">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC3">
         <v>9.6</v>
       </c>
       <c r="AD3">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AE3">
         <v>50</v>
@@ -1203,7 +1203,7 @@
         <v>11</v>
       </c>
       <c r="AH3">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AI3">
         <v>44</v>
@@ -1221,7 +1221,7 @@
         <v>70</v>
       </c>
       <c r="AN3">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AO3">
         <v>32</v>
@@ -1230,7 +1230,7 @@
         <v>16</v>
       </c>
       <c r="AQ3">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AR3">
         <v>30</v>
@@ -1251,7 +1251,7 @@
         <v>36</v>
       </c>
       <c r="AX3">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AY3">
         <v>9.6</v>
@@ -1266,7 +1266,7 @@
         <v>21</v>
       </c>
       <c r="BC3">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BD3">
         <v>24</v>
@@ -1281,10 +1281,10 @@
         <v>20</v>
       </c>
       <c r="BH3">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BI3">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BJ3">
         <v>8.800000000000001</v>
@@ -1296,7 +1296,7 @@
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BN3">
         <v>5</v>
@@ -1314,7 +1314,7 @@
         <v>32</v>
       </c>
       <c r="BS3">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BT3">
         <v>7.8</v>
@@ -1326,13 +1326,13 @@
         <v>40</v>
       </c>
       <c r="BW3">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX3">
         <v>48</v>
       </c>
       <c r="BY3">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BZ3">
         <v>16</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-24.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="94">
   <si>
     <t>League</t>
   </si>
@@ -262,6 +262,9 @@
     <t>US MLS</t>
   </si>
   <si>
+    <t>Canadian Premier League</t>
+  </si>
+  <si>
     <t>2026-09-24</t>
   </si>
   <si>
@@ -271,19 +274,28 @@
     <t>01:30:00</t>
   </si>
   <si>
+    <t>02:00:00</t>
+  </si>
+  <si>
     <t>America de Cali S.A</t>
   </si>
   <si>
     <t>Seattle Sounders</t>
   </si>
   <si>
+    <t>Vancouver FC</t>
+  </si>
+  <si>
     <t>Aguilas Doradas</t>
   </si>
   <si>
     <t>Real Salt Lake</t>
   </si>
   <si>
-    <t>2026-09-22 06:10:38</t>
+    <t>Inter Toronto FC</t>
+  </si>
+  <si>
+    <t>2026-09-22 08:21:15</t>
   </si>
 </sst>
 </file>
@@ -615,7 +627,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB3"/>
+  <dimension ref="A1:CB4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -865,22 +877,22 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F2">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="G2">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="H2">
         <v>5.9</v>
@@ -910,7 +922,7 @@
         <v>1.8</v>
       </c>
       <c r="Q2">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="R2">
         <v>1.3</v>
@@ -928,7 +940,7 @@
         <v>1.17</v>
       </c>
       <c r="W2">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="X2">
         <v>13</v>
@@ -958,7 +970,7 @@
         <v>9.6</v>
       </c>
       <c r="AG2">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH2">
         <v>34</v>
@@ -967,7 +979,7 @@
         <v>120</v>
       </c>
       <c r="AJ2">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AK2">
         <v>29</v>
@@ -979,7 +991,7 @@
         <v>190</v>
       </c>
       <c r="AN2">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="AO2">
         <v>180</v>
@@ -991,10 +1003,10 @@
         <v>15.5</v>
       </c>
       <c r="AR2">
-        <v>8</v>
+        <v>6.4</v>
       </c>
       <c r="AS2">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="AT2">
         <v>6.6</v>
@@ -1003,13 +1015,13 @@
         <v>7.8</v>
       </c>
       <c r="AV2">
-        <v>6.6</v>
+        <v>17.5</v>
       </c>
       <c r="AW2">
+        <v>6.8</v>
+      </c>
+      <c r="AX2">
         <v>8.4</v>
-      </c>
-      <c r="AX2">
-        <v>8.6</v>
       </c>
       <c r="AY2">
         <v>9</v>
@@ -1018,25 +1030,25 @@
         <v>14</v>
       </c>
       <c r="BA2">
-        <v>8.4</v>
+        <v>6.8</v>
       </c>
       <c r="BB2">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BC2">
         <v>17</v>
       </c>
       <c r="BD2">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="BE2">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="BF2">
         <v>11.5</v>
       </c>
       <c r="BG2">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="BH2">
         <v>3.7</v>
@@ -1048,7 +1060,7 @@
         <v>13.5</v>
       </c>
       <c r="BK2">
-        <v>4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL2">
         <v>1000</v>
@@ -1099,7 +1111,7 @@
         <v>4.9</v>
       </c>
       <c r="CB2" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1107,22 +1119,22 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F3">
         <v>1.93</v>
       </c>
       <c r="G3">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="H3">
         <v>4</v>
@@ -1158,7 +1170,7 @@
         <v>1.59</v>
       </c>
       <c r="S3">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="T3">
         <v>1.61</v>
@@ -1170,7 +1182,7 @@
         <v>1.3</v>
       </c>
       <c r="W3">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="X3">
         <v>22</v>
@@ -1185,25 +1197,25 @@
         <v>85</v>
       </c>
       <c r="AB3">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AC3">
         <v>9.6</v>
       </c>
       <c r="AD3">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE3">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AF3">
         <v>14.5</v>
       </c>
       <c r="AG3">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH3">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI3">
         <v>44</v>
@@ -1218,19 +1230,19 @@
         <v>26</v>
       </c>
       <c r="AM3">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AN3">
         <v>9.4</v>
       </c>
       <c r="AO3">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AP3">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AQ3">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AR3">
         <v>30</v>
@@ -1266,7 +1278,7 @@
         <v>21</v>
       </c>
       <c r="BC3">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BD3">
         <v>24</v>
@@ -1278,16 +1290,16 @@
         <v>8.6</v>
       </c>
       <c r="BG3">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="BH3">
         <v>4.2</v>
       </c>
       <c r="BI3">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BJ3">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BK3">
         <v>7.8</v>
@@ -1296,7 +1308,7 @@
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="BN3">
         <v>5</v>
@@ -1314,7 +1326,7 @@
         <v>32</v>
       </c>
       <c r="BS3">
-        <v>9.6</v>
+        <v>8</v>
       </c>
       <c r="BT3">
         <v>7.8</v>
@@ -1326,22 +1338,264 @@
         <v>40</v>
       </c>
       <c r="BW3">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="BX3">
         <v>48</v>
       </c>
       <c r="BY3">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BZ3">
         <v>16</v>
       </c>
       <c r="CA3">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="CB3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4" spans="1:80">
+      <c r="A4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D4" t="s">
         <v>89</v>
+      </c>
+      <c r="E4" t="s">
+        <v>92</v>
+      </c>
+      <c r="F4">
+        <v>1.04</v>
+      </c>
+      <c r="G4">
+        <v>1000</v>
+      </c>
+      <c r="H4">
+        <v>1.04</v>
+      </c>
+      <c r="I4">
+        <v>1000</v>
+      </c>
+      <c r="J4">
+        <v>1.01</v>
+      </c>
+      <c r="K4">
+        <v>950</v>
+      </c>
+      <c r="L4">
+        <v>1.01</v>
+      </c>
+      <c r="M4">
+        <v>1.01</v>
+      </c>
+      <c r="N4">
+        <v>1.1</v>
+      </c>
+      <c r="O4">
+        <v>1.16</v>
+      </c>
+      <c r="P4">
+        <v>1.1</v>
+      </c>
+      <c r="Q4">
+        <v>1.16</v>
+      </c>
+      <c r="R4">
+        <v>1.08</v>
+      </c>
+      <c r="S4">
+        <v>1.16</v>
+      </c>
+      <c r="T4">
+        <v>1.01</v>
+      </c>
+      <c r="U4">
+        <v>1.01</v>
+      </c>
+      <c r="V4">
+        <v>1.01</v>
+      </c>
+      <c r="W4">
+        <v>1.01</v>
+      </c>
+      <c r="X4">
+        <v>1000</v>
+      </c>
+      <c r="Y4">
+        <v>1000</v>
+      </c>
+      <c r="Z4">
+        <v>1000</v>
+      </c>
+      <c r="AA4">
+        <v>1000</v>
+      </c>
+      <c r="AB4">
+        <v>1000</v>
+      </c>
+      <c r="AC4">
+        <v>1000</v>
+      </c>
+      <c r="AD4">
+        <v>1000</v>
+      </c>
+      <c r="AE4">
+        <v>1000</v>
+      </c>
+      <c r="AF4">
+        <v>1000</v>
+      </c>
+      <c r="AG4">
+        <v>1000</v>
+      </c>
+      <c r="AH4">
+        <v>1000</v>
+      </c>
+      <c r="AI4">
+        <v>1000</v>
+      </c>
+      <c r="AJ4">
+        <v>1000</v>
+      </c>
+      <c r="AK4">
+        <v>1000</v>
+      </c>
+      <c r="AL4">
+        <v>1000</v>
+      </c>
+      <c r="AM4">
+        <v>1000</v>
+      </c>
+      <c r="AN4">
+        <v>1000</v>
+      </c>
+      <c r="AO4">
+        <v>1000</v>
+      </c>
+      <c r="AP4">
+        <v>1.03</v>
+      </c>
+      <c r="AQ4">
+        <v>1.03</v>
+      </c>
+      <c r="AR4">
+        <v>1.03</v>
+      </c>
+      <c r="AS4">
+        <v>1.03</v>
+      </c>
+      <c r="AT4">
+        <v>1.03</v>
+      </c>
+      <c r="AU4">
+        <v>1.03</v>
+      </c>
+      <c r="AV4">
+        <v>1.03</v>
+      </c>
+      <c r="AW4">
+        <v>1.03</v>
+      </c>
+      <c r="AX4">
+        <v>1.03</v>
+      </c>
+      <c r="AY4">
+        <v>1.03</v>
+      </c>
+      <c r="AZ4">
+        <v>1.03</v>
+      </c>
+      <c r="BA4">
+        <v>1.03</v>
+      </c>
+      <c r="BB4">
+        <v>1.03</v>
+      </c>
+      <c r="BC4">
+        <v>1.03</v>
+      </c>
+      <c r="BD4">
+        <v>1.03</v>
+      </c>
+      <c r="BE4">
+        <v>1.03</v>
+      </c>
+      <c r="BF4">
+        <v>1.01</v>
+      </c>
+      <c r="BG4">
+        <v>1.01</v>
+      </c>
+      <c r="BH4">
+        <v>1000</v>
+      </c>
+      <c r="BI4">
+        <v>1.01</v>
+      </c>
+      <c r="BJ4">
+        <v>1000</v>
+      </c>
+      <c r="BK4">
+        <v>1.01</v>
+      </c>
+      <c r="BL4">
+        <v>1000</v>
+      </c>
+      <c r="BM4">
+        <v>1.01</v>
+      </c>
+      <c r="BN4">
+        <v>1000</v>
+      </c>
+      <c r="BO4">
+        <v>1.01</v>
+      </c>
+      <c r="BP4">
+        <v>1000</v>
+      </c>
+      <c r="BQ4">
+        <v>1.01</v>
+      </c>
+      <c r="BR4">
+        <v>1000</v>
+      </c>
+      <c r="BS4">
+        <v>1.01</v>
+      </c>
+      <c r="BT4">
+        <v>1000</v>
+      </c>
+      <c r="BU4">
+        <v>1.01</v>
+      </c>
+      <c r="BV4">
+        <v>1000</v>
+      </c>
+      <c r="BW4">
+        <v>1.01</v>
+      </c>
+      <c r="BX4">
+        <v>1000</v>
+      </c>
+      <c r="BY4">
+        <v>1.01</v>
+      </c>
+      <c r="BZ4">
+        <v>1000</v>
+      </c>
+      <c r="CA4">
+        <v>1.01</v>
+      </c>
+      <c r="CB4" t="s">
+        <v>93</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-24.xlsx
@@ -295,7 +295,7 @@
     <t>Inter Toronto FC</t>
   </si>
   <si>
-    <t>2026-09-22 08:21:15</t>
+    <t>2026-09-22 10:55:09</t>
   </si>
 </sst>
 </file>
@@ -889,7 +889,7 @@
         <v>90</v>
       </c>
       <c r="F2">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="G2">
         <v>1.75</v>
@@ -904,7 +904,7 @@
         <v>3.7</v>
       </c>
       <c r="K2">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L2">
         <v>1.38</v>
@@ -913,31 +913,31 @@
         <v>1.08</v>
       </c>
       <c r="N2">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O2">
         <v>1.38</v>
       </c>
       <c r="P2">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="Q2">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="R2">
         <v>1.3</v>
       </c>
       <c r="S2">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="T2">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U2">
         <v>1.87</v>
       </c>
       <c r="V2">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W2">
         <v>2.32</v>
@@ -952,7 +952,7 @@
         <v>60</v>
       </c>
       <c r="AA2">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="AB2">
         <v>8.6</v>
@@ -964,7 +964,7 @@
         <v>34</v>
       </c>
       <c r="AE2">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AF2">
         <v>9.6</v>
@@ -973,10 +973,10 @@
         <v>12.5</v>
       </c>
       <c r="AH2">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="AI2">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AJ2">
         <v>22</v>
@@ -1009,7 +1009,7 @@
         <v>7</v>
       </c>
       <c r="AT2">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU2">
         <v>7.8</v>
@@ -1033,16 +1033,16 @@
         <v>6.8</v>
       </c>
       <c r="BB2">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BC2">
         <v>17</v>
       </c>
       <c r="BD2">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BE2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BF2">
         <v>11.5</v>
@@ -1060,7 +1060,7 @@
         <v>13.5</v>
       </c>
       <c r="BK2">
-        <v>8.199999999999999</v>
+        <v>4</v>
       </c>
       <c r="BL2">
         <v>1000</v>
@@ -1155,25 +1155,25 @@
         <v>1.04</v>
       </c>
       <c r="N3">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="O3">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P3">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="Q3">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="R3">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="S3">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="T3">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="U3">
         <v>2.54</v>
@@ -1185,7 +1185,7 @@
         <v>2.02</v>
       </c>
       <c r="X3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y3">
         <v>21</v>
@@ -1206,7 +1206,7 @@
         <v>17</v>
       </c>
       <c r="AE3">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AF3">
         <v>14.5</v>
@@ -1224,7 +1224,7 @@
         <v>24</v>
       </c>
       <c r="AK3">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AL3">
         <v>26</v>
@@ -1233,13 +1233,13 @@
         <v>65</v>
       </c>
       <c r="AN3">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO3">
         <v>36</v>
       </c>
       <c r="AP3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ3">
         <v>17.5</v>
@@ -1287,16 +1287,16 @@
         <v>50</v>
       </c>
       <c r="BF3">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BG3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BH3">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BI3">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BJ3">
         <v>11</v>
@@ -1326,7 +1326,7 @@
         <v>32</v>
       </c>
       <c r="BS3">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BT3">
         <v>7.8</v>
@@ -1338,19 +1338,19 @@
         <v>40</v>
       </c>
       <c r="BW3">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BX3">
         <v>48</v>
       </c>
       <c r="BY3">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BZ3">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="CA3">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="CB3" t="s">
         <v>93</v>
@@ -1373,22 +1373,22 @@
         <v>92</v>
       </c>
       <c r="F4">
-        <v>1.04</v>
+        <v>1.86</v>
       </c>
       <c r="G4">
-        <v>1000</v>
+        <v>2.04</v>
       </c>
       <c r="H4">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="I4">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="J4">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="K4">
-        <v>950</v>
+        <v>5.4</v>
       </c>
       <c r="L4">
         <v>1.01</v>
@@ -1397,88 +1397,88 @@
         <v>1.01</v>
       </c>
       <c r="N4">
-        <v>1.1</v>
+        <v>3.45</v>
       </c>
       <c r="O4">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P4">
-        <v>1.1</v>
+        <v>2.34</v>
       </c>
       <c r="Q4">
-        <v>1.16</v>
+        <v>1.52</v>
       </c>
       <c r="R4">
-        <v>1.08</v>
+        <v>1.63</v>
       </c>
       <c r="S4">
-        <v>1.16</v>
+        <v>2.2</v>
       </c>
       <c r="T4">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="U4">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="V4">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="W4">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="X4">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Y4">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Z4">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AA4">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB4">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AC4">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AD4">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE4">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AF4">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AG4">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH4">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AI4">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AJ4">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AK4">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL4">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM4">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AN4">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AO4">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AP4">
         <v>1.03</v>
@@ -1529,10 +1529,10 @@
         <v>1.03</v>
       </c>
       <c r="BF4">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BG4">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BH4">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-24.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="117">
   <si>
     <t>League</t>
   </si>
@@ -265,6 +265,12 @@
     <t>Canadian Premier League</t>
   </si>
   <si>
+    <t>Nigerian Premier League</t>
+  </si>
+  <si>
+    <t>UEFA Nations League</t>
+  </si>
+  <si>
     <t>2026-09-24</t>
   </si>
   <si>
@@ -277,6 +283,15 @@
     <t>02:00:00</t>
   </si>
   <si>
+    <t>15:00:00</t>
+  </si>
+  <si>
+    <t>16:00:00</t>
+  </si>
+  <si>
+    <t>18:45:00</t>
+  </si>
+  <si>
     <t>America de Cali S.A</t>
   </si>
   <si>
@@ -286,6 +301,33 @@
     <t>Vancouver FC</t>
   </si>
   <si>
+    <t>Rivers United FC</t>
+  </si>
+  <si>
+    <t>Andorra</t>
+  </si>
+  <si>
+    <t>Liechtenstein</t>
+  </si>
+  <si>
+    <t>Netherlands</t>
+  </si>
+  <si>
+    <t>Austria</t>
+  </si>
+  <si>
+    <t>Norway</t>
+  </si>
+  <si>
+    <t>Kosovo</t>
+  </si>
+  <si>
+    <t>Serbia</t>
+  </si>
+  <si>
+    <t>Portugal</t>
+  </si>
+  <si>
     <t>Aguilas Doradas</t>
   </si>
   <si>
@@ -295,7 +337,34 @@
     <t>Inter Toronto FC</t>
   </si>
   <si>
-    <t>2026-09-22 10:55:09</t>
+    <t>Kun Khalifat FC</t>
+  </si>
+  <si>
+    <t>Malta</t>
+  </si>
+  <si>
+    <t>Lithuania</t>
+  </si>
+  <si>
+    <t>Germany</t>
+  </si>
+  <si>
+    <t>Israel</t>
+  </si>
+  <si>
+    <t>Denmark</t>
+  </si>
+  <si>
+    <t>Republic of Ireland</t>
+  </si>
+  <si>
+    <t>Greece</t>
+  </si>
+  <si>
+    <t>Wales</t>
+  </si>
+  <si>
+    <t>2026-09-22 13:07:11</t>
   </si>
 </sst>
 </file>
@@ -627,7 +696,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB4"/>
+  <dimension ref="A1:CB13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -877,19 +946,19 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D2" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E2" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="F2">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="G2">
         <v>1.75</v>
@@ -904,7 +973,7 @@
         <v>3.7</v>
       </c>
       <c r="K2">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L2">
         <v>1.38</v>
@@ -919,13 +988,13 @@
         <v>1.38</v>
       </c>
       <c r="P2">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="Q2">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R2">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S2">
         <v>3.95</v>
@@ -934,7 +1003,7 @@
         <v>2.08</v>
       </c>
       <c r="U2">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="V2">
         <v>1.18</v>
@@ -973,13 +1042,13 @@
         <v>12.5</v>
       </c>
       <c r="AH2">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="AI2">
         <v>130</v>
       </c>
       <c r="AJ2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK2">
         <v>29</v>
@@ -1009,7 +1078,7 @@
         <v>7</v>
       </c>
       <c r="AT2">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AU2">
         <v>7.8</v>
@@ -1033,7 +1102,7 @@
         <v>6.8</v>
       </c>
       <c r="BB2">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BC2">
         <v>17</v>
@@ -1042,7 +1111,7 @@
         <v>6.4</v>
       </c>
       <c r="BE2">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BF2">
         <v>11.5</v>
@@ -1111,7 +1180,7 @@
         <v>4.9</v>
       </c>
       <c r="CB2" t="s">
-        <v>93</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1119,25 +1188,25 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D3" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="E3" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="F3">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="G3">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="H3">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I3">
         <v>4.3</v>
@@ -1167,7 +1236,7 @@
         <v>1.63</v>
       </c>
       <c r="R3">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="S3">
         <v>2.56</v>
@@ -1176,13 +1245,13 @@
         <v>1.6</v>
       </c>
       <c r="U3">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="V3">
         <v>1.3</v>
       </c>
       <c r="W3">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="X3">
         <v>23</v>
@@ -1194,25 +1263,25 @@
         <v>34</v>
       </c>
       <c r="AA3">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AB3">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AC3">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD3">
         <v>17</v>
       </c>
       <c r="AE3">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AF3">
         <v>14.5</v>
       </c>
       <c r="AG3">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH3">
         <v>16</v>
@@ -1221,7 +1290,7 @@
         <v>44</v>
       </c>
       <c r="AJ3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK3">
         <v>18</v>
@@ -1242,7 +1311,7 @@
         <v>20</v>
       </c>
       <c r="AQ3">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AR3">
         <v>30</v>
@@ -1269,13 +1338,13 @@
         <v>9.6</v>
       </c>
       <c r="AZ3">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA3">
         <v>36</v>
       </c>
       <c r="BB3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC3">
         <v>16</v>
@@ -1287,10 +1356,10 @@
         <v>50</v>
       </c>
       <c r="BF3">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BG3">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="BH3">
         <v>4.3</v>
@@ -1299,16 +1368,16 @@
         <v>3.9</v>
       </c>
       <c r="BJ3">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BK3">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BL3">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BM3">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BN3">
         <v>5</v>
@@ -1323,10 +1392,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BR3">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="BS3">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BT3">
         <v>7.8</v>
@@ -1335,25 +1404,25 @@
         <v>6.8</v>
       </c>
       <c r="BV3">
+        <v>36</v>
+      </c>
+      <c r="BW3">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BX3">
         <v>40</v>
       </c>
-      <c r="BW3">
-        <v>8.4</v>
-      </c>
-      <c r="BX3">
-        <v>48</v>
-      </c>
       <c r="BY3">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ3">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="CA3">
         <v>6.8</v>
       </c>
       <c r="CB3" t="s">
-        <v>93</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1361,16 +1430,16 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D4" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="E4" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="F4">
         <v>1.86</v>
@@ -1382,7 +1451,7 @@
         <v>3.25</v>
       </c>
       <c r="I4">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="J4">
         <v>3.85</v>
@@ -1391,7 +1460,7 @@
         <v>5.4</v>
       </c>
       <c r="L4">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="M4">
         <v>1.01</v>
@@ -1421,7 +1490,7 @@
         <v>2.3</v>
       </c>
       <c r="V4">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W4">
         <v>1.96</v>
@@ -1535,16 +1604,16 @@
         <v>19</v>
       </c>
       <c r="BH4">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BI4">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BJ4">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK4">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BL4">
         <v>1000</v>
@@ -1553,49 +1622,2227 @@
         <v>1.01</v>
       </c>
       <c r="BN4">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BO4">
+        <v>4</v>
+      </c>
+      <c r="BP4">
+        <v>15</v>
+      </c>
+      <c r="BQ4">
+        <v>9</v>
+      </c>
+      <c r="BR4">
+        <v>25</v>
+      </c>
+      <c r="BS4">
+        <v>14.5</v>
+      </c>
+      <c r="BT4">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BU4">
+        <v>5.8</v>
+      </c>
+      <c r="BV4">
+        <v>32</v>
+      </c>
+      <c r="BW4">
+        <v>19</v>
+      </c>
+      <c r="BX4">
+        <v>38</v>
+      </c>
+      <c r="BY4">
+        <v>21</v>
+      </c>
+      <c r="BZ4">
+        <v>17</v>
+      </c>
+      <c r="CA4">
+        <v>10</v>
+      </c>
+      <c r="CB4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="5" spans="1:80">
+      <c r="A5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D5" t="s">
+        <v>95</v>
+      </c>
+      <c r="E5" t="s">
+        <v>107</v>
+      </c>
+      <c r="F5">
+        <v>1.1</v>
+      </c>
+      <c r="G5">
+        <v>1000</v>
+      </c>
+      <c r="H5">
+        <v>1.1</v>
+      </c>
+      <c r="I5">
+        <v>1000</v>
+      </c>
+      <c r="J5">
+        <v>1.1</v>
+      </c>
+      <c r="K5">
+        <v>920</v>
+      </c>
+      <c r="L5">
         <v>1.01</v>
       </c>
-      <c r="BP4">
-        <v>1000</v>
-      </c>
-      <c r="BQ4">
+      <c r="M5">
         <v>1.01</v>
       </c>
-      <c r="BR4">
-        <v>1000</v>
-      </c>
-      <c r="BS4">
+      <c r="N5">
+        <v>1.12</v>
+      </c>
+      <c r="O5">
+        <v>1.16</v>
+      </c>
+      <c r="P5">
+        <v>1.12</v>
+      </c>
+      <c r="Q5">
+        <v>1.16</v>
+      </c>
+      <c r="R5">
+        <v>1.08</v>
+      </c>
+      <c r="S5">
+        <v>1.16</v>
+      </c>
+      <c r="T5">
         <v>1.01</v>
       </c>
-      <c r="BT4">
-        <v>1000</v>
-      </c>
-      <c r="BU4">
+      <c r="U5">
         <v>1.01</v>
       </c>
-      <c r="BV4">
-        <v>1000</v>
-      </c>
-      <c r="BW4">
+      <c r="V5">
         <v>1.01</v>
       </c>
-      <c r="BX4">
-        <v>1000</v>
-      </c>
-      <c r="BY4">
+      <c r="W5">
         <v>1.01</v>
       </c>
-      <c r="BZ4">
-        <v>1000</v>
-      </c>
-      <c r="CA4">
+      <c r="X5">
+        <v>1000</v>
+      </c>
+      <c r="Y5">
+        <v>1000</v>
+      </c>
+      <c r="Z5">
+        <v>1000</v>
+      </c>
+      <c r="AA5">
+        <v>1000</v>
+      </c>
+      <c r="AB5">
+        <v>1000</v>
+      </c>
+      <c r="AC5">
+        <v>1000</v>
+      </c>
+      <c r="AD5">
+        <v>1000</v>
+      </c>
+      <c r="AE5">
+        <v>1000</v>
+      </c>
+      <c r="AF5">
+        <v>1000</v>
+      </c>
+      <c r="AG5">
+        <v>1000</v>
+      </c>
+      <c r="AH5">
+        <v>1000</v>
+      </c>
+      <c r="AI5">
+        <v>1000</v>
+      </c>
+      <c r="AJ5">
+        <v>1000</v>
+      </c>
+      <c r="AK5">
+        <v>1000</v>
+      </c>
+      <c r="AL5">
+        <v>1000</v>
+      </c>
+      <c r="AM5">
+        <v>1000</v>
+      </c>
+      <c r="AN5">
+        <v>1000</v>
+      </c>
+      <c r="AO5">
+        <v>1000</v>
+      </c>
+      <c r="AP5">
         <v>1.01</v>
       </c>
-      <c r="CB4" t="s">
-        <v>93</v>
+      <c r="AQ5">
+        <v>1.01</v>
+      </c>
+      <c r="AR5">
+        <v>1.01</v>
+      </c>
+      <c r="AS5">
+        <v>1.01</v>
+      </c>
+      <c r="AT5">
+        <v>1.01</v>
+      </c>
+      <c r="AU5">
+        <v>1.01</v>
+      </c>
+      <c r="AV5">
+        <v>1.01</v>
+      </c>
+      <c r="AW5">
+        <v>1.01</v>
+      </c>
+      <c r="AX5">
+        <v>1.01</v>
+      </c>
+      <c r="AY5">
+        <v>1.01</v>
+      </c>
+      <c r="AZ5">
+        <v>1.01</v>
+      </c>
+      <c r="BA5">
+        <v>1.01</v>
+      </c>
+      <c r="BB5">
+        <v>1.01</v>
+      </c>
+      <c r="BC5">
+        <v>1.01</v>
+      </c>
+      <c r="BD5">
+        <v>1.01</v>
+      </c>
+      <c r="BE5">
+        <v>1.01</v>
+      </c>
+      <c r="BF5">
+        <v>1.01</v>
+      </c>
+      <c r="BG5">
+        <v>1.01</v>
+      </c>
+      <c r="BH5">
+        <v>1000</v>
+      </c>
+      <c r="BI5">
+        <v>1.01</v>
+      </c>
+      <c r="BJ5">
+        <v>1000</v>
+      </c>
+      <c r="BK5">
+        <v>1.01</v>
+      </c>
+      <c r="BL5">
+        <v>1000</v>
+      </c>
+      <c r="BM5">
+        <v>1.01</v>
+      </c>
+      <c r="BN5">
+        <v>1000</v>
+      </c>
+      <c r="BO5">
+        <v>1.01</v>
+      </c>
+      <c r="BP5">
+        <v>1000</v>
+      </c>
+      <c r="BQ5">
+        <v>1.01</v>
+      </c>
+      <c r="BR5">
+        <v>1000</v>
+      </c>
+      <c r="BS5">
+        <v>1.01</v>
+      </c>
+      <c r="BT5">
+        <v>1000</v>
+      </c>
+      <c r="BU5">
+        <v>1.01</v>
+      </c>
+      <c r="BV5">
+        <v>1000</v>
+      </c>
+      <c r="BW5">
+        <v>1.01</v>
+      </c>
+      <c r="BX5">
+        <v>1000</v>
+      </c>
+      <c r="BY5">
+        <v>1.01</v>
+      </c>
+      <c r="BZ5">
+        <v>1000</v>
+      </c>
+      <c r="CA5">
+        <v>1.01</v>
+      </c>
+      <c r="CB5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="6" spans="1:80">
+      <c r="A6" t="s">
+        <v>84</v>
+      </c>
+      <c r="B6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C6" t="s">
+        <v>90</v>
+      </c>
+      <c r="D6" t="s">
+        <v>96</v>
+      </c>
+      <c r="E6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F6">
+        <v>4</v>
+      </c>
+      <c r="G6">
+        <v>4.1</v>
+      </c>
+      <c r="H6">
+        <v>2.46</v>
+      </c>
+      <c r="I6">
+        <v>2.5</v>
+      </c>
+      <c r="J6">
+        <v>2.88</v>
+      </c>
+      <c r="K6">
+        <v>2.9</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>1.38</v>
+      </c>
+      <c r="Q6">
+        <v>3.5</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>2.48</v>
+      </c>
+      <c r="U6">
+        <v>1.61</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>6.4</v>
+      </c>
+      <c r="Y6">
+        <v>6.4</v>
+      </c>
+      <c r="Z6">
+        <v>13</v>
+      </c>
+      <c r="AA6">
+        <v>42</v>
+      </c>
+      <c r="AB6">
+        <v>9</v>
+      </c>
+      <c r="AC6">
+        <v>7</v>
+      </c>
+      <c r="AD6">
+        <v>14.5</v>
+      </c>
+      <c r="AE6">
+        <v>48</v>
+      </c>
+      <c r="AF6">
+        <v>25</v>
+      </c>
+      <c r="AG6">
+        <v>21</v>
+      </c>
+      <c r="AH6">
+        <v>34</v>
+      </c>
+      <c r="AI6">
+        <v>110</v>
+      </c>
+      <c r="AJ6">
+        <v>110</v>
+      </c>
+      <c r="AK6">
+        <v>90</v>
+      </c>
+      <c r="AL6">
+        <v>140</v>
+      </c>
+      <c r="AM6">
+        <v>350</v>
+      </c>
+      <c r="AN6">
+        <v>160</v>
+      </c>
+      <c r="AO6">
+        <v>55</v>
+      </c>
+      <c r="AP6">
+        <v>6</v>
+      </c>
+      <c r="AQ6">
+        <v>5.9</v>
+      </c>
+      <c r="AR6">
+        <v>11.5</v>
+      </c>
+      <c r="AS6">
+        <v>34</v>
+      </c>
+      <c r="AT6">
+        <v>8.4</v>
+      </c>
+      <c r="AU6">
+        <v>6.6</v>
+      </c>
+      <c r="AV6">
+        <v>13</v>
+      </c>
+      <c r="AW6">
+        <v>40</v>
+      </c>
+      <c r="AX6">
+        <v>20</v>
+      </c>
+      <c r="AY6">
+        <v>18.5</v>
+      </c>
+      <c r="AZ6">
+        <v>28</v>
+      </c>
+      <c r="BA6">
+        <v>15.5</v>
+      </c>
+      <c r="BB6">
+        <v>15.5</v>
+      </c>
+      <c r="BC6">
+        <v>15.5</v>
+      </c>
+      <c r="BD6">
+        <v>15.5</v>
+      </c>
+      <c r="BE6">
+        <v>12.5</v>
+      </c>
+      <c r="BF6">
+        <v>14.5</v>
+      </c>
+      <c r="BG6">
+        <v>42</v>
+      </c>
+      <c r="BH6">
+        <v>0</v>
+      </c>
+      <c r="BI6">
+        <v>0</v>
+      </c>
+      <c r="BJ6">
+        <v>0</v>
+      </c>
+      <c r="BK6">
+        <v>0</v>
+      </c>
+      <c r="BL6">
+        <v>0</v>
+      </c>
+      <c r="BM6">
+        <v>0</v>
+      </c>
+      <c r="BN6">
+        <v>0</v>
+      </c>
+      <c r="BO6">
+        <v>0</v>
+      </c>
+      <c r="BP6">
+        <v>0</v>
+      </c>
+      <c r="BQ6">
+        <v>0</v>
+      </c>
+      <c r="BR6">
+        <v>0</v>
+      </c>
+      <c r="BS6">
+        <v>0</v>
+      </c>
+      <c r="BT6">
+        <v>0</v>
+      </c>
+      <c r="BU6">
+        <v>0</v>
+      </c>
+      <c r="BV6">
+        <v>0</v>
+      </c>
+      <c r="BW6">
+        <v>0</v>
+      </c>
+      <c r="BX6">
+        <v>0</v>
+      </c>
+      <c r="BY6">
+        <v>0</v>
+      </c>
+      <c r="BZ6">
+        <v>0</v>
+      </c>
+      <c r="CA6">
+        <v>0</v>
+      </c>
+      <c r="CB6" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="7" spans="1:80">
+      <c r="A7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C7" t="s">
+        <v>91</v>
+      </c>
+      <c r="D7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E7" t="s">
+        <v>109</v>
+      </c>
+      <c r="F7">
+        <v>13.5</v>
+      </c>
+      <c r="G7">
+        <v>17</v>
+      </c>
+      <c r="H7">
+        <v>1.33</v>
+      </c>
+      <c r="I7">
+        <v>1.34</v>
+      </c>
+      <c r="J7">
+        <v>5.4</v>
+      </c>
+      <c r="K7">
+        <v>5.6</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>1.74</v>
+      </c>
+      <c r="Q7">
+        <v>2.22</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>2.88</v>
+      </c>
+      <c r="U7">
+        <v>1.47</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>12.5</v>
+      </c>
+      <c r="Y7">
+        <v>5.9</v>
+      </c>
+      <c r="Z7">
+        <v>6.4</v>
+      </c>
+      <c r="AA7">
+        <v>12</v>
+      </c>
+      <c r="AB7">
+        <v>34</v>
+      </c>
+      <c r="AC7">
+        <v>15.5</v>
+      </c>
+      <c r="AD7">
+        <v>13</v>
+      </c>
+      <c r="AE7">
+        <v>19</v>
+      </c>
+      <c r="AF7">
+        <v>210</v>
+      </c>
+      <c r="AG7">
+        <v>95</v>
+      </c>
+      <c r="AH7">
+        <v>70</v>
+      </c>
+      <c r="AI7">
+        <v>85</v>
+      </c>
+      <c r="AJ7">
+        <v>1000</v>
+      </c>
+      <c r="AK7">
+        <v>1000</v>
+      </c>
+      <c r="AL7">
+        <v>420</v>
+      </c>
+      <c r="AM7">
+        <v>570</v>
+      </c>
+      <c r="AN7">
+        <v>1000</v>
+      </c>
+      <c r="AO7">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AP7">
+        <v>11</v>
+      </c>
+      <c r="AQ7">
+        <v>5.2</v>
+      </c>
+      <c r="AR7">
+        <v>5.6</v>
+      </c>
+      <c r="AS7">
+        <v>8.6</v>
+      </c>
+      <c r="AT7">
+        <v>23</v>
+      </c>
+      <c r="AU7">
+        <v>11.5</v>
+      </c>
+      <c r="AV7">
+        <v>10.5</v>
+      </c>
+      <c r="AW7">
+        <v>17</v>
+      </c>
+      <c r="AX7">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY7">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ7">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BA7">
+        <v>9</v>
+      </c>
+      <c r="BB7">
+        <v>9</v>
+      </c>
+      <c r="BC7">
+        <v>9</v>
+      </c>
+      <c r="BD7">
+        <v>9</v>
+      </c>
+      <c r="BE7">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF7">
+        <v>9</v>
+      </c>
+      <c r="BG7">
+        <v>7</v>
+      </c>
+      <c r="BH7">
+        <v>0</v>
+      </c>
+      <c r="BI7">
+        <v>0</v>
+      </c>
+      <c r="BJ7">
+        <v>0</v>
+      </c>
+      <c r="BK7">
+        <v>0</v>
+      </c>
+      <c r="BL7">
+        <v>0</v>
+      </c>
+      <c r="BM7">
+        <v>0</v>
+      </c>
+      <c r="BN7">
+        <v>0</v>
+      </c>
+      <c r="BO7">
+        <v>0</v>
+      </c>
+      <c r="BP7">
+        <v>0</v>
+      </c>
+      <c r="BQ7">
+        <v>0</v>
+      </c>
+      <c r="BR7">
+        <v>0</v>
+      </c>
+      <c r="BS7">
+        <v>0</v>
+      </c>
+      <c r="BT7">
+        <v>0</v>
+      </c>
+      <c r="BU7">
+        <v>0</v>
+      </c>
+      <c r="BV7">
+        <v>0</v>
+      </c>
+      <c r="BW7">
+        <v>0</v>
+      </c>
+      <c r="BX7">
+        <v>0</v>
+      </c>
+      <c r="BY7">
+        <v>0</v>
+      </c>
+      <c r="BZ7">
+        <v>0</v>
+      </c>
+      <c r="CA7">
+        <v>0</v>
+      </c>
+      <c r="CB7" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="8" spans="1:80">
+      <c r="A8" t="s">
+        <v>84</v>
+      </c>
+      <c r="B8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C8" t="s">
+        <v>91</v>
+      </c>
+      <c r="D8" t="s">
+        <v>98</v>
+      </c>
+      <c r="E8" t="s">
+        <v>110</v>
+      </c>
+      <c r="F8">
+        <v>2.52</v>
+      </c>
+      <c r="G8">
+        <v>2.54</v>
+      </c>
+      <c r="H8">
+        <v>2.84</v>
+      </c>
+      <c r="I8">
+        <v>2.86</v>
+      </c>
+      <c r="J8">
+        <v>3.9</v>
+      </c>
+      <c r="K8">
+        <v>4</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>1.04</v>
+      </c>
+      <c r="N8">
+        <v>5.9</v>
+      </c>
+      <c r="O8">
+        <v>1.19</v>
+      </c>
+      <c r="P8">
+        <v>2.6</v>
+      </c>
+      <c r="Q8">
+        <v>1.59</v>
+      </c>
+      <c r="R8">
+        <v>1.65</v>
+      </c>
+      <c r="S8">
+        <v>2.4</v>
+      </c>
+      <c r="T8">
+        <v>1.52</v>
+      </c>
+      <c r="U8">
+        <v>2.8</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>25</v>
+      </c>
+      <c r="Y8">
+        <v>18.5</v>
+      </c>
+      <c r="Z8">
+        <v>24</v>
+      </c>
+      <c r="AA8">
+        <v>50</v>
+      </c>
+      <c r="AB8">
+        <v>17</v>
+      </c>
+      <c r="AC8">
+        <v>9.6</v>
+      </c>
+      <c r="AD8">
+        <v>13.5</v>
+      </c>
+      <c r="AE8">
+        <v>28</v>
+      </c>
+      <c r="AF8">
+        <v>21</v>
+      </c>
+      <c r="AG8">
+        <v>13</v>
+      </c>
+      <c r="AH8">
+        <v>14.5</v>
+      </c>
+      <c r="AI8">
+        <v>34</v>
+      </c>
+      <c r="AJ8">
+        <v>40</v>
+      </c>
+      <c r="AK8">
+        <v>24</v>
+      </c>
+      <c r="AL8">
+        <v>30</v>
+      </c>
+      <c r="AM8">
+        <v>65</v>
+      </c>
+      <c r="AN8">
+        <v>13.5</v>
+      </c>
+      <c r="AO8">
+        <v>16</v>
+      </c>
+      <c r="AP8">
+        <v>22</v>
+      </c>
+      <c r="AQ8">
+        <v>16</v>
+      </c>
+      <c r="AR8">
+        <v>18</v>
+      </c>
+      <c r="AS8">
+        <v>32</v>
+      </c>
+      <c r="AT8">
+        <v>14.5</v>
+      </c>
+      <c r="AU8">
+        <v>8.4</v>
+      </c>
+      <c r="AV8">
+        <v>11.5</v>
+      </c>
+      <c r="AW8">
+        <v>8.4</v>
+      </c>
+      <c r="AX8">
+        <v>17.5</v>
+      </c>
+      <c r="AY8">
+        <v>11.5</v>
+      </c>
+      <c r="AZ8">
+        <v>12.5</v>
+      </c>
+      <c r="BA8">
+        <v>21</v>
+      </c>
+      <c r="BB8">
+        <v>18</v>
+      </c>
+      <c r="BC8">
+        <v>20</v>
+      </c>
+      <c r="BD8">
+        <v>20</v>
+      </c>
+      <c r="BE8">
+        <v>23</v>
+      </c>
+      <c r="BF8">
+        <v>11.5</v>
+      </c>
+      <c r="BG8">
+        <v>14</v>
+      </c>
+      <c r="BH8">
+        <v>4.4</v>
+      </c>
+      <c r="BI8">
+        <v>4.1</v>
+      </c>
+      <c r="BJ8">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BK8">
+        <v>7.2</v>
+      </c>
+      <c r="BL8">
+        <v>75</v>
+      </c>
+      <c r="BM8">
+        <v>13.5</v>
+      </c>
+      <c r="BN8">
+        <v>5.9</v>
+      </c>
+      <c r="BO8">
+        <v>5.4</v>
+      </c>
+      <c r="BP8">
+        <v>17</v>
+      </c>
+      <c r="BQ8">
+        <v>8.4</v>
+      </c>
+      <c r="BR8">
+        <v>24</v>
+      </c>
+      <c r="BS8">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BT8">
+        <v>6.4</v>
+      </c>
+      <c r="BU8">
+        <v>5.8</v>
+      </c>
+      <c r="BV8">
+        <v>19.5</v>
+      </c>
+      <c r="BW8">
+        <v>9</v>
+      </c>
+      <c r="BX8">
+        <v>26</v>
+      </c>
+      <c r="BY8">
+        <v>10</v>
+      </c>
+      <c r="BZ8">
+        <v>16</v>
+      </c>
+      <c r="CA8">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="CB8" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="9" spans="1:80">
+      <c r="A9" t="s">
+        <v>84</v>
+      </c>
+      <c r="B9" t="s">
+        <v>85</v>
+      </c>
+      <c r="C9" t="s">
+        <v>91</v>
+      </c>
+      <c r="D9" t="s">
+        <v>99</v>
+      </c>
+      <c r="E9" t="s">
+        <v>111</v>
+      </c>
+      <c r="F9">
+        <v>1.48</v>
+      </c>
+      <c r="G9">
+        <v>1.49</v>
+      </c>
+      <c r="H9">
+        <v>7.6</v>
+      </c>
+      <c r="I9">
+        <v>7.8</v>
+      </c>
+      <c r="J9">
+        <v>5</v>
+      </c>
+      <c r="K9">
+        <v>5.2</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>1.03</v>
+      </c>
+      <c r="N9">
+        <v>6</v>
+      </c>
+      <c r="O9">
+        <v>1.17</v>
+      </c>
+      <c r="P9">
+        <v>2.74</v>
+      </c>
+      <c r="Q9">
+        <v>1.54</v>
+      </c>
+      <c r="R9">
+        <v>1.67</v>
+      </c>
+      <c r="S9">
+        <v>2.2</v>
+      </c>
+      <c r="T9">
+        <v>1.74</v>
+      </c>
+      <c r="U9">
+        <v>2.18</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>30</v>
+      </c>
+      <c r="Y9">
+        <v>38</v>
+      </c>
+      <c r="Z9">
+        <v>90</v>
+      </c>
+      <c r="AA9">
+        <v>270</v>
+      </c>
+      <c r="AB9">
+        <v>13.5</v>
+      </c>
+      <c r="AC9">
+        <v>14</v>
+      </c>
+      <c r="AD9">
+        <v>32</v>
+      </c>
+      <c r="AE9">
+        <v>120</v>
+      </c>
+      <c r="AF9">
+        <v>11.5</v>
+      </c>
+      <c r="AG9">
+        <v>10.5</v>
+      </c>
+      <c r="AH9">
+        <v>27</v>
+      </c>
+      <c r="AI9">
+        <v>95</v>
+      </c>
+      <c r="AJ9">
+        <v>13.5</v>
+      </c>
+      <c r="AK9">
+        <v>17.5</v>
+      </c>
+      <c r="AL9">
+        <v>36</v>
+      </c>
+      <c r="AM9">
+        <v>110</v>
+      </c>
+      <c r="AN9">
+        <v>6</v>
+      </c>
+      <c r="AO9">
+        <v>110</v>
+      </c>
+      <c r="AP9">
+        <v>11</v>
+      </c>
+      <c r="AQ9">
+        <v>5.4</v>
+      </c>
+      <c r="AR9">
+        <v>5.9</v>
+      </c>
+      <c r="AS9">
+        <v>6.2</v>
+      </c>
+      <c r="AT9">
+        <v>10</v>
+      </c>
+      <c r="AU9">
+        <v>10.5</v>
+      </c>
+      <c r="AV9">
+        <v>20</v>
+      </c>
+      <c r="AW9">
+        <v>6</v>
+      </c>
+      <c r="AX9">
+        <v>9.4</v>
+      </c>
+      <c r="AY9">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ9">
+        <v>16</v>
+      </c>
+      <c r="BA9">
+        <v>5.9</v>
+      </c>
+      <c r="BB9">
+        <v>11.5</v>
+      </c>
+      <c r="BC9">
+        <v>12</v>
+      </c>
+      <c r="BD9">
+        <v>20</v>
+      </c>
+      <c r="BE9">
+        <v>6</v>
+      </c>
+      <c r="BF9">
+        <v>4.6</v>
+      </c>
+      <c r="BG9">
+        <v>6</v>
+      </c>
+      <c r="BH9">
+        <v>4.7</v>
+      </c>
+      <c r="BI9">
+        <v>4.1</v>
+      </c>
+      <c r="BJ9">
+        <v>12.5</v>
+      </c>
+      <c r="BK9">
+        <v>4.6</v>
+      </c>
+      <c r="BL9">
+        <v>1000</v>
+      </c>
+      <c r="BM9">
+        <v>6</v>
+      </c>
+      <c r="BN9">
+        <v>4.3</v>
+      </c>
+      <c r="BO9">
+        <v>3.8</v>
+      </c>
+      <c r="BP9">
+        <v>10.5</v>
+      </c>
+      <c r="BQ9">
+        <v>7.4</v>
+      </c>
+      <c r="BR9">
+        <v>24</v>
+      </c>
+      <c r="BS9">
+        <v>5.1</v>
+      </c>
+      <c r="BT9">
+        <v>13.5</v>
+      </c>
+      <c r="BU9">
+        <v>4.7</v>
+      </c>
+      <c r="BV9">
+        <v>70</v>
+      </c>
+      <c r="BW9">
+        <v>5.9</v>
+      </c>
+      <c r="BX9">
+        <v>65</v>
+      </c>
+      <c r="BY9">
+        <v>5.8</v>
+      </c>
+      <c r="BZ9">
+        <v>14</v>
+      </c>
+      <c r="CA9">
+        <v>4.8</v>
+      </c>
+      <c r="CB9" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="10" spans="1:80">
+      <c r="A10" t="s">
+        <v>84</v>
+      </c>
+      <c r="B10" t="s">
+        <v>85</v>
+      </c>
+      <c r="C10" t="s">
+        <v>91</v>
+      </c>
+      <c r="D10" t="s">
+        <v>100</v>
+      </c>
+      <c r="E10" t="s">
+        <v>112</v>
+      </c>
+      <c r="F10">
+        <v>1.8</v>
+      </c>
+      <c r="G10">
+        <v>1.82</v>
+      </c>
+      <c r="H10">
+        <v>4.5</v>
+      </c>
+      <c r="I10">
+        <v>4.7</v>
+      </c>
+      <c r="J10">
+        <v>4.2</v>
+      </c>
+      <c r="K10">
+        <v>4.3</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>1.05</v>
+      </c>
+      <c r="N10">
+        <v>4.5</v>
+      </c>
+      <c r="O10">
+        <v>1.26</v>
+      </c>
+      <c r="P10">
+        <v>2.2</v>
+      </c>
+      <c r="Q10">
+        <v>1.77</v>
+      </c>
+      <c r="R10">
+        <v>1.47</v>
+      </c>
+      <c r="S10">
+        <v>2.88</v>
+      </c>
+      <c r="T10">
+        <v>1.76</v>
+      </c>
+      <c r="U10">
+        <v>2.24</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <v>19</v>
+      </c>
+      <c r="Y10">
+        <v>19.5</v>
+      </c>
+      <c r="Z10">
+        <v>40</v>
+      </c>
+      <c r="AA10">
+        <v>120</v>
+      </c>
+      <c r="AB10">
+        <v>10.5</v>
+      </c>
+      <c r="AC10">
+        <v>9.6</v>
+      </c>
+      <c r="AD10">
+        <v>19</v>
+      </c>
+      <c r="AE10">
+        <v>60</v>
+      </c>
+      <c r="AF10">
+        <v>12</v>
+      </c>
+      <c r="AG10">
+        <v>11</v>
+      </c>
+      <c r="AH10">
+        <v>19</v>
+      </c>
+      <c r="AI10">
+        <v>65</v>
+      </c>
+      <c r="AJ10">
+        <v>19.5</v>
+      </c>
+      <c r="AK10">
+        <v>18.5</v>
+      </c>
+      <c r="AL10">
+        <v>34</v>
+      </c>
+      <c r="AM10">
+        <v>100</v>
+      </c>
+      <c r="AN10">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AO10">
+        <v>65</v>
+      </c>
+      <c r="AP10">
+        <v>16.5</v>
+      </c>
+      <c r="AQ10">
+        <v>16</v>
+      </c>
+      <c r="AR10">
+        <v>9.4</v>
+      </c>
+      <c r="AS10">
+        <v>10.5</v>
+      </c>
+      <c r="AT10">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU10">
+        <v>8.4</v>
+      </c>
+      <c r="AV10">
+        <v>16</v>
+      </c>
+      <c r="AW10">
+        <v>42</v>
+      </c>
+      <c r="AX10">
+        <v>10.5</v>
+      </c>
+      <c r="AY10">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ10">
+        <v>16</v>
+      </c>
+      <c r="BA10">
+        <v>42</v>
+      </c>
+      <c r="BB10">
+        <v>17</v>
+      </c>
+      <c r="BC10">
+        <v>15.5</v>
+      </c>
+      <c r="BD10">
+        <v>23</v>
+      </c>
+      <c r="BE10">
+        <v>11</v>
+      </c>
+      <c r="BF10">
+        <v>8.4</v>
+      </c>
+      <c r="BG10">
+        <v>10</v>
+      </c>
+      <c r="BH10">
+        <v>3.9</v>
+      </c>
+      <c r="BI10">
+        <v>3.45</v>
+      </c>
+      <c r="BJ10">
+        <v>9.6</v>
+      </c>
+      <c r="BK10">
+        <v>5.9</v>
+      </c>
+      <c r="BL10">
+        <v>1000</v>
+      </c>
+      <c r="BM10">
+        <v>12.5</v>
+      </c>
+      <c r="BN10">
+        <v>4.6</v>
+      </c>
+      <c r="BO10">
+        <v>4.2</v>
+      </c>
+      <c r="BP10">
+        <v>12</v>
+      </c>
+      <c r="BQ10">
+        <v>6.6</v>
+      </c>
+      <c r="BR10">
+        <v>25</v>
+      </c>
+      <c r="BS10">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BT10">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU10">
+        <v>7.4</v>
+      </c>
+      <c r="BV10">
+        <v>40</v>
+      </c>
+      <c r="BW10">
+        <v>10.5</v>
+      </c>
+      <c r="BX10">
+        <v>46</v>
+      </c>
+      <c r="BY10">
+        <v>11</v>
+      </c>
+      <c r="BZ10">
+        <v>19</v>
+      </c>
+      <c r="CA10">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="CB10" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="11" spans="1:80">
+      <c r="A11" t="s">
+        <v>84</v>
+      </c>
+      <c r="B11" t="s">
+        <v>85</v>
+      </c>
+      <c r="C11" t="s">
+        <v>91</v>
+      </c>
+      <c r="D11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E11" t="s">
+        <v>113</v>
+      </c>
+      <c r="F11">
+        <v>2.52</v>
+      </c>
+      <c r="G11">
+        <v>2.56</v>
+      </c>
+      <c r="H11">
+        <v>3.3</v>
+      </c>
+      <c r="I11">
+        <v>3.35</v>
+      </c>
+      <c r="J11">
+        <v>3.25</v>
+      </c>
+      <c r="K11">
+        <v>3.3</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>1.1</v>
+      </c>
+      <c r="N11">
+        <v>2.94</v>
+      </c>
+      <c r="O11">
+        <v>1.46</v>
+      </c>
+      <c r="P11">
+        <v>1.65</v>
+      </c>
+      <c r="Q11">
+        <v>2.38</v>
+      </c>
+      <c r="R11">
+        <v>1.24</v>
+      </c>
+      <c r="S11">
+        <v>4.7</v>
+      </c>
+      <c r="T11">
+        <v>2.02</v>
+      </c>
+      <c r="U11">
+        <v>1.88</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <v>12</v>
+      </c>
+      <c r="Y11">
+        <v>10</v>
+      </c>
+      <c r="Z11">
+        <v>23</v>
+      </c>
+      <c r="AA11">
+        <v>75</v>
+      </c>
+      <c r="AB11">
+        <v>8.6</v>
+      </c>
+      <c r="AC11">
+        <v>7.6</v>
+      </c>
+      <c r="AD11">
+        <v>15</v>
+      </c>
+      <c r="AE11">
+        <v>60</v>
+      </c>
+      <c r="AF11">
+        <v>16.5</v>
+      </c>
+      <c r="AG11">
+        <v>13</v>
+      </c>
+      <c r="AH11">
+        <v>28</v>
+      </c>
+      <c r="AI11">
+        <v>75</v>
+      </c>
+      <c r="AJ11">
+        <v>36</v>
+      </c>
+      <c r="AK11">
+        <v>38</v>
+      </c>
+      <c r="AL11">
+        <v>70</v>
+      </c>
+      <c r="AM11">
+        <v>180</v>
+      </c>
+      <c r="AN11">
+        <v>34</v>
+      </c>
+      <c r="AO11">
+        <v>65</v>
+      </c>
+      <c r="AP11">
+        <v>9.6</v>
+      </c>
+      <c r="AQ11">
+        <v>9</v>
+      </c>
+      <c r="AR11">
+        <v>18.5</v>
+      </c>
+      <c r="AS11">
+        <v>42</v>
+      </c>
+      <c r="AT11">
+        <v>7.8</v>
+      </c>
+      <c r="AU11">
+        <v>6.8</v>
+      </c>
+      <c r="AV11">
+        <v>13</v>
+      </c>
+      <c r="AW11">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX11">
+        <v>13</v>
+      </c>
+      <c r="AY11">
+        <v>11</v>
+      </c>
+      <c r="AZ11">
+        <v>17</v>
+      </c>
+      <c r="BA11">
+        <v>8.4</v>
+      </c>
+      <c r="BB11">
+        <v>30</v>
+      </c>
+      <c r="BC11">
+        <v>7.4</v>
+      </c>
+      <c r="BD11">
+        <v>8.4</v>
+      </c>
+      <c r="BE11">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF11">
+        <v>7.4</v>
+      </c>
+      <c r="BG11">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BH11">
+        <v>2.88</v>
+      </c>
+      <c r="BI11">
+        <v>2.66</v>
+      </c>
+      <c r="BJ11">
+        <v>10.5</v>
+      </c>
+      <c r="BK11">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BL11">
+        <v>1000</v>
+      </c>
+      <c r="BM11">
+        <v>15</v>
+      </c>
+      <c r="BN11">
+        <v>5.3</v>
+      </c>
+      <c r="BO11">
+        <v>4.7</v>
+      </c>
+      <c r="BP11">
+        <v>22</v>
+      </c>
+      <c r="BQ11">
+        <v>9.4</v>
+      </c>
+      <c r="BR11">
+        <v>1000</v>
+      </c>
+      <c r="BS11">
+        <v>11.5</v>
+      </c>
+      <c r="BT11">
+        <v>6.4</v>
+      </c>
+      <c r="BU11">
+        <v>5.6</v>
+      </c>
+      <c r="BV11">
+        <v>1000</v>
+      </c>
+      <c r="BW11">
+        <v>10.5</v>
+      </c>
+      <c r="BX11">
+        <v>1000</v>
+      </c>
+      <c r="BY11">
+        <v>12</v>
+      </c>
+      <c r="BZ11">
+        <v>1000</v>
+      </c>
+      <c r="CA11">
+        <v>11.5</v>
+      </c>
+      <c r="CB11" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="12" spans="1:80">
+      <c r="A12" t="s">
+        <v>84</v>
+      </c>
+      <c r="B12" t="s">
+        <v>85</v>
+      </c>
+      <c r="C12" t="s">
+        <v>91</v>
+      </c>
+      <c r="D12" t="s">
+        <v>102</v>
+      </c>
+      <c r="E12" t="s">
+        <v>114</v>
+      </c>
+      <c r="F12">
+        <v>2.72</v>
+      </c>
+      <c r="G12">
+        <v>2.78</v>
+      </c>
+      <c r="H12">
+        <v>2.86</v>
+      </c>
+      <c r="I12">
+        <v>2.9</v>
+      </c>
+      <c r="J12">
+        <v>3.4</v>
+      </c>
+      <c r="K12">
+        <v>3.45</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>1.09</v>
+      </c>
+      <c r="N12">
+        <v>3.3</v>
+      </c>
+      <c r="O12">
+        <v>1.4</v>
+      </c>
+      <c r="P12">
+        <v>1.79</v>
+      </c>
+      <c r="Q12">
+        <v>2.22</v>
+      </c>
+      <c r="R12">
+        <v>1.3</v>
+      </c>
+      <c r="S12">
+        <v>4.1</v>
+      </c>
+      <c r="T12">
+        <v>1.9</v>
+      </c>
+      <c r="U12">
+        <v>2.02</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>12</v>
+      </c>
+      <c r="Y12">
+        <v>11</v>
+      </c>
+      <c r="Z12">
+        <v>18.5</v>
+      </c>
+      <c r="AA12">
+        <v>55</v>
+      </c>
+      <c r="AB12">
+        <v>10.5</v>
+      </c>
+      <c r="AC12">
+        <v>7.6</v>
+      </c>
+      <c r="AD12">
+        <v>13.5</v>
+      </c>
+      <c r="AE12">
+        <v>40</v>
+      </c>
+      <c r="AF12">
+        <v>17.5</v>
+      </c>
+      <c r="AG12">
+        <v>13.5</v>
+      </c>
+      <c r="AH12">
+        <v>20</v>
+      </c>
+      <c r="AI12">
+        <v>60</v>
+      </c>
+      <c r="AJ12">
+        <v>44</v>
+      </c>
+      <c r="AK12">
+        <v>38</v>
+      </c>
+      <c r="AL12">
+        <v>60</v>
+      </c>
+      <c r="AM12">
+        <v>140</v>
+      </c>
+      <c r="AN12">
+        <v>34</v>
+      </c>
+      <c r="AO12">
+        <v>38</v>
+      </c>
+      <c r="AP12">
+        <v>11.5</v>
+      </c>
+      <c r="AQ12">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR12">
+        <v>15.5</v>
+      </c>
+      <c r="AS12">
+        <v>21</v>
+      </c>
+      <c r="AT12">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU12">
+        <v>7.2</v>
+      </c>
+      <c r="AV12">
+        <v>11.5</v>
+      </c>
+      <c r="AW12">
+        <v>17.5</v>
+      </c>
+      <c r="AX12">
+        <v>14.5</v>
+      </c>
+      <c r="AY12">
+        <v>11.5</v>
+      </c>
+      <c r="AZ12">
+        <v>16.5</v>
+      </c>
+      <c r="BA12">
+        <v>23</v>
+      </c>
+      <c r="BB12">
+        <v>32</v>
+      </c>
+      <c r="BC12">
+        <v>25</v>
+      </c>
+      <c r="BD12">
+        <v>36</v>
+      </c>
+      <c r="BE12">
+        <v>9.6</v>
+      </c>
+      <c r="BF12">
+        <v>24</v>
+      </c>
+      <c r="BG12">
+        <v>17.5</v>
+      </c>
+      <c r="BH12">
+        <v>3.1</v>
+      </c>
+      <c r="BI12">
+        <v>2.84</v>
+      </c>
+      <c r="BJ12">
+        <v>11.5</v>
+      </c>
+      <c r="BK12">
+        <v>4.8</v>
+      </c>
+      <c r="BL12">
+        <v>1000</v>
+      </c>
+      <c r="BM12">
+        <v>7</v>
+      </c>
+      <c r="BN12">
+        <v>6.4</v>
+      </c>
+      <c r="BO12">
+        <v>5.1</v>
+      </c>
+      <c r="BP12">
+        <v>26</v>
+      </c>
+      <c r="BQ12">
+        <v>5.8</v>
+      </c>
+      <c r="BR12">
+        <v>44</v>
+      </c>
+      <c r="BS12">
+        <v>6.4</v>
+      </c>
+      <c r="BT12">
+        <v>6.6</v>
+      </c>
+      <c r="BU12">
+        <v>5.3</v>
+      </c>
+      <c r="BV12">
+        <v>28</v>
+      </c>
+      <c r="BW12">
+        <v>5.9</v>
+      </c>
+      <c r="BX12">
+        <v>46</v>
+      </c>
+      <c r="BY12">
+        <v>6.4</v>
+      </c>
+      <c r="BZ12">
+        <v>40</v>
+      </c>
+      <c r="CA12">
+        <v>6.2</v>
+      </c>
+      <c r="CB12" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="13" spans="1:80">
+      <c r="A13" t="s">
+        <v>84</v>
+      </c>
+      <c r="B13" t="s">
+        <v>85</v>
+      </c>
+      <c r="C13" t="s">
+        <v>91</v>
+      </c>
+      <c r="D13" t="s">
+        <v>103</v>
+      </c>
+      <c r="E13" t="s">
+        <v>115</v>
+      </c>
+      <c r="F13">
+        <v>1.25</v>
+      </c>
+      <c r="G13">
+        <v>1.26</v>
+      </c>
+      <c r="H13">
+        <v>17</v>
+      </c>
+      <c r="I13">
+        <v>17.5</v>
+      </c>
+      <c r="J13">
+        <v>7</v>
+      </c>
+      <c r="K13">
+        <v>7.2</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>1.04</v>
+      </c>
+      <c r="N13">
+        <v>5.9</v>
+      </c>
+      <c r="O13">
+        <v>1.18</v>
+      </c>
+      <c r="P13">
+        <v>2.68</v>
+      </c>
+      <c r="Q13">
+        <v>1.54</v>
+      </c>
+      <c r="R13">
+        <v>1.67</v>
+      </c>
+      <c r="S13">
+        <v>2.36</v>
+      </c>
+      <c r="T13">
+        <v>2.3</v>
+      </c>
+      <c r="U13">
+        <v>1.75</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>28</v>
+      </c>
+      <c r="Y13">
+        <v>55</v>
+      </c>
+      <c r="Z13">
+        <v>210</v>
+      </c>
+      <c r="AA13">
+        <v>1000</v>
+      </c>
+      <c r="AB13">
+        <v>10.5</v>
+      </c>
+      <c r="AC13">
+        <v>16.5</v>
+      </c>
+      <c r="AD13">
+        <v>60</v>
+      </c>
+      <c r="AE13">
+        <v>320</v>
+      </c>
+      <c r="AF13">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AG13">
+        <v>12.5</v>
+      </c>
+      <c r="AH13">
+        <v>40</v>
+      </c>
+      <c r="AI13">
+        <v>220</v>
+      </c>
+      <c r="AJ13">
+        <v>9</v>
+      </c>
+      <c r="AK13">
+        <v>14.5</v>
+      </c>
+      <c r="AL13">
+        <v>48</v>
+      </c>
+      <c r="AM13">
+        <v>240</v>
+      </c>
+      <c r="AN13">
+        <v>3.8</v>
+      </c>
+      <c r="AO13">
+        <v>460</v>
+      </c>
+      <c r="AP13">
+        <v>24</v>
+      </c>
+      <c r="AQ13">
+        <v>12.5</v>
+      </c>
+      <c r="AR13">
+        <v>14</v>
+      </c>
+      <c r="AS13">
+        <v>15</v>
+      </c>
+      <c r="AT13">
+        <v>9.4</v>
+      </c>
+      <c r="AU13">
+        <v>14.5</v>
+      </c>
+      <c r="AV13">
+        <v>13</v>
+      </c>
+      <c r="AW13">
+        <v>14</v>
+      </c>
+      <c r="AX13">
+        <v>7.4</v>
+      </c>
+      <c r="AY13">
+        <v>10.5</v>
+      </c>
+      <c r="AZ13">
+        <v>11.5</v>
+      </c>
+      <c r="BA13">
+        <v>14.5</v>
+      </c>
+      <c r="BB13">
+        <v>8</v>
+      </c>
+      <c r="BC13">
+        <v>13</v>
+      </c>
+      <c r="BD13">
+        <v>12</v>
+      </c>
+      <c r="BE13">
+        <v>14.5</v>
+      </c>
+      <c r="BF13">
+        <v>3.65</v>
+      </c>
+      <c r="BG13">
+        <v>14.5</v>
+      </c>
+      <c r="BH13">
+        <v>4.4</v>
+      </c>
+      <c r="BI13">
+        <v>4</v>
+      </c>
+      <c r="BJ13">
+        <v>15.5</v>
+      </c>
+      <c r="BK13">
+        <v>6.2</v>
+      </c>
+      <c r="BL13">
+        <v>210</v>
+      </c>
+      <c r="BM13">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BN13">
+        <v>3.7</v>
+      </c>
+      <c r="BO13">
+        <v>3.4</v>
+      </c>
+      <c r="BP13">
+        <v>6.8</v>
+      </c>
+      <c r="BQ13">
+        <v>6</v>
+      </c>
+      <c r="BR13">
+        <v>28</v>
+      </c>
+      <c r="BS13">
+        <v>7.6</v>
+      </c>
+      <c r="BT13">
+        <v>20</v>
+      </c>
+      <c r="BU13">
+        <v>6.8</v>
+      </c>
+      <c r="BV13">
+        <v>160</v>
+      </c>
+      <c r="BW13">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BX13">
+        <v>130</v>
+      </c>
+      <c r="BY13">
+        <v>9.6</v>
+      </c>
+      <c r="BZ13">
+        <v>0</v>
+      </c>
+      <c r="CA13">
+        <v>0</v>
+      </c>
+      <c r="CB13" t="s">
+        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-24.xlsx
@@ -364,7 +364,7 @@
     <t>Wales</t>
   </si>
   <si>
-    <t>2026-09-22 13:07:11</t>
+    <t>2026-09-22 15:17:44</t>
   </si>
 </sst>
 </file>
@@ -976,7 +976,7 @@
         <v>4</v>
       </c>
       <c r="L2">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="M2">
         <v>1.08</v>
@@ -988,7 +988,7 @@
         <v>1.38</v>
       </c>
       <c r="P2">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="Q2">
         <v>2.12</v>
@@ -1000,10 +1000,10 @@
         <v>3.95</v>
       </c>
       <c r="T2">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U2">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="V2">
         <v>1.18</v>
@@ -1203,19 +1203,19 @@
         <v>1.92</v>
       </c>
       <c r="G3">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="H3">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I3">
         <v>4.3</v>
       </c>
       <c r="J3">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K3">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L3">
         <v>1.31</v>
@@ -1233,10 +1233,10 @@
         <v>2.52</v>
       </c>
       <c r="Q3">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="R3">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="S3">
         <v>2.56</v>
@@ -1245,7 +1245,7 @@
         <v>1.6</v>
       </c>
       <c r="U3">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="V3">
         <v>1.3</v>
@@ -1254,7 +1254,7 @@
         <v>2.04</v>
       </c>
       <c r="X3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Y3">
         <v>21</v>
@@ -1269,19 +1269,19 @@
         <v>13</v>
       </c>
       <c r="AC3">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD3">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE3">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AF3">
         <v>14.5</v>
       </c>
       <c r="AG3">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH3">
         <v>16</v>
@@ -1305,7 +1305,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AO3">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AP3">
         <v>20</v>
@@ -1338,7 +1338,7 @@
         <v>9.6</v>
       </c>
       <c r="AZ3">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA3">
         <v>36</v>
@@ -1350,7 +1350,7 @@
         <v>16</v>
       </c>
       <c r="BD3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BE3">
         <v>50</v>
@@ -1359,7 +1359,7 @@
         <v>8.6</v>
       </c>
       <c r="BG3">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="BH3">
         <v>4.3</v>
@@ -1451,10 +1451,10 @@
         <v>3.25</v>
       </c>
       <c r="I4">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J4">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="K4">
         <v>5.4</v>
@@ -1466,7 +1466,7 @@
         <v>1.01</v>
       </c>
       <c r="N4">
-        <v>3.45</v>
+        <v>4.4</v>
       </c>
       <c r="O4">
         <v>1.17</v>
@@ -1699,7 +1699,7 @@
         <v>1.1</v>
       </c>
       <c r="K5">
-        <v>920</v>
+        <v>950</v>
       </c>
       <c r="L5">
         <v>1.01</v>
@@ -1708,22 +1708,22 @@
         <v>1.01</v>
       </c>
       <c r="N5">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="O5">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="P5">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Q5">
-        <v>1.16</v>
+        <v>1.62</v>
       </c>
       <c r="R5">
         <v>1.08</v>
       </c>
       <c r="S5">
-        <v>1.16</v>
+        <v>1.87</v>
       </c>
       <c r="T5">
         <v>1.01</v>
@@ -1732,10 +1732,10 @@
         <v>1.01</v>
       </c>
       <c r="V5">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W5">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X5">
         <v>1000</v>
@@ -1792,52 +1792,52 @@
         <v>1000</v>
       </c>
       <c r="AP5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF5">
         <v>1.01</v>
@@ -1926,16 +1926,16 @@
         <v>108</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="G6">
         <v>4.1</v>
       </c>
       <c r="H6">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="I6">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="J6">
         <v>2.88</v>
@@ -1944,46 +1944,46 @@
         <v>2.9</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="P6">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="Q6">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="T6">
         <v>2.48</v>
       </c>
       <c r="U6">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X6">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="Y6">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="Z6">
         <v>13</v>
@@ -1992,7 +1992,7 @@
         <v>42</v>
       </c>
       <c r="AB6">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC6">
         <v>7</v>
@@ -2004,7 +2004,7 @@
         <v>48</v>
       </c>
       <c r="AF6">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG6">
         <v>21</v>
@@ -2013,7 +2013,7 @@
         <v>34</v>
       </c>
       <c r="AI6">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AJ6">
         <v>110</v>
@@ -2025,7 +2025,7 @@
         <v>140</v>
       </c>
       <c r="AM6">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="AN6">
         <v>160</v>
@@ -2034,16 +2034,16 @@
         <v>55</v>
       </c>
       <c r="AP6">
+        <v>6.2</v>
+      </c>
+      <c r="AQ6">
         <v>6</v>
       </c>
-      <c r="AQ6">
-        <v>5.9</v>
-      </c>
       <c r="AR6">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AS6">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AT6">
         <v>8.4</v>
@@ -2055,97 +2055,97 @@
         <v>13</v>
       </c>
       <c r="AW6">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AX6">
         <v>20</v>
       </c>
       <c r="AY6">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AZ6">
         <v>28</v>
       </c>
       <c r="BA6">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="BB6">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="BC6">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="BD6">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="BE6">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BF6">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG6">
         <v>42</v>
       </c>
       <c r="BH6">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="BI6">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BJ6">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BK6">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="BL6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM6">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN6">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BO6">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BP6">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="BQ6">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BR6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS6">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BT6">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BU6">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BV6">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BW6">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BX6">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="BY6">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BZ6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA6">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="CB6" t="s">
         <v>116</v>
@@ -2168,22 +2168,22 @@
         <v>109</v>
       </c>
       <c r="F7">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="G7">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="H7">
         <v>1.33</v>
       </c>
       <c r="I7">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="J7">
         <v>5.4</v>
       </c>
       <c r="K7">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -2198,10 +2198,10 @@
         <v>0</v>
       </c>
       <c r="P7">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q7">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -2210,7 +2210,7 @@
         <v>0</v>
       </c>
       <c r="T7">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="U7">
         <v>1.47</v>
@@ -2267,7 +2267,7 @@
         <v>420</v>
       </c>
       <c r="AM7">
-        <v>570</v>
+        <v>1000</v>
       </c>
       <c r="AN7">
         <v>1000</v>
@@ -2279,7 +2279,7 @@
         <v>11</v>
       </c>
       <c r="AQ7">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AR7">
         <v>5.6</v>
@@ -2303,13 +2303,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AY7">
+        <v>8.6</v>
+      </c>
+      <c r="AZ7">
+        <v>8.6</v>
+      </c>
+      <c r="BA7">
         <v>8.800000000000001</v>
-      </c>
-      <c r="AZ7">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BA7">
-        <v>9</v>
       </c>
       <c r="BB7">
         <v>9</v>
@@ -2324,7 +2324,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BF7">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG7">
         <v>7</v>
@@ -2410,13 +2410,13 @@
         <v>110</v>
       </c>
       <c r="F8">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="G8">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="H8">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="I8">
         <v>2.86</v>
@@ -2434,7 +2434,7 @@
         <v>1.04</v>
       </c>
       <c r="N8">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="O8">
         <v>1.19</v>
@@ -2473,7 +2473,7 @@
         <v>24</v>
       </c>
       <c r="AA8">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AB8">
         <v>17</v>
@@ -2539,7 +2539,7 @@
         <v>11.5</v>
       </c>
       <c r="AW8">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AX8">
         <v>17.5</v>
@@ -2569,7 +2569,7 @@
         <v>11.5</v>
       </c>
       <c r="BG8">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BH8">
         <v>4.4</v>
@@ -2652,10 +2652,10 @@
         <v>111</v>
       </c>
       <c r="F9">
+        <v>1.47</v>
+      </c>
+      <c r="G9">
         <v>1.48</v>
-      </c>
-      <c r="G9">
-        <v>1.49</v>
       </c>
       <c r="H9">
         <v>7.6</v>
@@ -2664,10 +2664,10 @@
         <v>7.8</v>
       </c>
       <c r="J9">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="K9">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -2685,13 +2685,13 @@
         <v>2.74</v>
       </c>
       <c r="Q9">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="R9">
         <v>1.67</v>
       </c>
       <c r="S9">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="T9">
         <v>1.74</v>
@@ -2730,7 +2730,7 @@
         <v>120</v>
       </c>
       <c r="AF9">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG9">
         <v>10.5</v>
@@ -2763,13 +2763,13 @@
         <v>11</v>
       </c>
       <c r="AQ9">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AR9">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AS9">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AT9">
         <v>10</v>
@@ -2781,19 +2781,19 @@
         <v>20</v>
       </c>
       <c r="AW9">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AX9">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY9">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ9">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA9">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BB9">
         <v>11.5</v>
@@ -2802,16 +2802,16 @@
         <v>12</v>
       </c>
       <c r="BD9">
-        <v>20</v>
+        <v>5.7</v>
       </c>
       <c r="BE9">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF9">
         <v>4.6</v>
       </c>
       <c r="BG9">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BH9">
         <v>4.7</v>
@@ -2900,7 +2900,7 @@
         <v>1.82</v>
       </c>
       <c r="H10">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I10">
         <v>4.7</v>
@@ -2924,19 +2924,19 @@
         <v>1.26</v>
       </c>
       <c r="P10">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q10">
+        <v>1.76</v>
+      </c>
+      <c r="R10">
+        <v>1.49</v>
+      </c>
+      <c r="S10">
+        <v>2.92</v>
+      </c>
+      <c r="T10">
         <v>1.77</v>
-      </c>
-      <c r="R10">
-        <v>1.47</v>
-      </c>
-      <c r="S10">
-        <v>2.88</v>
-      </c>
-      <c r="T10">
-        <v>1.76</v>
       </c>
       <c r="U10">
         <v>2.24</v>
@@ -2951,10 +2951,10 @@
         <v>19</v>
       </c>
       <c r="Y10">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Z10">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA10">
         <v>120</v>
@@ -2981,19 +2981,19 @@
         <v>19</v>
       </c>
       <c r="AI10">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ10">
         <v>19.5</v>
       </c>
       <c r="AK10">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AL10">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM10">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AN10">
         <v>9.800000000000001</v>
@@ -3008,10 +3008,10 @@
         <v>16</v>
       </c>
       <c r="AR10">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AS10">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AT10">
         <v>9.199999999999999</v>
@@ -3035,7 +3035,7 @@
         <v>16</v>
       </c>
       <c r="BA10">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="BB10">
         <v>17</v>
@@ -3044,19 +3044,19 @@
         <v>15.5</v>
       </c>
       <c r="BD10">
-        <v>23</v>
+        <v>9.4</v>
       </c>
       <c r="BE10">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BF10">
         <v>8.4</v>
       </c>
       <c r="BG10">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH10">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BI10">
         <v>3.45</v>
@@ -3071,7 +3071,7 @@
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN10">
         <v>4.6</v>
@@ -3089,7 +3089,7 @@
         <v>25</v>
       </c>
       <c r="BS10">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BT10">
         <v>8.199999999999999</v>
@@ -3101,19 +3101,19 @@
         <v>40</v>
       </c>
       <c r="BW10">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BX10">
         <v>46</v>
       </c>
       <c r="BY10">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BZ10">
         <v>19</v>
       </c>
       <c r="CA10">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="CB10" t="s">
         <v>116</v>
@@ -3136,13 +3136,13 @@
         <v>113</v>
       </c>
       <c r="F11">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="G11">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="H11">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="I11">
         <v>3.35</v>
@@ -3157,7 +3157,7 @@
         <v>0</v>
       </c>
       <c r="M11">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N11">
         <v>2.94</v>
@@ -3169,13 +3169,13 @@
         <v>1.65</v>
       </c>
       <c r="Q11">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R11">
         <v>1.24</v>
       </c>
       <c r="S11">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T11">
         <v>2.02</v>
@@ -3208,7 +3208,7 @@
         <v>7.6</v>
       </c>
       <c r="AD11">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AE11">
         <v>60</v>
@@ -3229,7 +3229,7 @@
         <v>36</v>
       </c>
       <c r="AK11">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AL11">
         <v>70</v>
@@ -3256,7 +3256,7 @@
         <v>42</v>
       </c>
       <c r="AT11">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AU11">
         <v>6.8</v>
@@ -3265,7 +3265,7 @@
         <v>13</v>
       </c>
       <c r="AW11">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AX11">
         <v>13</v>
@@ -3277,7 +3277,7 @@
         <v>17</v>
       </c>
       <c r="BA11">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB11">
         <v>30</v>
@@ -3286,7 +3286,7 @@
         <v>7.4</v>
       </c>
       <c r="BD11">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BE11">
         <v>9.199999999999999</v>
@@ -3295,7 +3295,7 @@
         <v>7.4</v>
       </c>
       <c r="BG11">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BH11">
         <v>2.88</v>
@@ -3331,7 +3331,7 @@
         <v>1000</v>
       </c>
       <c r="BS11">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BT11">
         <v>6.4</v>
@@ -3355,7 +3355,7 @@
         <v>1000</v>
       </c>
       <c r="CA11">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="CB11" t="s">
         <v>116</v>
@@ -3381,13 +3381,13 @@
         <v>2.72</v>
       </c>
       <c r="G12">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="H12">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="I12">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="J12">
         <v>3.4</v>
@@ -3408,16 +3408,16 @@
         <v>1.4</v>
       </c>
       <c r="P12">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="Q12">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="R12">
         <v>1.3</v>
       </c>
       <c r="S12">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T12">
         <v>1.9</v>
@@ -3450,7 +3450,7 @@
         <v>7.6</v>
       </c>
       <c r="AD12">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE12">
         <v>40</v>
@@ -3486,7 +3486,7 @@
         <v>38</v>
       </c>
       <c r="AP12">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AQ12">
         <v>9.199999999999999</v>
@@ -3501,7 +3501,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AU12">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AV12">
         <v>11.5</v>
@@ -3531,7 +3531,7 @@
         <v>36</v>
       </c>
       <c r="BE12">
-        <v>9.6</v>
+        <v>34</v>
       </c>
       <c r="BF12">
         <v>24</v>
@@ -3620,10 +3620,10 @@
         <v>115</v>
       </c>
       <c r="F13">
+        <v>1.24</v>
+      </c>
+      <c r="G13">
         <v>1.25</v>
-      </c>
-      <c r="G13">
-        <v>1.26</v>
       </c>
       <c r="H13">
         <v>17</v>
@@ -3644,28 +3644,28 @@
         <v>1.04</v>
       </c>
       <c r="N13">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="O13">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P13">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="Q13">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="R13">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="S13">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="T13">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="U13">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="V13">
         <v>0</v>
@@ -3695,7 +3695,7 @@
         <v>60</v>
       </c>
       <c r="AE13">
-        <v>320</v>
+        <v>360</v>
       </c>
       <c r="AF13">
         <v>8.199999999999999</v>
@@ -3722,22 +3722,22 @@
         <v>240</v>
       </c>
       <c r="AN13">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AO13">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="AP13">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AQ13">
-        <v>12.5</v>
+        <v>38</v>
       </c>
       <c r="AR13">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AS13">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AT13">
         <v>9.4</v>
@@ -3746,40 +3746,40 @@
         <v>14.5</v>
       </c>
       <c r="AV13">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AW13">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AX13">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AY13">
         <v>10.5</v>
       </c>
       <c r="AZ13">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BA13">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BB13">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC13">
         <v>13</v>
       </c>
       <c r="BD13">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BE13">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BF13">
         <v>3.65</v>
       </c>
       <c r="BG13">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BH13">
         <v>4.4</v>
@@ -3797,7 +3797,7 @@
         <v>210</v>
       </c>
       <c r="BM13">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN13">
         <v>3.7</v>
@@ -3812,7 +3812,7 @@
         <v>6</v>
       </c>
       <c r="BR13">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BS13">
         <v>7.6</v>
@@ -3833,7 +3833,7 @@
         <v>130</v>
       </c>
       <c r="BY13">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ13">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-24.xlsx
@@ -364,7 +364,7 @@
     <t>Wales</t>
   </si>
   <si>
-    <t>2026-09-22 15:17:44</t>
+    <t>2026-09-22 17:29:27</t>
   </si>
 </sst>
 </file>
@@ -988,7 +988,7 @@
         <v>1.38</v>
       </c>
       <c r="P2">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="Q2">
         <v>2.12</v>
@@ -1048,7 +1048,7 @@
         <v>130</v>
       </c>
       <c r="AJ2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK2">
         <v>29</v>
@@ -1060,7 +1060,7 @@
         <v>190</v>
       </c>
       <c r="AN2">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AO2">
         <v>180</v>
@@ -1102,7 +1102,7 @@
         <v>6.8</v>
       </c>
       <c r="BB2">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BC2">
         <v>17</v>
@@ -1120,7 +1120,7 @@
         <v>6.8</v>
       </c>
       <c r="BH2">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="BI2">
         <v>2.58</v>
@@ -1129,7 +1129,7 @@
         <v>13.5</v>
       </c>
       <c r="BK2">
-        <v>4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL2">
         <v>1000</v>
@@ -1147,7 +1147,7 @@
         <v>14.5</v>
       </c>
       <c r="BQ2">
-        <v>4.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR2">
         <v>38</v>
@@ -1159,7 +1159,7 @@
         <v>11.5</v>
       </c>
       <c r="BU2">
-        <v>3.85</v>
+        <v>7</v>
       </c>
       <c r="BV2">
         <v>85</v>
@@ -1200,13 +1200,13 @@
         <v>105</v>
       </c>
       <c r="F3">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="G3">
         <v>1.96</v>
       </c>
       <c r="H3">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I3">
         <v>4.3</v>
@@ -1224,28 +1224,28 @@
         <v>1.04</v>
       </c>
       <c r="N3">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="O3">
         <v>1.21</v>
       </c>
       <c r="P3">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="Q3">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="R3">
         <v>1.6</v>
       </c>
       <c r="S3">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="T3">
         <v>1.6</v>
       </c>
       <c r="U3">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="V3">
         <v>1.3</v>
@@ -1254,13 +1254,13 @@
         <v>2.04</v>
       </c>
       <c r="X3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y3">
         <v>21</v>
       </c>
       <c r="Z3">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AA3">
         <v>1000</v>
@@ -1272,10 +1272,10 @@
         <v>9.6</v>
       </c>
       <c r="AD3">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AE3">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF3">
         <v>14.5</v>
@@ -1302,10 +1302,10 @@
         <v>65</v>
       </c>
       <c r="AN3">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AO3">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AP3">
         <v>20</v>
@@ -1323,7 +1323,7 @@
         <v>11.5</v>
       </c>
       <c r="AU3">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AV3">
         <v>15</v>
@@ -1350,7 +1350,7 @@
         <v>16</v>
       </c>
       <c r="BD3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BE3">
         <v>50</v>
@@ -1359,7 +1359,7 @@
         <v>8.6</v>
       </c>
       <c r="BG3">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="BH3">
         <v>4.3</v>
@@ -1371,13 +1371,13 @@
         <v>9</v>
       </c>
       <c r="BK3">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BL3">
         <v>100</v>
       </c>
       <c r="BM3">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN3">
         <v>5</v>
@@ -1407,16 +1407,16 @@
         <v>36</v>
       </c>
       <c r="BW3">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BX3">
         <v>40</v>
       </c>
       <c r="BY3">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BZ3">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="CA3">
         <v>6.8</v>
@@ -1448,16 +1448,16 @@
         <v>2.04</v>
       </c>
       <c r="H4">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="I4">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J4">
         <v>4.2</v>
       </c>
       <c r="K4">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="L4">
         <v>1.22</v>
@@ -1466,22 +1466,22 @@
         <v>1.01</v>
       </c>
       <c r="N4">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="O4">
         <v>1.17</v>
       </c>
       <c r="P4">
-        <v>2.34</v>
+        <v>2.6</v>
       </c>
       <c r="Q4">
         <v>1.52</v>
       </c>
       <c r="R4">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="S4">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="T4">
         <v>1.45</v>
@@ -1490,10 +1490,10 @@
         <v>2.3</v>
       </c>
       <c r="V4">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W4">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="X4">
         <v>34</v>
@@ -1550,10 +1550,10 @@
         <v>32</v>
       </c>
       <c r="AP4">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="AQ4">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="AR4">
         <v>1.03</v>
@@ -1562,37 +1562,37 @@
         <v>1.03</v>
       </c>
       <c r="AT4">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AU4">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AV4">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AW4">
         <v>1.03</v>
       </c>
       <c r="AX4">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AY4">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ4">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="BA4">
         <v>1.03</v>
       </c>
       <c r="BB4">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="BC4">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="BD4">
-        <v>1.03</v>
+        <v>18.5</v>
       </c>
       <c r="BE4">
         <v>1.03</v>
@@ -1619,7 +1619,7 @@
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BN4">
         <v>6.2</v>
@@ -1687,16 +1687,16 @@
         <v>1.1</v>
       </c>
       <c r="G5">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H5">
         <v>1.1</v>
       </c>
       <c r="I5">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J5">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="K5">
         <v>950</v>
@@ -1711,19 +1711,19 @@
         <v>1.13</v>
       </c>
       <c r="O5">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="P5">
         <v>1.13</v>
       </c>
       <c r="Q5">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="R5">
         <v>1.08</v>
       </c>
       <c r="S5">
-        <v>1.87</v>
+        <v>1.25</v>
       </c>
       <c r="T5">
         <v>1.01</v>
@@ -1732,10 +1732,10 @@
         <v>1.01</v>
       </c>
       <c r="V5">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W5">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X5">
         <v>1000</v>
@@ -1926,16 +1926,16 @@
         <v>108</v>
       </c>
       <c r="F6">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="G6">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="H6">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="I6">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="J6">
         <v>2.88</v>
@@ -1944,19 +1944,19 @@
         <v>2.9</v>
       </c>
       <c r="L6">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="M6">
         <v>1.17</v>
       </c>
       <c r="N6">
-        <v>2.24</v>
+        <v>2.14</v>
       </c>
       <c r="O6">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="P6">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="Q6">
         <v>3.45</v>
@@ -1968,16 +1968,16 @@
         <v>8</v>
       </c>
       <c r="T6">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="U6">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="V6">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="W6">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="X6">
         <v>6.6</v>
@@ -1992,13 +1992,13 @@
         <v>42</v>
       </c>
       <c r="AB6">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC6">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AD6">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AE6">
         <v>48</v>
@@ -2007,10 +2007,10 @@
         <v>24</v>
       </c>
       <c r="AG6">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH6">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AI6">
         <v>100</v>
@@ -2025,10 +2025,10 @@
         <v>140</v>
       </c>
       <c r="AM6">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="AN6">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AO6">
         <v>55</v>
@@ -2040,13 +2040,13 @@
         <v>6</v>
       </c>
       <c r="AR6">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AS6">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="AT6">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU6">
         <v>6.6</v>
@@ -2055,49 +2055,49 @@
         <v>13</v>
       </c>
       <c r="AW6">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AX6">
         <v>20</v>
       </c>
       <c r="AY6">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AZ6">
         <v>28</v>
       </c>
       <c r="BA6">
+        <v>14.5</v>
+      </c>
+      <c r="BB6">
+        <v>14.5</v>
+      </c>
+      <c r="BC6">
+        <v>15</v>
+      </c>
+      <c r="BD6">
+        <v>14</v>
+      </c>
+      <c r="BE6">
         <v>13</v>
       </c>
-      <c r="BB6">
-        <v>13</v>
-      </c>
-      <c r="BC6">
-        <v>13</v>
-      </c>
-      <c r="BD6">
-        <v>13.5</v>
-      </c>
-      <c r="BE6">
-        <v>12</v>
-      </c>
       <c r="BF6">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BG6">
         <v>42</v>
       </c>
       <c r="BH6">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="BI6">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="BJ6">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BK6">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BL6">
         <v>1000</v>
@@ -2106,16 +2106,16 @@
         <v>21</v>
       </c>
       <c r="BN6">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BO6">
         <v>6</v>
       </c>
       <c r="BP6">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="BQ6">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BR6">
         <v>1000</v>
@@ -2124,22 +2124,22 @@
         <v>21</v>
       </c>
       <c r="BT6">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BU6">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BV6">
         <v>25</v>
       </c>
       <c r="BW6">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BX6">
         <v>60</v>
       </c>
       <c r="BY6">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BZ6">
         <v>1000</v>
@@ -2168,7 +2168,7 @@
         <v>109</v>
       </c>
       <c r="F7">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="G7">
         <v>16.5</v>
@@ -2183,91 +2183,91 @@
         <v>5.4</v>
       </c>
       <c r="K7">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="P7">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q7">
         <v>2.2</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="T7">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="U7">
         <v>1.47</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X7">
         <v>12.5</v>
       </c>
       <c r="Y7">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="Z7">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AA7">
-        <v>12</v>
+        <v>9.6</v>
       </c>
       <c r="AB7">
         <v>34</v>
       </c>
       <c r="AC7">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AD7">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE7">
         <v>19</v>
       </c>
       <c r="AF7">
-        <v>210</v>
+        <v>170</v>
       </c>
       <c r="AG7">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="AH7">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AI7">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AJ7">
         <v>1000</v>
       </c>
       <c r="AK7">
-        <v>1000</v>
+        <v>550</v>
       </c>
       <c r="AL7">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="AM7">
-        <v>1000</v>
+        <v>560</v>
       </c>
       <c r="AN7">
         <v>1000</v>
@@ -2276,10 +2276,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AP7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ7">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AR7">
         <v>5.6</v>
@@ -2288,106 +2288,106 @@
         <v>8.6</v>
       </c>
       <c r="AT7">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AU7">
         <v>11.5</v>
       </c>
       <c r="AV7">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW7">
         <v>17</v>
       </c>
       <c r="AX7">
-        <v>8.800000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="AY7">
-        <v>8.6</v>
+        <v>50</v>
       </c>
       <c r="AZ7">
-        <v>8.6</v>
+        <v>44</v>
       </c>
       <c r="BA7">
-        <v>8.800000000000001</v>
+        <v>60</v>
       </c>
       <c r="BB7">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BC7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD7">
-        <v>9</v>
+        <v>14.5</v>
       </c>
       <c r="BE7">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF7">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BG7">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BH7">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BI7">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="BJ7">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BK7">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BL7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM7">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN7">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BO7">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BP7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BR7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS7">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BT7">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BU7">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="BV7">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BW7">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BX7">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BY7">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BZ7">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="CA7">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="CB7" t="s">
         <v>116</v>
@@ -2410,7 +2410,7 @@
         <v>110</v>
       </c>
       <c r="F8">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="G8">
         <v>2.56</v>
@@ -2419,7 +2419,7 @@
         <v>2.82</v>
       </c>
       <c r="I8">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="J8">
         <v>3.9</v>
@@ -2428,148 +2428,148 @@
         <v>4</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="M8">
         <v>1.04</v>
       </c>
       <c r="N8">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="O8">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P8">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="Q8">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="R8">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="S8">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="T8">
         <v>1.52</v>
       </c>
       <c r="U8">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="X8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Y8">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Z8">
         <v>24</v>
       </c>
       <c r="AA8">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AB8">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AC8">
         <v>9.6</v>
       </c>
       <c r="AD8">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE8">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF8">
         <v>21</v>
       </c>
       <c r="AG8">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH8">
         <v>14.5</v>
       </c>
       <c r="AI8">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ8">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AK8">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL8">
         <v>30</v>
       </c>
       <c r="AM8">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="AN8">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AO8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP8">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AQ8">
         <v>16</v>
       </c>
       <c r="AR8">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AS8">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AT8">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AU8">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV8">
         <v>11.5</v>
       </c>
       <c r="AW8">
-        <v>8.6</v>
+        <v>12</v>
       </c>
       <c r="AX8">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AY8">
         <v>11.5</v>
       </c>
       <c r="AZ8">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BA8">
+        <v>27</v>
+      </c>
+      <c r="BB8">
+        <v>34</v>
+      </c>
+      <c r="BC8">
         <v>21</v>
       </c>
-      <c r="BB8">
-        <v>18</v>
-      </c>
-      <c r="BC8">
-        <v>20</v>
-      </c>
       <c r="BD8">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BE8">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="BF8">
         <v>11.5</v>
       </c>
       <c r="BG8">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BH8">
         <v>4.4</v>
@@ -2652,16 +2652,16 @@
         <v>111</v>
       </c>
       <c r="F9">
+        <v>1.46</v>
+      </c>
+      <c r="G9">
         <v>1.47</v>
       </c>
-      <c r="G9">
-        <v>1.48</v>
-      </c>
       <c r="H9">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="I9">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="J9">
         <v>5.1</v>
@@ -2670,7 +2670,7 @@
         <v>5.3</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M9">
         <v>1.03</v>
@@ -2679,10 +2679,10 @@
         <v>6</v>
       </c>
       <c r="O9">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P9">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="Q9">
         <v>1.56</v>
@@ -2700,118 +2700,118 @@
         <v>2.18</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="X9">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="Y9">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Z9">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AA9">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="AB9">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC9">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AD9">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AE9">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AF9">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG9">
         <v>10.5</v>
       </c>
       <c r="AH9">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="AI9">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AJ9">
         <v>13.5</v>
       </c>
       <c r="AK9">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="AL9">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AM9">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AN9">
         <v>6</v>
       </c>
       <c r="AO9">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="AP9">
         <v>11</v>
       </c>
       <c r="AQ9">
-        <v>5.6</v>
+        <v>30</v>
       </c>
       <c r="AR9">
-        <v>6.2</v>
+        <v>60</v>
       </c>
       <c r="AS9">
-        <v>6.6</v>
+        <v>10</v>
       </c>
       <c r="AT9">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU9">
+        <v>11</v>
+      </c>
+      <c r="AV9">
+        <v>25</v>
+      </c>
+      <c r="AW9">
         <v>10.5</v>
-      </c>
-      <c r="AV9">
-        <v>20</v>
-      </c>
-      <c r="AW9">
-        <v>6.4</v>
       </c>
       <c r="AX9">
         <v>9.199999999999999</v>
       </c>
       <c r="AY9">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ9">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BA9">
-        <v>6.2</v>
+        <v>65</v>
       </c>
       <c r="BB9">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BC9">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BD9">
-        <v>5.7</v>
+        <v>8.4</v>
       </c>
       <c r="BE9">
-        <v>6.2</v>
+        <v>10.5</v>
       </c>
       <c r="BF9">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BG9">
-        <v>6.2</v>
+        <v>60</v>
       </c>
       <c r="BH9">
         <v>4.7</v>
@@ -2847,7 +2847,7 @@
         <v>24</v>
       </c>
       <c r="BS9">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BT9">
         <v>13.5</v>
@@ -2871,7 +2871,7 @@
         <v>14</v>
       </c>
       <c r="CA9">
-        <v>4.8</v>
+        <v>8.4</v>
       </c>
       <c r="CB9" t="s">
         <v>116</v>
@@ -2894,16 +2894,16 @@
         <v>112</v>
       </c>
       <c r="F10">
+        <v>1.79</v>
+      </c>
+      <c r="G10">
         <v>1.8</v>
       </c>
-      <c r="G10">
-        <v>1.82</v>
-      </c>
       <c r="H10">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I10">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J10">
         <v>4.2</v>
@@ -2912,61 +2912,61 @@
         <v>4.3</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M10">
         <v>1.05</v>
       </c>
       <c r="N10">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O10">
+        <v>1.27</v>
+      </c>
+      <c r="P10">
+        <v>2.2</v>
+      </c>
+      <c r="Q10">
+        <v>1.8</v>
+      </c>
+      <c r="R10">
+        <v>1.47</v>
+      </c>
+      <c r="S10">
+        <v>2.98</v>
+      </c>
+      <c r="T10">
+        <v>1.8</v>
+      </c>
+      <c r="U10">
+        <v>2.16</v>
+      </c>
+      <c r="V10">
         <v>1.26</v>
       </c>
-      <c r="P10">
-        <v>2.22</v>
-      </c>
-      <c r="Q10">
-        <v>1.76</v>
-      </c>
-      <c r="R10">
-        <v>1.49</v>
-      </c>
-      <c r="S10">
-        <v>2.92</v>
-      </c>
-      <c r="T10">
-        <v>1.77</v>
-      </c>
-      <c r="U10">
+      <c r="W10">
         <v>2.24</v>
       </c>
-      <c r="V10">
-        <v>0</v>
-      </c>
-      <c r="W10">
-        <v>0</v>
-      </c>
       <c r="X10">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Y10">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Z10">
         <v>38</v>
       </c>
       <c r="AA10">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AB10">
         <v>10.5</v>
       </c>
       <c r="AC10">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD10">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE10">
         <v>60</v>
@@ -2975,22 +2975,22 @@
         <v>12</v>
       </c>
       <c r="AG10">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH10">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AI10">
         <v>60</v>
       </c>
       <c r="AJ10">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AK10">
         <v>18</v>
       </c>
       <c r="AL10">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AM10">
         <v>90</v>
@@ -2999,79 +2999,79 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AO10">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AP10">
         <v>16.5</v>
       </c>
       <c r="AQ10">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR10">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="AS10">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AT10">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AU10">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AV10">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW10">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AX10">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY10">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ10">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BA10">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="BB10">
+        <v>17.5</v>
+      </c>
+      <c r="BC10">
         <v>17</v>
       </c>
-      <c r="BC10">
-        <v>15.5</v>
-      </c>
       <c r="BD10">
-        <v>9.4</v>
+        <v>29</v>
       </c>
       <c r="BE10">
-        <v>11.5</v>
+        <v>70</v>
       </c>
       <c r="BF10">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BG10">
-        <v>10.5</v>
+        <v>46</v>
       </c>
       <c r="BH10">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BI10">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="BJ10">
         <v>9.6</v>
       </c>
       <c r="BK10">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BN10">
         <v>4.6</v>
@@ -3083,13 +3083,13 @@
         <v>12</v>
       </c>
       <c r="BQ10">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BR10">
         <v>25</v>
       </c>
       <c r="BS10">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT10">
         <v>8.199999999999999</v>
@@ -3101,19 +3101,19 @@
         <v>40</v>
       </c>
       <c r="BW10">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BX10">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BY10">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BZ10">
         <v>19</v>
       </c>
       <c r="CA10">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB10" t="s">
         <v>116</v>
@@ -3136,13 +3136,13 @@
         <v>113</v>
       </c>
       <c r="F11">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="G11">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="H11">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I11">
         <v>3.35</v>
@@ -3154,73 +3154,73 @@
         <v>3.3</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="M11">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N11">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="O11">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P11">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="Q11">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="R11">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S11">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="T11">
         <v>2.02</v>
       </c>
       <c r="U11">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="X11">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="Y11">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Z11">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA11">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AB11">
         <v>8.6</v>
       </c>
       <c r="AC11">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD11">
         <v>15.5</v>
       </c>
       <c r="AE11">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AF11">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AG11">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH11">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AI11">
         <v>75</v>
@@ -3232,40 +3232,40 @@
         <v>34</v>
       </c>
       <c r="AL11">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AM11">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="AN11">
         <v>34</v>
       </c>
       <c r="AO11">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AP11">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ11">
         <v>9.6</v>
       </c>
-      <c r="AQ11">
-        <v>9</v>
-      </c>
       <c r="AR11">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AS11">
         <v>42</v>
       </c>
       <c r="AT11">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU11">
         <v>6.8</v>
       </c>
       <c r="AV11">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AW11">
-        <v>8.4</v>
+        <v>40</v>
       </c>
       <c r="AX11">
         <v>13</v>
@@ -3274,46 +3274,46 @@
         <v>11</v>
       </c>
       <c r="AZ11">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BA11">
-        <v>8.6</v>
+        <v>55</v>
       </c>
       <c r="BB11">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BC11">
-        <v>7.4</v>
+        <v>28</v>
       </c>
       <c r="BD11">
-        <v>8.6</v>
+        <v>48</v>
       </c>
       <c r="BE11">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BF11">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="BG11">
-        <v>8.4</v>
+        <v>44</v>
       </c>
       <c r="BH11">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="BI11">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="BJ11">
         <v>10.5</v>
       </c>
       <c r="BK11">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BN11">
         <v>5.3</v>
@@ -3322,16 +3322,16 @@
         <v>4.7</v>
       </c>
       <c r="BP11">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BQ11">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR11">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS11">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BT11">
         <v>6.4</v>
@@ -3340,10 +3340,10 @@
         <v>5.6</v>
       </c>
       <c r="BV11">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BW11">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX11">
         <v>1000</v>
@@ -3355,7 +3355,7 @@
         <v>1000</v>
       </c>
       <c r="CA11">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="CB11" t="s">
         <v>116</v>
@@ -3387,7 +3387,7 @@
         <v>2.88</v>
       </c>
       <c r="I12">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="J12">
         <v>3.4</v>
@@ -3396,7 +3396,7 @@
         <v>3.45</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M12">
         <v>1.09</v>
@@ -3405,13 +3405,13 @@
         <v>3.3</v>
       </c>
       <c r="O12">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P12">
         <v>1.77</v>
       </c>
       <c r="Q12">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="R12">
         <v>1.3</v>
@@ -3420,127 +3420,127 @@
         <v>4.2</v>
       </c>
       <c r="T12">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="U12">
         <v>2.02</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="X12">
         <v>12</v>
       </c>
       <c r="Y12">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z12">
         <v>18.5</v>
       </c>
       <c r="AA12">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AB12">
         <v>10.5</v>
       </c>
       <c r="AC12">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD12">
+        <v>13.5</v>
+      </c>
+      <c r="AE12">
+        <v>36</v>
+      </c>
+      <c r="AF12">
+        <v>17</v>
+      </c>
+      <c r="AG12">
         <v>13</v>
       </c>
-      <c r="AE12">
-        <v>40</v>
-      </c>
-      <c r="AF12">
-        <v>17.5</v>
-      </c>
-      <c r="AG12">
-        <v>13.5</v>
-      </c>
       <c r="AH12">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI12">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ12">
         <v>44</v>
       </c>
       <c r="AK12">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AL12">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AM12">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AN12">
         <v>34</v>
       </c>
       <c r="AO12">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AP12">
         <v>11</v>
       </c>
       <c r="AQ12">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR12">
+        <v>16.5</v>
+      </c>
+      <c r="AS12">
+        <v>42</v>
+      </c>
+      <c r="AT12">
+        <v>9.4</v>
+      </c>
+      <c r="AU12">
+        <v>7</v>
+      </c>
+      <c r="AV12">
+        <v>12</v>
+      </c>
+      <c r="AW12">
+        <v>32</v>
+      </c>
+      <c r="AX12">
         <v>15.5</v>
       </c>
-      <c r="AS12">
-        <v>21</v>
-      </c>
-      <c r="AT12">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU12">
-        <v>6.8</v>
-      </c>
-      <c r="AV12">
-        <v>11.5</v>
-      </c>
-      <c r="AW12">
-        <v>17.5</v>
-      </c>
-      <c r="AX12">
-        <v>14.5</v>
-      </c>
       <c r="AY12">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AZ12">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA12">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="BB12">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BC12">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="BD12">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="BE12">
         <v>34</v>
       </c>
       <c r="BF12">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="BG12">
-        <v>17.5</v>
+        <v>30</v>
       </c>
       <c r="BH12">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BI12">
         <v>2.84</v>
@@ -3549,16 +3549,16 @@
         <v>11.5</v>
       </c>
       <c r="BK12">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN12">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="BO12">
         <v>5.1</v>
@@ -3567,16 +3567,16 @@
         <v>26</v>
       </c>
       <c r="BQ12">
-        <v>5.8</v>
+        <v>7.4</v>
       </c>
       <c r="BR12">
         <v>44</v>
       </c>
       <c r="BS12">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="BT12">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="BU12">
         <v>5.3</v>
@@ -3585,19 +3585,19 @@
         <v>28</v>
       </c>
       <c r="BW12">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="BX12">
         <v>46</v>
       </c>
       <c r="BY12">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="BZ12">
         <v>40</v>
       </c>
       <c r="CA12">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="CB12" t="s">
         <v>116</v>
@@ -3623,10 +3623,10 @@
         <v>1.24</v>
       </c>
       <c r="G13">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="H13">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="I13">
         <v>17.5</v>
@@ -3638,7 +3638,7 @@
         <v>7.2</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="M13">
         <v>1.04</v>
@@ -3659,7 +3659,7 @@
         <v>1.66</v>
       </c>
       <c r="S13">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="T13">
         <v>2.28</v>
@@ -3668,43 +3668,43 @@
         <v>1.73</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="X13">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="Y13">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="Z13">
-        <v>210</v>
+        <v>170</v>
       </c>
       <c r="AA13">
-        <v>1000</v>
+        <v>910</v>
       </c>
       <c r="AB13">
         <v>10.5</v>
       </c>
       <c r="AC13">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AD13">
         <v>60</v>
       </c>
       <c r="AE13">
-        <v>360</v>
+        <v>310</v>
       </c>
       <c r="AF13">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AG13">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH13">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AI13">
         <v>220</v>
@@ -3713,31 +3713,31 @@
         <v>9</v>
       </c>
       <c r="AK13">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AL13">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM13">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="AN13">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AO13">
-        <v>450</v>
+        <v>370</v>
       </c>
       <c r="AP13">
         <v>23</v>
       </c>
       <c r="AQ13">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AR13">
-        <v>13.5</v>
+        <v>19</v>
       </c>
       <c r="AS13">
-        <v>14.5</v>
+        <v>20</v>
       </c>
       <c r="AT13">
         <v>9.4</v>
@@ -3746,52 +3746,52 @@
         <v>14.5</v>
       </c>
       <c r="AV13">
-        <v>12.5</v>
+        <v>48</v>
       </c>
       <c r="AW13">
-        <v>13.5</v>
+        <v>20</v>
       </c>
       <c r="AX13">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AY13">
         <v>10.5</v>
       </c>
       <c r="AZ13">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="BA13">
-        <v>13</v>
+        <v>19.5</v>
       </c>
       <c r="BB13">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BC13">
         <v>13</v>
       </c>
       <c r="BD13">
-        <v>11.5</v>
+        <v>36</v>
       </c>
       <c r="BE13">
-        <v>14</v>
+        <v>19.5</v>
       </c>
       <c r="BF13">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="BG13">
-        <v>13.5</v>
+        <v>19.5</v>
       </c>
       <c r="BH13">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BI13">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BJ13">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BK13">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BL13">
         <v>210</v>
@@ -3803,13 +3803,13 @@
         <v>3.7</v>
       </c>
       <c r="BO13">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BP13">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BQ13">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BR13">
         <v>27</v>
@@ -3818,10 +3818,10 @@
         <v>7.6</v>
       </c>
       <c r="BT13">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BU13">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BV13">
         <v>160</v>
@@ -3833,7 +3833,7 @@
         <v>130</v>
       </c>
       <c r="BY13">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BZ13">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-24.xlsx
@@ -364,7 +364,7 @@
     <t>Wales</t>
   </si>
   <si>
-    <t>2026-09-22 17:29:27</t>
+    <t>2026-09-22 19:40:27</t>
   </si>
 </sst>
 </file>
@@ -967,13 +967,13 @@
         <v>5.9</v>
       </c>
       <c r="I2">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J2">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K2">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L2">
         <v>1.37</v>
@@ -1003,7 +1003,7 @@
         <v>2.06</v>
       </c>
       <c r="U2">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="V2">
         <v>1.18</v>
@@ -1015,25 +1015,25 @@
         <v>13</v>
       </c>
       <c r="Y2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z2">
         <v>60</v>
       </c>
       <c r="AA2">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AB2">
         <v>8.6</v>
       </c>
       <c r="AC2">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD2">
         <v>34</v>
       </c>
       <c r="AE2">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AF2">
         <v>9.6</v>
@@ -1045,13 +1045,13 @@
         <v>34</v>
       </c>
       <c r="AI2">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AJ2">
         <v>22</v>
       </c>
       <c r="AK2">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="AL2">
         <v>55</v>
@@ -1063,7 +1063,7 @@
         <v>15</v>
       </c>
       <c r="AO2">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AP2">
         <v>11</v>
@@ -1072,10 +1072,10 @@
         <v>15.5</v>
       </c>
       <c r="AR2">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AS2">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AT2">
         <v>6.6</v>
@@ -1084,13 +1084,13 @@
         <v>7.8</v>
       </c>
       <c r="AV2">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AW2">
         <v>6.8</v>
       </c>
       <c r="AX2">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AY2">
         <v>9</v>
@@ -1108,7 +1108,7 @@
         <v>17</v>
       </c>
       <c r="BD2">
-        <v>6.4</v>
+        <v>36</v>
       </c>
       <c r="BE2">
         <v>6.8</v>
@@ -1200,13 +1200,13 @@
         <v>105</v>
       </c>
       <c r="F3">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="G3">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="H3">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I3">
         <v>4.3</v>
@@ -1224,13 +1224,13 @@
         <v>1.04</v>
       </c>
       <c r="N3">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O3">
         <v>1.21</v>
       </c>
       <c r="P3">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="Q3">
         <v>1.63</v>
@@ -1239,19 +1239,19 @@
         <v>1.6</v>
       </c>
       <c r="S3">
+        <v>2.56</v>
+      </c>
+      <c r="T3">
+        <v>1.59</v>
+      </c>
+      <c r="U3">
         <v>2.58</v>
-      </c>
-      <c r="T3">
-        <v>1.6</v>
-      </c>
-      <c r="U3">
-        <v>2.56</v>
       </c>
       <c r="V3">
         <v>1.3</v>
       </c>
       <c r="W3">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="X3">
         <v>23</v>
@@ -1260,7 +1260,7 @@
         <v>21</v>
       </c>
       <c r="Z3">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AA3">
         <v>1000</v>
@@ -1272,7 +1272,7 @@
         <v>9.6</v>
       </c>
       <c r="AD3">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE3">
         <v>50</v>
@@ -1305,7 +1305,7 @@
         <v>9.4</v>
       </c>
       <c r="AO3">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AP3">
         <v>20</v>
@@ -1359,7 +1359,7 @@
         <v>8.6</v>
       </c>
       <c r="BG3">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="BH3">
         <v>4.3</v>
@@ -1377,7 +1377,7 @@
         <v>100</v>
       </c>
       <c r="BM3">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BN3">
         <v>5</v>
@@ -1407,16 +1407,16 @@
         <v>36</v>
       </c>
       <c r="BW3">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX3">
         <v>40</v>
       </c>
       <c r="BY3">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ3">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="CA3">
         <v>6.8</v>
@@ -1442,88 +1442,88 @@
         <v>106</v>
       </c>
       <c r="F4">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="G4">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="H4">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="I4">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="J4">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="K4">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L4">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="M4">
+        <v>1.04</v>
+      </c>
+      <c r="N4">
+        <v>4.5</v>
+      </c>
+      <c r="O4">
+        <v>1.18</v>
+      </c>
+      <c r="P4">
+        <v>2.34</v>
+      </c>
+      <c r="Q4">
+        <v>1.58</v>
+      </c>
+      <c r="R4">
+        <v>1.59</v>
+      </c>
+      <c r="S4">
+        <v>2.46</v>
+      </c>
+      <c r="T4">
         <v>1.01</v>
       </c>
-      <c r="N4">
-        <v>5.7</v>
-      </c>
-      <c r="O4">
-        <v>1.17</v>
-      </c>
-      <c r="P4">
-        <v>2.6</v>
-      </c>
-      <c r="Q4">
-        <v>1.52</v>
-      </c>
-      <c r="R4">
-        <v>1.64</v>
-      </c>
-      <c r="S4">
+      <c r="U4">
         <v>2.28</v>
       </c>
-      <c r="T4">
-        <v>1.45</v>
-      </c>
-      <c r="U4">
-        <v>2.3</v>
-      </c>
       <c r="V4">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W4">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="X4">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="Y4">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Z4">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AA4">
         <v>85</v>
       </c>
       <c r="AB4">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AC4">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AD4">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AE4">
         <v>48</v>
       </c>
       <c r="AF4">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AG4">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH4">
         <v>19</v>
@@ -1532,7 +1532,7 @@
         <v>48</v>
       </c>
       <c r="AJ4">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK4">
         <v>22</v>
@@ -1544,16 +1544,16 @@
         <v>70</v>
       </c>
       <c r="AN4">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO4">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AP4">
-        <v>19.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ4">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="AR4">
         <v>1.03</v>
@@ -1562,106 +1562,106 @@
         <v>1.03</v>
       </c>
       <c r="AT4">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AU4">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AV4">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AW4">
         <v>1.03</v>
       </c>
       <c r="AX4">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AY4">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AZ4">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA4">
         <v>1.03</v>
       </c>
       <c r="BB4">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="BC4">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="BD4">
-        <v>18.5</v>
+        <v>1.03</v>
       </c>
       <c r="BE4">
         <v>1.03</v>
       </c>
       <c r="BF4">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG4">
         <v>19</v>
       </c>
       <c r="BH4">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="BI4">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="BJ4">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK4">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BN4">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BO4">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BP4">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BQ4">
+        <v>9.4</v>
+      </c>
+      <c r="BR4">
+        <v>28</v>
+      </c>
+      <c r="BS4">
+        <v>16</v>
+      </c>
+      <c r="BT4">
         <v>9</v>
       </c>
-      <c r="BR4">
-        <v>25</v>
-      </c>
-      <c r="BS4">
-        <v>14.5</v>
-      </c>
-      <c r="BT4">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BU4">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BV4">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BW4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BX4">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BY4">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BZ4">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="CA4">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="CB4" t="s">
         <v>116</v>
@@ -1705,25 +1705,25 @@
         <v>1.01</v>
       </c>
       <c r="M5">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N5">
         <v>1.13</v>
       </c>
       <c r="O5">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P5">
         <v>1.13</v>
       </c>
       <c r="Q5">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="R5">
         <v>1.08</v>
       </c>
       <c r="S5">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T5">
         <v>1.01</v>
@@ -1732,10 +1732,10 @@
         <v>1.01</v>
       </c>
       <c r="V5">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W5">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X5">
         <v>1000</v>
@@ -1926,10 +1926,10 @@
         <v>108</v>
       </c>
       <c r="F6">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="G6">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="H6">
         <v>2.52</v>
@@ -1941,7 +1941,7 @@
         <v>2.88</v>
       </c>
       <c r="K6">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="L6">
         <v>1.7</v>
@@ -1950,13 +1950,13 @@
         <v>1.17</v>
       </c>
       <c r="N6">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="O6">
         <v>1.73</v>
       </c>
       <c r="P6">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="Q6">
         <v>3.45</v>
@@ -1968,19 +1968,19 @@
         <v>8</v>
       </c>
       <c r="T6">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="U6">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="V6">
         <v>1.64</v>
       </c>
       <c r="W6">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="X6">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="Y6">
         <v>6.6</v>
@@ -1995,10 +1995,10 @@
         <v>9</v>
       </c>
       <c r="AC6">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AD6">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE6">
         <v>48</v>
@@ -2007,13 +2007,13 @@
         <v>24</v>
       </c>
       <c r="AG6">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AH6">
         <v>32</v>
       </c>
       <c r="AI6">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AJ6">
         <v>110</v>
@@ -2022,10 +2022,10 @@
         <v>90</v>
       </c>
       <c r="AL6">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AM6">
-        <v>330</v>
+        <v>350</v>
       </c>
       <c r="AN6">
         <v>150</v>
@@ -2043,7 +2043,7 @@
         <v>11.5</v>
       </c>
       <c r="AS6">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AT6">
         <v>8.199999999999999</v>
@@ -2067,31 +2067,31 @@
         <v>28</v>
       </c>
       <c r="BA6">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BB6">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BC6">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="BD6">
+        <v>13.5</v>
+      </c>
+      <c r="BE6">
         <v>14</v>
       </c>
-      <c r="BE6">
-        <v>13</v>
-      </c>
       <c r="BF6">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG6">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BH6">
         <v>2.44</v>
       </c>
       <c r="BI6">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="BJ6">
         <v>13</v>
@@ -2171,7 +2171,7 @@
         <v>13.5</v>
       </c>
       <c r="G7">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="H7">
         <v>1.33</v>
@@ -2183,7 +2183,7 @@
         <v>5.4</v>
       </c>
       <c r="K7">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="L7">
         <v>1.44</v>
@@ -2198,22 +2198,22 @@
         <v>1.41</v>
       </c>
       <c r="P7">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="Q7">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="R7">
         <v>1.28</v>
       </c>
       <c r="S7">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T7">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="U7">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="V7">
         <v>3.9</v>
@@ -2222,7 +2222,7 @@
         <v>1.06</v>
       </c>
       <c r="X7">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Y7">
         <v>5.8</v>
@@ -2231,7 +2231,7 @@
         <v>6.2</v>
       </c>
       <c r="AA7">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AB7">
         <v>34</v>
@@ -2246,7 +2246,7 @@
         <v>19</v>
       </c>
       <c r="AF7">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AG7">
         <v>70</v>
@@ -2255,13 +2255,13 @@
         <v>60</v>
       </c>
       <c r="AI7">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AJ7">
         <v>1000</v>
       </c>
       <c r="AK7">
-        <v>550</v>
+        <v>530</v>
       </c>
       <c r="AL7">
         <v>410</v>
@@ -2276,10 +2276,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AP7">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AQ7">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AR7">
         <v>5.6</v>
@@ -2294,7 +2294,7 @@
         <v>11.5</v>
       </c>
       <c r="AV7">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AW7">
         <v>17</v>
@@ -2303,7 +2303,7 @@
         <v>13.5</v>
       </c>
       <c r="AY7">
-        <v>50</v>
+        <v>12.5</v>
       </c>
       <c r="AZ7">
         <v>44</v>
@@ -2312,19 +2312,19 @@
         <v>60</v>
       </c>
       <c r="BB7">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BC7">
         <v>10</v>
       </c>
       <c r="BD7">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BE7">
         <v>10</v>
       </c>
       <c r="BF7">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BG7">
         <v>7.2</v>
@@ -2333,7 +2333,7 @@
         <v>3.25</v>
       </c>
       <c r="BI7">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="BJ7">
         <v>25</v>
@@ -2348,7 +2348,7 @@
         <v>21</v>
       </c>
       <c r="BN7">
-        <v>18.5</v>
+        <v>26</v>
       </c>
       <c r="BO7">
         <v>15.5</v>
@@ -2366,7 +2366,7 @@
         <v>21</v>
       </c>
       <c r="BT7">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BU7">
         <v>2.98</v>
@@ -2443,19 +2443,19 @@
         <v>2.66</v>
       </c>
       <c r="Q8">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="R8">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="S8">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="T8">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="U8">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="V8">
         <v>1.54</v>
@@ -2464,40 +2464,40 @@
         <v>1.64</v>
       </c>
       <c r="X8">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Y8">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Z8">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA8">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AB8">
         <v>16.5</v>
       </c>
       <c r="AC8">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD8">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE8">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AF8">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG8">
         <v>12.5</v>
       </c>
       <c r="AH8">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AI8">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AJ8">
         <v>38</v>
@@ -2506,22 +2506,22 @@
         <v>23</v>
       </c>
       <c r="AL8">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AM8">
         <v>50</v>
       </c>
       <c r="AN8">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AO8">
         <v>15</v>
       </c>
       <c r="AP8">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ8">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AR8">
         <v>21</v>
@@ -2530,28 +2530,28 @@
         <v>40</v>
       </c>
       <c r="AT8">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AU8">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV8">
         <v>11.5</v>
       </c>
       <c r="AW8">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="AX8">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AY8">
         <v>11.5</v>
       </c>
       <c r="AZ8">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BA8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BB8">
         <v>34</v>
@@ -2566,7 +2566,7 @@
         <v>44</v>
       </c>
       <c r="BF8">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BG8">
         <v>14</v>
@@ -2652,7 +2652,7 @@
         <v>111</v>
       </c>
       <c r="F9">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="G9">
         <v>1.47</v>
@@ -2661,13 +2661,13 @@
         <v>8</v>
       </c>
       <c r="I9">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J9">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="K9">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="L9">
         <v>1.28</v>
@@ -2676,13 +2676,13 @@
         <v>1.03</v>
       </c>
       <c r="N9">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="O9">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="P9">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="Q9">
         <v>1.56</v>
@@ -2691,19 +2691,19 @@
         <v>1.67</v>
       </c>
       <c r="S9">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="T9">
         <v>1.74</v>
       </c>
       <c r="U9">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="V9">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="W9">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="X9">
         <v>28</v>
@@ -2718,13 +2718,13 @@
         <v>250</v>
       </c>
       <c r="AB9">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC9">
         <v>12.5</v>
       </c>
       <c r="AD9">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AE9">
         <v>100</v>
@@ -2751,7 +2751,7 @@
         <v>30</v>
       </c>
       <c r="AM9">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN9">
         <v>6</v>
@@ -2769,13 +2769,13 @@
         <v>60</v>
       </c>
       <c r="AS9">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT9">
         <v>10.5</v>
       </c>
       <c r="AU9">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AV9">
         <v>25</v>
@@ -2847,7 +2847,7 @@
         <v>24</v>
       </c>
       <c r="BS9">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="BT9">
         <v>13.5</v>
@@ -2871,7 +2871,7 @@
         <v>14</v>
       </c>
       <c r="CA9">
-        <v>8.4</v>
+        <v>4.8</v>
       </c>
       <c r="CB9" t="s">
         <v>116</v>
@@ -2894,10 +2894,10 @@
         <v>112</v>
       </c>
       <c r="F10">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="G10">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="H10">
         <v>4.7</v>
@@ -2924,28 +2924,28 @@
         <v>1.27</v>
       </c>
       <c r="P10">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Q10">
         <v>1.8</v>
       </c>
       <c r="R10">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="S10">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="T10">
         <v>1.8</v>
       </c>
       <c r="U10">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V10">
         <v>1.26</v>
       </c>
       <c r="W10">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="X10">
         <v>18</v>
@@ -2960,37 +2960,37 @@
         <v>110</v>
       </c>
       <c r="AB10">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AC10">
         <v>9.4</v>
       </c>
       <c r="AD10">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE10">
         <v>60</v>
       </c>
       <c r="AF10">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG10">
         <v>10.5</v>
       </c>
       <c r="AH10">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI10">
         <v>60</v>
       </c>
       <c r="AJ10">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AK10">
         <v>18</v>
       </c>
       <c r="AL10">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM10">
         <v>90</v>
@@ -3002,7 +3002,7 @@
         <v>55</v>
       </c>
       <c r="AP10">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AQ10">
         <v>17</v>
@@ -3011,10 +3011,10 @@
         <v>34</v>
       </c>
       <c r="AS10">
-        <v>14.5</v>
+        <v>18.5</v>
       </c>
       <c r="AT10">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AU10">
         <v>9</v>
@@ -3044,7 +3044,7 @@
         <v>17</v>
       </c>
       <c r="BD10">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BE10">
         <v>70</v>
@@ -3053,7 +3053,7 @@
         <v>9</v>
       </c>
       <c r="BG10">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BH10">
         <v>3.8</v>
@@ -3065,7 +3065,7 @@
         <v>9.6</v>
       </c>
       <c r="BK10">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BL10">
         <v>1000</v>
@@ -3083,7 +3083,7 @@
         <v>12</v>
       </c>
       <c r="BQ10">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BR10">
         <v>25</v>
@@ -3160,19 +3160,19 @@
         <v>1.1</v>
       </c>
       <c r="N11">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="O11">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="P11">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="Q11">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="R11">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="S11">
         <v>4.7</v>
@@ -3181,7 +3181,7 @@
         <v>2.02</v>
       </c>
       <c r="U11">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="V11">
         <v>1.42</v>
@@ -3208,7 +3208,7 @@
         <v>7.4</v>
       </c>
       <c r="AD11">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE11">
         <v>50</v>
@@ -3229,34 +3229,34 @@
         <v>36</v>
       </c>
       <c r="AK11">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AL11">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AM11">
         <v>150</v>
       </c>
       <c r="AN11">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO11">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP11">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AQ11">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AR11">
         <v>19</v>
       </c>
       <c r="AS11">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AT11">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AU11">
         <v>6.8</v>
@@ -3289,7 +3289,7 @@
         <v>48</v>
       </c>
       <c r="BE11">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BF11">
         <v>10.5</v>
@@ -3307,13 +3307,13 @@
         <v>10.5</v>
       </c>
       <c r="BK11">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="BN11">
         <v>5.3</v>
@@ -3325,13 +3325,13 @@
         <v>21</v>
       </c>
       <c r="BQ11">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BR11">
         <v>55</v>
       </c>
       <c r="BS11">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BT11">
         <v>6.4</v>
@@ -3343,19 +3343,19 @@
         <v>42</v>
       </c>
       <c r="BW11">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BX11">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY11">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BZ11">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA11">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="CB11" t="s">
         <v>116</v>
@@ -3396,7 +3396,7 @@
         <v>3.45</v>
       </c>
       <c r="L12">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="M12">
         <v>1.09</v>
@@ -3411,7 +3411,7 @@
         <v>1.77</v>
       </c>
       <c r="Q12">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R12">
         <v>1.3</v>
@@ -3432,7 +3432,7 @@
         <v>1.56</v>
       </c>
       <c r="X12">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Y12">
         <v>10.5</v>
@@ -3462,13 +3462,13 @@
         <v>13</v>
       </c>
       <c r="AH12">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI12">
         <v>55</v>
       </c>
       <c r="AJ12">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AK12">
         <v>34</v>
@@ -3480,13 +3480,13 @@
         <v>120</v>
       </c>
       <c r="AN12">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO12">
         <v>36</v>
       </c>
       <c r="AP12">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ12">
         <v>9.800000000000001</v>
@@ -3516,7 +3516,7 @@
         <v>12.5</v>
       </c>
       <c r="AZ12">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA12">
         <v>44</v>
@@ -3543,37 +3543,37 @@
         <v>3.05</v>
       </c>
       <c r="BI12">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="BJ12">
         <v>11.5</v>
       </c>
       <c r="BK12">
-        <v>5.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL12">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="BM12">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BN12">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BO12">
         <v>5.1</v>
       </c>
       <c r="BP12">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BQ12">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR12">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="BS12">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="BT12">
         <v>5.9</v>
@@ -3582,22 +3582,22 @@
         <v>5.3</v>
       </c>
       <c r="BV12">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="BW12">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX12">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="BY12">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="BZ12">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="CA12">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="CB12" t="s">
         <v>116</v>
@@ -3623,13 +3623,13 @@
         <v>1.24</v>
       </c>
       <c r="G13">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="H13">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="I13">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="J13">
         <v>7</v>
@@ -3665,13 +3665,13 @@
         <v>2.28</v>
       </c>
       <c r="U13">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="V13">
         <v>1.06</v>
       </c>
       <c r="W13">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="X13">
         <v>26</v>
@@ -3683,7 +3683,7 @@
         <v>170</v>
       </c>
       <c r="AA13">
-        <v>910</v>
+        <v>900</v>
       </c>
       <c r="AB13">
         <v>10.5</v>
@@ -3719,13 +3719,13 @@
         <v>46</v>
       </c>
       <c r="AM13">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="AN13">
         <v>3.9</v>
       </c>
       <c r="AO13">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="AP13">
         <v>23</v>
@@ -3770,7 +3770,7 @@
         <v>13</v>
       </c>
       <c r="BD13">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BE13">
         <v>19.5</v>
@@ -3797,7 +3797,7 @@
         <v>210</v>
       </c>
       <c r="BM13">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="BN13">
         <v>3.7</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-24.xlsx
@@ -364,7 +364,7 @@
     <t>Wales</t>
   </si>
   <si>
-    <t>2026-09-22 19:40:27</t>
+    <t>2026-09-22 21:51:31</t>
   </si>
 </sst>
 </file>
@@ -961,7 +961,7 @@
         <v>1.7</v>
       </c>
       <c r="G2">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="H2">
         <v>5.9</v>
@@ -973,10 +973,10 @@
         <v>3.8</v>
       </c>
       <c r="K2">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L2">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="M2">
         <v>1.08</v>
@@ -988,7 +988,7 @@
         <v>1.38</v>
       </c>
       <c r="P2">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="Q2">
         <v>2.12</v>
@@ -1009,7 +1009,7 @@
         <v>1.18</v>
       </c>
       <c r="W2">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="X2">
         <v>13</v>
@@ -1066,7 +1066,7 @@
         <v>170</v>
       </c>
       <c r="AP2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ2">
         <v>15.5</v>
@@ -1108,7 +1108,7 @@
         <v>17</v>
       </c>
       <c r="BD2">
-        <v>36</v>
+        <v>6.2</v>
       </c>
       <c r="BE2">
         <v>6.8</v>
@@ -1135,7 +1135,7 @@
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BN2">
         <v>4.2</v>
@@ -1153,7 +1153,7 @@
         <v>38</v>
       </c>
       <c r="BS2">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BT2">
         <v>11.5</v>
@@ -1165,10 +1165,10 @@
         <v>85</v>
       </c>
       <c r="BW2">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BX2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="BY2">
         <v>5.4</v>
@@ -1177,7 +1177,7 @@
         <v>32</v>
       </c>
       <c r="CA2">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="CB2" t="s">
         <v>116</v>
@@ -1233,7 +1233,7 @@
         <v>2.5</v>
       </c>
       <c r="Q3">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="R3">
         <v>1.6</v>
@@ -1263,7 +1263,7 @@
         <v>40</v>
       </c>
       <c r="AA3">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB3">
         <v>13</v>
@@ -1317,7 +1317,7 @@
         <v>30</v>
       </c>
       <c r="AS3">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AT3">
         <v>11.5</v>
@@ -1332,7 +1332,7 @@
         <v>36</v>
       </c>
       <c r="AX3">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AY3">
         <v>9.6</v>
@@ -1371,7 +1371,7 @@
         <v>9</v>
       </c>
       <c r="BK3">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BL3">
         <v>100</v>
@@ -1442,58 +1442,58 @@
         <v>106</v>
       </c>
       <c r="F4">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="G4">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H4">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="I4">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J4">
         <v>4</v>
       </c>
       <c r="K4">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="L4">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="M4">
         <v>1.04</v>
       </c>
       <c r="N4">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="O4">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="P4">
         <v>2.34</v>
       </c>
       <c r="Q4">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="R4">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="S4">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="T4">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="U4">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="V4">
         <v>1.3</v>
       </c>
       <c r="W4">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="X4">
         <v>27</v>
@@ -1520,7 +1520,7 @@
         <v>48</v>
       </c>
       <c r="AF4">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG4">
         <v>13</v>
@@ -1550,10 +1550,10 @@
         <v>36</v>
       </c>
       <c r="AP4">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="AQ4">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AR4">
         <v>1.03</v>
@@ -1562,46 +1562,46 @@
         <v>1.03</v>
       </c>
       <c r="AT4">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU4">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AV4">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AW4">
         <v>1.03</v>
       </c>
       <c r="AX4">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AY4">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AZ4">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="BA4">
         <v>1.03</v>
       </c>
       <c r="BB4">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="BC4">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="BD4">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="BE4">
         <v>1.03</v>
       </c>
       <c r="BF4">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BG4">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="BH4">
         <v>4.9</v>
@@ -1634,7 +1634,7 @@
         <v>9.4</v>
       </c>
       <c r="BR4">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BS4">
         <v>16</v>
@@ -1643,7 +1643,7 @@
         <v>9</v>
       </c>
       <c r="BU4">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BV4">
         <v>34</v>
@@ -1655,7 +1655,7 @@
         <v>40</v>
       </c>
       <c r="BY4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BZ4">
         <v>20</v>
@@ -1732,10 +1732,10 @@
         <v>1.01</v>
       </c>
       <c r="V5">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W5">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X5">
         <v>1000</v>
@@ -1926,16 +1926,16 @@
         <v>108</v>
       </c>
       <c r="F6">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="G6">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="H6">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="I6">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="J6">
         <v>2.88</v>
@@ -1944,7 +1944,7 @@
         <v>2.92</v>
       </c>
       <c r="L6">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="M6">
         <v>1.17</v>
@@ -1956,10 +1956,10 @@
         <v>1.73</v>
       </c>
       <c r="P6">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="Q6">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="R6">
         <v>1.13</v>
@@ -1977,13 +1977,13 @@
         <v>1.64</v>
       </c>
       <c r="W6">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="X6">
         <v>6.8</v>
       </c>
       <c r="Y6">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="Z6">
         <v>13</v>
@@ -2007,7 +2007,7 @@
         <v>24</v>
       </c>
       <c r="AG6">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AH6">
         <v>32</v>
@@ -2019,7 +2019,7 @@
         <v>110</v>
       </c>
       <c r="AK6">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AL6">
         <v>130</v>
@@ -2043,7 +2043,7 @@
         <v>11.5</v>
       </c>
       <c r="AS6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT6">
         <v>8.199999999999999</v>
@@ -2067,22 +2067,22 @@
         <v>28</v>
       </c>
       <c r="BA6">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BB6">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BC6">
-        <v>12.5</v>
+        <v>65</v>
       </c>
       <c r="BD6">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BE6">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BF6">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BG6">
         <v>44</v>
@@ -2192,7 +2192,7 @@
         <v>1.08</v>
       </c>
       <c r="N7">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O7">
         <v>1.41</v>
@@ -2213,10 +2213,10 @@
         <v>2.84</v>
       </c>
       <c r="U7">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="V7">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="W7">
         <v>1.06</v>
@@ -2225,13 +2225,13 @@
         <v>13</v>
       </c>
       <c r="Y7">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Z7">
         <v>6.2</v>
       </c>
       <c r="AA7">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AB7">
         <v>34</v>
@@ -2279,7 +2279,7 @@
         <v>12.5</v>
       </c>
       <c r="AQ7">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AR7">
         <v>5.6</v>
@@ -2300,10 +2300,10 @@
         <v>17</v>
       </c>
       <c r="AX7">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AY7">
-        <v>12.5</v>
+        <v>50</v>
       </c>
       <c r="AZ7">
         <v>44</v>
@@ -2312,13 +2312,13 @@
         <v>60</v>
       </c>
       <c r="BB7">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BC7">
         <v>10</v>
       </c>
       <c r="BD7">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BE7">
         <v>10</v>
@@ -2333,7 +2333,7 @@
         <v>3.25</v>
       </c>
       <c r="BI7">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="BJ7">
         <v>25</v>
@@ -2410,16 +2410,16 @@
         <v>110</v>
       </c>
       <c r="F8">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="G8">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="H8">
+        <v>2.8</v>
+      </c>
+      <c r="I8">
         <v>2.82</v>
-      </c>
-      <c r="I8">
-        <v>2.84</v>
       </c>
       <c r="J8">
         <v>3.9</v>
@@ -2461,13 +2461,13 @@
         <v>1.54</v>
       </c>
       <c r="W8">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="X8">
         <v>25</v>
       </c>
       <c r="Y8">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Z8">
         <v>23</v>
@@ -2476,13 +2476,13 @@
         <v>44</v>
       </c>
       <c r="AB8">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AC8">
         <v>9.4</v>
       </c>
       <c r="AD8">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AE8">
         <v>26</v>
@@ -2518,7 +2518,7 @@
         <v>15</v>
       </c>
       <c r="AP8">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ8">
         <v>16.5</v>
@@ -2536,13 +2536,13 @@
         <v>9</v>
       </c>
       <c r="AV8">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW8">
         <v>23</v>
       </c>
       <c r="AX8">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AY8">
         <v>11.5</v>
@@ -2551,7 +2551,7 @@
         <v>12.5</v>
       </c>
       <c r="BA8">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BB8">
         <v>34</v>
@@ -2566,10 +2566,10 @@
         <v>44</v>
       </c>
       <c r="BF8">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BG8">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BH8">
         <v>4.4</v>
@@ -2655,10 +2655,10 @@
         <v>1.45</v>
       </c>
       <c r="G9">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="H9">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="I9">
         <v>8.199999999999999</v>
@@ -2667,7 +2667,7 @@
         <v>5.2</v>
       </c>
       <c r="K9">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="L9">
         <v>1.28</v>
@@ -2676,7 +2676,7 @@
         <v>1.03</v>
       </c>
       <c r="N9">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="O9">
         <v>1.18</v>
@@ -2691,25 +2691,25 @@
         <v>1.67</v>
       </c>
       <c r="S9">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="T9">
         <v>1.74</v>
       </c>
       <c r="U9">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V9">
         <v>1.13</v>
       </c>
       <c r="W9">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="X9">
         <v>28</v>
       </c>
       <c r="Y9">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Z9">
         <v>80</v>
@@ -2724,7 +2724,7 @@
         <v>12.5</v>
       </c>
       <c r="AD9">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AE9">
         <v>100</v>
@@ -2751,7 +2751,7 @@
         <v>30</v>
       </c>
       <c r="AM9">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AN9">
         <v>6</v>
@@ -2769,13 +2769,13 @@
         <v>60</v>
       </c>
       <c r="AS9">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AT9">
         <v>10.5</v>
       </c>
       <c r="AU9">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AV9">
         <v>25</v>
@@ -2808,7 +2808,7 @@
         <v>10.5</v>
       </c>
       <c r="BF9">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="BG9">
         <v>60</v>
@@ -2900,10 +2900,10 @@
         <v>1.81</v>
       </c>
       <c r="H10">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I10">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J10">
         <v>4.2</v>
@@ -2924,7 +2924,7 @@
         <v>1.27</v>
       </c>
       <c r="P10">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q10">
         <v>1.8</v>
@@ -2936,16 +2936,16 @@
         <v>3</v>
       </c>
       <c r="T10">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="U10">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V10">
         <v>1.26</v>
       </c>
       <c r="W10">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="X10">
         <v>18</v>
@@ -2954,7 +2954,7 @@
         <v>18.5</v>
       </c>
       <c r="Z10">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA10">
         <v>110</v>
@@ -2966,7 +2966,7 @@
         <v>9.4</v>
       </c>
       <c r="AD10">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AE10">
         <v>60</v>
@@ -3011,10 +3011,10 @@
         <v>34</v>
       </c>
       <c r="AS10">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AT10">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU10">
         <v>9</v>
@@ -3047,10 +3047,10 @@
         <v>28</v>
       </c>
       <c r="BE10">
-        <v>70</v>
+        <v>19</v>
       </c>
       <c r="BF10">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG10">
         <v>44</v>
@@ -3136,16 +3136,16 @@
         <v>113</v>
       </c>
       <c r="F11">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="G11">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="H11">
+        <v>3.2</v>
+      </c>
+      <c r="I11">
         <v>3.3</v>
-      </c>
-      <c r="I11">
-        <v>3.35</v>
       </c>
       <c r="J11">
         <v>3.25</v>
@@ -3163,10 +3163,10 @@
         <v>2.94</v>
       </c>
       <c r="O11">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P11">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="Q11">
         <v>2.4</v>
@@ -3181,28 +3181,28 @@
         <v>2.02</v>
       </c>
       <c r="U11">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="V11">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W11">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="X11">
         <v>10.5</v>
       </c>
       <c r="Y11">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Z11">
         <v>22</v>
       </c>
       <c r="AA11">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB11">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC11">
         <v>7.4</v>
@@ -3232,10 +3232,10 @@
         <v>36</v>
       </c>
       <c r="AL11">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM11">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="AN11">
         <v>32</v>
@@ -3250,22 +3250,22 @@
         <v>9.4</v>
       </c>
       <c r="AR11">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AS11">
         <v>50</v>
       </c>
       <c r="AT11">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU11">
         <v>6.8</v>
       </c>
       <c r="AV11">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AW11">
-        <v>40</v>
+        <v>11.5</v>
       </c>
       <c r="AX11">
         <v>13</v>
@@ -3274,7 +3274,7 @@
         <v>11</v>
       </c>
       <c r="AZ11">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BA11">
         <v>55</v>
@@ -3286,16 +3286,16 @@
         <v>28</v>
       </c>
       <c r="BD11">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="BE11">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BF11">
-        <v>10.5</v>
+        <v>27</v>
       </c>
       <c r="BG11">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BH11">
         <v>2.86</v>
@@ -3307,7 +3307,7 @@
         <v>10.5</v>
       </c>
       <c r="BK11">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BL11">
         <v>1000</v>
@@ -3378,16 +3378,16 @@
         <v>114</v>
       </c>
       <c r="F12">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="G12">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="H12">
+        <v>2.86</v>
+      </c>
+      <c r="I12">
         <v>2.88</v>
-      </c>
-      <c r="I12">
-        <v>2.94</v>
       </c>
       <c r="J12">
         <v>3.4</v>
@@ -3408,25 +3408,25 @@
         <v>1.41</v>
       </c>
       <c r="P12">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="Q12">
         <v>2.2</v>
       </c>
       <c r="R12">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S12">
         <v>4.2</v>
       </c>
       <c r="T12">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="U12">
         <v>2.02</v>
       </c>
       <c r="V12">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="W12">
         <v>1.56</v>
@@ -3438,7 +3438,7 @@
         <v>10.5</v>
       </c>
       <c r="Z12">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AA12">
         <v>48</v>
@@ -3498,7 +3498,7 @@
         <v>42</v>
       </c>
       <c r="AT12">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AU12">
         <v>7</v>
@@ -3626,7 +3626,7 @@
         <v>1.25</v>
       </c>
       <c r="H13">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="I13">
         <v>18</v>
@@ -3635,7 +3635,7 @@
         <v>7</v>
       </c>
       <c r="K13">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="L13">
         <v>1.29</v>
@@ -3665,10 +3665,10 @@
         <v>2.28</v>
       </c>
       <c r="U13">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="V13">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W13">
         <v>5</v>
@@ -3680,13 +3680,13 @@
         <v>50</v>
       </c>
       <c r="Z13">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AA13">
         <v>900</v>
       </c>
       <c r="AB13">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC13">
         <v>16</v>
@@ -3698,7 +3698,7 @@
         <v>310</v>
       </c>
       <c r="AF13">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AG13">
         <v>11.5</v>
@@ -3719,7 +3719,7 @@
         <v>46</v>
       </c>
       <c r="AM13">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AN13">
         <v>3.9</v>
@@ -3734,7 +3734,7 @@
         <v>42</v>
       </c>
       <c r="AR13">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AS13">
         <v>20</v>
@@ -3749,22 +3749,22 @@
         <v>48</v>
       </c>
       <c r="AW13">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX13">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AY13">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ13">
         <v>32</v>
       </c>
       <c r="BA13">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="BB13">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BC13">
         <v>13</v>
@@ -3773,13 +3773,13 @@
         <v>38</v>
       </c>
       <c r="BE13">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BF13">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BG13">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BH13">
         <v>4.5</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-24.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="121">
   <si>
     <t>League</t>
   </si>
@@ -271,6 +271,9 @@
     <t>UEFA Nations League</t>
   </si>
   <si>
+    <t>Moroccan Botola Pro 1</t>
+  </si>
+  <si>
     <t>2026-09-24</t>
   </si>
   <si>
@@ -292,6 +295,9 @@
     <t>18:45:00</t>
   </si>
   <si>
+    <t>20:00:00</t>
+  </si>
+  <si>
     <t>America de Cali S.A</t>
   </si>
   <si>
@@ -313,21 +319,24 @@
     <t>Netherlands</t>
   </si>
   <si>
+    <t>Norway</t>
+  </si>
+  <si>
+    <t>Kosovo</t>
+  </si>
+  <si>
     <t>Austria</t>
   </si>
   <si>
-    <t>Norway</t>
-  </si>
-  <si>
-    <t>Kosovo</t>
-  </si>
-  <si>
     <t>Serbia</t>
   </si>
   <si>
     <t>Portugal</t>
   </si>
   <si>
+    <t>US Amal Tiznit</t>
+  </si>
+  <si>
     <t>Aguilas Doradas</t>
   </si>
   <si>
@@ -349,22 +358,25 @@
     <t>Germany</t>
   </si>
   <si>
+    <t>Denmark</t>
+  </si>
+  <si>
+    <t>Republic of Ireland</t>
+  </si>
+  <si>
     <t>Israel</t>
   </si>
   <si>
-    <t>Denmark</t>
-  </si>
-  <si>
-    <t>Republic of Ireland</t>
-  </si>
-  <si>
     <t>Greece</t>
   </si>
   <si>
     <t>Wales</t>
   </si>
   <si>
-    <t>2026-09-22 21:51:31</t>
+    <t>IRT Tanger</t>
+  </si>
+  <si>
+    <t>2026-09-23 00:02:48</t>
   </si>
 </sst>
 </file>
@@ -696,7 +708,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB13"/>
+  <dimension ref="A1:CB14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -946,22 +958,22 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E2" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="F2">
         <v>1.7</v>
       </c>
       <c r="G2">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="H2">
         <v>5.9</v>
@@ -976,7 +988,7 @@
         <v>4</v>
       </c>
       <c r="L2">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="M2">
         <v>1.08</v>
@@ -1009,13 +1021,13 @@
         <v>1.18</v>
       </c>
       <c r="W2">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="X2">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Y2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z2">
         <v>60</v>
@@ -1024,34 +1036,34 @@
         <v>220</v>
       </c>
       <c r="AB2">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC2">
         <v>8.800000000000001</v>
       </c>
       <c r="AD2">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AE2">
         <v>120</v>
       </c>
       <c r="AF2">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AG2">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH2">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AI2">
         <v>120</v>
       </c>
       <c r="AJ2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AL2">
         <v>55</v>
@@ -1060,7 +1072,7 @@
         <v>190</v>
       </c>
       <c r="AN2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AO2">
         <v>170</v>
@@ -1069,10 +1081,10 @@
         <v>11.5</v>
       </c>
       <c r="AQ2">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AR2">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="AS2">
         <v>6.8</v>
@@ -1090,13 +1102,13 @@
         <v>6.8</v>
       </c>
       <c r="AX2">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AY2">
         <v>9</v>
       </c>
       <c r="AZ2">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="BA2">
         <v>6.8</v>
@@ -1105,7 +1117,7 @@
         <v>14.5</v>
       </c>
       <c r="BC2">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BD2">
         <v>6.2</v>
@@ -1114,13 +1126,13 @@
         <v>6.8</v>
       </c>
       <c r="BF2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BG2">
-        <v>6.8</v>
+        <v>36</v>
       </c>
       <c r="BH2">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BI2">
         <v>2.58</v>
@@ -1129,16 +1141,16 @@
         <v>13.5</v>
       </c>
       <c r="BK2">
-        <v>8.199999999999999</v>
+        <v>4.1</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BN2">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BO2">
         <v>3.7</v>
@@ -1147,31 +1159,31 @@
         <v>14.5</v>
       </c>
       <c r="BQ2">
-        <v>8.800000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="BR2">
         <v>38</v>
       </c>
       <c r="BS2">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BT2">
         <v>11.5</v>
       </c>
       <c r="BU2">
-        <v>7</v>
+        <v>3.95</v>
       </c>
       <c r="BV2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="BW2">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BX2">
         <v>75</v>
       </c>
       <c r="BY2">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BZ2">
         <v>32</v>
@@ -1180,7 +1192,7 @@
         <v>5</v>
       </c>
       <c r="CB2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1188,25 +1200,25 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="F3">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="G3">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="H3">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I3">
         <v>4.3</v>
@@ -1230,7 +1242,7 @@
         <v>1.21</v>
       </c>
       <c r="P3">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="Q3">
         <v>1.62</v>
@@ -1245,13 +1257,13 @@
         <v>1.59</v>
       </c>
       <c r="U3">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="V3">
         <v>1.3</v>
       </c>
       <c r="W3">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="X3">
         <v>23</v>
@@ -1260,7 +1272,7 @@
         <v>21</v>
       </c>
       <c r="Z3">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AA3">
         <v>85</v>
@@ -1287,7 +1299,7 @@
         <v>16</v>
       </c>
       <c r="AI3">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AJ3">
         <v>23</v>
@@ -1320,7 +1332,7 @@
         <v>65</v>
       </c>
       <c r="AT3">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU3">
         <v>9</v>
@@ -1335,7 +1347,7 @@
         <v>13</v>
       </c>
       <c r="AY3">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ3">
         <v>14.5</v>
@@ -1344,7 +1356,7 @@
         <v>36</v>
       </c>
       <c r="BB3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC3">
         <v>16</v>
@@ -1362,7 +1374,7 @@
         <v>27</v>
       </c>
       <c r="BH3">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BI3">
         <v>3.9</v>
@@ -1371,13 +1383,13 @@
         <v>9</v>
       </c>
       <c r="BK3">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BL3">
         <v>100</v>
       </c>
       <c r="BM3">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="BN3">
         <v>5</v>
@@ -1386,16 +1398,16 @@
         <v>4.5</v>
       </c>
       <c r="BP3">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BQ3">
-        <v>9.199999999999999</v>
+        <v>5.9</v>
       </c>
       <c r="BR3">
         <v>27</v>
       </c>
       <c r="BS3">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BT3">
         <v>7.8</v>
@@ -1407,22 +1419,22 @@
         <v>36</v>
       </c>
       <c r="BW3">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="BX3">
         <v>40</v>
       </c>
       <c r="BY3">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BZ3">
         <v>19</v>
       </c>
       <c r="CA3">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="CB3" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1430,25 +1442,25 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D4" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E4" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F4">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="G4">
         <v>2.08</v>
       </c>
       <c r="H4">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="I4">
         <v>4.3</v>
@@ -1457,40 +1469,40 @@
         <v>4</v>
       </c>
       <c r="K4">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L4">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="M4">
         <v>1.04</v>
       </c>
       <c r="N4">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="O4">
         <v>1.21</v>
       </c>
       <c r="P4">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="Q4">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="R4">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="S4">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="T4">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="U4">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="V4">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W4">
         <v>1.93</v>
@@ -1499,25 +1511,25 @@
         <v>27</v>
       </c>
       <c r="Y4">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Z4">
         <v>38</v>
       </c>
       <c r="AA4">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AB4">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC4">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD4">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AE4">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AF4">
         <v>17</v>
@@ -1526,34 +1538,34 @@
         <v>13</v>
       </c>
       <c r="AH4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI4">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AJ4">
         <v>27</v>
       </c>
       <c r="AK4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL4">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AM4">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AN4">
-        <v>9.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="AO4">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AP4">
         <v>16</v>
       </c>
       <c r="AQ4">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AR4">
         <v>1.03</v>
@@ -1562,7 +1574,7 @@
         <v>1.03</v>
       </c>
       <c r="AT4">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AU4">
         <v>7.2</v>
@@ -1580,7 +1592,7 @@
         <v>8</v>
       </c>
       <c r="AZ4">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BA4">
         <v>1.03</v>
@@ -1589,7 +1601,7 @@
         <v>16.5</v>
       </c>
       <c r="BC4">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BD4">
         <v>20</v>
@@ -1598,73 +1610,73 @@
         <v>1.03</v>
       </c>
       <c r="BF4">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BG4">
         <v>23</v>
       </c>
       <c r="BH4">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="BI4">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="BJ4">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK4">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="BN4">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="BO4">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BP4">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BR4">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BS4">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BT4">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BU4">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BV4">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW4">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BX4">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BY4">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="CA4">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="CB4" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1672,16 +1684,16 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E5" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="F5">
         <v>1.1</v>
@@ -1696,7 +1708,7 @@
         <v>110</v>
       </c>
       <c r="J5">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="K5">
         <v>950</v>
@@ -1732,10 +1744,10 @@
         <v>1.01</v>
       </c>
       <c r="V5">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W5">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X5">
         <v>1000</v>
@@ -1906,7 +1918,7 @@
         <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1914,25 +1926,25 @@
         <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D6" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E6" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F6">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="G6">
         <v>3.9</v>
       </c>
       <c r="H6">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="I6">
         <v>2.54</v>
@@ -1950,13 +1962,13 @@
         <v>1.17</v>
       </c>
       <c r="N6">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="O6">
         <v>1.73</v>
       </c>
       <c r="P6">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="Q6">
         <v>3.5</v>
@@ -1965,7 +1977,7 @@
         <v>1.13</v>
       </c>
       <c r="S6">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="T6">
         <v>2.52</v>
@@ -2022,7 +2034,7 @@
         <v>85</v>
       </c>
       <c r="AL6">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AM6">
         <v>350</v>
@@ -2043,7 +2055,7 @@
         <v>11.5</v>
       </c>
       <c r="AS6">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AT6">
         <v>8.199999999999999</v>
@@ -2073,13 +2085,13 @@
         <v>14.5</v>
       </c>
       <c r="BC6">
-        <v>65</v>
+        <v>14.5</v>
       </c>
       <c r="BD6">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BE6">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BF6">
         <v>14.5</v>
@@ -2088,13 +2100,13 @@
         <v>44</v>
       </c>
       <c r="BH6">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="BI6">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="BJ6">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BK6">
         <v>10.5</v>
@@ -2112,7 +2124,7 @@
         <v>6</v>
       </c>
       <c r="BP6">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BQ6">
         <v>30</v>
@@ -2121,7 +2133,7 @@
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="BT6">
         <v>5.2</v>
@@ -2130,25 +2142,25 @@
         <v>4.5</v>
       </c>
       <c r="BV6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BW6">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BX6">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY6">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BZ6">
         <v>1000</v>
       </c>
       <c r="CA6">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="CB6" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2156,19 +2168,19 @@
         <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D7" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E7" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="F7">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="G7">
         <v>17</v>
@@ -2177,13 +2189,13 @@
         <v>1.33</v>
       </c>
       <c r="I7">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="J7">
         <v>5.4</v>
       </c>
       <c r="K7">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="L7">
         <v>1.44</v>
@@ -2192,10 +2204,10 @@
         <v>1.08</v>
       </c>
       <c r="N7">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O7">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P7">
         <v>1.75</v>
@@ -2207,10 +2219,10 @@
         <v>1.28</v>
       </c>
       <c r="S7">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T7">
-        <v>2.84</v>
+        <v>2.96</v>
       </c>
       <c r="U7">
         <v>1.47</v>
@@ -2231,7 +2243,7 @@
         <v>6.2</v>
       </c>
       <c r="AA7">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AB7">
         <v>34</v>
@@ -2249,13 +2261,13 @@
         <v>160</v>
       </c>
       <c r="AG7">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AH7">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AI7">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AJ7">
         <v>1000</v>
@@ -2264,7 +2276,7 @@
         <v>530</v>
       </c>
       <c r="AL7">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="AM7">
         <v>560</v>
@@ -2276,10 +2288,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AP7">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AQ7">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AR7">
         <v>5.6</v>
@@ -2303,28 +2315,28 @@
         <v>13</v>
       </c>
       <c r="AY7">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AZ7">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="BA7">
         <v>60</v>
       </c>
       <c r="BB7">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="BC7">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BD7">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BE7">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BF7">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BG7">
         <v>7.2</v>
@@ -2336,10 +2348,10 @@
         <v>2.9</v>
       </c>
       <c r="BJ7">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BK7">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="BL7">
         <v>1000</v>
@@ -2348,7 +2360,7 @@
         <v>21</v>
       </c>
       <c r="BN7">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BO7">
         <v>15.5</v>
@@ -2375,22 +2387,22 @@
         <v>8</v>
       </c>
       <c r="BW7">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BX7">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY7">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="BZ7">
         <v>18.5</v>
       </c>
       <c r="CA7">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="CB7" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2398,16 +2410,16 @@
         <v>84</v>
       </c>
       <c r="B8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D8" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E8" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F8">
         <v>2.54</v>
@@ -2416,10 +2428,10 @@
         <v>2.58</v>
       </c>
       <c r="H8">
+        <v>2.76</v>
+      </c>
+      <c r="I8">
         <v>2.8</v>
-      </c>
-      <c r="I8">
-        <v>2.82</v>
       </c>
       <c r="J8">
         <v>3.9</v>
@@ -2428,7 +2440,7 @@
         <v>4</v>
       </c>
       <c r="L8">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="M8">
         <v>1.04</v>
@@ -2440,13 +2452,13 @@
         <v>1.18</v>
       </c>
       <c r="P8">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="Q8">
         <v>1.57</v>
       </c>
       <c r="R8">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="S8">
         <v>2.36</v>
@@ -2458,7 +2470,7 @@
         <v>2.82</v>
       </c>
       <c r="V8">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W8">
         <v>1.63</v>
@@ -2467,13 +2479,13 @@
         <v>25</v>
       </c>
       <c r="Y8">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Z8">
         <v>23</v>
       </c>
       <c r="AA8">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AB8">
         <v>17</v>
@@ -2485,7 +2497,7 @@
         <v>13</v>
       </c>
       <c r="AE8">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF8">
         <v>20</v>
@@ -2542,13 +2554,13 @@
         <v>23</v>
       </c>
       <c r="AX8">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AY8">
         <v>11.5</v>
       </c>
       <c r="AZ8">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BA8">
         <v>27</v>
@@ -2599,10 +2611,10 @@
         <v>17</v>
       </c>
       <c r="BQ8">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR8">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BS8">
         <v>9.800000000000001</v>
@@ -2617,7 +2629,7 @@
         <v>19.5</v>
       </c>
       <c r="BW8">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX8">
         <v>26</v>
@@ -2629,10 +2641,10 @@
         <v>16</v>
       </c>
       <c r="CA8">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="CB8" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2640,241 +2652,241 @@
         <v>84</v>
       </c>
       <c r="B9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E9" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="F9">
-        <v>1.45</v>
+        <v>1.79</v>
       </c>
       <c r="G9">
-        <v>1.46</v>
+        <v>1.8</v>
       </c>
       <c r="H9">
-        <v>7.6</v>
+        <v>4.8</v>
       </c>
       <c r="I9">
-        <v>8.199999999999999</v>
+        <v>4.9</v>
       </c>
       <c r="J9">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="K9">
-        <v>5.5</v>
+        <v>4.3</v>
       </c>
       <c r="L9">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="M9">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="N9">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="O9">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="P9">
-        <v>2.64</v>
+        <v>2.22</v>
       </c>
       <c r="Q9">
-        <v>1.56</v>
+        <v>1.78</v>
       </c>
       <c r="R9">
-        <v>1.67</v>
+        <v>1.48</v>
       </c>
       <c r="S9">
-        <v>2.3</v>
+        <v>2.96</v>
       </c>
       <c r="T9">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="U9">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="V9">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="W9">
-        <v>3.1</v>
+        <v>2.24</v>
       </c>
       <c r="X9">
-        <v>28</v>
+        <v>18.5</v>
       </c>
       <c r="Y9">
+        <v>18.5</v>
+      </c>
+      <c r="Z9">
         <v>38</v>
       </c>
-      <c r="Z9">
-        <v>80</v>
-      </c>
       <c r="AA9">
-        <v>250</v>
+        <v>110</v>
       </c>
       <c r="AB9">
-        <v>13.5</v>
+        <v>10</v>
       </c>
       <c r="AC9">
-        <v>12.5</v>
+        <v>9.4</v>
       </c>
       <c r="AD9">
-        <v>36</v>
+        <v>18.5</v>
       </c>
       <c r="AE9">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="AF9">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AG9">
         <v>10.5</v>
       </c>
       <c r="AH9">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AI9">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="AJ9">
+        <v>18.5</v>
+      </c>
+      <c r="AK9">
+        <v>17.5</v>
+      </c>
+      <c r="AL9">
+        <v>32</v>
+      </c>
+      <c r="AM9">
+        <v>90</v>
+      </c>
+      <c r="AN9">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AO9">
+        <v>55</v>
+      </c>
+      <c r="AP9">
+        <v>17</v>
+      </c>
+      <c r="AQ9">
+        <v>17</v>
+      </c>
+      <c r="AR9">
+        <v>34</v>
+      </c>
+      <c r="AS9">
+        <v>18</v>
+      </c>
+      <c r="AT9">
+        <v>9.6</v>
+      </c>
+      <c r="AU9">
+        <v>9</v>
+      </c>
+      <c r="AV9">
+        <v>17</v>
+      </c>
+      <c r="AW9">
+        <v>50</v>
+      </c>
+      <c r="AX9">
+        <v>11</v>
+      </c>
+      <c r="AY9">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ9">
+        <v>17.5</v>
+      </c>
+      <c r="BA9">
+        <v>50</v>
+      </c>
+      <c r="BB9">
+        <v>16.5</v>
+      </c>
+      <c r="BC9">
+        <v>16.5</v>
+      </c>
+      <c r="BD9">
+        <v>28</v>
+      </c>
+      <c r="BE9">
+        <v>17.5</v>
+      </c>
+      <c r="BF9">
+        <v>9</v>
+      </c>
+      <c r="BG9">
+        <v>15.5</v>
+      </c>
+      <c r="BH9">
+        <v>3.85</v>
+      </c>
+      <c r="BI9">
+        <v>3.55</v>
+      </c>
+      <c r="BJ9">
+        <v>9.6</v>
+      </c>
+      <c r="BK9">
+        <v>8.4</v>
+      </c>
+      <c r="BL9">
+        <v>110</v>
+      </c>
+      <c r="BM9">
         <v>13.5</v>
       </c>
-      <c r="AK9">
-        <v>14.5</v>
-      </c>
-      <c r="AL9">
-        <v>30</v>
-      </c>
-      <c r="AM9">
-        <v>95</v>
-      </c>
-      <c r="AN9">
-        <v>6</v>
-      </c>
-      <c r="AO9">
-        <v>85</v>
-      </c>
-      <c r="AP9">
+      <c r="BN9">
+        <v>4.6</v>
+      </c>
+      <c r="BO9">
+        <v>4.2</v>
+      </c>
+      <c r="BP9">
+        <v>11.5</v>
+      </c>
+      <c r="BQ9">
+        <v>6.6</v>
+      </c>
+      <c r="BR9">
+        <v>25</v>
+      </c>
+      <c r="BS9">
+        <v>9.6</v>
+      </c>
+      <c r="BT9">
+        <v>8.4</v>
+      </c>
+      <c r="BU9">
+        <v>7.4</v>
+      </c>
+      <c r="BV9">
+        <v>40</v>
+      </c>
+      <c r="BW9">
         <v>11</v>
       </c>
-      <c r="AQ9">
-        <v>30</v>
-      </c>
-      <c r="AR9">
-        <v>60</v>
-      </c>
-      <c r="AS9">
-        <v>9</v>
-      </c>
-      <c r="AT9">
-        <v>10.5</v>
-      </c>
-      <c r="AU9">
-        <v>11</v>
-      </c>
-      <c r="AV9">
-        <v>25</v>
-      </c>
-      <c r="AW9">
-        <v>10.5</v>
-      </c>
-      <c r="AX9">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY9">
-        <v>9.6</v>
-      </c>
-      <c r="AZ9">
+      <c r="BX9">
+        <v>44</v>
+      </c>
+      <c r="BY9">
+        <v>11.5</v>
+      </c>
+      <c r="BZ9">
         <v>19</v>
       </c>
-      <c r="BA9">
-        <v>65</v>
-      </c>
-      <c r="BB9">
-        <v>12</v>
-      </c>
-      <c r="BC9">
-        <v>12.5</v>
-      </c>
-      <c r="BD9">
-        <v>8.4</v>
-      </c>
-      <c r="BE9">
-        <v>10.5</v>
-      </c>
-      <c r="BF9">
-        <v>4.6</v>
-      </c>
-      <c r="BG9">
-        <v>60</v>
-      </c>
-      <c r="BH9">
-        <v>4.7</v>
-      </c>
-      <c r="BI9">
-        <v>4.1</v>
-      </c>
-      <c r="BJ9">
-        <v>12.5</v>
-      </c>
-      <c r="BK9">
-        <v>4.6</v>
-      </c>
-      <c r="BL9">
-        <v>1000</v>
-      </c>
-      <c r="BM9">
-        <v>6</v>
-      </c>
-      <c r="BN9">
-        <v>4.3</v>
-      </c>
-      <c r="BO9">
-        <v>3.8</v>
-      </c>
-      <c r="BP9">
-        <v>10.5</v>
-      </c>
-      <c r="BQ9">
-        <v>7.4</v>
-      </c>
-      <c r="BR9">
-        <v>24</v>
-      </c>
-      <c r="BS9">
-        <v>5.1</v>
-      </c>
-      <c r="BT9">
-        <v>13.5</v>
-      </c>
-      <c r="BU9">
-        <v>4.7</v>
-      </c>
-      <c r="BV9">
-        <v>70</v>
-      </c>
-      <c r="BW9">
-        <v>5.9</v>
-      </c>
-      <c r="BX9">
-        <v>65</v>
-      </c>
-      <c r="BY9">
-        <v>5.8</v>
-      </c>
-      <c r="BZ9">
-        <v>14</v>
-      </c>
       <c r="CA9">
-        <v>4.8</v>
+        <v>8.6</v>
       </c>
       <c r="CB9" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2882,241 +2894,241 @@
         <v>84</v>
       </c>
       <c r="B10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D10" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E10" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="F10">
-        <v>1.8</v>
+        <v>2.54</v>
       </c>
       <c r="G10">
-        <v>1.81</v>
+        <v>2.58</v>
       </c>
       <c r="H10">
-        <v>4.8</v>
+        <v>3.25</v>
       </c>
       <c r="I10">
-        <v>4.9</v>
+        <v>3.35</v>
       </c>
       <c r="J10">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="K10">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="L10">
-        <v>1.36</v>
+        <v>1.51</v>
       </c>
       <c r="M10">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="N10">
-        <v>4.4</v>
+        <v>2.98</v>
       </c>
       <c r="O10">
-        <v>1.27</v>
+        <v>1.46</v>
       </c>
       <c r="P10">
-        <v>2.2</v>
+        <v>1.66</v>
       </c>
       <c r="Q10">
-        <v>1.8</v>
+        <v>2.38</v>
       </c>
       <c r="R10">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="S10">
-        <v>3</v>
+        <v>4.7</v>
       </c>
       <c r="T10">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="U10">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="V10">
-        <v>1.26</v>
+        <v>1.43</v>
       </c>
       <c r="W10">
-        <v>2.24</v>
+        <v>1.63</v>
       </c>
       <c r="X10">
-        <v>18</v>
+        <v>10.5</v>
       </c>
       <c r="Y10">
-        <v>18.5</v>
+        <v>10</v>
       </c>
       <c r="Z10">
+        <v>21</v>
+      </c>
+      <c r="AA10">
+        <v>60</v>
+      </c>
+      <c r="AB10">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC10">
+        <v>7.4</v>
+      </c>
+      <c r="AD10">
+        <v>15</v>
+      </c>
+      <c r="AE10">
+        <v>46</v>
+      </c>
+      <c r="AF10">
+        <v>15</v>
+      </c>
+      <c r="AG10">
+        <v>12.5</v>
+      </c>
+      <c r="AH10">
+        <v>21</v>
+      </c>
+      <c r="AI10">
+        <v>70</v>
+      </c>
+      <c r="AJ10">
+        <v>38</v>
+      </c>
+      <c r="AK10">
         <v>36</v>
       </c>
-      <c r="AA10">
-        <v>110</v>
-      </c>
-      <c r="AB10">
-        <v>9.6</v>
-      </c>
-      <c r="AC10">
-        <v>9.4</v>
-      </c>
-      <c r="AD10">
-        <v>18.5</v>
-      </c>
-      <c r="AE10">
-        <v>60</v>
-      </c>
-      <c r="AF10">
-        <v>11.5</v>
-      </c>
-      <c r="AG10">
-        <v>10.5</v>
-      </c>
-      <c r="AH10">
-        <v>19</v>
-      </c>
-      <c r="AI10">
-        <v>60</v>
-      </c>
-      <c r="AJ10">
-        <v>18.5</v>
-      </c>
-      <c r="AK10">
-        <v>18</v>
-      </c>
       <c r="AL10">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="AM10">
-        <v>90</v>
+        <v>170</v>
       </c>
       <c r="AN10">
-        <v>9.800000000000001</v>
+        <v>34</v>
       </c>
       <c r="AO10">
         <v>55</v>
       </c>
       <c r="AP10">
-        <v>17</v>
+        <v>9.6</v>
       </c>
       <c r="AQ10">
-        <v>17</v>
+        <v>9.4</v>
       </c>
       <c r="AR10">
-        <v>34</v>
+        <v>18.5</v>
       </c>
       <c r="AS10">
-        <v>19.5</v>
+        <v>50</v>
       </c>
       <c r="AT10">
+        <v>8</v>
+      </c>
+      <c r="AU10">
+        <v>6.8</v>
+      </c>
+      <c r="AV10">
+        <v>13</v>
+      </c>
+      <c r="AW10">
+        <v>38</v>
+      </c>
+      <c r="AX10">
+        <v>13</v>
+      </c>
+      <c r="AY10">
+        <v>11</v>
+      </c>
+      <c r="AZ10">
+        <v>19</v>
+      </c>
+      <c r="BA10">
+        <v>55</v>
+      </c>
+      <c r="BB10">
+        <v>32</v>
+      </c>
+      <c r="BC10">
+        <v>28</v>
+      </c>
+      <c r="BD10">
+        <v>48</v>
+      </c>
+      <c r="BE10">
+        <v>15</v>
+      </c>
+      <c r="BF10">
+        <v>27</v>
+      </c>
+      <c r="BG10">
+        <v>42</v>
+      </c>
+      <c r="BH10">
+        <v>2.86</v>
+      </c>
+      <c r="BI10">
+        <v>2.68</v>
+      </c>
+      <c r="BJ10">
+        <v>10.5</v>
+      </c>
+      <c r="BK10">
         <v>9.199999999999999</v>
       </c>
-      <c r="AU10">
-        <v>9</v>
-      </c>
-      <c r="AV10">
-        <v>17</v>
-      </c>
-      <c r="AW10">
-        <v>48</v>
-      </c>
-      <c r="AX10">
-        <v>11</v>
-      </c>
-      <c r="AY10">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ10">
-        <v>17.5</v>
-      </c>
-      <c r="BA10">
-        <v>50</v>
-      </c>
-      <c r="BB10">
-        <v>17.5</v>
-      </c>
-      <c r="BC10">
-        <v>17</v>
-      </c>
-      <c r="BD10">
-        <v>28</v>
-      </c>
-      <c r="BE10">
-        <v>19</v>
-      </c>
-      <c r="BF10">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BG10">
-        <v>44</v>
-      </c>
-      <c r="BH10">
-        <v>3.8</v>
-      </c>
-      <c r="BI10">
-        <v>3.55</v>
-      </c>
-      <c r="BJ10">
+      <c r="BL10">
+        <v>1000</v>
+      </c>
+      <c r="BM10">
+        <v>15.5</v>
+      </c>
+      <c r="BN10">
+        <v>5.3</v>
+      </c>
+      <c r="BO10">
+        <v>4.7</v>
+      </c>
+      <c r="BP10">
+        <v>22</v>
+      </c>
+      <c r="BQ10">
         <v>9.6</v>
       </c>
-      <c r="BK10">
-        <v>6</v>
-      </c>
-      <c r="BL10">
-        <v>1000</v>
-      </c>
-      <c r="BM10">
-        <v>14</v>
-      </c>
-      <c r="BN10">
-        <v>4.6</v>
-      </c>
-      <c r="BO10">
-        <v>4.2</v>
-      </c>
-      <c r="BP10">
+      <c r="BR10">
+        <v>1000</v>
+      </c>
+      <c r="BS10">
         <v>12</v>
       </c>
-      <c r="BQ10">
-        <v>6.8</v>
-      </c>
-      <c r="BR10">
-        <v>25</v>
-      </c>
-      <c r="BS10">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BT10">
-        <v>8.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="BU10">
-        <v>7.4</v>
+        <v>5.6</v>
       </c>
       <c r="BV10">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BW10">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BX10">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BY10">
+        <v>12.5</v>
+      </c>
+      <c r="BZ10">
+        <v>1000</v>
+      </c>
+      <c r="CA10">
         <v>12</v>
       </c>
-      <c r="BZ10">
-        <v>19</v>
-      </c>
-      <c r="CA10">
-        <v>8.800000000000001</v>
-      </c>
       <c r="CB10" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3124,241 +3136,241 @@
         <v>84</v>
       </c>
       <c r="B11" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D11" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E11" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="F11">
-        <v>2.54</v>
+        <v>1.45</v>
       </c>
       <c r="G11">
-        <v>2.58</v>
+        <v>1.47</v>
       </c>
       <c r="H11">
-        <v>3.2</v>
+        <v>7.6</v>
       </c>
       <c r="I11">
-        <v>3.3</v>
+        <v>8</v>
       </c>
       <c r="J11">
-        <v>3.25</v>
+        <v>5.3</v>
       </c>
       <c r="K11">
-        <v>3.3</v>
+        <v>5.5</v>
       </c>
       <c r="L11">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="M11">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="N11">
-        <v>2.94</v>
+        <v>6</v>
       </c>
       <c r="O11">
-        <v>1.47</v>
+        <v>1.17</v>
       </c>
       <c r="P11">
-        <v>1.68</v>
+        <v>2.68</v>
       </c>
       <c r="Q11">
-        <v>2.4</v>
+        <v>1.54</v>
       </c>
       <c r="R11">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="S11">
-        <v>4.7</v>
+        <v>2.26</v>
       </c>
       <c r="T11">
-        <v>2.02</v>
+        <v>1.74</v>
       </c>
       <c r="U11">
-        <v>1.9</v>
+        <v>2.18</v>
       </c>
       <c r="V11">
-        <v>1.43</v>
+        <v>1.14</v>
       </c>
       <c r="W11">
-        <v>1.63</v>
+        <v>3.1</v>
       </c>
       <c r="X11">
+        <v>28</v>
+      </c>
+      <c r="Y11">
+        <v>38</v>
+      </c>
+      <c r="Z11">
+        <v>75</v>
+      </c>
+      <c r="AA11">
+        <v>230</v>
+      </c>
+      <c r="AB11">
+        <v>12.5</v>
+      </c>
+      <c r="AC11">
+        <v>12.5</v>
+      </c>
+      <c r="AD11">
+        <v>32</v>
+      </c>
+      <c r="AE11">
+        <v>100</v>
+      </c>
+      <c r="AF11">
         <v>10.5</v>
       </c>
-      <c r="Y11">
-        <v>10</v>
-      </c>
-      <c r="Z11">
+      <c r="AG11">
+        <v>10.5</v>
+      </c>
+      <c r="AH11">
         <v>22</v>
       </c>
-      <c r="AA11">
+      <c r="AI11">
+        <v>80</v>
+      </c>
+      <c r="AJ11">
+        <v>13.5</v>
+      </c>
+      <c r="AK11">
+        <v>14.5</v>
+      </c>
+      <c r="AL11">
+        <v>29</v>
+      </c>
+      <c r="AM11">
+        <v>110</v>
+      </c>
+      <c r="AN11">
+        <v>5.1</v>
+      </c>
+      <c r="AO11">
+        <v>90</v>
+      </c>
+      <c r="AP11">
+        <v>23</v>
+      </c>
+      <c r="AQ11">
+        <v>30</v>
+      </c>
+      <c r="AR11">
         <v>60</v>
       </c>
-      <c r="AB11">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AC11">
-        <v>7.4</v>
-      </c>
-      <c r="AD11">
-        <v>15</v>
-      </c>
-      <c r="AE11">
-        <v>50</v>
-      </c>
-      <c r="AF11">
-        <v>15</v>
-      </c>
-      <c r="AG11">
-        <v>12.5</v>
-      </c>
-      <c r="AH11">
-        <v>23</v>
-      </c>
-      <c r="AI11">
-        <v>75</v>
-      </c>
-      <c r="AJ11">
-        <v>36</v>
-      </c>
-      <c r="AK11">
-        <v>36</v>
-      </c>
-      <c r="AL11">
-        <v>60</v>
-      </c>
-      <c r="AM11">
-        <v>170</v>
-      </c>
-      <c r="AN11">
-        <v>32</v>
-      </c>
-      <c r="AO11">
-        <v>55</v>
-      </c>
-      <c r="AP11">
+      <c r="AS11">
+        <v>13</v>
+      </c>
+      <c r="AT11">
+        <v>10.5</v>
+      </c>
+      <c r="AU11">
+        <v>11</v>
+      </c>
+      <c r="AV11">
+        <v>25</v>
+      </c>
+      <c r="AW11">
+        <v>14.5</v>
+      </c>
+      <c r="AX11">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY11">
         <v>9.6</v>
-      </c>
-      <c r="AQ11">
-        <v>9.4</v>
-      </c>
-      <c r="AR11">
-        <v>18.5</v>
-      </c>
-      <c r="AS11">
-        <v>50</v>
-      </c>
-      <c r="AT11">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU11">
-        <v>6.8</v>
-      </c>
-      <c r="AV11">
-        <v>13</v>
-      </c>
-      <c r="AW11">
-        <v>11.5</v>
-      </c>
-      <c r="AX11">
-        <v>13</v>
-      </c>
-      <c r="AY11">
-        <v>11</v>
       </c>
       <c r="AZ11">
         <v>18.5</v>
       </c>
       <c r="BA11">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="BB11">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="BC11">
-        <v>28</v>
+        <v>12.5</v>
       </c>
       <c r="BD11">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="BE11">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BF11">
-        <v>27</v>
+        <v>4.6</v>
       </c>
       <c r="BG11">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="BH11">
-        <v>2.86</v>
+        <v>4.7</v>
       </c>
       <c r="BI11">
-        <v>2.68</v>
+        <v>4.1</v>
       </c>
       <c r="BJ11">
+        <v>12.5</v>
+      </c>
+      <c r="BK11">
+        <v>4.6</v>
+      </c>
+      <c r="BL11">
+        <v>1000</v>
+      </c>
+      <c r="BM11">
+        <v>6</v>
+      </c>
+      <c r="BN11">
+        <v>4.3</v>
+      </c>
+      <c r="BO11">
+        <v>3.8</v>
+      </c>
+      <c r="BP11">
         <v>10.5</v>
       </c>
-      <c r="BK11">
-        <v>9.4</v>
-      </c>
-      <c r="BL11">
-        <v>1000</v>
-      </c>
-      <c r="BM11">
-        <v>16.5</v>
-      </c>
-      <c r="BN11">
-        <v>5.3</v>
-      </c>
-      <c r="BO11">
+      <c r="BQ11">
+        <v>7.4</v>
+      </c>
+      <c r="BR11">
+        <v>24</v>
+      </c>
+      <c r="BS11">
+        <v>5.1</v>
+      </c>
+      <c r="BT11">
+        <v>13.5</v>
+      </c>
+      <c r="BU11">
         <v>4.7</v>
       </c>
-      <c r="BP11">
-        <v>21</v>
-      </c>
-      <c r="BQ11">
-        <v>10.5</v>
-      </c>
-      <c r="BR11">
-        <v>55</v>
-      </c>
-      <c r="BS11">
-        <v>12.5</v>
-      </c>
-      <c r="BT11">
-        <v>6.4</v>
-      </c>
-      <c r="BU11">
-        <v>5.6</v>
-      </c>
       <c r="BV11">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="BW11">
-        <v>11</v>
+        <v>5.9</v>
       </c>
       <c r="BX11">
         <v>65</v>
       </c>
       <c r="BY11">
-        <v>13</v>
+        <v>5.8</v>
       </c>
       <c r="BZ11">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="CA11">
-        <v>12.5</v>
+        <v>8.4</v>
       </c>
       <c r="CB11" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3366,22 +3378,22 @@
         <v>84</v>
       </c>
       <c r="B12" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D12" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E12" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="F12">
         <v>2.76</v>
       </c>
       <c r="G12">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="H12">
         <v>2.86</v>
@@ -3405,10 +3417,10 @@
         <v>3.3</v>
       </c>
       <c r="O12">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P12">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="Q12">
         <v>2.2</v>
@@ -3417,7 +3429,7 @@
         <v>1.29</v>
       </c>
       <c r="S12">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T12">
         <v>1.91</v>
@@ -3429,7 +3441,7 @@
         <v>1.53</v>
       </c>
       <c r="W12">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="X12">
         <v>12.5</v>
@@ -3438,19 +3450,19 @@
         <v>10.5</v>
       </c>
       <c r="Z12">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AA12">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AB12">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC12">
         <v>7.4</v>
       </c>
       <c r="AD12">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE12">
         <v>36</v>
@@ -3465,7 +3477,7 @@
         <v>19</v>
       </c>
       <c r="AI12">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AJ12">
         <v>42</v>
@@ -3480,7 +3492,7 @@
         <v>120</v>
       </c>
       <c r="AN12">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AO12">
         <v>36</v>
@@ -3507,7 +3519,7 @@
         <v>12</v>
       </c>
       <c r="AW12">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AX12">
         <v>15.5</v>
@@ -3522,19 +3534,19 @@
         <v>44</v>
       </c>
       <c r="BB12">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BC12">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BD12">
         <v>44</v>
       </c>
       <c r="BE12">
-        <v>34</v>
+        <v>14.5</v>
       </c>
       <c r="BF12">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BG12">
         <v>30</v>
@@ -3543,7 +3555,7 @@
         <v>3.05</v>
       </c>
       <c r="BI12">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="BJ12">
         <v>11.5</v>
@@ -3567,13 +3579,13 @@
         <v>24</v>
       </c>
       <c r="BQ12">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BR12">
         <v>40</v>
       </c>
       <c r="BS12">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT12">
         <v>5.9</v>
@@ -3585,10 +3597,10 @@
         <v>25</v>
       </c>
       <c r="BW12">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BX12">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BY12">
         <v>9.4</v>
@@ -3600,7 +3612,7 @@
         <v>9</v>
       </c>
       <c r="CB12" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3608,16 +3620,16 @@
         <v>84</v>
       </c>
       <c r="B13" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D13" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E13" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F13">
         <v>1.24</v>
@@ -3650,7 +3662,7 @@
         <v>1.19</v>
       </c>
       <c r="P13">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="Q13">
         <v>1.57</v>
@@ -3677,7 +3689,7 @@
         <v>26</v>
       </c>
       <c r="Y13">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="Z13">
         <v>180</v>
@@ -3686,7 +3698,7 @@
         <v>900</v>
       </c>
       <c r="AB13">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC13">
         <v>16</v>
@@ -3698,7 +3710,7 @@
         <v>310</v>
       </c>
       <c r="AF13">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AG13">
         <v>11.5</v>
@@ -3710,7 +3722,7 @@
         <v>220</v>
       </c>
       <c r="AJ13">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AK13">
         <v>14</v>
@@ -3719,22 +3731,22 @@
         <v>46</v>
       </c>
       <c r="AM13">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AN13">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AO13">
         <v>360</v>
       </c>
       <c r="AP13">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ13">
         <v>42</v>
       </c>
       <c r="AR13">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS13">
         <v>20</v>
@@ -3749,16 +3761,16 @@
         <v>48</v>
       </c>
       <c r="AW13">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX13">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AY13">
         <v>11</v>
       </c>
       <c r="AZ13">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BA13">
         <v>23</v>
@@ -3773,10 +3785,10 @@
         <v>38</v>
       </c>
       <c r="BE13">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BF13">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BG13">
         <v>21</v>
@@ -3791,7 +3803,7 @@
         <v>16</v>
       </c>
       <c r="BK13">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BL13">
         <v>210</v>
@@ -3800,7 +3812,7 @@
         <v>23</v>
       </c>
       <c r="BN13">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="BO13">
         <v>3.45</v>
@@ -3812,28 +3824,28 @@
         <v>5.9</v>
       </c>
       <c r="BR13">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BS13">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="BT13">
         <v>21</v>
       </c>
       <c r="BU13">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BV13">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="BW13">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BX13">
         <v>130</v>
       </c>
       <c r="BY13">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BZ13">
         <v>0</v>
@@ -3842,7 +3854,249 @@
         <v>0</v>
       </c>
       <c r="CB13" t="s">
-        <v>116</v>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="14" spans="1:80">
+      <c r="A14" t="s">
+        <v>85</v>
+      </c>
+      <c r="B14" t="s">
+        <v>86</v>
+      </c>
+      <c r="C14" t="s">
+        <v>93</v>
+      </c>
+      <c r="D14" t="s">
+        <v>106</v>
+      </c>
+      <c r="E14" t="s">
+        <v>119</v>
+      </c>
+      <c r="F14">
+        <v>3.1</v>
+      </c>
+      <c r="G14">
+        <v>4.1</v>
+      </c>
+      <c r="H14">
+        <v>2.4</v>
+      </c>
+      <c r="I14">
+        <v>2.84</v>
+      </c>
+      <c r="J14">
+        <v>2.8</v>
+      </c>
+      <c r="K14">
+        <v>3.15</v>
+      </c>
+      <c r="L14">
+        <v>1.01</v>
+      </c>
+      <c r="M14">
+        <v>1.15</v>
+      </c>
+      <c r="N14">
+        <v>2.32</v>
+      </c>
+      <c r="O14">
+        <v>1.63</v>
+      </c>
+      <c r="P14">
+        <v>1.46</v>
+      </c>
+      <c r="Q14">
+        <v>2.66</v>
+      </c>
+      <c r="R14">
+        <v>1.14</v>
+      </c>
+      <c r="S14">
+        <v>1.01</v>
+      </c>
+      <c r="T14">
+        <v>2.24</v>
+      </c>
+      <c r="U14">
+        <v>1.64</v>
+      </c>
+      <c r="V14">
+        <v>1.54</v>
+      </c>
+      <c r="W14">
+        <v>1.32</v>
+      </c>
+      <c r="X14">
+        <v>8.6</v>
+      </c>
+      <c r="Y14">
+        <v>8.4</v>
+      </c>
+      <c r="Z14">
+        <v>17.5</v>
+      </c>
+      <c r="AA14">
+        <v>55</v>
+      </c>
+      <c r="AB14">
+        <v>11</v>
+      </c>
+      <c r="AC14">
+        <v>7.4</v>
+      </c>
+      <c r="AD14">
+        <v>16.5</v>
+      </c>
+      <c r="AE14">
+        <v>55</v>
+      </c>
+      <c r="AF14">
+        <v>26</v>
+      </c>
+      <c r="AG14">
+        <v>22</v>
+      </c>
+      <c r="AH14">
+        <v>34</v>
+      </c>
+      <c r="AI14">
+        <v>100</v>
+      </c>
+      <c r="AJ14">
+        <v>110</v>
+      </c>
+      <c r="AK14">
+        <v>85</v>
+      </c>
+      <c r="AL14">
+        <v>130</v>
+      </c>
+      <c r="AM14">
+        <v>310</v>
+      </c>
+      <c r="AN14">
+        <v>140</v>
+      </c>
+      <c r="AO14">
+        <v>65</v>
+      </c>
+      <c r="AP14">
+        <v>1.01</v>
+      </c>
+      <c r="AQ14">
+        <v>1.01</v>
+      </c>
+      <c r="AR14">
+        <v>1.01</v>
+      </c>
+      <c r="AS14">
+        <v>1.01</v>
+      </c>
+      <c r="AT14">
+        <v>1.01</v>
+      </c>
+      <c r="AU14">
+        <v>1.01</v>
+      </c>
+      <c r="AV14">
+        <v>1.01</v>
+      </c>
+      <c r="AW14">
+        <v>1.01</v>
+      </c>
+      <c r="AX14">
+        <v>1.01</v>
+      </c>
+      <c r="AY14">
+        <v>1.01</v>
+      </c>
+      <c r="AZ14">
+        <v>1.01</v>
+      </c>
+      <c r="BA14">
+        <v>1.01</v>
+      </c>
+      <c r="BB14">
+        <v>1.01</v>
+      </c>
+      <c r="BC14">
+        <v>1.01</v>
+      </c>
+      <c r="BD14">
+        <v>1.01</v>
+      </c>
+      <c r="BE14">
+        <v>1.01</v>
+      </c>
+      <c r="BF14">
+        <v>1.01</v>
+      </c>
+      <c r="BG14">
+        <v>1.01</v>
+      </c>
+      <c r="BH14">
+        <v>2.6</v>
+      </c>
+      <c r="BI14">
+        <v>1.01</v>
+      </c>
+      <c r="BJ14">
+        <v>1000</v>
+      </c>
+      <c r="BK14">
+        <v>1.64</v>
+      </c>
+      <c r="BL14">
+        <v>1000</v>
+      </c>
+      <c r="BM14">
+        <v>1.64</v>
+      </c>
+      <c r="BN14">
+        <v>1000</v>
+      </c>
+      <c r="BO14">
+        <v>1.64</v>
+      </c>
+      <c r="BP14">
+        <v>1000</v>
+      </c>
+      <c r="BQ14">
+        <v>1.64</v>
+      </c>
+      <c r="BR14">
+        <v>1000</v>
+      </c>
+      <c r="BS14">
+        <v>1.64</v>
+      </c>
+      <c r="BT14">
+        <v>1000</v>
+      </c>
+      <c r="BU14">
+        <v>1.64</v>
+      </c>
+      <c r="BV14">
+        <v>1000</v>
+      </c>
+      <c r="BW14">
+        <v>1.64</v>
+      </c>
+      <c r="BX14">
+        <v>1000</v>
+      </c>
+      <c r="BY14">
+        <v>1.64</v>
+      </c>
+      <c r="BZ14">
+        <v>0</v>
+      </c>
+      <c r="CA14">
+        <v>0</v>
+      </c>
+      <c r="CB14" t="s">
+        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-24.xlsx
@@ -376,7 +376,7 @@
     <t>IRT Tanger</t>
   </si>
   <si>
-    <t>2026-09-23 00:02:48</t>
+    <t>2026-09-23 02:13:27</t>
   </si>
 </sst>
 </file>
@@ -988,7 +988,7 @@
         <v>4</v>
       </c>
       <c r="L2">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="M2">
         <v>1.08</v>
@@ -1000,25 +1000,25 @@
         <v>1.38</v>
       </c>
       <c r="P2">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q2">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R2">
         <v>1.31</v>
       </c>
       <c r="S2">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="T2">
         <v>2.06</v>
       </c>
       <c r="U2">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="V2">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W2">
         <v>2.36</v>
@@ -1093,7 +1093,7 @@
         <v>6.6</v>
       </c>
       <c r="AU2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV2">
         <v>20</v>
@@ -1135,7 +1135,7 @@
         <v>3.7</v>
       </c>
       <c r="BI2">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="BJ2">
         <v>13.5</v>
@@ -1147,10 +1147,10 @@
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BN2">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BO2">
         <v>3.7</v>
@@ -1159,37 +1159,37 @@
         <v>14.5</v>
       </c>
       <c r="BQ2">
-        <v>4.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR2">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BS2">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BT2">
         <v>11.5</v>
       </c>
       <c r="BU2">
-        <v>3.95</v>
+        <v>7</v>
       </c>
       <c r="BV2">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BW2">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BX2">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="BY2">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BZ2">
         <v>32</v>
       </c>
       <c r="CA2">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="CB2" t="s">
         <v>120</v>
@@ -1236,7 +1236,7 @@
         <v>1.04</v>
       </c>
       <c r="N3">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="O3">
         <v>1.21</v>
@@ -1245,13 +1245,13 @@
         <v>2.52</v>
       </c>
       <c r="Q3">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="R3">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="S3">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="T3">
         <v>1.59</v>
@@ -1266,7 +1266,7 @@
         <v>2.04</v>
       </c>
       <c r="X3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y3">
         <v>21</v>
@@ -1287,16 +1287,16 @@
         <v>16.5</v>
       </c>
       <c r="AE3">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AF3">
         <v>14.5</v>
       </c>
       <c r="AG3">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH3">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI3">
         <v>55</v>
@@ -1305,7 +1305,7 @@
         <v>23</v>
       </c>
       <c r="AK3">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AL3">
         <v>26</v>
@@ -1314,7 +1314,7 @@
         <v>65</v>
       </c>
       <c r="AN3">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO3">
         <v>32</v>
@@ -1323,7 +1323,7 @@
         <v>20</v>
       </c>
       <c r="AQ3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR3">
         <v>30</v>
@@ -1353,7 +1353,7 @@
         <v>14.5</v>
       </c>
       <c r="BA3">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BB3">
         <v>21</v>
@@ -1371,7 +1371,7 @@
         <v>8.6</v>
       </c>
       <c r="BG3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BH3">
         <v>4.2</v>
@@ -1389,7 +1389,7 @@
         <v>100</v>
       </c>
       <c r="BM3">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BN3">
         <v>5</v>
@@ -1398,10 +1398,10 @@
         <v>4.5</v>
       </c>
       <c r="BP3">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BQ3">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BR3">
         <v>27</v>
@@ -1410,22 +1410,22 @@
         <v>7.2</v>
       </c>
       <c r="BT3">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BU3">
         <v>6.8</v>
       </c>
       <c r="BV3">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BW3">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BX3">
         <v>40</v>
       </c>
       <c r="BY3">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BZ3">
         <v>19</v>
@@ -1454,16 +1454,16 @@
         <v>109</v>
       </c>
       <c r="F4">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="G4">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="H4">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I4">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="J4">
         <v>4</v>
@@ -1472,40 +1472,40 @@
         <v>4.4</v>
       </c>
       <c r="L4">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M4">
         <v>1.04</v>
       </c>
       <c r="N4">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="O4">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P4">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="Q4">
         <v>1.64</v>
       </c>
       <c r="R4">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="S4">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="T4">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="U4">
         <v>2.36</v>
       </c>
       <c r="V4">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W4">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="X4">
         <v>27</v>
@@ -1562,7 +1562,7 @@
         <v>40</v>
       </c>
       <c r="AP4">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AQ4">
         <v>13.5</v>
@@ -1586,7 +1586,7 @@
         <v>1.03</v>
       </c>
       <c r="AX4">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AY4">
         <v>8</v>
@@ -1598,22 +1598,22 @@
         <v>1.03</v>
       </c>
       <c r="BB4">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BC4">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BD4">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="BE4">
         <v>1.03</v>
       </c>
       <c r="BF4">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BG4">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1708,7 +1708,7 @@
         <v>110</v>
       </c>
       <c r="J5">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="K5">
         <v>950</v>
@@ -1723,19 +1723,19 @@
         <v>1.13</v>
       </c>
       <c r="O5">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P5">
         <v>1.13</v>
       </c>
       <c r="Q5">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="R5">
         <v>1.08</v>
       </c>
       <c r="S5">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="T5">
         <v>1.01</v>
@@ -1744,10 +1744,10 @@
         <v>1.01</v>
       </c>
       <c r="V5">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W5">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X5">
         <v>1000</v>
@@ -1938,16 +1938,16 @@
         <v>111</v>
       </c>
       <c r="F6">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="G6">
         <v>3.9</v>
       </c>
       <c r="H6">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="I6">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="J6">
         <v>2.88</v>
@@ -1956,7 +1956,7 @@
         <v>2.92</v>
       </c>
       <c r="L6">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="M6">
         <v>1.17</v>
@@ -1965,7 +1965,7 @@
         <v>2.22</v>
       </c>
       <c r="O6">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="P6">
         <v>1.38</v>
@@ -1980,13 +1980,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="T6">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="U6">
         <v>1.61</v>
       </c>
       <c r="V6">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W6">
         <v>1.34</v>
@@ -1998,7 +1998,7 @@
         <v>6.4</v>
       </c>
       <c r="Z6">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AA6">
         <v>42</v>
@@ -2079,7 +2079,7 @@
         <v>28</v>
       </c>
       <c r="BA6">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BB6">
         <v>14.5</v>
@@ -2091,19 +2091,19 @@
         <v>13.5</v>
       </c>
       <c r="BE6">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BF6">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BG6">
         <v>44</v>
       </c>
       <c r="BH6">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="BI6">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="BJ6">
         <v>13.5</v>
@@ -2124,7 +2124,7 @@
         <v>6</v>
       </c>
       <c r="BP6">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BQ6">
         <v>30</v>
@@ -2180,7 +2180,7 @@
         <v>112</v>
       </c>
       <c r="F7">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G7">
         <v>17</v>
@@ -2189,7 +2189,7 @@
         <v>1.33</v>
       </c>
       <c r="I7">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="J7">
         <v>5.4</v>
@@ -2204,28 +2204,28 @@
         <v>1.08</v>
       </c>
       <c r="N7">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O7">
         <v>1.4</v>
       </c>
       <c r="P7">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="Q7">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R7">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S7">
         <v>4.1</v>
       </c>
       <c r="T7">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="U7">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="V7">
         <v>3.85</v>
@@ -2249,10 +2249,10 @@
         <v>34</v>
       </c>
       <c r="AC7">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AD7">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE7">
         <v>19</v>
@@ -2261,7 +2261,7 @@
         <v>160</v>
       </c>
       <c r="AG7">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AH7">
         <v>55</v>
@@ -2276,7 +2276,7 @@
         <v>530</v>
       </c>
       <c r="AL7">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="AM7">
         <v>560</v>
@@ -2285,7 +2285,7 @@
         <v>1000</v>
       </c>
       <c r="AO7">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AP7">
         <v>12</v>
@@ -2294,10 +2294,10 @@
         <v>5.4</v>
       </c>
       <c r="AR7">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AS7">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT7">
         <v>26</v>
@@ -2312,31 +2312,31 @@
         <v>17</v>
       </c>
       <c r="AX7">
-        <v>13</v>
+        <v>16.5</v>
       </c>
       <c r="AY7">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AZ7">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BA7">
         <v>60</v>
       </c>
       <c r="BB7">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BC7">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="BD7">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="BE7">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="BF7">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BG7">
         <v>7.2</v>
@@ -2345,10 +2345,10 @@
         <v>3.25</v>
       </c>
       <c r="BI7">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="BJ7">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BK7">
         <v>12</v>
@@ -2381,7 +2381,7 @@
         <v>3.3</v>
       </c>
       <c r="BU7">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="BV7">
         <v>8</v>
@@ -2390,16 +2390,16 @@
         <v>7</v>
       </c>
       <c r="BX7">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY7">
         <v>26</v>
       </c>
       <c r="BZ7">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="CA7">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="CB7" t="s">
         <v>120</v>
@@ -2422,13 +2422,13 @@
         <v>113</v>
       </c>
       <c r="F8">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="G8">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="H8">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="I8">
         <v>2.8</v>
@@ -2437,7 +2437,7 @@
         <v>3.9</v>
       </c>
       <c r="K8">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L8">
         <v>1.29</v>
@@ -2452,10 +2452,10 @@
         <v>1.18</v>
       </c>
       <c r="P8">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="Q8">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="R8">
         <v>1.68</v>
@@ -2467,13 +2467,13 @@
         <v>1.51</v>
       </c>
       <c r="U8">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="V8">
         <v>1.55</v>
       </c>
       <c r="W8">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="X8">
         <v>25</v>
@@ -2503,7 +2503,7 @@
         <v>20</v>
       </c>
       <c r="AG8">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH8">
         <v>14</v>
@@ -2554,7 +2554,7 @@
         <v>23</v>
       </c>
       <c r="AX8">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AY8">
         <v>11.5</v>
@@ -2578,7 +2578,7 @@
         <v>44</v>
       </c>
       <c r="BF8">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BG8">
         <v>13.5</v>
@@ -2596,10 +2596,10 @@
         <v>7.2</v>
       </c>
       <c r="BL8">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BM8">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BN8">
         <v>5.9</v>
@@ -2611,13 +2611,13 @@
         <v>17</v>
       </c>
       <c r="BQ8">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR8">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BS8">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BT8">
         <v>6.4</v>
@@ -2626,22 +2626,22 @@
         <v>5.8</v>
       </c>
       <c r="BV8">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BW8">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX8">
         <v>26</v>
       </c>
       <c r="BY8">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ8">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="CA8">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB8" t="s">
         <v>120</v>
@@ -2670,10 +2670,10 @@
         <v>1.8</v>
       </c>
       <c r="H9">
+        <v>4.7</v>
+      </c>
+      <c r="I9">
         <v>4.8</v>
-      </c>
-      <c r="I9">
-        <v>4.9</v>
       </c>
       <c r="J9">
         <v>4.2</v>
@@ -2688,31 +2688,31 @@
         <v>1.05</v>
       </c>
       <c r="N9">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O9">
         <v>1.26</v>
       </c>
       <c r="P9">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="Q9">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="R9">
         <v>1.48</v>
       </c>
       <c r="S9">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="T9">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="U9">
         <v>2.24</v>
       </c>
       <c r="V9">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W9">
         <v>2.24</v>
@@ -2721,7 +2721,7 @@
         <v>18.5</v>
       </c>
       <c r="Y9">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="Z9">
         <v>38</v>
@@ -2730,7 +2730,7 @@
         <v>110</v>
       </c>
       <c r="AB9">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC9">
         <v>9.4</v>
@@ -2742,7 +2742,7 @@
         <v>60</v>
       </c>
       <c r="AF9">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AG9">
         <v>10.5</v>
@@ -2775,13 +2775,13 @@
         <v>17</v>
       </c>
       <c r="AQ9">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AR9">
         <v>34</v>
       </c>
       <c r="AS9">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AT9">
         <v>9.6</v>
@@ -2802,13 +2802,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ9">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BA9">
         <v>50</v>
       </c>
       <c r="BB9">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BC9">
         <v>16.5</v>
@@ -2817,13 +2817,13 @@
         <v>28</v>
       </c>
       <c r="BE9">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="BF9">
         <v>9</v>
       </c>
       <c r="BG9">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="BH9">
         <v>3.85</v>
@@ -2841,7 +2841,7 @@
         <v>110</v>
       </c>
       <c r="BM9">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BN9">
         <v>4.6</v>
@@ -2859,7 +2859,7 @@
         <v>25</v>
       </c>
       <c r="BS9">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT9">
         <v>8.4</v>
@@ -2868,7 +2868,7 @@
         <v>7.4</v>
       </c>
       <c r="BV9">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BW9">
         <v>11</v>
@@ -2924,7 +2924,7 @@
         <v>3.3</v>
       </c>
       <c r="L10">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="M10">
         <v>1.1</v>
@@ -2933,13 +2933,13 @@
         <v>2.98</v>
       </c>
       <c r="O10">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P10">
         <v>1.66</v>
       </c>
       <c r="Q10">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R10">
         <v>1.25</v>
@@ -2948,10 +2948,10 @@
         <v>4.7</v>
       </c>
       <c r="T10">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="U10">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="V10">
         <v>1.43</v>
@@ -2963,7 +2963,7 @@
         <v>10.5</v>
       </c>
       <c r="Y10">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z10">
         <v>21</v>
@@ -3005,7 +3005,7 @@
         <v>55</v>
       </c>
       <c r="AM10">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AN10">
         <v>34</v>
@@ -3026,7 +3026,7 @@
         <v>50</v>
       </c>
       <c r="AT10">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AU10">
         <v>6.8</v>
@@ -3056,16 +3056,16 @@
         <v>28</v>
       </c>
       <c r="BD10">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="BE10">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BF10">
         <v>27</v>
       </c>
       <c r="BG10">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BH10">
         <v>2.86</v>
@@ -3077,13 +3077,13 @@
         <v>10.5</v>
       </c>
       <c r="BK10">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BN10">
         <v>5.3</v>
@@ -3095,16 +3095,16 @@
         <v>22</v>
       </c>
       <c r="BQ10">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BR10">
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BT10">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BU10">
         <v>5.6</v>
@@ -3113,19 +3113,19 @@
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX10">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY10">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BZ10">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="CB10" t="s">
         <v>120</v>
@@ -3178,7 +3178,7 @@
         <v>1.17</v>
       </c>
       <c r="P11">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="Q11">
         <v>1.54</v>
@@ -3190,10 +3190,10 @@
         <v>2.26</v>
       </c>
       <c r="T11">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U11">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V11">
         <v>1.14</v>
@@ -3214,16 +3214,16 @@
         <v>230</v>
       </c>
       <c r="AB11">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC11">
         <v>12.5</v>
       </c>
       <c r="AD11">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AE11">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AF11">
         <v>10.5</v>
@@ -3232,7 +3232,7 @@
         <v>10.5</v>
       </c>
       <c r="AH11">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AI11">
         <v>80</v>
@@ -3241,7 +3241,7 @@
         <v>13.5</v>
       </c>
       <c r="AK11">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AL11">
         <v>29</v>
@@ -3250,13 +3250,13 @@
         <v>110</v>
       </c>
       <c r="AN11">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AO11">
         <v>90</v>
       </c>
       <c r="AP11">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="AQ11">
         <v>30</v>
@@ -3265,19 +3265,19 @@
         <v>60</v>
       </c>
       <c r="AS11">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AT11">
         <v>10.5</v>
       </c>
       <c r="AU11">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AV11">
         <v>25</v>
       </c>
       <c r="AW11">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AX11">
         <v>9.199999999999999</v>
@@ -3289,28 +3289,28 @@
         <v>18.5</v>
       </c>
       <c r="BA11">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB11">
         <v>12</v>
       </c>
       <c r="BC11">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BD11">
         <v>24</v>
       </c>
       <c r="BE11">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BF11">
+        <v>4.7</v>
+      </c>
+      <c r="BG11">
+        <v>13.5</v>
+      </c>
+      <c r="BH11">
         <v>4.6</v>
-      </c>
-      <c r="BG11">
-        <v>12</v>
-      </c>
-      <c r="BH11">
-        <v>4.7</v>
       </c>
       <c r="BI11">
         <v>4.1</v>
@@ -3325,25 +3325,25 @@
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BN11">
         <v>4.3</v>
       </c>
       <c r="BO11">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BP11">
         <v>10.5</v>
       </c>
       <c r="BQ11">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BR11">
         <v>24</v>
       </c>
       <c r="BS11">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BT11">
         <v>13.5</v>
@@ -3355,19 +3355,19 @@
         <v>70</v>
       </c>
       <c r="BW11">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BX11">
         <v>65</v>
       </c>
       <c r="BY11">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BZ11">
         <v>14</v>
       </c>
       <c r="CA11">
-        <v>8.4</v>
+        <v>4.8</v>
       </c>
       <c r="CB11" t="s">
         <v>120</v>
@@ -3390,7 +3390,7 @@
         <v>117</v>
       </c>
       <c r="F12">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="G12">
         <v>2.8</v>
@@ -3591,7 +3591,7 @@
         <v>5.9</v>
       </c>
       <c r="BU12">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BV12">
         <v>25</v>
@@ -3647,7 +3647,7 @@
         <v>7</v>
       </c>
       <c r="K13">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="L13">
         <v>1.29</v>
@@ -3656,7 +3656,7 @@
         <v>1.04</v>
       </c>
       <c r="N13">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="O13">
         <v>1.19</v>
@@ -3671,10 +3671,10 @@
         <v>1.66</v>
       </c>
       <c r="S13">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="T13">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="U13">
         <v>1.73</v>
@@ -3692,7 +3692,7 @@
         <v>55</v>
       </c>
       <c r="Z13">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AA13">
         <v>900</v>
@@ -3719,7 +3719,7 @@
         <v>38</v>
       </c>
       <c r="AI13">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="AJ13">
         <v>8.800000000000001</v>
@@ -3731,7 +3731,7 @@
         <v>46</v>
       </c>
       <c r="AM13">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="AN13">
         <v>3.95</v>
@@ -3740,16 +3740,16 @@
         <v>360</v>
       </c>
       <c r="AP13">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AQ13">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AR13">
         <v>22</v>
       </c>
       <c r="AS13">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AT13">
         <v>9.4</v>
@@ -3761,7 +3761,7 @@
         <v>48</v>
       </c>
       <c r="AW13">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX13">
         <v>7.2</v>
@@ -3788,19 +3788,19 @@
         <v>20</v>
       </c>
       <c r="BF13">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BG13">
         <v>21</v>
       </c>
       <c r="BH13">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BI13">
         <v>4.1</v>
       </c>
       <c r="BJ13">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BK13">
         <v>6.2</v>
@@ -3815,7 +3815,7 @@
         <v>3.8</v>
       </c>
       <c r="BO13">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BP13">
         <v>6.4</v>
@@ -3827,7 +3827,7 @@
         <v>28</v>
       </c>
       <c r="BS13">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BT13">
         <v>21</v>
@@ -3839,13 +3839,13 @@
         <v>170</v>
       </c>
       <c r="BW13">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BX13">
         <v>130</v>
       </c>
       <c r="BY13">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ13">
         <v>0</v>
@@ -3883,10 +3883,10 @@
         <v>2.4</v>
       </c>
       <c r="I14">
+        <v>2.76</v>
+      </c>
+      <c r="J14">
         <v>2.84</v>
-      </c>
-      <c r="J14">
-        <v>2.8</v>
       </c>
       <c r="K14">
         <v>3.15</v>
@@ -3898,10 +3898,10 @@
         <v>1.15</v>
       </c>
       <c r="N14">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="O14">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="P14">
         <v>1.46</v>
@@ -3922,7 +3922,7 @@
         <v>1.64</v>
       </c>
       <c r="V14">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="W14">
         <v>1.32</v>
@@ -3931,34 +3931,34 @@
         <v>8.6</v>
       </c>
       <c r="Y14">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="Z14">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AA14">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AB14">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AC14">
         <v>7.4</v>
       </c>
       <c r="AD14">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AE14">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AF14">
         <v>26</v>
       </c>
       <c r="AG14">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AH14">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AI14">
         <v>100</v>
@@ -3967,7 +3967,7 @@
         <v>110</v>
       </c>
       <c r="AK14">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AL14">
         <v>130</v>
@@ -3979,61 +3979,61 @@
         <v>140</v>
       </c>
       <c r="AO14">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AP14">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AQ14">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AR14">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AS14">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AT14">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AU14">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AV14">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AW14">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AX14">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AY14">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AZ14">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BA14">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BB14">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BC14">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BD14">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BE14">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BF14">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BG14">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BH14">
         <v>2.6</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-24.xlsx
@@ -376,7 +376,7 @@
     <t>IRT Tanger</t>
   </si>
   <si>
-    <t>2026-09-23 02:13:27</t>
+    <t>2026-09-23 03:30:34</t>
   </si>
 </sst>
 </file>
@@ -970,52 +970,52 @@
         <v>107</v>
       </c>
       <c r="F2">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="G2">
         <v>1.73</v>
       </c>
       <c r="H2">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="I2">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J2">
+        <v>3.95</v>
+      </c>
+      <c r="K2">
+        <v>4.2</v>
+      </c>
+      <c r="L2">
+        <v>1.4</v>
+      </c>
+      <c r="M2">
+        <v>1.07</v>
+      </c>
+      <c r="N2">
         <v>3.8</v>
       </c>
-      <c r="K2">
-        <v>4</v>
-      </c>
-      <c r="L2">
-        <v>1.45</v>
-      </c>
-      <c r="M2">
-        <v>1.08</v>
-      </c>
-      <c r="N2">
-        <v>3.45</v>
-      </c>
       <c r="O2">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="P2">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="Q2">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="R2">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="S2">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="T2">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="U2">
-        <v>1.89</v>
+        <v>1.96</v>
       </c>
       <c r="V2">
         <v>1.19</v>
@@ -1024,172 +1024,172 @@
         <v>2.36</v>
       </c>
       <c r="X2">
-        <v>13.5</v>
+        <v>18.5</v>
       </c>
       <c r="Y2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z2">
         <v>60</v>
       </c>
       <c r="AA2">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="AB2">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC2">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD2">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AE2">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AF2">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AG2">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AH2">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AI2">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AJ2">
+        <v>20</v>
+      </c>
+      <c r="AK2">
         <v>21</v>
       </c>
-      <c r="AK2">
-        <v>24</v>
-      </c>
       <c r="AL2">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AM2">
-        <v>190</v>
+        <v>150</v>
       </c>
       <c r="AN2">
+        <v>12</v>
+      </c>
+      <c r="AO2">
+        <v>130</v>
+      </c>
+      <c r="AP2">
         <v>13</v>
       </c>
-      <c r="AO2">
-        <v>170</v>
-      </c>
-      <c r="AP2">
-        <v>11.5</v>
-      </c>
       <c r="AQ2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR2">
         <v>6.4</v>
       </c>
       <c r="AS2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AT2">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV2">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AW2">
         <v>6.8</v>
       </c>
       <c r="AX2">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY2">
         <v>9</v>
       </c>
       <c r="AZ2">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="BA2">
         <v>6.8</v>
       </c>
       <c r="BB2">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BC2">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="BD2">
         <v>6.2</v>
       </c>
       <c r="BE2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BF2">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="BG2">
-        <v>36</v>
+        <v>7.2</v>
       </c>
       <c r="BH2">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="BI2">
-        <v>2.6</v>
+        <v>2.76</v>
       </c>
       <c r="BJ2">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BK2">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="BN2">
         <v>4.2</v>
       </c>
       <c r="BO2">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="BP2">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="BQ2">
-        <v>8.800000000000001</v>
+        <v>4.3</v>
       </c>
       <c r="BR2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BS2">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="BT2">
-        <v>11.5</v>
+        <v>9.4</v>
       </c>
       <c r="BU2">
-        <v>7</v>
+        <v>3.95</v>
       </c>
       <c r="BV2">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BW2">
+        <v>6.2</v>
+      </c>
+      <c r="BX2">
+        <v>75</v>
+      </c>
+      <c r="BY2">
+        <v>6.2</v>
+      </c>
+      <c r="BZ2">
+        <v>26</v>
+      </c>
+      <c r="CA2">
         <v>5.4</v>
-      </c>
-      <c r="BX2">
-        <v>1000</v>
-      </c>
-      <c r="BY2">
-        <v>5.4</v>
-      </c>
-      <c r="BZ2">
-        <v>32</v>
-      </c>
-      <c r="CA2">
-        <v>4.9</v>
       </c>
       <c r="CB2" t="s">
         <v>120</v>
@@ -1212,82 +1212,82 @@
         <v>108</v>
       </c>
       <c r="F3">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="G3">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="H3">
+        <v>4.2</v>
+      </c>
+      <c r="I3">
+        <v>4.4</v>
+      </c>
+      <c r="J3">
         <v>4.1</v>
       </c>
-      <c r="I3">
-        <v>4.3</v>
-      </c>
-      <c r="J3">
-        <v>3.95</v>
-      </c>
       <c r="K3">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L3">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="M3">
         <v>1.04</v>
       </c>
       <c r="N3">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="O3">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P3">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="Q3">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="R3">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="S3">
-        <v>2.58</v>
+        <v>2.48</v>
       </c>
       <c r="T3">
         <v>1.59</v>
       </c>
       <c r="U3">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="V3">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W3">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="X3">
+        <v>24</v>
+      </c>
+      <c r="Y3">
         <v>22</v>
       </c>
-      <c r="Y3">
-        <v>21</v>
-      </c>
       <c r="Z3">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AA3">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AB3">
         <v>13</v>
       </c>
       <c r="AC3">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD3">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AE3">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AF3">
         <v>14.5</v>
@@ -1299,10 +1299,10 @@
         <v>15.5</v>
       </c>
       <c r="AI3">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AJ3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK3">
         <v>17.5</v>
@@ -1311,10 +1311,10 @@
         <v>26</v>
       </c>
       <c r="AM3">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AN3">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AO3">
         <v>32</v>
@@ -1356,40 +1356,40 @@
         <v>38</v>
       </c>
       <c r="BB3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC3">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BD3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BE3">
         <v>50</v>
       </c>
       <c r="BF3">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="BG3">
         <v>28</v>
       </c>
       <c r="BH3">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BI3">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BJ3">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK3">
         <v>7.8</v>
       </c>
       <c r="BL3">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="BM3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BN3">
         <v>5</v>
@@ -1398,19 +1398,19 @@
         <v>4.5</v>
       </c>
       <c r="BP3">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BQ3">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BR3">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BS3">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BT3">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BU3">
         <v>6.8</v>
@@ -1419,19 +1419,19 @@
         <v>34</v>
       </c>
       <c r="BW3">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BX3">
         <v>40</v>
       </c>
       <c r="BY3">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ3">
-        <v>19</v>
+        <v>14.5</v>
       </c>
       <c r="CA3">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="CB3" t="s">
         <v>120</v>
@@ -1478,25 +1478,25 @@
         <v>1.04</v>
       </c>
       <c r="N4">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="O4">
         <v>1.22</v>
       </c>
       <c r="P4">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="Q4">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="R4">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="S4">
         <v>2.66</v>
       </c>
       <c r="T4">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="U4">
         <v>2.36</v>
@@ -1616,64 +1616,64 @@
         <v>10</v>
       </c>
       <c r="BH4">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BI4">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BJ4">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK4">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="BN4">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BO4">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BP4">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BQ4">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BR4">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BS4">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BT4">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BU4">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BV4">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW4">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BX4">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BY4">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BZ4">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="CA4">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="CB4" t="s">
         <v>120</v>
@@ -1696,19 +1696,19 @@
         <v>110</v>
       </c>
       <c r="F5">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="G5">
         <v>110</v>
       </c>
       <c r="H5">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="I5">
         <v>110</v>
       </c>
       <c r="J5">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="K5">
         <v>950</v>
@@ -1723,19 +1723,19 @@
         <v>1.13</v>
       </c>
       <c r="O5">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="P5">
         <v>1.13</v>
       </c>
       <c r="Q5">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="R5">
         <v>1.08</v>
       </c>
       <c r="S5">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="T5">
         <v>1.01</v>
@@ -1744,10 +1744,10 @@
         <v>1.01</v>
       </c>
       <c r="V5">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W5">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X5">
         <v>1000</v>
@@ -1998,7 +1998,7 @@
         <v>6.4</v>
       </c>
       <c r="Z6">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AA6">
         <v>42</v>
@@ -2088,10 +2088,10 @@
         <v>14.5</v>
       </c>
       <c r="BD6">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BE6">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BF6">
         <v>15</v>
@@ -2103,7 +2103,7 @@
         <v>2.4</v>
       </c>
       <c r="BI6">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="BJ6">
         <v>13.5</v>
@@ -2118,7 +2118,7 @@
         <v>21</v>
       </c>
       <c r="BN6">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BO6">
         <v>6</v>
@@ -2180,7 +2180,7 @@
         <v>112</v>
       </c>
       <c r="F7">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="G7">
         <v>17</v>
@@ -2213,16 +2213,16 @@
         <v>1.78</v>
       </c>
       <c r="Q7">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="R7">
         <v>1.29</v>
       </c>
       <c r="S7">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T7">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="U7">
         <v>1.49</v>
@@ -2243,7 +2243,7 @@
         <v>6.2</v>
       </c>
       <c r="AA7">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AB7">
         <v>34</v>
@@ -2345,7 +2345,7 @@
         <v>3.25</v>
       </c>
       <c r="BI7">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="BJ7">
         <v>24</v>
@@ -2381,7 +2381,7 @@
         <v>3.3</v>
       </c>
       <c r="BU7">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BV7">
         <v>8</v>
@@ -2422,7 +2422,7 @@
         <v>113</v>
       </c>
       <c r="F8">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="G8">
         <v>2.6</v>
@@ -2431,7 +2431,7 @@
         <v>2.78</v>
       </c>
       <c r="I8">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="J8">
         <v>3.9</v>
@@ -2449,13 +2449,13 @@
         <v>5.9</v>
       </c>
       <c r="O8">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P8">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="Q8">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="R8">
         <v>1.68</v>
@@ -2467,10 +2467,10 @@
         <v>1.51</v>
       </c>
       <c r="U8">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="V8">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="W8">
         <v>1.62</v>
@@ -2488,7 +2488,7 @@
         <v>42</v>
       </c>
       <c r="AB8">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AC8">
         <v>9.4</v>
@@ -2497,7 +2497,7 @@
         <v>13</v>
       </c>
       <c r="AE8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AF8">
         <v>20</v>
@@ -2524,7 +2524,7 @@
         <v>50</v>
       </c>
       <c r="AN8">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AO8">
         <v>15</v>
@@ -2533,7 +2533,7 @@
         <v>23</v>
       </c>
       <c r="AQ8">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AR8">
         <v>21</v>
@@ -2563,7 +2563,7 @@
         <v>13</v>
       </c>
       <c r="BA8">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BB8">
         <v>34</v>
@@ -2572,13 +2572,13 @@
         <v>21</v>
       </c>
       <c r="BD8">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BE8">
         <v>44</v>
       </c>
       <c r="BF8">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BG8">
         <v>13.5</v>
@@ -2664,16 +2664,16 @@
         <v>114</v>
       </c>
       <c r="F9">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="G9">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="H9">
         <v>4.7</v>
       </c>
       <c r="I9">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J9">
         <v>4.2</v>
@@ -2682,7 +2682,7 @@
         <v>4.3</v>
       </c>
       <c r="L9">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M9">
         <v>1.05</v>
@@ -2700,10 +2700,10 @@
         <v>1.77</v>
       </c>
       <c r="R9">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S9">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="T9">
         <v>1.76</v>
@@ -2715,7 +2715,7 @@
         <v>1.26</v>
       </c>
       <c r="W9">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="X9">
         <v>18.5</v>
@@ -2742,7 +2742,7 @@
         <v>60</v>
       </c>
       <c r="AF9">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG9">
         <v>10.5</v>
@@ -2766,7 +2766,7 @@
         <v>90</v>
       </c>
       <c r="AN9">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AO9">
         <v>55</v>
@@ -2781,7 +2781,7 @@
         <v>34</v>
       </c>
       <c r="AS9">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AT9">
         <v>9.6</v>
@@ -2817,13 +2817,13 @@
         <v>28</v>
       </c>
       <c r="BE9">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BF9">
         <v>9</v>
       </c>
       <c r="BG9">
-        <v>13.5</v>
+        <v>44</v>
       </c>
       <c r="BH9">
         <v>3.85</v>
@@ -2909,13 +2909,13 @@
         <v>2.54</v>
       </c>
       <c r="G10">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="H10">
         <v>3.25</v>
       </c>
       <c r="I10">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="J10">
         <v>3.25</v>
@@ -2933,7 +2933,7 @@
         <v>2.98</v>
       </c>
       <c r="O10">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="P10">
         <v>1.66</v>
@@ -2957,7 +2957,7 @@
         <v>1.43</v>
       </c>
       <c r="W10">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="X10">
         <v>10.5</v>
@@ -2996,7 +2996,7 @@
         <v>70</v>
       </c>
       <c r="AJ10">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AK10">
         <v>36</v>
@@ -3005,7 +3005,7 @@
         <v>55</v>
       </c>
       <c r="AM10">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AN10">
         <v>34</v>
@@ -3026,7 +3026,7 @@
         <v>50</v>
       </c>
       <c r="AT10">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AU10">
         <v>6.8</v>
@@ -3056,7 +3056,7 @@
         <v>28</v>
       </c>
       <c r="BD10">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BE10">
         <v>15.5</v>
@@ -3095,7 +3095,7 @@
         <v>22</v>
       </c>
       <c r="BQ10">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="BR10">
         <v>1000</v>
@@ -3151,19 +3151,19 @@
         <v>1.45</v>
       </c>
       <c r="G11">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="H11">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="I11">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J11">
         <v>5.3</v>
       </c>
       <c r="K11">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="L11">
         <v>1.28</v>
@@ -3184,10 +3184,10 @@
         <v>1.54</v>
       </c>
       <c r="R11">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="S11">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="T11">
         <v>1.75</v>
@@ -3196,10 +3196,10 @@
         <v>2.2</v>
       </c>
       <c r="V11">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="W11">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="X11">
         <v>28</v>
@@ -3211,7 +3211,7 @@
         <v>75</v>
       </c>
       <c r="AA11">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="AB11">
         <v>12</v>
@@ -3220,7 +3220,7 @@
         <v>12.5</v>
       </c>
       <c r="AD11">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AE11">
         <v>95</v>
@@ -3235,7 +3235,7 @@
         <v>24</v>
       </c>
       <c r="AI11">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AJ11">
         <v>13.5</v>
@@ -3271,7 +3271,7 @@
         <v>10.5</v>
       </c>
       <c r="AU11">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AV11">
         <v>25</v>
@@ -3286,7 +3286,7 @@
         <v>9.6</v>
       </c>
       <c r="AZ11">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA11">
         <v>15</v>
@@ -3307,7 +3307,7 @@
         <v>4.7</v>
       </c>
       <c r="BG11">
-        <v>13.5</v>
+        <v>60</v>
       </c>
       <c r="BH11">
         <v>4.6</v>
@@ -3337,7 +3337,7 @@
         <v>10.5</v>
       </c>
       <c r="BQ11">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BR11">
         <v>24</v>
@@ -3390,16 +3390,16 @@
         <v>117</v>
       </c>
       <c r="F12">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="G12">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="H12">
+        <v>2.82</v>
+      </c>
+      <c r="I12">
         <v>2.86</v>
-      </c>
-      <c r="I12">
-        <v>2.88</v>
       </c>
       <c r="J12">
         <v>3.4</v>
@@ -3450,16 +3450,16 @@
         <v>10.5</v>
       </c>
       <c r="Z12">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AA12">
         <v>46</v>
       </c>
       <c r="AB12">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC12">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD12">
         <v>13</v>
@@ -3510,7 +3510,7 @@
         <v>42</v>
       </c>
       <c r="AT12">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AU12">
         <v>7</v>
@@ -3543,7 +3543,7 @@
         <v>44</v>
       </c>
       <c r="BE12">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BF12">
         <v>29</v>
@@ -3591,7 +3591,7 @@
         <v>5.9</v>
       </c>
       <c r="BU12">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BV12">
         <v>25</v>
@@ -3668,7 +3668,7 @@
         <v>1.57</v>
       </c>
       <c r="R13">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="S13">
         <v>2.44</v>
@@ -3677,7 +3677,7 @@
         <v>2.32</v>
       </c>
       <c r="U13">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="V13">
         <v>1.05</v>
@@ -3692,7 +3692,7 @@
         <v>55</v>
       </c>
       <c r="Z13">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AA13">
         <v>900</v>
@@ -3719,7 +3719,7 @@
         <v>38</v>
       </c>
       <c r="AI13">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="AJ13">
         <v>8.800000000000001</v>
@@ -3731,7 +3731,7 @@
         <v>46</v>
       </c>
       <c r="AM13">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AN13">
         <v>3.95</v>
@@ -3749,7 +3749,7 @@
         <v>22</v>
       </c>
       <c r="AS13">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AT13">
         <v>9.4</v>
@@ -3776,7 +3776,7 @@
         <v>23</v>
       </c>
       <c r="BB13">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BC13">
         <v>13</v>
@@ -3788,7 +3788,7 @@
         <v>20</v>
       </c>
       <c r="BF13">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BG13">
         <v>21</v>
@@ -3800,10 +3800,10 @@
         <v>4.1</v>
       </c>
       <c r="BJ13">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BK13">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BL13">
         <v>210</v>
@@ -3812,7 +3812,7 @@
         <v>23</v>
       </c>
       <c r="BN13">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="BO13">
         <v>3.4</v>
@@ -3827,25 +3827,25 @@
         <v>28</v>
       </c>
       <c r="BS13">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BT13">
         <v>21</v>
       </c>
       <c r="BU13">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BV13">
         <v>170</v>
       </c>
       <c r="BW13">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BX13">
         <v>130</v>
       </c>
       <c r="BY13">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BZ13">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-24.xlsx
@@ -376,7 +376,7 @@
     <t>IRT Tanger</t>
   </si>
   <si>
-    <t>2026-09-23 03:30:34</t>
+    <t>2026-09-23 05:41:42</t>
   </si>
 </sst>
 </file>
@@ -970,16 +970,16 @@
         <v>107</v>
       </c>
       <c r="F2">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="G2">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="H2">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="I2">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="J2">
         <v>3.95</v>
@@ -988,43 +988,43 @@
         <v>4.2</v>
       </c>
       <c r="L2">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="M2">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N2">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="O2">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="P2">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="Q2">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="R2">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="S2">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="T2">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="U2">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="V2">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="W2">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="X2">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="Y2">
         <v>23</v>
@@ -1033,34 +1033,34 @@
         <v>60</v>
       </c>
       <c r="AA2">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AB2">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AC2">
         <v>9.199999999999999</v>
       </c>
       <c r="AD2">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AE2">
         <v>110</v>
       </c>
       <c r="AF2">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AG2">
         <v>12.5</v>
       </c>
       <c r="AH2">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AI2">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AJ2">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AK2">
         <v>21</v>
@@ -1069,127 +1069,127 @@
         <v>46</v>
       </c>
       <c r="AM2">
+        <v>170</v>
+      </c>
+      <c r="AN2">
+        <v>13</v>
+      </c>
+      <c r="AO2">
         <v>150</v>
       </c>
-      <c r="AN2">
-        <v>12</v>
-      </c>
-      <c r="AO2">
-        <v>130</v>
-      </c>
       <c r="AP2">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AQ2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR2">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AS2">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AT2">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AU2">
         <v>8.199999999999999</v>
       </c>
       <c r="AV2">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AW2">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AX2">
+        <v>8.4</v>
+      </c>
+      <c r="AY2">
         <v>8.800000000000001</v>
       </c>
-      <c r="AY2">
-        <v>9</v>
-      </c>
       <c r="AZ2">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="BA2">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BB2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC2">
         <v>16</v>
       </c>
       <c r="BD2">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BE2">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BF2">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BG2">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="BH2">
+        <v>3.9</v>
+      </c>
+      <c r="BI2">
+        <v>2.8</v>
+      </c>
+      <c r="BJ2">
+        <v>11</v>
+      </c>
+      <c r="BK2">
+        <v>8.4</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>5</v>
+      </c>
+      <c r="BN2">
         <v>4.1</v>
       </c>
-      <c r="BI2">
-        <v>2.76</v>
-      </c>
-      <c r="BJ2">
-        <v>13</v>
-      </c>
-      <c r="BK2">
-        <v>4.5</v>
-      </c>
-      <c r="BL2">
-        <v>1000</v>
-      </c>
-      <c r="BM2">
-        <v>6.6</v>
-      </c>
-      <c r="BN2">
-        <v>4.2</v>
-      </c>
       <c r="BO2">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="BP2">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>4.3</v>
+        <v>8.4</v>
       </c>
       <c r="BR2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BS2">
-        <v>5.7</v>
+        <v>4.4</v>
       </c>
       <c r="BT2">
         <v>9.4</v>
       </c>
       <c r="BU2">
-        <v>3.95</v>
+        <v>3.3</v>
       </c>
       <c r="BV2">
         <v>65</v>
       </c>
       <c r="BW2">
-        <v>6.2</v>
+        <v>4.8</v>
       </c>
       <c r="BX2">
         <v>75</v>
       </c>
       <c r="BY2">
-        <v>6.2</v>
+        <v>4.8</v>
       </c>
       <c r="BZ2">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="CA2">
-        <v>5.4</v>
+        <v>4.2</v>
       </c>
       <c r="CB2" t="s">
         <v>120</v>
@@ -1212,7 +1212,7 @@
         <v>108</v>
       </c>
       <c r="F3">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="G3">
         <v>1.91</v>
@@ -1221,10 +1221,10 @@
         <v>4.2</v>
       </c>
       <c r="I3">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J3">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K3">
         <v>4.2</v>
@@ -1239,13 +1239,13 @@
         <v>5.7</v>
       </c>
       <c r="O3">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P3">
         <v>2.6</v>
       </c>
       <c r="Q3">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="R3">
         <v>1.64</v>
@@ -1257,7 +1257,7 @@
         <v>1.59</v>
       </c>
       <c r="U3">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="V3">
         <v>1.29</v>
@@ -1275,7 +1275,7 @@
         <v>36</v>
       </c>
       <c r="AA3">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB3">
         <v>13</v>
@@ -1290,7 +1290,7 @@
         <v>44</v>
       </c>
       <c r="AF3">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG3">
         <v>11</v>
@@ -1299,13 +1299,13 @@
         <v>15.5</v>
       </c>
       <c r="AI3">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AJ3">
         <v>22</v>
       </c>
       <c r="AK3">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AL3">
         <v>26</v>
@@ -1320,10 +1320,10 @@
         <v>32</v>
       </c>
       <c r="AP3">
+        <v>21</v>
+      </c>
+      <c r="AQ3">
         <v>20</v>
-      </c>
-      <c r="AQ3">
-        <v>19</v>
       </c>
       <c r="AR3">
         <v>30</v>
@@ -1344,7 +1344,7 @@
         <v>36</v>
       </c>
       <c r="AX3">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AY3">
         <v>9.800000000000001</v>
@@ -1368,7 +1368,7 @@
         <v>50</v>
       </c>
       <c r="BF3">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BG3">
         <v>28</v>
@@ -1389,7 +1389,7 @@
         <v>95</v>
       </c>
       <c r="BM3">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BN3">
         <v>5</v>
@@ -1398,16 +1398,16 @@
         <v>4.5</v>
       </c>
       <c r="BP3">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="BQ3">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BR3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BS3">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BT3">
         <v>7.8</v>
@@ -1419,19 +1419,19 @@
         <v>34</v>
       </c>
       <c r="BW3">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BX3">
         <v>40</v>
       </c>
       <c r="BY3">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BZ3">
         <v>14.5</v>
       </c>
       <c r="CA3">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="CB3" t="s">
         <v>120</v>
@@ -1454,19 +1454,19 @@
         <v>109</v>
       </c>
       <c r="F4">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="G4">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="H4">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="I4">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="J4">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K4">
         <v>4.4</v>
@@ -1478,7 +1478,7 @@
         <v>1.04</v>
       </c>
       <c r="N4">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="O4">
         <v>1.22</v>
@@ -1487,28 +1487,28 @@
         <v>2.4</v>
       </c>
       <c r="Q4">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="R4">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="S4">
-        <v>2.66</v>
+        <v>2.78</v>
       </c>
       <c r="T4">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="U4">
         <v>2.36</v>
       </c>
       <c r="V4">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W4">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="X4">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Y4">
         <v>23</v>
@@ -1517,7 +1517,7 @@
         <v>38</v>
       </c>
       <c r="AA4">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AB4">
         <v>14.5</v>
@@ -1529,7 +1529,7 @@
         <v>20</v>
       </c>
       <c r="AE4">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF4">
         <v>17</v>
@@ -1568,7 +1568,7 @@
         <v>13.5</v>
       </c>
       <c r="AR4">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AS4">
         <v>1.03</v>
@@ -1583,7 +1583,7 @@
         <v>12</v>
       </c>
       <c r="AW4">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AX4">
         <v>10</v>
@@ -1595,7 +1595,7 @@
         <v>12</v>
       </c>
       <c r="BA4">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="BB4">
         <v>16</v>
@@ -1604,7 +1604,7 @@
         <v>13.5</v>
       </c>
       <c r="BD4">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="BE4">
         <v>1.03</v>
@@ -1616,7 +1616,7 @@
         <v>10</v>
       </c>
       <c r="BH4">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="BI4">
         <v>3.25</v>
@@ -1625,7 +1625,7 @@
         <v>11</v>
       </c>
       <c r="BK4">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BL4">
         <v>1000</v>
@@ -1634,7 +1634,7 @@
         <v>55</v>
       </c>
       <c r="BN4">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BO4">
         <v>3.9</v>
@@ -1643,7 +1643,7 @@
         <v>15.5</v>
       </c>
       <c r="BQ4">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BR4">
         <v>28</v>
@@ -1664,7 +1664,7 @@
         <v>20</v>
       </c>
       <c r="BX4">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BY4">
         <v>24</v>
@@ -1696,19 +1696,19 @@
         <v>110</v>
       </c>
       <c r="F5">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="G5">
-        <v>110</v>
+        <v>1.24</v>
       </c>
       <c r="H5">
-        <v>1.11</v>
+        <v>5.4</v>
       </c>
       <c r="I5">
         <v>110</v>
       </c>
       <c r="J5">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="K5">
         <v>950</v>
@@ -1717,25 +1717,25 @@
         <v>1.01</v>
       </c>
       <c r="M5">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N5">
         <v>1.13</v>
       </c>
       <c r="O5">
-        <v>1.2</v>
+        <v>1.02</v>
       </c>
       <c r="P5">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Q5">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="R5">
         <v>1.08</v>
       </c>
       <c r="S5">
-        <v>1.2</v>
+        <v>1.83</v>
       </c>
       <c r="T5">
         <v>1.01</v>
@@ -1744,10 +1744,10 @@
         <v>1.01</v>
       </c>
       <c r="V5">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="W5">
-        <v>1.08</v>
+        <v>5.1</v>
       </c>
       <c r="X5">
         <v>1000</v>
@@ -1938,31 +1938,31 @@
         <v>111</v>
       </c>
       <c r="F6">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="G6">
         <v>3.9</v>
       </c>
       <c r="H6">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="I6">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="J6">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="K6">
         <v>2.92</v>
       </c>
       <c r="L6">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="M6">
         <v>1.17</v>
       </c>
       <c r="N6">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="O6">
         <v>1.74</v>
@@ -1977,7 +1977,7 @@
         <v>1.13</v>
       </c>
       <c r="S6">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="T6">
         <v>2.5</v>
@@ -1986,7 +1986,7 @@
         <v>1.61</v>
       </c>
       <c r="V6">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="W6">
         <v>1.34</v>
@@ -1998,13 +1998,13 @@
         <v>6.4</v>
       </c>
       <c r="Z6">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AA6">
         <v>42</v>
       </c>
       <c r="AB6">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC6">
         <v>7</v>
@@ -2025,7 +2025,7 @@
         <v>32</v>
       </c>
       <c r="AI6">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AJ6">
         <v>110</v>
@@ -2034,10 +2034,10 @@
         <v>85</v>
       </c>
       <c r="AL6">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="AM6">
-        <v>350</v>
+        <v>320</v>
       </c>
       <c r="AN6">
         <v>150</v>
@@ -2079,10 +2079,10 @@
         <v>28</v>
       </c>
       <c r="BA6">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BB6">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BC6">
         <v>14.5</v>
@@ -2091,10 +2091,10 @@
         <v>14.5</v>
       </c>
       <c r="BE6">
+        <v>14</v>
+      </c>
+      <c r="BF6">
         <v>14.5</v>
-      </c>
-      <c r="BF6">
-        <v>15</v>
       </c>
       <c r="BG6">
         <v>44</v>
@@ -2103,7 +2103,7 @@
         <v>2.4</v>
       </c>
       <c r="BI6">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="BJ6">
         <v>13.5</v>
@@ -2180,10 +2180,10 @@
         <v>112</v>
       </c>
       <c r="F7">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="G7">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H7">
         <v>1.33</v>
@@ -2204,34 +2204,34 @@
         <v>1.08</v>
       </c>
       <c r="N7">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="O7">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P7">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="Q7">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="R7">
         <v>1.29</v>
       </c>
       <c r="S7">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="T7">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="U7">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="V7">
         <v>3.85</v>
       </c>
       <c r="W7">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X7">
         <v>13</v>
@@ -2249,7 +2249,7 @@
         <v>34</v>
       </c>
       <c r="AC7">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AD7">
         <v>12</v>
@@ -2261,28 +2261,28 @@
         <v>160</v>
       </c>
       <c r="AG7">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AH7">
         <v>55</v>
       </c>
       <c r="AI7">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ7">
         <v>1000</v>
       </c>
       <c r="AK7">
-        <v>530</v>
+        <v>490</v>
       </c>
       <c r="AL7">
-        <v>430</v>
+        <v>400</v>
       </c>
       <c r="AM7">
-        <v>560</v>
+        <v>570</v>
       </c>
       <c r="AN7">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="AO7">
         <v>8</v>
@@ -2291,16 +2291,16 @@
         <v>12</v>
       </c>
       <c r="AQ7">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AR7">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AS7">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AT7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AU7">
         <v>11.5</v>
@@ -2309,37 +2309,37 @@
         <v>10.5</v>
       </c>
       <c r="AW7">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AX7">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AY7">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AZ7">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BA7">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BB7">
+        <v>16</v>
+      </c>
+      <c r="BC7">
+        <v>15.5</v>
+      </c>
+      <c r="BD7">
         <v>15</v>
       </c>
-      <c r="BC7">
-        <v>14.5</v>
-      </c>
-      <c r="BD7">
-        <v>14.5</v>
-      </c>
       <c r="BE7">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BF7">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BG7">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BH7">
         <v>3.25</v>
@@ -2348,7 +2348,7 @@
         <v>3</v>
       </c>
       <c r="BJ7">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BK7">
         <v>12</v>
@@ -2390,7 +2390,7 @@
         <v>7</v>
       </c>
       <c r="BX7">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BY7">
         <v>26</v>
@@ -2422,7 +2422,7 @@
         <v>113</v>
       </c>
       <c r="F8">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="G8">
         <v>2.6</v>
@@ -2446,28 +2446,28 @@
         <v>1.04</v>
       </c>
       <c r="N8">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="O8">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P8">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="Q8">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="R8">
         <v>1.68</v>
       </c>
       <c r="S8">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="T8">
         <v>1.51</v>
       </c>
       <c r="U8">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="V8">
         <v>1.54</v>
@@ -2497,7 +2497,7 @@
         <v>13</v>
       </c>
       <c r="AE8">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF8">
         <v>20</v>
@@ -2509,16 +2509,16 @@
         <v>14</v>
       </c>
       <c r="AI8">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AJ8">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AK8">
         <v>23</v>
       </c>
       <c r="AL8">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM8">
         <v>50</v>
@@ -2545,7 +2545,7 @@
         <v>15</v>
       </c>
       <c r="AU8">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV8">
         <v>12</v>
@@ -2554,7 +2554,7 @@
         <v>23</v>
       </c>
       <c r="AX8">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AY8">
         <v>11.5</v>
@@ -2563,7 +2563,7 @@
         <v>13</v>
       </c>
       <c r="BA8">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BB8">
         <v>34</v>
@@ -2572,7 +2572,7 @@
         <v>21</v>
       </c>
       <c r="BD8">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BE8">
         <v>44</v>
@@ -2664,16 +2664,16 @@
         <v>114</v>
       </c>
       <c r="F9">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="G9">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="H9">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I9">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J9">
         <v>4.2</v>
@@ -2691,43 +2691,43 @@
         <v>4.6</v>
       </c>
       <c r="O9">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P9">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="Q9">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="R9">
         <v>1.49</v>
       </c>
       <c r="S9">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="T9">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="U9">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="V9">
         <v>1.26</v>
       </c>
       <c r="W9">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="X9">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="Y9">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Z9">
         <v>38</v>
       </c>
       <c r="AA9">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AB9">
         <v>10.5</v>
@@ -2739,16 +2739,16 @@
         <v>18.5</v>
       </c>
       <c r="AE9">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF9">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AG9">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH9">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI9">
         <v>60</v>
@@ -2763,10 +2763,10 @@
         <v>32</v>
       </c>
       <c r="AM9">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN9">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AO9">
         <v>55</v>
@@ -2784,7 +2784,7 @@
         <v>15.5</v>
       </c>
       <c r="AT9">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU9">
         <v>9</v>
@@ -2793,13 +2793,13 @@
         <v>17</v>
       </c>
       <c r="AW9">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AX9">
         <v>11</v>
       </c>
       <c r="AY9">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ9">
         <v>17</v>
@@ -2811,19 +2811,19 @@
         <v>17.5</v>
       </c>
       <c r="BC9">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BD9">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BE9">
-        <v>16.5</v>
+        <v>70</v>
       </c>
       <c r="BF9">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BG9">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="BH9">
         <v>3.85</v>
@@ -2841,7 +2841,7 @@
         <v>110</v>
       </c>
       <c r="BM9">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BN9">
         <v>4.6</v>
@@ -2853,10 +2853,10 @@
         <v>11.5</v>
       </c>
       <c r="BQ9">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR9">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BS9">
         <v>9.800000000000001</v>
@@ -2871,19 +2871,19 @@
         <v>38</v>
       </c>
       <c r="BW9">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BX9">
         <v>44</v>
       </c>
       <c r="BY9">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BZ9">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="CA9">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB9" t="s">
         <v>120</v>
@@ -2906,16 +2906,16 @@
         <v>115</v>
       </c>
       <c r="F10">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="G10">
         <v>2.56</v>
       </c>
       <c r="H10">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I10">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="J10">
         <v>3.25</v>
@@ -2924,22 +2924,22 @@
         <v>3.3</v>
       </c>
       <c r="L10">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="M10">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N10">
         <v>2.98</v>
       </c>
       <c r="O10">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P10">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="Q10">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="R10">
         <v>1.25</v>
@@ -2954,7 +2954,7 @@
         <v>1.88</v>
       </c>
       <c r="V10">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W10">
         <v>1.64</v>
@@ -2963,7 +2963,7 @@
         <v>10.5</v>
       </c>
       <c r="Y10">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="Z10">
         <v>21</v>
@@ -2972,7 +2972,7 @@
         <v>60</v>
       </c>
       <c r="AB10">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC10">
         <v>7.4</v>
@@ -2996,19 +2996,19 @@
         <v>70</v>
       </c>
       <c r="AJ10">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AK10">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL10">
         <v>55</v>
       </c>
       <c r="AM10">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AN10">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO10">
         <v>55</v>
@@ -3026,7 +3026,7 @@
         <v>50</v>
       </c>
       <c r="AT10">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AU10">
         <v>6.8</v>
@@ -3035,7 +3035,7 @@
         <v>13</v>
       </c>
       <c r="AW10">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AX10">
         <v>13</v>
@@ -3044,7 +3044,7 @@
         <v>11</v>
       </c>
       <c r="AZ10">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA10">
         <v>55</v>
@@ -3056,22 +3056,22 @@
         <v>28</v>
       </c>
       <c r="BD10">
-        <v>13.5</v>
+        <v>48</v>
       </c>
       <c r="BE10">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BF10">
         <v>27</v>
       </c>
       <c r="BG10">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BH10">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="BI10">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="BJ10">
         <v>10.5</v>
@@ -3083,31 +3083,31 @@
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BN10">
         <v>5.3</v>
       </c>
       <c r="BO10">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BP10">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BQ10">
         <v>16</v>
       </c>
       <c r="BR10">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS10">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BT10">
         <v>6.2</v>
       </c>
       <c r="BU10">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BV10">
         <v>1000</v>
@@ -3116,16 +3116,16 @@
         <v>11.5</v>
       </c>
       <c r="BX10">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BY10">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BZ10">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="CA10">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="CB10" t="s">
         <v>120</v>
@@ -3154,16 +3154,16 @@
         <v>1.46</v>
       </c>
       <c r="H11">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="I11">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="J11">
         <v>5.3</v>
       </c>
       <c r="K11">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="L11">
         <v>1.28</v>
@@ -3175,13 +3175,13 @@
         <v>6</v>
       </c>
       <c r="O11">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P11">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="Q11">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="R11">
         <v>1.68</v>
@@ -3190,19 +3190,19 @@
         <v>2.3</v>
       </c>
       <c r="T11">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U11">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V11">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W11">
         <v>3.15</v>
       </c>
       <c r="X11">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="Y11">
         <v>38</v>
@@ -3211,7 +3211,7 @@
         <v>75</v>
       </c>
       <c r="AA11">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AB11">
         <v>12</v>
@@ -3220,7 +3220,7 @@
         <v>12.5</v>
       </c>
       <c r="AD11">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AE11">
         <v>95</v>
@@ -3229,13 +3229,13 @@
         <v>10.5</v>
       </c>
       <c r="AG11">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH11">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AI11">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AJ11">
         <v>13.5</v>
@@ -3244,10 +3244,10 @@
         <v>14</v>
       </c>
       <c r="AL11">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AM11">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AN11">
         <v>5.2</v>
@@ -3256,7 +3256,7 @@
         <v>90</v>
       </c>
       <c r="AP11">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="AQ11">
         <v>30</v>
@@ -3265,7 +3265,7 @@
         <v>60</v>
       </c>
       <c r="AS11">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AT11">
         <v>10.5</v>
@@ -3277,7 +3277,7 @@
         <v>25</v>
       </c>
       <c r="AW11">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AX11">
         <v>9.199999999999999</v>
@@ -3289,22 +3289,22 @@
         <v>19</v>
       </c>
       <c r="BA11">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="BB11">
         <v>12</v>
       </c>
       <c r="BC11">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BD11">
         <v>24</v>
       </c>
       <c r="BE11">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BF11">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BG11">
         <v>60</v>
@@ -3390,16 +3390,16 @@
         <v>117</v>
       </c>
       <c r="F12">
+        <v>2.78</v>
+      </c>
+      <c r="G12">
         <v>2.8</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <v>2.84</v>
       </c>
-      <c r="H12">
-        <v>2.82</v>
-      </c>
       <c r="I12">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="J12">
         <v>3.4</v>
@@ -3420,10 +3420,10 @@
         <v>1.4</v>
       </c>
       <c r="P12">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="Q12">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R12">
         <v>1.29</v>
@@ -3432,7 +3432,7 @@
         <v>4.1</v>
       </c>
       <c r="T12">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="U12">
         <v>2.02</v>
@@ -3471,22 +3471,22 @@
         <v>17</v>
       </c>
       <c r="AG12">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH12">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AI12">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ12">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AK12">
         <v>34</v>
       </c>
       <c r="AL12">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM12">
         <v>120</v>
@@ -3507,13 +3507,13 @@
         <v>16.5</v>
       </c>
       <c r="AS12">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AT12">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU12">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV12">
         <v>12</v>
@@ -3528,7 +3528,7 @@
         <v>12.5</v>
       </c>
       <c r="AZ12">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA12">
         <v>44</v>
@@ -3543,13 +3543,13 @@
         <v>44</v>
       </c>
       <c r="BE12">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="BF12">
         <v>29</v>
       </c>
       <c r="BG12">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BH12">
         <v>3.05</v>
@@ -3567,49 +3567,49 @@
         <v>160</v>
       </c>
       <c r="BM12">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BN12">
         <v>5.7</v>
       </c>
       <c r="BO12">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BP12">
         <v>24</v>
       </c>
       <c r="BQ12">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR12">
         <v>40</v>
       </c>
       <c r="BS12">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BT12">
         <v>5.9</v>
       </c>
       <c r="BU12">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BV12">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BW12">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX12">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BY12">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BZ12">
         <v>36</v>
       </c>
       <c r="CA12">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB12" t="s">
         <v>120</v>
@@ -3644,10 +3644,10 @@
         <v>18</v>
       </c>
       <c r="J13">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="K13">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="L13">
         <v>1.29</v>
@@ -3656,7 +3656,7 @@
         <v>1.04</v>
       </c>
       <c r="N13">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="O13">
         <v>1.19</v>
@@ -3671,19 +3671,19 @@
         <v>1.65</v>
       </c>
       <c r="S13">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="T13">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="U13">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V13">
         <v>1.05</v>
       </c>
       <c r="W13">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="X13">
         <v>26</v>
@@ -3695,13 +3695,13 @@
         <v>180</v>
       </c>
       <c r="AA13">
-        <v>900</v>
+        <v>880</v>
       </c>
       <c r="AB13">
         <v>9.800000000000001</v>
       </c>
       <c r="AC13">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AD13">
         <v>60</v>
@@ -3713,7 +3713,7 @@
         <v>7.6</v>
       </c>
       <c r="AG13">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH13">
         <v>38</v>
@@ -3746,10 +3746,10 @@
         <v>44</v>
       </c>
       <c r="AR13">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AS13">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AT13">
         <v>9.4</v>
@@ -3758,10 +3758,10 @@
         <v>14.5</v>
       </c>
       <c r="AV13">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AW13">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AX13">
         <v>7.2</v>
@@ -3773,7 +3773,7 @@
         <v>34</v>
       </c>
       <c r="BA13">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BB13">
         <v>8.4</v>
@@ -3785,13 +3785,13 @@
         <v>38</v>
       </c>
       <c r="BE13">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BF13">
         <v>3.75</v>
       </c>
       <c r="BG13">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="BH13">
         <v>4.4</v>
@@ -3818,10 +3818,10 @@
         <v>3.4</v>
       </c>
       <c r="BP13">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BQ13">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BR13">
         <v>28</v>
@@ -3833,7 +3833,7 @@
         <v>21</v>
       </c>
       <c r="BU13">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BV13">
         <v>170</v>
@@ -3907,7 +3907,7 @@
         <v>1.46</v>
       </c>
       <c r="Q14">
-        <v>2.66</v>
+        <v>2.92</v>
       </c>
       <c r="R14">
         <v>1.14</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-24.xlsx
@@ -376,7 +376,7 @@
     <t>IRT Tanger</t>
   </si>
   <si>
-    <t>2026-09-23 05:41:42</t>
+    <t>2026-09-23 07:53:17</t>
   </si>
 </sst>
 </file>
@@ -970,16 +970,16 @@
         <v>107</v>
       </c>
       <c r="F2">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="G2">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="H2">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="I2">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J2">
         <v>3.95</v>
@@ -991,13 +991,13 @@
         <v>1.42</v>
       </c>
       <c r="M2">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N2">
         <v>3.6</v>
       </c>
       <c r="O2">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P2">
         <v>1.91</v>
@@ -1012,22 +1012,22 @@
         <v>3.7</v>
       </c>
       <c r="T2">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U2">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="V2">
         <v>1.17</v>
       </c>
       <c r="W2">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="X2">
         <v>17</v>
       </c>
       <c r="Y2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Z2">
         <v>60</v>
@@ -1039,34 +1039,34 @@
         <v>7.8</v>
       </c>
       <c r="AC2">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AD2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AE2">
         <v>110</v>
       </c>
       <c r="AF2">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AG2">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI2">
         <v>110</v>
       </c>
       <c r="AJ2">
+        <v>20</v>
+      </c>
+      <c r="AK2">
         <v>19.5</v>
       </c>
-      <c r="AK2">
-        <v>21</v>
-      </c>
       <c r="AL2">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AM2">
         <v>170</v>
@@ -1078,64 +1078,64 @@
         <v>150</v>
       </c>
       <c r="AP2">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ2">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AR2">
-        <v>6.2</v>
+        <v>38</v>
       </c>
       <c r="AS2">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AT2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU2">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV2">
-        <v>20</v>
+        <v>6.4</v>
       </c>
       <c r="AW2">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="AX2">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AY2">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ2">
-        <v>5.5</v>
+        <v>10.5</v>
       </c>
       <c r="BA2">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BB2">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BC2">
         <v>16</v>
       </c>
       <c r="BD2">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BE2">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BF2">
         <v>10</v>
       </c>
       <c r="BG2">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BH2">
         <v>3.9</v>
       </c>
       <c r="BI2">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="BJ2">
         <v>11</v>
@@ -1147,49 +1147,49 @@
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>5</v>
+        <v>7.6</v>
       </c>
       <c r="BN2">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BO2">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="BP2">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BQ2">
         <v>8.4</v>
       </c>
       <c r="BR2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BS2">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="BT2">
         <v>9.4</v>
       </c>
       <c r="BU2">
-        <v>3.3</v>
+        <v>7.2</v>
       </c>
       <c r="BV2">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BW2">
-        <v>4.8</v>
+        <v>7</v>
       </c>
       <c r="BX2">
         <v>75</v>
       </c>
       <c r="BY2">
-        <v>4.8</v>
+        <v>7</v>
       </c>
       <c r="BZ2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="CA2">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="CB2" t="s">
         <v>120</v>
@@ -1212,10 +1212,10 @@
         <v>108</v>
       </c>
       <c r="F3">
+        <v>1.88</v>
+      </c>
+      <c r="G3">
         <v>1.9</v>
-      </c>
-      <c r="G3">
-        <v>1.91</v>
       </c>
       <c r="H3">
         <v>4.2</v>
@@ -1230,7 +1230,7 @@
         <v>4.2</v>
       </c>
       <c r="L3">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M3">
         <v>1.04</v>
@@ -1242,7 +1242,7 @@
         <v>1.19</v>
       </c>
       <c r="P3">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="Q3">
         <v>1.59</v>
@@ -1254,28 +1254,28 @@
         <v>2.48</v>
       </c>
       <c r="T3">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="U3">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="V3">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W3">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="X3">
         <v>24</v>
       </c>
       <c r="Y3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z3">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AA3">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="AB3">
         <v>13</v>
@@ -1287,19 +1287,19 @@
         <v>17.5</v>
       </c>
       <c r="AE3">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AF3">
         <v>14</v>
       </c>
       <c r="AG3">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH3">
         <v>15.5</v>
       </c>
       <c r="AI3">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ3">
         <v>22</v>
@@ -1314,31 +1314,31 @@
         <v>60</v>
       </c>
       <c r="AN3">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AO3">
         <v>32</v>
       </c>
       <c r="AP3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ3">
         <v>20</v>
       </c>
       <c r="AR3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AS3">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="AT3">
         <v>12</v>
       </c>
       <c r="AU3">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV3">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AW3">
         <v>36</v>
@@ -1350,7 +1350,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ3">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA3">
         <v>38</v>
@@ -1359,7 +1359,7 @@
         <v>20</v>
       </c>
       <c r="BC3">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BD3">
         <v>23</v>
@@ -1368,7 +1368,7 @@
         <v>50</v>
       </c>
       <c r="BF3">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BG3">
         <v>28</v>
@@ -1389,7 +1389,7 @@
         <v>95</v>
       </c>
       <c r="BM3">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BN3">
         <v>5</v>
@@ -1401,13 +1401,13 @@
         <v>12</v>
       </c>
       <c r="BQ3">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR3">
         <v>24</v>
       </c>
       <c r="BS3">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BT3">
         <v>7.8</v>
@@ -1419,10 +1419,10 @@
         <v>34</v>
       </c>
       <c r="BW3">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX3">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BY3">
         <v>10.5</v>
@@ -1431,7 +1431,7 @@
         <v>14.5</v>
       </c>
       <c r="CA3">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB3" t="s">
         <v>120</v>
@@ -1454,64 +1454,64 @@
         <v>109</v>
       </c>
       <c r="F4">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="G4">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H4">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="I4">
+        <v>4.1</v>
+      </c>
+      <c r="J4">
         <v>3.95</v>
       </c>
-      <c r="J4">
-        <v>4.1</v>
-      </c>
       <c r="K4">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="L4">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="M4">
         <v>1.04</v>
       </c>
       <c r="N4">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="O4">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="P4">
+        <v>2.38</v>
+      </c>
+      <c r="Q4">
+        <v>1.61</v>
+      </c>
+      <c r="R4">
+        <v>1.58</v>
+      </c>
+      <c r="S4">
+        <v>2.52</v>
+      </c>
+      <c r="T4">
+        <v>1.54</v>
+      </c>
+      <c r="U4">
         <v>2.4</v>
       </c>
-      <c r="Q4">
-        <v>1.66</v>
-      </c>
-      <c r="R4">
-        <v>1.52</v>
-      </c>
-      <c r="S4">
-        <v>2.78</v>
-      </c>
-      <c r="T4">
-        <v>1.52</v>
-      </c>
-      <c r="U4">
-        <v>2.36</v>
-      </c>
       <c r="V4">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W4">
         <v>1.96</v>
       </c>
       <c r="X4">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="Y4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Z4">
         <v>38</v>
@@ -1520,91 +1520,91 @@
         <v>85</v>
       </c>
       <c r="AB4">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AC4">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AD4">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AE4">
+        <v>48</v>
+      </c>
+      <c r="AF4">
+        <v>18</v>
+      </c>
+      <c r="AG4">
+        <v>13.5</v>
+      </c>
+      <c r="AH4">
+        <v>19.5</v>
+      </c>
+      <c r="AI4">
         <v>50</v>
       </c>
-      <c r="AF4">
-        <v>17</v>
-      </c>
-      <c r="AG4">
-        <v>13</v>
-      </c>
-      <c r="AH4">
-        <v>20</v>
-      </c>
-      <c r="AI4">
-        <v>55</v>
-      </c>
       <c r="AJ4">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AK4">
         <v>23</v>
       </c>
       <c r="AL4">
+        <v>34</v>
+      </c>
+      <c r="AM4">
+        <v>80</v>
+      </c>
+      <c r="AN4">
+        <v>10</v>
+      </c>
+      <c r="AO4">
         <v>36</v>
       </c>
-      <c r="AM4">
-        <v>85</v>
-      </c>
-      <c r="AN4">
-        <v>12.5</v>
-      </c>
-      <c r="AO4">
-        <v>40</v>
-      </c>
       <c r="AP4">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AQ4">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR4">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AS4">
         <v>1.03</v>
       </c>
       <c r="AT4">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AU4">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV4">
         <v>12</v>
       </c>
       <c r="AW4">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AX4">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY4">
         <v>8</v>
       </c>
       <c r="AZ4">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BA4">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="BB4">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BC4">
         <v>13.5</v>
       </c>
       <c r="BD4">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="BE4">
         <v>1.03</v>
@@ -1613,19 +1613,19 @@
         <v>7</v>
       </c>
       <c r="BG4">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="BH4">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BI4">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="BJ4">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK4">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BL4">
         <v>1000</v>
@@ -1634,22 +1634,22 @@
         <v>55</v>
       </c>
       <c r="BN4">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BO4">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BP4">
         <v>15.5</v>
       </c>
       <c r="BQ4">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR4">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BS4">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BT4">
         <v>9</v>
@@ -1661,19 +1661,19 @@
         <v>34</v>
       </c>
       <c r="BW4">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BX4">
         <v>40</v>
       </c>
       <c r="BY4">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BZ4">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="CA4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="CB4" t="s">
         <v>120</v>
@@ -1696,22 +1696,22 @@
         <v>110</v>
       </c>
       <c r="F5">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="G5">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="H5">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="I5">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="J5">
-        <v>1.12</v>
+        <v>5.3</v>
       </c>
       <c r="K5">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L5">
         <v>1.01</v>
@@ -1729,13 +1729,13 @@
         <v>1.12</v>
       </c>
       <c r="Q5">
-        <v>1.24</v>
+        <v>1.02</v>
       </c>
       <c r="R5">
         <v>1.08</v>
       </c>
       <c r="S5">
-        <v>1.83</v>
+        <v>1.02</v>
       </c>
       <c r="T5">
         <v>1.01</v>
@@ -1744,10 +1744,10 @@
         <v>1.01</v>
       </c>
       <c r="V5">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="W5">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="X5">
         <v>1000</v>
@@ -1941,13 +1941,13 @@
         <v>3.75</v>
       </c>
       <c r="G6">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="H6">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="I6">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="J6">
         <v>2.9</v>
@@ -1956,22 +1956,22 @@
         <v>2.92</v>
       </c>
       <c r="L6">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="M6">
         <v>1.17</v>
       </c>
       <c r="N6">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="O6">
         <v>1.74</v>
       </c>
       <c r="P6">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="Q6">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="R6">
         <v>1.13</v>
@@ -1980,7 +1980,7 @@
         <v>8</v>
       </c>
       <c r="T6">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="U6">
         <v>1.61</v>
@@ -1989,7 +1989,7 @@
         <v>1.64</v>
       </c>
       <c r="W6">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="X6">
         <v>6.8</v>
@@ -1998,7 +1998,7 @@
         <v>6.4</v>
       </c>
       <c r="Z6">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AA6">
         <v>42</v>
@@ -2019,13 +2019,13 @@
         <v>24</v>
       </c>
       <c r="AG6">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AH6">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AI6">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="AJ6">
         <v>110</v>
@@ -2034,7 +2034,7 @@
         <v>85</v>
       </c>
       <c r="AL6">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AM6">
         <v>320</v>
@@ -2055,7 +2055,7 @@
         <v>11.5</v>
       </c>
       <c r="AS6">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AT6">
         <v>8.199999999999999</v>
@@ -2079,13 +2079,13 @@
         <v>28</v>
       </c>
       <c r="BA6">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BB6">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BC6">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BD6">
         <v>14.5</v>
@@ -2180,67 +2180,67 @@
         <v>112</v>
       </c>
       <c r="F7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G7">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="H7">
         <v>1.33</v>
       </c>
       <c r="I7">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="J7">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="K7">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="L7">
         <v>1.44</v>
       </c>
       <c r="M7">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N7">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="O7">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="P7">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="Q7">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="R7">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="S7">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="T7">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="U7">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="V7">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="W7">
         <v>1.07</v>
       </c>
       <c r="X7">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y7">
+        <v>5.5</v>
+      </c>
+      <c r="Z7">
         <v>5.9</v>
-      </c>
-      <c r="Z7">
-        <v>6.2</v>
       </c>
       <c r="AA7">
         <v>9.6</v>
@@ -2252,94 +2252,94 @@
         <v>13.5</v>
       </c>
       <c r="AD7">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AF7">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AG7">
+        <v>70</v>
+      </c>
+      <c r="AH7">
         <v>65</v>
       </c>
-      <c r="AH7">
-        <v>55</v>
-      </c>
       <c r="AI7">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AJ7">
         <v>1000</v>
       </c>
       <c r="AK7">
-        <v>490</v>
+        <v>670</v>
       </c>
       <c r="AL7">
-        <v>400</v>
+        <v>520</v>
       </c>
       <c r="AM7">
-        <v>570</v>
+        <v>760</v>
       </c>
       <c r="AN7">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="AO7">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AP7">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AQ7">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="AR7">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="AS7">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AT7">
         <v>27</v>
       </c>
       <c r="AU7">
+        <v>12.5</v>
+      </c>
+      <c r="AV7">
         <v>11.5</v>
       </c>
-      <c r="AV7">
-        <v>10.5</v>
-      </c>
       <c r="AW7">
+        <v>18</v>
+      </c>
+      <c r="AX7">
+        <v>17.5</v>
+      </c>
+      <c r="AY7">
+        <v>55</v>
+      </c>
+      <c r="AZ7">
+        <v>50</v>
+      </c>
+      <c r="BA7">
+        <v>16</v>
+      </c>
+      <c r="BB7">
+        <v>18.5</v>
+      </c>
+      <c r="BC7">
         <v>16.5</v>
       </c>
-      <c r="AX7">
-        <v>15</v>
-      </c>
-      <c r="AY7">
-        <v>50</v>
-      </c>
-      <c r="AZ7">
-        <v>40</v>
-      </c>
-      <c r="BA7">
-        <v>55</v>
-      </c>
-      <c r="BB7">
-        <v>16</v>
-      </c>
-      <c r="BC7">
-        <v>15.5</v>
-      </c>
       <c r="BD7">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BE7">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BF7">
-        <v>15.5</v>
+        <v>19.5</v>
       </c>
       <c r="BG7">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BH7">
         <v>3.25</v>
@@ -2363,7 +2363,7 @@
         <v>1000</v>
       </c>
       <c r="BO7">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="BP7">
         <v>1000</v>
@@ -2390,7 +2390,7 @@
         <v>7</v>
       </c>
       <c r="BX7">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY7">
         <v>26</v>
@@ -2399,7 +2399,7 @@
         <v>18</v>
       </c>
       <c r="CA7">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="CB7" t="s">
         <v>120</v>
@@ -2422,16 +2422,16 @@
         <v>113</v>
       </c>
       <c r="F8">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="G8">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="H8">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="I8">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="J8">
         <v>3.9</v>
@@ -2464,31 +2464,31 @@
         <v>2.38</v>
       </c>
       <c r="T8">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="U8">
         <v>2.84</v>
       </c>
       <c r="V8">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="W8">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="X8">
         <v>25</v>
       </c>
       <c r="Y8">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Z8">
         <v>23</v>
       </c>
       <c r="AA8">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AB8">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AC8">
         <v>9.4</v>
@@ -2497,7 +2497,7 @@
         <v>13</v>
       </c>
       <c r="AE8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AF8">
         <v>20</v>
@@ -2509,13 +2509,13 @@
         <v>14</v>
       </c>
       <c r="AI8">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AJ8">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AK8">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL8">
         <v>27</v>
@@ -2527,34 +2527,34 @@
         <v>13.5</v>
       </c>
       <c r="AO8">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AP8">
         <v>23</v>
       </c>
       <c r="AQ8">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AR8">
         <v>21</v>
       </c>
       <c r="AS8">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AT8">
         <v>15</v>
       </c>
       <c r="AU8">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AV8">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW8">
         <v>23</v>
       </c>
       <c r="AX8">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AY8">
         <v>11.5</v>
@@ -2563,7 +2563,7 @@
         <v>13</v>
       </c>
       <c r="BA8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BB8">
         <v>34</v>
@@ -2578,13 +2578,13 @@
         <v>44</v>
       </c>
       <c r="BF8">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BG8">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BH8">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BI8">
         <v>4.1</v>
@@ -2599,25 +2599,25 @@
         <v>70</v>
       </c>
       <c r="BM8">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="BN8">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BO8">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BP8">
         <v>17</v>
       </c>
       <c r="BQ8">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BR8">
         <v>24</v>
       </c>
       <c r="BS8">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT8">
         <v>6.4</v>
@@ -2626,22 +2626,22 @@
         <v>5.8</v>
       </c>
       <c r="BV8">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BW8">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BX8">
         <v>26</v>
       </c>
       <c r="BY8">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BZ8">
         <v>15.5</v>
       </c>
       <c r="CA8">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="CB8" t="s">
         <v>120</v>
@@ -2670,7 +2670,7 @@
         <v>1.83</v>
       </c>
       <c r="H9">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I9">
         <v>4.8</v>
@@ -2688,25 +2688,25 @@
         <v>1.05</v>
       </c>
       <c r="N9">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="O9">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P9">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q9">
+        <v>1.73</v>
+      </c>
+      <c r="R9">
+        <v>1.52</v>
+      </c>
+      <c r="S9">
+        <v>2.8</v>
+      </c>
+      <c r="T9">
         <v>1.74</v>
-      </c>
-      <c r="R9">
-        <v>1.49</v>
-      </c>
-      <c r="S9">
-        <v>2.86</v>
-      </c>
-      <c r="T9">
-        <v>1.75</v>
       </c>
       <c r="U9">
         <v>2.28</v>
@@ -2730,10 +2730,10 @@
         <v>100</v>
       </c>
       <c r="AB9">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC9">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD9">
         <v>18.5</v>
@@ -2745,7 +2745,7 @@
         <v>12</v>
       </c>
       <c r="AG9">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH9">
         <v>18</v>
@@ -2763,34 +2763,34 @@
         <v>32</v>
       </c>
       <c r="AM9">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN9">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AO9">
         <v>55</v>
       </c>
       <c r="AP9">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ9">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AR9">
         <v>34</v>
       </c>
       <c r="AS9">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AT9">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU9">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV9">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AW9">
         <v>48</v>
@@ -2805,7 +2805,7 @@
         <v>17</v>
       </c>
       <c r="BA9">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BB9">
         <v>17.5</v>
@@ -2820,13 +2820,13 @@
         <v>70</v>
       </c>
       <c r="BF9">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG9">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="BH9">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BI9">
         <v>3.55</v>
@@ -2841,7 +2841,7 @@
         <v>110</v>
       </c>
       <c r="BM9">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BN9">
         <v>4.6</v>
@@ -2853,13 +2853,13 @@
         <v>11.5</v>
       </c>
       <c r="BQ9">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BR9">
         <v>24</v>
       </c>
       <c r="BS9">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BT9">
         <v>8.4</v>
@@ -2871,19 +2871,19 @@
         <v>38</v>
       </c>
       <c r="BW9">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BX9">
         <v>44</v>
       </c>
       <c r="BY9">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BZ9">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="CA9">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="CB9" t="s">
         <v>120</v>
@@ -2924,34 +2924,34 @@
         <v>3.3</v>
       </c>
       <c r="L10">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="M10">
         <v>1.11</v>
       </c>
       <c r="N10">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="O10">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="P10">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="Q10">
         <v>2.44</v>
       </c>
       <c r="R10">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S10">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T10">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U10">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="V10">
         <v>1.42</v>
@@ -2969,7 +2969,7 @@
         <v>21</v>
       </c>
       <c r="AA10">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AB10">
         <v>8.6</v>
@@ -2981,31 +2981,31 @@
         <v>15</v>
       </c>
       <c r="AE10">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AF10">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG10">
         <v>12.5</v>
       </c>
       <c r="AH10">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI10">
         <v>70</v>
       </c>
       <c r="AJ10">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AK10">
         <v>34</v>
       </c>
       <c r="AL10">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM10">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AN10">
         <v>32</v>
@@ -3032,10 +3032,10 @@
         <v>6.8</v>
       </c>
       <c r="AV10">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AW10">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="AX10">
         <v>13</v>
@@ -3053,25 +3053,25 @@
         <v>32</v>
       </c>
       <c r="BC10">
+        <v>29</v>
+      </c>
+      <c r="BD10">
+        <v>50</v>
+      </c>
+      <c r="BE10">
+        <v>14.5</v>
+      </c>
+      <c r="BF10">
         <v>28</v>
-      </c>
-      <c r="BD10">
-        <v>48</v>
-      </c>
-      <c r="BE10">
-        <v>16</v>
-      </c>
-      <c r="BF10">
-        <v>27</v>
       </c>
       <c r="BG10">
         <v>46</v>
       </c>
       <c r="BH10">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="BI10">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="BJ10">
         <v>10.5</v>
@@ -3083,10 +3083,10 @@
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="BN10">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BO10">
         <v>4.8</v>
@@ -3095,13 +3095,13 @@
         <v>21</v>
       </c>
       <c r="BQ10">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="BR10">
         <v>40</v>
       </c>
       <c r="BS10">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BT10">
         <v>6.2</v>
@@ -3110,22 +3110,22 @@
         <v>5.7</v>
       </c>
       <c r="BV10">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BW10">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="BZ10">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="CA10">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="CB10" t="s">
         <v>120</v>
@@ -3154,10 +3154,10 @@
         <v>1.46</v>
       </c>
       <c r="H11">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="I11">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J11">
         <v>5.3</v>
@@ -3181,22 +3181,22 @@
         <v>2.74</v>
       </c>
       <c r="Q11">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="R11">
         <v>1.68</v>
       </c>
       <c r="S11">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="T11">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="U11">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V11">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="W11">
         <v>3.15</v>
@@ -3211,7 +3211,7 @@
         <v>75</v>
       </c>
       <c r="AA11">
-        <v>230</v>
+        <v>260</v>
       </c>
       <c r="AB11">
         <v>12</v>
@@ -3220,10 +3220,10 @@
         <v>12.5</v>
       </c>
       <c r="AD11">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE11">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AF11">
         <v>10.5</v>
@@ -3235,13 +3235,13 @@
         <v>22</v>
       </c>
       <c r="AI11">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AJ11">
         <v>13.5</v>
       </c>
       <c r="AK11">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AL11">
         <v>28</v>
@@ -3250,7 +3250,7 @@
         <v>90</v>
       </c>
       <c r="AN11">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AO11">
         <v>90</v>
@@ -3265,7 +3265,7 @@
         <v>60</v>
       </c>
       <c r="AS11">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AT11">
         <v>10.5</v>
@@ -3277,13 +3277,13 @@
         <v>25</v>
       </c>
       <c r="AW11">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AX11">
         <v>9.199999999999999</v>
       </c>
       <c r="AY11">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ11">
         <v>19</v>
@@ -3298,13 +3298,13 @@
         <v>12.5</v>
       </c>
       <c r="BD11">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BE11">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BF11">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BG11">
         <v>60</v>
@@ -3319,13 +3319,13 @@
         <v>12.5</v>
       </c>
       <c r="BK11">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BL11">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="BM11">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BN11">
         <v>4.3</v>
@@ -3334,7 +3334,7 @@
         <v>3.85</v>
       </c>
       <c r="BP11">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="BQ11">
         <v>7.4</v>
@@ -3343,31 +3343,31 @@
         <v>24</v>
       </c>
       <c r="BS11">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BT11">
         <v>13.5</v>
       </c>
       <c r="BU11">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BV11">
         <v>70</v>
       </c>
       <c r="BW11">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BX11">
         <v>65</v>
       </c>
       <c r="BY11">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BZ11">
         <v>14</v>
       </c>
       <c r="CA11">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="CB11" t="s">
         <v>120</v>
@@ -3393,13 +3393,13 @@
         <v>2.78</v>
       </c>
       <c r="G12">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="H12">
         <v>2.84</v>
       </c>
       <c r="I12">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="J12">
         <v>3.4</v>
@@ -3426,7 +3426,7 @@
         <v>2.22</v>
       </c>
       <c r="R12">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S12">
         <v>4.1</v>
@@ -3435,7 +3435,7 @@
         <v>1.94</v>
       </c>
       <c r="U12">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V12">
         <v>1.53</v>
@@ -3447,10 +3447,10 @@
         <v>12.5</v>
       </c>
       <c r="Y12">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Z12">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AA12">
         <v>46</v>
@@ -3477,7 +3477,7 @@
         <v>19.5</v>
       </c>
       <c r="AI12">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AJ12">
         <v>44</v>
@@ -3495,7 +3495,7 @@
         <v>34</v>
       </c>
       <c r="AO12">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AP12">
         <v>11.5</v>
@@ -3510,7 +3510,7 @@
         <v>38</v>
       </c>
       <c r="AT12">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AU12">
         <v>7.2</v>
@@ -3543,19 +3543,19 @@
         <v>44</v>
       </c>
       <c r="BE12">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="BF12">
         <v>29</v>
       </c>
       <c r="BG12">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BH12">
         <v>3.05</v>
       </c>
       <c r="BI12">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="BJ12">
         <v>11.5</v>
@@ -3579,16 +3579,16 @@
         <v>24</v>
       </c>
       <c r="BQ12">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BR12">
         <v>40</v>
       </c>
       <c r="BS12">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BT12">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BU12">
         <v>5.2</v>
@@ -3597,19 +3597,19 @@
         <v>24</v>
       </c>
       <c r="BW12">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BX12">
         <v>44</v>
       </c>
       <c r="BY12">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ12">
         <v>36</v>
       </c>
       <c r="CA12">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="CB12" t="s">
         <v>120</v>
@@ -3641,7 +3641,7 @@
         <v>17.5</v>
       </c>
       <c r="I13">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="J13">
         <v>7.2</v>
@@ -3653,7 +3653,7 @@
         <v>1.29</v>
       </c>
       <c r="M13">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N13">
         <v>5.8</v>
@@ -3665,13 +3665,13 @@
         <v>2.64</v>
       </c>
       <c r="Q13">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="R13">
         <v>1.65</v>
       </c>
       <c r="S13">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="T13">
         <v>2.28</v>
@@ -3719,7 +3719,7 @@
         <v>38</v>
       </c>
       <c r="AI13">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="AJ13">
         <v>8.800000000000001</v>
@@ -3731,7 +3731,7 @@
         <v>46</v>
       </c>
       <c r="AM13">
-        <v>230</v>
+        <v>260</v>
       </c>
       <c r="AN13">
         <v>3.95</v>
@@ -3740,28 +3740,28 @@
         <v>360</v>
       </c>
       <c r="AP13">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ13">
         <v>44</v>
       </c>
       <c r="AR13">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="AS13">
         <v>19</v>
       </c>
       <c r="AT13">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU13">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AV13">
         <v>50</v>
       </c>
       <c r="AW13">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AX13">
         <v>7.2</v>
@@ -3773,28 +3773,28 @@
         <v>34</v>
       </c>
       <c r="BA13">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BB13">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC13">
         <v>13</v>
       </c>
       <c r="BD13">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BE13">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BF13">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BG13">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BH13">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BI13">
         <v>4.1</v>
@@ -3821,13 +3821,13 @@
         <v>6.6</v>
       </c>
       <c r="BQ13">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BR13">
         <v>28</v>
       </c>
       <c r="BS13">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BT13">
         <v>21</v>
@@ -3839,13 +3839,13 @@
         <v>170</v>
       </c>
       <c r="BW13">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BX13">
         <v>130</v>
       </c>
       <c r="BY13">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BZ13">
         <v>0</v>
@@ -3874,7 +3874,7 @@
         <v>119</v>
       </c>
       <c r="F14">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="G14">
         <v>4.1</v>
@@ -3892,7 +3892,7 @@
         <v>3.15</v>
       </c>
       <c r="L14">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="M14">
         <v>1.15</v>
@@ -3901,7 +3901,7 @@
         <v>2.34</v>
       </c>
       <c r="O14">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="P14">
         <v>1.46</v>
@@ -4036,58 +4036,58 @@
         <v>6.6</v>
       </c>
       <c r="BH14">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="BI14">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="BJ14">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK14">
-        <v>1.64</v>
+        <v>5.8</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>1.64</v>
+        <v>2.04</v>
       </c>
       <c r="BN14">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BO14">
-        <v>1.64</v>
+        <v>4.2</v>
       </c>
       <c r="BP14">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BQ14">
-        <v>1.64</v>
+        <v>1.97</v>
       </c>
       <c r="BR14">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BS14">
-        <v>1.64</v>
+        <v>2</v>
       </c>
       <c r="BT14">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BU14">
-        <v>1.64</v>
+        <v>3.55</v>
       </c>
       <c r="BV14">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BW14">
-        <v>1.64</v>
+        <v>1.91</v>
       </c>
       <c r="BX14">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY14">
-        <v>1.64</v>
+        <v>2</v>
       </c>
       <c r="BZ14">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-24.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="128">
   <si>
     <t>League</t>
   </si>
@@ -271,6 +271,12 @@
     <t>UEFA Nations League</t>
   </si>
   <si>
+    <t>CONCACAF Nations League B</t>
+  </si>
+  <si>
+    <t>Ecuadorian Serie B</t>
+  </si>
+  <si>
     <t>Moroccan Botola Pro 1</t>
   </si>
   <si>
@@ -295,6 +301,9 @@
     <t>18:45:00</t>
   </si>
   <si>
+    <t>19:00:00</t>
+  </si>
+  <si>
     <t>20:00:00</t>
   </si>
   <si>
@@ -334,6 +343,12 @@
     <t>Portugal</t>
   </si>
   <si>
+    <t>Puerto Rico</t>
+  </si>
+  <si>
+    <t>Atletico Rojiblanco</t>
+  </si>
+  <si>
     <t>US Amal Tiznit</t>
   </si>
   <si>
@@ -373,10 +388,16 @@
     <t>Wales</t>
   </si>
   <si>
+    <t>Guyana</t>
+  </si>
+  <si>
+    <t>CD Cuenca Juniors</t>
+  </si>
+  <si>
     <t>IRT Tanger</t>
   </si>
   <si>
-    <t>2026-09-23 07:53:17</t>
+    <t>2026-09-23 10:07:11</t>
   </si>
 </sst>
 </file>
@@ -708,7 +729,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB14"/>
+  <dimension ref="A1:CB16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -958,16 +979,16 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E2" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="F2">
         <v>1.67</v>
@@ -979,10 +1000,10 @@
         <v>6</v>
       </c>
       <c r="I2">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J2">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K2">
         <v>4.2</v>
@@ -994,13 +1015,13 @@
         <v>1.07</v>
       </c>
       <c r="N2">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="O2">
         <v>1.35</v>
       </c>
       <c r="P2">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="Q2">
         <v>2.04</v>
@@ -1015,16 +1036,16 @@
         <v>2.02</v>
       </c>
       <c r="U2">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="V2">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W2">
         <v>2.44</v>
       </c>
       <c r="X2">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="Y2">
         <v>24</v>
@@ -1039,67 +1060,67 @@
         <v>7.8</v>
       </c>
       <c r="AC2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD2">
+        <v>24</v>
+      </c>
+      <c r="AE2">
+        <v>120</v>
+      </c>
+      <c r="AF2">
         <v>9.4</v>
       </c>
-      <c r="AD2">
-        <v>30</v>
-      </c>
-      <c r="AE2">
-        <v>110</v>
-      </c>
-      <c r="AF2">
-        <v>9.6</v>
-      </c>
       <c r="AG2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH2">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AI2">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AJ2">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="AK2">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AL2">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AM2">
+        <v>160</v>
+      </c>
+      <c r="AN2">
+        <v>11.5</v>
+      </c>
+      <c r="AO2">
         <v>170</v>
-      </c>
-      <c r="AN2">
-        <v>13</v>
-      </c>
-      <c r="AO2">
-        <v>150</v>
       </c>
       <c r="AP2">
         <v>12</v>
       </c>
       <c r="AQ2">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AR2">
         <v>38</v>
       </c>
       <c r="AS2">
-        <v>7.2</v>
+        <v>12.5</v>
       </c>
       <c r="AT2">
         <v>7</v>
       </c>
       <c r="AU2">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV2">
-        <v>6.4</v>
+        <v>20</v>
       </c>
       <c r="AW2">
-        <v>7.8</v>
+        <v>60</v>
       </c>
       <c r="AX2">
         <v>8.6</v>
@@ -1108,10 +1129,10 @@
         <v>9</v>
       </c>
       <c r="AZ2">
-        <v>10.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA2">
-        <v>7.8</v>
+        <v>55</v>
       </c>
       <c r="BB2">
         <v>14.5</v>
@@ -1120,34 +1141,34 @@
         <v>16</v>
       </c>
       <c r="BD2">
-        <v>6.4</v>
+        <v>28</v>
       </c>
       <c r="BE2">
-        <v>7</v>
+        <v>90</v>
       </c>
       <c r="BF2">
         <v>10</v>
       </c>
       <c r="BG2">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="BH2">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BI2">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="BJ2">
         <v>11</v>
       </c>
       <c r="BK2">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BL2">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="BM2">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN2">
         <v>4.2</v>
@@ -1156,43 +1177,43 @@
         <v>3.75</v>
       </c>
       <c r="BP2">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BQ2">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="BR2">
         <v>34</v>
       </c>
       <c r="BS2">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BT2">
         <v>9.4</v>
       </c>
       <c r="BU2">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="BV2">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BW2">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BX2">
         <v>75</v>
       </c>
       <c r="BY2">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BZ2">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="CA2">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="CB2" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1200,76 +1221,76 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E3" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="F3">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="G3">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="H3">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="I3">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="J3">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K3">
         <v>4.2</v>
       </c>
       <c r="L3">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="M3">
         <v>1.04</v>
       </c>
       <c r="N3">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="O3">
         <v>1.19</v>
       </c>
       <c r="P3">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="Q3">
+        <v>1.58</v>
+      </c>
+      <c r="R3">
+        <v>1.65</v>
+      </c>
+      <c r="S3">
+        <v>2.46</v>
+      </c>
+      <c r="T3">
         <v>1.59</v>
       </c>
-      <c r="R3">
-        <v>1.64</v>
-      </c>
-      <c r="S3">
-        <v>2.48</v>
-      </c>
-      <c r="T3">
-        <v>1.58</v>
-      </c>
       <c r="U3">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="V3">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W3">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="X3">
         <v>24</v>
       </c>
       <c r="Y3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Z3">
         <v>38</v>
@@ -1278,13 +1299,13 @@
         <v>90</v>
       </c>
       <c r="AB3">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AC3">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD3">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AE3">
         <v>46</v>
@@ -1296,16 +1317,16 @@
         <v>10.5</v>
       </c>
       <c r="AH3">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AI3">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AJ3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK3">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AL3">
         <v>26</v>
@@ -1314,10 +1335,10 @@
         <v>60</v>
       </c>
       <c r="AN3">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AO3">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AP3">
         <v>22</v>
@@ -1326,37 +1347,37 @@
         <v>20</v>
       </c>
       <c r="AR3">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AS3">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AT3">
         <v>12</v>
       </c>
       <c r="AU3">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AV3">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AW3">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AX3">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AY3">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ3">
         <v>14</v>
       </c>
       <c r="BA3">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BB3">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BC3">
         <v>15</v>
@@ -1365,10 +1386,10 @@
         <v>23</v>
       </c>
       <c r="BE3">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BF3">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BG3">
         <v>28</v>
@@ -1377,10 +1398,10 @@
         <v>4.4</v>
       </c>
       <c r="BI3">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BJ3">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BK3">
         <v>7.8</v>
@@ -1389,52 +1410,52 @@
         <v>95</v>
       </c>
       <c r="BM3">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BN3">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BO3">
         <v>4.5</v>
       </c>
       <c r="BP3">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BQ3">
-        <v>6.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR3">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BS3">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT3">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BU3">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BV3">
+        <v>32</v>
+      </c>
+      <c r="BW3">
+        <v>11.5</v>
+      </c>
+      <c r="BX3">
         <v>34</v>
       </c>
-      <c r="BW3">
-        <v>10.5</v>
-      </c>
-      <c r="BX3">
-        <v>38</v>
-      </c>
       <c r="BY3">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BZ3">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="CA3">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB3" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1442,175 +1463,175 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D4" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E4" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="F4">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="G4">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="H4">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="I4">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="J4">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="K4">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="L4">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M4">
         <v>1.04</v>
       </c>
       <c r="N4">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="O4">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P4">
-        <v>2.38</v>
+        <v>2.52</v>
       </c>
       <c r="Q4">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="R4">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="S4">
+        <v>2.5</v>
+      </c>
+      <c r="T4">
+        <v>1.59</v>
+      </c>
+      <c r="U4">
         <v>2.52</v>
-      </c>
-      <c r="T4">
-        <v>1.54</v>
-      </c>
-      <c r="U4">
-        <v>2.4</v>
       </c>
       <c r="V4">
         <v>1.33</v>
       </c>
       <c r="W4">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="X4">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Y4">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Z4">
+        <v>40</v>
+      </c>
+      <c r="AA4">
+        <v>90</v>
+      </c>
+      <c r="AB4">
+        <v>13</v>
+      </c>
+      <c r="AC4">
+        <v>11.5</v>
+      </c>
+      <c r="AD4">
+        <v>21</v>
+      </c>
+      <c r="AE4">
+        <v>50</v>
+      </c>
+      <c r="AF4">
+        <v>17</v>
+      </c>
+      <c r="AG4">
+        <v>12.5</v>
+      </c>
+      <c r="AH4">
+        <v>18.5</v>
+      </c>
+      <c r="AI4">
+        <v>55</v>
+      </c>
+      <c r="AJ4">
+        <v>23</v>
+      </c>
+      <c r="AK4">
+        <v>22</v>
+      </c>
+      <c r="AL4">
+        <v>28</v>
+      </c>
+      <c r="AM4">
+        <v>85</v>
+      </c>
+      <c r="AN4">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AO4">
         <v>38</v>
-      </c>
-      <c r="AA4">
-        <v>85</v>
-      </c>
-      <c r="AB4">
-        <v>16</v>
-      </c>
-      <c r="AC4">
-        <v>12</v>
-      </c>
-      <c r="AD4">
-        <v>19.5</v>
-      </c>
-      <c r="AE4">
-        <v>48</v>
-      </c>
-      <c r="AF4">
-        <v>18</v>
-      </c>
-      <c r="AG4">
-        <v>13.5</v>
-      </c>
-      <c r="AH4">
-        <v>19.5</v>
-      </c>
-      <c r="AI4">
-        <v>50</v>
-      </c>
-      <c r="AJ4">
-        <v>28</v>
-      </c>
-      <c r="AK4">
-        <v>23</v>
-      </c>
-      <c r="AL4">
-        <v>34</v>
-      </c>
-      <c r="AM4">
-        <v>80</v>
-      </c>
-      <c r="AN4">
-        <v>10</v>
-      </c>
-      <c r="AO4">
-        <v>36</v>
       </c>
       <c r="AP4">
         <v>17.5</v>
       </c>
       <c r="AQ4">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="AR4">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AS4">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="AT4">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU4">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV4">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW4">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AX4">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AY4">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ4">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BA4">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="BB4">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BC4">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BD4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BE4">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="BF4">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BG4">
         <v>21</v>
@@ -1634,7 +1655,7 @@
         <v>55</v>
       </c>
       <c r="BN4">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BO4">
         <v>3.95</v>
@@ -1643,10 +1664,10 @@
         <v>15.5</v>
       </c>
       <c r="BQ4">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BR4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BS4">
         <v>15.5</v>
@@ -1655,28 +1676,28 @@
         <v>9</v>
       </c>
       <c r="BU4">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BV4">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BW4">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BX4">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BY4">
         <v>22</v>
       </c>
       <c r="BZ4">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="CA4">
         <v>11</v>
       </c>
       <c r="CB4" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1684,16 +1705,16 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D5" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E5" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F5">
         <v>1.22</v>
@@ -1918,7 +1939,7 @@
         <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1926,19 +1947,19 @@
         <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C6" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D6" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E6" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="F6">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="G6">
         <v>3.85</v>
@@ -1950,61 +1971,61 @@
         <v>2.54</v>
       </c>
       <c r="J6">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="K6">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="L6">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="M6">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="N6">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="O6">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="P6">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="Q6">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="R6">
         <v>1.13</v>
       </c>
       <c r="S6">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="T6">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="U6">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="V6">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W6">
         <v>1.35</v>
       </c>
       <c r="X6">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="Y6">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="Z6">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AA6">
         <v>42</v>
       </c>
       <c r="AB6">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC6">
         <v>7</v>
@@ -2037,7 +2058,7 @@
         <v>140</v>
       </c>
       <c r="AM6">
-        <v>320</v>
+        <v>370</v>
       </c>
       <c r="AN6">
         <v>150</v>
@@ -2055,13 +2076,13 @@
         <v>11.5</v>
       </c>
       <c r="AS6">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="AT6">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AU6">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV6">
         <v>13</v>
@@ -2070,46 +2091,46 @@
         <v>40</v>
       </c>
       <c r="AX6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY6">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AZ6">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BA6">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="BB6">
-        <v>15</v>
+        <v>80</v>
       </c>
       <c r="BC6">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="BD6">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BE6">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="BF6">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BG6">
         <v>44</v>
       </c>
       <c r="BH6">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="BI6">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="BJ6">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BK6">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BL6">
         <v>1000</v>
@@ -2124,7 +2145,7 @@
         <v>6</v>
       </c>
       <c r="BP6">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BQ6">
         <v>30</v>
@@ -2133,7 +2154,7 @@
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="BT6">
         <v>5.2</v>
@@ -2142,16 +2163,16 @@
         <v>4.5</v>
       </c>
       <c r="BV6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BW6">
         <v>18</v>
       </c>
       <c r="BX6">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY6">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BZ6">
         <v>1000</v>
@@ -2160,7 +2181,7 @@
         <v>50</v>
       </c>
       <c r="CB6" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2168,16 +2189,16 @@
         <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D7" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E7" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="F7">
         <v>14</v>
@@ -2195,7 +2216,7 @@
         <v>5.3</v>
       </c>
       <c r="K7">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="L7">
         <v>1.44</v>
@@ -2210,10 +2231,10 @@
         <v>1.43</v>
       </c>
       <c r="P7">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="Q7">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="R7">
         <v>1.27</v>
@@ -2222,10 +2243,10 @@
         <v>4.3</v>
       </c>
       <c r="T7">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="U7">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="V7">
         <v>3.9</v>
@@ -2246,22 +2267,22 @@
         <v>9.6</v>
       </c>
       <c r="AB7">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AC7">
         <v>13.5</v>
       </c>
       <c r="AD7">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AE7">
         <v>20</v>
       </c>
       <c r="AF7">
-        <v>170</v>
+        <v>210</v>
       </c>
       <c r="AG7">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AH7">
         <v>65</v>
@@ -2273,10 +2294,10 @@
         <v>1000</v>
       </c>
       <c r="AK7">
-        <v>670</v>
+        <v>630</v>
       </c>
       <c r="AL7">
-        <v>520</v>
+        <v>510</v>
       </c>
       <c r="AM7">
         <v>760</v>
@@ -2297,7 +2318,7 @@
         <v>5.6</v>
       </c>
       <c r="AS7">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT7">
         <v>27</v>
@@ -2306,13 +2327,13 @@
         <v>12.5</v>
       </c>
       <c r="AV7">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW7">
         <v>18</v>
       </c>
       <c r="AX7">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AY7">
         <v>55</v>
@@ -2321,19 +2342,19 @@
         <v>50</v>
       </c>
       <c r="BA7">
+        <v>60</v>
+      </c>
+      <c r="BB7">
+        <v>19.5</v>
+      </c>
+      <c r="BC7">
+        <v>15.5</v>
+      </c>
+      <c r="BD7">
         <v>16</v>
       </c>
-      <c r="BB7">
-        <v>18.5</v>
-      </c>
-      <c r="BC7">
-        <v>16.5</v>
-      </c>
-      <c r="BD7">
-        <v>16.5</v>
-      </c>
       <c r="BE7">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BF7">
         <v>19.5</v>
@@ -2345,10 +2366,10 @@
         <v>3.25</v>
       </c>
       <c r="BI7">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="BJ7">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BK7">
         <v>12</v>
@@ -2360,7 +2381,7 @@
         <v>21</v>
       </c>
       <c r="BN7">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BO7">
         <v>13</v>
@@ -2381,7 +2402,7 @@
         <v>3.3</v>
       </c>
       <c r="BU7">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BV7">
         <v>8</v>
@@ -2402,7 +2423,7 @@
         <v>13</v>
       </c>
       <c r="CB7" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2410,106 +2431,106 @@
         <v>84</v>
       </c>
       <c r="B8" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D8" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E8" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="F8">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="G8">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="H8">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="I8">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="J8">
+        <v>3.85</v>
+      </c>
+      <c r="K8">
         <v>3.9</v>
       </c>
-      <c r="K8">
-        <v>3.95</v>
-      </c>
       <c r="L8">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="M8">
         <v>1.04</v>
       </c>
       <c r="N8">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="O8">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P8">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="Q8">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="R8">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="S8">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="T8">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="U8">
-        <v>2.84</v>
+        <v>2.94</v>
       </c>
       <c r="V8">
         <v>1.53</v>
       </c>
       <c r="W8">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="X8">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="Y8">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Z8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA8">
         <v>44</v>
       </c>
       <c r="AB8">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AC8">
         <v>9.4</v>
       </c>
       <c r="AD8">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AE8">
         <v>26</v>
       </c>
       <c r="AF8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG8">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH8">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AI8">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AJ8">
         <v>38</v>
@@ -2518,76 +2539,76 @@
         <v>22</v>
       </c>
       <c r="AL8">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AM8">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AN8">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AO8">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AP8">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AQ8">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AR8">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS8">
         <v>38</v>
       </c>
       <c r="AT8">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AU8">
         <v>9</v>
       </c>
       <c r="AV8">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW8">
         <v>23</v>
       </c>
       <c r="AX8">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AY8">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ8">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BA8">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BB8">
         <v>34</v>
       </c>
       <c r="BC8">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD8">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BE8">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="BF8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BG8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BH8">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BI8">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BJ8">
         <v>8.199999999999999</v>
@@ -2599,52 +2620,52 @@
         <v>70</v>
       </c>
       <c r="BM8">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BN8">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BO8">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BP8">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BQ8">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BR8">
         <v>24</v>
       </c>
       <c r="BS8">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BT8">
         <v>6.4</v>
       </c>
       <c r="BU8">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BV8">
         <v>19.5</v>
       </c>
       <c r="BW8">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX8">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BY8">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ8">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="CA8">
         <v>8</v>
       </c>
       <c r="CB8" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2652,22 +2673,22 @@
         <v>84</v>
       </c>
       <c r="B9" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D9" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E9" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F9">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="G9">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="H9">
         <v>4.7</v>
@@ -2676,13 +2697,13 @@
         <v>4.8</v>
       </c>
       <c r="J9">
+        <v>4.1</v>
+      </c>
+      <c r="K9">
         <v>4.2</v>
       </c>
-      <c r="K9">
-        <v>4.3</v>
-      </c>
       <c r="L9">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="M9">
         <v>1.05</v>
@@ -2694,28 +2715,28 @@
         <v>1.24</v>
       </c>
       <c r="P9">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="Q9">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="R9">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="S9">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="T9">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="U9">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V9">
         <v>1.26</v>
       </c>
       <c r="W9">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="X9">
         <v>19</v>
@@ -2733,10 +2754,10 @@
         <v>11</v>
       </c>
       <c r="AC9">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AD9">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE9">
         <v>55</v>
@@ -2745,22 +2766,22 @@
         <v>12</v>
       </c>
       <c r="AG9">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH9">
         <v>18</v>
       </c>
       <c r="AI9">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ9">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AK9">
         <v>17.5</v>
       </c>
       <c r="AL9">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM9">
         <v>80</v>
@@ -2769,31 +2790,31 @@
         <v>9</v>
       </c>
       <c r="AO9">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AP9">
         <v>18</v>
       </c>
       <c r="AQ9">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR9">
         <v>34</v>
       </c>
       <c r="AS9">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AT9">
         <v>10</v>
       </c>
       <c r="AU9">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV9">
         <v>17.5</v>
       </c>
       <c r="AW9">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AX9">
         <v>11</v>
@@ -2802,7 +2823,7 @@
         <v>10</v>
       </c>
       <c r="AZ9">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA9">
         <v>48</v>
@@ -2817,13 +2838,13 @@
         <v>27</v>
       </c>
       <c r="BE9">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BF9">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BG9">
-        <v>44</v>
+        <v>14.5</v>
       </c>
       <c r="BH9">
         <v>3.9</v>
@@ -2838,13 +2859,13 @@
         <v>8.4</v>
       </c>
       <c r="BL9">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="BM9">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BN9">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BO9">
         <v>4.2</v>
@@ -2859,7 +2880,7 @@
         <v>24</v>
       </c>
       <c r="BS9">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BT9">
         <v>8.4</v>
@@ -2874,19 +2895,19 @@
         <v>11</v>
       </c>
       <c r="BX9">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BY9">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BZ9">
         <v>18</v>
       </c>
       <c r="CA9">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="CB9" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2894,28 +2915,28 @@
         <v>84</v>
       </c>
       <c r="B10" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C10" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D10" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E10" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="F10">
+        <v>2.5</v>
+      </c>
+      <c r="G10">
         <v>2.52</v>
-      </c>
-      <c r="G10">
-        <v>2.56</v>
       </c>
       <c r="H10">
         <v>3.3</v>
       </c>
       <c r="I10">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="J10">
         <v>3.25</v>
@@ -2924,40 +2945,40 @@
         <v>3.3</v>
       </c>
       <c r="L10">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="M10">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N10">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="O10">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="P10">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="Q10">
         <v>2.44</v>
       </c>
       <c r="R10">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S10">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="T10">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="U10">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="V10">
         <v>1.42</v>
       </c>
       <c r="W10">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="X10">
         <v>10.5</v>
@@ -2990,19 +3011,19 @@
         <v>12.5</v>
       </c>
       <c r="AH10">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI10">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="AJ10">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AK10">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL10">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM10">
         <v>170</v>
@@ -3026,7 +3047,7 @@
         <v>50</v>
       </c>
       <c r="AT10">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AU10">
         <v>6.8</v>
@@ -3035,7 +3056,7 @@
         <v>13.5</v>
       </c>
       <c r="AW10">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="AX10">
         <v>13</v>
@@ -3059,7 +3080,7 @@
         <v>50</v>
       </c>
       <c r="BE10">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BF10">
         <v>28</v>
@@ -3068,10 +3089,10 @@
         <v>46</v>
       </c>
       <c r="BH10">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="BI10">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="BJ10">
         <v>10.5</v>
@@ -3083,10 +3104,10 @@
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BN10">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BO10">
         <v>4.8</v>
@@ -3095,13 +3116,13 @@
         <v>21</v>
       </c>
       <c r="BQ10">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BR10">
         <v>40</v>
       </c>
       <c r="BS10">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BT10">
         <v>6.2</v>
@@ -3110,25 +3131,25 @@
         <v>5.7</v>
       </c>
       <c r="BV10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BW10">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="BZ10">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="CA10">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="CB10" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3136,22 +3157,22 @@
         <v>84</v>
       </c>
       <c r="B11" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C11" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D11" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E11" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="F11">
+        <v>1.44</v>
+      </c>
+      <c r="G11">
         <v>1.45</v>
-      </c>
-      <c r="G11">
-        <v>1.46</v>
       </c>
       <c r="H11">
         <v>7.8</v>
@@ -3160,7 +3181,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="J11">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="K11">
         <v>5.5</v>
@@ -3178,7 +3199,7 @@
         <v>1.18</v>
       </c>
       <c r="P11">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="Q11">
         <v>1.56</v>
@@ -3187,19 +3208,19 @@
         <v>1.68</v>
       </c>
       <c r="S11">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="T11">
         <v>1.77</v>
       </c>
       <c r="U11">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V11">
         <v>1.13</v>
       </c>
       <c r="W11">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="X11">
         <v>26</v>
@@ -3223,7 +3244,7 @@
         <v>29</v>
       </c>
       <c r="AE11">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AF11">
         <v>10.5</v>
@@ -3235,7 +3256,7 @@
         <v>22</v>
       </c>
       <c r="AI11">
-        <v>170</v>
+        <v>85</v>
       </c>
       <c r="AJ11">
         <v>13.5</v>
@@ -3244,19 +3265,19 @@
         <v>14.5</v>
       </c>
       <c r="AL11">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AM11">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AN11">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AO11">
         <v>90</v>
       </c>
       <c r="AP11">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ11">
         <v>30</v>
@@ -3265,7 +3286,7 @@
         <v>60</v>
       </c>
       <c r="AS11">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AT11">
         <v>10.5</v>
@@ -3277,7 +3298,7 @@
         <v>25</v>
       </c>
       <c r="AW11">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AX11">
         <v>9.199999999999999</v>
@@ -3289,7 +3310,7 @@
         <v>19</v>
       </c>
       <c r="BA11">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="BB11">
         <v>12</v>
@@ -3301,16 +3322,16 @@
         <v>25</v>
       </c>
       <c r="BE11">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="BF11">
         <v>4.7</v>
       </c>
       <c r="BG11">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="BH11">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BI11">
         <v>4.1</v>
@@ -3319,22 +3340,22 @@
         <v>12.5</v>
       </c>
       <c r="BK11">
-        <v>4.9</v>
+        <v>9</v>
       </c>
       <c r="BL11">
         <v>120</v>
       </c>
       <c r="BM11">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="BN11">
         <v>4.3</v>
       </c>
       <c r="BO11">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BP11">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BQ11">
         <v>7.4</v>
@@ -3343,34 +3364,34 @@
         <v>24</v>
       </c>
       <c r="BS11">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BT11">
         <v>13.5</v>
       </c>
       <c r="BU11">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BV11">
         <v>70</v>
       </c>
       <c r="BW11">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BX11">
         <v>65</v>
       </c>
       <c r="BY11">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BZ11">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="CA11">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="CB11" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3378,28 +3399,28 @@
         <v>84</v>
       </c>
       <c r="B12" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C12" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D12" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="E12" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="F12">
+        <v>2.84</v>
+      </c>
+      <c r="G12">
+        <v>2.86</v>
+      </c>
+      <c r="H12">
         <v>2.78</v>
       </c>
-      <c r="G12">
-        <v>2.82</v>
-      </c>
-      <c r="H12">
-        <v>2.84</v>
-      </c>
       <c r="I12">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="J12">
         <v>3.4</v>
@@ -3417,19 +3438,19 @@
         <v>3.3</v>
       </c>
       <c r="O12">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P12">
         <v>1.76</v>
       </c>
       <c r="Q12">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="R12">
         <v>1.28</v>
       </c>
       <c r="S12">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T12">
         <v>1.94</v>
@@ -3438,28 +3459,28 @@
         <v>2</v>
       </c>
       <c r="V12">
+        <v>1.55</v>
+      </c>
+      <c r="W12">
         <v>1.53</v>
       </c>
-      <c r="W12">
-        <v>1.55</v>
-      </c>
       <c r="X12">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y12">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z12">
         <v>17.5</v>
       </c>
       <c r="AA12">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AB12">
         <v>9.800000000000001</v>
       </c>
       <c r="AC12">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD12">
         <v>13</v>
@@ -3468,10 +3489,10 @@
         <v>36</v>
       </c>
       <c r="AF12">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AG12">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH12">
         <v>19.5</v>
@@ -3480,10 +3501,10 @@
         <v>55</v>
       </c>
       <c r="AJ12">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AK12">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AL12">
         <v>55</v>
@@ -3492,22 +3513,22 @@
         <v>120</v>
       </c>
       <c r="AN12">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AO12">
         <v>34</v>
       </c>
       <c r="AP12">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AQ12">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR12">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AS12">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AT12">
         <v>9.4</v>
@@ -3528,7 +3549,7 @@
         <v>12.5</v>
       </c>
       <c r="AZ12">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BA12">
         <v>44</v>
@@ -3543,10 +3564,10 @@
         <v>44</v>
       </c>
       <c r="BE12">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BF12">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BG12">
         <v>30</v>
@@ -3567,52 +3588,52 @@
         <v>160</v>
       </c>
       <c r="BM12">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BN12">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BO12">
         <v>5.2</v>
       </c>
       <c r="BP12">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="BQ12">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR12">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="BS12">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="BT12">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BU12">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BV12">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="BW12">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX12">
         <v>44</v>
       </c>
       <c r="BY12">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BZ12">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="CA12">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="CB12" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3620,178 +3641,178 @@
         <v>84</v>
       </c>
       <c r="B13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C13" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D13" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E13" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="F13">
+        <v>1.23</v>
+      </c>
+      <c r="G13">
         <v>1.24</v>
-      </c>
-      <c r="G13">
-        <v>1.25</v>
       </c>
       <c r="H13">
         <v>17.5</v>
       </c>
       <c r="I13">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="J13">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="K13">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="L13">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="M13">
         <v>1.03</v>
       </c>
       <c r="N13">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="O13">
         <v>1.19</v>
       </c>
       <c r="P13">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="Q13">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="R13">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="S13">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="T13">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="U13">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="V13">
         <v>1.05</v>
       </c>
       <c r="W13">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="X13">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Y13">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="Z13">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="AA13">
-        <v>880</v>
+        <v>1000</v>
       </c>
       <c r="AB13">
         <v>9.800000000000001</v>
       </c>
       <c r="AC13">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AD13">
         <v>60</v>
       </c>
       <c r="AE13">
-        <v>310</v>
+        <v>420</v>
       </c>
       <c r="AF13">
         <v>7.6</v>
       </c>
       <c r="AG13">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH13">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AI13">
-        <v>230</v>
+        <v>270</v>
       </c>
       <c r="AJ13">
         <v>8.800000000000001</v>
       </c>
       <c r="AK13">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AL13">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AM13">
         <v>260</v>
       </c>
       <c r="AN13">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AO13">
-        <v>360</v>
+        <v>1000</v>
       </c>
       <c r="AP13">
         <v>24</v>
       </c>
       <c r="AQ13">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AR13">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="AS13">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AT13">
         <v>9.199999999999999</v>
       </c>
       <c r="AU13">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AV13">
         <v>50</v>
       </c>
       <c r="AW13">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AX13">
         <v>7.2</v>
       </c>
       <c r="AY13">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ13">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BA13">
-        <v>24</v>
+        <v>16.5</v>
       </c>
       <c r="BB13">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BC13">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BD13">
         <v>40</v>
       </c>
       <c r="BE13">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="BF13">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BG13">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="BH13">
         <v>4.5</v>
@@ -3803,7 +3824,7 @@
         <v>16</v>
       </c>
       <c r="BK13">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BL13">
         <v>210</v>
@@ -3821,7 +3842,7 @@
         <v>6.6</v>
       </c>
       <c r="BQ13">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BR13">
         <v>28</v>
@@ -3833,7 +3854,7 @@
         <v>21</v>
       </c>
       <c r="BU13">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BV13">
         <v>170</v>
@@ -3854,7 +3875,7 @@
         <v>0</v>
       </c>
       <c r="CB13" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -3862,241 +3883,725 @@
         <v>85</v>
       </c>
       <c r="B14" t="s">
+        <v>88</v>
+      </c>
+      <c r="C14" t="s">
+        <v>95</v>
+      </c>
+      <c r="D14" t="s">
+        <v>109</v>
+      </c>
+      <c r="E14" t="s">
+        <v>124</v>
+      </c>
+      <c r="F14">
+        <v>1.1</v>
+      </c>
+      <c r="G14">
+        <v>1000</v>
+      </c>
+      <c r="H14">
+        <v>1.1</v>
+      </c>
+      <c r="I14">
+        <v>1000</v>
+      </c>
+      <c r="J14">
+        <v>1.1</v>
+      </c>
+      <c r="K14">
+        <v>950</v>
+      </c>
+      <c r="L14">
+        <v>1.01</v>
+      </c>
+      <c r="M14">
+        <v>1.01</v>
+      </c>
+      <c r="N14">
+        <v>1.12</v>
+      </c>
+      <c r="O14">
+        <v>1.01</v>
+      </c>
+      <c r="P14">
+        <v>1.12</v>
+      </c>
+      <c r="Q14">
+        <v>1.01</v>
+      </c>
+      <c r="R14">
+        <v>1.08</v>
+      </c>
+      <c r="S14">
+        <v>1.01</v>
+      </c>
+      <c r="T14">
+        <v>1.01</v>
+      </c>
+      <c r="U14">
+        <v>1.01</v>
+      </c>
+      <c r="V14">
+        <v>1.01</v>
+      </c>
+      <c r="W14">
+        <v>1.01</v>
+      </c>
+      <c r="X14">
+        <v>1000</v>
+      </c>
+      <c r="Y14">
+        <v>1000</v>
+      </c>
+      <c r="Z14">
+        <v>1000</v>
+      </c>
+      <c r="AA14">
+        <v>1000</v>
+      </c>
+      <c r="AB14">
+        <v>1000</v>
+      </c>
+      <c r="AC14">
+        <v>1000</v>
+      </c>
+      <c r="AD14">
+        <v>1000</v>
+      </c>
+      <c r="AE14">
+        <v>1000</v>
+      </c>
+      <c r="AF14">
+        <v>1000</v>
+      </c>
+      <c r="AG14">
+        <v>1000</v>
+      </c>
+      <c r="AH14">
+        <v>1000</v>
+      </c>
+      <c r="AI14">
+        <v>1000</v>
+      </c>
+      <c r="AJ14">
+        <v>1000</v>
+      </c>
+      <c r="AK14">
+        <v>1000</v>
+      </c>
+      <c r="AL14">
+        <v>1000</v>
+      </c>
+      <c r="AM14">
+        <v>1000</v>
+      </c>
+      <c r="AN14">
+        <v>1000</v>
+      </c>
+      <c r="AO14">
+        <v>1000</v>
+      </c>
+      <c r="AP14">
+        <v>1.03</v>
+      </c>
+      <c r="AQ14">
+        <v>1.03</v>
+      </c>
+      <c r="AR14">
+        <v>1.03</v>
+      </c>
+      <c r="AS14">
+        <v>1.03</v>
+      </c>
+      <c r="AT14">
+        <v>1.03</v>
+      </c>
+      <c r="AU14">
+        <v>1.03</v>
+      </c>
+      <c r="AV14">
+        <v>1.03</v>
+      </c>
+      <c r="AW14">
+        <v>1.03</v>
+      </c>
+      <c r="AX14">
+        <v>1.03</v>
+      </c>
+      <c r="AY14">
+        <v>1.03</v>
+      </c>
+      <c r="AZ14">
+        <v>1.03</v>
+      </c>
+      <c r="BA14">
+        <v>1.03</v>
+      </c>
+      <c r="BB14">
+        <v>1.03</v>
+      </c>
+      <c r="BC14">
+        <v>1.03</v>
+      </c>
+      <c r="BD14">
+        <v>1.03</v>
+      </c>
+      <c r="BE14">
+        <v>1.03</v>
+      </c>
+      <c r="BF14">
+        <v>1.01</v>
+      </c>
+      <c r="BG14">
+        <v>1.01</v>
+      </c>
+      <c r="BH14">
+        <v>1000</v>
+      </c>
+      <c r="BI14">
+        <v>1.01</v>
+      </c>
+      <c r="BJ14">
+        <v>1000</v>
+      </c>
+      <c r="BK14">
+        <v>1.01</v>
+      </c>
+      <c r="BL14">
+        <v>1000</v>
+      </c>
+      <c r="BM14">
+        <v>1.01</v>
+      </c>
+      <c r="BN14">
+        <v>1000</v>
+      </c>
+      <c r="BO14">
+        <v>1.01</v>
+      </c>
+      <c r="BP14">
+        <v>1000</v>
+      </c>
+      <c r="BQ14">
+        <v>1.01</v>
+      </c>
+      <c r="BR14">
+        <v>1000</v>
+      </c>
+      <c r="BS14">
+        <v>1.01</v>
+      </c>
+      <c r="BT14">
+        <v>1000</v>
+      </c>
+      <c r="BU14">
+        <v>1.01</v>
+      </c>
+      <c r="BV14">
+        <v>1000</v>
+      </c>
+      <c r="BW14">
+        <v>1.01</v>
+      </c>
+      <c r="BX14">
+        <v>1000</v>
+      </c>
+      <c r="BY14">
+        <v>1.01</v>
+      </c>
+      <c r="BZ14">
+        <v>1000</v>
+      </c>
+      <c r="CA14">
+        <v>1.01</v>
+      </c>
+      <c r="CB14" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="15" spans="1:80">
+      <c r="A15" t="s">
         <v>86</v>
       </c>
-      <c r="C14" t="s">
-        <v>93</v>
-      </c>
-      <c r="D14" t="s">
-        <v>106</v>
-      </c>
-      <c r="E14" t="s">
-        <v>119</v>
-      </c>
-      <c r="F14">
-        <v>3.2</v>
-      </c>
-      <c r="G14">
+      <c r="B15" t="s">
+        <v>88</v>
+      </c>
+      <c r="C15" t="s">
+        <v>95</v>
+      </c>
+      <c r="D15" t="s">
+        <v>110</v>
+      </c>
+      <c r="E15" t="s">
+        <v>125</v>
+      </c>
+      <c r="F15">
+        <v>1.1</v>
+      </c>
+      <c r="G15">
+        <v>1000</v>
+      </c>
+      <c r="H15">
+        <v>1.1</v>
+      </c>
+      <c r="I15">
+        <v>1000</v>
+      </c>
+      <c r="J15">
+        <v>1.1</v>
+      </c>
+      <c r="K15">
+        <v>1000</v>
+      </c>
+      <c r="L15">
+        <v>1.01</v>
+      </c>
+      <c r="M15">
+        <v>1.01</v>
+      </c>
+      <c r="N15">
+        <v>1.06</v>
+      </c>
+      <c r="O15">
+        <v>1.01</v>
+      </c>
+      <c r="P15">
+        <v>1.06</v>
+      </c>
+      <c r="Q15">
+        <v>1.01</v>
+      </c>
+      <c r="R15">
+        <v>1.06</v>
+      </c>
+      <c r="S15">
+        <v>1.01</v>
+      </c>
+      <c r="T15">
+        <v>1.01</v>
+      </c>
+      <c r="U15">
+        <v>1.01</v>
+      </c>
+      <c r="V15">
+        <v>1.01</v>
+      </c>
+      <c r="W15">
+        <v>1.01</v>
+      </c>
+      <c r="X15">
+        <v>1000</v>
+      </c>
+      <c r="Y15">
+        <v>1000</v>
+      </c>
+      <c r="Z15">
+        <v>1000</v>
+      </c>
+      <c r="AA15">
+        <v>1000</v>
+      </c>
+      <c r="AB15">
+        <v>1000</v>
+      </c>
+      <c r="AC15">
+        <v>1000</v>
+      </c>
+      <c r="AD15">
+        <v>1000</v>
+      </c>
+      <c r="AE15">
+        <v>1000</v>
+      </c>
+      <c r="AF15">
+        <v>1000</v>
+      </c>
+      <c r="AG15">
+        <v>1000</v>
+      </c>
+      <c r="AH15">
+        <v>1000</v>
+      </c>
+      <c r="AI15">
+        <v>1000</v>
+      </c>
+      <c r="AJ15">
+        <v>1000</v>
+      </c>
+      <c r="AK15">
+        <v>1000</v>
+      </c>
+      <c r="AL15">
+        <v>1000</v>
+      </c>
+      <c r="AM15">
+        <v>1000</v>
+      </c>
+      <c r="AN15">
+        <v>1000</v>
+      </c>
+      <c r="AO15">
+        <v>1000</v>
+      </c>
+      <c r="AP15">
+        <v>1.03</v>
+      </c>
+      <c r="AQ15">
+        <v>1.03</v>
+      </c>
+      <c r="AR15">
+        <v>1.03</v>
+      </c>
+      <c r="AS15">
+        <v>1.03</v>
+      </c>
+      <c r="AT15">
+        <v>1.03</v>
+      </c>
+      <c r="AU15">
+        <v>1.03</v>
+      </c>
+      <c r="AV15">
+        <v>1.03</v>
+      </c>
+      <c r="AW15">
+        <v>1.03</v>
+      </c>
+      <c r="AX15">
+        <v>1.03</v>
+      </c>
+      <c r="AY15">
+        <v>1.03</v>
+      </c>
+      <c r="AZ15">
+        <v>1.03</v>
+      </c>
+      <c r="BA15">
+        <v>1.03</v>
+      </c>
+      <c r="BB15">
+        <v>1.03</v>
+      </c>
+      <c r="BC15">
+        <v>1.03</v>
+      </c>
+      <c r="BD15">
+        <v>1.03</v>
+      </c>
+      <c r="BE15">
+        <v>1.03</v>
+      </c>
+      <c r="BF15">
+        <v>1.01</v>
+      </c>
+      <c r="BG15">
+        <v>1.01</v>
+      </c>
+      <c r="BH15">
+        <v>1000</v>
+      </c>
+      <c r="BI15">
+        <v>1.01</v>
+      </c>
+      <c r="BJ15">
+        <v>1000</v>
+      </c>
+      <c r="BK15">
+        <v>1.01</v>
+      </c>
+      <c r="BL15">
+        <v>1000</v>
+      </c>
+      <c r="BM15">
+        <v>1.01</v>
+      </c>
+      <c r="BN15">
+        <v>1000</v>
+      </c>
+      <c r="BO15">
+        <v>1.01</v>
+      </c>
+      <c r="BP15">
+        <v>1000</v>
+      </c>
+      <c r="BQ15">
+        <v>1.01</v>
+      </c>
+      <c r="BR15">
+        <v>1000</v>
+      </c>
+      <c r="BS15">
+        <v>1.01</v>
+      </c>
+      <c r="BT15">
+        <v>1000</v>
+      </c>
+      <c r="BU15">
+        <v>1.01</v>
+      </c>
+      <c r="BV15">
+        <v>1000</v>
+      </c>
+      <c r="BW15">
+        <v>1.01</v>
+      </c>
+      <c r="BX15">
+        <v>1000</v>
+      </c>
+      <c r="BY15">
+        <v>1.01</v>
+      </c>
+      <c r="BZ15">
+        <v>1000</v>
+      </c>
+      <c r="CA15">
+        <v>1.01</v>
+      </c>
+      <c r="CB15" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="16" spans="1:80">
+      <c r="A16" t="s">
+        <v>87</v>
+      </c>
+      <c r="B16" t="s">
+        <v>88</v>
+      </c>
+      <c r="C16" t="s">
+        <v>96</v>
+      </c>
+      <c r="D16" t="s">
+        <v>111</v>
+      </c>
+      <c r="E16" t="s">
+        <v>126</v>
+      </c>
+      <c r="F16">
+        <v>3.4</v>
+      </c>
+      <c r="G16">
         <v>4.1</v>
       </c>
-      <c r="H14">
+      <c r="H16">
         <v>2.4</v>
       </c>
-      <c r="I14">
-        <v>2.76</v>
-      </c>
-      <c r="J14">
+      <c r="I16">
+        <v>2.74</v>
+      </c>
+      <c r="J16">
         <v>2.84</v>
       </c>
-      <c r="K14">
-        <v>3.15</v>
-      </c>
-      <c r="L14">
+      <c r="K16">
+        <v>3.05</v>
+      </c>
+      <c r="L16">
         <v>1.55</v>
       </c>
-      <c r="M14">
+      <c r="M16">
         <v>1.15</v>
       </c>
-      <c r="N14">
-        <v>2.34</v>
-      </c>
-      <c r="O14">
-        <v>1.63</v>
-      </c>
-      <c r="P14">
-        <v>1.46</v>
-      </c>
-      <c r="Q14">
+      <c r="N16">
+        <v>2.24</v>
+      </c>
+      <c r="O16">
+        <v>1.64</v>
+      </c>
+      <c r="P16">
+        <v>1.41</v>
+      </c>
+      <c r="Q16">
         <v>2.92</v>
       </c>
-      <c r="R14">
+      <c r="R16">
         <v>1.14</v>
       </c>
-      <c r="S14">
-        <v>1.01</v>
-      </c>
-      <c r="T14">
+      <c r="S16">
+        <v>6.4</v>
+      </c>
+      <c r="T16">
         <v>2.24</v>
       </c>
-      <c r="U14">
+      <c r="U16">
         <v>1.64</v>
       </c>
-      <c r="V14">
-        <v>1.56</v>
-      </c>
-      <c r="W14">
+      <c r="V16">
+        <v>1.57</v>
+      </c>
+      <c r="W16">
         <v>1.32</v>
       </c>
-      <c r="X14">
+      <c r="X16">
         <v>8.6</v>
       </c>
-      <c r="Y14">
+      <c r="Y16">
         <v>7.2</v>
       </c>
-      <c r="Z14">
+      <c r="Z16">
         <v>15.5</v>
       </c>
-      <c r="AA14">
+      <c r="AA16">
         <v>46</v>
       </c>
-      <c r="AB14">
+      <c r="AB16">
         <v>9.6</v>
       </c>
-      <c r="AC14">
+      <c r="AC16">
         <v>7.4</v>
       </c>
-      <c r="AD14">
+      <c r="AD16">
         <v>14</v>
       </c>
-      <c r="AE14">
+      <c r="AE16">
         <v>44</v>
       </c>
-      <c r="AF14">
+      <c r="AF16">
         <v>26</v>
       </c>
-      <c r="AG14">
+      <c r="AG16">
         <v>18.5</v>
       </c>
-      <c r="AH14">
+      <c r="AH16">
         <v>29</v>
       </c>
-      <c r="AI14">
+      <c r="AI16">
         <v>100</v>
       </c>
-      <c r="AJ14">
+      <c r="AJ16">
         <v>110</v>
       </c>
-      <c r="AK14">
+      <c r="AK16">
         <v>75</v>
       </c>
-      <c r="AL14">
+      <c r="AL16">
         <v>130</v>
       </c>
-      <c r="AM14">
+      <c r="AM16">
         <v>310</v>
       </c>
-      <c r="AN14">
+      <c r="AN16">
         <v>140</v>
       </c>
-      <c r="AO14">
+      <c r="AO16">
         <v>55</v>
       </c>
-      <c r="AP14">
+      <c r="AP16">
         <v>4</v>
       </c>
-      <c r="AQ14">
+      <c r="AQ16">
         <v>3.7</v>
       </c>
-      <c r="AR14">
+      <c r="AR16">
         <v>5.1</v>
       </c>
-      <c r="AS14">
+      <c r="AS16">
         <v>6.6</v>
       </c>
-      <c r="AT14">
+      <c r="AT16">
         <v>4.2</v>
       </c>
-      <c r="AU14">
+      <c r="AU16">
         <v>3.75</v>
       </c>
-      <c r="AV14">
+      <c r="AV16">
         <v>4.9</v>
       </c>
-      <c r="AW14">
+      <c r="AW16">
         <v>6.4</v>
       </c>
-      <c r="AX14">
+      <c r="AX16">
         <v>5.9</v>
       </c>
-      <c r="AY14">
+      <c r="AY16">
         <v>5.4</v>
       </c>
-      <c r="AZ14">
+      <c r="AZ16">
         <v>6</v>
       </c>
-      <c r="BA14">
+      <c r="BA16">
         <v>7</v>
       </c>
-      <c r="BB14">
+      <c r="BB16">
         <v>7.2</v>
       </c>
-      <c r="BC14">
+      <c r="BC16">
         <v>7</v>
       </c>
-      <c r="BD14">
+      <c r="BD16">
         <v>7.2</v>
       </c>
-      <c r="BE14">
+      <c r="BE16">
         <v>7.4</v>
       </c>
-      <c r="BF14">
+      <c r="BF16">
         <v>7.2</v>
       </c>
-      <c r="BG14">
+      <c r="BG16">
         <v>6.6</v>
       </c>
-      <c r="BH14">
+      <c r="BH16">
         <v>2.56</v>
       </c>
-      <c r="BI14">
-        <v>2.24</v>
-      </c>
-      <c r="BJ14">
+      <c r="BI16">
+        <v>2.06</v>
+      </c>
+      <c r="BJ16">
         <v>13</v>
       </c>
-      <c r="BK14">
+      <c r="BK16">
         <v>5.8</v>
       </c>
-      <c r="BL14">
-        <v>1000</v>
-      </c>
-      <c r="BM14">
-        <v>2.04</v>
-      </c>
-      <c r="BN14">
+      <c r="BL16">
+        <v>1000</v>
+      </c>
+      <c r="BM16">
+        <v>10</v>
+      </c>
+      <c r="BN16">
         <v>7</v>
       </c>
-      <c r="BO14">
-        <v>4.2</v>
-      </c>
-      <c r="BP14">
+      <c r="BO16">
+        <v>5</v>
+      </c>
+      <c r="BP16">
         <v>42</v>
       </c>
-      <c r="BQ14">
-        <v>1.97</v>
-      </c>
-      <c r="BR14">
+      <c r="BQ16">
+        <v>8.4</v>
+      </c>
+      <c r="BR16">
         <v>75</v>
       </c>
-      <c r="BS14">
-        <v>2</v>
-      </c>
-      <c r="BT14">
+      <c r="BS16">
+        <v>9.4</v>
+      </c>
+      <c r="BT16">
         <v>5.4</v>
       </c>
-      <c r="BU14">
-        <v>3.55</v>
-      </c>
-      <c r="BV14">
+      <c r="BU16">
+        <v>3.95</v>
+      </c>
+      <c r="BV16">
         <v>25</v>
       </c>
-      <c r="BW14">
-        <v>1.91</v>
-      </c>
-      <c r="BX14">
+      <c r="BW16">
+        <v>7.4</v>
+      </c>
+      <c r="BX16">
         <v>60</v>
       </c>
-      <c r="BY14">
-        <v>2</v>
-      </c>
-      <c r="BZ14">
+      <c r="BY16">
+        <v>9</v>
+      </c>
+      <c r="BZ16">
         <v>0</v>
       </c>
-      <c r="CA14">
+      <c r="CA16">
         <v>0</v>
       </c>
-      <c r="CB14" t="s">
-        <v>120</v>
+      <c r="CB16" t="s">
+        <v>127</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-24.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="131">
   <si>
     <t>League</t>
   </si>
@@ -307,6 +307,9 @@
     <t>20:00:00</t>
   </si>
   <si>
+    <t>20:30:00</t>
+  </si>
+  <si>
     <t>America de Cali S.A</t>
   </si>
   <si>
@@ -352,6 +355,9 @@
     <t>US Amal Tiznit</t>
   </si>
   <si>
+    <t>Independiente Juniors</t>
+  </si>
+  <si>
     <t>Aguilas Doradas</t>
   </si>
   <si>
@@ -397,7 +403,10 @@
     <t>IRT Tanger</t>
   </si>
   <si>
-    <t>2026-09-23 10:07:11</t>
+    <t>Vinotinto Ecuador</t>
+  </si>
+  <si>
+    <t>2026-09-23 12:21:57</t>
   </si>
 </sst>
 </file>
@@ -729,7 +738,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB16"/>
+  <dimension ref="A1:CB17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -985,22 +994,22 @@
         <v>89</v>
       </c>
       <c r="D2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F2">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="G2">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="H2">
         <v>6</v>
       </c>
       <c r="I2">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J2">
         <v>4</v>
@@ -1015,13 +1024,13 @@
         <v>1.07</v>
       </c>
       <c r="N2">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O2">
         <v>1.35</v>
       </c>
       <c r="P2">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="Q2">
         <v>2.04</v>
@@ -1039,7 +1048,7 @@
         <v>1.93</v>
       </c>
       <c r="V2">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W2">
         <v>2.44</v>
@@ -1051,10 +1060,10 @@
         <v>24</v>
       </c>
       <c r="Z2">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA2">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="AB2">
         <v>7.8</v>
@@ -1075,61 +1084,61 @@
         <v>10</v>
       </c>
       <c r="AH2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI2">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AJ2">
         <v>16.5</v>
       </c>
       <c r="AK2">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AL2">
         <v>40</v>
       </c>
       <c r="AM2">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AN2">
         <v>11.5</v>
       </c>
       <c r="AO2">
-        <v>170</v>
+        <v>130</v>
       </c>
       <c r="AP2">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AQ2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AR2">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AS2">
-        <v>12.5</v>
+        <v>110</v>
       </c>
       <c r="AT2">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU2">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW2">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AX2">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AY2">
         <v>9</v>
       </c>
       <c r="AZ2">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA2">
         <v>55</v>
@@ -1138,10 +1147,10 @@
         <v>14.5</v>
       </c>
       <c r="BC2">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BD2">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="BE2">
         <v>90</v>
@@ -1150,70 +1159,70 @@
         <v>10</v>
       </c>
       <c r="BG2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BH2">
         <v>3.95</v>
       </c>
       <c r="BI2">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="BJ2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BK2">
-        <v>8</v>
+        <v>3.5</v>
       </c>
       <c r="BL2">
         <v>190</v>
       </c>
       <c r="BM2">
-        <v>8.199999999999999</v>
+        <v>4.7</v>
       </c>
       <c r="BN2">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BO2">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="BP2">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BQ2">
-        <v>7.4</v>
+        <v>3.55</v>
       </c>
       <c r="BR2">
         <v>34</v>
       </c>
       <c r="BS2">
-        <v>6.8</v>
+        <v>4.2</v>
       </c>
       <c r="BT2">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="BU2">
         <v>6.2</v>
       </c>
       <c r="BV2">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BW2">
-        <v>7.4</v>
+        <v>4.5</v>
       </c>
       <c r="BX2">
         <v>75</v>
       </c>
       <c r="BY2">
-        <v>7.8</v>
+        <v>4.5</v>
       </c>
       <c r="BZ2">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="CA2">
-        <v>6.2</v>
+        <v>4.1</v>
       </c>
       <c r="CB2" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1227,28 +1236,28 @@
         <v>90</v>
       </c>
       <c r="D3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F3">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="G3">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="H3">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="I3">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="J3">
         <v>4.1</v>
       </c>
       <c r="K3">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L3">
         <v>1.3</v>
@@ -1257,19 +1266,19 @@
         <v>1.04</v>
       </c>
       <c r="N3">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="O3">
         <v>1.19</v>
       </c>
       <c r="P3">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="Q3">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="R3">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="S3">
         <v>2.46</v>
@@ -1278,52 +1287,52 @@
         <v>1.59</v>
       </c>
       <c r="U3">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="V3">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="W3">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="X3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Y3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Z3">
         <v>38</v>
       </c>
       <c r="AA3">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AB3">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AC3">
         <v>10</v>
       </c>
       <c r="AD3">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AE3">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF3">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AG3">
         <v>10.5</v>
       </c>
       <c r="AH3">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI3">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK3">
         <v>16.5</v>
@@ -1335,22 +1344,22 @@
         <v>60</v>
       </c>
       <c r="AN3">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AO3">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AP3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR3">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AS3">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="AT3">
         <v>12</v>
@@ -1359,28 +1368,28 @@
         <v>9.4</v>
       </c>
       <c r="AV3">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AW3">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AX3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY3">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ3">
         <v>14</v>
       </c>
       <c r="BA3">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BB3">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BC3">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BD3">
         <v>23</v>
@@ -1389,10 +1398,10 @@
         <v>48</v>
       </c>
       <c r="BF3">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BG3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BH3">
         <v>4.4</v>
@@ -1401,7 +1410,7 @@
         <v>4</v>
       </c>
       <c r="BJ3">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK3">
         <v>7.8</v>
@@ -1410,52 +1419,52 @@
         <v>95</v>
       </c>
       <c r="BM3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BN3">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BO3">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BP3">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BQ3">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BR3">
         <v>21</v>
       </c>
       <c r="BS3">
-        <v>9.800000000000001</v>
+        <v>17.5</v>
       </c>
       <c r="BT3">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BU3">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BV3">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="BW3">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BX3">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="BY3">
         <v>11.5</v>
       </c>
       <c r="BZ3">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="CA3">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="CB3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1469,25 +1478,25 @@
         <v>91</v>
       </c>
       <c r="D4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E4" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F4">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="G4">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="H4">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="I4">
         <v>3.95</v>
       </c>
       <c r="J4">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K4">
         <v>4.5</v>
@@ -1499,34 +1508,34 @@
         <v>1.04</v>
       </c>
       <c r="N4">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="O4">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P4">
         <v>2.52</v>
       </c>
       <c r="Q4">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="R4">
         <v>1.6</v>
       </c>
       <c r="S4">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="T4">
         <v>1.59</v>
       </c>
       <c r="U4">
-        <v>2.52</v>
+        <v>2.44</v>
       </c>
       <c r="V4">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W4">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="X4">
         <v>32</v>
@@ -1538,103 +1547,103 @@
         <v>40</v>
       </c>
       <c r="AA4">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AB4">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC4">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD4">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE4">
+        <v>48</v>
+      </c>
+      <c r="AF4">
+        <v>14.5</v>
+      </c>
+      <c r="AG4">
+        <v>10.5</v>
+      </c>
+      <c r="AH4">
+        <v>19</v>
+      </c>
+      <c r="AI4">
         <v>50</v>
       </c>
-      <c r="AF4">
-        <v>17</v>
-      </c>
-      <c r="AG4">
-        <v>12.5</v>
-      </c>
-      <c r="AH4">
-        <v>18.5</v>
-      </c>
-      <c r="AI4">
-        <v>55</v>
-      </c>
       <c r="AJ4">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AK4">
         <v>22</v>
       </c>
       <c r="AL4">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AM4">
         <v>85</v>
       </c>
       <c r="AN4">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AO4">
         <v>38</v>
       </c>
       <c r="AP4">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AQ4">
         <v>17.5</v>
       </c>
       <c r="AR4">
-        <v>5.4</v>
+        <v>26</v>
       </c>
       <c r="AS4">
-        <v>5.9</v>
+        <v>50</v>
       </c>
       <c r="AT4">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AU4">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AV4">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AW4">
-        <v>5.6</v>
+        <v>32</v>
       </c>
       <c r="AX4">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AY4">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ4">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BA4">
-        <v>5.7</v>
+        <v>29</v>
       </c>
       <c r="BB4">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="BC4">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="BD4">
         <v>21</v>
       </c>
       <c r="BE4">
-        <v>5.9</v>
+        <v>55</v>
       </c>
       <c r="BF4">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BG4">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BH4">
         <v>5.1</v>
@@ -1646,7 +1655,7 @@
         <v>10.5</v>
       </c>
       <c r="BK4">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL4">
         <v>1000</v>
@@ -1655,49 +1664,49 @@
         <v>55</v>
       </c>
       <c r="BN4">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BO4">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BP4">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BQ4">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BR4">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BS4">
         <v>15.5</v>
       </c>
       <c r="BT4">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU4">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BV4">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BW4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BX4">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BY4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BZ4">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="CA4">
         <v>11</v>
       </c>
       <c r="CB4" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1711,25 +1720,25 @@
         <v>92</v>
       </c>
       <c r="D5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F5">
         <v>1.22</v>
       </c>
       <c r="G5">
-        <v>1.23</v>
+        <v>1.53</v>
       </c>
       <c r="H5">
-        <v>5.6</v>
+        <v>1.1</v>
       </c>
       <c r="I5">
         <v>1000</v>
       </c>
       <c r="J5">
-        <v>5.3</v>
+        <v>1.12</v>
       </c>
       <c r="K5">
         <v>1000</v>
@@ -1756,7 +1765,7 @@
         <v>1.08</v>
       </c>
       <c r="S5">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="T5">
         <v>1.01</v>
@@ -1768,7 +1777,7 @@
         <v>1.02</v>
       </c>
       <c r="W5">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="X5">
         <v>1000</v>
@@ -1939,7 +1948,7 @@
         <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1953,55 +1962,55 @@
         <v>93</v>
       </c>
       <c r="D6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E6" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F6">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="G6">
         <v>3.85</v>
       </c>
       <c r="H6">
+        <v>2.5</v>
+      </c>
+      <c r="I6">
         <v>2.52</v>
-      </c>
-      <c r="I6">
-        <v>2.54</v>
       </c>
       <c r="J6">
         <v>2.92</v>
       </c>
       <c r="K6">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="L6">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="M6">
         <v>1.18</v>
       </c>
       <c r="N6">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="O6">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="P6">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="Q6">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="R6">
         <v>1.13</v>
       </c>
       <c r="S6">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="T6">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="U6">
         <v>1.6</v>
@@ -2013,10 +2022,10 @@
         <v>1.35</v>
       </c>
       <c r="X6">
+        <v>6.6</v>
+      </c>
+      <c r="Y6">
         <v>6.4</v>
-      </c>
-      <c r="Y6">
-        <v>6.2</v>
       </c>
       <c r="Z6">
         <v>12.5</v>
@@ -2025,7 +2034,7 @@
         <v>42</v>
       </c>
       <c r="AB6">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC6">
         <v>7</v>
@@ -2034,19 +2043,19 @@
         <v>14.5</v>
       </c>
       <c r="AE6">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF6">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AG6">
         <v>19.5</v>
       </c>
       <c r="AH6">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AI6">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AJ6">
         <v>110</v>
@@ -2058,7 +2067,7 @@
         <v>140</v>
       </c>
       <c r="AM6">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="AN6">
         <v>150</v>
@@ -2067,7 +2076,7 @@
         <v>55</v>
       </c>
       <c r="AP6">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AQ6">
         <v>6</v>
@@ -2085,7 +2094,7 @@
         <v>6.8</v>
       </c>
       <c r="AV6">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AW6">
         <v>40</v>
@@ -2094,13 +2103,13 @@
         <v>21</v>
       </c>
       <c r="AY6">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AZ6">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BA6">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="BB6">
         <v>80</v>
@@ -2109,19 +2118,19 @@
         <v>55</v>
       </c>
       <c r="BD6">
-        <v>15.5</v>
+        <v>42</v>
       </c>
       <c r="BE6">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="BF6">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="BG6">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BH6">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="BI6">
         <v>2.2</v>
@@ -2139,7 +2148,7 @@
         <v>21</v>
       </c>
       <c r="BN6">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BO6">
         <v>6</v>
@@ -2166,7 +2175,7 @@
         <v>27</v>
       </c>
       <c r="BW6">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BX6">
         <v>65</v>
@@ -2181,7 +2190,7 @@
         <v>50</v>
       </c>
       <c r="CB6" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2195,16 +2204,16 @@
         <v>94</v>
       </c>
       <c r="D7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E7" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F7">
         <v>14</v>
       </c>
       <c r="G7">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="H7">
         <v>1.33</v>
@@ -2213,28 +2222,28 @@
         <v>1.34</v>
       </c>
       <c r="J7">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="K7">
         <v>5.6</v>
       </c>
       <c r="L7">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M7">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N7">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O7">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="P7">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="Q7">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="R7">
         <v>1.27</v>
@@ -2243,7 +2252,7 @@
         <v>4.3</v>
       </c>
       <c r="T7">
-        <v>3.1</v>
+        <v>2.86</v>
       </c>
       <c r="U7">
         <v>1.44</v>
@@ -2252,7 +2261,7 @@
         <v>3.9</v>
       </c>
       <c r="W7">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X7">
         <v>12.5</v>
@@ -2261,31 +2270,31 @@
         <v>5.5</v>
       </c>
       <c r="Z7">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="AA7">
         <v>9.6</v>
       </c>
       <c r="AB7">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AC7">
         <v>13.5</v>
       </c>
       <c r="AD7">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE7">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AF7">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AG7">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AH7">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AI7">
         <v>85</v>
@@ -2297,16 +2306,16 @@
         <v>630</v>
       </c>
       <c r="AL7">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="AM7">
-        <v>760</v>
+        <v>720</v>
       </c>
       <c r="AN7">
         <v>1000</v>
       </c>
       <c r="AO7">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AP7">
         <v>11.5</v>
@@ -2315,7 +2324,7 @@
         <v>5.3</v>
       </c>
       <c r="AR7">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="AS7">
         <v>8.800000000000001</v>
@@ -2330,46 +2339,46 @@
         <v>12</v>
       </c>
       <c r="AW7">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AX7">
-        <v>15.5</v>
+        <v>23</v>
       </c>
       <c r="AY7">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AZ7">
         <v>50</v>
       </c>
       <c r="BA7">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="BB7">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="BC7">
-        <v>15.5</v>
+        <v>25</v>
       </c>
       <c r="BD7">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BE7">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="BF7">
-        <v>19.5</v>
+        <v>26</v>
       </c>
       <c r="BG7">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH7">
         <v>3.25</v>
       </c>
       <c r="BI7">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="BJ7">
-        <v>24</v>
+        <v>16.5</v>
       </c>
       <c r="BK7">
         <v>12</v>
@@ -2384,7 +2393,7 @@
         <v>25</v>
       </c>
       <c r="BO7">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BP7">
         <v>1000</v>
@@ -2402,7 +2411,7 @@
         <v>3.3</v>
       </c>
       <c r="BU7">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BV7">
         <v>8</v>
@@ -2417,13 +2426,13 @@
         <v>26</v>
       </c>
       <c r="BZ7">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="CA7">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="CB7" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2437,19 +2446,19 @@
         <v>94</v>
       </c>
       <c r="D8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E8" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F8">
         <v>2.54</v>
       </c>
       <c r="G8">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="H8">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="I8">
         <v>2.88</v>
@@ -2473,31 +2482,31 @@
         <v>1.17</v>
       </c>
       <c r="P8">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="Q8">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="R8">
         <v>1.74</v>
       </c>
       <c r="S8">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="T8">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="U8">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="V8">
         <v>1.53</v>
       </c>
       <c r="W8">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="X8">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y8">
         <v>19</v>
@@ -2512,7 +2521,7 @@
         <v>17.5</v>
       </c>
       <c r="AC8">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD8">
         <v>14</v>
@@ -2524,7 +2533,7 @@
         <v>21</v>
       </c>
       <c r="AG8">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH8">
         <v>13.5</v>
@@ -2536,7 +2545,7 @@
         <v>38</v>
       </c>
       <c r="AK8">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL8">
         <v>26</v>
@@ -2551,7 +2560,7 @@
         <v>14.5</v>
       </c>
       <c r="AP8">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AQ8">
         <v>18</v>
@@ -2566,10 +2575,10 @@
         <v>16.5</v>
       </c>
       <c r="AU8">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AV8">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AW8">
         <v>23</v>
@@ -2665,7 +2674,7 @@
         <v>8</v>
       </c>
       <c r="CB8" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2679,22 +2688,22 @@
         <v>94</v>
       </c>
       <c r="D9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E9" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F9">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="G9">
         <v>1.84</v>
       </c>
       <c r="H9">
+        <v>4.6</v>
+      </c>
+      <c r="I9">
         <v>4.7</v>
-      </c>
-      <c r="I9">
-        <v>4.8</v>
       </c>
       <c r="J9">
         <v>4.1</v>
@@ -2715,31 +2724,31 @@
         <v>1.24</v>
       </c>
       <c r="P9">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="Q9">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="R9">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="S9">
         <v>2.78</v>
       </c>
       <c r="T9">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="U9">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="V9">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W9">
         <v>2.18</v>
       </c>
       <c r="X9">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="Y9">
         <v>20</v>
@@ -2757,13 +2766,13 @@
         <v>9.4</v>
       </c>
       <c r="AD9">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AE9">
         <v>55</v>
       </c>
       <c r="AF9">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AG9">
         <v>11</v>
@@ -2802,13 +2811,13 @@
         <v>34</v>
       </c>
       <c r="AS9">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AT9">
         <v>10</v>
       </c>
       <c r="AU9">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV9">
         <v>17.5</v>
@@ -2817,7 +2826,7 @@
         <v>46</v>
       </c>
       <c r="AX9">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AY9">
         <v>10</v>
@@ -2826,7 +2835,7 @@
         <v>16.5</v>
       </c>
       <c r="BA9">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BB9">
         <v>17.5</v>
@@ -2844,7 +2853,7 @@
         <v>8.4</v>
       </c>
       <c r="BG9">
-        <v>14.5</v>
+        <v>42</v>
       </c>
       <c r="BH9">
         <v>3.9</v>
@@ -2907,7 +2916,7 @@
         <v>8.4</v>
       </c>
       <c r="CB9" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2921,19 +2930,19 @@
         <v>94</v>
       </c>
       <c r="D10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E10" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F10">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="G10">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="H10">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I10">
         <v>3.4</v>
@@ -2948,37 +2957,37 @@
         <v>1.53</v>
       </c>
       <c r="M10">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N10">
         <v>3</v>
       </c>
       <c r="O10">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="P10">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="Q10">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="R10">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S10">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="T10">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U10">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="V10">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W10">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="X10">
         <v>10.5</v>
@@ -2993,7 +3002,7 @@
         <v>65</v>
       </c>
       <c r="AB10">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC10">
         <v>7.4</v>
@@ -3014,7 +3023,7 @@
         <v>21</v>
       </c>
       <c r="AI10">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="AJ10">
         <v>36</v>
@@ -3026,7 +3035,7 @@
         <v>55</v>
       </c>
       <c r="AM10">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AN10">
         <v>32</v>
@@ -3062,10 +3071,10 @@
         <v>13</v>
       </c>
       <c r="AY10">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ10">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BA10">
         <v>55</v>
@@ -3074,25 +3083,25 @@
         <v>32</v>
       </c>
       <c r="BC10">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BD10">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BE10">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BF10">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BG10">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BH10">
         <v>2.86</v>
       </c>
       <c r="BI10">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="BJ10">
         <v>10.5</v>
@@ -3104,7 +3113,7 @@
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="BN10">
         <v>5.3</v>
@@ -3122,34 +3131,34 @@
         <v>40</v>
       </c>
       <c r="BS10">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BT10">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BU10">
         <v>5.7</v>
       </c>
       <c r="BV10">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BW10">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BX10">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY10">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BZ10">
         <v>40</v>
       </c>
       <c r="CA10">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="CB10" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3163,10 +3172,10 @@
         <v>94</v>
       </c>
       <c r="D11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E11" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F11">
         <v>1.44</v>
@@ -3175,7 +3184,7 @@
         <v>1.45</v>
       </c>
       <c r="H11">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="I11">
         <v>8.199999999999999</v>
@@ -3199,7 +3208,7 @@
         <v>1.18</v>
       </c>
       <c r="P11">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="Q11">
         <v>1.56</v>
@@ -3208,7 +3217,7 @@
         <v>1.68</v>
       </c>
       <c r="S11">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="T11">
         <v>1.77</v>
@@ -3226,7 +3235,7 @@
         <v>26</v>
       </c>
       <c r="Y11">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="Z11">
         <v>75</v>
@@ -3250,7 +3259,7 @@
         <v>10.5</v>
       </c>
       <c r="AG11">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AH11">
         <v>22</v>
@@ -3262,16 +3271,16 @@
         <v>13.5</v>
       </c>
       <c r="AK11">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AL11">
         <v>29</v>
       </c>
       <c r="AM11">
-        <v>180</v>
+        <v>95</v>
       </c>
       <c r="AN11">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AO11">
         <v>90</v>
@@ -3289,7 +3298,7 @@
         <v>15.5</v>
       </c>
       <c r="AT11">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU11">
         <v>11</v>
@@ -3298,37 +3307,37 @@
         <v>25</v>
       </c>
       <c r="AW11">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AX11">
         <v>9.199999999999999</v>
       </c>
       <c r="AY11">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ11">
         <v>19</v>
       </c>
       <c r="BA11">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="BB11">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BC11">
         <v>12.5</v>
       </c>
       <c r="BD11">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BE11">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="BF11">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BG11">
-        <v>14</v>
+        <v>70</v>
       </c>
       <c r="BH11">
         <v>4.7</v>
@@ -3346,7 +3355,7 @@
         <v>120</v>
       </c>
       <c r="BM11">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BN11">
         <v>4.3</v>
@@ -3355,7 +3364,7 @@
         <v>3.9</v>
       </c>
       <c r="BP11">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BQ11">
         <v>7.4</v>
@@ -3364,34 +3373,34 @@
         <v>24</v>
       </c>
       <c r="BS11">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BT11">
         <v>13.5</v>
       </c>
       <c r="BU11">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BV11">
         <v>70</v>
       </c>
       <c r="BW11">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BX11">
         <v>65</v>
       </c>
       <c r="BY11">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BZ11">
         <v>13.5</v>
       </c>
       <c r="CA11">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="CB11" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3405,22 +3414,22 @@
         <v>94</v>
       </c>
       <c r="D12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E12" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F12">
+        <v>2.82</v>
+      </c>
+      <c r="G12">
         <v>2.84</v>
       </c>
-      <c r="G12">
-        <v>2.86</v>
-      </c>
       <c r="H12">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="I12">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="J12">
         <v>3.4</v>
@@ -3444,7 +3453,7 @@
         <v>1.76</v>
       </c>
       <c r="Q12">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="R12">
         <v>1.28</v>
@@ -3459,10 +3468,10 @@
         <v>2</v>
       </c>
       <c r="V12">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="W12">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="X12">
         <v>12</v>
@@ -3492,7 +3501,7 @@
         <v>17.5</v>
       </c>
       <c r="AG12">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH12">
         <v>19.5</v>
@@ -3522,7 +3531,7 @@
         <v>11</v>
       </c>
       <c r="AQ12">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AR12">
         <v>16</v>
@@ -3546,7 +3555,7 @@
         <v>15.5</v>
       </c>
       <c r="AY12">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AZ12">
         <v>17.5</v>
@@ -3564,13 +3573,13 @@
         <v>44</v>
       </c>
       <c r="BE12">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BF12">
         <v>30</v>
       </c>
       <c r="BG12">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BH12">
         <v>3.05</v>
@@ -3588,7 +3597,7 @@
         <v>160</v>
       </c>
       <c r="BM12">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN12">
         <v>5.8</v>
@@ -3600,22 +3609,22 @@
         <v>27</v>
       </c>
       <c r="BQ12">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BR12">
         <v>46</v>
       </c>
       <c r="BS12">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BT12">
         <v>5.7</v>
       </c>
       <c r="BU12">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BV12">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="BW12">
         <v>8.199999999999999</v>
@@ -3624,16 +3633,16 @@
         <v>44</v>
       </c>
       <c r="BY12">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BZ12">
         <v>40</v>
       </c>
       <c r="CA12">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB12" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3647,10 +3656,10 @@
         <v>94</v>
       </c>
       <c r="D13" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E13" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F13">
         <v>1.23</v>
@@ -3662,16 +3671,16 @@
         <v>17.5</v>
       </c>
       <c r="I13">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="J13">
         <v>7.4</v>
       </c>
       <c r="K13">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="L13">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="M13">
         <v>1.03</v>
@@ -3683,10 +3692,10 @@
         <v>1.19</v>
       </c>
       <c r="P13">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="Q13">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="R13">
         <v>1.63</v>
@@ -3719,7 +3728,7 @@
         <v>1000</v>
       </c>
       <c r="AB13">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AC13">
         <v>17</v>
@@ -3728,7 +3737,7 @@
         <v>60</v>
       </c>
       <c r="AE13">
-        <v>420</v>
+        <v>390</v>
       </c>
       <c r="AF13">
         <v>7.6</v>
@@ -3737,7 +3746,7 @@
         <v>12.5</v>
       </c>
       <c r="AH13">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AI13">
         <v>270</v>
@@ -3767,13 +3776,13 @@
         <v>46</v>
       </c>
       <c r="AR13">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS13">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AT13">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AU13">
         <v>15.5</v>
@@ -3782,7 +3791,7 @@
         <v>50</v>
       </c>
       <c r="AW13">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AX13">
         <v>7.2</v>
@@ -3794,79 +3803,79 @@
         <v>36</v>
       </c>
       <c r="BA13">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BB13">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC13">
         <v>13.5</v>
       </c>
       <c r="BD13">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BE13">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BF13">
         <v>3.75</v>
       </c>
       <c r="BG13">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BH13">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BI13">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="BJ13">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="BK13">
-        <v>6.2</v>
+        <v>2.24</v>
       </c>
       <c r="BL13">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="BM13">
         <v>23</v>
       </c>
       <c r="BN13">
-        <v>3.7</v>
+        <v>1000</v>
       </c>
       <c r="BO13">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="BP13">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BQ13">
-        <v>5.8</v>
+        <v>1.77</v>
       </c>
       <c r="BR13">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BS13">
-        <v>7.4</v>
+        <v>2.24</v>
       </c>
       <c r="BT13">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BU13">
-        <v>6.8</v>
+        <v>2.24</v>
       </c>
       <c r="BV13">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="BW13">
-        <v>9.6</v>
+        <v>2.24</v>
       </c>
       <c r="BX13">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="BY13">
-        <v>9.4</v>
+        <v>2.24</v>
       </c>
       <c r="BZ13">
         <v>0</v>
@@ -3875,7 +3884,7 @@
         <v>0</v>
       </c>
       <c r="CB13" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -3889,151 +3898,151 @@
         <v>95</v>
       </c>
       <c r="D14" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E14" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F14">
-        <v>1.1</v>
+        <v>2.76</v>
       </c>
       <c r="G14">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="H14">
-        <v>1.1</v>
+        <v>2.64</v>
       </c>
       <c r="I14">
-        <v>1000</v>
+        <v>2.9</v>
       </c>
       <c r="J14">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="K14">
-        <v>950</v>
+        <v>3.55</v>
       </c>
       <c r="L14">
         <v>1.01</v>
       </c>
       <c r="M14">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N14">
-        <v>1.12</v>
+        <v>3</v>
       </c>
       <c r="O14">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="P14">
-        <v>1.12</v>
+        <v>1.71</v>
       </c>
       <c r="Q14">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="R14">
-        <v>1.08</v>
+        <v>1.27</v>
       </c>
       <c r="S14">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="T14">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="U14">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="V14">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="W14">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="X14">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y14">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z14">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA14">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB14">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC14">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD14">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE14">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AF14">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG14">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AH14">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI14">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ14">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK14">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AL14">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM14">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN14">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AO14">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AP14">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AQ14">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AR14">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AS14">
         <v>1.03</v>
       </c>
       <c r="AT14">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU14">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AV14">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW14">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="AX14">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="AY14">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AZ14">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="BA14">
         <v>1.03</v>
@@ -4051,16 +4060,16 @@
         <v>1.03</v>
       </c>
       <c r="BF14">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="BG14">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BH14">
         <v>1000</v>
       </c>
       <c r="BI14">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="BJ14">
         <v>1000</v>
@@ -4117,7 +4126,7 @@
         <v>1.01</v>
       </c>
       <c r="CB14" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4131,28 +4140,28 @@
         <v>95</v>
       </c>
       <c r="D15" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E15" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F15">
         <v>1.1</v>
       </c>
       <c r="G15">
-        <v>1000</v>
+        <v>880</v>
       </c>
       <c r="H15">
         <v>1.1</v>
       </c>
       <c r="I15">
-        <v>1000</v>
+        <v>880</v>
       </c>
       <c r="J15">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="K15">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L15">
         <v>1.01</v>
@@ -4161,22 +4170,22 @@
         <v>1.01</v>
       </c>
       <c r="N15">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="O15">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P15">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="Q15">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="R15">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="S15">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="T15">
         <v>1.01</v>
@@ -4185,10 +4194,10 @@
         <v>1.01</v>
       </c>
       <c r="V15">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W15">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X15">
         <v>1000</v>
@@ -4359,7 +4368,7 @@
         <v>1.01</v>
       </c>
       <c r="CB15" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4373,10 +4382,10 @@
         <v>96</v>
       </c>
       <c r="D16" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E16" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F16">
         <v>3.4</v>
@@ -4394,7 +4403,7 @@
         <v>2.84</v>
       </c>
       <c r="K16">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="L16">
         <v>1.55</v>
@@ -4403,7 +4412,7 @@
         <v>1.15</v>
       </c>
       <c r="N16">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="O16">
         <v>1.64</v>
@@ -4436,34 +4445,34 @@
         <v>8.6</v>
       </c>
       <c r="Y16">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="Z16">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AA16">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AB16">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AC16">
         <v>7.4</v>
       </c>
       <c r="AD16">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AE16">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AF16">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AG16">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AH16">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AI16">
         <v>100</v>
@@ -4484,67 +4493,67 @@
         <v>140</v>
       </c>
       <c r="AO16">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AP16">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="AQ16">
-        <v>3.7</v>
+        <v>5.2</v>
       </c>
       <c r="AR16">
+        <v>12</v>
+      </c>
+      <c r="AS16">
+        <v>4.7</v>
+      </c>
+      <c r="AT16">
+        <v>6.8</v>
+      </c>
+      <c r="AU16">
+        <v>5.3</v>
+      </c>
+      <c r="AV16">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW16">
+        <v>34</v>
+      </c>
+      <c r="AX16">
+        <v>20</v>
+      </c>
+      <c r="AY16">
+        <v>14.5</v>
+      </c>
+      <c r="AZ16">
+        <v>6.2</v>
+      </c>
+      <c r="BA16">
+        <v>4.9</v>
+      </c>
+      <c r="BB16">
+        <v>4.9</v>
+      </c>
+      <c r="BC16">
+        <v>4.8</v>
+      </c>
+      <c r="BD16">
+        <v>5</v>
+      </c>
+      <c r="BE16">
         <v>5.1</v>
       </c>
-      <c r="AS16">
-        <v>6.6</v>
-      </c>
-      <c r="AT16">
-        <v>4.2</v>
-      </c>
-      <c r="AU16">
-        <v>3.75</v>
-      </c>
-      <c r="AV16">
-        <v>4.9</v>
-      </c>
-      <c r="AW16">
-        <v>6.4</v>
-      </c>
-      <c r="AX16">
-        <v>5.9</v>
-      </c>
-      <c r="AY16">
-        <v>5.4</v>
-      </c>
-      <c r="AZ16">
-        <v>6</v>
-      </c>
-      <c r="BA16">
-        <v>7</v>
-      </c>
-      <c r="BB16">
-        <v>7.2</v>
-      </c>
-      <c r="BC16">
-        <v>7</v>
-      </c>
-      <c r="BD16">
-        <v>7.2</v>
-      </c>
-      <c r="BE16">
-        <v>7.4</v>
-      </c>
       <c r="BF16">
-        <v>7.2</v>
+        <v>5</v>
       </c>
       <c r="BG16">
-        <v>6.6</v>
+        <v>4.8</v>
       </c>
       <c r="BH16">
         <v>2.56</v>
       </c>
       <c r="BI16">
-        <v>2.06</v>
+        <v>2.24</v>
       </c>
       <c r="BJ16">
         <v>13</v>
@@ -4601,7 +4610,249 @@
         <v>0</v>
       </c>
       <c r="CB16" t="s">
-        <v>127</v>
+        <v>130</v>
+      </c>
+    </row>
+    <row r="17" spans="1:80">
+      <c r="A17" t="s">
+        <v>86</v>
+      </c>
+      <c r="B17" t="s">
+        <v>88</v>
+      </c>
+      <c r="C17" t="s">
+        <v>97</v>
+      </c>
+      <c r="D17" t="s">
+        <v>113</v>
+      </c>
+      <c r="E17" t="s">
+        <v>129</v>
+      </c>
+      <c r="F17">
+        <v>1.1</v>
+      </c>
+      <c r="G17">
+        <v>880</v>
+      </c>
+      <c r="H17">
+        <v>1.1</v>
+      </c>
+      <c r="I17">
+        <v>880</v>
+      </c>
+      <c r="J17">
+        <v>1.12</v>
+      </c>
+      <c r="K17">
+        <v>950</v>
+      </c>
+      <c r="L17">
+        <v>1.01</v>
+      </c>
+      <c r="M17">
+        <v>1.01</v>
+      </c>
+      <c r="N17">
+        <v>1.09</v>
+      </c>
+      <c r="O17">
+        <v>1.01</v>
+      </c>
+      <c r="P17">
+        <v>1.09</v>
+      </c>
+      <c r="Q17">
+        <v>1.47</v>
+      </c>
+      <c r="R17">
+        <v>1.08</v>
+      </c>
+      <c r="S17">
+        <v>1.47</v>
+      </c>
+      <c r="T17">
+        <v>1.01</v>
+      </c>
+      <c r="U17">
+        <v>1.01</v>
+      </c>
+      <c r="V17">
+        <v>1.01</v>
+      </c>
+      <c r="W17">
+        <v>1.01</v>
+      </c>
+      <c r="X17">
+        <v>1000</v>
+      </c>
+      <c r="Y17">
+        <v>1000</v>
+      </c>
+      <c r="Z17">
+        <v>1000</v>
+      </c>
+      <c r="AA17">
+        <v>1000</v>
+      </c>
+      <c r="AB17">
+        <v>1000</v>
+      </c>
+      <c r="AC17">
+        <v>1000</v>
+      </c>
+      <c r="AD17">
+        <v>1000</v>
+      </c>
+      <c r="AE17">
+        <v>1000</v>
+      </c>
+      <c r="AF17">
+        <v>1000</v>
+      </c>
+      <c r="AG17">
+        <v>1000</v>
+      </c>
+      <c r="AH17">
+        <v>1000</v>
+      </c>
+      <c r="AI17">
+        <v>1000</v>
+      </c>
+      <c r="AJ17">
+        <v>1000</v>
+      </c>
+      <c r="AK17">
+        <v>1000</v>
+      </c>
+      <c r="AL17">
+        <v>1000</v>
+      </c>
+      <c r="AM17">
+        <v>1000</v>
+      </c>
+      <c r="AN17">
+        <v>1000</v>
+      </c>
+      <c r="AO17">
+        <v>1000</v>
+      </c>
+      <c r="AP17">
+        <v>1.03</v>
+      </c>
+      <c r="AQ17">
+        <v>1.03</v>
+      </c>
+      <c r="AR17">
+        <v>1.03</v>
+      </c>
+      <c r="AS17">
+        <v>1.03</v>
+      </c>
+      <c r="AT17">
+        <v>1.03</v>
+      </c>
+      <c r="AU17">
+        <v>1.03</v>
+      </c>
+      <c r="AV17">
+        <v>1.03</v>
+      </c>
+      <c r="AW17">
+        <v>1.03</v>
+      </c>
+      <c r="AX17">
+        <v>1.03</v>
+      </c>
+      <c r="AY17">
+        <v>1.03</v>
+      </c>
+      <c r="AZ17">
+        <v>1.03</v>
+      </c>
+      <c r="BA17">
+        <v>1.03</v>
+      </c>
+      <c r="BB17">
+        <v>1.03</v>
+      </c>
+      <c r="BC17">
+        <v>1.03</v>
+      </c>
+      <c r="BD17">
+        <v>1.03</v>
+      </c>
+      <c r="BE17">
+        <v>1.03</v>
+      </c>
+      <c r="BF17">
+        <v>1.01</v>
+      </c>
+      <c r="BG17">
+        <v>1.01</v>
+      </c>
+      <c r="BH17">
+        <v>1000</v>
+      </c>
+      <c r="BI17">
+        <v>1.01</v>
+      </c>
+      <c r="BJ17">
+        <v>1000</v>
+      </c>
+      <c r="BK17">
+        <v>1.01</v>
+      </c>
+      <c r="BL17">
+        <v>1000</v>
+      </c>
+      <c r="BM17">
+        <v>1.01</v>
+      </c>
+      <c r="BN17">
+        <v>1000</v>
+      </c>
+      <c r="BO17">
+        <v>1.01</v>
+      </c>
+      <c r="BP17">
+        <v>1000</v>
+      </c>
+      <c r="BQ17">
+        <v>1.01</v>
+      </c>
+      <c r="BR17">
+        <v>1000</v>
+      </c>
+      <c r="BS17">
+        <v>1.01</v>
+      </c>
+      <c r="BT17">
+        <v>1000</v>
+      </c>
+      <c r="BU17">
+        <v>1.01</v>
+      </c>
+      <c r="BV17">
+        <v>1000</v>
+      </c>
+      <c r="BW17">
+        <v>1.01</v>
+      </c>
+      <c r="BX17">
+        <v>1000</v>
+      </c>
+      <c r="BY17">
+        <v>1.01</v>
+      </c>
+      <c r="BZ17">
+        <v>1000</v>
+      </c>
+      <c r="CA17">
+        <v>1.01</v>
+      </c>
+      <c r="CB17" t="s">
+        <v>130</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-24.xlsx
@@ -406,7 +406,7 @@
     <t>Vinotinto Ecuador</t>
   </si>
   <si>
-    <t>2026-09-23 12:21:57</t>
+    <t>2026-09-23 14:33:38</t>
   </si>
 </sst>
 </file>
@@ -1000,13 +1000,13 @@
         <v>114</v>
       </c>
       <c r="F2">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="G2">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="H2">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I2">
         <v>6.6</v>
@@ -1024,58 +1024,58 @@
         <v>1.07</v>
       </c>
       <c r="N2">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O2">
+        <v>1.34</v>
+      </c>
+      <c r="P2">
+        <v>1.96</v>
+      </c>
+      <c r="Q2">
+        <v>2.02</v>
+      </c>
+      <c r="R2">
         <v>1.35</v>
       </c>
-      <c r="P2">
-        <v>1.93</v>
-      </c>
-      <c r="Q2">
-        <v>2.04</v>
-      </c>
-      <c r="R2">
-        <v>1.34</v>
-      </c>
       <c r="S2">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="T2">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U2">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="V2">
         <v>1.17</v>
       </c>
       <c r="W2">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="X2">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y2">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="Z2">
         <v>55</v>
       </c>
       <c r="AA2">
-        <v>190</v>
+        <v>230</v>
       </c>
       <c r="AB2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AC2">
         <v>9.199999999999999</v>
       </c>
       <c r="AD2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE2">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AF2">
         <v>9.4</v>
@@ -1084,13 +1084,13 @@
         <v>10</v>
       </c>
       <c r="AH2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI2">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AJ2">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AK2">
         <v>18.5</v>
@@ -1099,10 +1099,10 @@
         <v>40</v>
       </c>
       <c r="AM2">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="AN2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AO2">
         <v>130</v>
@@ -1111,7 +1111,7 @@
         <v>12.5</v>
       </c>
       <c r="AQ2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AR2">
         <v>42</v>
@@ -1129,22 +1129,22 @@
         <v>21</v>
       </c>
       <c r="AW2">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AX2">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AY2">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ2">
         <v>20</v>
       </c>
       <c r="BA2">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="BB2">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BC2">
         <v>16.5</v>
@@ -1156,7 +1156,7 @@
         <v>90</v>
       </c>
       <c r="BF2">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG2">
         <v>75</v>
@@ -1165,61 +1165,61 @@
         <v>3.95</v>
       </c>
       <c r="BI2">
-        <v>2.72</v>
+        <v>2.82</v>
       </c>
       <c r="BJ2">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BK2">
-        <v>3.5</v>
+        <v>5.2</v>
       </c>
       <c r="BL2">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="BM2">
-        <v>4.7</v>
+        <v>9.4</v>
       </c>
       <c r="BN2">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="BO2">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="BP2">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="BQ2">
-        <v>3.55</v>
+        <v>5.2</v>
       </c>
       <c r="BR2">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="BS2">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="BT2">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU2">
         <v>6.2</v>
       </c>
       <c r="BV2">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="BW2">
-        <v>4.5</v>
+        <v>8.4</v>
       </c>
       <c r="BX2">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="BY2">
-        <v>4.5</v>
+        <v>8.6</v>
       </c>
       <c r="BZ2">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="CA2">
-        <v>4.1</v>
+        <v>6.8</v>
       </c>
       <c r="CB2" t="s">
         <v>130</v>
@@ -1242,22 +1242,22 @@
         <v>115</v>
       </c>
       <c r="F3">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="G3">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="H3">
+        <v>4.3</v>
+      </c>
+      <c r="I3">
+        <v>4.6</v>
+      </c>
+      <c r="J3">
         <v>4.2</v>
       </c>
-      <c r="I3">
+      <c r="K3">
         <v>4.4</v>
-      </c>
-      <c r="J3">
-        <v>4.1</v>
-      </c>
-      <c r="K3">
-        <v>4.3</v>
       </c>
       <c r="L3">
         <v>1.3</v>
@@ -1266,13 +1266,13 @@
         <v>1.04</v>
       </c>
       <c r="N3">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="O3">
         <v>1.19</v>
       </c>
       <c r="P3">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="Q3">
         <v>1.59</v>
@@ -1281,22 +1281,22 @@
         <v>1.66</v>
       </c>
       <c r="S3">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="T3">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="U3">
         <v>2.6</v>
       </c>
       <c r="V3">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="W3">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="X3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Y3">
         <v>23</v>
@@ -1305,10 +1305,10 @@
         <v>38</v>
       </c>
       <c r="AA3">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AB3">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC3">
         <v>10</v>
@@ -1317,10 +1317,10 @@
         <v>17.5</v>
       </c>
       <c r="AE3">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AF3">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG3">
         <v>10.5</v>
@@ -1329,79 +1329,79 @@
         <v>15.5</v>
       </c>
       <c r="AI3">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AJ3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK3">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AL3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AM3">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AN3">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AO3">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AP3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ3">
         <v>21</v>
       </c>
       <c r="AR3">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AS3">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="AT3">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AU3">
         <v>9.4</v>
       </c>
       <c r="AV3">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AW3">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AX3">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AY3">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ3">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA3">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BB3">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BC3">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BD3">
         <v>23</v>
       </c>
       <c r="BE3">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BF3">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BG3">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BH3">
         <v>4.4</v>
@@ -1419,34 +1419,34 @@
         <v>95</v>
       </c>
       <c r="BM3">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="BN3">
         <v>5</v>
       </c>
       <c r="BO3">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BP3">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BQ3">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BR3">
         <v>21</v>
       </c>
       <c r="BS3">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BT3">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU3">
         <v>7</v>
       </c>
       <c r="BV3">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="BW3">
         <v>10</v>
@@ -1455,10 +1455,10 @@
         <v>40</v>
       </c>
       <c r="BY3">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BZ3">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="CA3">
         <v>10.5</v>
@@ -1484,64 +1484,64 @@
         <v>116</v>
       </c>
       <c r="F4">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="G4">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="H4">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="I4">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="J4">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K4">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="L4">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="M4">
         <v>1.04</v>
       </c>
       <c r="N4">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="O4">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="P4">
-        <v>2.52</v>
+        <v>2.64</v>
       </c>
       <c r="Q4">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="R4">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="S4">
-        <v>2.52</v>
+        <v>2.4</v>
       </c>
       <c r="T4">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="U4">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="V4">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W4">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="X4">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Y4">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="Z4">
         <v>40</v>
@@ -1550,34 +1550,34 @@
         <v>85</v>
       </c>
       <c r="AB4">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC4">
         <v>11</v>
       </c>
       <c r="AD4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE4">
         <v>48</v>
       </c>
       <c r="AF4">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AG4">
         <v>10.5</v>
       </c>
       <c r="AH4">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AI4">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AJ4">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AK4">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL4">
         <v>32</v>
@@ -1586,16 +1586,16 @@
         <v>85</v>
       </c>
       <c r="AN4">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="AO4">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AP4">
         <v>18</v>
       </c>
       <c r="AQ4">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AR4">
         <v>26</v>
@@ -1607,7 +1607,7 @@
         <v>10.5</v>
       </c>
       <c r="AU4">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AV4">
         <v>14.5</v>
@@ -1619,13 +1619,13 @@
         <v>12</v>
       </c>
       <c r="AY4">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ4">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BB4">
         <v>19</v>
@@ -1637,31 +1637,31 @@
         <v>21</v>
       </c>
       <c r="BE4">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BF4">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BG4">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BH4">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BI4">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="BJ4">
         <v>10.5</v>
       </c>
       <c r="BK4">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BN4">
         <v>6</v>
@@ -1670,22 +1670,22 @@
         <v>3.9</v>
       </c>
       <c r="BP4">
+        <v>14.5</v>
+      </c>
+      <c r="BQ4">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BR4">
+        <v>25</v>
+      </c>
+      <c r="BS4">
         <v>15</v>
       </c>
-      <c r="BQ4">
-        <v>9</v>
-      </c>
-      <c r="BR4">
-        <v>26</v>
-      </c>
-      <c r="BS4">
-        <v>15.5</v>
-      </c>
       <c r="BT4">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BU4">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BV4">
         <v>34</v>
@@ -1694,16 +1694,16 @@
         <v>20</v>
       </c>
       <c r="BX4">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BY4">
         <v>23</v>
       </c>
       <c r="BZ4">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="CA4">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="CB4" t="s">
         <v>130</v>
@@ -1729,19 +1729,19 @@
         <v>1.22</v>
       </c>
       <c r="G5">
-        <v>1.53</v>
+        <v>1.99</v>
       </c>
       <c r="H5">
-        <v>1.1</v>
+        <v>2.06</v>
       </c>
       <c r="I5">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="J5">
-        <v>1.12</v>
+        <v>2.1</v>
       </c>
       <c r="K5">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="L5">
         <v>1.01</v>
@@ -1765,19 +1765,19 @@
         <v>1.08</v>
       </c>
       <c r="S5">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="T5">
         <v>1.01</v>
       </c>
       <c r="U5">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="V5">
         <v>1.02</v>
       </c>
       <c r="W5">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="X5">
         <v>1000</v>
@@ -1968,7 +1968,7 @@
         <v>118</v>
       </c>
       <c r="F6">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="G6">
         <v>3.85</v>
@@ -1977,7 +1977,7 @@
         <v>2.5</v>
       </c>
       <c r="I6">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="J6">
         <v>2.92</v>
@@ -1995,13 +1995,13 @@
         <v>2.24</v>
       </c>
       <c r="O6">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="P6">
         <v>1.39</v>
       </c>
       <c r="Q6">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="R6">
         <v>1.13</v>
@@ -2013,7 +2013,7 @@
         <v>2.54</v>
       </c>
       <c r="U6">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="V6">
         <v>1.65</v>
@@ -2034,19 +2034,19 @@
         <v>42</v>
       </c>
       <c r="AB6">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC6">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AD6">
         <v>14.5</v>
       </c>
       <c r="AE6">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF6">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AG6">
         <v>19.5</v>
@@ -2067,7 +2067,7 @@
         <v>140</v>
       </c>
       <c r="AM6">
-        <v>360</v>
+        <v>310</v>
       </c>
       <c r="AN6">
         <v>150</v>
@@ -2076,10 +2076,10 @@
         <v>55</v>
       </c>
       <c r="AP6">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AQ6">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AR6">
         <v>11.5</v>
@@ -2091,13 +2091,13 @@
         <v>8</v>
       </c>
       <c r="AU6">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV6">
         <v>13.5</v>
       </c>
       <c r="AW6">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AX6">
         <v>21</v>
@@ -2115,13 +2115,13 @@
         <v>80</v>
       </c>
       <c r="BC6">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="BD6">
         <v>42</v>
       </c>
       <c r="BE6">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BF6">
         <v>42</v>
@@ -2136,7 +2136,7 @@
         <v>2.2</v>
       </c>
       <c r="BJ6">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BK6">
         <v>11</v>
@@ -2210,10 +2210,10 @@
         <v>119</v>
       </c>
       <c r="F7">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="G7">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="H7">
         <v>1.33</v>
@@ -2225,7 +2225,7 @@
         <v>5.4</v>
       </c>
       <c r="K7">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="L7">
         <v>1.45</v>
@@ -2234,28 +2234,28 @@
         <v>1.08</v>
       </c>
       <c r="N7">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O7">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P7">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="Q7">
         <v>2.26</v>
       </c>
       <c r="R7">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S7">
         <v>4.3</v>
       </c>
       <c r="T7">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="U7">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="V7">
         <v>3.9</v>
@@ -2264,19 +2264,19 @@
         <v>1.06</v>
       </c>
       <c r="X7">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Y7">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="Z7">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AA7">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AB7">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AC7">
         <v>13.5</v>
@@ -2285,10 +2285,10 @@
         <v>12.5</v>
       </c>
       <c r="AE7">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AF7">
-        <v>200</v>
+        <v>170</v>
       </c>
       <c r="AG7">
         <v>70</v>
@@ -2303,31 +2303,31 @@
         <v>1000</v>
       </c>
       <c r="AK7">
+        <v>510</v>
+      </c>
+      <c r="AL7">
+        <v>480</v>
+      </c>
+      <c r="AM7">
         <v>630</v>
       </c>
-      <c r="AL7">
-        <v>500</v>
-      </c>
-      <c r="AM7">
-        <v>720</v>
-      </c>
       <c r="AN7">
         <v>1000</v>
       </c>
       <c r="AO7">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AP7">
         <v>11.5</v>
       </c>
       <c r="AQ7">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AR7">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AS7">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AT7">
         <v>27</v>
@@ -2336,40 +2336,40 @@
         <v>12.5</v>
       </c>
       <c r="AV7">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AW7">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AX7">
-        <v>23</v>
+        <v>17.5</v>
       </c>
       <c r="AY7">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AZ7">
         <v>50</v>
       </c>
       <c r="BA7">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="BB7">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BC7">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="BD7">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="BE7">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="BF7">
-        <v>26</v>
+        <v>90</v>
       </c>
       <c r="BG7">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BH7">
         <v>3.25</v>
@@ -2458,10 +2458,10 @@
         <v>2.56</v>
       </c>
       <c r="H8">
+        <v>2.82</v>
+      </c>
+      <c r="I8">
         <v>2.86</v>
-      </c>
-      <c r="I8">
-        <v>2.88</v>
       </c>
       <c r="J8">
         <v>3.85</v>
@@ -2482,16 +2482,16 @@
         <v>1.17</v>
       </c>
       <c r="P8">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="Q8">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="R8">
         <v>1.74</v>
       </c>
       <c r="S8">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="T8">
         <v>1.48</v>
@@ -2536,7 +2536,7 @@
         <v>13</v>
       </c>
       <c r="AH8">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AI8">
         <v>29</v>
@@ -2578,7 +2578,7 @@
         <v>9.4</v>
       </c>
       <c r="AV8">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AW8">
         <v>23</v>
@@ -2602,10 +2602,10 @@
         <v>20</v>
       </c>
       <c r="BD8">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BE8">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BF8">
         <v>11</v>
@@ -2629,7 +2629,7 @@
         <v>70</v>
       </c>
       <c r="BM8">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BN8">
         <v>5.9</v>
@@ -2641,13 +2641,13 @@
         <v>16.5</v>
       </c>
       <c r="BQ8">
-        <v>8.6</v>
+        <v>12</v>
       </c>
       <c r="BR8">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BS8">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BT8">
         <v>6.4</v>
@@ -2659,16 +2659,16 @@
         <v>19.5</v>
       </c>
       <c r="BW8">
-        <v>8.800000000000001</v>
+        <v>14</v>
       </c>
       <c r="BX8">
         <v>25</v>
       </c>
       <c r="BY8">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BZ8">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="CA8">
         <v>8</v>
@@ -2694,10 +2694,10 @@
         <v>121</v>
       </c>
       <c r="F9">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="G9">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="H9">
         <v>4.6</v>
@@ -2712,7 +2712,7 @@
         <v>4.2</v>
       </c>
       <c r="L9">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="M9">
         <v>1.05</v>
@@ -2736,16 +2736,16 @@
         <v>2.78</v>
       </c>
       <c r="T9">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="U9">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V9">
         <v>1.27</v>
       </c>
       <c r="W9">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="X9">
         <v>19.5</v>
@@ -2775,10 +2775,10 @@
         <v>12.5</v>
       </c>
       <c r="AG9">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH9">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI9">
         <v>55</v>
@@ -2787,7 +2787,7 @@
         <v>19</v>
       </c>
       <c r="AK9">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AL9">
         <v>30</v>
@@ -2811,7 +2811,7 @@
         <v>34</v>
       </c>
       <c r="AS9">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AT9">
         <v>10</v>
@@ -2820,7 +2820,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV9">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AW9">
         <v>46</v>
@@ -2835,13 +2835,13 @@
         <v>16.5</v>
       </c>
       <c r="BA9">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BB9">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BC9">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BD9">
         <v>27</v>
@@ -2850,7 +2850,7 @@
         <v>65</v>
       </c>
       <c r="BF9">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG9">
         <v>42</v>
@@ -2859,10 +2859,10 @@
         <v>3.9</v>
       </c>
       <c r="BI9">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BJ9">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BK9">
         <v>8.4</v>
@@ -2871,7 +2871,7 @@
         <v>100</v>
       </c>
       <c r="BM9">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BN9">
         <v>4.7</v>
@@ -2880,10 +2880,10 @@
         <v>4.2</v>
       </c>
       <c r="BP9">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BQ9">
-        <v>6.6</v>
+        <v>10</v>
       </c>
       <c r="BR9">
         <v>24</v>
@@ -2901,19 +2901,19 @@
         <v>38</v>
       </c>
       <c r="BW9">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BX9">
         <v>42</v>
       </c>
       <c r="BY9">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BZ9">
         <v>18</v>
       </c>
       <c r="CA9">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB9" t="s">
         <v>130</v>
@@ -2936,13 +2936,13 @@
         <v>122</v>
       </c>
       <c r="F10">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="G10">
         <v>2.54</v>
       </c>
       <c r="H10">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="I10">
         <v>3.4</v>
@@ -2966,7 +2966,7 @@
         <v>1.46</v>
       </c>
       <c r="P10">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="Q10">
         <v>2.38</v>
@@ -2981,10 +2981,10 @@
         <v>2.02</v>
       </c>
       <c r="U10">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="V10">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W10">
         <v>1.64</v>
@@ -3131,7 +3131,7 @@
         <v>40</v>
       </c>
       <c r="BS10">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BT10">
         <v>6.4</v>
@@ -3146,7 +3146,7 @@
         <v>11.5</v>
       </c>
       <c r="BX10">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BY10">
         <v>13.5</v>
@@ -3155,7 +3155,7 @@
         <v>40</v>
       </c>
       <c r="CA10">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="CB10" t="s">
         <v>130</v>
@@ -3178,16 +3178,16 @@
         <v>123</v>
       </c>
       <c r="F11">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="G11">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="H11">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="I11">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="J11">
         <v>5.4</v>
@@ -3214,28 +3214,28 @@
         <v>1.56</v>
       </c>
       <c r="R11">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="S11">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="T11">
         <v>1.77</v>
       </c>
       <c r="U11">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="V11">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W11">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="X11">
         <v>26</v>
       </c>
       <c r="Y11">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Z11">
         <v>75</v>
@@ -3253,19 +3253,19 @@
         <v>29</v>
       </c>
       <c r="AE11">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AF11">
         <v>10.5</v>
       </c>
       <c r="AG11">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH11">
         <v>22</v>
       </c>
       <c r="AI11">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AJ11">
         <v>13.5</v>
@@ -3274,7 +3274,7 @@
         <v>14</v>
       </c>
       <c r="AL11">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AM11">
         <v>95</v>
@@ -3289,13 +3289,13 @@
         <v>24</v>
       </c>
       <c r="AQ11">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AR11">
         <v>60</v>
       </c>
       <c r="AS11">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AT11">
         <v>11</v>
@@ -3307,7 +3307,7 @@
         <v>25</v>
       </c>
       <c r="AW11">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX11">
         <v>9.199999999999999</v>
@@ -3316,13 +3316,13 @@
         <v>9.6</v>
       </c>
       <c r="AZ11">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA11">
         <v>65</v>
       </c>
       <c r="BB11">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BC11">
         <v>12.5</v>
@@ -3334,10 +3334,10 @@
         <v>75</v>
       </c>
       <c r="BF11">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BG11">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="BH11">
         <v>4.7</v>
@@ -3450,10 +3450,10 @@
         <v>1.41</v>
       </c>
       <c r="P12">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="Q12">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="R12">
         <v>1.28</v>
@@ -3462,7 +3462,7 @@
         <v>4.2</v>
       </c>
       <c r="T12">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="U12">
         <v>2</v>
@@ -3483,10 +3483,10 @@
         <v>17.5</v>
       </c>
       <c r="AA12">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AB12">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AC12">
         <v>7.4</v>
@@ -3507,7 +3507,7 @@
         <v>19.5</v>
       </c>
       <c r="AI12">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ12">
         <v>46</v>
@@ -3516,7 +3516,7 @@
         <v>36</v>
       </c>
       <c r="AL12">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AM12">
         <v>120</v>
@@ -3540,7 +3540,7 @@
         <v>40</v>
       </c>
       <c r="AT12">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AU12">
         <v>7.2</v>
@@ -3555,7 +3555,7 @@
         <v>15.5</v>
       </c>
       <c r="AY12">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ12">
         <v>17.5</v>
@@ -3579,13 +3579,13 @@
         <v>30</v>
       </c>
       <c r="BG12">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BH12">
         <v>3.05</v>
       </c>
       <c r="BI12">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="BJ12">
         <v>11.5</v>
@@ -3674,7 +3674,7 @@
         <v>18.5</v>
       </c>
       <c r="J13">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="K13">
         <v>7.8</v>
@@ -3686,34 +3686,34 @@
         <v>1.03</v>
       </c>
       <c r="N13">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="O13">
         <v>1.19</v>
       </c>
       <c r="P13">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="Q13">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="R13">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="S13">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="T13">
         <v>2.36</v>
       </c>
       <c r="U13">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="V13">
         <v>1.05</v>
       </c>
       <c r="W13">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="X13">
         <v>27</v>
@@ -3722,13 +3722,13 @@
         <v>50</v>
       </c>
       <c r="Z13">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="AA13">
         <v>1000</v>
       </c>
       <c r="AB13">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AC13">
         <v>17</v>
@@ -3737,7 +3737,7 @@
         <v>60</v>
       </c>
       <c r="AE13">
-        <v>390</v>
+        <v>410</v>
       </c>
       <c r="AF13">
         <v>7.6</v>
@@ -3746,13 +3746,13 @@
         <v>12.5</v>
       </c>
       <c r="AH13">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AI13">
         <v>270</v>
       </c>
       <c r="AJ13">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AK13">
         <v>14.5</v>
@@ -3764,7 +3764,7 @@
         <v>260</v>
       </c>
       <c r="AN13">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AO13">
         <v>1000</v>
@@ -3776,22 +3776,22 @@
         <v>46</v>
       </c>
       <c r="AR13">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AS13">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AT13">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AU13">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AV13">
         <v>50</v>
       </c>
       <c r="AW13">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AX13">
         <v>7.2</v>
@@ -3800,10 +3800,10 @@
         <v>11.5</v>
       </c>
       <c r="AZ13">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BA13">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BB13">
         <v>8.199999999999999</v>
@@ -3815,13 +3815,13 @@
         <v>42</v>
       </c>
       <c r="BE13">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BF13">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="BG13">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BH13">
         <v>1000</v>
@@ -3904,16 +3904,16 @@
         <v>126</v>
       </c>
       <c r="F14">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="G14">
         <v>3.2</v>
       </c>
       <c r="H14">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="I14">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="J14">
         <v>3.1</v>
@@ -3922,10 +3922,10 @@
         <v>3.55</v>
       </c>
       <c r="L14">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M14">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N14">
         <v>3</v>
@@ -3946,10 +3946,10 @@
         <v>3.9</v>
       </c>
       <c r="T14">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="U14">
-        <v>1.83</v>
+        <v>1.99</v>
       </c>
       <c r="V14">
         <v>1.52</v>
@@ -3970,7 +3970,7 @@
         <v>55</v>
       </c>
       <c r="AB14">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AC14">
         <v>8</v>
@@ -3997,7 +3997,7 @@
         <v>60</v>
       </c>
       <c r="AK14">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AL14">
         <v>65</v>
@@ -4018,25 +4018,25 @@
         <v>7.4</v>
       </c>
       <c r="AR14">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AS14">
         <v>1.03</v>
       </c>
       <c r="AT14">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AU14">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AV14">
         <v>9.199999999999999</v>
       </c>
       <c r="AW14">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="AX14">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AY14">
         <v>9.6</v>
@@ -4197,7 +4197,7 @@
         <v>1.02</v>
       </c>
       <c r="W15">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X15">
         <v>1000</v>
@@ -4412,10 +4412,10 @@
         <v>1.15</v>
       </c>
       <c r="N16">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="O16">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="P16">
         <v>1.41</v>
@@ -4445,7 +4445,7 @@
         <v>8.6</v>
       </c>
       <c r="Y16">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="Z16">
         <v>17.5</v>
@@ -4457,7 +4457,7 @@
         <v>11</v>
       </c>
       <c r="AC16">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AD16">
         <v>16.5</v>
@@ -4481,7 +4481,7 @@
         <v>110</v>
       </c>
       <c r="AK16">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AL16">
         <v>130</v>
@@ -4502,10 +4502,10 @@
         <v>5.2</v>
       </c>
       <c r="AR16">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AS16">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="AT16">
         <v>6.8</v>
@@ -4517,43 +4517,43 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW16">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="AX16">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AY16">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AZ16">
-        <v>6.2</v>
+        <v>19.5</v>
       </c>
       <c r="BA16">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="BB16">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="BC16">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="BD16">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="BE16">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="BF16">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="BG16">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="BH16">
         <v>2.56</v>
       </c>
       <c r="BI16">
-        <v>2.24</v>
+        <v>2.06</v>
       </c>
       <c r="BJ16">
         <v>13</v>
@@ -4663,13 +4663,13 @@
         <v>1.09</v>
       </c>
       <c r="Q17">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="R17">
         <v>1.08</v>
       </c>
       <c r="S17">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="T17">
         <v>1.01</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-24.xlsx
@@ -406,7 +406,7 @@
     <t>Vinotinto Ecuador</t>
   </si>
   <si>
-    <t>2026-09-23 14:33:38</t>
+    <t>2026-09-23 16:46:10</t>
   </si>
 </sst>
 </file>
@@ -1000,130 +1000,130 @@
         <v>114</v>
       </c>
       <c r="F2">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="G2">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="H2">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="I2">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K2">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L2">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="M2">
         <v>1.07</v>
       </c>
       <c r="N2">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="O2">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P2">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="Q2">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R2">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S2">
         <v>3.6</v>
       </c>
       <c r="T2">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U2">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="V2">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W2">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="X2">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Y2">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="Z2">
         <v>55</v>
       </c>
       <c r="AA2">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="AB2">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AC2">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AD2">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AE2">
         <v>110</v>
       </c>
       <c r="AF2">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AG2">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI2">
         <v>110</v>
       </c>
       <c r="AJ2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK2">
+        <v>18</v>
+      </c>
+      <c r="AL2">
+        <v>42</v>
+      </c>
+      <c r="AM2">
+        <v>150</v>
+      </c>
+      <c r="AN2">
+        <v>10.5</v>
+      </c>
+      <c r="AO2">
+        <v>160</v>
+      </c>
+      <c r="AP2">
+        <v>13.5</v>
+      </c>
+      <c r="AQ2">
         <v>18.5</v>
-      </c>
-      <c r="AL2">
-        <v>40</v>
-      </c>
-      <c r="AM2">
-        <v>180</v>
-      </c>
-      <c r="AN2">
-        <v>11</v>
-      </c>
-      <c r="AO2">
-        <v>130</v>
-      </c>
-      <c r="AP2">
-        <v>12.5</v>
-      </c>
-      <c r="AQ2">
-        <v>17</v>
       </c>
       <c r="AR2">
         <v>42</v>
       </c>
       <c r="AS2">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AT2">
         <v>7.2</v>
       </c>
       <c r="AU2">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV2">
         <v>21</v>
@@ -1132,22 +1132,22 @@
         <v>60</v>
       </c>
       <c r="AX2">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY2">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA2">
         <v>75</v>
       </c>
       <c r="BB2">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BC2">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BD2">
         <v>34</v>
@@ -1156,70 +1156,70 @@
         <v>90</v>
       </c>
       <c r="BF2">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG2">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="BH2">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="BI2">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="BJ2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BK2">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BL2">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="BM2">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="BN2">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BO2">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BP2">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BQ2">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="BR2">
         <v>28</v>
       </c>
       <c r="BS2">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BT2">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BU2">
-        <v>6.2</v>
+        <v>4.8</v>
       </c>
       <c r="BV2">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="BW2">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BX2">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="BY2">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BZ2">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="CA2">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="CB2" t="s">
         <v>130</v>
@@ -1242,22 +1242,22 @@
         <v>115</v>
       </c>
       <c r="F3">
+        <v>1.83</v>
+      </c>
+      <c r="G3">
         <v>1.84</v>
       </c>
-      <c r="G3">
-        <v>1.86</v>
-      </c>
       <c r="H3">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="I3">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J3">
         <v>4.2</v>
       </c>
       <c r="K3">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L3">
         <v>1.3</v>
@@ -1266,58 +1266,58 @@
         <v>1.04</v>
       </c>
       <c r="N3">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="O3">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P3">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="Q3">
+        <v>1.57</v>
+      </c>
+      <c r="R3">
+        <v>1.68</v>
+      </c>
+      <c r="S3">
+        <v>2.42</v>
+      </c>
+      <c r="T3">
         <v>1.59</v>
       </c>
-      <c r="R3">
-        <v>1.66</v>
-      </c>
-      <c r="S3">
-        <v>2.44</v>
-      </c>
-      <c r="T3">
-        <v>1.6</v>
-      </c>
       <c r="U3">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="V3">
         <v>1.27</v>
       </c>
       <c r="W3">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="X3">
         <v>26</v>
       </c>
       <c r="Y3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Z3">
         <v>38</v>
       </c>
       <c r="AA3">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AB3">
         <v>13.5</v>
       </c>
       <c r="AC3">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD3">
         <v>17.5</v>
       </c>
       <c r="AE3">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF3">
         <v>14</v>
@@ -1329,7 +1329,7 @@
         <v>15.5</v>
       </c>
       <c r="AI3">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ3">
         <v>21</v>
@@ -1341,10 +1341,10 @@
         <v>25</v>
       </c>
       <c r="AM3">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AN3">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AO3">
         <v>34</v>
@@ -1359,7 +1359,7 @@
         <v>34</v>
       </c>
       <c r="AS3">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AT3">
         <v>12.5</v>
@@ -1368,19 +1368,19 @@
         <v>9.4</v>
       </c>
       <c r="AV3">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AW3">
         <v>40</v>
       </c>
       <c r="AX3">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AY3">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ3">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA3">
         <v>40</v>
@@ -1398,13 +1398,13 @@
         <v>50</v>
       </c>
       <c r="BF3">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BG3">
         <v>30</v>
       </c>
       <c r="BH3">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BI3">
         <v>4</v>
@@ -1416,7 +1416,7 @@
         <v>7.8</v>
       </c>
       <c r="BL3">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="BM3">
         <v>12.5</v>
@@ -1434,10 +1434,10 @@
         <v>10</v>
       </c>
       <c r="BR3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BS3">
-        <v>17</v>
+        <v>8.4</v>
       </c>
       <c r="BT3">
         <v>8.199999999999999</v>
@@ -1449,7 +1449,7 @@
         <v>38</v>
       </c>
       <c r="BW3">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX3">
         <v>40</v>
@@ -1458,7 +1458,7 @@
         <v>10.5</v>
       </c>
       <c r="BZ3">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="CA3">
         <v>10.5</v>
@@ -1484,226 +1484,226 @@
         <v>116</v>
       </c>
       <c r="F4">
-        <v>1.89</v>
+        <v>2.58</v>
       </c>
       <c r="G4">
-        <v>1.92</v>
+        <v>2.7</v>
       </c>
       <c r="H4">
-        <v>3.85</v>
+        <v>2.56</v>
       </c>
       <c r="I4">
-        <v>4</v>
+        <v>2.64</v>
       </c>
       <c r="J4">
+        <v>4.1</v>
+      </c>
+      <c r="K4">
         <v>4.4</v>
       </c>
-      <c r="K4">
-        <v>4.8</v>
-      </c>
       <c r="L4">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="M4">
         <v>1.04</v>
       </c>
       <c r="N4">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="O4">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="P4">
         <v>2.64</v>
       </c>
       <c r="Q4">
+        <v>1.58</v>
+      </c>
+      <c r="R4">
+        <v>1.62</v>
+      </c>
+      <c r="S4">
+        <v>2.48</v>
+      </c>
+      <c r="T4">
         <v>1.55</v>
       </c>
-      <c r="R4">
-        <v>1.65</v>
-      </c>
-      <c r="S4">
-        <v>2.4</v>
-      </c>
-      <c r="T4">
-        <v>1.57</v>
-      </c>
       <c r="U4">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="V4">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="W4">
-        <v>2.08</v>
+        <v>1.58</v>
       </c>
       <c r="X4">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="Y4">
+        <v>17</v>
+      </c>
+      <c r="Z4">
+        <v>23</v>
+      </c>
+      <c r="AA4">
+        <v>40</v>
+      </c>
+      <c r="AB4">
+        <v>16</v>
+      </c>
+      <c r="AC4">
+        <v>10.5</v>
+      </c>
+      <c r="AD4">
+        <v>13</v>
+      </c>
+      <c r="AE4">
+        <v>25</v>
+      </c>
+      <c r="AF4">
+        <v>22</v>
+      </c>
+      <c r="AG4">
+        <v>12.5</v>
+      </c>
+      <c r="AH4">
+        <v>15.5</v>
+      </c>
+      <c r="AI4">
+        <v>29</v>
+      </c>
+      <c r="AJ4">
+        <v>40</v>
+      </c>
+      <c r="AK4">
         <v>26</v>
       </c>
-      <c r="Z4">
-        <v>40</v>
-      </c>
-      <c r="AA4">
-        <v>85</v>
-      </c>
-      <c r="AB4">
+      <c r="AL4">
+        <v>30</v>
+      </c>
+      <c r="AM4">
+        <v>60</v>
+      </c>
+      <c r="AN4">
+        <v>16.5</v>
+      </c>
+      <c r="AO4">
+        <v>19.5</v>
+      </c>
+      <c r="AP4">
+        <v>21</v>
+      </c>
+      <c r="AQ4">
+        <v>14.5</v>
+      </c>
+      <c r="AR4">
+        <v>18.5</v>
+      </c>
+      <c r="AS4">
+        <v>32</v>
+      </c>
+      <c r="AT4">
         <v>13.5</v>
       </c>
-      <c r="AC4">
+      <c r="AU4">
+        <v>9</v>
+      </c>
+      <c r="AV4">
+        <v>11.5</v>
+      </c>
+      <c r="AW4">
+        <v>21</v>
+      </c>
+      <c r="AX4">
+        <v>18.5</v>
+      </c>
+      <c r="AY4">
         <v>11</v>
       </c>
-      <c r="AD4">
+      <c r="AZ4">
+        <v>13.5</v>
+      </c>
+      <c r="BA4">
+        <v>26</v>
+      </c>
+      <c r="BB4">
+        <v>32</v>
+      </c>
+      <c r="BC4">
         <v>21</v>
       </c>
-      <c r="AE4">
-        <v>48</v>
-      </c>
-      <c r="AF4">
-        <v>16.5</v>
-      </c>
-      <c r="AG4">
-        <v>10.5</v>
-      </c>
-      <c r="AH4">
-        <v>17</v>
-      </c>
-      <c r="AI4">
-        <v>48</v>
-      </c>
-      <c r="AJ4">
-        <v>23</v>
-      </c>
-      <c r="AK4">
-        <v>21</v>
-      </c>
-      <c r="AL4">
-        <v>32</v>
-      </c>
-      <c r="AM4">
-        <v>85</v>
-      </c>
-      <c r="AN4">
-        <v>8.6</v>
-      </c>
-      <c r="AO4">
-        <v>32</v>
-      </c>
-      <c r="AP4">
-        <v>18</v>
-      </c>
-      <c r="AQ4">
-        <v>18.5</v>
-      </c>
-      <c r="AR4">
+      <c r="BD4">
         <v>26</v>
       </c>
-      <c r="AS4">
-        <v>50</v>
-      </c>
-      <c r="AT4">
-        <v>10.5</v>
-      </c>
-      <c r="AU4">
-        <v>9.6</v>
-      </c>
-      <c r="AV4">
-        <v>14.5</v>
-      </c>
-      <c r="AW4">
-        <v>32</v>
-      </c>
-      <c r="AX4">
-        <v>12</v>
-      </c>
-      <c r="AY4">
-        <v>9</v>
-      </c>
-      <c r="AZ4">
-        <v>14.5</v>
-      </c>
-      <c r="BA4">
-        <v>30</v>
-      </c>
-      <c r="BB4">
-        <v>19</v>
-      </c>
-      <c r="BC4">
-        <v>15.5</v>
-      </c>
-      <c r="BD4">
-        <v>21</v>
-      </c>
       <c r="BE4">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="BF4">
-        <v>7.2</v>
+        <v>13</v>
       </c>
       <c r="BG4">
-        <v>18</v>
+        <v>13.5</v>
       </c>
       <c r="BH4">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BI4">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="BJ4">
         <v>10.5</v>
       </c>
       <c r="BK4">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BL4">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BM4">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="BN4">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="BO4">
-        <v>3.9</v>
+        <v>5.3</v>
       </c>
       <c r="BP4">
-        <v>14.5</v>
+        <v>23</v>
       </c>
       <c r="BQ4">
-        <v>8.800000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="BR4">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="BS4">
-        <v>15</v>
+        <v>4.4</v>
       </c>
       <c r="BT4">
-        <v>9.4</v>
+        <v>7.2</v>
       </c>
       <c r="BU4">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="BV4">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="BW4">
+        <v>4.1</v>
+      </c>
+      <c r="BX4">
+        <v>36</v>
+      </c>
+      <c r="BY4">
+        <v>5.3</v>
+      </c>
+      <c r="BZ4">
         <v>20</v>
       </c>
-      <c r="BX4">
-        <v>38</v>
-      </c>
-      <c r="BY4">
-        <v>23</v>
-      </c>
-      <c r="BZ4">
-        <v>17.5</v>
-      </c>
       <c r="CA4">
-        <v>10.5</v>
+        <v>4.1</v>
       </c>
       <c r="CB4" t="s">
         <v>130</v>
@@ -1729,16 +1729,16 @@
         <v>1.22</v>
       </c>
       <c r="G5">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="H5">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="I5">
         <v>400</v>
       </c>
       <c r="J5">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="K5">
         <v>60</v>
@@ -1777,7 +1777,7 @@
         <v>1.02</v>
       </c>
       <c r="W5">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X5">
         <v>1000</v>
@@ -1974,13 +1974,13 @@
         <v>3.85</v>
       </c>
       <c r="H6">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="I6">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="J6">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="K6">
         <v>2.96</v>
@@ -1989,31 +1989,31 @@
         <v>1.67</v>
       </c>
       <c r="M6">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="N6">
         <v>2.24</v>
       </c>
       <c r="O6">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="P6">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="Q6">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="R6">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="S6">
         <v>7.8</v>
       </c>
       <c r="T6">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="U6">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="V6">
         <v>1.65</v>
@@ -2031,13 +2031,13 @@
         <v>12.5</v>
       </c>
       <c r="AA6">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AB6">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC6">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AD6">
         <v>14.5</v>
@@ -2055,19 +2055,19 @@
         <v>32</v>
       </c>
       <c r="AI6">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AJ6">
         <v>110</v>
       </c>
       <c r="AK6">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AL6">
         <v>140</v>
       </c>
       <c r="AM6">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="AN6">
         <v>150</v>
@@ -2085,7 +2085,7 @@
         <v>11.5</v>
       </c>
       <c r="AS6">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AT6">
         <v>8</v>
@@ -2106,10 +2106,10 @@
         <v>17.5</v>
       </c>
       <c r="AZ6">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BA6">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BB6">
         <v>80</v>
@@ -2121,25 +2121,25 @@
         <v>42</v>
       </c>
       <c r="BE6">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="BF6">
         <v>42</v>
       </c>
       <c r="BG6">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="BH6">
-        <v>2.34</v>
+        <v>1000</v>
       </c>
       <c r="BI6">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="BJ6">
-        <v>13.5</v>
+        <v>17</v>
       </c>
       <c r="BK6">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL6">
         <v>1000</v>
@@ -2148,16 +2148,16 @@
         <v>21</v>
       </c>
       <c r="BN6">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO6">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="BP6">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="BR6">
         <v>1000</v>
@@ -2166,28 +2166,28 @@
         <v>21</v>
       </c>
       <c r="BT6">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BU6">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="BV6">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="BW6">
+        <v>17.5</v>
+      </c>
+      <c r="BX6">
+        <v>1000</v>
+      </c>
+      <c r="BY6">
         <v>21</v>
       </c>
-      <c r="BX6">
-        <v>65</v>
-      </c>
-      <c r="BY6">
-        <v>42</v>
-      </c>
       <c r="BZ6">
         <v>1000</v>
       </c>
       <c r="CA6">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="CB6" t="s">
         <v>130</v>
@@ -2210,10 +2210,10 @@
         <v>119</v>
       </c>
       <c r="F7">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="G7">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="H7">
         <v>1.33</v>
@@ -2222,40 +2222,40 @@
         <v>1.34</v>
       </c>
       <c r="J7">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="K7">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="L7">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M7">
         <v>1.08</v>
       </c>
       <c r="N7">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="O7">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P7">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="Q7">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="R7">
         <v>1.28</v>
       </c>
       <c r="S7">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="T7">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="U7">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="V7">
         <v>3.9</v>
@@ -2270,19 +2270,19 @@
         <v>5.7</v>
       </c>
       <c r="Z7">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AA7">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AB7">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AC7">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD7">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE7">
         <v>19</v>
@@ -2291,7 +2291,7 @@
         <v>170</v>
       </c>
       <c r="AG7">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="AH7">
         <v>60</v>
@@ -2303,13 +2303,13 @@
         <v>1000</v>
       </c>
       <c r="AK7">
-        <v>510</v>
+        <v>490</v>
       </c>
       <c r="AL7">
-        <v>480</v>
+        <v>470</v>
       </c>
       <c r="AM7">
-        <v>630</v>
+        <v>610</v>
       </c>
       <c r="AN7">
         <v>1000</v>
@@ -2318,58 +2318,58 @@
         <v>7.8</v>
       </c>
       <c r="AP7">
+        <v>12.5</v>
+      </c>
+      <c r="AQ7">
+        <v>5.5</v>
+      </c>
+      <c r="AR7">
+        <v>5.7</v>
+      </c>
+      <c r="AS7">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT7">
+        <v>26</v>
+      </c>
+      <c r="AU7">
         <v>11.5</v>
       </c>
-      <c r="AQ7">
-        <v>5.6</v>
-      </c>
-      <c r="AR7">
-        <v>5.6</v>
-      </c>
-      <c r="AS7">
-        <v>8.6</v>
-      </c>
-      <c r="AT7">
-        <v>27</v>
-      </c>
-      <c r="AU7">
-        <v>12.5</v>
-      </c>
       <c r="AV7">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AW7">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AX7">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AY7">
         <v>55</v>
       </c>
       <c r="AZ7">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BA7">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="BB7">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="BC7">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BD7">
         <v>16.5</v>
       </c>
       <c r="BE7">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BF7">
         <v>90</v>
       </c>
       <c r="BG7">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BH7">
         <v>3.25</v>
@@ -2414,7 +2414,7 @@
         <v>3.05</v>
       </c>
       <c r="BV7">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BW7">
         <v>7</v>
@@ -2458,16 +2458,16 @@
         <v>2.56</v>
       </c>
       <c r="H8">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="I8">
         <v>2.86</v>
       </c>
       <c r="J8">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K8">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L8">
         <v>1.28</v>
@@ -2485,7 +2485,7 @@
         <v>2.8</v>
       </c>
       <c r="Q8">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="R8">
         <v>1.74</v>
@@ -2494,10 +2494,10 @@
         <v>2.26</v>
       </c>
       <c r="T8">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="U8">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="V8">
         <v>1.53</v>
@@ -2506,7 +2506,7 @@
         <v>1.64</v>
       </c>
       <c r="X8">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Y8">
         <v>19</v>
@@ -2524,22 +2524,22 @@
         <v>9.6</v>
       </c>
       <c r="AD8">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE8">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF8">
         <v>21</v>
       </c>
       <c r="AG8">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH8">
         <v>13</v>
       </c>
       <c r="AI8">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AJ8">
         <v>38</v>
@@ -2569,7 +2569,7 @@
         <v>22</v>
       </c>
       <c r="AS8">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AT8">
         <v>16.5</v>
@@ -2584,10 +2584,10 @@
         <v>23</v>
       </c>
       <c r="AX8">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AY8">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AZ8">
         <v>12.5</v>
@@ -2602,16 +2602,16 @@
         <v>20</v>
       </c>
       <c r="BD8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BE8">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BF8">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BG8">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BH8">
         <v>4.6</v>
@@ -2626,7 +2626,7 @@
         <v>7.2</v>
       </c>
       <c r="BL8">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BM8">
         <v>14</v>
@@ -2671,7 +2671,7 @@
         <v>14.5</v>
       </c>
       <c r="CA8">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB8" t="s">
         <v>130</v>
@@ -2694,10 +2694,10 @@
         <v>121</v>
       </c>
       <c r="F9">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="G9">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="H9">
         <v>4.6</v>
@@ -2718,7 +2718,7 @@
         <v>1.05</v>
       </c>
       <c r="N9">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O9">
         <v>1.24</v>
@@ -2727,25 +2727,25 @@
         <v>2.3</v>
       </c>
       <c r="Q9">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="R9">
         <v>1.53</v>
       </c>
       <c r="S9">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="T9">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="U9">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V9">
         <v>1.27</v>
       </c>
       <c r="W9">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="X9">
         <v>19.5</v>
@@ -2766,7 +2766,7 @@
         <v>9.4</v>
       </c>
       <c r="AD9">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE9">
         <v>55</v>
@@ -2793,31 +2793,31 @@
         <v>30</v>
       </c>
       <c r="AM9">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN9">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO9">
         <v>48</v>
       </c>
       <c r="AP9">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AQ9">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AR9">
         <v>34</v>
       </c>
       <c r="AS9">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="AT9">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU9">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV9">
         <v>17</v>
@@ -2829,31 +2829,31 @@
         <v>11.5</v>
       </c>
       <c r="AY9">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ9">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BA9">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BB9">
         <v>18</v>
       </c>
       <c r="BC9">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BD9">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BE9">
         <v>65</v>
       </c>
       <c r="BF9">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BG9">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BH9">
         <v>3.9</v>
@@ -2871,7 +2871,7 @@
         <v>100</v>
       </c>
       <c r="BM9">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BN9">
         <v>4.7</v>
@@ -2892,7 +2892,7 @@
         <v>9.4</v>
       </c>
       <c r="BT9">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU9">
         <v>7.4</v>
@@ -2901,19 +2901,19 @@
         <v>38</v>
       </c>
       <c r="BW9">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BX9">
         <v>42</v>
       </c>
       <c r="BY9">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BZ9">
         <v>18</v>
       </c>
       <c r="CA9">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="CB9" t="s">
         <v>130</v>
@@ -2945,7 +2945,7 @@
         <v>3.3</v>
       </c>
       <c r="I10">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J10">
         <v>3.25</v>
@@ -2954,10 +2954,10 @@
         <v>3.3</v>
       </c>
       <c r="L10">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="M10">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N10">
         <v>3</v>
@@ -2966,10 +2966,10 @@
         <v>1.46</v>
       </c>
       <c r="P10">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="Q10">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R10">
         <v>1.26</v>
@@ -2993,7 +2993,7 @@
         <v>10.5</v>
       </c>
       <c r="Y10">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Z10">
         <v>21</v>
@@ -3002,19 +3002,19 @@
         <v>65</v>
       </c>
       <c r="AB10">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC10">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD10">
         <v>15</v>
       </c>
       <c r="AE10">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AF10">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG10">
         <v>12.5</v>
@@ -3044,22 +3044,22 @@
         <v>55</v>
       </c>
       <c r="AP10">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ10">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR10">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AS10">
         <v>50</v>
       </c>
       <c r="AT10">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU10">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AV10">
         <v>13.5</v>
@@ -3074,7 +3074,7 @@
         <v>11.5</v>
       </c>
       <c r="AZ10">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA10">
         <v>55</v>
@@ -3089,7 +3089,7 @@
         <v>48</v>
       </c>
       <c r="BE10">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BF10">
         <v>27</v>
@@ -3113,25 +3113,25 @@
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BN10">
         <v>5.3</v>
       </c>
       <c r="BO10">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BP10">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BQ10">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BR10">
         <v>40</v>
       </c>
       <c r="BS10">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BT10">
         <v>6.4</v>
@@ -3143,19 +3143,19 @@
         <v>30</v>
       </c>
       <c r="BW10">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BX10">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY10">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BZ10">
         <v>40</v>
       </c>
       <c r="CA10">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="CB10" t="s">
         <v>130</v>
@@ -3178,22 +3178,22 @@
         <v>123</v>
       </c>
       <c r="F11">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="G11">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="H11">
         <v>7.6</v>
       </c>
       <c r="I11">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="J11">
+        <v>5.3</v>
+      </c>
+      <c r="K11">
         <v>5.4</v>
-      </c>
-      <c r="K11">
-        <v>5.5</v>
       </c>
       <c r="L11">
         <v>1.28</v>
@@ -3208,10 +3208,10 @@
         <v>1.18</v>
       </c>
       <c r="P11">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="Q11">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="R11">
         <v>1.69</v>
@@ -3229,7 +3229,7 @@
         <v>1.14</v>
       </c>
       <c r="W11">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="X11">
         <v>26</v>
@@ -3241,7 +3241,7 @@
         <v>75</v>
       </c>
       <c r="AA11">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AB11">
         <v>12</v>
@@ -3277,7 +3277,7 @@
         <v>28</v>
       </c>
       <c r="AM11">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN11">
         <v>5.1</v>
@@ -3304,19 +3304,19 @@
         <v>11</v>
       </c>
       <c r="AV11">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW11">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AX11">
         <v>9.199999999999999</v>
       </c>
       <c r="AY11">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ11">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BA11">
         <v>65</v>
@@ -3328,7 +3328,7 @@
         <v>12.5</v>
       </c>
       <c r="BD11">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BE11">
         <v>75</v>
@@ -3340,7 +3340,7 @@
         <v>14</v>
       </c>
       <c r="BH11">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BI11">
         <v>4.1</v>
@@ -3355,7 +3355,7 @@
         <v>120</v>
       </c>
       <c r="BM11">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BN11">
         <v>4.3</v>
@@ -3364,7 +3364,7 @@
         <v>3.9</v>
       </c>
       <c r="BP11">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BQ11">
         <v>7.4</v>
@@ -3385,13 +3385,13 @@
         <v>70</v>
       </c>
       <c r="BW11">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BX11">
         <v>65</v>
       </c>
       <c r="BY11">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BZ11">
         <v>13.5</v>
@@ -3420,7 +3420,7 @@
         <v>124</v>
       </c>
       <c r="F12">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="G12">
         <v>2.84</v>
@@ -3435,7 +3435,7 @@
         <v>3.4</v>
       </c>
       <c r="K12">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L12">
         <v>1.48</v>
@@ -3444,28 +3444,28 @@
         <v>1.09</v>
       </c>
       <c r="N12">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O12">
         <v>1.41</v>
       </c>
       <c r="P12">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="Q12">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="R12">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S12">
         <v>4.2</v>
       </c>
       <c r="T12">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="U12">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V12">
         <v>1.54</v>
@@ -3480,31 +3480,31 @@
         <v>9.800000000000001</v>
       </c>
       <c r="Z12">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AA12">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AB12">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC12">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD12">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE12">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF12">
         <v>17.5</v>
       </c>
       <c r="AG12">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH12">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI12">
         <v>50</v>
@@ -3513,16 +3513,16 @@
         <v>46</v>
       </c>
       <c r="AK12">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL12">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AM12">
         <v>120</v>
       </c>
       <c r="AN12">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AO12">
         <v>34</v>
@@ -3540,7 +3540,7 @@
         <v>40</v>
       </c>
       <c r="AT12">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AU12">
         <v>7.2</v>
@@ -3552,13 +3552,13 @@
         <v>30</v>
       </c>
       <c r="AX12">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AY12">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AZ12">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA12">
         <v>44</v>
@@ -3570,16 +3570,16 @@
         <v>30</v>
       </c>
       <c r="BD12">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BE12">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="BF12">
         <v>30</v>
       </c>
       <c r="BG12">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BH12">
         <v>3.05</v>
@@ -3612,7 +3612,7 @@
         <v>8.6</v>
       </c>
       <c r="BR12">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="BS12">
         <v>9</v>
@@ -3627,7 +3627,7 @@
         <v>24</v>
       </c>
       <c r="BW12">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BX12">
         <v>44</v>
@@ -3668,7 +3668,7 @@
         <v>1.24</v>
       </c>
       <c r="H13">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="I13">
         <v>18.5</v>
@@ -3683,16 +3683,16 @@
         <v>1.24</v>
       </c>
       <c r="M13">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N13">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="O13">
         <v>1.19</v>
       </c>
       <c r="P13">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="Q13">
         <v>1.58</v>
@@ -3704,10 +3704,10 @@
         <v>2.44</v>
       </c>
       <c r="T13">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="U13">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="V13">
         <v>1.05</v>
@@ -3716,7 +3716,7 @@
         <v>5.3</v>
       </c>
       <c r="X13">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Y13">
         <v>50</v>
@@ -3728,7 +3728,7 @@
         <v>1000</v>
       </c>
       <c r="AB13">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC13">
         <v>17</v>
@@ -3737,13 +3737,13 @@
         <v>60</v>
       </c>
       <c r="AE13">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="AF13">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AG13">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH13">
         <v>44</v>
@@ -3752,7 +3752,7 @@
         <v>270</v>
       </c>
       <c r="AJ13">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AK13">
         <v>14.5</v>
@@ -3770,19 +3770,19 @@
         <v>1000</v>
       </c>
       <c r="AP13">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AQ13">
         <v>46</v>
       </c>
       <c r="AR13">
-        <v>18.5</v>
+        <v>29</v>
       </c>
       <c r="AS13">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="AT13">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU13">
         <v>16</v>
@@ -3791,37 +3791,37 @@
         <v>50</v>
       </c>
       <c r="AW13">
-        <v>19.5</v>
+        <v>26</v>
       </c>
       <c r="AX13">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AY13">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AZ13">
         <v>38</v>
       </c>
       <c r="BA13">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="BB13">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BC13">
         <v>13.5</v>
       </c>
       <c r="BD13">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BE13">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="BF13">
         <v>3.65</v>
       </c>
       <c r="BG13">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="BH13">
         <v>1000</v>
@@ -3904,19 +3904,19 @@
         <v>126</v>
       </c>
       <c r="F14">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="G14">
+        <v>3.05</v>
+      </c>
+      <c r="H14">
+        <v>2.64</v>
+      </c>
+      <c r="I14">
+        <v>2.98</v>
+      </c>
+      <c r="J14">
         <v>3.2</v>
-      </c>
-      <c r="H14">
-        <v>2.6</v>
-      </c>
-      <c r="I14">
-        <v>2.92</v>
-      </c>
-      <c r="J14">
-        <v>3.1</v>
       </c>
       <c r="K14">
         <v>3.55</v>
@@ -3928,34 +3928,34 @@
         <v>1.08</v>
       </c>
       <c r="N14">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="O14">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="P14">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="Q14">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="R14">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="S14">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="T14">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="U14">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="V14">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W14">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="X14">
         <v>14.5</v>
@@ -3967,109 +3967,109 @@
         <v>22</v>
       </c>
       <c r="AA14">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AB14">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC14">
         <v>8</v>
       </c>
       <c r="AD14">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AE14">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF14">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AG14">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AH14">
-        <v>23</v>
+        <v>18.5</v>
       </c>
       <c r="AI14">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ14">
         <v>60</v>
       </c>
       <c r="AK14">
+        <v>36</v>
+      </c>
+      <c r="AL14">
+        <v>55</v>
+      </c>
+      <c r="AM14">
+        <v>120</v>
+      </c>
+      <c r="AN14">
+        <v>40</v>
+      </c>
+      <c r="AO14">
         <v>38</v>
       </c>
-      <c r="AL14">
-        <v>65</v>
-      </c>
-      <c r="AM14">
-        <v>140</v>
-      </c>
-      <c r="AN14">
-        <v>44</v>
-      </c>
-      <c r="AO14">
-        <v>42</v>
-      </c>
       <c r="AP14">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ14">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR14">
         <v>13</v>
       </c>
       <c r="AS14">
-        <v>1.03</v>
+        <v>22</v>
       </c>
       <c r="AT14">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU14">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV14">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AW14">
-        <v>1.03</v>
+        <v>18.5</v>
       </c>
       <c r="AX14">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AY14">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AZ14">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BA14">
-        <v>1.03</v>
+        <v>24</v>
       </c>
       <c r="BB14">
-        <v>1.03</v>
+        <v>24</v>
       </c>
       <c r="BC14">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="BD14">
-        <v>1.03</v>
+        <v>26</v>
       </c>
       <c r="BE14">
         <v>1.03</v>
       </c>
       <c r="BF14">
-        <v>25</v>
+        <v>18.5</v>
       </c>
       <c r="BG14">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BH14">
         <v>1000</v>
       </c>
       <c r="BI14">
-        <v>2.56</v>
+        <v>2.78</v>
       </c>
       <c r="BJ14">
         <v>1000</v>
@@ -4149,7 +4149,7 @@
         <v>1.1</v>
       </c>
       <c r="G15">
-        <v>880</v>
+        <v>110</v>
       </c>
       <c r="H15">
         <v>1.1</v>
@@ -4194,10 +4194,10 @@
         <v>1.01</v>
       </c>
       <c r="V15">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W15">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X15">
         <v>1000</v>
@@ -4397,13 +4397,13 @@
         <v>2.4</v>
       </c>
       <c r="I16">
+        <v>2.76</v>
+      </c>
+      <c r="J16">
         <v>2.74</v>
       </c>
-      <c r="J16">
-        <v>2.84</v>
-      </c>
       <c r="K16">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L16">
         <v>1.55</v>
@@ -4436,7 +4436,7 @@
         <v>1.64</v>
       </c>
       <c r="V16">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W16">
         <v>1.32</v>
@@ -4445,34 +4445,34 @@
         <v>8.6</v>
       </c>
       <c r="Y16">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="Z16">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AA16">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AB16">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AC16">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AD16">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AE16">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AF16">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AG16">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AH16">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AI16">
         <v>100</v>
@@ -4493,7 +4493,7 @@
         <v>140</v>
       </c>
       <c r="AO16">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AP16">
         <v>5.4</v>
@@ -4505,7 +4505,7 @@
         <v>10.5</v>
       </c>
       <c r="AS16">
-        <v>4</v>
+        <v>6.4</v>
       </c>
       <c r="AT16">
         <v>6.8</v>
@@ -4517,7 +4517,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW16">
-        <v>4</v>
+        <v>6.4</v>
       </c>
       <c r="AX16">
         <v>17.5</v>
@@ -4529,31 +4529,31 @@
         <v>19.5</v>
       </c>
       <c r="BA16">
-        <v>4.1</v>
+        <v>6.8</v>
       </c>
       <c r="BB16">
-        <v>4.2</v>
+        <v>6.8</v>
       </c>
       <c r="BC16">
-        <v>4.1</v>
+        <v>6.6</v>
       </c>
       <c r="BD16">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="BE16">
-        <v>4.3</v>
+        <v>7.2</v>
       </c>
       <c r="BF16">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="BG16">
-        <v>4.1</v>
+        <v>32</v>
       </c>
       <c r="BH16">
         <v>2.56</v>
       </c>
       <c r="BI16">
-        <v>2.06</v>
+        <v>2.24</v>
       </c>
       <c r="BJ16">
         <v>13</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-24.xlsx
@@ -406,7 +406,7 @@
     <t>Vinotinto Ecuador</t>
   </si>
   <si>
-    <t>2026-09-23 16:46:10</t>
+    <t>2026-09-23 18:58:20</t>
   </si>
 </sst>
 </file>
@@ -1000,226 +1000,226 @@
         <v>114</v>
       </c>
       <c r="F2">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="G2">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="H2">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="I2">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="J2">
+        <v>4.7</v>
+      </c>
+      <c r="K2">
+        <v>4.9</v>
+      </c>
+      <c r="L2">
+        <v>1.38</v>
+      </c>
+      <c r="M2">
+        <v>1.06</v>
+      </c>
+      <c r="N2">
         <v>4.1</v>
       </c>
-      <c r="K2">
-        <v>4.3</v>
-      </c>
-      <c r="L2">
-        <v>1.41</v>
-      </c>
-      <c r="M2">
-        <v>1.07</v>
-      </c>
-      <c r="N2">
-        <v>3.85</v>
-      </c>
       <c r="O2">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="P2">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="Q2">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="R2">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S2">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="T2">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="U2">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="V2">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="W2">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="X2">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y2">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="Z2">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AA2">
-        <v>210</v>
+        <v>350</v>
       </c>
       <c r="AB2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AC2">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AD2">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AE2">
-        <v>110</v>
+        <v>160</v>
       </c>
       <c r="AF2">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG2">
         <v>9.800000000000001</v>
       </c>
       <c r="AH2">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AI2">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AJ2">
+        <v>12.5</v>
+      </c>
+      <c r="AK2">
+        <v>16.5</v>
+      </c>
+      <c r="AL2">
+        <v>40</v>
+      </c>
+      <c r="AM2">
+        <v>180</v>
+      </c>
+      <c r="AN2">
+        <v>8</v>
+      </c>
+      <c r="AO2">
+        <v>240</v>
+      </c>
+      <c r="AP2">
         <v>15</v>
       </c>
-      <c r="AK2">
-        <v>18</v>
-      </c>
-      <c r="AL2">
-        <v>42</v>
-      </c>
-      <c r="AM2">
-        <v>150</v>
-      </c>
-      <c r="AN2">
-        <v>10.5</v>
-      </c>
-      <c r="AO2">
-        <v>160</v>
-      </c>
-      <c r="AP2">
-        <v>13.5</v>
-      </c>
       <c r="AQ2">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AR2">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="AS2">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="AT2">
         <v>7.2</v>
       </c>
       <c r="AU2">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV2">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AW2">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="AX2">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AY2">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ2">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BA2">
         <v>75</v>
       </c>
       <c r="BB2">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="BC2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BD2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BE2">
         <v>90</v>
       </c>
       <c r="BF2">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="BG2">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="BH2">
+        <v>4.1</v>
+      </c>
+      <c r="BI2">
+        <v>3.35</v>
+      </c>
+      <c r="BJ2">
+        <v>14</v>
+      </c>
+      <c r="BK2">
+        <v>10</v>
+      </c>
+      <c r="BL2">
+        <v>200</v>
+      </c>
+      <c r="BM2">
+        <v>7.2</v>
+      </c>
+      <c r="BN2">
         <v>3.85</v>
       </c>
-      <c r="BI2">
-        <v>2.76</v>
-      </c>
-      <c r="BJ2">
-        <v>11.5</v>
-      </c>
-      <c r="BK2">
-        <v>5</v>
-      </c>
-      <c r="BL2">
-        <v>190</v>
-      </c>
-      <c r="BM2">
-        <v>8.6</v>
-      </c>
-      <c r="BN2">
-        <v>4</v>
-      </c>
       <c r="BO2">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="BP2">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="BQ2">
-        <v>4.8</v>
+        <v>8</v>
       </c>
       <c r="BR2">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BS2">
+        <v>6</v>
+      </c>
+      <c r="BT2">
+        <v>13.5</v>
+      </c>
+      <c r="BU2">
+        <v>10</v>
+      </c>
+      <c r="BV2">
+        <v>100</v>
+      </c>
+      <c r="BW2">
+        <v>7</v>
+      </c>
+      <c r="BX2">
+        <v>75</v>
+      </c>
+      <c r="BY2">
         <v>6.8</v>
       </c>
-      <c r="BT2">
-        <v>10.5</v>
-      </c>
-      <c r="BU2">
-        <v>4.8</v>
-      </c>
-      <c r="BV2">
-        <v>75</v>
-      </c>
-      <c r="BW2">
-        <v>7.8</v>
-      </c>
-      <c r="BX2">
-        <v>80</v>
-      </c>
-      <c r="BY2">
-        <v>8</v>
-      </c>
       <c r="BZ2">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="CA2">
-        <v>6.6</v>
+        <v>5.5</v>
       </c>
       <c r="CB2" t="s">
         <v>130</v>
@@ -1242,7 +1242,7 @@
         <v>115</v>
       </c>
       <c r="F3">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="G3">
         <v>1.84</v>
@@ -1254,16 +1254,16 @@
         <v>4.7</v>
       </c>
       <c r="J3">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K3">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L3">
         <v>1.3</v>
       </c>
       <c r="M3">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N3">
         <v>6.2</v>
@@ -1272,22 +1272,22 @@
         <v>1.18</v>
       </c>
       <c r="P3">
+        <v>2.74</v>
+      </c>
+      <c r="Q3">
+        <v>1.56</v>
+      </c>
+      <c r="R3">
+        <v>1.71</v>
+      </c>
+      <c r="S3">
+        <v>2.38</v>
+      </c>
+      <c r="T3">
+        <v>1.57</v>
+      </c>
+      <c r="U3">
         <v>2.68</v>
-      </c>
-      <c r="Q3">
-        <v>1.57</v>
-      </c>
-      <c r="R3">
-        <v>1.68</v>
-      </c>
-      <c r="S3">
-        <v>2.42</v>
-      </c>
-      <c r="T3">
-        <v>1.59</v>
-      </c>
-      <c r="U3">
-        <v>2.62</v>
       </c>
       <c r="V3">
         <v>1.27</v>
@@ -1296,22 +1296,22 @@
         <v>2.18</v>
       </c>
       <c r="X3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Y3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Z3">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AA3">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AB3">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AC3">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD3">
         <v>17.5</v>
@@ -1332,40 +1332,40 @@
         <v>44</v>
       </c>
       <c r="AJ3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK3">
         <v>16</v>
       </c>
       <c r="AL3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AM3">
         <v>60</v>
       </c>
       <c r="AN3">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AO3">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AP3">
         <v>24</v>
       </c>
       <c r="AQ3">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AR3">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AS3">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AT3">
         <v>12.5</v>
       </c>
       <c r="AU3">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AV3">
         <v>16.5</v>
@@ -1383,7 +1383,7 @@
         <v>14</v>
       </c>
       <c r="BA3">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BB3">
         <v>18.5</v>
@@ -1392,10 +1392,10 @@
         <v>15</v>
       </c>
       <c r="BD3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BE3">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="BF3">
         <v>7.2</v>
@@ -1407,7 +1407,7 @@
         <v>4.5</v>
       </c>
       <c r="BI3">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BJ3">
         <v>8.800000000000001</v>
@@ -1419,10 +1419,10 @@
         <v>90</v>
       </c>
       <c r="BM3">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BN3">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BO3">
         <v>4.5</v>
@@ -1431,37 +1431,37 @@
         <v>11.5</v>
       </c>
       <c r="BQ3">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR3">
         <v>20</v>
       </c>
       <c r="BS3">
+        <v>16.5</v>
+      </c>
+      <c r="BT3">
         <v>8.4</v>
       </c>
-      <c r="BT3">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BU3">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BV3">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="BW3">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX3">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BY3">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ3">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="CA3">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="CB3" t="s">
         <v>130</v>
@@ -1484,22 +1484,22 @@
         <v>116</v>
       </c>
       <c r="F4">
+        <v>2.54</v>
+      </c>
+      <c r="G4">
+        <v>2.64</v>
+      </c>
+      <c r="H4">
         <v>2.58</v>
       </c>
-      <c r="G4">
-        <v>2.7</v>
-      </c>
-      <c r="H4">
-        <v>2.56</v>
-      </c>
       <c r="I4">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="J4">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K4">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L4">
         <v>1.32</v>
@@ -1514,13 +1514,13 @@
         <v>1.2</v>
       </c>
       <c r="P4">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="Q4">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="R4">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="S4">
         <v>2.48</v>
@@ -1529,55 +1529,55 @@
         <v>1.55</v>
       </c>
       <c r="U4">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="V4">
+        <v>1.59</v>
+      </c>
+      <c r="W4">
         <v>1.6</v>
       </c>
-      <c r="W4">
-        <v>1.58</v>
-      </c>
       <c r="X4">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Y4">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z4">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA4">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AB4">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AC4">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD4">
         <v>13</v>
       </c>
       <c r="AE4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AF4">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG4">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH4">
         <v>15.5</v>
       </c>
       <c r="AI4">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AJ4">
         <v>40</v>
       </c>
       <c r="AK4">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL4">
         <v>30</v>
@@ -1586,13 +1586,13 @@
         <v>60</v>
       </c>
       <c r="AN4">
+        <v>16</v>
+      </c>
+      <c r="AO4">
         <v>16.5</v>
       </c>
-      <c r="AO4">
+      <c r="AP4">
         <v>19.5</v>
-      </c>
-      <c r="AP4">
-        <v>21</v>
       </c>
       <c r="AQ4">
         <v>14.5</v>
@@ -1601,13 +1601,13 @@
         <v>18.5</v>
       </c>
       <c r="AS4">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AT4">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AU4">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV4">
         <v>11.5</v>
@@ -1616,16 +1616,16 @@
         <v>21</v>
       </c>
       <c r="AX4">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AY4">
         <v>11</v>
       </c>
       <c r="AZ4">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BA4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BB4">
         <v>32</v>
@@ -1637,10 +1637,10 @@
         <v>26</v>
       </c>
       <c r="BE4">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BF4">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BG4">
         <v>13.5</v>
@@ -1661,16 +1661,16 @@
         <v>100</v>
       </c>
       <c r="BM4">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BN4">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BO4">
         <v>5.3</v>
       </c>
       <c r="BP4">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BQ4">
         <v>4.2</v>
@@ -1679,28 +1679,28 @@
         <v>32</v>
       </c>
       <c r="BS4">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BT4">
         <v>7.2</v>
       </c>
       <c r="BU4">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BV4">
         <v>21</v>
       </c>
       <c r="BW4">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BX4">
         <v>36</v>
       </c>
       <c r="BY4">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BZ4">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="CA4">
         <v>4.1</v>
@@ -1729,16 +1729,16 @@
         <v>1.22</v>
       </c>
       <c r="G5">
-        <v>1.97</v>
+        <v>1.51</v>
       </c>
       <c r="H5">
-        <v>2.1</v>
+        <v>5.4</v>
       </c>
       <c r="I5">
         <v>400</v>
       </c>
       <c r="J5">
-        <v>2.12</v>
+        <v>4.3</v>
       </c>
       <c r="K5">
         <v>60</v>
@@ -1774,10 +1774,10 @@
         <v>1.47</v>
       </c>
       <c r="V5">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W5">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="X5">
         <v>1000</v>
@@ -1828,64 +1828,64 @@
         <v>1000</v>
       </c>
       <c r="AN5">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AO5">
         <v>1000</v>
       </c>
       <c r="AP5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF5">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="BG5">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -1971,22 +1971,22 @@
         <v>3.8</v>
       </c>
       <c r="G6">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="H6">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="I6">
         <v>2.52</v>
       </c>
       <c r="J6">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="K6">
         <v>2.96</v>
       </c>
       <c r="L6">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="M6">
         <v>1.17</v>
@@ -1995,13 +1995,13 @@
         <v>2.24</v>
       </c>
       <c r="O6">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="P6">
         <v>1.4</v>
       </c>
       <c r="Q6">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="R6">
         <v>1.14</v>
@@ -2019,7 +2019,7 @@
         <v>1.65</v>
       </c>
       <c r="W6">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="X6">
         <v>6.6</v>
@@ -2043,7 +2043,7 @@
         <v>14.5</v>
       </c>
       <c r="AE6">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AF6">
         <v>24</v>
@@ -2064,7 +2064,7 @@
         <v>80</v>
       </c>
       <c r="AL6">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AM6">
         <v>300</v>
@@ -2073,7 +2073,7 @@
         <v>150</v>
       </c>
       <c r="AO6">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AP6">
         <v>6.2</v>
@@ -2088,7 +2088,7 @@
         <v>34</v>
       </c>
       <c r="AT6">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AU6">
         <v>7</v>
@@ -2097,7 +2097,7 @@
         <v>13.5</v>
       </c>
       <c r="AW6">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AX6">
         <v>21</v>
@@ -2106,7 +2106,7 @@
         <v>17.5</v>
       </c>
       <c r="AZ6">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BA6">
         <v>38</v>
@@ -2115,25 +2115,25 @@
         <v>80</v>
       </c>
       <c r="BC6">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="BD6">
         <v>42</v>
       </c>
       <c r="BE6">
-        <v>20</v>
+        <v>120</v>
       </c>
       <c r="BF6">
         <v>42</v>
       </c>
       <c r="BG6">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="BH6">
         <v>1000</v>
       </c>
       <c r="BI6">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="BJ6">
         <v>17</v>
@@ -2166,10 +2166,10 @@
         <v>21</v>
       </c>
       <c r="BT6">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BU6">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BV6">
         <v>32</v>
@@ -2210,16 +2210,16 @@
         <v>119</v>
       </c>
       <c r="F7">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="G7">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="H7">
         <v>1.33</v>
       </c>
       <c r="I7">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="J7">
         <v>5.3</v>
@@ -2228,22 +2228,22 @@
         <v>5.5</v>
       </c>
       <c r="L7">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="M7">
         <v>1.08</v>
       </c>
       <c r="N7">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O7">
         <v>1.4</v>
       </c>
       <c r="P7">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="Q7">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="R7">
         <v>1.28</v>
@@ -2258,16 +2258,16 @@
         <v>1.47</v>
       </c>
       <c r="V7">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="W7">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X7">
         <v>13</v>
       </c>
       <c r="Y7">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Z7">
         <v>5.9</v>
@@ -2276,7 +2276,7 @@
         <v>9.4</v>
       </c>
       <c r="AB7">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AC7">
         <v>12.5</v>
@@ -2285,7 +2285,7 @@
         <v>12</v>
       </c>
       <c r="AE7">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AF7">
         <v>170</v>
@@ -2306,13 +2306,13 @@
         <v>490</v>
       </c>
       <c r="AL7">
-        <v>470</v>
+        <v>430</v>
       </c>
       <c r="AM7">
-        <v>610</v>
+        <v>540</v>
       </c>
       <c r="AN7">
-        <v>1000</v>
+        <v>870</v>
       </c>
       <c r="AO7">
         <v>7.8</v>
@@ -2321,7 +2321,7 @@
         <v>12.5</v>
       </c>
       <c r="AQ7">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AR7">
         <v>5.7</v>
@@ -2342,10 +2342,10 @@
         <v>17</v>
       </c>
       <c r="AX7">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AY7">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AZ7">
         <v>48</v>
@@ -2354,22 +2354,22 @@
         <v>65</v>
       </c>
       <c r="BB7">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="BC7">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD7">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BE7">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BF7">
         <v>90</v>
       </c>
       <c r="BG7">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH7">
         <v>3.25</v>
@@ -2458,46 +2458,46 @@
         <v>2.56</v>
       </c>
       <c r="H8">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="I8">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="J8">
+        <v>3.85</v>
+      </c>
+      <c r="K8">
         <v>3.9</v>
       </c>
-      <c r="K8">
-        <v>3.95</v>
-      </c>
       <c r="L8">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="M8">
         <v>1.04</v>
       </c>
       <c r="N8">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O8">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P8">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="Q8">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="R8">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="S8">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="T8">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="U8">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="V8">
         <v>1.53</v>
@@ -2506,19 +2506,19 @@
         <v>1.64</v>
       </c>
       <c r="X8">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="Y8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Z8">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA8">
         <v>44</v>
       </c>
       <c r="AB8">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AC8">
         <v>9.6</v>
@@ -2527,10 +2527,10 @@
         <v>13.5</v>
       </c>
       <c r="AE8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AF8">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG8">
         <v>12.5</v>
@@ -2554,13 +2554,13 @@
         <v>46</v>
       </c>
       <c r="AN8">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AO8">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AP8">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ8">
         <v>18</v>
@@ -2569,10 +2569,10 @@
         <v>22</v>
       </c>
       <c r="AS8">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AT8">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AU8">
         <v>9.4</v>
@@ -2590,10 +2590,10 @@
         <v>11.5</v>
       </c>
       <c r="AZ8">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BA8">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB8">
         <v>34</v>
@@ -2608,70 +2608,70 @@
         <v>40</v>
       </c>
       <c r="BF8">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BG8">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BH8">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="BI8">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="BJ8">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BK8">
-        <v>7.2</v>
+        <v>5.9</v>
       </c>
       <c r="BL8">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BM8">
-        <v>14</v>
+        <v>2.1</v>
       </c>
       <c r="BN8">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="BO8">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="BP8">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>12</v>
+        <v>2.18</v>
       </c>
       <c r="BR8">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BS8">
-        <v>10</v>
+        <v>2.18</v>
       </c>
       <c r="BT8">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BU8">
-        <v>5.9</v>
+        <v>5</v>
       </c>
       <c r="BV8">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="BW8">
-        <v>14</v>
+        <v>2.18</v>
       </c>
       <c r="BX8">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BY8">
-        <v>10.5</v>
+        <v>2.18</v>
       </c>
       <c r="BZ8">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="CA8">
-        <v>8.199999999999999</v>
+        <v>2.18</v>
       </c>
       <c r="CB8" t="s">
         <v>130</v>
@@ -2694,79 +2694,79 @@
         <v>121</v>
       </c>
       <c r="F9">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="G9">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="H9">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I9">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J9">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K9">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L9">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="M9">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N9">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="O9">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="P9">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="Q9">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="R9">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="S9">
-        <v>2.72</v>
+        <v>2.54</v>
       </c>
       <c r="T9">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="U9">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="V9">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W9">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="X9">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="Y9">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Z9">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AA9">
         <v>100</v>
       </c>
       <c r="AB9">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AC9">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD9">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AE9">
         <v>55</v>
@@ -2775,52 +2775,52 @@
         <v>12.5</v>
       </c>
       <c r="AG9">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH9">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI9">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AJ9">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AK9">
         <v>17</v>
       </c>
       <c r="AL9">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AM9">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AN9">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO9">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AP9">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AQ9">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AR9">
         <v>34</v>
       </c>
       <c r="AS9">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="AT9">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AU9">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AV9">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AW9">
         <v>46</v>
@@ -2829,91 +2829,91 @@
         <v>11.5</v>
       </c>
       <c r="AY9">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA9">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="BB9">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BC9">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BD9">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="BE9">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="BF9">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="BG9">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="BH9">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="BI9">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="BJ9">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK9">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL9">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="BM9">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BN9">
         <v>4.7</v>
       </c>
       <c r="BO9">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BP9">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BQ9">
         <v>10</v>
       </c>
       <c r="BR9">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BS9">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BT9">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BU9">
         <v>7.4</v>
       </c>
       <c r="BV9">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BW9">
+        <v>10.5</v>
+      </c>
+      <c r="BX9">
+        <v>40</v>
+      </c>
+      <c r="BY9">
+        <v>10.5</v>
+      </c>
+      <c r="BZ9">
+        <v>16.5</v>
+      </c>
+      <c r="CA9">
         <v>11</v>
-      </c>
-      <c r="BX9">
-        <v>42</v>
-      </c>
-      <c r="BY9">
-        <v>11</v>
-      </c>
-      <c r="BZ9">
-        <v>18</v>
-      </c>
-      <c r="CA9">
-        <v>8.6</v>
       </c>
       <c r="CB9" t="s">
         <v>130</v>
@@ -2954,10 +2954,10 @@
         <v>3.3</v>
       </c>
       <c r="L10">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="M10">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N10">
         <v>3</v>
@@ -2966,7 +2966,7 @@
         <v>1.46</v>
       </c>
       <c r="P10">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="Q10">
         <v>2.4</v>
@@ -2981,7 +2981,7 @@
         <v>2.02</v>
       </c>
       <c r="U10">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="V10">
         <v>1.42</v>
@@ -2999,7 +2999,7 @@
         <v>21</v>
       </c>
       <c r="AA10">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB10">
         <v>8.6</v>
@@ -3044,7 +3044,7 @@
         <v>55</v>
       </c>
       <c r="AP10">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AQ10">
         <v>9.800000000000001</v>
@@ -3074,7 +3074,7 @@
         <v>11.5</v>
       </c>
       <c r="AZ10">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BA10">
         <v>55</v>
@@ -3089,73 +3089,73 @@
         <v>48</v>
       </c>
       <c r="BE10">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BF10">
         <v>27</v>
       </c>
       <c r="BG10">
-        <v>44</v>
+        <v>12.5</v>
       </c>
       <c r="BH10">
-        <v>2.86</v>
+        <v>3.1</v>
       </c>
       <c r="BI10">
-        <v>2.66</v>
+        <v>2.46</v>
       </c>
       <c r="BJ10">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK10">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>16.5</v>
+        <v>2.88</v>
       </c>
       <c r="BN10">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="BO10">
+        <v>4.5</v>
+      </c>
+      <c r="BP10">
+        <v>1000</v>
+      </c>
+      <c r="BQ10">
+        <v>2.88</v>
+      </c>
+      <c r="BR10">
+        <v>1000</v>
+      </c>
+      <c r="BS10">
+        <v>2.88</v>
+      </c>
+      <c r="BT10">
+        <v>1000</v>
+      </c>
+      <c r="BU10">
         <v>4.9</v>
       </c>
-      <c r="BP10">
-        <v>22</v>
-      </c>
-      <c r="BQ10">
-        <v>14.5</v>
-      </c>
-      <c r="BR10">
-        <v>40</v>
-      </c>
-      <c r="BS10">
-        <v>12.5</v>
-      </c>
-      <c r="BT10">
-        <v>6.4</v>
-      </c>
-      <c r="BU10">
-        <v>5.7</v>
-      </c>
       <c r="BV10">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BW10">
+        <v>2.88</v>
+      </c>
+      <c r="BX10">
+        <v>1000</v>
+      </c>
+      <c r="BY10">
+        <v>11.5</v>
+      </c>
+      <c r="BZ10">
+        <v>1000</v>
+      </c>
+      <c r="CA10">
         <v>11</v>
-      </c>
-      <c r="BX10">
-        <v>48</v>
-      </c>
-      <c r="BY10">
-        <v>13</v>
-      </c>
-      <c r="BZ10">
-        <v>40</v>
-      </c>
-      <c r="CA10">
-        <v>12.5</v>
       </c>
       <c r="CB10" t="s">
         <v>130</v>
@@ -3187,13 +3187,13 @@
         <v>7.6</v>
       </c>
       <c r="I11">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J11">
+        <v>5.2</v>
+      </c>
+      <c r="K11">
         <v>5.3</v>
-      </c>
-      <c r="K11">
-        <v>5.4</v>
       </c>
       <c r="L11">
         <v>1.28</v>
@@ -3202,28 +3202,28 @@
         <v>1.03</v>
       </c>
       <c r="N11">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="O11">
         <v>1.18</v>
       </c>
       <c r="P11">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="Q11">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="R11">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="S11">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="T11">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="U11">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="V11">
         <v>1.14</v>
@@ -3232,25 +3232,25 @@
         <v>3.1</v>
       </c>
       <c r="X11">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Y11">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Z11">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AA11">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="AB11">
         <v>12</v>
       </c>
       <c r="AC11">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD11">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AE11">
         <v>120</v>
@@ -3259,85 +3259,85 @@
         <v>10.5</v>
       </c>
       <c r="AG11">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH11">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI11">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AJ11">
         <v>13.5</v>
       </c>
       <c r="AK11">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AL11">
         <v>28</v>
       </c>
       <c r="AM11">
-        <v>90</v>
+        <v>320</v>
       </c>
       <c r="AN11">
         <v>5.1</v>
       </c>
       <c r="AO11">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AP11">
         <v>24</v>
       </c>
       <c r="AQ11">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AR11">
         <v>60</v>
       </c>
       <c r="AS11">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AT11">
         <v>11</v>
       </c>
       <c r="AU11">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AV11">
         <v>24</v>
       </c>
       <c r="AW11">
-        <v>14</v>
+        <v>80</v>
       </c>
       <c r="AX11">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AY11">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ11">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BA11">
         <v>65</v>
       </c>
       <c r="BB11">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BC11">
         <v>12.5</v>
       </c>
       <c r="BD11">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BE11">
         <v>75</v>
       </c>
       <c r="BF11">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="BG11">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="BH11">
         <v>4.6</v>
@@ -3355,7 +3355,7 @@
         <v>120</v>
       </c>
       <c r="BM11">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BN11">
         <v>4.3</v>
@@ -3364,7 +3364,7 @@
         <v>3.9</v>
       </c>
       <c r="BP11">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BQ11">
         <v>7.4</v>
@@ -3373,31 +3373,31 @@
         <v>24</v>
       </c>
       <c r="BS11">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BT11">
         <v>13.5</v>
       </c>
       <c r="BU11">
-        <v>5.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BV11">
         <v>70</v>
       </c>
       <c r="BW11">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BX11">
         <v>65</v>
       </c>
       <c r="BY11">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BZ11">
         <v>13.5</v>
       </c>
       <c r="CA11">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="CB11" t="s">
         <v>130</v>
@@ -3435,7 +3435,7 @@
         <v>3.4</v>
       </c>
       <c r="K12">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L12">
         <v>1.48</v>
@@ -3450,7 +3450,7 @@
         <v>1.41</v>
       </c>
       <c r="P12">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="Q12">
         <v>2.24</v>
@@ -3462,7 +3462,7 @@
         <v>4.2</v>
       </c>
       <c r="T12">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="U12">
         <v>2.02</v>
@@ -3477,13 +3477,13 @@
         <v>12</v>
       </c>
       <c r="Y12">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="Z12">
         <v>17</v>
       </c>
       <c r="AA12">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AB12">
         <v>9.800000000000001</v>
@@ -3561,7 +3561,7 @@
         <v>18</v>
       </c>
       <c r="BA12">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BB12">
         <v>40</v>
@@ -3570,25 +3570,25 @@
         <v>30</v>
       </c>
       <c r="BD12">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BE12">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="BF12">
         <v>30</v>
       </c>
       <c r="BG12">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BH12">
         <v>3.05</v>
       </c>
       <c r="BI12">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="BJ12">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BK12">
         <v>8.800000000000001</v>
@@ -3597,7 +3597,7 @@
         <v>160</v>
       </c>
       <c r="BM12">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BN12">
         <v>5.8</v>
@@ -3609,13 +3609,13 @@
         <v>27</v>
       </c>
       <c r="BQ12">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR12">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BS12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BT12">
         <v>5.7</v>
@@ -3627,19 +3627,19 @@
         <v>24</v>
       </c>
       <c r="BW12">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX12">
         <v>44</v>
       </c>
       <c r="BY12">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BZ12">
         <v>40</v>
       </c>
       <c r="CA12">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="CB12" t="s">
         <v>130</v>
@@ -3662,13 +3662,13 @@
         <v>125</v>
       </c>
       <c r="F13">
+        <v>1.22</v>
+      </c>
+      <c r="G13">
         <v>1.23</v>
       </c>
-      <c r="G13">
-        <v>1.24</v>
-      </c>
       <c r="H13">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="I13">
         <v>18.5</v>
@@ -3692,19 +3692,19 @@
         <v>1.19</v>
       </c>
       <c r="P13">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="Q13">
         <v>1.58</v>
       </c>
       <c r="R13">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="S13">
         <v>2.44</v>
       </c>
       <c r="T13">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="U13">
         <v>1.7</v>
@@ -3716,13 +3716,13 @@
         <v>5.3</v>
       </c>
       <c r="X13">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Y13">
         <v>50</v>
       </c>
       <c r="Z13">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AA13">
         <v>1000</v>
@@ -3737,10 +3737,10 @@
         <v>60</v>
       </c>
       <c r="AE13">
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="AF13">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AG13">
         <v>12</v>
@@ -3749,10 +3749,10 @@
         <v>44</v>
       </c>
       <c r="AI13">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="AJ13">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AK13">
         <v>14.5</v>
@@ -3776,13 +3776,13 @@
         <v>46</v>
       </c>
       <c r="AR13">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AS13">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="AT13">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AU13">
         <v>16</v>
@@ -3791,7 +3791,7 @@
         <v>50</v>
       </c>
       <c r="AW13">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AX13">
         <v>7</v>
@@ -3803,10 +3803,10 @@
         <v>38</v>
       </c>
       <c r="BA13">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="BB13">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC13">
         <v>13.5</v>
@@ -3815,16 +3815,16 @@
         <v>44</v>
       </c>
       <c r="BE13">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BF13">
         <v>3.65</v>
       </c>
       <c r="BG13">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="BH13">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BI13">
         <v>3.65</v>
@@ -3842,7 +3842,7 @@
         <v>23</v>
       </c>
       <c r="BN13">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BO13">
         <v>3.1</v>
@@ -3851,7 +3851,7 @@
         <v>1000</v>
       </c>
       <c r="BQ13">
-        <v>1.77</v>
+        <v>4.9</v>
       </c>
       <c r="BR13">
         <v>1000</v>
@@ -3904,7 +3904,7 @@
         <v>126</v>
       </c>
       <c r="F14">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="G14">
         <v>3.05</v>
@@ -3913,10 +3913,10 @@
         <v>2.64</v>
       </c>
       <c r="I14">
-        <v>2.98</v>
+        <v>2.82</v>
       </c>
       <c r="J14">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K14">
         <v>3.55</v>
@@ -3928,7 +3928,7 @@
         <v>1.08</v>
       </c>
       <c r="N14">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="O14">
         <v>1.36</v>
@@ -3937,22 +3937,22 @@
         <v>1.79</v>
       </c>
       <c r="Q14">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R14">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S14">
         <v>3.75</v>
       </c>
       <c r="T14">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="U14">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="V14">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="W14">
         <v>1.48</v>
@@ -3979,7 +3979,7 @@
         <v>13</v>
       </c>
       <c r="AE14">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AF14">
         <v>20</v>
@@ -4006,13 +4006,13 @@
         <v>120</v>
       </c>
       <c r="AN14">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AO14">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AP14">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ14">
         <v>8.800000000000001</v>
@@ -4027,13 +4027,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AU14">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV14">
         <v>10.5</v>
       </c>
       <c r="AW14">
-        <v>18.5</v>
+        <v>14.5</v>
       </c>
       <c r="AX14">
         <v>16</v>
@@ -4045,25 +4045,25 @@
         <v>15</v>
       </c>
       <c r="BA14">
-        <v>24</v>
+        <v>6.4</v>
       </c>
       <c r="BB14">
         <v>24</v>
       </c>
       <c r="BC14">
-        <v>19</v>
+        <v>14.5</v>
       </c>
       <c r="BD14">
         <v>26</v>
       </c>
       <c r="BE14">
-        <v>1.03</v>
+        <v>28</v>
       </c>
       <c r="BF14">
-        <v>18.5</v>
+        <v>6.2</v>
       </c>
       <c r="BG14">
-        <v>22</v>
+        <v>6.2</v>
       </c>
       <c r="BH14">
         <v>1000</v>
@@ -4146,19 +4146,19 @@
         <v>127</v>
       </c>
       <c r="F15">
-        <v>1.1</v>
+        <v>1.55</v>
       </c>
       <c r="G15">
         <v>110</v>
       </c>
       <c r="H15">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="I15">
-        <v>880</v>
+        <v>110</v>
       </c>
       <c r="J15">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="K15">
         <v>950</v>
@@ -4173,7 +4173,7 @@
         <v>1.09</v>
       </c>
       <c r="O15">
-        <v>1.02</v>
+        <v>1.45</v>
       </c>
       <c r="P15">
         <v>1.09</v>
@@ -4185,7 +4185,7 @@
         <v>1.08</v>
       </c>
       <c r="S15">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="T15">
         <v>1.01</v>
@@ -4194,112 +4194,112 @@
         <v>1.01</v>
       </c>
       <c r="V15">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W15">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X15">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Y15">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z15">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA15">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB15">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC15">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AD15">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE15">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF15">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG15">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH15">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI15">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ15">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK15">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL15">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM15">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN15">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO15">
         <v>1000</v>
       </c>
       <c r="AP15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF15">
         <v>1.01</v>
@@ -4388,31 +4388,31 @@
         <v>128</v>
       </c>
       <c r="F16">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="G16">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="H16">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="I16">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="J16">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="K16">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="L16">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="M16">
         <v>1.15</v>
       </c>
       <c r="N16">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="O16">
         <v>1.63</v>
@@ -4421,7 +4421,7 @@
         <v>1.41</v>
       </c>
       <c r="Q16">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="R16">
         <v>1.14</v>
@@ -4436,13 +4436,13 @@
         <v>1.64</v>
       </c>
       <c r="V16">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="W16">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="X16">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="Y16">
         <v>7.4</v>
@@ -4463,10 +4463,10 @@
         <v>14</v>
       </c>
       <c r="AE16">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF16">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AG16">
         <v>18.5</v>
@@ -4475,91 +4475,91 @@
         <v>29</v>
       </c>
       <c r="AI16">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AJ16">
         <v>110</v>
       </c>
       <c r="AK16">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AL16">
         <v>130</v>
       </c>
       <c r="AM16">
-        <v>310</v>
+        <v>500</v>
       </c>
       <c r="AN16">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AO16">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP16">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AQ16">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="AR16">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AS16">
-        <v>6.4</v>
+        <v>17.5</v>
       </c>
       <c r="AT16">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AU16">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="AV16">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AW16">
-        <v>6.4</v>
+        <v>17.5</v>
       </c>
       <c r="AX16">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AY16">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AZ16">
-        <v>19.5</v>
+        <v>6.6</v>
       </c>
       <c r="BA16">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BB16">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BC16">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BD16">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE16">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BF16">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG16">
-        <v>32</v>
+        <v>7.4</v>
       </c>
       <c r="BH16">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="BI16">
-        <v>2.24</v>
+        <v>2.08</v>
       </c>
       <c r="BJ16">
         <v>13</v>
       </c>
       <c r="BK16">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BL16">
         <v>1000</v>
@@ -4577,10 +4577,10 @@
         <v>42</v>
       </c>
       <c r="BQ16">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BR16">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="BS16">
         <v>9.4</v>
@@ -4598,7 +4598,7 @@
         <v>7.4</v>
       </c>
       <c r="BX16">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY16">
         <v>9</v>
@@ -4657,7 +4657,7 @@
         <v>1.09</v>
       </c>
       <c r="O17">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P17">
         <v>1.09</v>
@@ -4669,7 +4669,7 @@
         <v>1.08</v>
       </c>
       <c r="S17">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="T17">
         <v>1.01</v>
@@ -4738,52 +4738,52 @@
         <v>1000</v>
       </c>
       <c r="AP17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF17">
         <v>1.01</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-24.xlsx
@@ -406,7 +406,7 @@
     <t>Vinotinto Ecuador</t>
   </si>
   <si>
-    <t>2026-09-23 18:58:20</t>
+    <t>2026-09-23 21:10:53</t>
   </si>
 </sst>
 </file>
@@ -1000,139 +1000,139 @@
         <v>114</v>
       </c>
       <c r="F2">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="G2">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="H2">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="I2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J2">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="K2">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L2">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="M2">
         <v>1.06</v>
       </c>
       <c r="N2">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O2">
         <v>1.3</v>
       </c>
       <c r="P2">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q2">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R2">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S2">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="T2">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="U2">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="V2">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="W2">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="X2">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Y2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Z2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AA2">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="AB2">
         <v>7.8</v>
       </c>
       <c r="AC2">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD2">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AE2">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="AF2">
+        <v>8.6</v>
+      </c>
+      <c r="AG2">
+        <v>9.6</v>
+      </c>
+      <c r="AH2">
+        <v>25</v>
+      </c>
+      <c r="AI2">
+        <v>110</v>
+      </c>
+      <c r="AJ2">
+        <v>13</v>
+      </c>
+      <c r="AK2">
+        <v>15.5</v>
+      </c>
+      <c r="AL2">
+        <v>38</v>
+      </c>
+      <c r="AM2">
+        <v>170</v>
+      </c>
+      <c r="AN2">
         <v>8.199999999999999</v>
       </c>
-      <c r="AG2">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AH2">
-        <v>27</v>
-      </c>
-      <c r="AI2">
-        <v>130</v>
-      </c>
-      <c r="AJ2">
-        <v>12.5</v>
-      </c>
-      <c r="AK2">
-        <v>16.5</v>
-      </c>
-      <c r="AL2">
-        <v>40</v>
-      </c>
-      <c r="AM2">
-        <v>180</v>
-      </c>
-      <c r="AN2">
-        <v>8</v>
-      </c>
       <c r="AO2">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="AP2">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AQ2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR2">
         <v>60</v>
       </c>
       <c r="AS2">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="AT2">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU2">
         <v>9.800000000000001</v>
       </c>
       <c r="AV2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AW2">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AX2">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY2">
         <v>9.199999999999999</v>
@@ -1141,85 +1141,85 @@
         <v>24</v>
       </c>
       <c r="BA2">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="BB2">
+        <v>12</v>
+      </c>
+      <c r="BC2">
+        <v>14.5</v>
+      </c>
+      <c r="BD2">
+        <v>32</v>
+      </c>
+      <c r="BE2">
+        <v>110</v>
+      </c>
+      <c r="BF2">
+        <v>7.8</v>
+      </c>
+      <c r="BG2">
+        <v>120</v>
+      </c>
+      <c r="BH2">
+        <v>3.65</v>
+      </c>
+      <c r="BI2">
+        <v>3.4</v>
+      </c>
+      <c r="BJ2">
         <v>11</v>
       </c>
-      <c r="BC2">
-        <v>14</v>
-      </c>
-      <c r="BD2">
-        <v>36</v>
-      </c>
-      <c r="BE2">
-        <v>90</v>
-      </c>
-      <c r="BF2">
-        <v>7.2</v>
-      </c>
-      <c r="BG2">
+      <c r="BK2">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BL2">
+        <v>180</v>
+      </c>
+      <c r="BM2">
         <v>130</v>
       </c>
-      <c r="BH2">
-        <v>4.1</v>
-      </c>
-      <c r="BI2">
-        <v>3.35</v>
-      </c>
-      <c r="BJ2">
-        <v>14</v>
-      </c>
-      <c r="BK2">
-        <v>10</v>
-      </c>
-      <c r="BL2">
-        <v>200</v>
-      </c>
-      <c r="BM2">
-        <v>7.2</v>
-      </c>
       <c r="BN2">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BO2">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="BP2">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BQ2">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BR2">
         <v>32</v>
       </c>
       <c r="BS2">
-        <v>6</v>
+        <v>15.5</v>
       </c>
       <c r="BT2">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="BU2">
+        <v>9.6</v>
+      </c>
+      <c r="BV2">
+        <v>70</v>
+      </c>
+      <c r="BW2">
+        <v>14</v>
+      </c>
+      <c r="BX2">
+        <v>70</v>
+      </c>
+      <c r="BY2">
+        <v>13</v>
+      </c>
+      <c r="BZ2">
+        <v>16.5</v>
+      </c>
+      <c r="CA2">
         <v>10</v>
-      </c>
-      <c r="BV2">
-        <v>100</v>
-      </c>
-      <c r="BW2">
-        <v>7</v>
-      </c>
-      <c r="BX2">
-        <v>75</v>
-      </c>
-      <c r="BY2">
-        <v>6.8</v>
-      </c>
-      <c r="BZ2">
-        <v>20</v>
-      </c>
-      <c r="CA2">
-        <v>5.5</v>
       </c>
       <c r="CB2" t="s">
         <v>130</v>
@@ -1242,10 +1242,10 @@
         <v>115</v>
       </c>
       <c r="F3">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="G3">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="H3">
         <v>4.5</v>
@@ -1257,25 +1257,25 @@
         <v>4.1</v>
       </c>
       <c r="K3">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L3">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="M3">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N3">
         <v>6.2</v>
       </c>
       <c r="O3">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P3">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="Q3">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="R3">
         <v>1.71</v>
@@ -1287,19 +1287,19 @@
         <v>1.57</v>
       </c>
       <c r="U3">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="V3">
         <v>1.27</v>
       </c>
       <c r="W3">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="X3">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Y3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Z3">
         <v>40</v>
@@ -1314,10 +1314,10 @@
         <v>10</v>
       </c>
       <c r="AD3">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AE3">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF3">
         <v>14</v>
@@ -1341,16 +1341,16 @@
         <v>24</v>
       </c>
       <c r="AM3">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AN3">
         <v>7.6</v>
       </c>
       <c r="AO3">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AP3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AQ3">
         <v>23</v>
@@ -1359,13 +1359,13 @@
         <v>36</v>
       </c>
       <c r="AS3">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AT3">
         <v>12.5</v>
       </c>
       <c r="AU3">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AV3">
         <v>16.5</v>
@@ -1383,19 +1383,19 @@
         <v>14</v>
       </c>
       <c r="BA3">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BB3">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BC3">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BD3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BE3">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="BF3">
         <v>7.2</v>
@@ -1410,7 +1410,7 @@
         <v>4.1</v>
       </c>
       <c r="BJ3">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BK3">
         <v>7.8</v>
@@ -1419,7 +1419,7 @@
         <v>90</v>
       </c>
       <c r="BM3">
-        <v>11</v>
+        <v>60</v>
       </c>
       <c r="BN3">
         <v>4.9</v>
@@ -1431,7 +1431,7 @@
         <v>11.5</v>
       </c>
       <c r="BQ3">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BR3">
         <v>20</v>
@@ -1440,28 +1440,28 @@
         <v>16.5</v>
       </c>
       <c r="BT3">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU3">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BV3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BW3">
-        <v>9.199999999999999</v>
+        <v>16</v>
       </c>
       <c r="BX3">
         <v>42</v>
       </c>
       <c r="BY3">
-        <v>9.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="BZ3">
-        <v>16.5</v>
+        <v>13</v>
       </c>
       <c r="CA3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CB3" t="s">
         <v>130</v>
@@ -1484,148 +1484,148 @@
         <v>116</v>
       </c>
       <c r="F4">
+        <v>2.5</v>
+      </c>
+      <c r="G4">
         <v>2.54</v>
       </c>
-      <c r="G4">
-        <v>2.64</v>
-      </c>
       <c r="H4">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="I4">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="J4">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="K4">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="L4">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="M4">
         <v>1.04</v>
       </c>
       <c r="N4">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="O4">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P4">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="Q4">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="R4">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="S4">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="T4">
         <v>1.55</v>
       </c>
       <c r="U4">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="V4">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="W4">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="X4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Y4">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Z4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA4">
         <v>42</v>
       </c>
       <c r="AB4">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AC4">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD4">
         <v>13</v>
       </c>
       <c r="AE4">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF4">
         <v>21</v>
       </c>
       <c r="AG4">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH4">
         <v>15.5</v>
       </c>
       <c r="AI4">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AJ4">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AK4">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL4">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AM4">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AN4">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AO4">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AP4">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AQ4">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AR4">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AS4">
         <v>34</v>
       </c>
       <c r="AT4">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AU4">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV4">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AW4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX4">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AY4">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ4">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA4">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BB4">
         <v>32</v>
@@ -1634,76 +1634,76 @@
         <v>21</v>
       </c>
       <c r="BD4">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BE4">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="BF4">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BG4">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BH4">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BI4">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="BJ4">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK4">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BL4">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="BM4">
-        <v>5.1</v>
+        <v>60</v>
       </c>
       <c r="BN4">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BO4">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BP4">
         <v>22</v>
       </c>
       <c r="BQ4">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BR4">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BS4">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BT4">
         <v>7.2</v>
       </c>
       <c r="BU4">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BV4">
         <v>21</v>
       </c>
       <c r="BW4">
+        <v>4.3</v>
+      </c>
+      <c r="BX4">
+        <v>34</v>
+      </c>
+      <c r="BY4">
+        <v>5.3</v>
+      </c>
+      <c r="BZ4">
+        <v>18.5</v>
+      </c>
+      <c r="CA4">
         <v>4.2</v>
-      </c>
-      <c r="BX4">
-        <v>36</v>
-      </c>
-      <c r="BY4">
-        <v>5.2</v>
-      </c>
-      <c r="BZ4">
-        <v>19.5</v>
-      </c>
-      <c r="CA4">
-        <v>4.1</v>
       </c>
       <c r="CB4" t="s">
         <v>130</v>
@@ -1777,7 +1777,7 @@
         <v>1.03</v>
       </c>
       <c r="W5">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="X5">
         <v>1000</v>
@@ -1828,7 +1828,7 @@
         <v>1000</v>
       </c>
       <c r="AN5">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="AO5">
         <v>1000</v>
@@ -1837,13 +1837,13 @@
         <v>1.01</v>
       </c>
       <c r="AQ5">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="AR5">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="AS5">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="AT5">
         <v>1.01</v>
@@ -1852,10 +1852,10 @@
         <v>1.01</v>
       </c>
       <c r="AV5">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="AW5">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="AX5">
         <v>1.01</v>
@@ -1867,7 +1867,7 @@
         <v>1.01</v>
       </c>
       <c r="BA5">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="BB5">
         <v>1.01</v>
@@ -1885,7 +1885,7 @@
         <v>1.95</v>
       </c>
       <c r="BG5">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -1974,13 +1974,13 @@
         <v>3.9</v>
       </c>
       <c r="H6">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="I6">
         <v>2.52</v>
       </c>
       <c r="J6">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="K6">
         <v>2.96</v>
@@ -1992,10 +1992,10 @@
         <v>1.17</v>
       </c>
       <c r="N6">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="O6">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="P6">
         <v>1.4</v>
@@ -2010,7 +2010,7 @@
         <v>7.8</v>
       </c>
       <c r="T6">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="U6">
         <v>1.6</v>
@@ -2043,7 +2043,7 @@
         <v>14.5</v>
       </c>
       <c r="AE6">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AF6">
         <v>24</v>
@@ -2064,10 +2064,10 @@
         <v>80</v>
       </c>
       <c r="AL6">
-        <v>1000</v>
+        <v>530</v>
       </c>
       <c r="AM6">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="AN6">
         <v>150</v>
@@ -2076,7 +2076,7 @@
         <v>50</v>
       </c>
       <c r="AP6">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AQ6">
         <v>6.2</v>
@@ -2109,7 +2109,7 @@
         <v>29</v>
       </c>
       <c r="BA6">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="BB6">
         <v>80</v>
@@ -2121,13 +2121,13 @@
         <v>42</v>
       </c>
       <c r="BE6">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="BF6">
         <v>42</v>
       </c>
       <c r="BG6">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -2213,7 +2213,7 @@
         <v>13.5</v>
       </c>
       <c r="G7">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="H7">
         <v>1.33</v>
@@ -2234,16 +2234,16 @@
         <v>1.08</v>
       </c>
       <c r="N7">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O7">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P7">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="Q7">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="R7">
         <v>1.28</v>
@@ -2252,10 +2252,10 @@
         <v>4.2</v>
       </c>
       <c r="T7">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="U7">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="V7">
         <v>3.8</v>
@@ -2264,7 +2264,7 @@
         <v>1.07</v>
       </c>
       <c r="X7">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y7">
         <v>5.8</v>
@@ -2273,7 +2273,7 @@
         <v>5.9</v>
       </c>
       <c r="AA7">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AB7">
         <v>32</v>
@@ -2291,7 +2291,7 @@
         <v>170</v>
       </c>
       <c r="AG7">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AH7">
         <v>60</v>
@@ -2312,13 +2312,13 @@
         <v>540</v>
       </c>
       <c r="AN7">
-        <v>870</v>
+        <v>850</v>
       </c>
       <c r="AO7">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AP7">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AQ7">
         <v>5.6</v>
@@ -2327,7 +2327,7 @@
         <v>5.7</v>
       </c>
       <c r="AS7">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT7">
         <v>26</v>
@@ -2342,7 +2342,7 @@
         <v>17</v>
       </c>
       <c r="AX7">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AY7">
         <v>50</v>
@@ -2354,16 +2354,16 @@
         <v>65</v>
       </c>
       <c r="BB7">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BC7">
+        <v>21</v>
+      </c>
+      <c r="BD7">
         <v>20</v>
       </c>
-      <c r="BD7">
-        <v>17</v>
-      </c>
       <c r="BE7">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BF7">
         <v>90</v>
@@ -2381,7 +2381,7 @@
         <v>16.5</v>
       </c>
       <c r="BK7">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BL7">
         <v>1000</v>
@@ -2393,7 +2393,7 @@
         <v>25</v>
       </c>
       <c r="BO7">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="BP7">
         <v>1000</v>
@@ -2414,22 +2414,22 @@
         <v>3.05</v>
       </c>
       <c r="BV7">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BW7">
         <v>7</v>
       </c>
       <c r="BX7">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BY7">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BZ7">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="CA7">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="CB7" t="s">
         <v>130</v>
@@ -2470,25 +2470,25 @@
         <v>3.9</v>
       </c>
       <c r="L8">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="M8">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N8">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="O8">
         <v>1.16</v>
       </c>
       <c r="P8">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="Q8">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="R8">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="S8">
         <v>2.2</v>
@@ -2497,7 +2497,7 @@
         <v>1.46</v>
       </c>
       <c r="U8">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="V8">
         <v>1.53</v>
@@ -2518,7 +2518,7 @@
         <v>44</v>
       </c>
       <c r="AB8">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AC8">
         <v>9.6</v>
@@ -2527,7 +2527,7 @@
         <v>13.5</v>
       </c>
       <c r="AE8">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF8">
         <v>22</v>
@@ -2536,7 +2536,7 @@
         <v>12.5</v>
       </c>
       <c r="AH8">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AI8">
         <v>28</v>
@@ -2560,22 +2560,22 @@
         <v>14</v>
       </c>
       <c r="AP8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ8">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR8">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AS8">
         <v>38</v>
       </c>
       <c r="AT8">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AU8">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV8">
         <v>13</v>
@@ -2584,7 +2584,7 @@
         <v>23</v>
       </c>
       <c r="AX8">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AY8">
         <v>11.5</v>
@@ -2608,70 +2608,70 @@
         <v>40</v>
       </c>
       <c r="BF8">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BG8">
         <v>12.5</v>
       </c>
       <c r="BH8">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="BI8">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="BJ8">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BK8">
+        <v>7.2</v>
+      </c>
+      <c r="BL8">
+        <v>65</v>
+      </c>
+      <c r="BM8">
+        <v>12</v>
+      </c>
+      <c r="BN8">
+        <v>6</v>
+      </c>
+      <c r="BO8">
+        <v>5.5</v>
+      </c>
+      <c r="BP8">
+        <v>16.5</v>
+      </c>
+      <c r="BQ8">
+        <v>8.4</v>
+      </c>
+      <c r="BR8">
+        <v>23</v>
+      </c>
+      <c r="BS8">
+        <v>9.6</v>
+      </c>
+      <c r="BT8">
+        <v>6.4</v>
+      </c>
+      <c r="BU8">
         <v>5.9</v>
       </c>
-      <c r="BL8">
-        <v>1000</v>
-      </c>
-      <c r="BM8">
-        <v>2.1</v>
-      </c>
-      <c r="BN8">
-        <v>1000</v>
-      </c>
-      <c r="BO8">
-        <v>4.8</v>
-      </c>
-      <c r="BP8">
-        <v>1000</v>
-      </c>
-      <c r="BQ8">
-        <v>2.18</v>
-      </c>
-      <c r="BR8">
-        <v>1000</v>
-      </c>
-      <c r="BS8">
-        <v>2.18</v>
-      </c>
-      <c r="BT8">
-        <v>1000</v>
-      </c>
-      <c r="BU8">
-        <v>5</v>
-      </c>
       <c r="BV8">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BW8">
-        <v>2.18</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX8">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BY8">
-        <v>2.18</v>
+        <v>10</v>
       </c>
       <c r="BZ8">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="CA8">
-        <v>2.18</v>
+        <v>7.6</v>
       </c>
       <c r="CB8" t="s">
         <v>130</v>
@@ -2697,7 +2697,7 @@
         <v>1.79</v>
       </c>
       <c r="G9">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="H9">
         <v>4.7</v>
@@ -2712,46 +2712,46 @@
         <v>4.3</v>
       </c>
       <c r="L9">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="M9">
         <v>1.04</v>
       </c>
       <c r="N9">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="O9">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P9">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="Q9">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="R9">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="S9">
         <v>2.54</v>
       </c>
       <c r="T9">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="U9">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="V9">
         <v>1.26</v>
       </c>
       <c r="W9">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="X9">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y9">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z9">
         <v>40</v>
@@ -2760,10 +2760,10 @@
         <v>100</v>
       </c>
       <c r="AB9">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AC9">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD9">
         <v>18.5</v>
@@ -2778,7 +2778,7 @@
         <v>11</v>
       </c>
       <c r="AH9">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI9">
         <v>46</v>
@@ -2793,31 +2793,31 @@
         <v>27</v>
       </c>
       <c r="AM9">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AN9">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AO9">
         <v>42</v>
       </c>
       <c r="AP9">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ9">
         <v>21</v>
       </c>
       <c r="AR9">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AS9">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="AT9">
         <v>11.5</v>
       </c>
       <c r="AU9">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AV9">
         <v>17.5</v>
@@ -2835,13 +2835,13 @@
         <v>15</v>
       </c>
       <c r="BA9">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BB9">
         <v>17</v>
       </c>
       <c r="BC9">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BD9">
         <v>25</v>
@@ -2850,16 +2850,16 @@
         <v>55</v>
       </c>
       <c r="BF9">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BG9">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BH9">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BI9">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="BJ9">
         <v>9.199999999999999</v>
@@ -2868,16 +2868,16 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BL9">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="BM9">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BN9">
         <v>4.7</v>
       </c>
       <c r="BO9">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BP9">
         <v>11.5</v>
@@ -2886,10 +2886,10 @@
         <v>10</v>
       </c>
       <c r="BR9">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BS9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BT9">
         <v>8.4</v>
@@ -2904,16 +2904,16 @@
         <v>10.5</v>
       </c>
       <c r="BX9">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BY9">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BZ9">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="CA9">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="CB9" t="s">
         <v>130</v>
@@ -2936,10 +2936,10 @@
         <v>122</v>
       </c>
       <c r="F10">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="G10">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="H10">
         <v>3.3</v>
@@ -2954,7 +2954,7 @@
         <v>3.3</v>
       </c>
       <c r="L10">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="M10">
         <v>1.11</v>
@@ -2966,7 +2966,7 @@
         <v>1.46</v>
       </c>
       <c r="P10">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q10">
         <v>2.4</v>
@@ -2990,7 +2990,7 @@
         <v>1.64</v>
       </c>
       <c r="X10">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Y10">
         <v>10.5</v>
@@ -3005,7 +3005,7 @@
         <v>8.6</v>
       </c>
       <c r="AC10">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD10">
         <v>15</v>
@@ -3089,73 +3089,73 @@
         <v>48</v>
       </c>
       <c r="BE10">
-        <v>15.5</v>
+        <v>29</v>
       </c>
       <c r="BF10">
         <v>27</v>
       </c>
       <c r="BG10">
-        <v>12.5</v>
+        <v>44</v>
       </c>
       <c r="BH10">
-        <v>3.1</v>
+        <v>2.82</v>
       </c>
       <c r="BI10">
-        <v>2.46</v>
+        <v>2.66</v>
       </c>
       <c r="BJ10">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK10">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>2.88</v>
+        <v>17.5</v>
       </c>
       <c r="BN10">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BO10">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BP10">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BQ10">
-        <v>2.88</v>
+        <v>10.5</v>
       </c>
       <c r="BR10">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS10">
-        <v>2.88</v>
+        <v>13</v>
       </c>
       <c r="BT10">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU10">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BV10">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BW10">
-        <v>2.88</v>
+        <v>11.5</v>
       </c>
       <c r="BX10">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY10">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="BZ10">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="CA10">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="CB10" t="s">
         <v>130</v>
@@ -3187,13 +3187,13 @@
         <v>7.6</v>
       </c>
       <c r="I11">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="J11">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="K11">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="L11">
         <v>1.28</v>
@@ -3202,28 +3202,28 @@
         <v>1.03</v>
       </c>
       <c r="N11">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="O11">
         <v>1.18</v>
       </c>
       <c r="P11">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="Q11">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="R11">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="S11">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="T11">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U11">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="V11">
         <v>1.14</v>
@@ -3232,7 +3232,7 @@
         <v>3.1</v>
       </c>
       <c r="X11">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Y11">
         <v>34</v>
@@ -3286,7 +3286,7 @@
         <v>80</v>
       </c>
       <c r="AP11">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ11">
         <v>30</v>
@@ -3304,19 +3304,19 @@
         <v>11.5</v>
       </c>
       <c r="AV11">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AW11">
         <v>80</v>
       </c>
       <c r="AX11">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AY11">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ11">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA11">
         <v>65</v>
@@ -3328,13 +3328,13 @@
         <v>12.5</v>
       </c>
       <c r="BD11">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BE11">
         <v>75</v>
       </c>
       <c r="BF11">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BG11">
         <v>17</v>
@@ -3423,19 +3423,19 @@
         <v>2.8</v>
       </c>
       <c r="G12">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="H12">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="I12">
         <v>2.82</v>
       </c>
       <c r="J12">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K12">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L12">
         <v>1.48</v>
@@ -3450,7 +3450,7 @@
         <v>1.41</v>
       </c>
       <c r="P12">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="Q12">
         <v>2.24</v>
@@ -3462,7 +3462,7 @@
         <v>4.2</v>
       </c>
       <c r="T12">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="U12">
         <v>2.02</v>
@@ -3477,7 +3477,7 @@
         <v>12</v>
       </c>
       <c r="Y12">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z12">
         <v>17</v>
@@ -3558,7 +3558,7 @@
         <v>12</v>
       </c>
       <c r="AZ12">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BA12">
         <v>46</v>
@@ -3570,7 +3570,7 @@
         <v>30</v>
       </c>
       <c r="BD12">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BE12">
         <v>60</v>
@@ -3662,31 +3662,31 @@
         <v>125</v>
       </c>
       <c r="F13">
+        <v>1.21</v>
+      </c>
+      <c r="G13">
         <v>1.22</v>
       </c>
-      <c r="G13">
-        <v>1.23</v>
-      </c>
       <c r="H13">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="I13">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="J13">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="K13">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="L13">
         <v>1.24</v>
       </c>
       <c r="M13">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N13">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="O13">
         <v>1.19</v>
@@ -3704,7 +3704,7 @@
         <v>2.44</v>
       </c>
       <c r="T13">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="U13">
         <v>1.7</v>
@@ -3713,16 +3713,16 @@
         <v>1.05</v>
       </c>
       <c r="W13">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="X13">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="Y13">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="Z13">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="AA13">
         <v>1000</v>
@@ -3731,25 +3731,25 @@
         <v>9.4</v>
       </c>
       <c r="AC13">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AD13">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AE13">
-        <v>440</v>
+        <v>460</v>
       </c>
       <c r="AF13">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AG13">
         <v>12</v>
       </c>
       <c r="AH13">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AI13">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="AJ13">
         <v>8.6</v>
@@ -3758,40 +3758,40 @@
         <v>14.5</v>
       </c>
       <c r="AL13">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AM13">
-        <v>260</v>
+        <v>290</v>
       </c>
       <c r="AN13">
         <v>3.85</v>
       </c>
       <c r="AO13">
-        <v>1000</v>
+        <v>570</v>
       </c>
       <c r="AP13">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AQ13">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AR13">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AS13">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AT13">
         <v>9</v>
       </c>
       <c r="AU13">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AV13">
         <v>50</v>
       </c>
       <c r="AW13">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AX13">
         <v>7</v>
@@ -3803,7 +3803,7 @@
         <v>38</v>
       </c>
       <c r="BA13">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="BB13">
         <v>8.199999999999999</v>
@@ -3812,70 +3812,70 @@
         <v>13.5</v>
       </c>
       <c r="BD13">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="BE13">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="BF13">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BG13">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BH13">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="BI13">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="BJ13">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BK13">
-        <v>2.24</v>
+        <v>12.5</v>
       </c>
       <c r="BL13">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="BM13">
         <v>23</v>
       </c>
       <c r="BN13">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="BO13">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="BP13">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BQ13">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BR13">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BS13">
-        <v>2.24</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT13">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BU13">
-        <v>2.24</v>
+        <v>15.5</v>
       </c>
       <c r="BV13">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="BW13">
-        <v>2.24</v>
+        <v>10.5</v>
       </c>
       <c r="BX13">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="BY13">
-        <v>2.24</v>
+        <v>10.5</v>
       </c>
       <c r="BZ13">
         <v>0</v>
@@ -3904,10 +3904,10 @@
         <v>126</v>
       </c>
       <c r="F14">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="G14">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="H14">
         <v>2.64</v>
@@ -3946,13 +3946,13 @@
         <v>3.75</v>
       </c>
       <c r="T14">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="U14">
         <v>2.06</v>
       </c>
       <c r="V14">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W14">
         <v>1.48</v>
@@ -3967,7 +3967,7 @@
         <v>22</v>
       </c>
       <c r="AA14">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AB14">
         <v>11.5</v>
@@ -4152,13 +4152,13 @@
         <v>110</v>
       </c>
       <c r="H15">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="I15">
         <v>110</v>
       </c>
       <c r="J15">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="K15">
         <v>950</v>
@@ -4170,16 +4170,16 @@
         <v>1.01</v>
       </c>
       <c r="N15">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="O15">
-        <v>1.45</v>
+        <v>1.02</v>
       </c>
       <c r="P15">
-        <v>1.09</v>
+        <v>1.46</v>
       </c>
       <c r="Q15">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="R15">
         <v>1.08</v>
@@ -4188,7 +4188,7 @@
         <v>1.49</v>
       </c>
       <c r="T15">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="U15">
         <v>1.01</v>
@@ -4197,7 +4197,7 @@
         <v>1.02</v>
       </c>
       <c r="W15">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X15">
         <v>500</v>
@@ -4305,7 +4305,7 @@
         <v>1.01</v>
       </c>
       <c r="BG15">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH15">
         <v>1000</v>
@@ -4391,16 +4391,16 @@
         <v>3.45</v>
       </c>
       <c r="G16">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="H16">
         <v>2.42</v>
       </c>
       <c r="I16">
+        <v>2.76</v>
+      </c>
+      <c r="J16">
         <v>2.74</v>
-      </c>
-      <c r="J16">
-        <v>2.78</v>
       </c>
       <c r="K16">
         <v>3.05</v>
@@ -4415,7 +4415,7 @@
         <v>2.32</v>
       </c>
       <c r="O16">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="P16">
         <v>1.41</v>
@@ -4430,16 +4430,16 @@
         <v>6.4</v>
       </c>
       <c r="T16">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="U16">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="V16">
         <v>1.58</v>
       </c>
       <c r="W16">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="X16">
         <v>7.6</v>
@@ -4472,13 +4472,13 @@
         <v>18.5</v>
       </c>
       <c r="AH16">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI16">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="AJ16">
-        <v>110</v>
+        <v>900</v>
       </c>
       <c r="AK16">
         <v>75</v>
@@ -4526,40 +4526,40 @@
         <v>14.5</v>
       </c>
       <c r="AZ16">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BA16">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BB16">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC16">
         <v>8</v>
       </c>
-      <c r="BC16">
-        <v>7.8</v>
-      </c>
       <c r="BD16">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BE16">
+        <v>8.6</v>
+      </c>
+      <c r="BF16">
         <v>8.4</v>
       </c>
-      <c r="BF16">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BG16">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH16">
         <v>2.58</v>
       </c>
       <c r="BI16">
-        <v>2.08</v>
+        <v>2.24</v>
       </c>
       <c r="BJ16">
         <v>13</v>
       </c>
       <c r="BK16">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BL16">
         <v>1000</v>
@@ -4577,13 +4577,13 @@
         <v>42</v>
       </c>
       <c r="BQ16">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BR16">
         <v>1000</v>
       </c>
       <c r="BS16">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BT16">
         <v>5.4</v>
@@ -4592,7 +4592,7 @@
         <v>3.95</v>
       </c>
       <c r="BV16">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BW16">
         <v>7.4</v>
@@ -4601,7 +4601,7 @@
         <v>1000</v>
       </c>
       <c r="BY16">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ16">
         <v>0</v>
@@ -4630,16 +4630,16 @@
         <v>129</v>
       </c>
       <c r="F17">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="G17">
-        <v>880</v>
+        <v>830</v>
       </c>
       <c r="H17">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="I17">
-        <v>880</v>
+        <v>830</v>
       </c>
       <c r="J17">
         <v>1.12</v>
@@ -4663,16 +4663,16 @@
         <v>1.09</v>
       </c>
       <c r="Q17">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="R17">
         <v>1.08</v>
       </c>
       <c r="S17">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="T17">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="U17">
         <v>1.01</v>
@@ -4789,7 +4789,7 @@
         <v>1.01</v>
       </c>
       <c r="BG17">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH17">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-24.xlsx
@@ -406,7 +406,7 @@
     <t>Vinotinto Ecuador</t>
   </si>
   <si>
-    <t>2026-09-23 21:10:53</t>
+    <t>2026-09-23 23:23:35</t>
   </si>
 </sst>
 </file>
@@ -1000,226 +1000,226 @@
         <v>114</v>
       </c>
       <c r="F2">
-        <v>1.52</v>
+        <v>1.07</v>
       </c>
       <c r="G2">
-        <v>1.53</v>
+        <v>1.08</v>
       </c>
       <c r="H2">
-        <v>7.6</v>
+        <v>500</v>
       </c>
       <c r="I2">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="J2">
+        <v>13.5</v>
+      </c>
+      <c r="K2">
+        <v>16</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>1.26</v>
+      </c>
+      <c r="O2">
+        <v>4.5</v>
+      </c>
+      <c r="P2">
+        <v>1.01</v>
+      </c>
+      <c r="Q2">
+        <v>50</v>
+      </c>
+      <c r="R2">
+        <v>1.01</v>
+      </c>
+      <c r="S2">
+        <v>170</v>
+      </c>
+      <c r="T2">
+        <v>1.72</v>
+      </c>
+      <c r="U2">
+        <v>1.01</v>
+      </c>
+      <c r="V2">
+        <v>1.01</v>
+      </c>
+      <c r="W2">
+        <v>12</v>
+      </c>
+      <c r="X2">
+        <v>1000</v>
+      </c>
+      <c r="Y2">
+        <v>1000</v>
+      </c>
+      <c r="Z2">
+        <v>1000</v>
+      </c>
+      <c r="AA2">
+        <v>1000</v>
+      </c>
+      <c r="AB2">
+        <v>1.28</v>
+      </c>
+      <c r="AC2">
+        <v>770</v>
+      </c>
+      <c r="AD2">
+        <v>1000</v>
+      </c>
+      <c r="AE2">
+        <v>1000</v>
+      </c>
+      <c r="AF2">
+        <v>780</v>
+      </c>
+      <c r="AG2">
+        <v>1000</v>
+      </c>
+      <c r="AH2">
+        <v>1000</v>
+      </c>
+      <c r="AI2">
+        <v>1000</v>
+      </c>
+      <c r="AJ2">
+        <v>1000</v>
+      </c>
+      <c r="AK2">
+        <v>1000</v>
+      </c>
+      <c r="AL2">
+        <v>1000</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>1000</v>
+      </c>
+      <c r="AO2">
+        <v>1000</v>
+      </c>
+      <c r="AP2">
+        <v>7</v>
+      </c>
+      <c r="AQ2">
+        <v>6.6</v>
+      </c>
+      <c r="AR2">
+        <v>48</v>
+      </c>
+      <c r="AS2">
+        <v>7</v>
+      </c>
+      <c r="AT2">
+        <v>1.08</v>
+      </c>
+      <c r="AU2">
+        <v>12</v>
+      </c>
+      <c r="AV2">
+        <v>110</v>
+      </c>
+      <c r="AW2">
+        <v>7</v>
+      </c>
+      <c r="AX2">
         <v>4.6</v>
       </c>
-      <c r="K2">
-        <v>4.8</v>
-      </c>
-      <c r="L2">
-        <v>1.37</v>
-      </c>
-      <c r="M2">
-        <v>1.06</v>
-      </c>
-      <c r="N2">
-        <v>4.2</v>
-      </c>
-      <c r="O2">
-        <v>1.3</v>
-      </c>
-      <c r="P2">
-        <v>2.08</v>
-      </c>
-      <c r="Q2">
-        <v>1.9</v>
-      </c>
-      <c r="R2">
-        <v>1.41</v>
-      </c>
-      <c r="S2">
-        <v>3.25</v>
-      </c>
-      <c r="T2">
-        <v>2.02</v>
-      </c>
-      <c r="U2">
-        <v>1.93</v>
-      </c>
-      <c r="V2">
-        <v>1.14</v>
-      </c>
-      <c r="W2">
-        <v>2.88</v>
-      </c>
-      <c r="X2">
-        <v>17</v>
-      </c>
-      <c r="Y2">
-        <v>25</v>
-      </c>
-      <c r="Z2">
-        <v>85</v>
-      </c>
-      <c r="AA2">
-        <v>300</v>
-      </c>
-      <c r="AB2">
-        <v>7.8</v>
-      </c>
-      <c r="AC2">
-        <v>10.5</v>
-      </c>
-      <c r="AD2">
-        <v>28</v>
-      </c>
-      <c r="AE2">
-        <v>130</v>
-      </c>
-      <c r="AF2">
-        <v>8.6</v>
-      </c>
-      <c r="AG2">
-        <v>9.6</v>
-      </c>
-      <c r="AH2">
-        <v>25</v>
-      </c>
-      <c r="AI2">
-        <v>110</v>
-      </c>
-      <c r="AJ2">
-        <v>13</v>
-      </c>
-      <c r="AK2">
-        <v>15.5</v>
-      </c>
-      <c r="AL2">
-        <v>38</v>
-      </c>
-      <c r="AM2">
-        <v>170</v>
-      </c>
-      <c r="AN2">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AO2">
-        <v>200</v>
-      </c>
-      <c r="AP2">
-        <v>15.5</v>
-      </c>
-      <c r="AQ2">
-        <v>22</v>
-      </c>
-      <c r="AR2">
+      <c r="AY2">
+        <v>7</v>
+      </c>
+      <c r="AZ2">
+        <v>20</v>
+      </c>
+      <c r="BA2">
+        <v>7</v>
+      </c>
+      <c r="BB2">
+        <v>7</v>
+      </c>
+      <c r="BC2">
         <v>60</v>
       </c>
-      <c r="AS2">
-        <v>150</v>
-      </c>
-      <c r="AT2">
-        <v>7.4</v>
-      </c>
-      <c r="AU2">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AV2">
-        <v>25</v>
-      </c>
-      <c r="AW2">
-        <v>100</v>
-      </c>
-      <c r="AX2">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY2">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ2">
-        <v>24</v>
-      </c>
-      <c r="BA2">
-        <v>90</v>
-      </c>
-      <c r="BB2">
-        <v>12</v>
-      </c>
-      <c r="BC2">
-        <v>14.5</v>
-      </c>
       <c r="BD2">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="BE2">
-        <v>110</v>
+        <v>6.2</v>
       </c>
       <c r="BF2">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="BG2">
-        <v>120</v>
+        <v>6.6</v>
       </c>
       <c r="BH2">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="BI2">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BJ2">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BK2">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BL2">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="BM2">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="BN2">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="BO2">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="BP2">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BQ2">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BR2">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BS2">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="BT2">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BU2">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="BV2">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="BW2">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BX2">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="BY2">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BZ2">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="CA2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="s">
         <v>130</v>
@@ -1242,226 +1242,226 @@
         <v>115</v>
       </c>
       <c r="F3">
-        <v>1.83</v>
+        <v>2.14</v>
       </c>
       <c r="G3">
+        <v>2.16</v>
+      </c>
+      <c r="H3">
+        <v>4.8</v>
+      </c>
+      <c r="I3">
+        <v>4.9</v>
+      </c>
+      <c r="J3">
+        <v>3</v>
+      </c>
+      <c r="K3">
+        <v>3.05</v>
+      </c>
+      <c r="L3">
+        <v>4.9</v>
+      </c>
+      <c r="M3">
+        <v>1.18</v>
+      </c>
+      <c r="N3">
+        <v>2.16</v>
+      </c>
+      <c r="O3">
         <v>1.85</v>
       </c>
-      <c r="H3">
-        <v>4.5</v>
-      </c>
-      <c r="I3">
-        <v>4.7</v>
-      </c>
-      <c r="J3">
-        <v>4.1</v>
-      </c>
-      <c r="K3">
-        <v>4.3</v>
-      </c>
-      <c r="L3">
-        <v>1.29</v>
-      </c>
-      <c r="M3">
+      <c r="P3">
+        <v>1.33</v>
+      </c>
+      <c r="Q3">
+        <v>3.9</v>
+      </c>
+      <c r="R3">
+        <v>1.11</v>
+      </c>
+      <c r="S3">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="T3">
+        <v>2.68</v>
+      </c>
+      <c r="U3">
+        <v>1.52</v>
+      </c>
+      <c r="V3">
+        <v>1.25</v>
+      </c>
+      <c r="W3">
+        <v>1.86</v>
+      </c>
+      <c r="X3">
+        <v>6.6</v>
+      </c>
+      <c r="Y3">
+        <v>10.5</v>
+      </c>
+      <c r="Z3">
+        <v>32</v>
+      </c>
+      <c r="AA3">
+        <v>170</v>
+      </c>
+      <c r="AB3">
+        <v>5.9</v>
+      </c>
+      <c r="AC3">
+        <v>7.2</v>
+      </c>
+      <c r="AD3">
+        <v>25</v>
+      </c>
+      <c r="AE3">
+        <v>140</v>
+      </c>
+      <c r="AF3">
+        <v>11</v>
+      </c>
+      <c r="AG3">
+        <v>14</v>
+      </c>
+      <c r="AH3">
+        <v>44</v>
+      </c>
+      <c r="AI3">
+        <v>220</v>
+      </c>
+      <c r="AJ3">
+        <v>28</v>
+      </c>
+      <c r="AK3">
+        <v>42</v>
+      </c>
+      <c r="AL3">
+        <v>150</v>
+      </c>
+      <c r="AM3">
+        <v>1000</v>
+      </c>
+      <c r="AN3">
+        <v>50</v>
+      </c>
+      <c r="AO3">
+        <v>340</v>
+      </c>
+      <c r="AP3">
+        <v>6</v>
+      </c>
+      <c r="AQ3">
+        <v>9.4</v>
+      </c>
+      <c r="AR3">
+        <v>27</v>
+      </c>
+      <c r="AS3">
+        <v>100</v>
+      </c>
+      <c r="AT3">
+        <v>5.3</v>
+      </c>
+      <c r="AU3">
+        <v>6.8</v>
+      </c>
+      <c r="AV3">
+        <v>19</v>
+      </c>
+      <c r="AW3">
+        <v>80</v>
+      </c>
+      <c r="AX3">
+        <v>9.6</v>
+      </c>
+      <c r="AY3">
+        <v>12</v>
+      </c>
+      <c r="AZ3">
+        <v>32</v>
+      </c>
+      <c r="BA3">
+        <v>140</v>
+      </c>
+      <c r="BB3">
+        <v>24</v>
+      </c>
+      <c r="BC3">
+        <v>32</v>
+      </c>
+      <c r="BD3">
+        <v>85</v>
+      </c>
+      <c r="BE3">
+        <v>360</v>
+      </c>
+      <c r="BF3">
+        <v>34</v>
+      </c>
+      <c r="BG3">
+        <v>13.5</v>
+      </c>
+      <c r="BH3">
+        <v>1.18</v>
+      </c>
+      <c r="BI3">
         <v>1.04</v>
       </c>
-      <c r="N3">
-        <v>6.2</v>
-      </c>
-      <c r="O3">
-        <v>1.17</v>
-      </c>
-      <c r="P3">
-        <v>2.72</v>
-      </c>
-      <c r="Q3">
-        <v>1.57</v>
-      </c>
-      <c r="R3">
-        <v>1.71</v>
-      </c>
-      <c r="S3">
-        <v>2.38</v>
-      </c>
-      <c r="T3">
-        <v>1.57</v>
-      </c>
-      <c r="U3">
-        <v>2.7</v>
-      </c>
-      <c r="V3">
-        <v>1.27</v>
-      </c>
-      <c r="W3">
-        <v>2.16</v>
-      </c>
-      <c r="X3">
-        <v>26</v>
-      </c>
-      <c r="Y3">
-        <v>26</v>
-      </c>
-      <c r="Z3">
-        <v>40</v>
-      </c>
-      <c r="AA3">
-        <v>95</v>
-      </c>
-      <c r="AB3">
-        <v>14</v>
-      </c>
-      <c r="AC3">
-        <v>10</v>
-      </c>
-      <c r="AD3">
-        <v>18</v>
-      </c>
-      <c r="AE3">
-        <v>44</v>
-      </c>
-      <c r="AF3">
-        <v>14</v>
-      </c>
-      <c r="AG3">
-        <v>10.5</v>
-      </c>
-      <c r="AH3">
-        <v>15.5</v>
-      </c>
-      <c r="AI3">
-        <v>44</v>
-      </c>
-      <c r="AJ3">
-        <v>20</v>
-      </c>
-      <c r="AK3">
+      <c r="BJ3">
+        <v>1000</v>
+      </c>
+      <c r="BK3">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
+        <v>4.4</v>
+      </c>
+      <c r="BN3">
+        <v>36</v>
+      </c>
+      <c r="BO3">
+        <v>6.6</v>
+      </c>
+      <c r="BP3">
+        <v>1000</v>
+      </c>
+      <c r="BQ3">
+        <v>4.4</v>
+      </c>
+      <c r="BR3">
+        <v>1000</v>
+      </c>
+      <c r="BS3">
+        <v>4.4</v>
+      </c>
+      <c r="BT3">
+        <v>60</v>
+      </c>
+      <c r="BU3">
         <v>16</v>
       </c>
-      <c r="AL3">
-        <v>24</v>
-      </c>
-      <c r="AM3">
-        <v>55</v>
-      </c>
-      <c r="AN3">
-        <v>7.6</v>
-      </c>
-      <c r="AO3">
-        <v>34</v>
-      </c>
-      <c r="AP3">
-        <v>23</v>
-      </c>
-      <c r="AQ3">
-        <v>23</v>
-      </c>
-      <c r="AR3">
-        <v>36</v>
-      </c>
-      <c r="AS3">
-        <v>75</v>
-      </c>
-      <c r="AT3">
-        <v>12.5</v>
-      </c>
-      <c r="AU3">
-        <v>9.4</v>
-      </c>
-      <c r="AV3">
-        <v>16.5</v>
-      </c>
-      <c r="AW3">
-        <v>40</v>
-      </c>
-      <c r="AX3">
-        <v>13</v>
-      </c>
-      <c r="AY3">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ3">
-        <v>14</v>
-      </c>
-      <c r="BA3">
-        <v>40</v>
-      </c>
-      <c r="BB3">
-        <v>19</v>
-      </c>
-      <c r="BC3">
-        <v>14.5</v>
-      </c>
-      <c r="BD3">
-        <v>23</v>
-      </c>
-      <c r="BE3">
-        <v>46</v>
-      </c>
-      <c r="BF3">
-        <v>7.2</v>
-      </c>
-      <c r="BG3">
-        <v>30</v>
-      </c>
-      <c r="BH3">
-        <v>4.5</v>
-      </c>
-      <c r="BI3">
-        <v>4.1</v>
-      </c>
-      <c r="BJ3">
-        <v>8.6</v>
-      </c>
-      <c r="BK3">
-        <v>7.8</v>
-      </c>
-      <c r="BL3">
-        <v>90</v>
-      </c>
-      <c r="BM3">
-        <v>60</v>
-      </c>
-      <c r="BN3">
-        <v>4.9</v>
-      </c>
-      <c r="BO3">
-        <v>4.5</v>
-      </c>
-      <c r="BP3">
-        <v>11.5</v>
-      </c>
-      <c r="BQ3">
-        <v>9.6</v>
-      </c>
-      <c r="BR3">
-        <v>20</v>
-      </c>
-      <c r="BS3">
-        <v>16.5</v>
-      </c>
-      <c r="BT3">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BU3">
-        <v>7.6</v>
-      </c>
       <c r="BV3">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BW3">
-        <v>16</v>
+        <v>4.4</v>
       </c>
       <c r="BX3">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BY3">
-        <v>12.5</v>
+        <v>4.4</v>
       </c>
       <c r="BZ3">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="CA3">
-        <v>11</v>
+        <v>4.4</v>
       </c>
       <c r="CB3" t="s">
         <v>130</v>
@@ -1484,226 +1484,226 @@
         <v>116</v>
       </c>
       <c r="F4">
-        <v>2.5</v>
+        <v>1.49</v>
       </c>
       <c r="G4">
-        <v>2.54</v>
+        <v>1.52</v>
       </c>
       <c r="H4">
-        <v>2.62</v>
+        <v>6.8</v>
       </c>
       <c r="I4">
-        <v>2.7</v>
+        <v>7.4</v>
       </c>
       <c r="J4">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="K4">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="L4">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>18</v>
+      </c>
+      <c r="O4">
+        <v>1.05</v>
+      </c>
+      <c r="P4">
+        <v>4.6</v>
+      </c>
+      <c r="Q4">
+        <v>1.22</v>
+      </c>
+      <c r="R4">
+        <v>2.32</v>
+      </c>
+      <c r="S4">
+        <v>1.71</v>
+      </c>
+      <c r="T4">
         <v>1.04</v>
       </c>
-      <c r="N4">
-        <v>5.6</v>
-      </c>
-      <c r="O4">
-        <v>1.19</v>
-      </c>
-      <c r="P4">
-        <v>2.66</v>
-      </c>
-      <c r="Q4">
-        <v>1.56</v>
-      </c>
-      <c r="R4">
-        <v>1.65</v>
-      </c>
-      <c r="S4">
-        <v>2.38</v>
-      </c>
-      <c r="T4">
-        <v>1.55</v>
-      </c>
       <c r="U4">
-        <v>2.68</v>
+        <v>3.5</v>
       </c>
       <c r="V4">
-        <v>1.58</v>
+        <v>1.14</v>
       </c>
       <c r="W4">
-        <v>1.63</v>
+        <v>3</v>
       </c>
       <c r="X4">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="Y4">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Z4">
+        <v>1000</v>
+      </c>
+      <c r="AA4">
+        <v>1000</v>
+      </c>
+      <c r="AB4">
         <v>23</v>
       </c>
-      <c r="AA4">
-        <v>42</v>
-      </c>
-      <c r="AB4">
-        <v>17</v>
-      </c>
       <c r="AC4">
-        <v>10.5</v>
+        <v>17.5</v>
       </c>
       <c r="AD4">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="AE4">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="AF4">
+        <v>16.5</v>
+      </c>
+      <c r="AG4">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AH4">
+        <v>12.5</v>
+      </c>
+      <c r="AI4">
+        <v>38</v>
+      </c>
+      <c r="AJ4">
+        <v>19.5</v>
+      </c>
+      <c r="AK4">
+        <v>12</v>
+      </c>
+      <c r="AL4">
         <v>21</v>
       </c>
-      <c r="AG4">
-        <v>11.5</v>
-      </c>
-      <c r="AH4">
-        <v>15.5</v>
-      </c>
-      <c r="AI4">
-        <v>30</v>
-      </c>
-      <c r="AJ4">
-        <v>42</v>
-      </c>
-      <c r="AK4">
-        <v>24</v>
-      </c>
-      <c r="AL4">
-        <v>29</v>
-      </c>
       <c r="AM4">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AN4">
-        <v>14</v>
+        <v>6.2</v>
       </c>
       <c r="AO4">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="AP4">
-        <v>22</v>
+        <v>6.2</v>
       </c>
       <c r="AQ4">
-        <v>15</v>
+        <v>6.4</v>
       </c>
       <c r="AR4">
         <v>21</v>
       </c>
       <c r="AS4">
-        <v>34</v>
+        <v>6.2</v>
       </c>
       <c r="AT4">
+        <v>16.5</v>
+      </c>
+      <c r="AU4">
+        <v>12.5</v>
+      </c>
+      <c r="AV4">
+        <v>16</v>
+      </c>
+      <c r="AW4">
+        <v>40</v>
+      </c>
+      <c r="AX4">
+        <v>11.5</v>
+      </c>
+      <c r="AY4">
+        <v>7.4</v>
+      </c>
+      <c r="AZ4">
+        <v>11</v>
+      </c>
+      <c r="BA4">
+        <v>24</v>
+      </c>
+      <c r="BB4">
+        <v>14</v>
+      </c>
+      <c r="BC4">
+        <v>10</v>
+      </c>
+      <c r="BD4">
         <v>14.5</v>
       </c>
-      <c r="AU4">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV4">
-        <v>11</v>
-      </c>
-      <c r="AW4">
+      <c r="BE4">
+        <v>25</v>
+      </c>
+      <c r="BF4">
+        <v>4.5</v>
+      </c>
+      <c r="BG4">
+        <v>23</v>
+      </c>
+      <c r="BH4">
+        <v>1000</v>
+      </c>
+      <c r="BI4">
+        <v>7</v>
+      </c>
+      <c r="BJ4">
+        <v>6.4</v>
+      </c>
+      <c r="BK4">
+        <v>5.4</v>
+      </c>
+      <c r="BL4">
+        <v>46</v>
+      </c>
+      <c r="BM4">
+        <v>29</v>
+      </c>
+      <c r="BN4">
+        <v>3.45</v>
+      </c>
+      <c r="BO4">
+        <v>3.2</v>
+      </c>
+      <c r="BP4">
+        <v>5.5</v>
+      </c>
+      <c r="BQ4">
+        <v>4.8</v>
+      </c>
+      <c r="BR4">
+        <v>11.5</v>
+      </c>
+      <c r="BS4">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT4">
+        <v>1000</v>
+      </c>
+      <c r="BU4">
+        <v>7</v>
+      </c>
+      <c r="BV4">
+        <v>1000</v>
+      </c>
+      <c r="BW4">
+        <v>7</v>
+      </c>
+      <c r="BX4">
+        <v>32</v>
+      </c>
+      <c r="BY4">
         <v>22</v>
       </c>
-      <c r="AX4">
-        <v>18.5</v>
-      </c>
-      <c r="AY4">
-        <v>10.5</v>
-      </c>
-      <c r="AZ4">
-        <v>13.5</v>
-      </c>
-      <c r="BA4">
-        <v>26</v>
-      </c>
-      <c r="BB4">
-        <v>32</v>
-      </c>
-      <c r="BC4">
-        <v>21</v>
-      </c>
-      <c r="BD4">
-        <v>25</v>
-      </c>
-      <c r="BE4">
-        <v>46</v>
-      </c>
-      <c r="BF4">
-        <v>12</v>
-      </c>
-      <c r="BG4">
-        <v>12.5</v>
-      </c>
-      <c r="BH4">
-        <v>5.2</v>
-      </c>
-      <c r="BI4">
-        <v>3.85</v>
-      </c>
-      <c r="BJ4">
-        <v>10</v>
-      </c>
-      <c r="BK4">
-        <v>7.4</v>
-      </c>
-      <c r="BL4">
-        <v>95</v>
-      </c>
-      <c r="BM4">
-        <v>60</v>
-      </c>
-      <c r="BN4">
-        <v>7.4</v>
-      </c>
-      <c r="BO4">
-        <v>5.4</v>
-      </c>
-      <c r="BP4">
-        <v>22</v>
-      </c>
-      <c r="BQ4">
-        <v>4.3</v>
-      </c>
-      <c r="BR4">
-        <v>30</v>
-      </c>
-      <c r="BS4">
-        <v>4.3</v>
-      </c>
-      <c r="BT4">
-        <v>7.2</v>
-      </c>
-      <c r="BU4">
-        <v>5.4</v>
-      </c>
-      <c r="BV4">
-        <v>21</v>
-      </c>
-      <c r="BW4">
-        <v>4.3</v>
-      </c>
-      <c r="BX4">
-        <v>34</v>
-      </c>
-      <c r="BY4">
-        <v>5.3</v>
-      </c>
       <c r="BZ4">
-        <v>18.5</v>
+        <v>8.6</v>
       </c>
       <c r="CA4">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="CB4" t="s">
         <v>130</v>
@@ -1729,10 +1729,10 @@
         <v>1.22</v>
       </c>
       <c r="G5">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="H5">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="I5">
         <v>400</v>
@@ -1777,7 +1777,7 @@
         <v>1.03</v>
       </c>
       <c r="W5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X5">
         <v>1000</v>
@@ -1834,7 +1834,7 @@
         <v>1000</v>
       </c>
       <c r="AP5">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AQ5">
         <v>2.5</v>
@@ -1846,10 +1846,10 @@
         <v>2.5</v>
       </c>
       <c r="AT5">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AU5">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AV5">
         <v>2.5</v>
@@ -1858,28 +1858,28 @@
         <v>2.5</v>
       </c>
       <c r="AX5">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AY5">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AZ5">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BA5">
         <v>2.5</v>
       </c>
       <c r="BB5">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BC5">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BD5">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BE5">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BF5">
         <v>1.95</v>
@@ -1989,31 +1989,31 @@
         <v>1.66</v>
       </c>
       <c r="M6">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="N6">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="O6">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="P6">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="Q6">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="R6">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="S6">
         <v>7.8</v>
       </c>
       <c r="T6">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="U6">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="V6">
         <v>1.65</v>
@@ -2025,7 +2025,7 @@
         <v>6.6</v>
       </c>
       <c r="Y6">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="Z6">
         <v>12.5</v>
@@ -2034,7 +2034,7 @@
         <v>40</v>
       </c>
       <c r="AB6">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC6">
         <v>7.4</v>
@@ -2043,7 +2043,7 @@
         <v>14.5</v>
       </c>
       <c r="AE6">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF6">
         <v>24</v>
@@ -2052,16 +2052,16 @@
         <v>19.5</v>
       </c>
       <c r="AH6">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AI6">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="AJ6">
         <v>110</v>
       </c>
       <c r="AK6">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AL6">
         <v>530</v>
@@ -2073,13 +2073,13 @@
         <v>150</v>
       </c>
       <c r="AO6">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AP6">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AQ6">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AR6">
         <v>11.5</v>
@@ -2088,7 +2088,7 @@
         <v>34</v>
       </c>
       <c r="AT6">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU6">
         <v>7</v>
@@ -2103,19 +2103,19 @@
         <v>21</v>
       </c>
       <c r="AY6">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AZ6">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BA6">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="BB6">
         <v>80</v>
       </c>
       <c r="BC6">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BD6">
         <v>42</v>
@@ -2127,7 +2127,7 @@
         <v>42</v>
       </c>
       <c r="BG6">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -2213,13 +2213,13 @@
         <v>13.5</v>
       </c>
       <c r="G7">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="H7">
         <v>1.33</v>
       </c>
       <c r="I7">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="J7">
         <v>5.3</v>
@@ -2240,7 +2240,7 @@
         <v>1.39</v>
       </c>
       <c r="P7">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="Q7">
         <v>2.22</v>
@@ -2252,7 +2252,7 @@
         <v>4.2</v>
       </c>
       <c r="T7">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="U7">
         <v>1.48</v>
@@ -2273,7 +2273,7 @@
         <v>5.9</v>
       </c>
       <c r="AA7">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AB7">
         <v>32</v>
@@ -2285,13 +2285,13 @@
         <v>12</v>
       </c>
       <c r="AE7">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AF7">
         <v>170</v>
       </c>
       <c r="AG7">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AH7">
         <v>60</v>
@@ -2312,7 +2312,7 @@
         <v>540</v>
       </c>
       <c r="AN7">
-        <v>850</v>
+        <v>840</v>
       </c>
       <c r="AO7">
         <v>8</v>
@@ -2327,7 +2327,7 @@
         <v>5.7</v>
       </c>
       <c r="AS7">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT7">
         <v>26</v>
@@ -2342,7 +2342,7 @@
         <v>17</v>
       </c>
       <c r="AX7">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AY7">
         <v>50</v>
@@ -2354,22 +2354,22 @@
         <v>65</v>
       </c>
       <c r="BB7">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BC7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD7">
         <v>20</v>
       </c>
       <c r="BE7">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BF7">
         <v>90</v>
       </c>
       <c r="BG7">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BH7">
         <v>3.25</v>
@@ -2390,7 +2390,7 @@
         <v>21</v>
       </c>
       <c r="BN7">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BO7">
         <v>12.5</v>
@@ -2458,10 +2458,10 @@
         <v>2.56</v>
       </c>
       <c r="H8">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="I8">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="J8">
         <v>3.85</v>
@@ -2488,10 +2488,10 @@
         <v>1.5</v>
       </c>
       <c r="R8">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="S8">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="T8">
         <v>1.46</v>
@@ -2608,7 +2608,7 @@
         <v>40</v>
       </c>
       <c r="BF8">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BG8">
         <v>12.5</v>
@@ -2623,7 +2623,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BK8">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BL8">
         <v>65</v>
@@ -2632,22 +2632,22 @@
         <v>12</v>
       </c>
       <c r="BN8">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BO8">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BP8">
         <v>16.5</v>
       </c>
       <c r="BQ8">
-        <v>8.4</v>
+        <v>12</v>
       </c>
       <c r="BR8">
         <v>23</v>
       </c>
       <c r="BS8">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BT8">
         <v>6.4</v>
@@ -2659,19 +2659,19 @@
         <v>19.5</v>
       </c>
       <c r="BW8">
-        <v>9.199999999999999</v>
+        <v>13.5</v>
       </c>
       <c r="BX8">
         <v>25</v>
       </c>
       <c r="BY8">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BZ8">
         <v>14</v>
       </c>
       <c r="CA8">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="CB8" t="s">
         <v>130</v>
@@ -2694,16 +2694,16 @@
         <v>121</v>
       </c>
       <c r="F9">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="G9">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="H9">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="I9">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="J9">
         <v>4.2</v>
@@ -2712,28 +2712,28 @@
         <v>4.3</v>
       </c>
       <c r="L9">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="M9">
         <v>1.04</v>
       </c>
       <c r="N9">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="O9">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P9">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="Q9">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="R9">
         <v>1.63</v>
       </c>
       <c r="S9">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="T9">
         <v>1.65</v>
@@ -2742,16 +2742,16 @@
         <v>2.46</v>
       </c>
       <c r="V9">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W9">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="X9">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Y9">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Z9">
         <v>40</v>
@@ -2766,7 +2766,7 @@
         <v>10</v>
       </c>
       <c r="AD9">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AE9">
         <v>55</v>
@@ -2787,7 +2787,7 @@
         <v>18.5</v>
       </c>
       <c r="AK9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL9">
         <v>27</v>
@@ -2805,13 +2805,13 @@
         <v>21</v>
       </c>
       <c r="AQ9">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR9">
         <v>36</v>
       </c>
       <c r="AS9">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="AT9">
         <v>11.5</v>
@@ -2826,7 +2826,7 @@
         <v>46</v>
       </c>
       <c r="AX9">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AY9">
         <v>10</v>
@@ -2835,7 +2835,7 @@
         <v>15</v>
       </c>
       <c r="BA9">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BB9">
         <v>17</v>
@@ -2844,7 +2844,7 @@
         <v>15</v>
       </c>
       <c r="BD9">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BE9">
         <v>55</v>
@@ -2853,7 +2853,7 @@
         <v>7.2</v>
       </c>
       <c r="BG9">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BH9">
         <v>4.1</v>
@@ -2871,7 +2871,7 @@
         <v>90</v>
       </c>
       <c r="BM9">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BN9">
         <v>4.7</v>
@@ -2886,10 +2886,10 @@
         <v>10</v>
       </c>
       <c r="BR9">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BS9">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BT9">
         <v>8.4</v>
@@ -2901,19 +2901,19 @@
         <v>36</v>
       </c>
       <c r="BW9">
+        <v>10</v>
+      </c>
+      <c r="BX9">
+        <v>40</v>
+      </c>
+      <c r="BY9">
         <v>10.5</v>
       </c>
-      <c r="BX9">
-        <v>38</v>
-      </c>
-      <c r="BY9">
-        <v>11</v>
-      </c>
       <c r="BZ9">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="CA9">
-        <v>11.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB9" t="s">
         <v>130</v>
@@ -2936,16 +2936,16 @@
         <v>122</v>
       </c>
       <c r="F10">
+        <v>2.5</v>
+      </c>
+      <c r="G10">
         <v>2.52</v>
-      </c>
-      <c r="G10">
-        <v>2.56</v>
       </c>
       <c r="H10">
         <v>3.3</v>
       </c>
       <c r="I10">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="J10">
         <v>3.25</v>
@@ -2963,31 +2963,31 @@
         <v>3</v>
       </c>
       <c r="O10">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P10">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="Q10">
         <v>2.4</v>
       </c>
       <c r="R10">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S10">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="T10">
         <v>2.02</v>
       </c>
       <c r="U10">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="V10">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W10">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="X10">
         <v>10</v>
@@ -3038,7 +3038,7 @@
         <v>150</v>
       </c>
       <c r="AN10">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AO10">
         <v>55</v>
@@ -3113,7 +3113,7 @@
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BN10">
         <v>5.3</v>
@@ -3125,13 +3125,13 @@
         <v>21</v>
       </c>
       <c r="BQ10">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="BR10">
         <v>40</v>
       </c>
       <c r="BS10">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BT10">
         <v>6.4</v>
@@ -3143,10 +3143,10 @@
         <v>30</v>
       </c>
       <c r="BW10">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BX10">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BY10">
         <v>14</v>
@@ -3155,7 +3155,7 @@
         <v>40</v>
       </c>
       <c r="CA10">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="CB10" t="s">
         <v>130</v>
@@ -3190,10 +3190,10 @@
         <v>8</v>
       </c>
       <c r="J11">
+        <v>5.2</v>
+      </c>
+      <c r="K11">
         <v>5.3</v>
-      </c>
-      <c r="K11">
-        <v>5.4</v>
       </c>
       <c r="L11">
         <v>1.28</v>
@@ -3217,7 +3217,7 @@
         <v>1.7</v>
       </c>
       <c r="S11">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="T11">
         <v>1.76</v>
@@ -3229,7 +3229,7 @@
         <v>1.14</v>
       </c>
       <c r="W11">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="X11">
         <v>26</v>
@@ -3238,7 +3238,7 @@
         <v>34</v>
       </c>
       <c r="Z11">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AA11">
         <v>260</v>
@@ -3277,10 +3277,10 @@
         <v>28</v>
       </c>
       <c r="AM11">
-        <v>320</v>
+        <v>110</v>
       </c>
       <c r="AN11">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AO11">
         <v>80</v>
@@ -3304,7 +3304,7 @@
         <v>11.5</v>
       </c>
       <c r="AV11">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AW11">
         <v>80</v>
@@ -3337,7 +3337,7 @@
         <v>4.8</v>
       </c>
       <c r="BG11">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="BH11">
         <v>4.6</v>
@@ -3355,7 +3355,7 @@
         <v>120</v>
       </c>
       <c r="BM11">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="BN11">
         <v>4.3</v>
@@ -3364,7 +3364,7 @@
         <v>3.9</v>
       </c>
       <c r="BP11">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BQ11">
         <v>7.4</v>
@@ -3373,7 +3373,7 @@
         <v>24</v>
       </c>
       <c r="BS11">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="BT11">
         <v>13.5</v>
@@ -3385,19 +3385,19 @@
         <v>70</v>
       </c>
       <c r="BW11">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BX11">
         <v>65</v>
       </c>
       <c r="BY11">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BZ11">
         <v>13.5</v>
       </c>
       <c r="CA11">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="CB11" t="s">
         <v>130</v>
@@ -3426,13 +3426,13 @@
         <v>2.82</v>
       </c>
       <c r="H12">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="I12">
         <v>2.82</v>
       </c>
       <c r="J12">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K12">
         <v>3.5</v>
@@ -3465,7 +3465,7 @@
         <v>1.92</v>
       </c>
       <c r="U12">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V12">
         <v>1.54</v>
@@ -3477,7 +3477,7 @@
         <v>12</v>
       </c>
       <c r="Y12">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="Z12">
         <v>17</v>
@@ -3558,7 +3558,7 @@
         <v>12</v>
       </c>
       <c r="AZ12">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA12">
         <v>46</v>
@@ -3570,7 +3570,7 @@
         <v>30</v>
       </c>
       <c r="BD12">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BE12">
         <v>60</v>
@@ -3668,19 +3668,19 @@
         <v>1.22</v>
       </c>
       <c r="H13">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="I13">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="J13">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="K13">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L13">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="M13">
         <v>1.03</v>
@@ -3695,13 +3695,13 @@
         <v>2.68</v>
       </c>
       <c r="Q13">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="R13">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="S13">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="T13">
         <v>2.38</v>
@@ -3713,7 +3713,7 @@
         <v>1.05</v>
       </c>
       <c r="W13">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="X13">
         <v>28</v>
@@ -3728,7 +3728,7 @@
         <v>1000</v>
       </c>
       <c r="AB13">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC13">
         <v>18.5</v>
@@ -3737,7 +3737,7 @@
         <v>75</v>
       </c>
       <c r="AE13">
-        <v>460</v>
+        <v>490</v>
       </c>
       <c r="AF13">
         <v>7.6</v>
@@ -3749,7 +3749,7 @@
         <v>46</v>
       </c>
       <c r="AI13">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="AJ13">
         <v>8.6</v>
@@ -3761,28 +3761,28 @@
         <v>46</v>
       </c>
       <c r="AM13">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="AN13">
         <v>3.85</v>
       </c>
       <c r="AO13">
-        <v>570</v>
+        <v>1000</v>
       </c>
       <c r="AP13">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AQ13">
         <v>48</v>
       </c>
       <c r="AR13">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="AS13">
         <v>20</v>
       </c>
       <c r="AT13">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU13">
         <v>17</v>
@@ -3800,10 +3800,10 @@
         <v>11</v>
       </c>
       <c r="AZ13">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BA13">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="BB13">
         <v>8.199999999999999</v>
@@ -3830,7 +3830,7 @@
         <v>4.1</v>
       </c>
       <c r="BJ13">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="BK13">
         <v>12.5</v>
@@ -3857,7 +3857,7 @@
         <v>28</v>
       </c>
       <c r="BS13">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BT13">
         <v>21</v>
@@ -3869,13 +3869,13 @@
         <v>180</v>
       </c>
       <c r="BW13">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BX13">
         <v>140</v>
       </c>
       <c r="BY13">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BZ13">
         <v>0</v>
@@ -3904,7 +3904,7 @@
         <v>126</v>
       </c>
       <c r="F14">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="G14">
         <v>3.1</v>
@@ -3913,7 +3913,7 @@
         <v>2.64</v>
       </c>
       <c r="I14">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="J14">
         <v>3.25</v>
@@ -3952,7 +3952,7 @@
         <v>2.06</v>
       </c>
       <c r="V14">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W14">
         <v>1.48</v>
@@ -3964,28 +3964,28 @@
         <v>12</v>
       </c>
       <c r="Z14">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA14">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AB14">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC14">
         <v>8</v>
       </c>
       <c r="AD14">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE14">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AF14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AH14">
         <v>18.5</v>
@@ -4009,7 +4009,7 @@
         <v>38</v>
       </c>
       <c r="AO14">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AP14">
         <v>9.800000000000001</v>
@@ -4045,7 +4045,7 @@
         <v>15</v>
       </c>
       <c r="BA14">
-        <v>6.4</v>
+        <v>34</v>
       </c>
       <c r="BB14">
         <v>24</v>
@@ -4152,13 +4152,13 @@
         <v>110</v>
       </c>
       <c r="H15">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="I15">
         <v>110</v>
       </c>
       <c r="J15">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="K15">
         <v>950</v>
@@ -4170,13 +4170,13 @@
         <v>1.01</v>
       </c>
       <c r="N15">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="O15">
         <v>1.02</v>
       </c>
       <c r="P15">
-        <v>1.46</v>
+        <v>1.09</v>
       </c>
       <c r="Q15">
         <v>1.5</v>
@@ -4197,7 +4197,7 @@
         <v>1.02</v>
       </c>
       <c r="W15">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X15">
         <v>500</v>
@@ -4403,7 +4403,7 @@
         <v>2.74</v>
       </c>
       <c r="K16">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="L16">
         <v>1.65</v>
@@ -4412,10 +4412,10 @@
         <v>1.15</v>
       </c>
       <c r="N16">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="O16">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="P16">
         <v>1.41</v>
@@ -4451,7 +4451,7 @@
         <v>15.5</v>
       </c>
       <c r="AA16">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AB16">
         <v>9.6</v>
@@ -4499,7 +4499,7 @@
         <v>6</v>
       </c>
       <c r="AQ16">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AR16">
         <v>12</v>
@@ -4526,10 +4526,10 @@
         <v>14.5</v>
       </c>
       <c r="AZ16">
-        <v>6.8</v>
+        <v>22</v>
       </c>
       <c r="BA16">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB16">
         <v>8.199999999999999</v>
@@ -4541,16 +4541,16 @@
         <v>8.4</v>
       </c>
       <c r="BE16">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF16">
         <v>8.4</v>
       </c>
       <c r="BG16">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH16">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="BI16">
         <v>2.24</v>
@@ -4583,7 +4583,7 @@
         <v>1000</v>
       </c>
       <c r="BS16">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT16">
         <v>5.4</v>
@@ -4598,10 +4598,10 @@
         <v>7.4</v>
       </c>
       <c r="BX16">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY16">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BZ16">
         <v>0</v>
@@ -4636,10 +4636,10 @@
         <v>830</v>
       </c>
       <c r="H17">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="I17">
-        <v>830</v>
+        <v>280</v>
       </c>
       <c r="J17">
         <v>1.12</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-24.xlsx
@@ -370,7 +370,7 @@
     <t>Vinotinto Ecuador</t>
   </si>
   <si>
-    <t>2026-09-24 01:37:00</t>
+    <t>2026-09-24 03:51:14</t>
   </si>
 </sst>
 </file>
@@ -964,175 +964,175 @@
         <v>105</v>
       </c>
       <c r="F2">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="G2">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="H2">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I2">
-        <v>400</v>
+        <v>16.5</v>
       </c>
       <c r="J2">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="K2">
-        <v>29</v>
+        <v>7.2</v>
       </c>
       <c r="L2">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M2">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N2">
-        <v>1.26</v>
+        <v>4.7</v>
       </c>
       <c r="O2">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="P2">
-        <v>1.26</v>
+        <v>2.22</v>
       </c>
       <c r="Q2">
-        <v>1.03</v>
+        <v>1.6</v>
       </c>
       <c r="R2">
-        <v>1.23</v>
+        <v>1.53</v>
       </c>
       <c r="S2">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="T2">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="U2">
-        <v>1.47</v>
+        <v>1.72</v>
       </c>
       <c r="V2">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="W2">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="X2">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Y2">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="Z2">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AA2">
         <v>1000</v>
       </c>
       <c r="AB2">
-        <v>32</v>
+        <v>9.4</v>
       </c>
       <c r="AC2">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="AD2">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AE2">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AF2">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AG2">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH2">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AI2">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AJ2">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AK2">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AL2">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AM2">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AN2">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="AO2">
-        <v>1000</v>
+        <v>390</v>
       </c>
       <c r="AP2">
-        <v>1.13</v>
+        <v>5.5</v>
       </c>
       <c r="AQ2">
-        <v>2.5</v>
+        <v>6</v>
       </c>
       <c r="AR2">
-        <v>2.5</v>
+        <v>6.8</v>
       </c>
       <c r="AS2">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="AT2">
-        <v>1.09</v>
+        <v>4</v>
       </c>
       <c r="AU2">
-        <v>1.1</v>
+        <v>4.8</v>
       </c>
       <c r="AV2">
-        <v>2.5</v>
+        <v>6.2</v>
       </c>
       <c r="AW2">
-        <v>2.5</v>
+        <v>6.8</v>
       </c>
       <c r="AX2">
-        <v>1.13</v>
+        <v>4</v>
       </c>
       <c r="AY2">
-        <v>1.13</v>
+        <v>8.4</v>
       </c>
       <c r="AZ2">
-        <v>1.13</v>
+        <v>5.9</v>
       </c>
       <c r="BA2">
-        <v>2.5</v>
+        <v>6.8</v>
       </c>
       <c r="BB2">
-        <v>1.13</v>
+        <v>7.4</v>
       </c>
       <c r="BC2">
-        <v>1.13</v>
+        <v>10.5</v>
       </c>
       <c r="BD2">
-        <v>1.13</v>
+        <v>6</v>
       </c>
       <c r="BE2">
-        <v>1.13</v>
+        <v>6.8</v>
       </c>
       <c r="BF2">
-        <v>1.95</v>
+        <v>4.1</v>
       </c>
       <c r="BG2">
         <v>10.5</v>
       </c>
       <c r="BH2">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BI2">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BJ2">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BK2">
         <v>1.01</v>
@@ -1144,25 +1144,25 @@
         <v>1.01</v>
       </c>
       <c r="BN2">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="BO2">
-        <v>1.01</v>
+        <v>2.92</v>
       </c>
       <c r="BP2">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BQ2">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS2">
         <v>1.01</v>
       </c>
       <c r="BT2">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BU2">
         <v>1.01</v>
@@ -1180,7 +1180,7 @@
         <v>1.01</v>
       </c>
       <c r="BZ2">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="CA2">
         <v>1.01</v>
@@ -1209,16 +1209,16 @@
         <v>3.8</v>
       </c>
       <c r="G3">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="H3">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="I3">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="J3">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="K3">
         <v>2.96</v>
@@ -1230,13 +1230,13 @@
         <v>1.18</v>
       </c>
       <c r="N3">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="O3">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="P3">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="Q3">
         <v>3.45</v>
@@ -1245,34 +1245,34 @@
         <v>1.13</v>
       </c>
       <c r="S3">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="T3">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="U3">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="V3">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="W3">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="X3">
         <v>6.6</v>
       </c>
       <c r="Y3">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="Z3">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AA3">
         <v>40</v>
       </c>
       <c r="AB3">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC3">
         <v>7.2</v>
@@ -1281,28 +1281,28 @@
         <v>14</v>
       </c>
       <c r="AE3">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF3">
         <v>24</v>
       </c>
       <c r="AG3">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AH3">
         <v>32</v>
       </c>
       <c r="AI3">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AJ3">
         <v>100</v>
       </c>
       <c r="AK3">
-        <v>160</v>
+        <v>80</v>
       </c>
       <c r="AL3">
-        <v>540</v>
+        <v>140</v>
       </c>
       <c r="AM3">
         <v>500</v>
@@ -1311,43 +1311,43 @@
         <v>150</v>
       </c>
       <c r="AO3">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AP3">
         <v>6.2</v>
       </c>
       <c r="AQ3">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AR3">
         <v>11.5</v>
       </c>
       <c r="AS3">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AT3">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AU3">
         <v>7</v>
       </c>
       <c r="AV3">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AW3">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AX3">
         <v>21</v>
       </c>
       <c r="AY3">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AZ3">
         <v>29</v>
       </c>
       <c r="BA3">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="BB3">
         <v>80</v>
@@ -1359,16 +1359,16 @@
         <v>42</v>
       </c>
       <c r="BE3">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="BF3">
         <v>42</v>
       </c>
       <c r="BG3">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BH3">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="BI3">
         <v>2.24</v>
@@ -1383,7 +1383,7 @@
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="BN3">
         <v>6.8</v>
@@ -1395,13 +1395,13 @@
         <v>46</v>
       </c>
       <c r="BQ3">
-        <v>30</v>
+        <v>13.5</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>50</v>
+        <v>2.06</v>
       </c>
       <c r="BT3">
         <v>5</v>
@@ -1413,19 +1413,19 @@
         <v>25</v>
       </c>
       <c r="BW3">
-        <v>17.5</v>
+        <v>11</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>40</v>
+        <v>14.5</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>50</v>
+        <v>2.06</v>
       </c>
       <c r="CB3" t="s">
         <v>118</v>
@@ -1457,7 +1457,7 @@
         <v>1.33</v>
       </c>
       <c r="I4">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="J4">
         <v>5.3</v>
@@ -1466,13 +1466,13 @@
         <v>5.5</v>
       </c>
       <c r="L4">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M4">
         <v>1.08</v>
       </c>
       <c r="N4">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O4">
         <v>1.4</v>
@@ -1493,7 +1493,7 @@
         <v>3</v>
       </c>
       <c r="U4">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="V4">
         <v>3.85</v>
@@ -1505,10 +1505,10 @@
         <v>12.5</v>
       </c>
       <c r="Y4">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="Z4">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AA4">
         <v>9.199999999999999</v>
@@ -1520,31 +1520,31 @@
         <v>12.5</v>
       </c>
       <c r="AD4">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE4">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AF4">
         <v>150</v>
       </c>
       <c r="AG4">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AH4">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="AI4">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AJ4">
         <v>1000</v>
       </c>
       <c r="AK4">
-        <v>470</v>
+        <v>510</v>
       </c>
       <c r="AL4">
-        <v>520</v>
+        <v>400</v>
       </c>
       <c r="AM4">
         <v>540</v>
@@ -1556,19 +1556,19 @@
         <v>8</v>
       </c>
       <c r="AP4">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ4">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="AR4">
         <v>5.7</v>
       </c>
       <c r="AS4">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AT4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AU4">
         <v>11.5</v>
@@ -1580,46 +1580,46 @@
         <v>17.5</v>
       </c>
       <c r="AX4">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AY4">
         <v>50</v>
       </c>
       <c r="AZ4">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="BA4">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="BB4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC4">
         <v>20</v>
       </c>
       <c r="BD4">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="BE4">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="BF4">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="BG4">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BH4">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BI4">
-        <v>2.76</v>
+        <v>2.98</v>
       </c>
       <c r="BJ4">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BK4">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BL4">
         <v>1000</v>
@@ -1628,10 +1628,10 @@
         <v>21</v>
       </c>
       <c r="BN4">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="BO4">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BP4">
         <v>1000</v>
@@ -1649,19 +1649,19 @@
         <v>3.3</v>
       </c>
       <c r="BU4">
-        <v>2.86</v>
+        <v>3.05</v>
       </c>
       <c r="BV4">
         <v>8</v>
       </c>
       <c r="BW4">
-        <v>7.2</v>
+        <v>5.1</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
@@ -1696,16 +1696,16 @@
         <v>1.77</v>
       </c>
       <c r="H5">
+        <v>4.8</v>
+      </c>
+      <c r="I5">
         <v>5</v>
       </c>
-      <c r="I5">
-        <v>5.1</v>
-      </c>
       <c r="J5">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K5">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L5">
         <v>1.31</v>
@@ -1714,40 +1714,40 @@
         <v>1.04</v>
       </c>
       <c r="N5">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="O5">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P5">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="Q5">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="R5">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="S5">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="T5">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="U5">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="V5">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W5">
         <v>2.28</v>
       </c>
       <c r="X5">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Y5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Z5">
         <v>42</v>
@@ -1756,10 +1756,10 @@
         <v>100</v>
       </c>
       <c r="AB5">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AC5">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD5">
         <v>19</v>
@@ -1771,13 +1771,13 @@
         <v>12.5</v>
       </c>
       <c r="AG5">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH5">
         <v>16</v>
       </c>
       <c r="AI5">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ5">
         <v>18.5</v>
@@ -1786,19 +1786,19 @@
         <v>16</v>
       </c>
       <c r="AL5">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AM5">
         <v>65</v>
       </c>
       <c r="AN5">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AO5">
         <v>42</v>
       </c>
       <c r="AP5">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AQ5">
         <v>22</v>
@@ -1810,19 +1810,19 @@
         <v>85</v>
       </c>
       <c r="AT5">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU5">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV5">
         <v>18</v>
       </c>
       <c r="AW5">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AX5">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AY5">
         <v>9.800000000000001</v>
@@ -1831,7 +1831,7 @@
         <v>15</v>
       </c>
       <c r="BA5">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BB5">
         <v>17</v>
@@ -1843,19 +1843,19 @@
         <v>24</v>
       </c>
       <c r="BE5">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BF5">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BG5">
         <v>36</v>
       </c>
       <c r="BH5">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BI5">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BJ5">
         <v>9.199999999999999</v>
@@ -1864,10 +1864,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BL5">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="BM5">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BN5">
         <v>4.7</v>
@@ -1903,13 +1903,13 @@
         <v>38</v>
       </c>
       <c r="BY5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BZ5">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="CA5">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="CB5" t="s">
         <v>118</v>
@@ -1956,28 +1956,28 @@
         <v>1.09</v>
       </c>
       <c r="N6">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O6">
         <v>1.41</v>
       </c>
       <c r="P6">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="Q6">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="R6">
         <v>1.29</v>
       </c>
       <c r="S6">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="T6">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="U6">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V6">
         <v>1.54</v>
@@ -1992,25 +1992,25 @@
         <v>9.800000000000001</v>
       </c>
       <c r="Z6">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AA6">
         <v>46</v>
       </c>
       <c r="AB6">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AC6">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD6">
         <v>12.5</v>
       </c>
       <c r="AE6">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AF6">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AG6">
         <v>12.5</v>
@@ -2034,7 +2034,7 @@
         <v>120</v>
       </c>
       <c r="AN6">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AO6">
         <v>34</v>
@@ -2058,10 +2058,10 @@
         <v>7.2</v>
       </c>
       <c r="AV6">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AW6">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AX6">
         <v>16</v>
@@ -2070,7 +2070,7 @@
         <v>12</v>
       </c>
       <c r="AZ6">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA6">
         <v>44</v>
@@ -2079,13 +2079,13 @@
         <v>40</v>
       </c>
       <c r="BC6">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BD6">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BE6">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="BF6">
         <v>30</v>
@@ -2094,64 +2094,64 @@
         <v>30</v>
       </c>
       <c r="BH6">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="BI6">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="BJ6">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK6">
-        <v>2.38</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL6">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="BM6">
+        <v>12</v>
+      </c>
+      <c r="BN6">
+        <v>5.7</v>
+      </c>
+      <c r="BO6">
+        <v>5.2</v>
+      </c>
+      <c r="BP6">
+        <v>27</v>
+      </c>
+      <c r="BQ6">
         <v>8.800000000000001</v>
       </c>
-      <c r="BN6">
-        <v>7.2</v>
-      </c>
-      <c r="BO6">
-        <v>4.5</v>
-      </c>
-      <c r="BP6">
-        <v>1000</v>
-      </c>
-      <c r="BQ6">
-        <v>6.8</v>
-      </c>
       <c r="BR6">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BS6">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="BT6">
-        <v>7.2</v>
+        <v>5.7</v>
       </c>
       <c r="BU6">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BV6">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BW6">
-        <v>6.4</v>
+        <v>8.6</v>
       </c>
       <c r="BX6">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BY6">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="BZ6">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA6">
-        <v>7.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB6" t="s">
         <v>118</v>
@@ -2180,16 +2180,16 @@
         <v>1.22</v>
       </c>
       <c r="H7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I7">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="J7">
+        <v>7.8</v>
+      </c>
+      <c r="K7">
         <v>8</v>
-      </c>
-      <c r="K7">
-        <v>8.199999999999999</v>
       </c>
       <c r="L7">
         <v>1.28</v>
@@ -2198,28 +2198,28 @@
         <v>1.03</v>
       </c>
       <c r="N7">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="O7">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P7">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="Q7">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="R7">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="S7">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="T7">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="U7">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="V7">
         <v>1.05</v>
@@ -2231,7 +2231,7 @@
         <v>28</v>
       </c>
       <c r="Y7">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="Z7">
         <v>220</v>
@@ -2246,10 +2246,10 @@
         <v>18</v>
       </c>
       <c r="AD7">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AE7">
-        <v>450</v>
+        <v>520</v>
       </c>
       <c r="AF7">
         <v>7.6</v>
@@ -2258,25 +2258,25 @@
         <v>11.5</v>
       </c>
       <c r="AH7">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AI7">
-        <v>240</v>
+        <v>330</v>
       </c>
       <c r="AJ7">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AK7">
         <v>14.5</v>
       </c>
       <c r="AL7">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM7">
         <v>260</v>
       </c>
       <c r="AN7">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="AO7">
         <v>570</v>
@@ -2285,61 +2285,61 @@
         <v>27</v>
       </c>
       <c r="AQ7">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AR7">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="AS7">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AT7">
         <v>9</v>
       </c>
       <c r="AU7">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AV7">
         <v>55</v>
       </c>
       <c r="AW7">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AX7">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AY7">
         <v>11</v>
       </c>
       <c r="AZ7">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BA7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BB7">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC7">
         <v>13.5</v>
       </c>
       <c r="BD7">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BE7">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="BF7">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="BG7">
-        <v>25</v>
+        <v>95</v>
       </c>
       <c r="BH7">
         <v>4.5</v>
       </c>
       <c r="BI7">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BJ7">
         <v>15</v>
@@ -2369,25 +2369,25 @@
         <v>28</v>
       </c>
       <c r="BS7">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="BT7">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="BU7">
         <v>15.5</v>
       </c>
       <c r="BV7">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="BW7">
-        <v>11</v>
+        <v>15.5</v>
       </c>
       <c r="BX7">
         <v>140</v>
       </c>
       <c r="BY7">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="BZ7">
         <v>0</v>
@@ -2428,40 +2428,40 @@
         <v>2.86</v>
       </c>
       <c r="J8">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K8">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L8">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="M8">
         <v>1.03</v>
       </c>
       <c r="N8">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="O8">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P8">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="Q8">
         <v>1.5</v>
       </c>
       <c r="R8">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="S8">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="T8">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="U8">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="V8">
         <v>1.53</v>
@@ -2470,37 +2470,37 @@
         <v>1.64</v>
       </c>
       <c r="X8">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Y8">
         <v>20</v>
       </c>
       <c r="Z8">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA8">
         <v>44</v>
       </c>
       <c r="AB8">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AC8">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD8">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE8">
         <v>25</v>
       </c>
       <c r="AF8">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG8">
         <v>12.5</v>
       </c>
       <c r="AH8">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AI8">
         <v>27</v>
@@ -2509,10 +2509,10 @@
         <v>38</v>
       </c>
       <c r="AK8">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AM8">
         <v>44</v>
@@ -2530,25 +2530,25 @@
         <v>19</v>
       </c>
       <c r="AR8">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AS8">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AT8">
         <v>18</v>
       </c>
       <c r="AU8">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV8">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AW8">
         <v>23</v>
       </c>
       <c r="AX8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY8">
         <v>11.5</v>
@@ -2569,43 +2569,43 @@
         <v>23</v>
       </c>
       <c r="BE8">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BF8">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BG8">
         <v>12</v>
       </c>
       <c r="BH8">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BI8">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BJ8">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BK8">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BL8">
         <v>65</v>
       </c>
       <c r="BM8">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BN8">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BO8">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BP8">
         <v>16.5</v>
       </c>
       <c r="BQ8">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BR8">
         <v>22</v>
@@ -2614,16 +2614,16 @@
         <v>10</v>
       </c>
       <c r="BT8">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BU8">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BV8">
         <v>19</v>
       </c>
       <c r="BW8">
-        <v>11.5</v>
+        <v>16</v>
       </c>
       <c r="BX8">
         <v>23</v>
@@ -2635,7 +2635,7 @@
         <v>13.5</v>
       </c>
       <c r="CA8">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="CB8" t="s">
         <v>118</v>
@@ -2658,58 +2658,58 @@
         <v>112</v>
       </c>
       <c r="F9">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="G9">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="H9">
+        <v>3.35</v>
+      </c>
+      <c r="I9">
+        <v>3.4</v>
+      </c>
+      <c r="J9">
         <v>3.3</v>
       </c>
-      <c r="I9">
+      <c r="K9">
         <v>3.35</v>
       </c>
-      <c r="J9">
-        <v>3.25</v>
-      </c>
-      <c r="K9">
-        <v>3.3</v>
-      </c>
       <c r="L9">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="M9">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N9">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O9">
         <v>1.46</v>
       </c>
       <c r="P9">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="Q9">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="R9">
         <v>1.25</v>
       </c>
       <c r="S9">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="T9">
         <v>2.02</v>
       </c>
       <c r="U9">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="V9">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W9">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="X9">
         <v>10</v>
@@ -2727,19 +2727,19 @@
         <v>8.4</v>
       </c>
       <c r="AC9">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AD9">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE9">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF9">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG9">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH9">
         <v>21</v>
@@ -2757,7 +2757,7 @@
         <v>55</v>
       </c>
       <c r="AM9">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN9">
         <v>30</v>
@@ -2769,13 +2769,13 @@
         <v>9.6</v>
       </c>
       <c r="AQ9">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR9">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AS9">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AT9">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>13.5</v>
       </c>
       <c r="AW9">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AX9">
         <v>13.5</v>
@@ -2796,7 +2796,7 @@
         <v>11</v>
       </c>
       <c r="AZ9">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA9">
         <v>55</v>
@@ -2805,25 +2805,25 @@
         <v>32</v>
       </c>
       <c r="BC9">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BD9">
         <v>48</v>
       </c>
       <c r="BE9">
-        <v>29</v>
+        <v>100</v>
       </c>
       <c r="BF9">
         <v>27</v>
       </c>
       <c r="BG9">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="BH9">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="BI9">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="BJ9">
         <v>10.5</v>
@@ -2835,7 +2835,7 @@
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BN9">
         <v>5.2</v>
@@ -2847,37 +2847,37 @@
         <v>21</v>
       </c>
       <c r="BQ9">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BR9">
         <v>40</v>
       </c>
       <c r="BS9">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BT9">
         <v>6.4</v>
       </c>
       <c r="BU9">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BV9">
         <v>30</v>
       </c>
       <c r="BW9">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BX9">
         <v>48</v>
       </c>
       <c r="BY9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BZ9">
         <v>40</v>
       </c>
       <c r="CA9">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="CB9" t="s">
         <v>118</v>
@@ -2903,7 +2903,7 @@
         <v>1.46</v>
       </c>
       <c r="G10">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="H10">
         <v>7.6</v>
@@ -2930,40 +2930,40 @@
         <v>1.18</v>
       </c>
       <c r="P10">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="Q10">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="R10">
         <v>1.7</v>
       </c>
       <c r="S10">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="T10">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="U10">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="V10">
         <v>1.14</v>
       </c>
       <c r="W10">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="X10">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="Y10">
         <v>34</v>
       </c>
       <c r="Z10">
-        <v>160</v>
+        <v>85</v>
       </c>
       <c r="AA10">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="AB10">
         <v>12</v>
@@ -2975,22 +2975,22 @@
         <v>28</v>
       </c>
       <c r="AE10">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="AF10">
         <v>10.5</v>
       </c>
       <c r="AG10">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH10">
         <v>21</v>
       </c>
       <c r="AI10">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AJ10">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AK10">
         <v>13.5</v>
@@ -2999,7 +2999,7 @@
         <v>28</v>
       </c>
       <c r="AM10">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AN10">
         <v>5.2</v>
@@ -3011,28 +3011,28 @@
         <v>25</v>
       </c>
       <c r="AQ10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AR10">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AS10">
-        <v>18.5</v>
+        <v>36</v>
       </c>
       <c r="AT10">
         <v>11</v>
       </c>
       <c r="AU10">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AV10">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW10">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AX10">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AY10">
         <v>9.800000000000001</v>
@@ -3056,16 +3056,16 @@
         <v>75</v>
       </c>
       <c r="BF10">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BG10">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="BH10">
         <v>4.6</v>
       </c>
       <c r="BI10">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BJ10">
         <v>12</v>
@@ -3077,7 +3077,7 @@
         <v>120</v>
       </c>
       <c r="BM10">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN10">
         <v>4.3</v>
@@ -3095,25 +3095,25 @@
         <v>24</v>
       </c>
       <c r="BS10">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BT10">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BU10">
-        <v>9.800000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="BV10">
         <v>65</v>
       </c>
       <c r="BW10">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX10">
         <v>60</v>
       </c>
       <c r="BY10">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ10">
         <v>11.5</v>
@@ -3142,55 +3142,55 @@
         <v>114</v>
       </c>
       <c r="F11">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="G11">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H11">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="I11">
-        <v>2.82</v>
+        <v>2.7</v>
       </c>
       <c r="J11">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K11">
         <v>3.55</v>
       </c>
       <c r="L11">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="M11">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N11">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="O11">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="P11">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="Q11">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="R11">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S11">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="T11">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="U11">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V11">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="W11">
         <v>1.48</v>
@@ -3205,10 +3205,10 @@
         <v>21</v>
       </c>
       <c r="AA11">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AB11">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC11">
         <v>8</v>
@@ -3217,7 +3217,7 @@
         <v>12.5</v>
       </c>
       <c r="AE11">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF11">
         <v>21</v>
@@ -3226,13 +3226,13 @@
         <v>13.5</v>
       </c>
       <c r="AH11">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI11">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AJ11">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AK11">
         <v>36</v>
@@ -3247,7 +3247,7 @@
         <v>38</v>
       </c>
       <c r="AO11">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AP11">
         <v>9.800000000000001</v>
@@ -3283,19 +3283,19 @@
         <v>15</v>
       </c>
       <c r="BA11">
-        <v>34</v>
+        <v>6.6</v>
       </c>
       <c r="BB11">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BC11">
         <v>14.5</v>
       </c>
       <c r="BD11">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="BE11">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BF11">
         <v>6.4</v>
@@ -3304,64 +3304,64 @@
         <v>6.2</v>
       </c>
       <c r="BH11">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="BI11">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="BJ11">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK11">
-        <v>7.2</v>
+        <v>3.4</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BN11">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BO11">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BP11">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BQ11">
-        <v>16.5</v>
+        <v>4.1</v>
       </c>
       <c r="BR11">
         <v>46</v>
       </c>
       <c r="BS11">
-        <v>26</v>
+        <v>4.4</v>
       </c>
       <c r="BT11">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BU11">
+        <v>4.2</v>
+      </c>
+      <c r="BV11">
+        <v>25</v>
+      </c>
+      <c r="BW11">
+        <v>4</v>
+      </c>
+      <c r="BX11">
+        <v>42</v>
+      </c>
+      <c r="BY11">
         <v>4.3</v>
       </c>
-      <c r="BV11">
-        <v>27</v>
-      </c>
-      <c r="BW11">
-        <v>16</v>
-      </c>
-      <c r="BX11">
-        <v>44</v>
-      </c>
-      <c r="BY11">
-        <v>26</v>
-      </c>
       <c r="BZ11">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="CA11">
-        <v>22</v>
+        <v>4.2</v>
       </c>
       <c r="CB11" t="s">
         <v>118</v>
@@ -3384,226 +3384,226 @@
         <v>115</v>
       </c>
       <c r="F12">
-        <v>1.55</v>
+        <v>2.2</v>
       </c>
       <c r="G12">
-        <v>5.8</v>
+        <v>2.32</v>
       </c>
       <c r="H12">
-        <v>2.14</v>
+        <v>3.8</v>
       </c>
       <c r="I12">
+        <v>4.2</v>
+      </c>
+      <c r="J12">
+        <v>3.1</v>
+      </c>
+      <c r="K12">
+        <v>3.35</v>
+      </c>
+      <c r="L12">
+        <v>1.57</v>
+      </c>
+      <c r="M12">
+        <v>1.12</v>
+      </c>
+      <c r="N12">
+        <v>2.72</v>
+      </c>
+      <c r="O12">
+        <v>1.53</v>
+      </c>
+      <c r="P12">
+        <v>1.56</v>
+      </c>
+      <c r="Q12">
+        <v>2.62</v>
+      </c>
+      <c r="R12">
+        <v>1.21</v>
+      </c>
+      <c r="S12">
+        <v>5.3</v>
+      </c>
+      <c r="T12">
+        <v>2.08</v>
+      </c>
+      <c r="U12">
+        <v>1.76</v>
+      </c>
+      <c r="V12">
+        <v>1.31</v>
+      </c>
+      <c r="W12">
+        <v>1.75</v>
+      </c>
+      <c r="X12">
+        <v>10.5</v>
+      </c>
+      <c r="Y12">
+        <v>13.5</v>
+      </c>
+      <c r="Z12">
+        <v>34</v>
+      </c>
+      <c r="AA12">
+        <v>120</v>
+      </c>
+      <c r="AB12">
+        <v>8.6</v>
+      </c>
+      <c r="AC12">
+        <v>7.6</v>
+      </c>
+      <c r="AD12">
+        <v>22</v>
+      </c>
+      <c r="AE12">
+        <v>85</v>
+      </c>
+      <c r="AF12">
+        <v>15.5</v>
+      </c>
+      <c r="AG12">
+        <v>14.5</v>
+      </c>
+      <c r="AH12">
+        <v>28</v>
+      </c>
+      <c r="AI12">
         <v>110</v>
       </c>
-      <c r="J12">
-        <v>2.7</v>
-      </c>
-      <c r="K12">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="L12">
-        <v>1.01</v>
-      </c>
-      <c r="M12">
-        <v>1.01</v>
-      </c>
-      <c r="N12">
-        <v>1.09</v>
-      </c>
-      <c r="O12">
-        <v>1.02</v>
-      </c>
-      <c r="P12">
-        <v>1.98</v>
-      </c>
-      <c r="Q12">
-        <v>1.5</v>
-      </c>
-      <c r="R12">
-        <v>1.08</v>
-      </c>
-      <c r="S12">
-        <v>1.5</v>
-      </c>
-      <c r="T12">
-        <v>1.04</v>
-      </c>
-      <c r="U12">
-        <v>1.01</v>
-      </c>
-      <c r="V12">
-        <v>1.1</v>
-      </c>
-      <c r="W12">
-        <v>1.45</v>
-      </c>
-      <c r="X12">
-        <v>500</v>
-      </c>
-      <c r="Y12">
-        <v>500</v>
-      </c>
-      <c r="Z12">
-        <v>500</v>
-      </c>
-      <c r="AA12">
-        <v>900</v>
-      </c>
-      <c r="AB12">
-        <v>500</v>
-      </c>
-      <c r="AC12">
-        <v>500</v>
-      </c>
-      <c r="AD12">
-        <v>500</v>
-      </c>
-      <c r="AE12">
-        <v>500</v>
-      </c>
-      <c r="AF12">
-        <v>500</v>
-      </c>
-      <c r="AG12">
-        <v>500</v>
-      </c>
-      <c r="AH12">
-        <v>500</v>
-      </c>
-      <c r="AI12">
-        <v>500</v>
-      </c>
       <c r="AJ12">
-        <v>900</v>
+        <v>40</v>
       </c>
       <c r="AK12">
-        <v>500</v>
+        <v>38</v>
       </c>
       <c r="AL12">
-        <v>500</v>
+        <v>70</v>
       </c>
       <c r="AM12">
         <v>500</v>
       </c>
       <c r="AN12">
-        <v>500</v>
+        <v>38</v>
       </c>
       <c r="AO12">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AP12">
-        <v>1.21</v>
+        <v>7.8</v>
       </c>
       <c r="AQ12">
-        <v>1.19</v>
+        <v>9.4</v>
       </c>
       <c r="AR12">
-        <v>1.2</v>
+        <v>20</v>
       </c>
       <c r="AS12">
-        <v>1.2</v>
+        <v>4.6</v>
       </c>
       <c r="AT12">
-        <v>1.18</v>
+        <v>6.4</v>
       </c>
       <c r="AU12">
-        <v>1.18</v>
+        <v>6.2</v>
       </c>
       <c r="AV12">
-        <v>1.19</v>
+        <v>14.5</v>
       </c>
       <c r="AW12">
-        <v>1.2</v>
+        <v>4.6</v>
       </c>
       <c r="AX12">
-        <v>1.19</v>
+        <v>10.5</v>
       </c>
       <c r="AY12">
-        <v>1.18</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ12">
-        <v>1.19</v>
+        <v>16.5</v>
       </c>
       <c r="BA12">
-        <v>1.21</v>
+        <v>4.6</v>
       </c>
       <c r="BB12">
-        <v>1.2</v>
+        <v>4.4</v>
       </c>
       <c r="BC12">
-        <v>1.19</v>
+        <v>4.3</v>
       </c>
       <c r="BD12">
-        <v>1.2</v>
+        <v>4.5</v>
       </c>
       <c r="BE12">
-        <v>1.21</v>
+        <v>4.7</v>
       </c>
       <c r="BF12">
-        <v>1.55</v>
+        <v>4.3</v>
       </c>
       <c r="BG12">
-        <v>1.55</v>
+        <v>4.6</v>
       </c>
       <c r="BH12">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="BI12">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="BJ12">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK12">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BN12">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BO12">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BP12">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BQ12">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BR12">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS12">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BT12">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BU12">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BV12">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BW12">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BX12">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BY12">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BZ12">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="CA12">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="CB12" t="s">
         <v>118</v>
@@ -3626,22 +3626,22 @@
         <v>116</v>
       </c>
       <c r="F13">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="G13">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="H13">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="I13">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="J13">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="K13">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="L13">
         <v>1.7</v>
@@ -3650,7 +3650,7 @@
         <v>1.16</v>
       </c>
       <c r="N13">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="O13">
         <v>1.7</v>
@@ -3662,22 +3662,22 @@
         <v>3.25</v>
       </c>
       <c r="R13">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="S13">
         <v>6.8</v>
       </c>
       <c r="T13">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="U13">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="V13">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W13">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="X13">
         <v>7</v>
@@ -3731,7 +3731,7 @@
         <v>130</v>
       </c>
       <c r="AO13">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AP13">
         <v>5.9</v>
@@ -3746,10 +3746,10 @@
         <v>30</v>
       </c>
       <c r="AT13">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU13">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AV13">
         <v>11.5</v>
@@ -3764,82 +3764,82 @@
         <v>14.5</v>
       </c>
       <c r="AZ13">
+        <v>23</v>
+      </c>
+      <c r="BA13">
+        <v>9</v>
+      </c>
+      <c r="BB13">
         <v>22</v>
       </c>
-      <c r="BA13">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BB13">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BC13">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD13">
-        <v>9.4</v>
+        <v>32</v>
       </c>
       <c r="BE13">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF13">
         <v>9.4</v>
       </c>
       <c r="BG13">
-        <v>8.6</v>
+        <v>38</v>
       </c>
       <c r="BH13">
-        <v>1000</v>
+        <v>2.52</v>
       </c>
       <c r="BI13">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="BJ13">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK13">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BN13">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BO13">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BP13">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BQ13">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR13">
         <v>1000</v>
       </c>
       <c r="BS13">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT13">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BU13">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BV13">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BW13">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BX13">
         <v>1000</v>
       </c>
       <c r="BY13">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BZ13">
         <v>0</v>
@@ -3868,175 +3868,175 @@
         <v>117</v>
       </c>
       <c r="F14">
+        <v>2.24</v>
+      </c>
+      <c r="G14">
+        <v>2.42</v>
+      </c>
+      <c r="H14">
+        <v>3.55</v>
+      </c>
+      <c r="I14">
+        <v>4.1</v>
+      </c>
+      <c r="J14">
+        <v>3.1</v>
+      </c>
+      <c r="K14">
+        <v>3.45</v>
+      </c>
+      <c r="L14">
         <v>1.55</v>
       </c>
-      <c r="G14">
-        <v>110</v>
-      </c>
-      <c r="H14">
-        <v>2.14</v>
-      </c>
-      <c r="I14">
-        <v>110</v>
-      </c>
-      <c r="J14">
-        <v>2.7</v>
-      </c>
-      <c r="K14">
-        <v>10</v>
-      </c>
-      <c r="L14">
-        <v>1.01</v>
-      </c>
       <c r="M14">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="N14">
-        <v>1.09</v>
+        <v>2.8</v>
       </c>
       <c r="O14">
-        <v>1.08</v>
+        <v>1.49</v>
       </c>
       <c r="P14">
-        <v>1.09</v>
+        <v>1.58</v>
       </c>
       <c r="Q14">
-        <v>1.46</v>
+        <v>2.5</v>
       </c>
       <c r="R14">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="S14">
-        <v>1.48</v>
+        <v>5</v>
       </c>
       <c r="T14">
-        <v>1.04</v>
+        <v>2</v>
       </c>
       <c r="U14">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="V14">
-        <v>1.1</v>
+        <v>1.33</v>
       </c>
       <c r="W14">
-        <v>1.2</v>
+        <v>1.71</v>
       </c>
       <c r="X14">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y14">
-        <v>160</v>
+        <v>13</v>
       </c>
       <c r="Z14">
-        <v>110</v>
+        <v>28</v>
       </c>
       <c r="AA14">
         <v>900</v>
       </c>
       <c r="AB14">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="AC14">
-        <v>95</v>
+        <v>7.6</v>
       </c>
       <c r="AD14">
-        <v>170</v>
+        <v>19.5</v>
       </c>
       <c r="AE14">
-        <v>260</v>
+        <v>160</v>
       </c>
       <c r="AF14">
-        <v>150</v>
+        <v>15.5</v>
       </c>
       <c r="AG14">
-        <v>120</v>
+        <v>13.5</v>
       </c>
       <c r="AH14">
-        <v>150</v>
+        <v>26</v>
       </c>
       <c r="AI14">
         <v>350</v>
       </c>
       <c r="AJ14">
-        <v>900</v>
+        <v>95</v>
       </c>
       <c r="AK14">
+        <v>34</v>
+      </c>
+      <c r="AL14">
         <v>150</v>
       </c>
-      <c r="AL14">
-        <v>210</v>
-      </c>
       <c r="AM14">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN14">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AO14">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AP14">
-        <v>1.2</v>
+        <v>3.95</v>
       </c>
       <c r="AQ14">
-        <v>1.18</v>
+        <v>4.2</v>
       </c>
       <c r="AR14">
-        <v>1.19</v>
+        <v>5</v>
       </c>
       <c r="AS14">
-        <v>1.2</v>
+        <v>5.8</v>
       </c>
       <c r="AT14">
-        <v>1.17</v>
+        <v>3.5</v>
       </c>
       <c r="AU14">
-        <v>1.17</v>
+        <v>3.4</v>
       </c>
       <c r="AV14">
-        <v>1.18</v>
+        <v>4.7</v>
       </c>
       <c r="AW14">
-        <v>1.2</v>
+        <v>5.7</v>
       </c>
       <c r="AX14">
-        <v>1.18</v>
+        <v>4.4</v>
       </c>
       <c r="AY14">
-        <v>1.17</v>
+        <v>4.2</v>
       </c>
       <c r="AZ14">
-        <v>1.18</v>
+        <v>5</v>
       </c>
       <c r="BA14">
-        <v>1.2</v>
+        <v>5.8</v>
       </c>
       <c r="BB14">
-        <v>1.19</v>
+        <v>5.3</v>
       </c>
       <c r="BC14">
-        <v>1.18</v>
+        <v>5.2</v>
       </c>
       <c r="BD14">
-        <v>1.19</v>
+        <v>5.6</v>
       </c>
       <c r="BE14">
-        <v>1.2</v>
+        <v>6</v>
       </c>
       <c r="BF14">
-        <v>1.55</v>
+        <v>5.2</v>
       </c>
       <c r="BG14">
-        <v>1.55</v>
+        <v>5.8</v>
       </c>
       <c r="BH14">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="BI14">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="BJ14">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK14">
         <v>1.01</v>
@@ -4048,31 +4048,31 @@
         <v>1.01</v>
       </c>
       <c r="BN14">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BO14">
         <v>1.01</v>
       </c>
       <c r="BP14">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BQ14">
         <v>1.01</v>
       </c>
       <c r="BR14">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BS14">
         <v>1.01</v>
       </c>
       <c r="BT14">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU14">
         <v>1.01</v>
       </c>
       <c r="BV14">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BW14">
         <v>1.01</v>
@@ -4084,7 +4084,7 @@
         <v>1.01</v>
       </c>
       <c r="BZ14">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="CA14">
         <v>1.01</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-24.xlsx
@@ -370,7 +370,7 @@
     <t>Vinotinto Ecuador</t>
   </si>
   <si>
-    <t>2026-09-24 03:51:14</t>
+    <t>2026-09-24 06:05:05</t>
   </si>
 </sst>
 </file>
@@ -964,19 +964,19 @@
         <v>105</v>
       </c>
       <c r="F2">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="G2">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="H2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I2">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="J2">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="K2">
         <v>7.2</v>
@@ -988,88 +988,88 @@
         <v>1.02</v>
       </c>
       <c r="N2">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="O2">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="P2">
-        <v>2.22</v>
+        <v>2.56</v>
       </c>
       <c r="Q2">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="R2">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="S2">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="T2">
-        <v>2.12</v>
+        <v>1.92</v>
       </c>
       <c r="U2">
-        <v>1.72</v>
+        <v>1.84</v>
       </c>
       <c r="V2">
         <v>1.06</v>
       </c>
       <c r="W2">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="X2">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="Y2">
         <v>120</v>
       </c>
       <c r="Z2">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="AA2">
         <v>1000</v>
       </c>
       <c r="AB2">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AC2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AD2">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AE2">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="AF2">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AG2">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AH2">
         <v>85</v>
       </c>
       <c r="AI2">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AJ2">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AK2">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AL2">
         <v>120</v>
       </c>
       <c r="AM2">
-        <v>220</v>
+        <v>130</v>
       </c>
       <c r="AN2">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AO2">
-        <v>390</v>
+        <v>280</v>
       </c>
       <c r="AP2">
         <v>5.5</v>
@@ -1078,49 +1078,49 @@
         <v>6</v>
       </c>
       <c r="AR2">
+        <v>6.6</v>
+      </c>
+      <c r="AS2">
         <v>6.8</v>
       </c>
-      <c r="AS2">
-        <v>7</v>
-      </c>
       <c r="AT2">
-        <v>4</v>
+        <v>7.6</v>
       </c>
       <c r="AU2">
-        <v>4.8</v>
+        <v>11</v>
       </c>
       <c r="AV2">
         <v>6.2</v>
       </c>
       <c r="AW2">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AX2">
-        <v>4</v>
+        <v>6.4</v>
       </c>
       <c r="AY2">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AZ2">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BA2">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BB2">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BC2">
         <v>10.5</v>
       </c>
       <c r="BD2">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BE2">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BF2">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="BG2">
         <v>10.5</v>
@@ -1129,61 +1129,61 @@
         <v>4.5</v>
       </c>
       <c r="BI2">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BJ2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BK2">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BN2">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BO2">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="BP2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BQ2">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BR2">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BS2">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BT2">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="BU2">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ2">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="CA2">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="CB2" t="s">
         <v>118</v>
@@ -1206,58 +1206,58 @@
         <v>106</v>
       </c>
       <c r="F3">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="G3">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="H3">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="I3">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="J3">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="K3">
         <v>2.96</v>
       </c>
       <c r="L3">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="M3">
         <v>1.18</v>
       </c>
       <c r="N3">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="O3">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="P3">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Q3">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="R3">
         <v>1.13</v>
       </c>
       <c r="S3">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="T3">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="U3">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="V3">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="W3">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="X3">
         <v>6.6</v>
@@ -1266,49 +1266,49 @@
         <v>6.4</v>
       </c>
       <c r="Z3">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AA3">
         <v>40</v>
       </c>
       <c r="AB3">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC3">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD3">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE3">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AF3">
         <v>24</v>
       </c>
       <c r="AG3">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AH3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AI3">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AJ3">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AK3">
         <v>80</v>
       </c>
       <c r="AL3">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AM3">
         <v>500</v>
       </c>
       <c r="AN3">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AO3">
         <v>55</v>
@@ -1320,7 +1320,7 @@
         <v>6.2</v>
       </c>
       <c r="AR3">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AS3">
         <v>36</v>
@@ -1329,103 +1329,103 @@
         <v>8.4</v>
       </c>
       <c r="AU3">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV3">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AW3">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AX3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ3">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BA3">
         <v>80</v>
       </c>
       <c r="BB3">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BC3">
         <v>65</v>
       </c>
       <c r="BD3">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="BE3">
         <v>110</v>
       </c>
       <c r="BF3">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="BG3">
         <v>42</v>
       </c>
       <c r="BH3">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="BI3">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="BJ3">
         <v>13.5</v>
       </c>
       <c r="BK3">
-        <v>10.5</v>
+        <v>7.4</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>18.5</v>
+        <v>14</v>
       </c>
       <c r="BN3">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BO3">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BP3">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BQ3">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="BR3">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BS3">
-        <v>2.06</v>
+        <v>12.5</v>
       </c>
       <c r="BT3">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BU3">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BV3">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BW3">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="BX3">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY3">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>2.06</v>
+        <v>12.5</v>
       </c>
       <c r="CB3" t="s">
         <v>118</v>
@@ -1448,7 +1448,7 @@
         <v>107</v>
       </c>
       <c r="F4">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="G4">
         <v>15.5</v>
@@ -1472,16 +1472,16 @@
         <v>1.08</v>
       </c>
       <c r="N4">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O4">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P4">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="Q4">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="R4">
         <v>1.28</v>
@@ -1493,31 +1493,31 @@
         <v>3</v>
       </c>
       <c r="U4">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="V4">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="W4">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X4">
         <v>12.5</v>
       </c>
       <c r="Y4">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Z4">
         <v>5.8</v>
       </c>
       <c r="AA4">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AB4">
         <v>32</v>
       </c>
       <c r="AC4">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AD4">
         <v>12</v>
@@ -1526,13 +1526,13 @@
         <v>19</v>
       </c>
       <c r="AF4">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="AG4">
         <v>70</v>
       </c>
       <c r="AH4">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="AI4">
         <v>80</v>
@@ -1541,73 +1541,73 @@
         <v>1000</v>
       </c>
       <c r="AK4">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="AL4">
-        <v>400</v>
+        <v>460</v>
       </c>
       <c r="AM4">
         <v>540</v>
       </c>
       <c r="AN4">
-        <v>820</v>
+        <v>1000</v>
       </c>
       <c r="AO4">
         <v>8</v>
       </c>
       <c r="AP4">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AQ4">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AR4">
         <v>5.7</v>
       </c>
       <c r="AS4">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AT4">
         <v>27</v>
       </c>
       <c r="AU4">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AV4">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AW4">
         <v>17.5</v>
       </c>
       <c r="AX4">
-        <v>28</v>
+        <v>85</v>
       </c>
       <c r="AY4">
         <v>50</v>
       </c>
       <c r="AZ4">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BA4">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="BB4">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="BC4">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="BD4">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BE4">
         <v>28</v>
       </c>
       <c r="BF4">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="BG4">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH4">
         <v>3.2</v>
@@ -1616,58 +1616,58 @@
         <v>2.98</v>
       </c>
       <c r="BJ4">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BK4">
-        <v>12.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BN4">
         <v>18</v>
       </c>
       <c r="BO4">
-        <v>13.5</v>
+        <v>9.6</v>
       </c>
       <c r="BP4">
         <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="BT4">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BU4">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BV4">
         <v>8</v>
       </c>
       <c r="BW4">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="BZ4">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="CA4">
-        <v>13</v>
+        <v>9.6</v>
       </c>
       <c r="CB4" t="s">
         <v>118</v>
@@ -1690,82 +1690,82 @@
         <v>108</v>
       </c>
       <c r="F5">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="G5">
-        <v>1.77</v>
+        <v>1.89</v>
       </c>
       <c r="H5">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="I5">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="J5">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="K5">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="L5">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M5">
         <v>1.04</v>
       </c>
       <c r="N5">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="O5">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="P5">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="Q5">
+        <v>1.65</v>
+      </c>
+      <c r="R5">
         <v>1.59</v>
       </c>
-      <c r="R5">
-        <v>1.65</v>
-      </c>
       <c r="S5">
-        <v>2.48</v>
+        <v>2.66</v>
       </c>
       <c r="T5">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="U5">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="V5">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="W5">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="X5">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="Y5">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="Z5">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AA5">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AB5">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC5">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD5">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AE5">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AF5">
         <v>12.5</v>
@@ -1774,127 +1774,127 @@
         <v>10</v>
       </c>
       <c r="AH5">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI5">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AJ5">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AK5">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL5">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AM5">
         <v>65</v>
       </c>
       <c r="AN5">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="AO5">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AP5">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AQ5">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AR5">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AS5">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AT5">
         <v>12</v>
       </c>
       <c r="AU5">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV5">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AW5">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AX5">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AY5">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ5">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA5">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BB5">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="BC5">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BD5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BE5">
         <v>55</v>
       </c>
       <c r="BF5">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="BG5">
         <v>36</v>
       </c>
       <c r="BH5">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BI5">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="BJ5">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BK5">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BL5">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BM5">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN5">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BO5">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BP5">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BQ5">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BR5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BS5">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BT5">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BU5">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="BV5">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BW5">
         <v>11</v>
@@ -1903,13 +1903,13 @@
         <v>38</v>
       </c>
       <c r="BY5">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BZ5">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="CA5">
-        <v>7.6</v>
+        <v>13.5</v>
       </c>
       <c r="CB5" t="s">
         <v>118</v>
@@ -1932,79 +1932,79 @@
         <v>109</v>
       </c>
       <c r="F6">
+        <v>2.84</v>
+      </c>
+      <c r="G6">
+        <v>2.86</v>
+      </c>
+      <c r="H6">
+        <v>2.78</v>
+      </c>
+      <c r="I6">
         <v>2.8</v>
       </c>
-      <c r="G6">
-        <v>2.84</v>
-      </c>
-      <c r="H6">
-        <v>2.8</v>
-      </c>
-      <c r="I6">
-        <v>2.82</v>
-      </c>
       <c r="J6">
+        <v>3.4</v>
+      </c>
+      <c r="K6">
         <v>3.45</v>
       </c>
-      <c r="K6">
-        <v>3.5</v>
-      </c>
       <c r="L6">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="M6">
         <v>1.09</v>
       </c>
       <c r="N6">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="O6">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="P6">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="Q6">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="R6">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S6">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="T6">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="U6">
         <v>2.04</v>
       </c>
       <c r="V6">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W6">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="X6">
         <v>12</v>
       </c>
       <c r="Y6">
+        <v>9.6</v>
+      </c>
+      <c r="Z6">
+        <v>16.5</v>
+      </c>
+      <c r="AA6">
+        <v>44</v>
+      </c>
+      <c r="AB6">
         <v>9.800000000000001</v>
-      </c>
-      <c r="Z6">
-        <v>17.5</v>
-      </c>
-      <c r="AA6">
-        <v>46</v>
-      </c>
-      <c r="AB6">
-        <v>9.6</v>
       </c>
       <c r="AC6">
         <v>7.4</v>
       </c>
       <c r="AD6">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE6">
         <v>36</v>
@@ -2025,7 +2025,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AL6">
         <v>50</v>
@@ -2052,7 +2052,7 @@
         <v>40</v>
       </c>
       <c r="AT6">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU6">
         <v>7.2</v>
@@ -2061,22 +2061,22 @@
         <v>11.5</v>
       </c>
       <c r="AW6">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AX6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AY6">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AZ6">
         <v>18</v>
       </c>
       <c r="BA6">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BB6">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BC6">
         <v>32</v>
@@ -2085,19 +2085,19 @@
         <v>46</v>
       </c>
       <c r="BE6">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BF6">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BG6">
         <v>30</v>
       </c>
       <c r="BH6">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BI6">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="BJ6">
         <v>10.5</v>
@@ -2106,37 +2106,37 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BL6">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="BM6">
         <v>12</v>
       </c>
       <c r="BN6">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BO6">
         <v>5.2</v>
       </c>
       <c r="BP6">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BQ6">
         <v>8.800000000000001</v>
       </c>
       <c r="BR6">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BS6">
         <v>10</v>
       </c>
       <c r="BT6">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BU6">
         <v>5.1</v>
       </c>
       <c r="BV6">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BW6">
         <v>8.6</v>
@@ -2148,10 +2148,10 @@
         <v>10</v>
       </c>
       <c r="BZ6">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="CA6">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="CB6" t="s">
         <v>118</v>
@@ -2174,10 +2174,10 @@
         <v>110</v>
       </c>
       <c r="F7">
+        <v>1.2</v>
+      </c>
+      <c r="G7">
         <v>1.21</v>
-      </c>
-      <c r="G7">
-        <v>1.22</v>
       </c>
       <c r="H7">
         <v>20</v>
@@ -2186,52 +2186,52 @@
         <v>21</v>
       </c>
       <c r="J7">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="K7">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L7">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="M7">
         <v>1.03</v>
       </c>
       <c r="N7">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="O7">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="P7">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="Q7">
-        <v>1.56</v>
+        <v>1.48</v>
       </c>
       <c r="R7">
-        <v>1.68</v>
+        <v>1.81</v>
       </c>
       <c r="S7">
-        <v>2.4</v>
+        <v>2.22</v>
       </c>
       <c r="T7">
-        <v>2.36</v>
+        <v>2.26</v>
       </c>
       <c r="U7">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="V7">
         <v>1.05</v>
       </c>
       <c r="W7">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="X7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Y7">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="Z7">
         <v>220</v>
@@ -2240,154 +2240,154 @@
         <v>1000</v>
       </c>
       <c r="AB7">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="AC7">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AD7">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AE7">
-        <v>520</v>
+        <v>430</v>
       </c>
       <c r="AF7">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AG7">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH7">
         <v>40</v>
       </c>
       <c r="AI7">
-        <v>330</v>
+        <v>230</v>
       </c>
       <c r="AJ7">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AK7">
         <v>14.5</v>
       </c>
       <c r="AL7">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM7">
-        <v>260</v>
+        <v>230</v>
       </c>
       <c r="AN7">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="AO7">
-        <v>570</v>
+        <v>480</v>
       </c>
       <c r="AP7">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ7">
         <v>55</v>
       </c>
       <c r="AR7">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="AS7">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="AT7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AU7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AV7">
         <v>55</v>
       </c>
       <c r="AW7">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="AX7">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AY7">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ7">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BA7">
-        <v>29</v>
+        <v>180</v>
       </c>
       <c r="BB7">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BC7">
         <v>13.5</v>
       </c>
       <c r="BD7">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="BE7">
-        <v>48</v>
+        <v>170</v>
       </c>
       <c r="BF7">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="BG7">
-        <v>95</v>
+        <v>32</v>
       </c>
       <c r="BH7">
+        <v>4.9</v>
+      </c>
+      <c r="BI7">
         <v>4.5</v>
       </c>
-      <c r="BI7">
-        <v>4.2</v>
-      </c>
       <c r="BJ7">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BK7">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BL7">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="BM7">
         <v>23</v>
       </c>
       <c r="BN7">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="BO7">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="BP7">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BQ7">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BR7">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="BS7">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BT7">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BU7">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BV7">
         <v>170</v>
       </c>
       <c r="BW7">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="BX7">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="BY7">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BZ7">
         <v>0</v>
@@ -2416,16 +2416,16 @@
         <v>111</v>
       </c>
       <c r="F8">
-        <v>2.54</v>
+        <v>2.64</v>
       </c>
       <c r="G8">
-        <v>2.56</v>
+        <v>2.68</v>
       </c>
       <c r="H8">
-        <v>2.82</v>
+        <v>2.7</v>
       </c>
       <c r="I8">
-        <v>2.86</v>
+        <v>2.72</v>
       </c>
       <c r="J8">
         <v>3.9</v>
@@ -2434,43 +2434,43 @@
         <v>3.95</v>
       </c>
       <c r="L8">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="M8">
         <v>1.03</v>
       </c>
       <c r="N8">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="O8">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P8">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="Q8">
         <v>1.5</v>
       </c>
       <c r="R8">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="S8">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="T8">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="U8">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="V8">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="W8">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="X8">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y8">
         <v>20</v>
@@ -2482,88 +2482,88 @@
         <v>44</v>
       </c>
       <c r="AB8">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AC8">
         <v>9.4</v>
       </c>
       <c r="AD8">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE8">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG8">
         <v>12.5</v>
       </c>
       <c r="AH8">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AI8">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ8">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AK8">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL8">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AM8">
         <v>44</v>
       </c>
       <c r="AN8">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AO8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AP8">
         <v>26</v>
       </c>
       <c r="AQ8">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AR8">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS8">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AT8">
         <v>18</v>
       </c>
       <c r="AU8">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AV8">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AW8">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AX8">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY8">
         <v>11.5</v>
       </c>
       <c r="AZ8">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BA8">
         <v>25</v>
       </c>
       <c r="BB8">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BC8">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BD8">
         <v>23</v>
@@ -2572,7 +2572,7 @@
         <v>40</v>
       </c>
       <c r="BF8">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BG8">
         <v>12</v>
@@ -2584,58 +2584,58 @@
         <v>4.3</v>
       </c>
       <c r="BJ8">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BK8">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BL8">
         <v>65</v>
       </c>
       <c r="BM8">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="BN8">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BO8">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BP8">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BQ8">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BR8">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BS8">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BT8">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BU8">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BV8">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="BW8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BX8">
         <v>23</v>
       </c>
       <c r="BY8">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BZ8">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="CA8">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="CB8" t="s">
         <v>118</v>
@@ -2658,58 +2658,58 @@
         <v>112</v>
       </c>
       <c r="F9">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="G9">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="H9">
+        <v>3.3</v>
+      </c>
+      <c r="I9">
         <v>3.35</v>
       </c>
-      <c r="I9">
-        <v>3.4</v>
-      </c>
       <c r="J9">
+        <v>3.25</v>
+      </c>
+      <c r="K9">
         <v>3.3</v>
-      </c>
-      <c r="K9">
-        <v>3.35</v>
       </c>
       <c r="L9">
         <v>1.54</v>
       </c>
       <c r="M9">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N9">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="O9">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P9">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="Q9">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="R9">
         <v>1.25</v>
       </c>
       <c r="S9">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="T9">
         <v>2.02</v>
       </c>
       <c r="U9">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="V9">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W9">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="X9">
         <v>10</v>
@@ -2730,7 +2730,7 @@
         <v>7.4</v>
       </c>
       <c r="AD9">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AE9">
         <v>46</v>
@@ -2739,7 +2739,7 @@
         <v>14</v>
       </c>
       <c r="AG9">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH9">
         <v>21</v>
@@ -2760,7 +2760,7 @@
         <v>140</v>
       </c>
       <c r="AN9">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AO9">
         <v>55</v>
@@ -2772,7 +2772,7 @@
         <v>10</v>
       </c>
       <c r="AR9">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AS9">
         <v>55</v>
@@ -2787,7 +2787,7 @@
         <v>13.5</v>
       </c>
       <c r="AW9">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AX9">
         <v>13.5</v>
@@ -2808,7 +2808,7 @@
         <v>29</v>
       </c>
       <c r="BD9">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BE9">
         <v>100</v>
@@ -2817,10 +2817,10 @@
         <v>27</v>
       </c>
       <c r="BG9">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BH9">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="BI9">
         <v>2.7</v>
@@ -2835,7 +2835,7 @@
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BN9">
         <v>5.2</v>
@@ -2844,40 +2844,40 @@
         <v>4.8</v>
       </c>
       <c r="BP9">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BQ9">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BR9">
         <v>40</v>
       </c>
       <c r="BS9">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BT9">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BU9">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BV9">
         <v>30</v>
       </c>
       <c r="BW9">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BX9">
         <v>48</v>
       </c>
       <c r="BY9">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BZ9">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="CA9">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="CB9" t="s">
         <v>118</v>
@@ -2900,22 +2900,22 @@
         <v>113</v>
       </c>
       <c r="F10">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="G10">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="H10">
+        <v>7.4</v>
+      </c>
+      <c r="I10">
         <v>7.6</v>
       </c>
-      <c r="I10">
-        <v>7.8</v>
-      </c>
       <c r="J10">
+        <v>5.1</v>
+      </c>
+      <c r="K10">
         <v>5.2</v>
-      </c>
-      <c r="K10">
-        <v>5.3</v>
       </c>
       <c r="L10">
         <v>1.28</v>
@@ -2936,34 +2936,34 @@
         <v>1.56</v>
       </c>
       <c r="R10">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="S10">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="T10">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="U10">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="V10">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W10">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="X10">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Y10">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Z10">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AA10">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="AB10">
         <v>12</v>
@@ -2972,40 +2972,40 @@
         <v>12</v>
       </c>
       <c r="AD10">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AE10">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AF10">
         <v>10.5</v>
       </c>
       <c r="AG10">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH10">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI10">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AJ10">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AK10">
         <v>13.5</v>
       </c>
       <c r="AL10">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM10">
+        <v>85</v>
+      </c>
+      <c r="AN10">
+        <v>5.3</v>
+      </c>
+      <c r="AO10">
         <v>90</v>
-      </c>
-      <c r="AN10">
-        <v>5.2</v>
-      </c>
-      <c r="AO10">
-        <v>85</v>
       </c>
       <c r="AP10">
         <v>25</v>
@@ -3017,7 +3017,7 @@
         <v>55</v>
       </c>
       <c r="AS10">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="AT10">
         <v>11</v>
@@ -3032,52 +3032,52 @@
         <v>75</v>
       </c>
       <c r="AX10">
+        <v>10</v>
+      </c>
+      <c r="AY10">
         <v>9.6</v>
       </c>
-      <c r="AY10">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AZ10">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA10">
         <v>60</v>
       </c>
       <c r="BB10">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BC10">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BD10">
         <v>25</v>
       </c>
       <c r="BE10">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BF10">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BG10">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BH10">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BI10">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BJ10">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BK10">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL10">
         <v>120</v>
       </c>
       <c r="BM10">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BN10">
         <v>4.3</v>
@@ -3086,40 +3086,40 @@
         <v>3.9</v>
       </c>
       <c r="BP10">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BQ10">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BR10">
         <v>24</v>
       </c>
       <c r="BS10">
-        <v>7</v>
+        <v>16.5</v>
       </c>
       <c r="BT10">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BU10">
-        <v>5.6</v>
+        <v>9.4</v>
       </c>
       <c r="BV10">
         <v>65</v>
       </c>
       <c r="BW10">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BX10">
         <v>60</v>
       </c>
       <c r="BY10">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BZ10">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="CA10">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="CB10" t="s">
         <v>118</v>
@@ -3142,16 +3142,16 @@
         <v>114</v>
       </c>
       <c r="F11">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="G11">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="H11">
         <v>2.58</v>
       </c>
       <c r="I11">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="J11">
         <v>3.35</v>
@@ -3163,55 +3163,55 @@
         <v>1.43</v>
       </c>
       <c r="M11">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N11">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="O11">
         <v>1.34</v>
       </c>
       <c r="P11">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="Q11">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="R11">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S11">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="T11">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U11">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="V11">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W11">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="X11">
         <v>14.5</v>
       </c>
       <c r="Y11">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z11">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AA11">
         <v>40</v>
       </c>
       <c r="AB11">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AC11">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AD11">
         <v>12.5</v>
@@ -3241,79 +3241,79 @@
         <v>55</v>
       </c>
       <c r="AM11">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN11">
         <v>38</v>
       </c>
       <c r="AO11">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AP11">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AQ11">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR11">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AS11">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="AT11">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AU11">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV11">
         <v>10.5</v>
       </c>
       <c r="AW11">
-        <v>14.5</v>
+        <v>22</v>
       </c>
       <c r="AX11">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AY11">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ11">
         <v>15</v>
       </c>
       <c r="BA11">
-        <v>6.6</v>
+        <v>32</v>
       </c>
       <c r="BB11">
-        <v>6.8</v>
+        <v>32</v>
       </c>
       <c r="BC11">
-        <v>14.5</v>
+        <v>26</v>
       </c>
       <c r="BD11">
         <v>36</v>
       </c>
       <c r="BE11">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="BF11">
-        <v>6.4</v>
+        <v>21</v>
       </c>
       <c r="BG11">
-        <v>6.2</v>
+        <v>20</v>
       </c>
       <c r="BH11">
         <v>3.8</v>
       </c>
       <c r="BI11">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="BJ11">
         <v>11.5</v>
       </c>
       <c r="BK11">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BL11">
         <v>1000</v>
@@ -3331,10 +3331,10 @@
         <v>29</v>
       </c>
       <c r="BQ11">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BR11">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BS11">
         <v>4.4</v>
@@ -3346,7 +3346,7 @@
         <v>4.2</v>
       </c>
       <c r="BV11">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BW11">
         <v>4</v>
@@ -3355,13 +3355,13 @@
         <v>42</v>
       </c>
       <c r="BY11">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BZ11">
         <v>36</v>
       </c>
       <c r="CA11">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="CB11" t="s">
         <v>118</v>
@@ -3384,196 +3384,196 @@
         <v>115</v>
       </c>
       <c r="F12">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="G12">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="H12">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="I12">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="J12">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K12">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="L12">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="M12">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N12">
-        <v>2.72</v>
+        <v>2.62</v>
       </c>
       <c r="O12">
+        <v>1.56</v>
+      </c>
+      <c r="P12">
         <v>1.53</v>
       </c>
-      <c r="P12">
-        <v>1.56</v>
-      </c>
       <c r="Q12">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="R12">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="S12">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="T12">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="U12">
+        <v>1.67</v>
+      </c>
+      <c r="V12">
+        <v>1.29</v>
+      </c>
+      <c r="W12">
         <v>1.76</v>
       </c>
-      <c r="V12">
-        <v>1.31</v>
-      </c>
-      <c r="W12">
-        <v>1.75</v>
-      </c>
       <c r="X12">
-        <v>10.5</v>
+        <v>500</v>
       </c>
       <c r="Y12">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="Z12">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="AA12">
-        <v>120</v>
+        <v>900</v>
       </c>
       <c r="AB12">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AC12">
         <v>7.6</v>
       </c>
       <c r="AD12">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="AE12">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AF12">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AG12">
-        <v>14.5</v>
+        <v>500</v>
       </c>
       <c r="AH12">
-        <v>28</v>
+        <v>500</v>
       </c>
       <c r="AI12">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AJ12">
-        <v>40</v>
+        <v>900</v>
       </c>
       <c r="AK12">
-        <v>38</v>
+        <v>500</v>
       </c>
       <c r="AL12">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AM12">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN12">
-        <v>38</v>
+        <v>600</v>
       </c>
       <c r="AO12">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AP12">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="AQ12">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR12">
-        <v>20</v>
+        <v>2.06</v>
       </c>
       <c r="AS12">
-        <v>4.6</v>
+        <v>2.1</v>
       </c>
       <c r="AT12">
-        <v>6.4</v>
+        <v>1.65</v>
       </c>
       <c r="AU12">
         <v>6.2</v>
       </c>
       <c r="AV12">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AW12">
-        <v>4.6</v>
+        <v>2.1</v>
       </c>
       <c r="AX12">
         <v>10.5</v>
       </c>
       <c r="AY12">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ12">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="BA12">
-        <v>4.6</v>
+        <v>2.1</v>
       </c>
       <c r="BB12">
-        <v>4.4</v>
+        <v>2.08</v>
       </c>
       <c r="BC12">
-        <v>4.3</v>
+        <v>2.06</v>
       </c>
       <c r="BD12">
-        <v>4.5</v>
+        <v>2.1</v>
       </c>
       <c r="BE12">
-        <v>4.7</v>
+        <v>2.12</v>
       </c>
       <c r="BF12">
-        <v>4.3</v>
+        <v>2.12</v>
       </c>
       <c r="BG12">
-        <v>4.6</v>
+        <v>2.12</v>
       </c>
       <c r="BH12">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="BI12">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="BJ12">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BK12">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BN12">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BO12">
         <v>4.1</v>
       </c>
       <c r="BP12">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BQ12">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BR12">
         <v>55</v>
@@ -3582,28 +3582,28 @@
         <v>4.6</v>
       </c>
       <c r="BT12">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BU12">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BV12">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BW12">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BX12">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BY12">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BZ12">
         <v>60</v>
       </c>
       <c r="CA12">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="CB12" t="s">
         <v>118</v>
@@ -3626,10 +3626,10 @@
         <v>116</v>
       </c>
       <c r="F13">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="G13">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="H13">
         <v>2.46</v>
@@ -3638,10 +3638,10 @@
         <v>2.62</v>
       </c>
       <c r="J13">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="K13">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="L13">
         <v>1.7</v>
@@ -3656,22 +3656,22 @@
         <v>1.7</v>
       </c>
       <c r="P13">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="Q13">
         <v>3.25</v>
       </c>
       <c r="R13">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="S13">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="T13">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="U13">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="V13">
         <v>1.61</v>
@@ -3683,7 +3683,7 @@
         <v>7</v>
       </c>
       <c r="Y13">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="Z13">
         <v>15</v>
@@ -3707,10 +3707,10 @@
         <v>25</v>
       </c>
       <c r="AG13">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AH13">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AI13">
         <v>190</v>
@@ -3719,7 +3719,7 @@
         <v>900</v>
       </c>
       <c r="AK13">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AL13">
         <v>130</v>
@@ -3728,19 +3728,19 @@
         <v>500</v>
       </c>
       <c r="AN13">
-        <v>130</v>
+        <v>600</v>
       </c>
       <c r="AO13">
-        <v>60</v>
+        <v>600</v>
       </c>
       <c r="AP13">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AQ13">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AR13">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AS13">
         <v>30</v>
@@ -3749,7 +3749,7 @@
         <v>7.4</v>
       </c>
       <c r="AU13">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV13">
         <v>11.5</v>
@@ -3761,40 +3761,40 @@
         <v>20</v>
       </c>
       <c r="AY13">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AZ13">
         <v>23</v>
       </c>
       <c r="BA13">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB13">
         <v>22</v>
       </c>
       <c r="BC13">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BD13">
         <v>32</v>
       </c>
       <c r="BE13">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BF13">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BG13">
         <v>38</v>
       </c>
       <c r="BH13">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="BI13">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="BJ13">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BK13">
         <v>6</v>
@@ -3812,16 +3812,16 @@
         <v>5</v>
       </c>
       <c r="BP13">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BQ13">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BR13">
         <v>1000</v>
       </c>
       <c r="BS13">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BT13">
         <v>5.4</v>
@@ -3833,13 +3833,13 @@
         <v>26</v>
       </c>
       <c r="BW13">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BX13">
         <v>1000</v>
       </c>
       <c r="BY13">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ13">
         <v>0</v>
@@ -3868,22 +3868,22 @@
         <v>117</v>
       </c>
       <c r="F14">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="G14">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="H14">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="I14">
         <v>4.1</v>
       </c>
       <c r="J14">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="K14">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="L14">
         <v>1.55</v>
@@ -3892,151 +3892,151 @@
         <v>1.11</v>
       </c>
       <c r="N14">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="O14">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="P14">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="Q14">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="R14">
         <v>1.2</v>
       </c>
       <c r="S14">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="T14">
-        <v>2</v>
+        <v>1.04</v>
       </c>
       <c r="U14">
-        <v>1.79</v>
+        <v>1.01</v>
       </c>
       <c r="V14">
         <v>1.33</v>
       </c>
       <c r="W14">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="X14">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="Y14">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="Z14">
-        <v>28</v>
+        <v>75</v>
       </c>
       <c r="AA14">
         <v>900</v>
       </c>
       <c r="AB14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC14">
         <v>7.6</v>
       </c>
       <c r="AD14">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AE14">
-        <v>160</v>
+        <v>260</v>
       </c>
       <c r="AF14">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AG14">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AH14">
-        <v>26</v>
+        <v>150</v>
       </c>
       <c r="AI14">
         <v>350</v>
       </c>
       <c r="AJ14">
-        <v>95</v>
+        <v>160</v>
       </c>
       <c r="AK14">
-        <v>34</v>
+        <v>150</v>
       </c>
       <c r="AL14">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="AM14">
-        <v>200</v>
+        <v>580</v>
       </c>
       <c r="AN14">
-        <v>34</v>
+        <v>600</v>
       </c>
       <c r="AO14">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AP14">
-        <v>3.95</v>
+        <v>1.83</v>
       </c>
       <c r="AQ14">
-        <v>4.2</v>
+        <v>1.97</v>
       </c>
       <c r="AR14">
-        <v>5</v>
+        <v>1.91</v>
       </c>
       <c r="AS14">
-        <v>5.8</v>
+        <v>2</v>
       </c>
       <c r="AT14">
-        <v>3.5</v>
+        <v>1.65</v>
       </c>
       <c r="AU14">
-        <v>3.4</v>
+        <v>1.6</v>
       </c>
       <c r="AV14">
-        <v>4.7</v>
+        <v>1.98</v>
       </c>
       <c r="AW14">
-        <v>5.7</v>
+        <v>1.98</v>
       </c>
       <c r="AX14">
-        <v>4.4</v>
+        <v>1.97</v>
       </c>
       <c r="AY14">
-        <v>4.2</v>
+        <v>1.95</v>
       </c>
       <c r="AZ14">
-        <v>5</v>
+        <v>1.96</v>
       </c>
       <c r="BA14">
-        <v>5.8</v>
+        <v>2</v>
       </c>
       <c r="BB14">
-        <v>5.3</v>
+        <v>1.93</v>
       </c>
       <c r="BC14">
-        <v>5.2</v>
+        <v>1.93</v>
       </c>
       <c r="BD14">
-        <v>5.6</v>
+        <v>2</v>
       </c>
       <c r="BE14">
-        <v>6</v>
+        <v>2.02</v>
       </c>
       <c r="BF14">
-        <v>5.2</v>
+        <v>1.93</v>
       </c>
       <c r="BG14">
-        <v>5.8</v>
+        <v>2.02</v>
       </c>
       <c r="BH14">
-        <v>3.1</v>
+        <v>1000</v>
       </c>
       <c r="BI14">
-        <v>2.36</v>
+        <v>1.01</v>
       </c>
       <c r="BJ14">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK14">
         <v>1.01</v>
@@ -4048,31 +4048,31 @@
         <v>1.01</v>
       </c>
       <c r="BN14">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="BO14">
         <v>1.01</v>
       </c>
       <c r="BP14">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BQ14">
         <v>1.01</v>
       </c>
       <c r="BR14">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BS14">
         <v>1.01</v>
       </c>
       <c r="BT14">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BU14">
         <v>1.01</v>
       </c>
       <c r="BV14">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BW14">
         <v>1.01</v>
@@ -4084,7 +4084,7 @@
         <v>1.01</v>
       </c>
       <c r="BZ14">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="CA14">
         <v>1.01</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-24.xlsx
@@ -370,7 +370,7 @@
     <t>Vinotinto Ecuador</t>
   </si>
   <si>
-    <t>2026-09-24 06:05:05</t>
+    <t>2026-09-24 08:19:37</t>
   </si>
 </sst>
 </file>
@@ -964,19 +964,19 @@
         <v>105</v>
       </c>
       <c r="F2">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="G2">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="H2">
         <v>14</v>
       </c>
       <c r="I2">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="J2">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="K2">
         <v>7.2</v>
@@ -988,34 +988,34 @@
         <v>1.02</v>
       </c>
       <c r="N2">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="O2">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P2">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="Q2">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="R2">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="S2">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="T2">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="U2">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="V2">
         <v>1.06</v>
       </c>
       <c r="W2">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="X2">
         <v>48</v>
@@ -1024,13 +1024,13 @@
         <v>120</v>
       </c>
       <c r="Z2">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AA2">
         <v>1000</v>
       </c>
       <c r="AB2">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC2">
         <v>16</v>
@@ -1039,88 +1039,88 @@
         <v>130</v>
       </c>
       <c r="AE2">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="AF2">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AG2">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH2">
         <v>85</v>
       </c>
       <c r="AI2">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AJ2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AK2">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AL2">
         <v>120</v>
       </c>
       <c r="AM2">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="AN2">
         <v>4.6</v>
       </c>
       <c r="AO2">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="AP2">
-        <v>5.5</v>
+        <v>20</v>
       </c>
       <c r="AQ2">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AR2">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AS2">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AT2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU2">
+        <v>12.5</v>
+      </c>
+      <c r="AV2">
+        <v>7</v>
+      </c>
+      <c r="AW2">
         <v>7.6</v>
       </c>
-      <c r="AU2">
-        <v>11</v>
-      </c>
-      <c r="AV2">
-        <v>6.2</v>
-      </c>
-      <c r="AW2">
-        <v>6.6</v>
-      </c>
       <c r="AX2">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AY2">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA2">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BB2">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BC2">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BD2">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BE2">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BF2">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BG2">
         <v>10.5</v>
@@ -1156,22 +1156,22 @@
         <v>5.5</v>
       </c>
       <c r="BR2">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BS2">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BT2">
         <v>15.5</v>
       </c>
       <c r="BU2">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX2">
         <v>1000</v>
@@ -1206,61 +1206,61 @@
         <v>106</v>
       </c>
       <c r="F3">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="G3">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="H3">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="I3">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="J3">
-        <v>2.94</v>
+        <v>2.84</v>
       </c>
       <c r="K3">
-        <v>2.96</v>
+        <v>2.86</v>
       </c>
       <c r="L3">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="M3">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="N3">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="O3">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="P3">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="Q3">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="R3">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="S3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T3">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="U3">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="V3">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="W3">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="X3">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="Y3">
         <v>6.4</v>
@@ -1269,163 +1269,163 @@
         <v>13</v>
       </c>
       <c r="AA3">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AB3">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC3">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AD3">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AE3">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AF3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH3">
         <v>30</v>
       </c>
       <c r="AI3">
+        <v>100</v>
+      </c>
+      <c r="AJ3">
         <v>95</v>
       </c>
-      <c r="AJ3">
-        <v>90</v>
-      </c>
       <c r="AK3">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AL3">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AM3">
         <v>500</v>
       </c>
       <c r="AN3">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AO3">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AP3">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="AQ3">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AR3">
         <v>12.5</v>
       </c>
       <c r="AS3">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AT3">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AU3">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW3">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AX3">
         <v>22</v>
       </c>
       <c r="AY3">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AZ3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BA3">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="BB3">
         <v>75</v>
       </c>
       <c r="BC3">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BD3">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="BE3">
         <v>110</v>
       </c>
       <c r="BF3">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="BG3">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="BH3">
-        <v>2.36</v>
+        <v>2.26</v>
       </c>
       <c r="BI3">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="BJ3">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BK3">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="BN3">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BO3">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BP3">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BQ3">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="BR3">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="BS3">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="BT3">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BU3">
         <v>4.7</v>
       </c>
       <c r="BV3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BW3">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="BX3">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BY3">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="CB3" t="s">
         <v>118</v>
@@ -1448,226 +1448,226 @@
         <v>107</v>
       </c>
       <c r="F4">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G4">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="H4">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="I4">
         <v>1.34</v>
       </c>
       <c r="J4">
+        <v>5.2</v>
+      </c>
+      <c r="K4">
+        <v>5.4</v>
+      </c>
+      <c r="L4">
+        <v>1.53</v>
+      </c>
+      <c r="M4">
+        <v>1.1</v>
+      </c>
+      <c r="N4">
+        <v>2.9</v>
+      </c>
+      <c r="O4">
+        <v>1.51</v>
+      </c>
+      <c r="P4">
+        <v>1.63</v>
+      </c>
+      <c r="Q4">
+        <v>2.56</v>
+      </c>
+      <c r="R4">
+        <v>1.22</v>
+      </c>
+      <c r="S4">
         <v>5.3</v>
       </c>
-      <c r="K4">
-        <v>5.5</v>
-      </c>
-      <c r="L4">
-        <v>1.47</v>
-      </c>
-      <c r="M4">
-        <v>1.08</v>
-      </c>
-      <c r="N4">
-        <v>3.3</v>
-      </c>
-      <c r="O4">
-        <v>1.41</v>
-      </c>
-      <c r="P4">
-        <v>1.77</v>
-      </c>
-      <c r="Q4">
-        <v>2.26</v>
-      </c>
-      <c r="R4">
-        <v>1.28</v>
-      </c>
-      <c r="S4">
-        <v>4.3</v>
-      </c>
       <c r="T4">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="U4">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="V4">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="W4">
         <v>1.06</v>
       </c>
       <c r="X4">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y4">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="Z4">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="AA4">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AB4">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AC4">
+        <v>14</v>
+      </c>
+      <c r="AD4">
         <v>13</v>
       </c>
-      <c r="AD4">
-        <v>12</v>
-      </c>
       <c r="AE4">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AF4">
-        <v>180</v>
+        <v>220</v>
       </c>
       <c r="AG4">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="AH4">
-        <v>65</v>
+        <v>290</v>
       </c>
       <c r="AI4">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AJ4">
         <v>1000</v>
       </c>
       <c r="AK4">
-        <v>500</v>
+        <v>920</v>
       </c>
       <c r="AL4">
-        <v>460</v>
+        <v>780</v>
       </c>
       <c r="AM4">
-        <v>540</v>
+        <v>970</v>
       </c>
       <c r="AN4">
         <v>1000</v>
       </c>
       <c r="AO4">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AP4">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ4">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="AR4">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="AS4">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT4">
+        <v>28</v>
+      </c>
+      <c r="AU4">
+        <v>13</v>
+      </c>
+      <c r="AV4">
+        <v>12.5</v>
+      </c>
+      <c r="AW4">
+        <v>20</v>
+      </c>
+      <c r="AX4">
+        <v>140</v>
+      </c>
+      <c r="AY4">
+        <v>70</v>
+      </c>
+      <c r="AZ4">
+        <v>70</v>
+      </c>
+      <c r="BA4">
+        <v>85</v>
+      </c>
+      <c r="BB4">
+        <v>26</v>
+      </c>
+      <c r="BC4">
         <v>27</v>
       </c>
-      <c r="AU4">
-        <v>12</v>
-      </c>
-      <c r="AV4">
-        <v>11</v>
-      </c>
-      <c r="AW4">
-        <v>17.5</v>
-      </c>
-      <c r="AX4">
-        <v>85</v>
-      </c>
-      <c r="AY4">
-        <v>50</v>
-      </c>
-      <c r="AZ4">
-        <v>50</v>
-      </c>
-      <c r="BA4">
-        <v>70</v>
-      </c>
-      <c r="BB4">
-        <v>90</v>
-      </c>
-      <c r="BC4">
-        <v>24</v>
-      </c>
       <c r="BD4">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="BE4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BF4">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="BG4">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH4">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="BI4">
-        <v>2.98</v>
+        <v>2.74</v>
       </c>
       <c r="BJ4">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="BK4">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
+        <v>2.78</v>
+      </c>
+      <c r="BN4">
         <v>19.5</v>
       </c>
-      <c r="BN4">
-        <v>18</v>
-      </c>
       <c r="BO4">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BP4">
         <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>19</v>
+        <v>2.76</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>18.5</v>
+        <v>2.76</v>
       </c>
       <c r="BT4">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="BU4">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="BV4">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BW4">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="BZ4">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="CA4">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="CB4" t="s">
         <v>118</v>
@@ -1690,16 +1690,16 @@
         <v>108</v>
       </c>
       <c r="F5">
+        <v>1.87</v>
+      </c>
+      <c r="G5">
         <v>1.88</v>
       </c>
-      <c r="G5">
-        <v>1.89</v>
-      </c>
       <c r="H5">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I5">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J5">
         <v>4</v>
@@ -1726,28 +1726,28 @@
         <v>1.65</v>
       </c>
       <c r="R5">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="S5">
         <v>2.66</v>
       </c>
       <c r="T5">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="U5">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="V5">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W5">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="X5">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z5">
         <v>36</v>
@@ -1759,13 +1759,13 @@
         <v>12.5</v>
       </c>
       <c r="AC5">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AD5">
         <v>17</v>
       </c>
       <c r="AE5">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AF5">
         <v>12.5</v>
@@ -1783,49 +1783,49 @@
         <v>21</v>
       </c>
       <c r="AK5">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AL5">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AM5">
         <v>65</v>
       </c>
       <c r="AN5">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO5">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AP5">
+        <v>20</v>
+      </c>
+      <c r="AQ5">
         <v>21</v>
       </c>
-      <c r="AQ5">
-        <v>19.5</v>
-      </c>
       <c r="AR5">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AS5">
         <v>75</v>
       </c>
       <c r="AT5">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AU5">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV5">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AW5">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AX5">
         <v>12</v>
       </c>
       <c r="AY5">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ5">
         <v>14.5</v>
@@ -1846,10 +1846,10 @@
         <v>55</v>
       </c>
       <c r="BF5">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG5">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BH5">
         <v>4.1</v>
@@ -1858,7 +1858,7 @@
         <v>3.8</v>
       </c>
       <c r="BJ5">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK5">
         <v>8</v>
@@ -1867,13 +1867,13 @@
         <v>90</v>
       </c>
       <c r="BM5">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BN5">
         <v>4.8</v>
       </c>
       <c r="BO5">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BP5">
         <v>12.5</v>
@@ -1882,10 +1882,10 @@
         <v>10.5</v>
       </c>
       <c r="BR5">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BS5">
-        <v>17</v>
+        <v>10.5</v>
       </c>
       <c r="BT5">
         <v>8</v>
@@ -1897,16 +1897,16 @@
         <v>32</v>
       </c>
       <c r="BW5">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="BX5">
         <v>38</v>
       </c>
       <c r="BY5">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BZ5">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="CA5">
         <v>13.5</v>
@@ -1932,28 +1932,28 @@
         <v>109</v>
       </c>
       <c r="F6">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="G6">
-        <v>2.86</v>
+        <v>2.96</v>
       </c>
       <c r="H6">
+        <v>2.76</v>
+      </c>
+      <c r="I6">
         <v>2.78</v>
       </c>
-      <c r="I6">
-        <v>2.8</v>
-      </c>
       <c r="J6">
+        <v>3.35</v>
+      </c>
+      <c r="K6">
         <v>3.4</v>
       </c>
-      <c r="K6">
-        <v>3.45</v>
-      </c>
       <c r="L6">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="M6">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N6">
         <v>3.25</v>
@@ -1962,37 +1962,37 @@
         <v>1.43</v>
       </c>
       <c r="P6">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q6">
         <v>2.3</v>
       </c>
       <c r="R6">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S6">
         <v>4.4</v>
       </c>
       <c r="T6">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="U6">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="V6">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W6">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="X6">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Y6">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Z6">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AA6">
         <v>44</v>
@@ -2004,7 +2004,7 @@
         <v>7.4</v>
       </c>
       <c r="AD6">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE6">
         <v>36</v>
@@ -2013,40 +2013,40 @@
         <v>18</v>
       </c>
       <c r="AG6">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH6">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AI6">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AJ6">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AK6">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AL6">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM6">
         <v>120</v>
       </c>
       <c r="AN6">
+        <v>40</v>
+      </c>
+      <c r="AO6">
         <v>36</v>
       </c>
-      <c r="AO6">
-        <v>34</v>
-      </c>
       <c r="AP6">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AQ6">
         <v>9.199999999999999</v>
       </c>
       <c r="AR6">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AS6">
         <v>40</v>
@@ -2055,103 +2055,103 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AU6">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV6">
         <v>11.5</v>
       </c>
       <c r="AW6">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AX6">
         <v>17</v>
       </c>
       <c r="AY6">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AZ6">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BA6">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BB6">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BC6">
+        <v>34</v>
+      </c>
+      <c r="BD6">
+        <v>48</v>
+      </c>
+      <c r="BE6">
+        <v>110</v>
+      </c>
+      <c r="BF6">
+        <v>34</v>
+      </c>
+      <c r="BG6">
         <v>32</v>
       </c>
-      <c r="BD6">
-        <v>46</v>
-      </c>
-      <c r="BE6">
-        <v>90</v>
-      </c>
-      <c r="BF6">
-        <v>32</v>
-      </c>
-      <c r="BG6">
-        <v>30</v>
-      </c>
       <c r="BH6">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="BI6">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="BJ6">
         <v>10.5</v>
       </c>
       <c r="BK6">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BL6">
         <v>170</v>
       </c>
       <c r="BM6">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="BN6">
         <v>5.8</v>
       </c>
       <c r="BO6">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BP6">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BQ6">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BR6">
+        <v>48</v>
+      </c>
+      <c r="BS6">
+        <v>12</v>
+      </c>
+      <c r="BT6">
+        <v>5.5</v>
+      </c>
+      <c r="BU6">
+        <v>5</v>
+      </c>
+      <c r="BV6">
+        <v>24</v>
+      </c>
+      <c r="BW6">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BX6">
         <v>46</v>
       </c>
-      <c r="BS6">
-        <v>10</v>
-      </c>
-      <c r="BT6">
-        <v>5.6</v>
-      </c>
-      <c r="BU6">
-        <v>5.1</v>
-      </c>
-      <c r="BV6">
-        <v>26</v>
-      </c>
-      <c r="BW6">
-        <v>8.6</v>
-      </c>
-      <c r="BX6">
-        <v>44</v>
-      </c>
       <c r="BY6">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BZ6">
         <v>42</v>
       </c>
       <c r="CA6">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="CB6" t="s">
         <v>118</v>
@@ -2186,160 +2186,160 @@
         <v>21</v>
       </c>
       <c r="J7">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K7">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="L7">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="M7">
         <v>1.03</v>
       </c>
       <c r="N7">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="O7">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="P7">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="Q7">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="R7">
+        <v>1.88</v>
+      </c>
+      <c r="S7">
+        <v>2.12</v>
+      </c>
+      <c r="T7">
+        <v>2.2</v>
+      </c>
+      <c r="U7">
         <v>1.81</v>
-      </c>
-      <c r="S7">
-        <v>2.22</v>
-      </c>
-      <c r="T7">
-        <v>2.26</v>
-      </c>
-      <c r="U7">
-        <v>1.77</v>
       </c>
       <c r="V7">
         <v>1.05</v>
       </c>
       <c r="W7">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="X7">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="Y7">
         <v>70</v>
       </c>
       <c r="Z7">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="AA7">
         <v>1000</v>
       </c>
       <c r="AB7">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC7">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AD7">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AE7">
-        <v>430</v>
+        <v>320</v>
       </c>
       <c r="AF7">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG7">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH7">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AI7">
         <v>230</v>
       </c>
       <c r="AJ7">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AK7">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AL7">
         <v>42</v>
       </c>
       <c r="AM7">
-        <v>230</v>
+        <v>190</v>
       </c>
       <c r="AN7">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="AO7">
-        <v>480</v>
+        <v>460</v>
       </c>
       <c r="AP7">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AQ7">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AR7">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AS7">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AT7">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AU7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AV7">
         <v>55</v>
       </c>
       <c r="AW7">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="AX7">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AY7">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ7">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BA7">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="BB7">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BC7">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BD7">
         <v>38</v>
       </c>
       <c r="BE7">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="BF7">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="BG7">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="BH7">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BI7">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BJ7">
         <v>14.5</v>
@@ -2348,7 +2348,7 @@
         <v>12</v>
       </c>
       <c r="BL7">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="BM7">
         <v>23</v>
@@ -2363,16 +2363,16 @@
         <v>6.2</v>
       </c>
       <c r="BQ7">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BR7">
         <v>23</v>
       </c>
       <c r="BS7">
-        <v>9.6</v>
+        <v>18</v>
       </c>
       <c r="BT7">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BU7">
         <v>16.5</v>
@@ -2381,13 +2381,13 @@
         <v>170</v>
       </c>
       <c r="BW7">
+        <v>14.5</v>
+      </c>
+      <c r="BX7">
+        <v>120</v>
+      </c>
+      <c r="BY7">
         <v>14</v>
-      </c>
-      <c r="BX7">
-        <v>130</v>
-      </c>
-      <c r="BY7">
-        <v>13.5</v>
       </c>
       <c r="BZ7">
         <v>0</v>
@@ -2416,22 +2416,22 @@
         <v>111</v>
       </c>
       <c r="F8">
-        <v>2.64</v>
+        <v>2.74</v>
       </c>
       <c r="G8">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="H8">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="I8">
-        <v>2.72</v>
+        <v>2.62</v>
       </c>
       <c r="J8">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K8">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L8">
         <v>1.28</v>
@@ -2440,64 +2440,64 @@
         <v>1.03</v>
       </c>
       <c r="N8">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="O8">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P8">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="Q8">
         <v>1.5</v>
       </c>
       <c r="R8">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="S8">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="T8">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="U8">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="V8">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="W8">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="X8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Y8">
         <v>20</v>
       </c>
       <c r="Z8">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA8">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AB8">
         <v>20</v>
       </c>
       <c r="AC8">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD8">
         <v>12.5</v>
       </c>
       <c r="AE8">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF8">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG8">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH8">
         <v>12.5</v>
@@ -2506,40 +2506,40 @@
         <v>26</v>
       </c>
       <c r="AJ8">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AK8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AM8">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AN8">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AO8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AP8">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ8">
         <v>18.5</v>
       </c>
       <c r="AR8">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS8">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AT8">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AU8">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AV8">
         <v>11.5</v>
@@ -2548,37 +2548,37 @@
         <v>22</v>
       </c>
       <c r="AX8">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY8">
+        <v>12</v>
+      </c>
+      <c r="AZ8">
+        <v>12</v>
+      </c>
+      <c r="BA8">
+        <v>24</v>
+      </c>
+      <c r="BB8">
+        <v>40</v>
+      </c>
+      <c r="BC8">
+        <v>23</v>
+      </c>
+      <c r="BD8">
+        <v>24</v>
+      </c>
+      <c r="BE8">
+        <v>38</v>
+      </c>
+      <c r="BF8">
         <v>11.5</v>
       </c>
-      <c r="AZ8">
-        <v>11.5</v>
-      </c>
-      <c r="BA8">
-        <v>25</v>
-      </c>
-      <c r="BB8">
-        <v>36</v>
-      </c>
-      <c r="BC8">
-        <v>22</v>
-      </c>
-      <c r="BD8">
-        <v>23</v>
-      </c>
-      <c r="BE8">
-        <v>40</v>
-      </c>
-      <c r="BF8">
+      <c r="BG8">
         <v>11</v>
       </c>
-      <c r="BG8">
-        <v>12</v>
-      </c>
       <c r="BH8">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BI8">
         <v>4.3</v>
@@ -2587,37 +2587,37 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BK8">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BL8">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BM8">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BN8">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BO8">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BP8">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BQ8">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BR8">
         <v>23</v>
       </c>
       <c r="BS8">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="BT8">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BU8">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BV8">
         <v>17.5</v>
@@ -2626,16 +2626,16 @@
         <v>15</v>
       </c>
       <c r="BX8">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BY8">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="BZ8">
         <v>14.5</v>
       </c>
       <c r="CA8">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="CB8" t="s">
         <v>118</v>
@@ -2664,10 +2664,10 @@
         <v>2.54</v>
       </c>
       <c r="H9">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I9">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="J9">
         <v>3.25</v>
@@ -2682,10 +2682,10 @@
         <v>1.11</v>
       </c>
       <c r="N9">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="O9">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="P9">
         <v>1.67</v>
@@ -2694,22 +2694,22 @@
         <v>2.46</v>
       </c>
       <c r="R9">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S9">
         <v>4.9</v>
       </c>
       <c r="T9">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U9">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="V9">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W9">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="X9">
         <v>10</v>
@@ -2742,13 +2742,13 @@
         <v>12</v>
       </c>
       <c r="AH9">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI9">
         <v>65</v>
       </c>
       <c r="AJ9">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AK9">
         <v>32</v>
@@ -2766,10 +2766,10 @@
         <v>55</v>
       </c>
       <c r="AP9">
+        <v>9.4</v>
+      </c>
+      <c r="AQ9">
         <v>9.6</v>
-      </c>
-      <c r="AQ9">
-        <v>10</v>
       </c>
       <c r="AR9">
         <v>19.5</v>
@@ -2787,13 +2787,13 @@
         <v>13.5</v>
       </c>
       <c r="AW9">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AX9">
         <v>13.5</v>
       </c>
       <c r="AY9">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ9">
         <v>19.5</v>
@@ -2802,7 +2802,7 @@
         <v>55</v>
       </c>
       <c r="BB9">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BC9">
         <v>29</v>
@@ -2814,16 +2814,16 @@
         <v>100</v>
       </c>
       <c r="BF9">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BG9">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BH9">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="BI9">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="BJ9">
         <v>10.5</v>
@@ -2835,7 +2835,7 @@
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BN9">
         <v>5.2</v>
@@ -2844,16 +2844,16 @@
         <v>4.8</v>
       </c>
       <c r="BP9">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BQ9">
-        <v>11</v>
+        <v>14.5</v>
       </c>
       <c r="BR9">
         <v>40</v>
       </c>
       <c r="BS9">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BT9">
         <v>6.2</v>
@@ -2865,19 +2865,19 @@
         <v>30</v>
       </c>
       <c r="BW9">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BX9">
         <v>48</v>
       </c>
       <c r="BY9">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BZ9">
         <v>42</v>
       </c>
       <c r="CA9">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="CB9" t="s">
         <v>118</v>
@@ -2900,7 +2900,7 @@
         <v>113</v>
       </c>
       <c r="F10">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="G10">
         <v>1.5</v>
@@ -2918,34 +2918,34 @@
         <v>5.2</v>
       </c>
       <c r="L10">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="M10">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N10">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="O10">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="P10">
-        <v>2.74</v>
+        <v>2.58</v>
       </c>
       <c r="Q10">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="R10">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="S10">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="T10">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="U10">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="V10">
         <v>1.15</v>
@@ -2954,7 +2954,7 @@
         <v>3</v>
       </c>
       <c r="X10">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="Y10">
         <v>32</v>
@@ -2966,73 +2966,73 @@
         <v>230</v>
       </c>
       <c r="AB10">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AC10">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD10">
         <v>26</v>
       </c>
       <c r="AE10">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AF10">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG10">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AH10">
         <v>20</v>
       </c>
       <c r="AI10">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AJ10">
         <v>13.5</v>
       </c>
       <c r="AK10">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AL10">
         <v>27</v>
       </c>
       <c r="AM10">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AN10">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="AO10">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AP10">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AQ10">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AR10">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AS10">
         <v>130</v>
       </c>
       <c r="AT10">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AU10">
         <v>11</v>
       </c>
       <c r="AV10">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW10">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AX10">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AY10">
         <v>9.6</v>
@@ -3041,49 +3041,49 @@
         <v>19</v>
       </c>
       <c r="BA10">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="BB10">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BC10">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BD10">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BE10">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BF10">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BG10">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="BH10">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BI10">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BJ10">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BK10">
         <v>8.800000000000001</v>
       </c>
       <c r="BL10">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="BM10">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BN10">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BO10">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BP10">
         <v>8.800000000000001</v>
@@ -3092,10 +3092,10 @@
         <v>7.8</v>
       </c>
       <c r="BR10">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BS10">
-        <v>16.5</v>
+        <v>9.6</v>
       </c>
       <c r="BT10">
         <v>11</v>
@@ -3107,19 +3107,19 @@
         <v>65</v>
       </c>
       <c r="BW10">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX10">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BY10">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ10">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="CA10">
-        <v>10</v>
+        <v>7.2</v>
       </c>
       <c r="CB10" t="s">
         <v>118</v>
@@ -3142,22 +3142,22 @@
         <v>114</v>
       </c>
       <c r="F11">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="G11">
         <v>3.1</v>
       </c>
       <c r="H11">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="I11">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="J11">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K11">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L11">
         <v>1.43</v>
@@ -3169,34 +3169,34 @@
         <v>3.7</v>
       </c>
       <c r="O11">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P11">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="Q11">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R11">
         <v>1.35</v>
       </c>
       <c r="S11">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T11">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U11">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V11">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="W11">
         <v>1.47</v>
       </c>
       <c r="X11">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y11">
         <v>11</v>
@@ -3208,10 +3208,10 @@
         <v>40</v>
       </c>
       <c r="AB11">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC11">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD11">
         <v>12.5</v>
@@ -3220,37 +3220,37 @@
         <v>30</v>
       </c>
       <c r="AF11">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG11">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH11">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AI11">
         <v>48</v>
       </c>
       <c r="AJ11">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AK11">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AL11">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AM11">
         <v>110</v>
       </c>
       <c r="AN11">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AO11">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AP11">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ11">
         <v>9.199999999999999</v>
@@ -3259,7 +3259,7 @@
         <v>14.5</v>
       </c>
       <c r="AS11">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AT11">
         <v>10.5</v>
@@ -3268,13 +3268,13 @@
         <v>7</v>
       </c>
       <c r="AV11">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AW11">
         <v>22</v>
       </c>
       <c r="AX11">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AY11">
         <v>11.5</v>
@@ -3286,19 +3286,19 @@
         <v>32</v>
       </c>
       <c r="BB11">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BC11">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BD11">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BE11">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BF11">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BG11">
         <v>20</v>
@@ -3384,22 +3384,22 @@
         <v>115</v>
       </c>
       <c r="F12">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="G12">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="H12">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="I12">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="J12">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K12">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L12">
         <v>1.61</v>
@@ -3411,82 +3411,82 @@
         <v>2.62</v>
       </c>
       <c r="O12">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="P12">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Q12">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="R12">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S12">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="T12">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="U12">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="V12">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="W12">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="X12">
-        <v>500</v>
+        <v>10</v>
       </c>
       <c r="Y12">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="Z12">
         <v>500</v>
       </c>
       <c r="AA12">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB12">
         <v>7.6</v>
       </c>
       <c r="AC12">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AD12">
-        <v>970</v>
+        <v>23</v>
       </c>
       <c r="AE12">
-        <v>500</v>
+        <v>110</v>
       </c>
       <c r="AF12">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AG12">
-        <v>500</v>
+        <v>14</v>
       </c>
       <c r="AH12">
-        <v>500</v>
+        <v>30</v>
       </c>
       <c r="AI12">
         <v>500</v>
       </c>
       <c r="AJ12">
-        <v>900</v>
+        <v>32</v>
       </c>
       <c r="AK12">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="AL12">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="AM12">
         <v>580</v>
       </c>
       <c r="AN12">
-        <v>600</v>
+        <v>34</v>
       </c>
       <c r="AO12">
         <v>1000</v>
@@ -3495,28 +3495,28 @@
         <v>7</v>
       </c>
       <c r="AQ12">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AR12">
-        <v>2.06</v>
+        <v>12.5</v>
       </c>
       <c r="AS12">
-        <v>2.1</v>
+        <v>4.7</v>
       </c>
       <c r="AT12">
-        <v>1.65</v>
+        <v>3.2</v>
       </c>
       <c r="AU12">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV12">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AW12">
-        <v>2.1</v>
+        <v>4.6</v>
       </c>
       <c r="AX12">
-        <v>10.5</v>
+        <v>5.7</v>
       </c>
       <c r="AY12">
         <v>10</v>
@@ -3525,25 +3525,25 @@
         <v>20</v>
       </c>
       <c r="BA12">
-        <v>2.1</v>
+        <v>4.7</v>
       </c>
       <c r="BB12">
-        <v>2.08</v>
+        <v>14</v>
       </c>
       <c r="BC12">
-        <v>2.06</v>
+        <v>13</v>
       </c>
       <c r="BD12">
-        <v>2.1</v>
+        <v>4.5</v>
       </c>
       <c r="BE12">
-        <v>2.12</v>
+        <v>4.7</v>
       </c>
       <c r="BF12">
-        <v>2.12</v>
+        <v>4.5</v>
       </c>
       <c r="BG12">
-        <v>2.12</v>
+        <v>4.8</v>
       </c>
       <c r="BH12">
         <v>3.05</v>
@@ -3552,10 +3552,10 @@
         <v>2.2</v>
       </c>
       <c r="BJ12">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BK12">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BL12">
         <v>1000</v>
@@ -3564,43 +3564,43 @@
         <v>5</v>
       </c>
       <c r="BN12">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="BO12">
+        <v>3.85</v>
+      </c>
+      <c r="BP12">
+        <v>21</v>
+      </c>
+      <c r="BQ12">
         <v>4.1</v>
-      </c>
-      <c r="BP12">
-        <v>24</v>
-      </c>
-      <c r="BQ12">
-        <v>4.2</v>
       </c>
       <c r="BR12">
         <v>55</v>
       </c>
       <c r="BS12">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BT12">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BU12">
-        <v>5.4</v>
+        <v>3.6</v>
       </c>
       <c r="BV12">
+        <v>65</v>
+      </c>
+      <c r="BW12">
+        <v>4.8</v>
+      </c>
+      <c r="BX12">
+        <v>90</v>
+      </c>
+      <c r="BY12">
+        <v>4.9</v>
+      </c>
+      <c r="BZ12">
         <v>55</v>
-      </c>
-      <c r="BW12">
-        <v>4.6</v>
-      </c>
-      <c r="BX12">
-        <v>80</v>
-      </c>
-      <c r="BY12">
-        <v>4.8</v>
-      </c>
-      <c r="BZ12">
-        <v>60</v>
       </c>
       <c r="CA12">
         <v>4.7</v>
@@ -3626,37 +3626,37 @@
         <v>116</v>
       </c>
       <c r="F13">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="G13">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="H13">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="I13">
-        <v>2.62</v>
+        <v>2.48</v>
       </c>
       <c r="J13">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="K13">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="L13">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="M13">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="N13">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="O13">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="P13">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="Q13">
         <v>3.25</v>
@@ -3665,34 +3665,34 @@
         <v>1.14</v>
       </c>
       <c r="S13">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="T13">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="U13">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="V13">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="W13">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="X13">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="Y13">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="Z13">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AA13">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AB13">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AC13">
         <v>7.4</v>
@@ -3701,13 +3701,13 @@
         <v>14.5</v>
       </c>
       <c r="AE13">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF13">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AG13">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AH13">
         <v>32</v>
@@ -3716,13 +3716,13 @@
         <v>190</v>
       </c>
       <c r="AJ13">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK13">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AL13">
-        <v>130</v>
+        <v>340</v>
       </c>
       <c r="AM13">
         <v>500</v>
@@ -3731,22 +3731,22 @@
         <v>600</v>
       </c>
       <c r="AO13">
-        <v>600</v>
+        <v>55</v>
       </c>
       <c r="AP13">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AQ13">
         <v>5.7</v>
       </c>
       <c r="AR13">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AS13">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="AT13">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AU13">
         <v>6.2</v>
@@ -3755,91 +3755,91 @@
         <v>11.5</v>
       </c>
       <c r="AW13">
-        <v>30</v>
+        <v>19.5</v>
       </c>
       <c r="AX13">
         <v>20</v>
       </c>
       <c r="AY13">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AZ13">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA13">
         <v>8.800000000000001</v>
       </c>
       <c r="BB13">
-        <v>22</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC13">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BD13">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="BE13">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF13">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG13">
-        <v>38</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH13">
         <v>2.5</v>
       </c>
       <c r="BI13">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="BJ13">
         <v>13.5</v>
       </c>
       <c r="BK13">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BN13">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BO13">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BP13">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BQ13">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR13">
         <v>1000</v>
       </c>
       <c r="BS13">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BT13">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BU13">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="BV13">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BW13">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BX13">
         <v>1000</v>
       </c>
       <c r="BY13">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BZ13">
         <v>0</v>
@@ -3868,226 +3868,226 @@
         <v>117</v>
       </c>
       <c r="F14">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="G14">
-        <v>2.48</v>
+        <v>2.74</v>
       </c>
       <c r="H14">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="I14">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="J14">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="K14">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="L14">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="M14">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="N14">
-        <v>2.78</v>
+        <v>2.66</v>
       </c>
       <c r="O14">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="P14">
+        <v>1.54</v>
+      </c>
+      <c r="Q14">
+        <v>2.7</v>
+      </c>
+      <c r="R14">
+        <v>1.19</v>
+      </c>
+      <c r="S14">
+        <v>5.6</v>
+      </c>
+      <c r="T14">
+        <v>2.08</v>
+      </c>
+      <c r="U14">
+        <v>1.79</v>
+      </c>
+      <c r="V14">
+        <v>1.39</v>
+      </c>
+      <c r="W14">
         <v>1.57</v>
       </c>
-      <c r="Q14">
-        <v>2.54</v>
-      </c>
-      <c r="R14">
-        <v>1.2</v>
-      </c>
-      <c r="S14">
-        <v>5.1</v>
-      </c>
-      <c r="T14">
-        <v>1.04</v>
-      </c>
-      <c r="U14">
-        <v>1.01</v>
-      </c>
-      <c r="V14">
-        <v>1.33</v>
-      </c>
-      <c r="W14">
-        <v>1.68</v>
-      </c>
       <c r="X14">
-        <v>970</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y14">
-        <v>970</v>
+        <v>10</v>
       </c>
       <c r="Z14">
+        <v>23</v>
+      </c>
+      <c r="AA14">
+        <v>170</v>
+      </c>
+      <c r="AB14">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC14">
+        <v>7.4</v>
+      </c>
+      <c r="AD14">
+        <v>17.5</v>
+      </c>
+      <c r="AE14">
         <v>75</v>
       </c>
-      <c r="AA14">
-        <v>900</v>
-      </c>
-      <c r="AB14">
-        <v>9</v>
-      </c>
-      <c r="AC14">
-        <v>7.6</v>
-      </c>
-      <c r="AD14">
-        <v>970</v>
-      </c>
-      <c r="AE14">
-        <v>260</v>
-      </c>
       <c r="AF14">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AG14">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AH14">
-        <v>150</v>
+        <v>29</v>
       </c>
       <c r="AI14">
         <v>350</v>
       </c>
       <c r="AJ14">
-        <v>160</v>
+        <v>46</v>
       </c>
       <c r="AK14">
-        <v>150</v>
+        <v>44</v>
       </c>
       <c r="AL14">
-        <v>210</v>
+        <v>80</v>
       </c>
       <c r="AM14">
         <v>580</v>
       </c>
       <c r="AN14">
-        <v>600</v>
+        <v>50</v>
       </c>
       <c r="AO14">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AP14">
-        <v>1.83</v>
+        <v>7.4</v>
       </c>
       <c r="AQ14">
-        <v>1.97</v>
+        <v>8.4</v>
       </c>
       <c r="AR14">
-        <v>1.91</v>
+        <v>19</v>
       </c>
       <c r="AS14">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="AT14">
-        <v>1.65</v>
+        <v>6.8</v>
       </c>
       <c r="AU14">
-        <v>1.6</v>
+        <v>6</v>
       </c>
       <c r="AV14">
-        <v>1.98</v>
+        <v>13.5</v>
       </c>
       <c r="AW14">
-        <v>1.98</v>
+        <v>34</v>
       </c>
       <c r="AX14">
-        <v>1.97</v>
+        <v>13</v>
       </c>
       <c r="AY14">
-        <v>1.95</v>
+        <v>11</v>
       </c>
       <c r="AZ14">
-        <v>1.96</v>
+        <v>19.5</v>
       </c>
       <c r="BA14">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="BB14">
-        <v>1.93</v>
+        <v>30</v>
       </c>
       <c r="BC14">
-        <v>1.93</v>
+        <v>28</v>
       </c>
       <c r="BD14">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="BE14">
-        <v>2.02</v>
+        <v>65</v>
       </c>
       <c r="BF14">
-        <v>1.93</v>
+        <v>32</v>
       </c>
       <c r="BG14">
-        <v>2.02</v>
+        <v>46</v>
       </c>
       <c r="BH14">
-        <v>1000</v>
+        <v>2.94</v>
       </c>
       <c r="BI14">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="BJ14">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK14">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BN14">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BO14">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BP14">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BQ14">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BR14">
         <v>1000</v>
       </c>
       <c r="BS14">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BT14">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU14">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BV14">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BW14">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BX14">
         <v>1000</v>
       </c>
       <c r="BY14">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BZ14">
         <v>1000</v>
       </c>
       <c r="CA14">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="CB14" t="s">
         <v>118</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-24.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="122">
   <si>
     <t>League</t>
   </si>
@@ -292,6 +292,9 @@
     <t>20:30:00</t>
   </si>
   <si>
+    <t>21:30:00</t>
+  </si>
+  <si>
     <t>Rivers United FC</t>
   </si>
   <si>
@@ -331,6 +334,9 @@
     <t>Independiente Juniors</t>
   </si>
   <si>
+    <t>LDU de Portoviejo</t>
+  </si>
+  <si>
     <t>Kun Khalifat FC</t>
   </si>
   <si>
@@ -370,7 +376,10 @@
     <t>Vinotinto Ecuador</t>
   </si>
   <si>
-    <t>2026-09-24 08:19:37</t>
+    <t>22 de Julio FC</t>
+  </si>
+  <si>
+    <t>2026-09-24 10:35:23</t>
   </si>
 </sst>
 </file>
@@ -702,7 +711,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB14"/>
+  <dimension ref="A1:CB15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -958,235 +967,235 @@
         <v>86</v>
       </c>
       <c r="D2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F2">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="G2">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="H2">
-        <v>14</v>
+        <v>5.4</v>
       </c>
       <c r="I2">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="J2">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="K2">
-        <v>7.2</v>
+        <v>12</v>
       </c>
       <c r="L2">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="M2">
         <v>1.02</v>
       </c>
       <c r="N2">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
       <c r="O2">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="P2">
-        <v>2.48</v>
+        <v>3.5</v>
       </c>
       <c r="Q2">
-        <v>1.53</v>
+        <v>1.24</v>
       </c>
       <c r="R2">
-        <v>1.63</v>
+        <v>2</v>
       </c>
       <c r="S2">
-        <v>2.28</v>
+        <v>1.81</v>
       </c>
       <c r="T2">
-        <v>1.98</v>
+        <v>1.01</v>
       </c>
       <c r="U2">
-        <v>1.83</v>
+        <v>2.08</v>
       </c>
       <c r="V2">
         <v>1.06</v>
       </c>
       <c r="W2">
-        <v>4.2</v>
+        <v>1.9</v>
       </c>
       <c r="X2">
-        <v>48</v>
+        <v>230</v>
       </c>
       <c r="Y2">
         <v>120</v>
       </c>
       <c r="Z2">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AA2">
         <v>1000</v>
       </c>
       <c r="AB2">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="AC2">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="AD2">
         <v>130</v>
       </c>
       <c r="AE2">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="AF2">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AG2">
-        <v>12.5</v>
+        <v>23</v>
       </c>
       <c r="AH2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AI2">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AJ2">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AK2">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AL2">
-        <v>120</v>
+        <v>970</v>
       </c>
       <c r="AM2">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AN2">
-        <v>4.6</v>
+        <v>29</v>
       </c>
       <c r="AO2">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="AP2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AQ2">
-        <v>6.8</v>
+        <v>4.2</v>
       </c>
       <c r="AR2">
-        <v>7.4</v>
+        <v>4.2</v>
       </c>
       <c r="AS2">
-        <v>7.8</v>
+        <v>4.2</v>
       </c>
       <c r="AT2">
-        <v>8.199999999999999</v>
+        <v>2.5</v>
       </c>
       <c r="AU2">
-        <v>12.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV2">
-        <v>7</v>
+        <v>4.2</v>
       </c>
       <c r="AW2">
-        <v>7.6</v>
+        <v>4.2</v>
       </c>
       <c r="AX2">
-        <v>7.2</v>
+        <v>5.6</v>
       </c>
       <c r="AY2">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AZ2">
-        <v>7</v>
+        <v>1.5</v>
       </c>
       <c r="BA2">
-        <v>7.6</v>
+        <v>4.2</v>
       </c>
       <c r="BB2">
-        <v>9</v>
+        <v>6.2</v>
       </c>
       <c r="BC2">
-        <v>12</v>
+        <v>9.4</v>
       </c>
       <c r="BD2">
-        <v>7</v>
+        <v>4.3</v>
       </c>
       <c r="BE2">
-        <v>7.4</v>
+        <v>1.54</v>
       </c>
       <c r="BF2">
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="BG2">
         <v>10.5</v>
       </c>
       <c r="BH2">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BI2">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="BJ2">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK2">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BN2">
-        <v>3.95</v>
+        <v>1000</v>
       </c>
       <c r="BO2">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="BP2">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BT2">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BU2">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="CA2">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="CB2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1200,31 +1209,31 @@
         <v>87</v>
       </c>
       <c r="D3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F3">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="G3">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="H3">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="I3">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="J3">
+        <v>2.82</v>
+      </c>
+      <c r="K3">
         <v>2.84</v>
       </c>
-      <c r="K3">
-        <v>2.86</v>
-      </c>
       <c r="L3">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="M3">
         <v>1.2</v>
@@ -1233,37 +1242,37 @@
         <v>2.12</v>
       </c>
       <c r="O3">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="P3">
         <v>1.36</v>
       </c>
       <c r="Q3">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="R3">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="S3">
         <v>9</v>
       </c>
       <c r="T3">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="U3">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="V3">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="W3">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="X3">
+        <v>5.9</v>
+      </c>
+      <c r="Y3">
         <v>6.2</v>
-      </c>
-      <c r="Y3">
-        <v>6.4</v>
       </c>
       <c r="Z3">
         <v>13</v>
@@ -1272,10 +1281,10 @@
         <v>44</v>
       </c>
       <c r="AB3">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AC3">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD3">
         <v>15</v>
@@ -1284,40 +1293,40 @@
         <v>46</v>
       </c>
       <c r="AF3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG3">
         <v>19</v>
       </c>
       <c r="AH3">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AI3">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AJ3">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AK3">
         <v>85</v>
       </c>
       <c r="AL3">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AM3">
         <v>500</v>
       </c>
       <c r="AN3">
-        <v>140</v>
+        <v>500</v>
       </c>
       <c r="AO3">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AP3">
+        <v>5.7</v>
+      </c>
+      <c r="AQ3">
         <v>5.8</v>
-      </c>
-      <c r="AQ3">
-        <v>6</v>
       </c>
       <c r="AR3">
         <v>12.5</v>
@@ -1326,7 +1335,7 @@
         <v>38</v>
       </c>
       <c r="AT3">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU3">
         <v>7</v>
@@ -1335,7 +1344,7 @@
         <v>14</v>
       </c>
       <c r="AW3">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AX3">
         <v>22</v>
@@ -1344,91 +1353,91 @@
         <v>17.5</v>
       </c>
       <c r="AZ3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BA3">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BB3">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BC3">
         <v>70</v>
       </c>
       <c r="BD3">
+        <v>110</v>
+      </c>
+      <c r="BE3">
+        <v>230</v>
+      </c>
+      <c r="BF3">
         <v>100</v>
       </c>
-      <c r="BE3">
-        <v>110</v>
-      </c>
-      <c r="BF3">
-        <v>75</v>
-      </c>
       <c r="BG3">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BH3">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="BI3">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="BJ3">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BK3">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>18</v>
+        <v>300</v>
       </c>
       <c r="BN3">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BO3">
         <v>6.2</v>
       </c>
       <c r="BP3">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BQ3">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BR3">
         <v>90</v>
       </c>
       <c r="BS3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BT3">
         <v>5.1</v>
       </c>
       <c r="BU3">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BV3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BW3">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BX3">
         <v>70</v>
       </c>
       <c r="BY3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BZ3">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="CA3">
-        <v>15.5</v>
+        <v>40</v>
       </c>
       <c r="CB3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1442,67 +1451,67 @@
         <v>88</v>
       </c>
       <c r="D4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E4" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F4">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="G4">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="H4">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="I4">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="J4">
+        <v>5</v>
+      </c>
+      <c r="K4">
         <v>5.2</v>
       </c>
-      <c r="K4">
+      <c r="L4">
+        <v>1.54</v>
+      </c>
+      <c r="M4">
+        <v>1.11</v>
+      </c>
+      <c r="N4">
+        <v>2.88</v>
+      </c>
+      <c r="O4">
+        <v>1.52</v>
+      </c>
+      <c r="P4">
+        <v>1.62</v>
+      </c>
+      <c r="Q4">
+        <v>2.58</v>
+      </c>
+      <c r="R4">
+        <v>1.21</v>
+      </c>
+      <c r="S4">
         <v>5.4</v>
       </c>
-      <c r="L4">
-        <v>1.53</v>
-      </c>
-      <c r="M4">
-        <v>1.1</v>
-      </c>
-      <c r="N4">
-        <v>2.9</v>
-      </c>
-      <c r="O4">
-        <v>1.51</v>
-      </c>
-      <c r="P4">
-        <v>1.63</v>
-      </c>
-      <c r="Q4">
-        <v>2.56</v>
-      </c>
-      <c r="R4">
-        <v>1.22</v>
-      </c>
-      <c r="S4">
-        <v>5.3</v>
-      </c>
       <c r="T4">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="U4">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="V4">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="W4">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X4">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y4">
         <v>4.9</v>
@@ -1514,25 +1523,25 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AB4">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AC4">
         <v>14</v>
       </c>
       <c r="AD4">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AE4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF4">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="AG4">
         <v>90</v>
       </c>
       <c r="AH4">
-        <v>290</v>
+        <v>140</v>
       </c>
       <c r="AI4">
         <v>120</v>
@@ -1541,25 +1550,25 @@
         <v>1000</v>
       </c>
       <c r="AK4">
-        <v>920</v>
+        <v>790</v>
       </c>
       <c r="AL4">
-        <v>780</v>
+        <v>820</v>
       </c>
       <c r="AM4">
-        <v>970</v>
+        <v>910</v>
       </c>
       <c r="AN4">
         <v>1000</v>
       </c>
       <c r="AO4">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AP4">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AQ4">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AR4">
         <v>5.2</v>
@@ -1574,103 +1583,103 @@
         <v>13</v>
       </c>
       <c r="AV4">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX4">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="AY4">
         <v>70</v>
       </c>
       <c r="AZ4">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BA4">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="BB4">
+        <v>29</v>
+      </c>
+      <c r="BC4">
+        <v>28</v>
+      </c>
+      <c r="BD4">
         <v>26</v>
       </c>
-      <c r="BC4">
-        <v>27</v>
-      </c>
-      <c r="BD4">
-        <v>27</v>
-      </c>
       <c r="BE4">
-        <v>29</v>
+        <v>250</v>
       </c>
       <c r="BF4">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="BG4">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BH4">
-        <v>2.92</v>
+        <v>1000</v>
       </c>
       <c r="BI4">
-        <v>2.74</v>
+        <v>1.42</v>
       </c>
       <c r="BJ4">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="BK4">
-        <v>10.5</v>
+        <v>2.68</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>2.78</v>
+        <v>320</v>
       </c>
       <c r="BN4">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="BO4">
-        <v>10.5</v>
+        <v>2.68</v>
       </c>
       <c r="BP4">
         <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="BT4">
-        <v>3.15</v>
+        <v>1000</v>
       </c>
       <c r="BU4">
-        <v>2.94</v>
+        <v>2.86</v>
       </c>
       <c r="BV4">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BW4">
-        <v>6</v>
+        <v>1.5</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>16</v>
+        <v>2.68</v>
       </c>
       <c r="BZ4">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="CA4">
-        <v>11.5</v>
+        <v>2.68</v>
       </c>
       <c r="CB4" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1684,16 +1693,16 @@
         <v>88</v>
       </c>
       <c r="D5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F5">
+        <v>1.86</v>
+      </c>
+      <c r="G5">
         <v>1.87</v>
-      </c>
-      <c r="G5">
-        <v>1.88</v>
       </c>
       <c r="H5">
         <v>4.5</v>
@@ -1708,55 +1717,55 @@
         <v>4.1</v>
       </c>
       <c r="L5">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="M5">
         <v>1.04</v>
       </c>
       <c r="N5">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="O5">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="P5">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="Q5">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="R5">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="S5">
-        <v>2.66</v>
+        <v>2.52</v>
       </c>
       <c r="T5">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="U5">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="V5">
         <v>1.27</v>
       </c>
       <c r="W5">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="X5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z5">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AA5">
         <v>90</v>
       </c>
       <c r="AB5">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC5">
         <v>9.4</v>
@@ -1765,40 +1774,40 @@
         <v>17</v>
       </c>
       <c r="AE5">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AF5">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AG5">
         <v>10</v>
       </c>
       <c r="AH5">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AI5">
         <v>42</v>
       </c>
       <c r="AJ5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK5">
         <v>16.5</v>
       </c>
       <c r="AL5">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AM5">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AN5">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AO5">
         <v>38</v>
       </c>
       <c r="AP5">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AQ5">
         <v>21</v>
@@ -1810,7 +1819,7 @@
         <v>75</v>
       </c>
       <c r="AT5">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AU5">
         <v>9</v>
@@ -1822,40 +1831,40 @@
         <v>44</v>
       </c>
       <c r="AX5">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AY5">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ5">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA5">
         <v>38</v>
       </c>
       <c r="BB5">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BC5">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BD5">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BE5">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BF5">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BG5">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BH5">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BI5">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="BJ5">
         <v>8.800000000000001</v>
@@ -1864,55 +1873,55 @@
         <v>8</v>
       </c>
       <c r="BL5">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="BM5">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="BN5">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BO5">
         <v>4.5</v>
       </c>
       <c r="BP5">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BQ5">
         <v>10.5</v>
       </c>
       <c r="BR5">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BS5">
-        <v>10.5</v>
+        <v>17.5</v>
       </c>
       <c r="BT5">
         <v>8</v>
       </c>
       <c r="BU5">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BV5">
         <v>32</v>
       </c>
       <c r="BW5">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BX5">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BY5">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BZ5">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="CA5">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="CB5" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1926,22 +1935,22 @@
         <v>88</v>
       </c>
       <c r="D6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E6" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F6">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="G6">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="H6">
+        <v>2.72</v>
+      </c>
+      <c r="I6">
         <v>2.76</v>
-      </c>
-      <c r="I6">
-        <v>2.78</v>
       </c>
       <c r="J6">
         <v>3.35</v>
@@ -1950,67 +1959,67 @@
         <v>3.4</v>
       </c>
       <c r="L6">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="M6">
         <v>1.1</v>
       </c>
       <c r="N6">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="O6">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="P6">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="Q6">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="R6">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="S6">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="T6">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="U6">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="V6">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W6">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="X6">
         <v>11</v>
       </c>
       <c r="Y6">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="Z6">
         <v>16</v>
       </c>
       <c r="AA6">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AB6">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AC6">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD6">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE6">
         <v>36</v>
       </c>
       <c r="AF6">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AG6">
         <v>13</v>
@@ -2025,25 +2034,25 @@
         <v>48</v>
       </c>
       <c r="AK6">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AL6">
         <v>55</v>
       </c>
       <c r="AM6">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AN6">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AO6">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AP6">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AQ6">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AR6">
         <v>15.5</v>
@@ -2070,46 +2079,46 @@
         <v>12.5</v>
       </c>
       <c r="AZ6">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA6">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BB6">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BC6">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BD6">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BE6">
         <v>110</v>
       </c>
       <c r="BF6">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BG6">
         <v>32</v>
       </c>
       <c r="BH6">
-        <v>2.98</v>
+        <v>2.86</v>
       </c>
       <c r="BI6">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="BJ6">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK6">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BL6">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="BM6">
-        <v>14.5</v>
+        <v>130</v>
       </c>
       <c r="BN6">
         <v>5.8</v>
@@ -2118,13 +2127,13 @@
         <v>5.3</v>
       </c>
       <c r="BP6">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="BQ6">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BR6">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="BS6">
         <v>12</v>
@@ -2142,19 +2151,19 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BX6">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BY6">
         <v>11.5</v>
       </c>
       <c r="BZ6">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="CA6">
         <v>11.5</v>
       </c>
       <c r="CB6" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2168,16 +2177,16 @@
         <v>88</v>
       </c>
       <c r="D7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F7">
+        <v>1.19</v>
+      </c>
+      <c r="G7">
         <v>1.2</v>
-      </c>
-      <c r="G7">
-        <v>1.21</v>
       </c>
       <c r="H7">
         <v>20</v>
@@ -2186,127 +2195,127 @@
         <v>21</v>
       </c>
       <c r="J7">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="K7">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="L7">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="M7">
         <v>1.03</v>
       </c>
       <c r="N7">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="O7">
         <v>1.14</v>
       </c>
       <c r="P7">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="Q7">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="R7">
-        <v>1.88</v>
+        <v>1.97</v>
       </c>
       <c r="S7">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="T7">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="U7">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="V7">
         <v>1.05</v>
       </c>
       <c r="W7">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="X7">
         <v>34</v>
       </c>
       <c r="Y7">
+        <v>80</v>
+      </c>
+      <c r="Z7">
+        <v>260</v>
+      </c>
+      <c r="AA7">
+        <v>1000</v>
+      </c>
+      <c r="AB7">
+        <v>13</v>
+      </c>
+      <c r="AC7">
+        <v>20</v>
+      </c>
+      <c r="AD7">
         <v>70</v>
       </c>
-      <c r="Z7">
-        <v>240</v>
-      </c>
-      <c r="AA7">
-        <v>1000</v>
-      </c>
-      <c r="AB7">
-        <v>12</v>
-      </c>
-      <c r="AC7">
-        <v>19</v>
-      </c>
-      <c r="AD7">
-        <v>65</v>
-      </c>
       <c r="AE7">
-        <v>320</v>
+        <v>360</v>
       </c>
       <c r="AF7">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AG7">
         <v>12.5</v>
       </c>
       <c r="AH7">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AI7">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AJ7">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AK7">
         <v>13.5</v>
       </c>
       <c r="AL7">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AM7">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="AN7">
-        <v>3.15</v>
+        <v>2.92</v>
       </c>
       <c r="AO7">
-        <v>460</v>
+        <v>410</v>
       </c>
       <c r="AP7">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AQ7">
+        <v>65</v>
+      </c>
+      <c r="AR7">
+        <v>80</v>
+      </c>
+      <c r="AS7">
+        <v>55</v>
+      </c>
+      <c r="AT7">
+        <v>12.5</v>
+      </c>
+      <c r="AU7">
+        <v>19.5</v>
+      </c>
+      <c r="AV7">
         <v>60</v>
       </c>
-      <c r="AR7">
-        <v>120</v>
-      </c>
-      <c r="AS7">
-        <v>30</v>
-      </c>
-      <c r="AT7">
-        <v>11.5</v>
-      </c>
-      <c r="AU7">
-        <v>18</v>
-      </c>
-      <c r="AV7">
-        <v>55</v>
-      </c>
       <c r="AW7">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="AX7">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY7">
         <v>12</v>
@@ -2315,79 +2324,79 @@
         <v>34</v>
       </c>
       <c r="BA7">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="BB7">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BC7">
         <v>12.5</v>
       </c>
       <c r="BD7">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BE7">
         <v>140</v>
       </c>
       <c r="BF7">
-        <v>3.05</v>
+        <v>2.86</v>
       </c>
       <c r="BG7">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BH7">
+        <v>5.5</v>
+      </c>
+      <c r="BI7">
         <v>5</v>
       </c>
-      <c r="BI7">
-        <v>4.7</v>
-      </c>
       <c r="BJ7">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BK7">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BL7">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="BM7">
-        <v>23</v>
+        <v>140</v>
       </c>
       <c r="BN7">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="BO7">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="BP7">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BQ7">
         <v>5.5</v>
       </c>
       <c r="BR7">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BS7">
         <v>18</v>
       </c>
       <c r="BT7">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BU7">
         <v>16.5</v>
       </c>
       <c r="BV7">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="BW7">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BX7">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="BY7">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BZ7">
         <v>0</v>
@@ -2396,7 +2405,7 @@
         <v>0</v>
       </c>
       <c r="CB7" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2410,28 +2419,28 @@
         <v>88</v>
       </c>
       <c r="D8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E8" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F8">
+        <v>2.72</v>
+      </c>
+      <c r="G8">
         <v>2.74</v>
       </c>
-      <c r="G8">
-        <v>2.76</v>
-      </c>
       <c r="H8">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="I8">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="J8">
+        <v>3.9</v>
+      </c>
+      <c r="K8">
         <v>3.95</v>
-      </c>
-      <c r="K8">
-        <v>4</v>
       </c>
       <c r="L8">
         <v>1.28</v>
@@ -2440,52 +2449,52 @@
         <v>1.03</v>
       </c>
       <c r="N8">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="O8">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P8">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="Q8">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="R8">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="S8">
         <v>2.22</v>
       </c>
       <c r="T8">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="U8">
         <v>3.1</v>
       </c>
       <c r="V8">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="W8">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="X8">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y8">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Z8">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA8">
         <v>40</v>
       </c>
       <c r="AB8">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AC8">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD8">
         <v>12.5</v>
@@ -2494,7 +2503,7 @@
         <v>23</v>
       </c>
       <c r="AF8">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG8">
         <v>13</v>
@@ -2512,31 +2521,31 @@
         <v>24</v>
       </c>
       <c r="AL8">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AM8">
         <v>42</v>
       </c>
       <c r="AN8">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AO8">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AP8">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AQ8">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AR8">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS8">
         <v>36</v>
       </c>
       <c r="AT8">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AU8">
         <v>9.4</v>
@@ -2548,16 +2557,16 @@
         <v>22</v>
       </c>
       <c r="AX8">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AY8">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ8">
         <v>12</v>
       </c>
       <c r="BA8">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB8">
         <v>40</v>
@@ -2572,34 +2581,34 @@
         <v>38</v>
       </c>
       <c r="BF8">
+        <v>12</v>
+      </c>
+      <c r="BG8">
         <v>11.5</v>
       </c>
-      <c r="BG8">
-        <v>11</v>
-      </c>
       <c r="BH8">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BI8">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BJ8">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BK8">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BL8">
         <v>60</v>
       </c>
       <c r="BM8">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="BN8">
         <v>6.2</v>
       </c>
       <c r="BO8">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BP8">
         <v>19</v>
@@ -2608,13 +2617,13 @@
         <v>16</v>
       </c>
       <c r="BR8">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BS8">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BT8">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BU8">
         <v>5.6</v>
@@ -2629,7 +2638,7 @@
         <v>22</v>
       </c>
       <c r="BY8">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ8">
         <v>14.5</v>
@@ -2638,7 +2647,7 @@
         <v>12</v>
       </c>
       <c r="CB8" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2652,10 +2661,10 @@
         <v>88</v>
       </c>
       <c r="D9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E9" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F9">
         <v>2.52</v>
@@ -2664,10 +2673,10 @@
         <v>2.54</v>
       </c>
       <c r="H9">
+        <v>3.3</v>
+      </c>
+      <c r="I9">
         <v>3.35</v>
-      </c>
-      <c r="I9">
-        <v>3.4</v>
       </c>
       <c r="J9">
         <v>3.25</v>
@@ -2676,19 +2685,19 @@
         <v>3.3</v>
       </c>
       <c r="L9">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="M9">
         <v>1.11</v>
       </c>
       <c r="N9">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="O9">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="P9">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="Q9">
         <v>2.46</v>
@@ -2703,19 +2712,19 @@
         <v>2.04</v>
       </c>
       <c r="U9">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="V9">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W9">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="X9">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Y9">
         <v>10</v>
-      </c>
-      <c r="Y9">
-        <v>10.5</v>
       </c>
       <c r="Z9">
         <v>21</v>
@@ -2730,7 +2739,7 @@
         <v>7.4</v>
       </c>
       <c r="AD9">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE9">
         <v>46</v>
@@ -2742,13 +2751,13 @@
         <v>12</v>
       </c>
       <c r="AH9">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI9">
         <v>65</v>
       </c>
       <c r="AJ9">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AK9">
         <v>32</v>
@@ -2757,10 +2766,10 @@
         <v>55</v>
       </c>
       <c r="AM9">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AN9">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AO9">
         <v>55</v>
@@ -2772,7 +2781,7 @@
         <v>9.6</v>
       </c>
       <c r="AR9">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AS9">
         <v>55</v>
@@ -2793,7 +2802,7 @@
         <v>13.5</v>
       </c>
       <c r="AY9">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AZ9">
         <v>19.5</v>
@@ -2808,34 +2817,34 @@
         <v>29</v>
       </c>
       <c r="BD9">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BE9">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="BF9">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BG9">
         <v>48</v>
       </c>
       <c r="BH9">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="BI9">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="BJ9">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK9">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BL9">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="BM9">
-        <v>21</v>
+        <v>140</v>
       </c>
       <c r="BN9">
         <v>5.2</v>
@@ -2847,40 +2856,40 @@
         <v>21</v>
       </c>
       <c r="BQ9">
+        <v>17.5</v>
+      </c>
+      <c r="BR9">
+        <v>42</v>
+      </c>
+      <c r="BS9">
         <v>14.5</v>
-      </c>
-      <c r="BR9">
-        <v>40</v>
-      </c>
-      <c r="BS9">
-        <v>15</v>
       </c>
       <c r="BT9">
         <v>6.2</v>
       </c>
       <c r="BU9">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BV9">
         <v>30</v>
       </c>
       <c r="BW9">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BX9">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BY9">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BZ9">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="CA9">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="CB9" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2894,16 +2903,16 @@
         <v>88</v>
       </c>
       <c r="D10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E10" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F10">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="G10">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="H10">
         <v>7.4</v>
@@ -2912,37 +2921,37 @@
         <v>7.6</v>
       </c>
       <c r="J10">
+        <v>5</v>
+      </c>
+      <c r="K10">
         <v>5.1</v>
       </c>
-      <c r="K10">
-        <v>5.2</v>
-      </c>
       <c r="L10">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M10">
         <v>1.04</v>
       </c>
       <c r="N10">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="O10">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P10">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="Q10">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="R10">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="S10">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="T10">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="U10">
         <v>2.2</v>
@@ -2951,25 +2960,25 @@
         <v>1.15</v>
       </c>
       <c r="W10">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="X10">
         <v>24</v>
       </c>
       <c r="Y10">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Z10">
         <v>65</v>
       </c>
       <c r="AA10">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="AB10">
         <v>10.5</v>
       </c>
       <c r="AC10">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD10">
         <v>26</v>
@@ -2978,10 +2987,10 @@
         <v>95</v>
       </c>
       <c r="AF10">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AG10">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AH10">
         <v>20</v>
@@ -3002,16 +3011,16 @@
         <v>95</v>
       </c>
       <c r="AN10">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AO10">
         <v>110</v>
       </c>
       <c r="AP10">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AQ10">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AR10">
         <v>60</v>
@@ -3020,25 +3029,25 @@
         <v>130</v>
       </c>
       <c r="AT10">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU10">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AV10">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW10">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AX10">
         <v>9.6</v>
       </c>
       <c r="AY10">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ10">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA10">
         <v>70</v>
@@ -3053,10 +3062,10 @@
         <v>26</v>
       </c>
       <c r="BE10">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BF10">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BG10">
         <v>80</v>
@@ -3065,7 +3074,7 @@
         <v>4.3</v>
       </c>
       <c r="BI10">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BJ10">
         <v>10.5</v>
@@ -3077,52 +3086,52 @@
         <v>130</v>
       </c>
       <c r="BM10">
-        <v>10.5</v>
+        <v>90</v>
       </c>
       <c r="BN10">
         <v>4.2</v>
       </c>
       <c r="BO10">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BP10">
+        <v>9</v>
+      </c>
+      <c r="BQ10">
+        <v>8</v>
+      </c>
+      <c r="BR10">
+        <v>26</v>
+      </c>
+      <c r="BS10">
         <v>8.800000000000001</v>
       </c>
-      <c r="BQ10">
-        <v>7.8</v>
-      </c>
-      <c r="BR10">
-        <v>25</v>
-      </c>
-      <c r="BS10">
-        <v>9.6</v>
-      </c>
       <c r="BT10">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BU10">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BV10">
         <v>65</v>
       </c>
       <c r="BW10">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BX10">
         <v>65</v>
       </c>
       <c r="BY10">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BZ10">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="CA10">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="CB10" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3136,235 +3145,235 @@
         <v>89</v>
       </c>
       <c r="D11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E11" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F11">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="G11">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="H11">
-        <v>2.56</v>
+        <v>2.44</v>
       </c>
       <c r="I11">
-        <v>2.68</v>
+        <v>2.52</v>
       </c>
       <c r="J11">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K11">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="L11">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="M11">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="N11">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="O11">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="P11">
-        <v>1.91</v>
+        <v>2.06</v>
       </c>
       <c r="Q11">
-        <v>2.02</v>
+        <v>1.89</v>
       </c>
       <c r="R11">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="S11">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="T11">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="U11">
-        <v>2.14</v>
+        <v>2.26</v>
       </c>
       <c r="V11">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="W11">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="X11">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="Y11">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z11">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AA11">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AB11">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC11">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD11">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE11">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AF11">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG11">
         <v>14.5</v>
       </c>
       <c r="AH11">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AI11">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="AJ11">
         <v>55</v>
       </c>
       <c r="AK11">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AL11">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AM11">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AN11">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="AO11">
-        <v>25</v>
+        <v>18.5</v>
       </c>
       <c r="AP11">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AQ11">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AR11">
         <v>14.5</v>
       </c>
       <c r="AS11">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AT11">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AU11">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AV11">
         <v>10</v>
       </c>
       <c r="AW11">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AX11">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AY11">
         <v>11.5</v>
       </c>
       <c r="AZ11">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA11">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="BB11">
         <v>34</v>
       </c>
       <c r="BC11">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="BD11">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="BE11">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="BF11">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="BG11">
-        <v>20</v>
+        <v>15.5</v>
       </c>
       <c r="BH11">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="BI11">
-        <v>2.64</v>
+        <v>3.2</v>
       </c>
       <c r="BJ11">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK11">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="BL11">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="BM11">
-        <v>4.7</v>
+        <v>3.85</v>
       </c>
       <c r="BN11">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BO11">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="BP11">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BQ11">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="BR11">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="BS11">
-        <v>4.4</v>
+        <v>3.65</v>
       </c>
       <c r="BT11">
         <v>6.6</v>
       </c>
       <c r="BU11">
+        <v>4.8</v>
+      </c>
+      <c r="BV11">
+        <v>1000</v>
+      </c>
+      <c r="BW11">
         <v>4.2</v>
       </c>
-      <c r="BV11">
-        <v>24</v>
-      </c>
-      <c r="BW11">
+      <c r="BX11">
+        <v>1000</v>
+      </c>
+      <c r="BY11">
         <v>4</v>
       </c>
-      <c r="BX11">
-        <v>42</v>
-      </c>
-      <c r="BY11">
-        <v>4.4</v>
-      </c>
       <c r="BZ11">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="CA11">
-        <v>4.3</v>
+        <v>3.65</v>
       </c>
       <c r="CB11" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3378,37 +3387,37 @@
         <v>89</v>
       </c>
       <c r="D12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E12" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F12">
-        <v>2.06</v>
+        <v>1.91</v>
       </c>
       <c r="G12">
-        <v>2.14</v>
+        <v>1.96</v>
       </c>
       <c r="H12">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="I12">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="J12">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="K12">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="L12">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="M12">
         <v>1.13</v>
       </c>
       <c r="N12">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="O12">
         <v>1.55</v>
@@ -3417,196 +3426,196 @@
         <v>1.54</v>
       </c>
       <c r="Q12">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="R12">
         <v>1.19</v>
       </c>
       <c r="S12">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="T12">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="U12">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="V12">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="W12">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="X12">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Y12">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="Z12">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AA12">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB12">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC12">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD12">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="AE12">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="AF12">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG12">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH12">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AI12">
-        <v>500</v>
+        <v>260</v>
       </c>
       <c r="AJ12">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AK12">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL12">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AM12">
         <v>580</v>
       </c>
       <c r="AN12">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AO12">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AP12">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AQ12">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR12">
         <v>12.5</v>
       </c>
       <c r="AS12">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AT12">
-        <v>3.2</v>
+        <v>5.4</v>
       </c>
       <c r="AU12">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV12">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AW12">
+        <v>5</v>
+      </c>
+      <c r="AX12">
+        <v>8.6</v>
+      </c>
+      <c r="AY12">
+        <v>9.6</v>
+      </c>
+      <c r="AZ12">
+        <v>13.5</v>
+      </c>
+      <c r="BA12">
+        <v>5</v>
+      </c>
+      <c r="BB12">
+        <v>19.5</v>
+      </c>
+      <c r="BC12">
+        <v>16</v>
+      </c>
+      <c r="BD12">
+        <v>4.8</v>
+      </c>
+      <c r="BE12">
+        <v>5.1</v>
+      </c>
+      <c r="BF12">
+        <v>20</v>
+      </c>
+      <c r="BG12">
         <v>4.6</v>
       </c>
-      <c r="AX12">
-        <v>5.7</v>
-      </c>
-      <c r="AY12">
-        <v>10</v>
-      </c>
-      <c r="AZ12">
-        <v>20</v>
-      </c>
-      <c r="BA12">
-        <v>4.7</v>
-      </c>
-      <c r="BB12">
-        <v>14</v>
-      </c>
-      <c r="BC12">
-        <v>13</v>
-      </c>
-      <c r="BD12">
-        <v>4.5</v>
-      </c>
-      <c r="BE12">
-        <v>4.7</v>
-      </c>
-      <c r="BF12">
-        <v>4.5</v>
-      </c>
-      <c r="BG12">
-        <v>4.8</v>
-      </c>
       <c r="BH12">
-        <v>3.05</v>
+        <v>1000</v>
       </c>
       <c r="BI12">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="BJ12">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BK12">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BN12">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="BO12">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BP12">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BR12">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BS12">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BT12">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BU12">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="BV12">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BW12">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BX12">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="BY12">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BZ12">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="CA12">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="CB12" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3620,28 +3629,28 @@
         <v>90</v>
       </c>
       <c r="D13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E13" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F13">
-        <v>3.75</v>
+        <v>2.78</v>
       </c>
       <c r="G13">
-        <v>4.1</v>
+        <v>2.92</v>
       </c>
       <c r="H13">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="I13">
-        <v>2.48</v>
+        <v>3.3</v>
       </c>
       <c r="J13">
         <v>2.9</v>
       </c>
       <c r="K13">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="L13">
         <v>1.71</v>
@@ -3653,7 +3662,7 @@
         <v>2.28</v>
       </c>
       <c r="O13">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="P13">
         <v>1.41</v>
@@ -3665,61 +3674,61 @@
         <v>1.14</v>
       </c>
       <c r="S13">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="T13">
         <v>2.38</v>
       </c>
       <c r="U13">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="V13">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="W13">
-        <v>1.33</v>
+        <v>1.52</v>
       </c>
       <c r="X13">
+        <v>7</v>
+      </c>
+      <c r="Y13">
+        <v>8</v>
+      </c>
+      <c r="Z13">
+        <v>19.5</v>
+      </c>
+      <c r="AA13">
+        <v>70</v>
+      </c>
+      <c r="AB13">
+        <v>7.4</v>
+      </c>
+      <c r="AC13">
         <v>7.2</v>
       </c>
-      <c r="Y13">
-        <v>6.8</v>
-      </c>
-      <c r="Z13">
-        <v>14.5</v>
-      </c>
-      <c r="AA13">
-        <v>42</v>
-      </c>
-      <c r="AB13">
-        <v>9.4</v>
-      </c>
-      <c r="AC13">
-        <v>7.4</v>
-      </c>
       <c r="AD13">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AE13">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="AF13">
-        <v>27</v>
+        <v>19.5</v>
       </c>
       <c r="AG13">
-        <v>19.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH13">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AI13">
-        <v>190</v>
+        <v>500</v>
       </c>
       <c r="AJ13">
-        <v>500</v>
+        <v>260</v>
       </c>
       <c r="AK13">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AL13">
         <v>340</v>
@@ -3728,118 +3737,118 @@
         <v>500</v>
       </c>
       <c r="AN13">
-        <v>600</v>
+        <v>95</v>
       </c>
       <c r="AO13">
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="AP13">
         <v>6</v>
       </c>
       <c r="AQ13">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="AR13">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AS13">
-        <v>16</v>
+        <v>9.4</v>
       </c>
       <c r="AT13">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="AU13">
         <v>6.2</v>
       </c>
       <c r="AV13">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AW13">
-        <v>19.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX13">
-        <v>20</v>
+        <v>13.5</v>
       </c>
       <c r="AY13">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AZ13">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BA13">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BB13">
-        <v>9.199999999999999</v>
+        <v>42</v>
       </c>
       <c r="BC13">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="BD13">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BE13">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF13">
         <v>9.199999999999999</v>
       </c>
       <c r="BG13">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BH13">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="BI13">
         <v>2.2</v>
       </c>
       <c r="BJ13">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BK13">
+        <v>6.4</v>
+      </c>
+      <c r="BL13">
+        <v>1000</v>
+      </c>
+      <c r="BM13">
+        <v>12.5</v>
+      </c>
+      <c r="BN13">
+        <v>5.7</v>
+      </c>
+      <c r="BO13">
+        <v>4.8</v>
+      </c>
+      <c r="BP13">
+        <v>30</v>
+      </c>
+      <c r="BQ13">
+        <v>9</v>
+      </c>
+      <c r="BR13">
+        <v>1000</v>
+      </c>
+      <c r="BS13">
+        <v>10.5</v>
+      </c>
+      <c r="BT13">
         <v>6.2</v>
       </c>
-      <c r="BL13">
-        <v>1000</v>
-      </c>
-      <c r="BM13">
+      <c r="BU13">
+        <v>5.2</v>
+      </c>
+      <c r="BV13">
+        <v>36</v>
+      </c>
+      <c r="BW13">
+        <v>9.6</v>
+      </c>
+      <c r="BX13">
+        <v>70</v>
+      </c>
+      <c r="BY13">
         <v>11</v>
-      </c>
-      <c r="BN13">
-        <v>7.2</v>
-      </c>
-      <c r="BO13">
-        <v>5.2</v>
-      </c>
-      <c r="BP13">
-        <v>46</v>
-      </c>
-      <c r="BQ13">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BR13">
-        <v>1000</v>
-      </c>
-      <c r="BS13">
-        <v>10</v>
-      </c>
-      <c r="BT13">
-        <v>5.2</v>
-      </c>
-      <c r="BU13">
-        <v>3.85</v>
-      </c>
-      <c r="BV13">
-        <v>25</v>
-      </c>
-      <c r="BW13">
-        <v>7.8</v>
-      </c>
-      <c r="BX13">
-        <v>1000</v>
-      </c>
-      <c r="BY13">
-        <v>9.6</v>
       </c>
       <c r="BZ13">
         <v>0</v>
@@ -3848,7 +3857,7 @@
         <v>0</v>
       </c>
       <c r="CB13" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -3862,70 +3871,70 @@
         <v>91</v>
       </c>
       <c r="D14" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E14" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F14">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="G14">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="H14">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="I14">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="J14">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="K14">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="L14">
         <v>1.59</v>
       </c>
       <c r="M14">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="N14">
         <v>2.66</v>
       </c>
       <c r="O14">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="P14">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="Q14">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="R14">
         <v>1.19</v>
       </c>
       <c r="S14">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="T14">
         <v>2.08</v>
       </c>
       <c r="U14">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="V14">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W14">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="X14">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="Y14">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="Z14">
         <v>23</v>
@@ -3934,37 +3943,37 @@
         <v>170</v>
       </c>
       <c r="AB14">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AC14">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD14">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE14">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AF14">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AG14">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AH14">
         <v>29</v>
       </c>
       <c r="AI14">
-        <v>350</v>
+        <v>100</v>
       </c>
       <c r="AJ14">
+        <v>50</v>
+      </c>
+      <c r="AK14">
         <v>46</v>
       </c>
-      <c r="AK14">
-        <v>44</v>
-      </c>
       <c r="AL14">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AM14">
         <v>580</v>
@@ -3973,37 +3982,37 @@
         <v>50</v>
       </c>
       <c r="AO14">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AP14">
         <v>7.4</v>
       </c>
       <c r="AQ14">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR14">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AS14">
         <v>46</v>
       </c>
       <c r="AT14">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU14">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV14">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AW14">
         <v>34</v>
       </c>
       <c r="AX14">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY14">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ14">
         <v>19.5</v>
@@ -4012,25 +4021,25 @@
         <v>50</v>
       </c>
       <c r="BB14">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BC14">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BD14">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BE14">
         <v>65</v>
       </c>
       <c r="BF14">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BG14">
         <v>46</v>
       </c>
       <c r="BH14">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="BI14">
         <v>2.3</v>
@@ -4039,58 +4048,300 @@
         <v>13</v>
       </c>
       <c r="BK14">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="BN14">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BO14">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="BP14">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BQ14">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="BR14">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS14">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="BT14">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BU14">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BV14">
         <v>38</v>
       </c>
       <c r="BW14">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="BX14">
         <v>1000</v>
       </c>
       <c r="BY14">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="BZ14">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="CA14">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="CB14" t="s">
-        <v>118</v>
+        <v>121</v>
+      </c>
+    </row>
+    <row r="15" spans="1:80">
+      <c r="A15" t="s">
+        <v>83</v>
+      </c>
+      <c r="B15" t="s">
+        <v>85</v>
+      </c>
+      <c r="C15" t="s">
+        <v>92</v>
+      </c>
+      <c r="D15" t="s">
+        <v>106</v>
+      </c>
+      <c r="E15" t="s">
+        <v>120</v>
+      </c>
+      <c r="F15">
+        <v>1.15</v>
+      </c>
+      <c r="G15">
+        <v>1.18</v>
+      </c>
+      <c r="H15">
+        <v>23</v>
+      </c>
+      <c r="I15">
+        <v>40</v>
+      </c>
+      <c r="J15">
+        <v>8.6</v>
+      </c>
+      <c r="K15">
+        <v>10.5</v>
+      </c>
+      <c r="L15">
+        <v>1.25</v>
+      </c>
+      <c r="M15">
+        <v>1.04</v>
+      </c>
+      <c r="N15">
+        <v>5.3</v>
+      </c>
+      <c r="O15">
+        <v>1.2</v>
+      </c>
+      <c r="P15">
+        <v>2.46</v>
+      </c>
+      <c r="Q15">
+        <v>1.58</v>
+      </c>
+      <c r="R15">
+        <v>1.59</v>
+      </c>
+      <c r="S15">
+        <v>2.46</v>
+      </c>
+      <c r="T15">
+        <v>2.86</v>
+      </c>
+      <c r="U15">
+        <v>1.45</v>
+      </c>
+      <c r="V15">
+        <v>1.02</v>
+      </c>
+      <c r="W15">
+        <v>6.6</v>
+      </c>
+      <c r="X15">
+        <v>34</v>
+      </c>
+      <c r="Y15">
+        <v>90</v>
+      </c>
+      <c r="Z15">
+        <v>460</v>
+      </c>
+      <c r="AA15">
+        <v>1000</v>
+      </c>
+      <c r="AB15">
+        <v>9</v>
+      </c>
+      <c r="AC15">
+        <v>27</v>
+      </c>
+      <c r="AD15">
+        <v>140</v>
+      </c>
+      <c r="AE15">
+        <v>1000</v>
+      </c>
+      <c r="AF15">
+        <v>7</v>
+      </c>
+      <c r="AG15">
+        <v>15</v>
+      </c>
+      <c r="AH15">
+        <v>80</v>
+      </c>
+      <c r="AI15">
+        <v>1000</v>
+      </c>
+      <c r="AJ15">
+        <v>7.6</v>
+      </c>
+      <c r="AK15">
+        <v>17.5</v>
+      </c>
+      <c r="AL15">
+        <v>95</v>
+      </c>
+      <c r="AM15">
+        <v>640</v>
+      </c>
+      <c r="AN15">
+        <v>3.75</v>
+      </c>
+      <c r="AO15">
+        <v>1000</v>
+      </c>
+      <c r="AP15">
+        <v>7.8</v>
+      </c>
+      <c r="AQ15">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR15">
+        <v>9</v>
+      </c>
+      <c r="AS15">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT15">
+        <v>7.4</v>
+      </c>
+      <c r="AU15">
+        <v>18.5</v>
+      </c>
+      <c r="AV15">
+        <v>8.6</v>
+      </c>
+      <c r="AW15">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX15">
+        <v>5.8</v>
+      </c>
+      <c r="AY15">
+        <v>12</v>
+      </c>
+      <c r="AZ15">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BA15">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB15">
+        <v>6.4</v>
+      </c>
+      <c r="BC15">
+        <v>12</v>
+      </c>
+      <c r="BD15">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE15">
+        <v>9</v>
+      </c>
+      <c r="BF15">
+        <v>3.2</v>
+      </c>
+      <c r="BG15">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BH15">
+        <v>4.8</v>
+      </c>
+      <c r="BI15">
+        <v>3.55</v>
+      </c>
+      <c r="BJ15">
+        <v>19.5</v>
+      </c>
+      <c r="BK15">
+        <v>11.5</v>
+      </c>
+      <c r="BL15">
+        <v>1000</v>
+      </c>
+      <c r="BM15">
+        <v>21</v>
+      </c>
+      <c r="BN15">
+        <v>3.5</v>
+      </c>
+      <c r="BO15">
+        <v>3</v>
+      </c>
+      <c r="BP15">
+        <v>5.8</v>
+      </c>
+      <c r="BQ15">
+        <v>4.3</v>
+      </c>
+      <c r="BR15">
+        <v>30</v>
+      </c>
+      <c r="BS15">
+        <v>21</v>
+      </c>
+      <c r="BT15">
+        <v>27</v>
+      </c>
+      <c r="BU15">
+        <v>16</v>
+      </c>
+      <c r="BV15">
+        <v>1000</v>
+      </c>
+      <c r="BW15">
+        <v>21</v>
+      </c>
+      <c r="BX15">
+        <v>1000</v>
+      </c>
+      <c r="BY15">
+        <v>21</v>
+      </c>
+      <c r="BZ15">
+        <v>8.6</v>
+      </c>
+      <c r="CA15">
+        <v>6.2</v>
+      </c>
+      <c r="CB15" t="s">
+        <v>121</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-24.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="126">
   <si>
     <t>League</t>
   </si>
@@ -271,6 +271,9 @@
     <t>Moroccan Botola Pro 1</t>
   </si>
   <si>
+    <t>CONCACAF Nations League A</t>
+  </si>
+  <si>
     <t>2026-09-24</t>
   </si>
   <si>
@@ -295,6 +298,9 @@
     <t>21:30:00</t>
   </si>
   <si>
+    <t>23:00:00</t>
+  </si>
+  <si>
     <t>Rivers United FC</t>
   </si>
   <si>
@@ -337,6 +343,9 @@
     <t>LDU de Portoviejo</t>
   </si>
   <si>
+    <t>Haiti</t>
+  </si>
+  <si>
     <t>Kun Khalifat FC</t>
   </si>
   <si>
@@ -379,7 +388,10 @@
     <t>22 de Julio FC</t>
   </si>
   <si>
-    <t>2026-09-24 10:35:23</t>
+    <t>Trinidad &amp; Tobago</t>
+  </si>
+  <si>
+    <t>2026-09-24 12:51:43</t>
   </si>
 </sst>
 </file>
@@ -711,7 +723,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB15"/>
+  <dimension ref="A1:CB16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -961,76 +973,76 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E2" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="F2">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="G2">
-        <v>1.55</v>
+        <v>1.11</v>
       </c>
       <c r="H2">
-        <v>5.4</v>
+        <v>40</v>
       </c>
       <c r="I2">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="J2">
-        <v>5.1</v>
+        <v>12</v>
       </c>
       <c r="K2">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="L2">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>12.5</v>
+      </c>
+      <c r="O2">
+        <v>1.08</v>
+      </c>
+      <c r="P2">
+        <v>4.1</v>
+      </c>
+      <c r="Q2">
+        <v>1.28</v>
+      </c>
+      <c r="R2">
+        <v>2.04</v>
+      </c>
+      <c r="S2">
+        <v>1.87</v>
+      </c>
+      <c r="T2">
+        <v>1.89</v>
+      </c>
+      <c r="U2">
+        <v>1.89</v>
+      </c>
+      <c r="V2">
         <v>1.02</v>
       </c>
-      <c r="N2">
-        <v>7.2</v>
-      </c>
-      <c r="O2">
-        <v>1.07</v>
-      </c>
-      <c r="P2">
-        <v>3.5</v>
-      </c>
-      <c r="Q2">
-        <v>1.24</v>
-      </c>
-      <c r="R2">
-        <v>2</v>
-      </c>
-      <c r="S2">
-        <v>1.81</v>
-      </c>
-      <c r="T2">
-        <v>1.01</v>
-      </c>
-      <c r="U2">
-        <v>2.08</v>
-      </c>
-      <c r="V2">
-        <v>1.06</v>
-      </c>
       <c r="W2">
-        <v>1.9</v>
+        <v>7.4</v>
       </c>
       <c r="X2">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="Y2">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="Z2">
         <v>1000</v>
@@ -1039,163 +1051,163 @@
         <v>1000</v>
       </c>
       <c r="AB2">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AC2">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="AD2">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AE2">
         <v>1000</v>
       </c>
       <c r="AF2">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG2">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AH2">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="AI2">
-        <v>1000</v>
+        <v>350</v>
       </c>
       <c r="AJ2">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AK2">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AL2">
-        <v>970</v>
+        <v>27</v>
       </c>
       <c r="AM2">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AN2">
-        <v>29</v>
+        <v>4.1</v>
       </c>
       <c r="AO2">
         <v>1000</v>
       </c>
       <c r="AP2">
-        <v>19</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ2">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="AR2">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="AS2">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT2">
-        <v>2.5</v>
+        <v>11.5</v>
       </c>
       <c r="AU2">
-        <v>9.800000000000001</v>
+        <v>20</v>
       </c>
       <c r="AV2">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="AW2">
-        <v>4.2</v>
+        <v>30</v>
       </c>
       <c r="AX2">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="AY2">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AZ2">
-        <v>1.5</v>
+        <v>28</v>
       </c>
       <c r="BA2">
-        <v>4.2</v>
+        <v>44</v>
       </c>
       <c r="BB2">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BC2">
+        <v>10</v>
+      </c>
+      <c r="BD2">
         <v>9.4</v>
       </c>
-      <c r="BD2">
-        <v>4.3</v>
-      </c>
       <c r="BE2">
-        <v>1.54</v>
+        <v>110</v>
       </c>
       <c r="BF2">
-        <v>2</v>
+        <v>3.35</v>
       </c>
       <c r="BG2">
-        <v>10.5</v>
+        <v>28</v>
       </c>
       <c r="BH2">
         <v>1000</v>
       </c>
       <c r="BI2">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BJ2">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK2">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BL2">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="BM2">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN2">
-        <v>1000</v>
+        <v>1.84</v>
       </c>
       <c r="BO2">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="BP2">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BQ2">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS2">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BT2">
         <v>1000</v>
       </c>
       <c r="BU2">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="BY2">
-        <v>1.01</v>
+        <v>75</v>
       </c>
       <c r="BZ2">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="CA2">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="CB2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1203,115 +1215,115 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F3">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="G3">
+        <v>4.4</v>
+      </c>
+      <c r="H3">
+        <v>2.42</v>
+      </c>
+      <c r="I3">
+        <v>2.44</v>
+      </c>
+      <c r="J3">
+        <v>2.8</v>
+      </c>
+      <c r="K3">
+        <v>2.82</v>
+      </c>
+      <c r="L3">
+        <v>1.86</v>
+      </c>
+      <c r="M3">
+        <v>1.22</v>
+      </c>
+      <c r="N3">
+        <v>2.06</v>
+      </c>
+      <c r="O3">
+        <v>1.93</v>
+      </c>
+      <c r="P3">
+        <v>1.33</v>
+      </c>
+      <c r="Q3">
         <v>3.95</v>
       </c>
-      <c r="H3">
-        <v>2.54</v>
-      </c>
-      <c r="I3">
-        <v>2.56</v>
-      </c>
-      <c r="J3">
-        <v>2.82</v>
-      </c>
-      <c r="K3">
-        <v>2.84</v>
-      </c>
-      <c r="L3">
-        <v>1.79</v>
-      </c>
-      <c r="M3">
-        <v>1.2</v>
-      </c>
-      <c r="N3">
-        <v>2.12</v>
-      </c>
-      <c r="O3">
-        <v>1.87</v>
-      </c>
-      <c r="P3">
-        <v>1.36</v>
-      </c>
-      <c r="Q3">
-        <v>3.7</v>
-      </c>
       <c r="R3">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="S3">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="T3">
+        <v>2.8</v>
+      </c>
+      <c r="U3">
+        <v>1.53</v>
+      </c>
+      <c r="V3">
+        <v>1.69</v>
+      </c>
+      <c r="W3">
+        <v>1.29</v>
+      </c>
+      <c r="X3">
+        <v>5.6</v>
+      </c>
+      <c r="Y3">
+        <v>5.5</v>
+      </c>
+      <c r="Z3">
+        <v>11.5</v>
+      </c>
+      <c r="AA3">
+        <v>38</v>
+      </c>
+      <c r="AB3">
         <v>9</v>
-      </c>
-      <c r="T3">
-        <v>2.7</v>
-      </c>
-      <c r="U3">
-        <v>1.57</v>
-      </c>
-      <c r="V3">
-        <v>1.64</v>
-      </c>
-      <c r="W3">
-        <v>1.34</v>
-      </c>
-      <c r="X3">
-        <v>5.9</v>
-      </c>
-      <c r="Y3">
-        <v>6.2</v>
-      </c>
-      <c r="Z3">
-        <v>13</v>
-      </c>
-      <c r="AA3">
-        <v>44</v>
-      </c>
-      <c r="AB3">
-        <v>8.4</v>
       </c>
       <c r="AC3">
         <v>7.2</v>
       </c>
       <c r="AD3">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE3">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AF3">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AG3">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AH3">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AI3">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AJ3">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="AK3">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="AL3">
-        <v>150</v>
+        <v>190</v>
       </c>
       <c r="AM3">
         <v>500</v>
@@ -1323,70 +1335,70 @@
         <v>65</v>
       </c>
       <c r="AP3">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="AQ3">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="AR3">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AS3">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AT3">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AU3">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV3">
         <v>14</v>
       </c>
       <c r="AW3">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AX3">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AY3">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AZ3">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BA3">
         <v>90</v>
       </c>
       <c r="BB3">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="BC3">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="BD3">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="BE3">
         <v>230</v>
       </c>
       <c r="BF3">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="BG3">
         <v>55</v>
       </c>
       <c r="BH3">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="BI3">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="BJ3">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BK3">
-        <v>7.8</v>
+        <v>12.5</v>
       </c>
       <c r="BL3">
         <v>1000</v>
@@ -1395,49 +1407,49 @@
         <v>300</v>
       </c>
       <c r="BN3">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BO3">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BP3">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BQ3">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BR3">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="BS3">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="BT3">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BU3">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BV3">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BW3">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="BX3">
         <v>70</v>
       </c>
       <c r="BY3">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BZ3">
         <v>85</v>
       </c>
       <c r="CA3">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="CB3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1445,34 +1457,34 @@
         <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E4" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="F4">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="G4">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="H4">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="I4">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="J4">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="K4">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="L4">
         <v>1.54</v>
@@ -1481,13 +1493,13 @@
         <v>1.11</v>
       </c>
       <c r="N4">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="O4">
         <v>1.52</v>
       </c>
       <c r="P4">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="Q4">
         <v>2.58</v>
@@ -1499,40 +1511,40 @@
         <v>5.4</v>
       </c>
       <c r="T4">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="U4">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="V4">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="W4">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X4">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="Y4">
         <v>4.9</v>
       </c>
       <c r="Z4">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AA4">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AB4">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AC4">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AD4">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE4">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AF4">
         <v>200</v>
@@ -1541,7 +1553,7 @@
         <v>90</v>
       </c>
       <c r="AH4">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AI4">
         <v>120</v>
@@ -1550,22 +1562,22 @@
         <v>1000</v>
       </c>
       <c r="AK4">
-        <v>790</v>
+        <v>890</v>
       </c>
       <c r="AL4">
         <v>820</v>
       </c>
       <c r="AM4">
-        <v>910</v>
+        <v>970</v>
       </c>
       <c r="AN4">
         <v>1000</v>
       </c>
       <c r="AO4">
-        <v>9.4</v>
+        <v>12.5</v>
       </c>
       <c r="AP4">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ4">
         <v>4.8</v>
@@ -1574,61 +1586,61 @@
         <v>5.2</v>
       </c>
       <c r="AS4">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AT4">
         <v>28</v>
       </c>
       <c r="AU4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV4">
         <v>13</v>
       </c>
       <c r="AW4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX4">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AY4">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AZ4">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BA4">
         <v>95</v>
       </c>
       <c r="BB4">
-        <v>29</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC4">
-        <v>28</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD4">
-        <v>26</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE4">
         <v>250</v>
       </c>
       <c r="BF4">
-        <v>80</v>
+        <v>15</v>
       </c>
       <c r="BG4">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH4">
-        <v>1000</v>
+        <v>2.84</v>
       </c>
       <c r="BI4">
-        <v>1.42</v>
+        <v>2.68</v>
       </c>
       <c r="BJ4">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BK4">
-        <v>2.68</v>
+        <v>11</v>
       </c>
       <c r="BL4">
         <v>1000</v>
@@ -1637,49 +1649,49 @@
         <v>320</v>
       </c>
       <c r="BN4">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BO4">
-        <v>2.68</v>
+        <v>11</v>
       </c>
       <c r="BP4">
         <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>2.68</v>
+        <v>20</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>2.68</v>
+        <v>20</v>
       </c>
       <c r="BT4">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="BU4">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="BV4">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BW4">
-        <v>1.5</v>
+        <v>7.2</v>
       </c>
       <c r="BX4">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY4">
-        <v>2.68</v>
+        <v>15</v>
       </c>
       <c r="BZ4">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="CA4">
-        <v>2.68</v>
+        <v>10.5</v>
       </c>
       <c r="CB4" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1687,241 +1699,241 @@
         <v>81</v>
       </c>
       <c r="B5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D5" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E5" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F5">
-        <v>1.86</v>
+        <v>1.64</v>
       </c>
       <c r="G5">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="H5">
+        <v>5.9</v>
+      </c>
+      <c r="I5">
+        <v>6</v>
+      </c>
+      <c r="J5">
         <v>4.5</v>
       </c>
-      <c r="I5">
+      <c r="K5">
         <v>4.6</v>
       </c>
-      <c r="J5">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>4.1</v>
-      </c>
       <c r="L5">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="M5">
         <v>1.04</v>
       </c>
       <c r="N5">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="O5">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P5">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="Q5">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="R5">
+        <v>1.66</v>
+      </c>
+      <c r="S5">
+        <v>2.46</v>
+      </c>
+      <c r="T5">
         <v>1.64</v>
       </c>
-      <c r="S5">
+      <c r="U5">
         <v>2.52</v>
       </c>
-      <c r="T5">
-        <v>1.6</v>
-      </c>
-      <c r="U5">
-        <v>2.6</v>
-      </c>
       <c r="V5">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="W5">
-        <v>2.14</v>
+        <v>2.54</v>
       </c>
       <c r="X5">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Y5">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="Z5">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="AA5">
-        <v>90</v>
+        <v>140</v>
       </c>
       <c r="AB5">
+        <v>12</v>
+      </c>
+      <c r="AC5">
+        <v>11</v>
+      </c>
+      <c r="AD5">
+        <v>21</v>
+      </c>
+      <c r="AE5">
+        <v>70</v>
+      </c>
+      <c r="AF5">
+        <v>11.5</v>
+      </c>
+      <c r="AG5">
+        <v>9.6</v>
+      </c>
+      <c r="AH5">
+        <v>16</v>
+      </c>
+      <c r="AI5">
+        <v>50</v>
+      </c>
+      <c r="AJ5">
+        <v>16</v>
+      </c>
+      <c r="AK5">
+        <v>14.5</v>
+      </c>
+      <c r="AL5">
+        <v>24</v>
+      </c>
+      <c r="AM5">
+        <v>70</v>
+      </c>
+      <c r="AN5">
+        <v>7</v>
+      </c>
+      <c r="AO5">
+        <v>60</v>
+      </c>
+      <c r="AP5">
+        <v>25</v>
+      </c>
+      <c r="AQ5">
+        <v>27</v>
+      </c>
+      <c r="AR5">
+        <v>48</v>
+      </c>
+      <c r="AS5">
+        <v>100</v>
+      </c>
+      <c r="AT5">
+        <v>11.5</v>
+      </c>
+      <c r="AU5">
+        <v>10</v>
+      </c>
+      <c r="AV5">
+        <v>20</v>
+      </c>
+      <c r="AW5">
+        <v>60</v>
+      </c>
+      <c r="AX5">
+        <v>11</v>
+      </c>
+      <c r="AY5">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ5">
+        <v>15.5</v>
+      </c>
+      <c r="BA5">
+        <v>46</v>
+      </c>
+      <c r="BB5">
+        <v>15</v>
+      </c>
+      <c r="BC5">
         <v>13.5</v>
-      </c>
-      <c r="AC5">
-        <v>9.4</v>
-      </c>
-      <c r="AD5">
-        <v>17</v>
-      </c>
-      <c r="AE5">
-        <v>50</v>
-      </c>
-      <c r="AF5">
-        <v>13</v>
-      </c>
-      <c r="AG5">
-        <v>10</v>
-      </c>
-      <c r="AH5">
-        <v>14.5</v>
-      </c>
-      <c r="AI5">
-        <v>42</v>
-      </c>
-      <c r="AJ5">
-        <v>20</v>
-      </c>
-      <c r="AK5">
-        <v>16.5</v>
-      </c>
-      <c r="AL5">
-        <v>25</v>
-      </c>
-      <c r="AM5">
-        <v>60</v>
-      </c>
-      <c r="AN5">
-        <v>8.4</v>
-      </c>
-      <c r="AO5">
-        <v>38</v>
-      </c>
-      <c r="AP5">
-        <v>22</v>
-      </c>
-      <c r="AQ5">
-        <v>21</v>
-      </c>
-      <c r="AR5">
-        <v>34</v>
-      </c>
-      <c r="AS5">
-        <v>75</v>
-      </c>
-      <c r="AT5">
-        <v>12.5</v>
-      </c>
-      <c r="AU5">
-        <v>9</v>
-      </c>
-      <c r="AV5">
-        <v>16</v>
-      </c>
-      <c r="AW5">
-        <v>44</v>
-      </c>
-      <c r="AX5">
-        <v>12.5</v>
-      </c>
-      <c r="AY5">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ5">
-        <v>13.5</v>
-      </c>
-      <c r="BA5">
-        <v>38</v>
-      </c>
-      <c r="BB5">
-        <v>19</v>
-      </c>
-      <c r="BC5">
-        <v>15.5</v>
       </c>
       <c r="BD5">
         <v>23</v>
       </c>
       <c r="BE5">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BF5">
-        <v>8</v>
+        <v>6.6</v>
       </c>
       <c r="BG5">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="BH5">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BI5">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BJ5">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BK5">
         <v>8</v>
       </c>
       <c r="BL5">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="BM5">
         <v>65</v>
       </c>
       <c r="BN5">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BO5">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BP5">
-        <v>12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BQ5">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="BR5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BS5">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BT5">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU5">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BV5">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="BW5">
-        <v>26</v>
+        <v>12.5</v>
       </c>
       <c r="BX5">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BY5">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BZ5">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="CA5">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="CB5" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1929,28 +1941,28 @@
         <v>81</v>
       </c>
       <c r="B6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D6" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E6" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="F6">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="G6">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="H6">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="I6">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="J6">
         <v>3.35</v>
@@ -1965,76 +1977,76 @@
         <v>1.1</v>
       </c>
       <c r="N6">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="O6">
         <v>1.46</v>
       </c>
       <c r="P6">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="Q6">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R6">
         <v>1.25</v>
       </c>
       <c r="S6">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T6">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="U6">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="V6">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W6">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="X6">
         <v>11</v>
       </c>
       <c r="Y6">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA6">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AB6">
         <v>9.6</v>
       </c>
       <c r="AC6">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AD6">
         <v>12</v>
       </c>
       <c r="AE6">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF6">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AG6">
         <v>13</v>
       </c>
       <c r="AH6">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AI6">
         <v>55</v>
       </c>
       <c r="AJ6">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AK6">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AL6">
         <v>55</v>
@@ -2043,52 +2055,52 @@
         <v>130</v>
       </c>
       <c r="AN6">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AO6">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AP6">
         <v>10</v>
       </c>
       <c r="AQ6">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AR6">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AS6">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AT6">
         <v>9.199999999999999</v>
       </c>
       <c r="AU6">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV6">
         <v>11.5</v>
       </c>
       <c r="AW6">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AX6">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AY6">
         <v>12.5</v>
       </c>
       <c r="AZ6">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA6">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BB6">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BC6">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BD6">
         <v>50</v>
@@ -2097,7 +2109,7 @@
         <v>110</v>
       </c>
       <c r="BF6">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BG6">
         <v>32</v>
@@ -2121,49 +2133,49 @@
         <v>130</v>
       </c>
       <c r="BN6">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BO6">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BP6">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="BQ6">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BR6">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="BS6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BT6">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BU6">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BV6">
         <v>24</v>
       </c>
       <c r="BW6">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BX6">
         <v>48</v>
       </c>
       <c r="BY6">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BZ6">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="CA6">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="CB6" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2171,106 +2183,106 @@
         <v>81</v>
       </c>
       <c r="B7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D7" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E7" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="F7">
+        <v>1.18</v>
+      </c>
+      <c r="G7">
         <v>1.19</v>
       </c>
-      <c r="G7">
-        <v>1.2</v>
-      </c>
       <c r="H7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J7">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="K7">
+        <v>9.6</v>
+      </c>
+      <c r="L7">
+        <v>1.21</v>
+      </c>
+      <c r="M7">
+        <v>1.02</v>
+      </c>
+      <c r="N7">
         <v>8.6</v>
       </c>
-      <c r="L7">
-        <v>1.22</v>
-      </c>
-      <c r="M7">
-        <v>1.03</v>
-      </c>
-      <c r="N7">
-        <v>8</v>
-      </c>
       <c r="O7">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="P7">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="Q7">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="R7">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="S7">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="T7">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="U7">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="V7">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W7">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="X7">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="Y7">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="Z7">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="AA7">
         <v>1000</v>
       </c>
       <c r="AB7">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AC7">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AD7">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AE7">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="AF7">
         <v>9</v>
       </c>
       <c r="AG7">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH7">
         <v>36</v>
       </c>
       <c r="AI7">
-        <v>220</v>
+        <v>190</v>
       </c>
       <c r="AJ7">
         <v>8.800000000000001</v>
@@ -2279,52 +2291,52 @@
         <v>13.5</v>
       </c>
       <c r="AL7">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM7">
         <v>170</v>
       </c>
       <c r="AN7">
-        <v>2.92</v>
+        <v>2.82</v>
       </c>
       <c r="AO7">
-        <v>410</v>
+        <v>380</v>
       </c>
       <c r="AP7">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AQ7">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AR7">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AS7">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="AT7">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU7">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AV7">
         <v>60</v>
       </c>
       <c r="AW7">
-        <v>46</v>
+        <v>85</v>
       </c>
       <c r="AX7">
         <v>8.800000000000001</v>
       </c>
       <c r="AY7">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ7">
         <v>34</v>
       </c>
       <c r="BA7">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="BB7">
         <v>8.6</v>
@@ -2333,70 +2345,70 @@
         <v>12.5</v>
       </c>
       <c r="BD7">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BE7">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="BF7">
-        <v>2.86</v>
+        <v>2.74</v>
       </c>
       <c r="BG7">
         <v>32</v>
       </c>
       <c r="BH7">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BI7">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BJ7">
         <v>14</v>
       </c>
       <c r="BK7">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BL7">
         <v>160</v>
       </c>
       <c r="BM7">
-        <v>140</v>
+        <v>23</v>
       </c>
       <c r="BN7">
         <v>3.95</v>
       </c>
       <c r="BO7">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BP7">
         <v>5.9</v>
       </c>
       <c r="BQ7">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="BR7">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BS7">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BT7">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BU7">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BV7">
         <v>150</v>
       </c>
       <c r="BW7">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BX7">
         <v>110</v>
       </c>
       <c r="BY7">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BZ7">
         <v>0</v>
@@ -2405,7 +2417,7 @@
         <v>0</v>
       </c>
       <c r="CB7" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2413,28 +2425,28 @@
         <v>81</v>
       </c>
       <c r="B8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D8" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E8" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="F8">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="G8">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="H8">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="I8">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="J8">
         <v>3.9</v>
@@ -2449,61 +2461,61 @@
         <v>1.03</v>
       </c>
       <c r="N8">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="O8">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P8">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="Q8">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="R8">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="S8">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="T8">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="U8">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="V8">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W8">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="X8">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="Y8">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Z8">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA8">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AB8">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AC8">
         <v>9.6</v>
       </c>
       <c r="AD8">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE8">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF8">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG8">
         <v>13</v>
@@ -2512,16 +2524,16 @@
         <v>12.5</v>
       </c>
       <c r="AI8">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AJ8">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AK8">
         <v>24</v>
       </c>
       <c r="AL8">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AM8">
         <v>42</v>
@@ -2530,19 +2542,19 @@
         <v>13.5</v>
       </c>
       <c r="AO8">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AP8">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AQ8">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AR8">
         <v>20</v>
       </c>
       <c r="AS8">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AT8">
         <v>18.5</v>
@@ -2554,10 +2566,10 @@
         <v>11.5</v>
       </c>
       <c r="AW8">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AX8">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY8">
         <v>12.5</v>
@@ -2566,7 +2578,7 @@
         <v>12</v>
       </c>
       <c r="BA8">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BB8">
         <v>40</v>
@@ -2575,7 +2587,7 @@
         <v>23</v>
       </c>
       <c r="BD8">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BE8">
         <v>38</v>
@@ -2584,19 +2596,19 @@
         <v>12</v>
       </c>
       <c r="BG8">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BH8">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BI8">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BJ8">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BK8">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BL8">
         <v>60</v>
@@ -2605,49 +2617,49 @@
         <v>55</v>
       </c>
       <c r="BN8">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BO8">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BP8">
         <v>19</v>
       </c>
       <c r="BQ8">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BR8">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BS8">
         <v>10.5</v>
       </c>
       <c r="BT8">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BU8">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BV8">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BW8">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BX8">
         <v>22</v>
       </c>
       <c r="BY8">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BZ8">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="CA8">
         <v>12</v>
       </c>
       <c r="CB8" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2655,16 +2667,16 @@
         <v>81</v>
       </c>
       <c r="B9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D9" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E9" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="F9">
         <v>2.52</v>
@@ -2691,28 +2703,28 @@
         <v>1.11</v>
       </c>
       <c r="N9">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="O9">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="P9">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="Q9">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="R9">
         <v>1.24</v>
       </c>
       <c r="S9">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="T9">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U9">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="V9">
         <v>1.42</v>
@@ -2724,7 +2736,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="Y9">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="Z9">
         <v>21</v>
@@ -2757,7 +2769,7 @@
         <v>65</v>
       </c>
       <c r="AJ9">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AK9">
         <v>32</v>
@@ -2772,13 +2784,13 @@
         <v>34</v>
       </c>
       <c r="AO9">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AP9">
         <v>9.4</v>
       </c>
       <c r="AQ9">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AR9">
         <v>19</v>
@@ -2787,7 +2799,7 @@
         <v>55</v>
       </c>
       <c r="AT9">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AU9">
         <v>7</v>
@@ -2826,7 +2838,7 @@
         <v>29</v>
       </c>
       <c r="BG9">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BH9">
         <v>2.8</v>
@@ -2847,7 +2859,7 @@
         <v>140</v>
       </c>
       <c r="BN9">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BO9">
         <v>4.8</v>
@@ -2856,40 +2868,40 @@
         <v>21</v>
       </c>
       <c r="BQ9">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BR9">
         <v>42</v>
       </c>
       <c r="BS9">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BT9">
         <v>6.2</v>
       </c>
       <c r="BU9">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BV9">
         <v>30</v>
       </c>
       <c r="BW9">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BX9">
         <v>50</v>
       </c>
       <c r="BY9">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BZ9">
         <v>44</v>
       </c>
       <c r="CA9">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="CB9" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2897,22 +2909,22 @@
         <v>81</v>
       </c>
       <c r="B10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D10" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E10" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F10">
+        <v>1.49</v>
+      </c>
+      <c r="G10">
         <v>1.5</v>
-      </c>
-      <c r="G10">
-        <v>1.51</v>
       </c>
       <c r="H10">
         <v>7.4</v>
@@ -2927,31 +2939,31 @@
         <v>5.1</v>
       </c>
       <c r="L10">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="M10">
         <v>1.04</v>
       </c>
       <c r="N10">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="O10">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P10">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="Q10">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="R10">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="S10">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="T10">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="U10">
         <v>2.2</v>
@@ -2960,28 +2972,28 @@
         <v>1.15</v>
       </c>
       <c r="W10">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="X10">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Y10">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Z10">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AA10">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AB10">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC10">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD10">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE10">
         <v>95</v>
@@ -2990,7 +3002,7 @@
         <v>10.5</v>
       </c>
       <c r="AG10">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH10">
         <v>20</v>
@@ -3008,22 +3020,22 @@
         <v>27</v>
       </c>
       <c r="AM10">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN10">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="AO10">
         <v>110</v>
       </c>
       <c r="AP10">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ10">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AR10">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AS10">
         <v>130</v>
@@ -3041,31 +3053,31 @@
         <v>80</v>
       </c>
       <c r="AX10">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY10">
         <v>9.4</v>
       </c>
       <c r="AZ10">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BA10">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BB10">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BC10">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BD10">
         <v>26</v>
       </c>
       <c r="BE10">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BF10">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="BG10">
         <v>80</v>
@@ -3074,13 +3086,13 @@
         <v>4.3</v>
       </c>
       <c r="BI10">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BJ10">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK10">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BL10">
         <v>130</v>
@@ -3092,7 +3104,7 @@
         <v>4.2</v>
       </c>
       <c r="BO10">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BP10">
         <v>9</v>
@@ -3101,37 +3113,37 @@
         <v>8</v>
       </c>
       <c r="BR10">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="BS10">
-        <v>8.800000000000001</v>
+        <v>18.5</v>
       </c>
       <c r="BT10">
         <v>10.5</v>
       </c>
       <c r="BU10">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BV10">
         <v>65</v>
       </c>
       <c r="BW10">
-        <v>9.6</v>
+        <v>14</v>
       </c>
       <c r="BX10">
         <v>65</v>
       </c>
       <c r="BY10">
-        <v>9.6</v>
+        <v>13.5</v>
       </c>
       <c r="BZ10">
-        <v>16.5</v>
+        <v>13</v>
       </c>
       <c r="CA10">
-        <v>6.8</v>
+        <v>11</v>
       </c>
       <c r="CB10" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3139,31 +3151,31 @@
         <v>82</v>
       </c>
       <c r="B11" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D11" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E11" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F11">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="G11">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="H11">
-        <v>2.44</v>
+        <v>2.34</v>
       </c>
       <c r="I11">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="J11">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K11">
         <v>3.75</v>
@@ -3184,28 +3196,28 @@
         <v>2.06</v>
       </c>
       <c r="Q11">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="R11">
         <v>1.41</v>
       </c>
       <c r="S11">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T11">
         <v>1.68</v>
       </c>
       <c r="U11">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V11">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="W11">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="X11">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Y11">
         <v>12</v>
@@ -3214,13 +3226,13 @@
         <v>17.5</v>
       </c>
       <c r="AA11">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AB11">
         <v>14.5</v>
       </c>
       <c r="AC11">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD11">
         <v>12</v>
@@ -3232,7 +3244,7 @@
         <v>23</v>
       </c>
       <c r="AG11">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH11">
         <v>17</v>
@@ -3244,19 +3256,19 @@
         <v>55</v>
       </c>
       <c r="AK11">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AL11">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AM11">
         <v>95</v>
       </c>
       <c r="AN11">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AO11">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AP11">
         <v>14</v>
@@ -3265,10 +3277,10 @@
         <v>10</v>
       </c>
       <c r="AR11">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AS11">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AT11">
         <v>12</v>
@@ -3283,7 +3295,7 @@
         <v>21</v>
       </c>
       <c r="AX11">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AY11">
         <v>11.5</v>
@@ -3295,58 +3307,58 @@
         <v>28</v>
       </c>
       <c r="BB11">
+        <v>38</v>
+      </c>
+      <c r="BC11">
+        <v>26</v>
+      </c>
+      <c r="BD11">
         <v>34</v>
       </c>
-      <c r="BC11">
-        <v>24</v>
-      </c>
-      <c r="BD11">
-        <v>30</v>
-      </c>
       <c r="BE11">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BF11">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="BG11">
         <v>15.5</v>
       </c>
       <c r="BH11">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="BI11">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="BJ11">
         <v>11</v>
       </c>
       <c r="BK11">
-        <v>3</v>
+        <v>7.8</v>
       </c>
       <c r="BL11">
         <v>120</v>
       </c>
       <c r="BM11">
-        <v>3.85</v>
+        <v>4.8</v>
       </c>
       <c r="BN11">
         <v>7.6</v>
       </c>
       <c r="BO11">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BP11">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BQ11">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="BR11">
         <v>40</v>
       </c>
       <c r="BS11">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="BT11">
         <v>6.6</v>
@@ -3355,25 +3367,25 @@
         <v>4.8</v>
       </c>
       <c r="BV11">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BW11">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="BX11">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY11">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BZ11">
         <v>28</v>
       </c>
       <c r="CA11">
-        <v>3.65</v>
+        <v>4.4</v>
       </c>
       <c r="CB11" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3381,34 +3393,34 @@
         <v>83</v>
       </c>
       <c r="B12" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E12" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F12">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="G12">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="H12">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="I12">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="J12">
         <v>3.25</v>
       </c>
       <c r="K12">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="L12">
         <v>1.6</v>
@@ -3423,7 +3435,7 @@
         <v>1.55</v>
       </c>
       <c r="P12">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="Q12">
         <v>2.68</v>
@@ -3435,16 +3447,16 @@
         <v>5.6</v>
       </c>
       <c r="T12">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="U12">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="V12">
         <v>1.22</v>
       </c>
       <c r="W12">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="X12">
         <v>10.5</v>
@@ -3453,22 +3465,22 @@
         <v>16</v>
       </c>
       <c r="Z12">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AA12">
         <v>900</v>
       </c>
       <c r="AB12">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="AC12">
         <v>8.199999999999999</v>
       </c>
       <c r="AD12">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AE12">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AF12">
         <v>12.5</v>
@@ -3477,7 +3489,7 @@
         <v>13.5</v>
       </c>
       <c r="AH12">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AI12">
         <v>260</v>
@@ -3489,7 +3501,7 @@
         <v>34</v>
       </c>
       <c r="AL12">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM12">
         <v>580</v>
@@ -3498,10 +3510,10 @@
         <v>29</v>
       </c>
       <c r="AO12">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="AP12">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AQ12">
         <v>11</v>
@@ -3510,7 +3522,7 @@
         <v>12.5</v>
       </c>
       <c r="AS12">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AT12">
         <v>5.4</v>
@@ -3519,22 +3531,22 @@
         <v>6.6</v>
       </c>
       <c r="AV12">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW12">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AX12">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY12">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ12">
         <v>13.5</v>
       </c>
       <c r="BA12">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BB12">
         <v>19.5</v>
@@ -3543,79 +3555,79 @@
         <v>16</v>
       </c>
       <c r="BD12">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BE12">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BF12">
         <v>20</v>
       </c>
       <c r="BG12">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BH12">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="BI12">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="BJ12">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK12">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BN12">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BO12">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BP12">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BQ12">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BR12">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BS12">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BT12">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU12">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BV12">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BW12">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BX12">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="BY12">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BZ12">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="CA12">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="CB12" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3623,28 +3635,28 @@
         <v>84</v>
       </c>
       <c r="B13" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C13" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D13" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E13" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F13">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="G13">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="H13">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="I13">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="J13">
         <v>2.9</v>
@@ -3662,7 +3674,7 @@
         <v>2.28</v>
       </c>
       <c r="O13">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="P13">
         <v>1.41</v>
@@ -3677,16 +3689,16 @@
         <v>7.4</v>
       </c>
       <c r="T13">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="U13">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="V13">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="W13">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="X13">
         <v>7</v>
@@ -3704,7 +3716,7 @@
         <v>7.4</v>
       </c>
       <c r="AC13">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AD13">
         <v>17</v>
@@ -3713,22 +3725,22 @@
         <v>65</v>
       </c>
       <c r="AF13">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AG13">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AH13">
         <v>30</v>
       </c>
       <c r="AI13">
-        <v>500</v>
+        <v>260</v>
       </c>
       <c r="AJ13">
-        <v>260</v>
+        <v>90</v>
       </c>
       <c r="AK13">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="AL13">
         <v>340</v>
@@ -3749,10 +3761,10 @@
         <v>6.8</v>
       </c>
       <c r="AR13">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AS13">
-        <v>9.4</v>
+        <v>30</v>
       </c>
       <c r="AT13">
         <v>6.4</v>
@@ -3764,19 +3776,19 @@
         <v>14</v>
       </c>
       <c r="AW13">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX13">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AY13">
         <v>13</v>
       </c>
       <c r="AZ13">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA13">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BB13">
         <v>42</v>
@@ -3785,52 +3797,52 @@
         <v>23</v>
       </c>
       <c r="BD13">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BE13">
+        <v>10.5</v>
+      </c>
+      <c r="BF13">
         <v>9.6</v>
       </c>
-      <c r="BE13">
-        <v>10</v>
-      </c>
-      <c r="BF13">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BG13">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH13">
         <v>2.48</v>
       </c>
       <c r="BI13">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="BJ13">
         <v>13</v>
       </c>
       <c r="BK13">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BN13">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BO13">
         <v>4.8</v>
       </c>
       <c r="BP13">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BQ13">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BR13">
         <v>1000</v>
       </c>
       <c r="BS13">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BT13">
         <v>6.2</v>
@@ -3842,13 +3854,13 @@
         <v>36</v>
       </c>
       <c r="BW13">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX13">
         <v>70</v>
       </c>
       <c r="BY13">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BZ13">
         <v>0</v>
@@ -3857,7 +3869,7 @@
         <v>0</v>
       </c>
       <c r="CB13" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -3865,31 +3877,31 @@
         <v>83</v>
       </c>
       <c r="B14" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C14" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D14" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E14" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F14">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="G14">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="H14">
         <v>3.3</v>
       </c>
       <c r="I14">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J14">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="K14">
         <v>3.1</v>
@@ -3904,13 +3916,13 @@
         <v>2.66</v>
       </c>
       <c r="O14">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="P14">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Q14">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="R14">
         <v>1.19</v>
@@ -3919,37 +3931,37 @@
         <v>5.7</v>
       </c>
       <c r="T14">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U14">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="V14">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W14">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="X14">
         <v>8.6</v>
       </c>
       <c r="Y14">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z14">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AA14">
         <v>170</v>
       </c>
       <c r="AB14">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC14">
         <v>7.2</v>
       </c>
       <c r="AD14">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE14">
         <v>65</v>
@@ -3967,10 +3979,10 @@
         <v>100</v>
       </c>
       <c r="AJ14">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="AK14">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AL14">
         <v>85</v>
@@ -3985,10 +3997,10 @@
         <v>90</v>
       </c>
       <c r="AP14">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AQ14">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AR14">
         <v>17.5</v>
@@ -3997,7 +4009,7 @@
         <v>46</v>
       </c>
       <c r="AT14">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU14">
         <v>6.2</v>
@@ -4021,85 +4033,85 @@
         <v>50</v>
       </c>
       <c r="BB14">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BC14">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BD14">
         <v>46</v>
       </c>
       <c r="BE14">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="BF14">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BG14">
         <v>46</v>
       </c>
       <c r="BH14">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="BI14">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="BJ14">
         <v>13</v>
       </c>
       <c r="BK14">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BN14">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BO14">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BP14">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BQ14">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BR14">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BS14">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BT14">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BU14">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BV14">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BW14">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BX14">
         <v>1000</v>
       </c>
       <c r="BY14">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BZ14">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="CA14">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="CB14" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4107,241 +4119,483 @@
         <v>83</v>
       </c>
       <c r="B15" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C15" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D15" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E15" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F15">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="G15">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="H15">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="I15">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="J15">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="K15">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="L15">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="M15">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="N15">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="O15">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="P15">
-        <v>2.46</v>
+        <v>2.82</v>
       </c>
       <c r="Q15">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
       <c r="R15">
-        <v>1.59</v>
+        <v>1.73</v>
       </c>
       <c r="S15">
-        <v>2.46</v>
+        <v>2.14</v>
       </c>
       <c r="T15">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="U15">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="V15">
         <v>1.02</v>
       </c>
       <c r="W15">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="X15">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="Y15">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="Z15">
-        <v>460</v>
+        <v>570</v>
       </c>
       <c r="AA15">
         <v>1000</v>
       </c>
       <c r="AB15">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="AC15">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AD15">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="AE15">
         <v>1000</v>
       </c>
       <c r="AF15">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AG15">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AH15">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AI15">
         <v>1000</v>
       </c>
       <c r="AJ15">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AK15">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AL15">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AM15">
-        <v>640</v>
+        <v>1000</v>
       </c>
       <c r="AN15">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="AO15">
         <v>1000</v>
       </c>
       <c r="AP15">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="AQ15">
-        <v>8.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="AR15">
-        <v>9</v>
+        <v>6.8</v>
       </c>
       <c r="AS15">
-        <v>9.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="AT15">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU15">
-        <v>18.5</v>
+        <v>6.2</v>
       </c>
       <c r="AV15">
-        <v>8.6</v>
+        <v>6.6</v>
       </c>
       <c r="AW15">
-        <v>9.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="AX15">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AY15">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AZ15">
-        <v>8.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="BA15">
-        <v>9.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="BB15">
+        <v>6.2</v>
+      </c>
+      <c r="BC15">
+        <v>14.5</v>
+      </c>
+      <c r="BD15">
         <v>6.4</v>
       </c>
-      <c r="BC15">
-        <v>12</v>
-      </c>
-      <c r="BD15">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BE15">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BF15">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="BG15">
-        <v>9.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="BH15">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BI15">
-        <v>3.55</v>
+        <v>4.4</v>
       </c>
       <c r="BJ15">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BK15">
-        <v>11.5</v>
+        <v>8</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>21</v>
+        <v>11.5</v>
       </c>
       <c r="BN15">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BO15">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BP15">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="BQ15">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BR15">
         <v>30</v>
       </c>
       <c r="BS15">
-        <v>21</v>
+        <v>8.4</v>
       </c>
       <c r="BT15">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="BU15">
-        <v>16</v>
+        <v>8.6</v>
       </c>
       <c r="BV15">
         <v>1000</v>
       </c>
       <c r="BW15">
-        <v>21</v>
+        <v>11.5</v>
       </c>
       <c r="BX15">
         <v>1000</v>
       </c>
       <c r="BY15">
+        <v>11</v>
+      </c>
+      <c r="BZ15">
+        <v>7.2</v>
+      </c>
+      <c r="CA15">
+        <v>6</v>
+      </c>
+      <c r="CB15" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="16" spans="1:80">
+      <c r="A16" t="s">
+        <v>85</v>
+      </c>
+      <c r="B16" t="s">
+        <v>86</v>
+      </c>
+      <c r="C16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D16" t="s">
+        <v>109</v>
+      </c>
+      <c r="E16" t="s">
+        <v>124</v>
+      </c>
+      <c r="F16">
+        <v>1.59</v>
+      </c>
+      <c r="G16">
+        <v>1.63</v>
+      </c>
+      <c r="H16">
+        <v>6.4</v>
+      </c>
+      <c r="I16">
+        <v>7.2</v>
+      </c>
+      <c r="J16">
+        <v>4.2</v>
+      </c>
+      <c r="K16">
+        <v>4.5</v>
+      </c>
+      <c r="L16">
+        <v>1.4</v>
+      </c>
+      <c r="M16">
+        <v>1.06</v>
+      </c>
+      <c r="N16">
+        <v>3.95</v>
+      </c>
+      <c r="O16">
+        <v>1.31</v>
+      </c>
+      <c r="P16">
+        <v>1.98</v>
+      </c>
+      <c r="Q16">
+        <v>1.95</v>
+      </c>
+      <c r="R16">
+        <v>1.37</v>
+      </c>
+      <c r="S16">
+        <v>3.45</v>
+      </c>
+      <c r="T16">
+        <v>2.02</v>
+      </c>
+      <c r="U16">
+        <v>1.87</v>
+      </c>
+      <c r="V16">
+        <v>1.16</v>
+      </c>
+      <c r="W16">
+        <v>2.58</v>
+      </c>
+      <c r="X16">
+        <v>18</v>
+      </c>
+      <c r="Y16">
         <v>21</v>
       </c>
-      <c r="BZ15">
+      <c r="Z16">
+        <v>65</v>
+      </c>
+      <c r="AA16">
+        <v>240</v>
+      </c>
+      <c r="AB16">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC16">
+        <v>10.5</v>
+      </c>
+      <c r="AD16">
+        <v>32</v>
+      </c>
+      <c r="AE16">
+        <v>130</v>
+      </c>
+      <c r="AF16">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AG16">
+        <v>10.5</v>
+      </c>
+      <c r="AH16">
+        <v>27</v>
+      </c>
+      <c r="AI16">
+        <v>190</v>
+      </c>
+      <c r="AJ16">
+        <v>15</v>
+      </c>
+      <c r="AK16">
+        <v>18.5</v>
+      </c>
+      <c r="AL16">
+        <v>46</v>
+      </c>
+      <c r="AM16">
+        <v>180</v>
+      </c>
+      <c r="AN16">
+        <v>9.4</v>
+      </c>
+      <c r="AO16">
+        <v>160</v>
+      </c>
+      <c r="AP16">
+        <v>12.5</v>
+      </c>
+      <c r="AQ16">
+        <v>17.5</v>
+      </c>
+      <c r="AR16">
+        <v>40</v>
+      </c>
+      <c r="AS16">
+        <v>12</v>
+      </c>
+      <c r="AT16">
+        <v>7.2</v>
+      </c>
+      <c r="AU16">
         <v>8.6</v>
       </c>
-      <c r="CA15">
-        <v>6.2</v>
-      </c>
-      <c r="CB15" t="s">
-        <v>121</v>
+      <c r="AV16">
+        <v>19.5</v>
+      </c>
+      <c r="AW16">
+        <v>55</v>
+      </c>
+      <c r="AX16">
+        <v>8</v>
+      </c>
+      <c r="AY16">
+        <v>9</v>
+      </c>
+      <c r="AZ16">
+        <v>18.5</v>
+      </c>
+      <c r="BA16">
+        <v>55</v>
+      </c>
+      <c r="BB16">
+        <v>12.5</v>
+      </c>
+      <c r="BC16">
+        <v>15</v>
+      </c>
+      <c r="BD16">
+        <v>26</v>
+      </c>
+      <c r="BE16">
+        <v>90</v>
+      </c>
+      <c r="BF16">
+        <v>8</v>
+      </c>
+      <c r="BG16">
+        <v>70</v>
+      </c>
+      <c r="BH16">
+        <v>3.55</v>
+      </c>
+      <c r="BI16">
+        <v>2.8</v>
+      </c>
+      <c r="BJ16">
+        <v>11.5</v>
+      </c>
+      <c r="BK16">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BL16">
+        <v>1000</v>
+      </c>
+      <c r="BM16">
+        <v>1.01</v>
+      </c>
+      <c r="BN16">
+        <v>4.1</v>
+      </c>
+      <c r="BO16">
+        <v>3.15</v>
+      </c>
+      <c r="BP16">
+        <v>10.5</v>
+      </c>
+      <c r="BQ16">
+        <v>7.6</v>
+      </c>
+      <c r="BR16">
+        <v>1000</v>
+      </c>
+      <c r="BS16">
+        <v>19</v>
+      </c>
+      <c r="BT16">
+        <v>10.5</v>
+      </c>
+      <c r="BU16">
+        <v>7.6</v>
+      </c>
+      <c r="BV16">
+        <v>1000</v>
+      </c>
+      <c r="BW16">
+        <v>44</v>
+      </c>
+      <c r="BX16">
+        <v>1000</v>
+      </c>
+      <c r="BY16">
+        <v>48</v>
+      </c>
+      <c r="BZ16">
+        <v>20</v>
+      </c>
+      <c r="CA16">
+        <v>14</v>
+      </c>
+      <c r="CB16" t="s">
+        <v>125</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-24.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="115">
   <si>
     <t>League</t>
   </si>
@@ -268,9 +268,6 @@
     <t>Moroccan Botola Pro 1</t>
   </si>
   <si>
-    <t>CONCACAF Nations League A</t>
-  </si>
-  <si>
     <t>2026-09-24</t>
   </si>
   <si>
@@ -289,9 +286,6 @@
     <t>21:30:00</t>
   </si>
   <si>
-    <t>23:00:00</t>
-  </si>
-  <si>
     <t>Liechtenstein</t>
   </si>
   <si>
@@ -328,9 +322,6 @@
     <t>LDU de Portoviejo</t>
   </si>
   <si>
-    <t>Haiti</t>
-  </si>
-  <si>
     <t>Lithuania</t>
   </si>
   <si>
@@ -367,10 +358,7 @@
     <t>22 de Julio FC</t>
   </si>
   <si>
-    <t>Trinidad &amp; Tobago</t>
-  </si>
-  <si>
-    <t>2026-09-24 15:20:46</t>
+    <t>2026-09-24 17:37:21</t>
   </si>
 </sst>
 </file>
@@ -702,7 +690,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB14"/>
+  <dimension ref="A1:CB13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -952,241 +940,241 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2" t="s">
         <v>85</v>
       </c>
-      <c r="C2" t="s">
-        <v>86</v>
-      </c>
       <c r="D2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="F2">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="G2">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="H2">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="I2">
-        <v>1.33</v>
+        <v>1000</v>
       </c>
       <c r="J2">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="K2">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="L2">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="M2">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <v>1.57</v>
+        <v>1.04</v>
       </c>
       <c r="Q2">
-        <v>2.72</v>
+        <v>21</v>
       </c>
       <c r="R2">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="S2">
-        <v>5.7</v>
+        <v>100</v>
       </c>
       <c r="T2">
-        <v>4.1</v>
+        <v>1.51</v>
       </c>
       <c r="U2">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="V2">
-        <v>4</v>
+        <v>440</v>
       </c>
       <c r="W2">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X2">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Y2">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="Z2">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="AA2">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AB2">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AC2">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AD2">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AE2">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AF2">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="AG2">
+        <v>1000</v>
+      </c>
+      <c r="AH2">
+        <v>1000</v>
+      </c>
+      <c r="AI2">
+        <v>1000</v>
+      </c>
+      <c r="AJ2">
+        <v>1000</v>
+      </c>
+      <c r="AK2">
+        <v>1000</v>
+      </c>
+      <c r="AL2">
+        <v>1000</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>1000</v>
+      </c>
+      <c r="AO2">
+        <v>1000</v>
+      </c>
+      <c r="AP2">
+        <v>28</v>
+      </c>
+      <c r="AQ2">
+        <v>28</v>
+      </c>
+      <c r="AR2">
+        <v>1.01</v>
+      </c>
+      <c r="AS2">
+        <v>1.01</v>
+      </c>
+      <c r="AT2">
+        <v>50</v>
+      </c>
+      <c r="AU2">
+        <v>28</v>
+      </c>
+      <c r="AV2">
+        <v>1.01</v>
+      </c>
+      <c r="AW2">
+        <v>1.01</v>
+      </c>
+      <c r="AX2">
+        <v>50</v>
+      </c>
+      <c r="AY2">
+        <v>50</v>
+      </c>
+      <c r="AZ2">
         <v>100</v>
       </c>
-      <c r="AH2">
-        <v>160</v>
-      </c>
-      <c r="AI2">
-        <v>200</v>
-      </c>
-      <c r="AJ2">
-        <v>1000</v>
-      </c>
-      <c r="AK2">
-        <v>990</v>
-      </c>
-      <c r="AL2">
-        <v>1000</v>
-      </c>
-      <c r="AM2">
-        <v>1000</v>
-      </c>
-      <c r="AN2">
-        <v>1000</v>
-      </c>
-      <c r="AO2">
-        <v>9.6</v>
-      </c>
-      <c r="AP2">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AQ2">
-        <v>4.7</v>
-      </c>
-      <c r="AR2">
-        <v>4.9</v>
-      </c>
-      <c r="AS2">
-        <v>8.4</v>
-      </c>
-      <c r="AT2">
-        <v>28</v>
-      </c>
-      <c r="AU2">
-        <v>14</v>
-      </c>
-      <c r="AV2">
-        <v>14.5</v>
-      </c>
-      <c r="AW2">
-        <v>23</v>
-      </c>
-      <c r="AX2">
-        <v>130</v>
-      </c>
-      <c r="AY2">
-        <v>85</v>
-      </c>
-      <c r="AZ2">
-        <v>85</v>
-      </c>
       <c r="BA2">
-        <v>100</v>
+        <v>1.01</v>
       </c>
       <c r="BB2">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="BC2">
-        <v>160</v>
+        <v>50</v>
       </c>
       <c r="BD2">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BE2">
-        <v>250</v>
+        <v>1.01</v>
       </c>
       <c r="BF2">
-        <v>80</v>
+        <v>1.01</v>
       </c>
       <c r="BG2">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BH2">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="BI2">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="BJ2">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BK2">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BL2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM2">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="BN2">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BO2">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BP2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ2">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS2">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BT2">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="BU2">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="BV2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BW2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BX2">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="BY2">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BZ2">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="CA2">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1194,241 +1182,241 @@
         <v>80</v>
       </c>
       <c r="B3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C3" t="s">
         <v>85</v>
       </c>
-      <c r="C3" t="s">
-        <v>86</v>
-      </c>
       <c r="D3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F3">
-        <v>1.64</v>
+        <v>1.09</v>
       </c>
       <c r="G3">
-        <v>1.65</v>
+        <v>1.1</v>
       </c>
       <c r="H3">
-        <v>5.7</v>
+        <v>190</v>
       </c>
       <c r="I3">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="J3">
-        <v>4.6</v>
+        <v>11</v>
       </c>
       <c r="K3">
-        <v>4.7</v>
+        <v>13</v>
       </c>
       <c r="L3">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="M3">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="N3">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="O3">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="P3">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="Q3">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="R3">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="S3">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="V3">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="W3">
-        <v>2.52</v>
+        <v>11</v>
       </c>
       <c r="X3">
+        <v>1000</v>
+      </c>
+      <c r="Y3">
+        <v>1000</v>
+      </c>
+      <c r="Z3">
+        <v>1000</v>
+      </c>
+      <c r="AA3">
+        <v>1000</v>
+      </c>
+      <c r="AB3">
+        <v>1000</v>
+      </c>
+      <c r="AC3">
+        <v>1000</v>
+      </c>
+      <c r="AD3">
+        <v>1000</v>
+      </c>
+      <c r="AE3">
+        <v>1000</v>
+      </c>
+      <c r="AF3">
+        <v>1000</v>
+      </c>
+      <c r="AG3">
+        <v>1000</v>
+      </c>
+      <c r="AH3">
+        <v>1000</v>
+      </c>
+      <c r="AI3">
+        <v>1000</v>
+      </c>
+      <c r="AJ3">
+        <v>1000</v>
+      </c>
+      <c r="AK3">
+        <v>1000</v>
+      </c>
+      <c r="AL3">
+        <v>1.14</v>
+      </c>
+      <c r="AM3">
+        <v>40</v>
+      </c>
+      <c r="AN3">
         <v>27</v>
       </c>
-      <c r="Y3">
-        <v>28</v>
-      </c>
-      <c r="Z3">
-        <v>48</v>
-      </c>
-      <c r="AA3">
-        <v>120</v>
-      </c>
-      <c r="AB3">
-        <v>12</v>
-      </c>
-      <c r="AC3">
-        <v>11</v>
-      </c>
-      <c r="AD3">
-        <v>20</v>
-      </c>
-      <c r="AE3">
-        <v>60</v>
-      </c>
-      <c r="AF3">
-        <v>11</v>
-      </c>
-      <c r="AG3">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AH3">
-        <v>15</v>
-      </c>
-      <c r="AI3">
-        <v>50</v>
-      </c>
-      <c r="AJ3">
-        <v>16</v>
-      </c>
-      <c r="AK3">
-        <v>14.5</v>
-      </c>
-      <c r="AL3">
-        <v>23</v>
-      </c>
-      <c r="AM3">
-        <v>65</v>
-      </c>
-      <c r="AN3">
-        <v>7.4</v>
-      </c>
       <c r="AO3">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AP3">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AQ3">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AR3">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AS3">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AT3">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AU3">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AV3">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AW3">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AX3">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AY3">
+        <v>1000</v>
+      </c>
+      <c r="AZ3">
+        <v>1000</v>
+      </c>
+      <c r="BA3">
+        <v>1000</v>
+      </c>
+      <c r="BB3">
+        <v>1000</v>
+      </c>
+      <c r="BC3">
+        <v>1000</v>
+      </c>
+      <c r="BD3">
+        <v>1.12</v>
+      </c>
+      <c r="BE3">
+        <v>12.5</v>
+      </c>
+      <c r="BF3">
         <v>9</v>
       </c>
-      <c r="AZ3">
-        <v>14.5</v>
-      </c>
-      <c r="BA3">
-        <v>46</v>
-      </c>
-      <c r="BB3">
-        <v>15.5</v>
-      </c>
-      <c r="BC3">
-        <v>14</v>
-      </c>
-      <c r="BD3">
-        <v>21</v>
-      </c>
-      <c r="BE3">
-        <v>60</v>
-      </c>
-      <c r="BF3">
-        <v>7</v>
-      </c>
       <c r="BG3">
-        <v>50</v>
+        <v>8.6</v>
       </c>
       <c r="BH3">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BI3">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BJ3">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BK3">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BL3">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="BM3">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="BN3">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BO3">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BP3">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BQ3">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BR3">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="BS3">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="BT3">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BU3">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BV3">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="BW3">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BX3">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="BY3">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BZ3">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="CA3">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1436,241 +1424,241 @@
         <v>80</v>
       </c>
       <c r="B4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C4" t="s">
         <v>85</v>
       </c>
-      <c r="C4" t="s">
-        <v>86</v>
-      </c>
       <c r="D4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E4" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F4">
-        <v>3.2</v>
+        <v>11</v>
       </c>
       <c r="G4">
-        <v>3.3</v>
+        <v>12.5</v>
       </c>
       <c r="H4">
-        <v>2.44</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I4">
-        <v>2.46</v>
+        <v>9</v>
       </c>
       <c r="J4">
-        <v>3.45</v>
+        <v>1.25</v>
       </c>
       <c r="K4">
-        <v>3.5</v>
+        <v>1.26</v>
       </c>
       <c r="L4">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="M4">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="N4">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O4">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="P4">
-        <v>1.84</v>
+        <v>1.27</v>
       </c>
       <c r="Q4">
-        <v>2.16</v>
+        <v>4.5</v>
       </c>
       <c r="R4">
-        <v>1.32</v>
+        <v>1.02</v>
       </c>
       <c r="S4">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="T4">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="V4">
-        <v>1.68</v>
+        <v>1.09</v>
       </c>
       <c r="W4">
-        <v>1.43</v>
+        <v>1.07</v>
       </c>
       <c r="X4">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Y4">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="Z4">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AA4">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AB4">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AC4">
-        <v>7.4</v>
+        <v>1.18</v>
       </c>
       <c r="AD4">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AE4">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AF4">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AG4">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH4">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AI4">
+        <v>1000</v>
+      </c>
+      <c r="AJ4">
+        <v>1000</v>
+      </c>
+      <c r="AK4">
+        <v>1000</v>
+      </c>
+      <c r="AL4">
+        <v>1000</v>
+      </c>
+      <c r="AM4">
+        <v>1000</v>
+      </c>
+      <c r="AN4">
+        <v>1000</v>
+      </c>
+      <c r="AO4">
+        <v>1000</v>
+      </c>
+      <c r="AP4">
+        <v>220</v>
+      </c>
+      <c r="AQ4">
+        <v>220</v>
+      </c>
+      <c r="AR4">
+        <v>220</v>
+      </c>
+      <c r="AS4">
+        <v>220</v>
+      </c>
+      <c r="AT4">
+        <v>40</v>
+      </c>
+      <c r="AU4">
+        <v>1.16</v>
+      </c>
+      <c r="AV4">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AW4">
+        <v>75</v>
+      </c>
+      <c r="AX4">
+        <v>40</v>
+      </c>
+      <c r="AY4">
+        <v>12.5</v>
+      </c>
+      <c r="AZ4">
         <v>42</v>
       </c>
-      <c r="AJ4">
-        <v>60</v>
-      </c>
-      <c r="AK4">
-        <v>40</v>
-      </c>
-      <c r="AL4">
-        <v>48</v>
-      </c>
-      <c r="AM4">
-        <v>100</v>
-      </c>
-      <c r="AN4">
-        <v>40</v>
-      </c>
-      <c r="AO4">
-        <v>24</v>
-      </c>
-      <c r="AP4">
-        <v>12</v>
-      </c>
-      <c r="AQ4">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AR4">
-        <v>14</v>
-      </c>
-      <c r="AS4">
-        <v>30</v>
-      </c>
-      <c r="AT4">
-        <v>11</v>
-      </c>
-      <c r="AU4">
-        <v>7.2</v>
-      </c>
-      <c r="AV4">
-        <v>10.5</v>
-      </c>
-      <c r="AW4">
-        <v>27</v>
-      </c>
-      <c r="AX4">
-        <v>20</v>
-      </c>
-      <c r="AY4">
-        <v>13</v>
-      </c>
-      <c r="AZ4">
-        <v>16.5</v>
-      </c>
       <c r="BA4">
-        <v>40</v>
+        <v>5.6</v>
       </c>
       <c r="BB4">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="BC4">
+        <v>6</v>
+      </c>
+      <c r="BD4">
+        <v>5.6</v>
+      </c>
+      <c r="BE4">
+        <v>160</v>
+      </c>
+      <c r="BF4">
+        <v>170</v>
+      </c>
+      <c r="BG4">
         <v>36</v>
       </c>
-      <c r="BD4">
-        <v>46</v>
-      </c>
-      <c r="BE4">
-        <v>90</v>
-      </c>
-      <c r="BF4">
-        <v>38</v>
-      </c>
-      <c r="BG4">
-        <v>22</v>
-      </c>
       <c r="BH4">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="BI4">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="BJ4">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="BK4">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BL4">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="BM4">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="BN4">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BO4">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BP4">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="BQ4">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BR4">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="BS4">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BT4">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="BU4">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BV4">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="BW4">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="BX4">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="BY4">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BZ4">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="CA4">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="CB4" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1678,232 +1666,232 @@
         <v>80</v>
       </c>
       <c r="B5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C5" t="s">
         <v>85</v>
       </c>
-      <c r="C5" t="s">
-        <v>86</v>
-      </c>
       <c r="D5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E5" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F5">
-        <v>1.18</v>
+        <v>1.02</v>
       </c>
       <c r="G5">
+        <v>1.03</v>
+      </c>
+      <c r="H5">
+        <v>100</v>
+      </c>
+      <c r="I5">
+        <v>1000</v>
+      </c>
+      <c r="J5">
+        <v>34</v>
+      </c>
+      <c r="K5">
+        <v>55</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>1.17</v>
+      </c>
+      <c r="O5">
+        <v>6.2</v>
+      </c>
+      <c r="P5">
+        <v>1.01</v>
+      </c>
+      <c r="Q5">
+        <v>50</v>
+      </c>
+      <c r="R5">
+        <v>1.01</v>
+      </c>
+      <c r="S5">
+        <v>500</v>
+      </c>
+      <c r="T5">
+        <v>1.72</v>
+      </c>
+      <c r="U5">
+        <v>1.02</v>
+      </c>
+      <c r="V5">
+        <v>1.01</v>
+      </c>
+      <c r="W5">
+        <v>17.5</v>
+      </c>
+      <c r="X5">
+        <v>1000</v>
+      </c>
+      <c r="Y5">
+        <v>1000</v>
+      </c>
+      <c r="Z5">
+        <v>1000</v>
+      </c>
+      <c r="AA5">
+        <v>1000</v>
+      </c>
+      <c r="AB5">
+        <v>1.2</v>
+      </c>
+      <c r="AC5">
+        <v>70</v>
+      </c>
+      <c r="AD5">
+        <v>1000</v>
+      </c>
+      <c r="AE5">
+        <v>1000</v>
+      </c>
+      <c r="AF5">
+        <v>13.5</v>
+      </c>
+      <c r="AG5">
+        <v>550</v>
+      </c>
+      <c r="AH5">
+        <v>1000</v>
+      </c>
+      <c r="AI5">
+        <v>1000</v>
+      </c>
+      <c r="AJ5">
+        <v>1000</v>
+      </c>
+      <c r="AK5">
+        <v>1000</v>
+      </c>
+      <c r="AL5">
+        <v>1000</v>
+      </c>
+      <c r="AM5">
+        <v>1000</v>
+      </c>
+      <c r="AN5">
+        <v>1000</v>
+      </c>
+      <c r="AO5">
+        <v>1000</v>
+      </c>
+      <c r="AP5">
+        <v>1000</v>
+      </c>
+      <c r="AQ5">
+        <v>1000</v>
+      </c>
+      <c r="AR5">
+        <v>1000</v>
+      </c>
+      <c r="AS5">
+        <v>1000</v>
+      </c>
+      <c r="AT5">
         <v>1.19</v>
       </c>
-      <c r="H5">
-        <v>21</v>
-      </c>
-      <c r="I5">
-        <v>22</v>
-      </c>
-      <c r="J5">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="K5">
-        <v>9.4</v>
-      </c>
-      <c r="L5">
-        <v>1.2</v>
-      </c>
-      <c r="M5">
-        <v>1.02</v>
-      </c>
-      <c r="N5">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="O5">
-        <v>1.11</v>
-      </c>
-      <c r="P5">
-        <v>3.7</v>
-      </c>
-      <c r="Q5">
-        <v>1.36</v>
-      </c>
-      <c r="R5">
-        <v>2.08</v>
-      </c>
-      <c r="S5">
-        <v>1.9</v>
-      </c>
-      <c r="T5">
-        <v>2.08</v>
-      </c>
-      <c r="U5">
-        <v>1.9</v>
-      </c>
-      <c r="V5">
-        <v>1.04</v>
-      </c>
-      <c r="W5">
+      <c r="AU5">
+        <v>26</v>
+      </c>
+      <c r="AV5">
         <v>6.4</v>
       </c>
-      <c r="X5">
-        <v>44</v>
-      </c>
-      <c r="Y5">
-        <v>90</v>
-      </c>
-      <c r="Z5">
-        <v>280</v>
-      </c>
-      <c r="AA5">
-        <v>1000</v>
-      </c>
-      <c r="AB5">
-        <v>14.5</v>
-      </c>
-      <c r="AC5">
-        <v>22</v>
-      </c>
-      <c r="AD5">
-        <v>75</v>
-      </c>
-      <c r="AE5">
-        <v>320</v>
-      </c>
-      <c r="AF5">
-        <v>9</v>
-      </c>
-      <c r="AG5">
-        <v>12</v>
-      </c>
-      <c r="AH5">
-        <v>38</v>
-      </c>
-      <c r="AI5">
-        <v>250</v>
-      </c>
-      <c r="AJ5">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AK5">
-        <v>12.5</v>
-      </c>
-      <c r="AL5">
-        <v>36</v>
-      </c>
-      <c r="AM5">
-        <v>150</v>
-      </c>
-      <c r="AN5">
-        <v>2.8</v>
-      </c>
-      <c r="AO5">
-        <v>350</v>
-      </c>
-      <c r="AP5">
-        <v>42</v>
-      </c>
-      <c r="AQ5">
-        <v>85</v>
-      </c>
-      <c r="AR5">
-        <v>38</v>
-      </c>
-      <c r="AS5">
-        <v>44</v>
-      </c>
-      <c r="AT5">
-        <v>13.5</v>
-      </c>
-      <c r="AU5">
-        <v>21</v>
-      </c>
-      <c r="AV5">
-        <v>65</v>
-      </c>
       <c r="AW5">
-        <v>38</v>
+        <v>6.2</v>
       </c>
       <c r="AX5">
-        <v>8.800000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="AY5">
-        <v>11.5</v>
+        <v>15.5</v>
       </c>
       <c r="AZ5">
-        <v>36</v>
+        <v>6.8</v>
       </c>
       <c r="BA5">
-        <v>130</v>
+        <v>6.8</v>
       </c>
       <c r="BB5">
-        <v>9</v>
+        <v>6.8</v>
       </c>
       <c r="BC5">
-        <v>11.5</v>
+        <v>6.4</v>
       </c>
       <c r="BD5">
-        <v>32</v>
+        <v>6.8</v>
       </c>
       <c r="BE5">
-        <v>120</v>
+        <v>6.8</v>
       </c>
       <c r="BF5">
-        <v>2.76</v>
+        <v>6.4</v>
       </c>
       <c r="BG5">
-        <v>38</v>
+        <v>6.8</v>
       </c>
       <c r="BH5">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BI5">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BJ5">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BK5">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BL5">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="BM5">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BN5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BO5">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="BP5">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BQ5">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="BR5">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="BS5">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="BT5">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="BU5">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="BV5">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="BW5">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BX5">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="BY5">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BZ5">
         <v>0</v>
@@ -1912,7 +1900,7 @@
         <v>0</v>
       </c>
       <c r="CB5" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1920,241 +1908,241 @@
         <v>80</v>
       </c>
       <c r="B6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C6" t="s">
         <v>85</v>
       </c>
-      <c r="C6" t="s">
-        <v>86</v>
-      </c>
       <c r="D6" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E6" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F6">
-        <v>2.76</v>
+        <v>50</v>
       </c>
       <c r="G6">
-        <v>2.78</v>
+        <v>70</v>
       </c>
       <c r="H6">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="I6">
-        <v>2.62</v>
+        <v>1.21</v>
       </c>
       <c r="J6">
-        <v>3.9</v>
+        <v>6.4</v>
       </c>
       <c r="K6">
+        <v>6.8</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>1.54</v>
+      </c>
+      <c r="O6">
+        <v>2.8</v>
+      </c>
+      <c r="P6">
+        <v>1.03</v>
+      </c>
+      <c r="Q6">
+        <v>26</v>
+      </c>
+      <c r="R6">
+        <v>1.01</v>
+      </c>
+      <c r="S6">
+        <v>110</v>
+      </c>
+      <c r="T6">
         <v>3.95</v>
       </c>
-      <c r="L6">
-        <v>1.28</v>
-      </c>
-      <c r="M6">
-        <v>1.03</v>
-      </c>
-      <c r="N6">
-        <v>7</v>
-      </c>
-      <c r="O6">
-        <v>1.16</v>
-      </c>
-      <c r="P6">
-        <v>2.96</v>
-      </c>
-      <c r="Q6">
-        <v>1.5</v>
-      </c>
-      <c r="R6">
-        <v>1.77</v>
-      </c>
-      <c r="S6">
-        <v>2.24</v>
-      </c>
-      <c r="T6">
-        <v>1.43</v>
-      </c>
       <c r="U6">
-        <v>3.25</v>
+        <v>1.3</v>
       </c>
       <c r="V6">
-        <v>1.62</v>
+        <v>5.5</v>
       </c>
       <c r="W6">
-        <v>1.55</v>
+        <v>1.01</v>
       </c>
       <c r="X6">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="Y6">
-        <v>19.5</v>
+        <v>1.53</v>
       </c>
       <c r="Z6">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="AA6">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AB6">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AC6">
-        <v>9.4</v>
+        <v>6.6</v>
       </c>
       <c r="AD6">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AE6">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AF6">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AG6">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH6">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AI6">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AJ6">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AK6">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AL6">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AM6">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AN6">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AO6">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AP6">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AQ6">
-        <v>19</v>
+        <v>1.51</v>
       </c>
       <c r="AR6">
-        <v>21</v>
+        <v>6.2</v>
       </c>
       <c r="AS6">
-        <v>36</v>
+        <v>90</v>
       </c>
       <c r="AT6">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AU6">
-        <v>9.199999999999999</v>
+        <v>5.3</v>
       </c>
       <c r="AV6">
+        <v>30</v>
+      </c>
+      <c r="AW6">
+        <v>44</v>
+      </c>
+      <c r="AX6">
+        <v>1000</v>
+      </c>
+      <c r="AY6">
+        <v>46</v>
+      </c>
+      <c r="AZ6">
+        <v>44</v>
+      </c>
+      <c r="BA6">
+        <v>10.5</v>
+      </c>
+      <c r="BB6">
+        <v>1000</v>
+      </c>
+      <c r="BC6">
         <v>11</v>
       </c>
-      <c r="AW6">
-        <v>21</v>
-      </c>
-      <c r="AX6">
-        <v>23</v>
-      </c>
-      <c r="AY6">
-        <v>12</v>
-      </c>
-      <c r="AZ6">
-        <v>12</v>
-      </c>
-      <c r="BA6">
-        <v>24</v>
-      </c>
-      <c r="BB6">
-        <v>40</v>
-      </c>
-      <c r="BC6">
-        <v>22</v>
-      </c>
       <c r="BD6">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="BE6">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="BF6">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BG6">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="BH6">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BI6">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BJ6">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BK6">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="BL6">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="BM6">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="BN6">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BO6">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BP6">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="BQ6">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BR6">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BS6">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BT6">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BU6">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BV6">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BW6">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BX6">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BY6">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BZ6">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="CA6">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="CB6" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2162,241 +2150,241 @@
         <v>80</v>
       </c>
       <c r="B7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C7" t="s">
         <v>85</v>
       </c>
-      <c r="C7" t="s">
-        <v>86</v>
-      </c>
       <c r="D7" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E7" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F7">
-        <v>2.48</v>
+        <v>1.02</v>
       </c>
       <c r="G7">
-        <v>2.5</v>
+        <v>1.03</v>
       </c>
       <c r="H7">
-        <v>3.4</v>
+        <v>50</v>
       </c>
       <c r="I7">
-        <v>3.45</v>
+        <v>1000</v>
       </c>
       <c r="J7">
-        <v>3.25</v>
+        <v>34</v>
       </c>
       <c r="K7">
-        <v>3.3</v>
+        <v>100</v>
       </c>
       <c r="L7">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M7">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="N7">
-        <v>2.78</v>
+        <v>1.04</v>
       </c>
       <c r="O7">
-        <v>1.54</v>
+        <v>21</v>
       </c>
       <c r="P7">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="Q7">
-        <v>2.62</v>
+        <v>100</v>
       </c>
       <c r="R7">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="S7">
-        <v>5.5</v>
+        <v>100</v>
       </c>
       <c r="T7">
-        <v>2.14</v>
+        <v>10</v>
       </c>
       <c r="U7">
-        <v>1.85</v>
+        <v>1.01</v>
       </c>
       <c r="V7">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="W7">
-        <v>1.66</v>
+        <v>100</v>
       </c>
       <c r="X7">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Y7">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Z7">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AA7">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AB7">
-        <v>7.6</v>
+        <v>1.05</v>
       </c>
       <c r="AC7">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="AD7">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AE7">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF7">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AG7">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH7">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI7">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ7">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AK7">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AL7">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM7">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AN7">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AO7">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AP7">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="AQ7">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AR7">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="AS7">
-        <v>60</v>
+        <v>11</v>
       </c>
       <c r="AT7">
-        <v>7.4</v>
+        <v>1.02</v>
       </c>
       <c r="AU7">
-        <v>7</v>
+        <v>19.5</v>
       </c>
       <c r="AV7">
-        <v>14</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW7">
-        <v>48</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX7">
-        <v>13</v>
+        <v>4.4</v>
       </c>
       <c r="AY7">
-        <v>11.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ7">
-        <v>21</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BA7">
-        <v>60</v>
+        <v>1.25</v>
       </c>
       <c r="BB7">
-        <v>34</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC7">
-        <v>32</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD7">
-        <v>50</v>
+        <v>1.25</v>
       </c>
       <c r="BE7">
-        <v>120</v>
+        <v>1.25</v>
       </c>
       <c r="BF7">
-        <v>30</v>
+        <v>1.25</v>
       </c>
       <c r="BG7">
-        <v>60</v>
+        <v>1.25</v>
       </c>
       <c r="BH7">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="BI7">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="BJ7">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BK7">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BL7">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="BM7">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="BN7">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BO7">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BP7">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BQ7">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="BR7">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="BS7">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="BT7">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BU7">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="BV7">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BW7">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="BX7">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="BY7">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="BZ7">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="CA7">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="CB7" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2404,241 +2392,241 @@
         <v>80</v>
       </c>
       <c r="B8" t="s">
+        <v>84</v>
+      </c>
+      <c r="C8" t="s">
         <v>85</v>
       </c>
-      <c r="C8" t="s">
-        <v>86</v>
-      </c>
       <c r="D8" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E8" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F8">
-        <v>1.49</v>
+        <v>3.4</v>
       </c>
       <c r="G8">
-        <v>1.5</v>
+        <v>3.45</v>
       </c>
       <c r="H8">
-        <v>7.8</v>
+        <v>48</v>
       </c>
       <c r="I8">
-        <v>8</v>
+        <v>100</v>
       </c>
       <c r="J8">
-        <v>4.8</v>
+        <v>1.43</v>
       </c>
       <c r="K8">
-        <v>5</v>
+        <v>1.44</v>
       </c>
       <c r="L8">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="M8">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="N8">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O8">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="P8">
-        <v>2.42</v>
+        <v>1.42</v>
       </c>
       <c r="Q8">
-        <v>1.67</v>
+        <v>3.3</v>
       </c>
       <c r="R8">
-        <v>1.55</v>
+        <v>1.03</v>
       </c>
       <c r="S8">
-        <v>2.72</v>
+        <v>23</v>
       </c>
       <c r="T8">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="U8">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="V8">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="W8">
-        <v>3</v>
+        <v>1.37</v>
       </c>
       <c r="X8">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Y8">
+        <v>1000</v>
+      </c>
+      <c r="Z8">
+        <v>1000</v>
+      </c>
+      <c r="AA8">
+        <v>1000</v>
+      </c>
+      <c r="AB8">
+        <v>1000</v>
+      </c>
+      <c r="AC8">
+        <v>1.43</v>
+      </c>
+      <c r="AD8">
+        <v>1000</v>
+      </c>
+      <c r="AE8">
+        <v>1000</v>
+      </c>
+      <c r="AF8">
+        <v>1000</v>
+      </c>
+      <c r="AG8">
+        <v>6</v>
+      </c>
+      <c r="AH8">
+        <v>1000</v>
+      </c>
+      <c r="AI8">
+        <v>1000</v>
+      </c>
+      <c r="AJ8">
+        <v>1000</v>
+      </c>
+      <c r="AK8">
+        <v>1000</v>
+      </c>
+      <c r="AL8">
+        <v>1000</v>
+      </c>
+      <c r="AM8">
+        <v>1000</v>
+      </c>
+      <c r="AN8">
+        <v>1000</v>
+      </c>
+      <c r="AO8">
+        <v>1000</v>
+      </c>
+      <c r="AP8">
+        <v>220</v>
+      </c>
+      <c r="AQ8">
+        <v>220</v>
+      </c>
+      <c r="AR8">
+        <v>220</v>
+      </c>
+      <c r="AS8">
+        <v>220</v>
+      </c>
+      <c r="AT8">
+        <v>110</v>
+      </c>
+      <c r="AU8">
+        <v>1.4</v>
+      </c>
+      <c r="AV8">
+        <v>36</v>
+      </c>
+      <c r="AW8">
+        <v>44</v>
+      </c>
+      <c r="AX8">
+        <v>110</v>
+      </c>
+      <c r="AY8">
+        <v>3.8</v>
+      </c>
+      <c r="AZ8">
+        <v>13.5</v>
+      </c>
+      <c r="BA8">
+        <v>9.6</v>
+      </c>
+      <c r="BB8">
+        <v>110</v>
+      </c>
+      <c r="BC8">
+        <v>18</v>
+      </c>
+      <c r="BD8">
+        <v>7.4</v>
+      </c>
+      <c r="BE8">
+        <v>7.4</v>
+      </c>
+      <c r="BF8">
+        <v>7.4</v>
+      </c>
+      <c r="BG8">
         <v>30</v>
       </c>
-      <c r="Z8">
-        <v>75</v>
-      </c>
-      <c r="AA8">
-        <v>230</v>
-      </c>
-      <c r="AB8">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC8">
-        <v>10.5</v>
-      </c>
-      <c r="AD8">
-        <v>26</v>
-      </c>
-      <c r="AE8">
-        <v>110</v>
-      </c>
-      <c r="AF8">
-        <v>9.6</v>
-      </c>
-      <c r="AG8">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AH8">
-        <v>19.5</v>
-      </c>
-      <c r="AI8">
-        <v>85</v>
-      </c>
-      <c r="AJ8">
-        <v>13.5</v>
-      </c>
-      <c r="AK8">
-        <v>14.5</v>
-      </c>
-      <c r="AL8">
-        <v>29</v>
-      </c>
-      <c r="AM8">
-        <v>100</v>
-      </c>
-      <c r="AN8">
-        <v>6.4</v>
-      </c>
-      <c r="AO8">
-        <v>110</v>
-      </c>
-      <c r="AP8">
-        <v>20</v>
-      </c>
-      <c r="AQ8">
-        <v>28</v>
-      </c>
-      <c r="AR8">
-        <v>65</v>
-      </c>
-      <c r="AS8">
-        <v>170</v>
-      </c>
-      <c r="AT8">
-        <v>9.4</v>
-      </c>
-      <c r="AU8">
-        <v>10</v>
-      </c>
-      <c r="AV8">
-        <v>25</v>
-      </c>
-      <c r="AW8">
-        <v>90</v>
-      </c>
-      <c r="AX8">
-        <v>9.4</v>
-      </c>
-      <c r="AY8">
-        <v>9</v>
-      </c>
-      <c r="AZ8">
-        <v>19</v>
-      </c>
-      <c r="BA8">
-        <v>75</v>
-      </c>
-      <c r="BB8">
-        <v>12.5</v>
-      </c>
-      <c r="BC8">
-        <v>14</v>
-      </c>
-      <c r="BD8">
-        <v>28</v>
-      </c>
-      <c r="BE8">
-        <v>85</v>
-      </c>
-      <c r="BF8">
-        <v>6</v>
-      </c>
-      <c r="BG8">
-        <v>80</v>
-      </c>
       <c r="BH8">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BI8">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BJ8">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BK8">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="BL8">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="BM8">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="BN8">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BO8">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="BP8">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BQ8">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BR8">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BS8">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="BT8">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BU8">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="BV8">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="BW8">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BX8">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="BY8">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="BZ8">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="CA8">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="CB8" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2646,241 +2634,241 @@
         <v>81</v>
       </c>
       <c r="B9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D9" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E9" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="F9">
-        <v>3.3</v>
+        <v>7</v>
       </c>
       <c r="G9">
-        <v>3.4</v>
+        <v>7.6</v>
       </c>
       <c r="H9">
-        <v>2.3</v>
+        <v>3.05</v>
       </c>
       <c r="I9">
-        <v>2.38</v>
+        <v>3.2</v>
       </c>
       <c r="J9">
-        <v>3.6</v>
+        <v>1.85</v>
       </c>
       <c r="K9">
-        <v>3.8</v>
+        <v>1.86</v>
       </c>
       <c r="L9">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M9">
-        <v>1.06</v>
+        <v>1.8</v>
       </c>
       <c r="N9">
-        <v>4.1</v>
+        <v>1.2</v>
       </c>
       <c r="O9">
-        <v>1.29</v>
+        <v>5.3</v>
       </c>
       <c r="P9">
-        <v>2.08</v>
+        <v>1.04</v>
       </c>
       <c r="Q9">
-        <v>1.88</v>
+        <v>22</v>
       </c>
       <c r="R9">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="S9">
-        <v>3.25</v>
+        <v>110</v>
       </c>
       <c r="T9">
-        <v>1.71</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="U9">
-        <v>2.28</v>
+        <v>1.09</v>
       </c>
       <c r="V9">
-        <v>1.71</v>
+        <v>1.47</v>
       </c>
       <c r="W9">
-        <v>1.42</v>
+        <v>1.14</v>
       </c>
       <c r="X9">
-        <v>17</v>
+        <v>2.16</v>
       </c>
       <c r="Y9">
-        <v>11.5</v>
+        <v>4.2</v>
       </c>
       <c r="Z9">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AA9">
-        <v>34</v>
+        <v>190</v>
       </c>
       <c r="AB9">
         <v>14.5</v>
       </c>
       <c r="AC9">
-        <v>8.6</v>
+        <v>17</v>
       </c>
       <c r="AD9">
-        <v>12</v>
+        <v>95</v>
       </c>
       <c r="AE9">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AF9">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AG9">
-        <v>14.5</v>
+        <v>200</v>
       </c>
       <c r="AH9">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AI9">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AJ9">
+        <v>1000</v>
+      </c>
+      <c r="AK9">
+        <v>1000</v>
+      </c>
+      <c r="AL9">
+        <v>1000</v>
+      </c>
+      <c r="AM9">
+        <v>1000</v>
+      </c>
+      <c r="AN9">
+        <v>1000</v>
+      </c>
+      <c r="AO9">
+        <v>1000</v>
+      </c>
+      <c r="AP9">
+        <v>2.04</v>
+      </c>
+      <c r="AQ9">
+        <v>3.5</v>
+      </c>
+      <c r="AR9">
+        <v>6.4</v>
+      </c>
+      <c r="AS9">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT9">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU9">
+        <v>13.5</v>
+      </c>
+      <c r="AV9">
+        <v>8.4</v>
+      </c>
+      <c r="AW9">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX9">
         <v>65</v>
       </c>
-      <c r="AK9">
-        <v>36</v>
-      </c>
-      <c r="AL9">
-        <v>44</v>
-      </c>
-      <c r="AM9">
-        <v>90</v>
-      </c>
-      <c r="AN9">
-        <v>32</v>
-      </c>
-      <c r="AO9">
-        <v>17.5</v>
-      </c>
-      <c r="AP9">
-        <v>14</v>
-      </c>
-      <c r="AQ9">
-        <v>10</v>
-      </c>
-      <c r="AR9">
-        <v>14</v>
-      </c>
-      <c r="AS9">
-        <v>19</v>
-      </c>
-      <c r="AT9">
-        <v>12.5</v>
-      </c>
-      <c r="AU9">
-        <v>7.4</v>
-      </c>
-      <c r="AV9">
-        <v>10</v>
-      </c>
-      <c r="AW9">
-        <v>21</v>
-      </c>
-      <c r="AX9">
-        <v>20</v>
-      </c>
       <c r="AY9">
-        <v>12</v>
+        <v>95</v>
       </c>
       <c r="AZ9">
-        <v>14.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BA9">
-        <v>28</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB9">
-        <v>38</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC9">
-        <v>19</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD9">
-        <v>24</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE9">
-        <v>29</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF9">
-        <v>23</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG9">
-        <v>15</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH9">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BI9">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="BJ9">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BK9">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BL9">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="BM9">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BN9">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BO9">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BP9">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="BQ9">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BR9">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BS9">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BT9">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BU9">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BV9">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BW9">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BX9">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BY9">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BZ9">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="CA9">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="CB9" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2888,52 +2876,52 @@
         <v>82</v>
       </c>
       <c r="B10" t="s">
+        <v>84</v>
+      </c>
+      <c r="C10" t="s">
+        <v>86</v>
+      </c>
+      <c r="D10" t="s">
+        <v>98</v>
+      </c>
+      <c r="E10" t="s">
+        <v>110</v>
+      </c>
+      <c r="F10">
+        <v>1.02</v>
+      </c>
+      <c r="G10">
+        <v>1.03</v>
+      </c>
+      <c r="H10">
+        <v>330</v>
+      </c>
+      <c r="I10">
+        <v>950</v>
+      </c>
+      <c r="J10">
+        <v>34</v>
+      </c>
+      <c r="K10">
         <v>85</v>
       </c>
-      <c r="C10" t="s">
-        <v>87</v>
-      </c>
-      <c r="D10" t="s">
-        <v>100</v>
-      </c>
-      <c r="E10" t="s">
-        <v>113</v>
-      </c>
-      <c r="F10">
-        <v>1.93</v>
-      </c>
-      <c r="G10">
-        <v>1.98</v>
-      </c>
-      <c r="H10">
-        <v>5</v>
-      </c>
-      <c r="I10">
-        <v>5.4</v>
-      </c>
-      <c r="J10">
-        <v>3.25</v>
-      </c>
-      <c r="K10">
-        <v>3.4</v>
-      </c>
       <c r="L10">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M10">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="N10">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="O10">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="P10">
-        <v>1.57</v>
+        <v>2.36</v>
       </c>
       <c r="Q10">
-        <v>2.64</v>
+        <v>1.7</v>
       </c>
       <c r="R10">
         <v>1.19</v>
@@ -2942,187 +2930,187 @@
         <v>5.6</v>
       </c>
       <c r="T10">
-        <v>2.32</v>
+        <v>4.3</v>
       </c>
       <c r="U10">
-        <v>1.63</v>
+        <v>1.25</v>
       </c>
       <c r="V10">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="W10">
-        <v>2.18</v>
+        <v>34</v>
       </c>
       <c r="X10">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="Y10">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Z10">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AA10">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AB10">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="AC10">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AD10">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AE10">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AF10">
-        <v>10.5</v>
+        <v>2.26</v>
       </c>
       <c r="AG10">
-        <v>12</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AH10">
-        <v>34</v>
+        <v>80</v>
       </c>
       <c r="AI10">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AJ10">
-        <v>24</v>
+        <v>4.3</v>
       </c>
       <c r="AK10">
-        <v>34</v>
+        <v>18.5</v>
       </c>
       <c r="AL10">
-        <v>75</v>
+        <v>220</v>
       </c>
       <c r="AM10">
-        <v>580</v>
+        <v>1000</v>
       </c>
       <c r="AN10">
-        <v>25</v>
+        <v>12.5</v>
       </c>
       <c r="AO10">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AP10">
+        <v>28</v>
+      </c>
+      <c r="AQ10">
+        <v>28</v>
+      </c>
+      <c r="AR10">
+        <v>28</v>
+      </c>
+      <c r="AS10">
+        <v>28</v>
+      </c>
+      <c r="AT10">
+        <v>28</v>
+      </c>
+      <c r="AU10">
+        <v>28</v>
+      </c>
+      <c r="AV10">
+        <v>28</v>
+      </c>
+      <c r="AW10">
+        <v>28</v>
+      </c>
+      <c r="AX10">
+        <v>2.06</v>
+      </c>
+      <c r="AY10">
         <v>7.8</v>
       </c>
-      <c r="AQ10">
-        <v>11.5</v>
-      </c>
-      <c r="AR10">
+      <c r="AZ10">
+        <v>46</v>
+      </c>
+      <c r="BA10">
         <v>12.5</v>
       </c>
-      <c r="AS10">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AT10">
-        <v>5.7</v>
-      </c>
-      <c r="AU10">
-        <v>7</v>
-      </c>
-      <c r="AV10">
-        <v>19.5</v>
-      </c>
-      <c r="AW10">
-        <v>32</v>
-      </c>
-      <c r="AX10">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY10">
-        <v>9.6</v>
-      </c>
-      <c r="AZ10">
-        <v>22</v>
-      </c>
-      <c r="BA10">
-        <v>8.6</v>
-      </c>
       <c r="BB10">
-        <v>19.5</v>
+        <v>4</v>
       </c>
       <c r="BC10">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="BD10">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="BE10">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="BF10">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="BG10">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BH10">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="BI10">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="BJ10">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BK10">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BL10">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM10">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BN10">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BO10">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BP10">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="BQ10">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BR10">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="BS10">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BT10">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BU10">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="BV10">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="BW10">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="BX10">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="BY10">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="BZ10">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="CA10">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="CB10" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3130,241 +3118,241 @@
         <v>83</v>
       </c>
       <c r="B11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D11" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E11" t="s">
+        <v>111</v>
+      </c>
+      <c r="F11">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="G11">
+        <v>11.5</v>
+      </c>
+      <c r="H11">
+        <v>1.51</v>
+      </c>
+      <c r="I11">
+        <v>1.53</v>
+      </c>
+      <c r="J11">
+        <v>4</v>
+      </c>
+      <c r="K11">
+        <v>4.3</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>4.4</v>
+      </c>
+      <c r="O11">
+        <v>1.28</v>
+      </c>
+      <c r="P11">
+        <v>1.76</v>
+      </c>
+      <c r="Q11">
+        <v>2.26</v>
+      </c>
+      <c r="R11">
+        <v>1.2</v>
+      </c>
+      <c r="S11">
+        <v>5.8</v>
+      </c>
+      <c r="T11">
+        <v>1.82</v>
+      </c>
+      <c r="U11">
+        <v>2.06</v>
+      </c>
+      <c r="V11">
+        <v>2.88</v>
+      </c>
+      <c r="W11">
+        <v>1.09</v>
+      </c>
+      <c r="X11">
+        <v>1000</v>
+      </c>
+      <c r="Y11">
+        <v>4.6</v>
+      </c>
+      <c r="Z11">
+        <v>6.6</v>
+      </c>
+      <c r="AA11">
+        <v>22</v>
+      </c>
+      <c r="AB11">
+        <v>1000</v>
+      </c>
+      <c r="AC11">
+        <v>5.5</v>
+      </c>
+      <c r="AD11">
+        <v>8.4</v>
+      </c>
+      <c r="AE11">
+        <v>25</v>
+      </c>
+      <c r="AF11">
+        <v>1000</v>
+      </c>
+      <c r="AG11">
+        <v>17.5</v>
+      </c>
+      <c r="AH11">
+        <v>22</v>
+      </c>
+      <c r="AI11">
+        <v>90</v>
+      </c>
+      <c r="AJ11">
+        <v>1000</v>
+      </c>
+      <c r="AK11">
+        <v>95</v>
+      </c>
+      <c r="AL11">
+        <v>140</v>
+      </c>
+      <c r="AM11">
+        <v>310</v>
+      </c>
+      <c r="AN11">
+        <v>300</v>
+      </c>
+      <c r="AO11">
+        <v>36</v>
+      </c>
+      <c r="AP11">
+        <v>28</v>
+      </c>
+      <c r="AQ11">
+        <v>4.2</v>
+      </c>
+      <c r="AR11">
+        <v>5.8</v>
+      </c>
+      <c r="AS11">
+        <v>16</v>
+      </c>
+      <c r="AT11">
+        <v>28</v>
+      </c>
+      <c r="AU11">
+        <v>5.1</v>
+      </c>
+      <c r="AV11">
+        <v>7.4</v>
+      </c>
+      <c r="AW11">
+        <v>21</v>
+      </c>
+      <c r="AX11">
+        <v>28</v>
+      </c>
+      <c r="AY11">
+        <v>14</v>
+      </c>
+      <c r="AZ11">
+        <v>18</v>
+      </c>
+      <c r="BA11">
+        <v>50</v>
+      </c>
+      <c r="BB11">
+        <v>28</v>
+      </c>
+      <c r="BC11">
+        <v>55</v>
+      </c>
+      <c r="BD11">
+        <v>80</v>
+      </c>
+      <c r="BE11">
+        <v>190</v>
+      </c>
+      <c r="BF11">
+        <v>80</v>
+      </c>
+      <c r="BG11">
+        <v>28</v>
+      </c>
+      <c r="BH11">
+        <v>1000</v>
+      </c>
+      <c r="BI11">
+        <v>11.5</v>
+      </c>
+      <c r="BJ11">
+        <v>9.4</v>
+      </c>
+      <c r="BK11">
+        <v>7</v>
+      </c>
+      <c r="BL11">
+        <v>1000</v>
+      </c>
+      <c r="BM11">
+        <v>11.5</v>
+      </c>
+      <c r="BN11">
+        <v>1000</v>
+      </c>
+      <c r="BO11">
+        <v>11.5</v>
+      </c>
+      <c r="BP11">
+        <v>1000</v>
+      </c>
+      <c r="BQ11">
+        <v>11.5</v>
+      </c>
+      <c r="BR11">
+        <v>130</v>
+      </c>
+      <c r="BS11">
+        <v>90</v>
+      </c>
+      <c r="BT11">
+        <v>1.46</v>
+      </c>
+      <c r="BU11">
+        <v>1.36</v>
+      </c>
+      <c r="BV11">
+        <v>11</v>
+      </c>
+      <c r="BW11">
+        <v>7.4</v>
+      </c>
+      <c r="BX11">
+        <v>55</v>
+      </c>
+      <c r="BY11">
+        <v>46</v>
+      </c>
+      <c r="BZ11">
+        <v>0</v>
+      </c>
+      <c r="CA11">
+        <v>0</v>
+      </c>
+      <c r="CB11" t="s">
         <v>114</v>
-      </c>
-      <c r="F11">
-        <v>2.9</v>
-      </c>
-      <c r="G11">
-        <v>3</v>
-      </c>
-      <c r="H11">
-        <v>3.05</v>
-      </c>
-      <c r="I11">
-        <v>3.2</v>
-      </c>
-      <c r="J11">
-        <v>2.86</v>
-      </c>
-      <c r="K11">
-        <v>2.98</v>
-      </c>
-      <c r="L11">
-        <v>1.71</v>
-      </c>
-      <c r="M11">
-        <v>1.17</v>
-      </c>
-      <c r="N11">
-        <v>2.28</v>
-      </c>
-      <c r="O11">
-        <v>1.73</v>
-      </c>
-      <c r="P11">
-        <v>1.4</v>
-      </c>
-      <c r="Q11">
-        <v>3.3</v>
-      </c>
-      <c r="R11">
-        <v>1.13</v>
-      </c>
-      <c r="S11">
-        <v>7.4</v>
-      </c>
-      <c r="T11">
-        <v>2.4</v>
-      </c>
-      <c r="U11">
-        <v>1.62</v>
-      </c>
-      <c r="V11">
-        <v>1.45</v>
-      </c>
-      <c r="W11">
-        <v>1.5</v>
-      </c>
-      <c r="X11">
-        <v>7</v>
-      </c>
-      <c r="Y11">
-        <v>7.8</v>
-      </c>
-      <c r="Z11">
-        <v>18</v>
-      </c>
-      <c r="AA11">
-        <v>160</v>
-      </c>
-      <c r="AB11">
-        <v>7.4</v>
-      </c>
-      <c r="AC11">
-        <v>7.4</v>
-      </c>
-      <c r="AD11">
-        <v>17</v>
-      </c>
-      <c r="AE11">
-        <v>150</v>
-      </c>
-      <c r="AF11">
-        <v>18</v>
-      </c>
-      <c r="AG11">
-        <v>16</v>
-      </c>
-      <c r="AH11">
-        <v>30</v>
-      </c>
-      <c r="AI11">
-        <v>260</v>
-      </c>
-      <c r="AJ11">
-        <v>90</v>
-      </c>
-      <c r="AK11">
-        <v>60</v>
-      </c>
-      <c r="AL11">
-        <v>340</v>
-      </c>
-      <c r="AM11">
-        <v>500</v>
-      </c>
-      <c r="AN11">
-        <v>110</v>
-      </c>
-      <c r="AO11">
-        <v>110</v>
-      </c>
-      <c r="AP11">
-        <v>6.2</v>
-      </c>
-      <c r="AQ11">
-        <v>6.6</v>
-      </c>
-      <c r="AR11">
-        <v>15</v>
-      </c>
-      <c r="AS11">
-        <v>30</v>
-      </c>
-      <c r="AT11">
-        <v>6.4</v>
-      </c>
-      <c r="AU11">
-        <v>6.2</v>
-      </c>
-      <c r="AV11">
-        <v>14</v>
-      </c>
-      <c r="AW11">
-        <v>29</v>
-      </c>
-      <c r="AX11">
-        <v>14</v>
-      </c>
-      <c r="AY11">
-        <v>13</v>
-      </c>
-      <c r="AZ11">
-        <v>23</v>
-      </c>
-      <c r="BA11">
-        <v>40</v>
-      </c>
-      <c r="BB11">
-        <v>42</v>
-      </c>
-      <c r="BC11">
-        <v>23</v>
-      </c>
-      <c r="BD11">
-        <v>10.5</v>
-      </c>
-      <c r="BE11">
-        <v>11.5</v>
-      </c>
-      <c r="BF11">
-        <v>10.5</v>
-      </c>
-      <c r="BG11">
-        <v>10.5</v>
-      </c>
-      <c r="BH11">
-        <v>2.46</v>
-      </c>
-      <c r="BI11">
-        <v>2.2</v>
-      </c>
-      <c r="BJ11">
-        <v>13</v>
-      </c>
-      <c r="BK11">
-        <v>6.4</v>
-      </c>
-      <c r="BL11">
-        <v>1000</v>
-      </c>
-      <c r="BM11">
-        <v>12</v>
-      </c>
-      <c r="BN11">
-        <v>5.9</v>
-      </c>
-      <c r="BO11">
-        <v>4.9</v>
-      </c>
-      <c r="BP11">
-        <v>32</v>
-      </c>
-      <c r="BQ11">
-        <v>9</v>
-      </c>
-      <c r="BR11">
-        <v>1000</v>
-      </c>
-      <c r="BS11">
-        <v>10.5</v>
-      </c>
-      <c r="BT11">
-        <v>6.2</v>
-      </c>
-      <c r="BU11">
-        <v>5.1</v>
-      </c>
-      <c r="BV11">
-        <v>34</v>
-      </c>
-      <c r="BW11">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BX11">
-        <v>70</v>
-      </c>
-      <c r="BY11">
-        <v>10.5</v>
-      </c>
-      <c r="BZ11">
-        <v>0</v>
-      </c>
-      <c r="CA11">
-        <v>0</v>
-      </c>
-      <c r="CB11" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3372,37 +3360,37 @@
         <v>82</v>
       </c>
       <c r="B12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D12" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E12" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="F12">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="G12">
+        <v>2.9</v>
+      </c>
+      <c r="H12">
+        <v>3.25</v>
+      </c>
+      <c r="I12">
+        <v>3.5</v>
+      </c>
+      <c r="J12">
+        <v>2.78</v>
+      </c>
+      <c r="K12">
         <v>2.92</v>
       </c>
-      <c r="H12">
-        <v>3.15</v>
-      </c>
-      <c r="I12">
-        <v>3.3</v>
-      </c>
-      <c r="J12">
-        <v>2.86</v>
-      </c>
-      <c r="K12">
-        <v>2.94</v>
-      </c>
       <c r="L12">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="M12">
         <v>1.14</v>
@@ -3411,88 +3399,88 @@
         <v>2.62</v>
       </c>
       <c r="O12">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="P12">
         <v>1.52</v>
       </c>
       <c r="Q12">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="R12">
         <v>1.19</v>
       </c>
       <c r="S12">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="T12">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="U12">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="V12">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W12">
         <v>1.52</v>
       </c>
       <c r="X12">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="Y12">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z12">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA12">
-        <v>65</v>
+        <v>900</v>
       </c>
       <c r="AB12">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AC12">
+        <v>7.6</v>
+      </c>
+      <c r="AD12">
+        <v>16</v>
+      </c>
+      <c r="AE12">
+        <v>260</v>
+      </c>
+      <c r="AF12">
+        <v>17</v>
+      </c>
+      <c r="AG12">
+        <v>14</v>
+      </c>
+      <c r="AH12">
+        <v>28</v>
+      </c>
+      <c r="AI12">
+        <v>240</v>
+      </c>
+      <c r="AJ12">
+        <v>900</v>
+      </c>
+      <c r="AK12">
+        <v>100</v>
+      </c>
+      <c r="AL12">
+        <v>180</v>
+      </c>
+      <c r="AM12">
+        <v>580</v>
+      </c>
+      <c r="AN12">
+        <v>600</v>
+      </c>
+      <c r="AO12">
+        <v>980</v>
+      </c>
+      <c r="AP12">
         <v>7.2</v>
-      </c>
-      <c r="AD12">
-        <v>15</v>
-      </c>
-      <c r="AE12">
-        <v>55</v>
-      </c>
-      <c r="AF12">
-        <v>17.5</v>
-      </c>
-      <c r="AG12">
-        <v>13.5</v>
-      </c>
-      <c r="AH12">
-        <v>25</v>
-      </c>
-      <c r="AI12">
-        <v>85</v>
-      </c>
-      <c r="AJ12">
-        <v>55</v>
-      </c>
-      <c r="AK12">
-        <v>55</v>
-      </c>
-      <c r="AL12">
-        <v>75</v>
-      </c>
-      <c r="AM12">
-        <v>210</v>
-      </c>
-      <c r="AN12">
-        <v>60</v>
-      </c>
-      <c r="AO12">
-        <v>85</v>
-      </c>
-      <c r="AP12">
-        <v>7.4</v>
       </c>
       <c r="AQ12">
         <v>8.199999999999999</v>
@@ -3501,112 +3489,112 @@
         <v>17</v>
       </c>
       <c r="AS12">
-        <v>46</v>
+        <v>6</v>
       </c>
       <c r="AT12">
         <v>7.4</v>
       </c>
       <c r="AU12">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV12">
         <v>13</v>
       </c>
       <c r="AW12">
-        <v>42</v>
+        <v>5.9</v>
       </c>
       <c r="AX12">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AY12">
         <v>12</v>
       </c>
       <c r="AZ12">
-        <v>21</v>
+        <v>16.5</v>
       </c>
       <c r="BA12">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="BB12">
-        <v>36</v>
+        <v>17.5</v>
       </c>
       <c r="BC12">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="BD12">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="BE12">
-        <v>120</v>
+        <v>6</v>
       </c>
       <c r="BF12">
-        <v>38</v>
+        <v>5.9</v>
       </c>
       <c r="BG12">
-        <v>46</v>
+        <v>6</v>
       </c>
       <c r="BH12">
-        <v>2.94</v>
+        <v>2.68</v>
       </c>
       <c r="BI12">
-        <v>2.26</v>
+        <v>2.46</v>
       </c>
       <c r="BJ12">
         <v>13</v>
       </c>
       <c r="BK12">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>5.9</v>
+        <v>7.8</v>
       </c>
       <c r="BN12">
         <v>6.4</v>
       </c>
       <c r="BO12">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BP12">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="BQ12">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="BR12">
         <v>60</v>
       </c>
       <c r="BS12">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="BT12">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BU12">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BV12">
         <v>34</v>
       </c>
       <c r="BW12">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="BX12">
         <v>1000</v>
       </c>
       <c r="BY12">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="BZ12">
-        <v>65</v>
+        <v>980</v>
       </c>
       <c r="CA12">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="CB12" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3614,22 +3602,22 @@
         <v>82</v>
       </c>
       <c r="B13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C13" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D13" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E13" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F13">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="G13">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="H13">
         <v>32</v>
@@ -3638,55 +3626,55 @@
         <v>55</v>
       </c>
       <c r="J13">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="K13">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="L13">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="M13">
         <v>1.03</v>
       </c>
       <c r="N13">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="O13">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="P13">
-        <v>2.7</v>
+        <v>2.98</v>
       </c>
       <c r="Q13">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="R13">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="S13">
-        <v>2.32</v>
+        <v>2.14</v>
       </c>
       <c r="T13">
         <v>3</v>
       </c>
       <c r="U13">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="V13">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W13">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="X13">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="Y13">
         <v>110</v>
       </c>
       <c r="Z13">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AA13">
         <v>1000</v>
@@ -3704,10 +3692,10 @@
         <v>1000</v>
       </c>
       <c r="AF13">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AG13">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AH13">
         <v>100</v>
@@ -3716,7 +3704,7 @@
         <v>1000</v>
       </c>
       <c r="AJ13">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AK13">
         <v>21</v>
@@ -3728,369 +3716,127 @@
         <v>1000</v>
       </c>
       <c r="AN13">
-        <v>3.2</v>
+        <v>2.84</v>
       </c>
       <c r="AO13">
         <v>1000</v>
       </c>
       <c r="AP13">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AQ13">
-        <v>7.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR13">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="AS13">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="AT13">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="AU13">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AV13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AW13">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="AX13">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AY13">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AZ13">
-        <v>7.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BA13">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="BB13">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BC13">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BD13">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="BE13">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="BF13">
-        <v>2.9</v>
+        <v>2.58</v>
       </c>
       <c r="BG13">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="BH13">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BI13">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BJ13">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BK13">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BN13">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="BO13">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="BP13">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ13">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BR13">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS13">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BT13">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BU13">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BV13">
         <v>1000</v>
       </c>
       <c r="BW13">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BX13">
         <v>1000</v>
       </c>
       <c r="BY13">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ13">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="CA13">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="CB13" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="14" spans="1:80">
-      <c r="A14" t="s">
-        <v>84</v>
-      </c>
-      <c r="B14" t="s">
-        <v>85</v>
-      </c>
-      <c r="C14" t="s">
-        <v>91</v>
-      </c>
-      <c r="D14" t="s">
-        <v>104</v>
-      </c>
-      <c r="E14" t="s">
-        <v>117</v>
-      </c>
-      <c r="F14">
-        <v>1.6</v>
-      </c>
-      <c r="G14">
-        <v>1.62</v>
-      </c>
-      <c r="H14">
-        <v>6.4</v>
-      </c>
-      <c r="I14">
-        <v>7</v>
-      </c>
-      <c r="J14">
-        <v>4.2</v>
-      </c>
-      <c r="K14">
-        <v>4.5</v>
-      </c>
-      <c r="L14">
-        <v>1.4</v>
-      </c>
-      <c r="M14">
-        <v>1.06</v>
-      </c>
-      <c r="N14">
-        <v>3.95</v>
-      </c>
-      <c r="O14">
-        <v>1.31</v>
-      </c>
-      <c r="P14">
-        <v>2</v>
-      </c>
-      <c r="Q14">
-        <v>1.94</v>
-      </c>
-      <c r="R14">
-        <v>1.38</v>
-      </c>
-      <c r="S14">
-        <v>3.45</v>
-      </c>
-      <c r="T14">
-        <v>2.02</v>
-      </c>
-      <c r="U14">
-        <v>1.87</v>
-      </c>
-      <c r="V14">
-        <v>1.16</v>
-      </c>
-      <c r="W14">
-        <v>2.58</v>
-      </c>
-      <c r="X14">
-        <v>16</v>
-      </c>
-      <c r="Y14">
-        <v>21</v>
-      </c>
-      <c r="Z14">
-        <v>60</v>
-      </c>
-      <c r="AA14">
-        <v>240</v>
-      </c>
-      <c r="AB14">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC14">
-        <v>10</v>
-      </c>
-      <c r="AD14">
-        <v>32</v>
-      </c>
-      <c r="AE14">
-        <v>120</v>
-      </c>
-      <c r="AF14">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AG14">
-        <v>10.5</v>
-      </c>
-      <c r="AH14">
-        <v>26</v>
-      </c>
-      <c r="AI14">
-        <v>190</v>
-      </c>
-      <c r="AJ14">
-        <v>15</v>
-      </c>
-      <c r="AK14">
-        <v>17.5</v>
-      </c>
-      <c r="AL14">
-        <v>44</v>
-      </c>
-      <c r="AM14">
-        <v>170</v>
-      </c>
-      <c r="AN14">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AO14">
-        <v>160</v>
-      </c>
-      <c r="AP14">
-        <v>13.5</v>
-      </c>
-      <c r="AQ14">
-        <v>17.5</v>
-      </c>
-      <c r="AR14">
-        <v>40</v>
-      </c>
-      <c r="AS14">
-        <v>12.5</v>
-      </c>
-      <c r="AT14">
-        <v>7.4</v>
-      </c>
-      <c r="AU14">
-        <v>8.6</v>
-      </c>
-      <c r="AV14">
-        <v>21</v>
-      </c>
-      <c r="AW14">
-        <v>55</v>
-      </c>
-      <c r="AX14">
-        <v>8</v>
-      </c>
-      <c r="AY14">
-        <v>9</v>
-      </c>
-      <c r="AZ14">
-        <v>18.5</v>
-      </c>
-      <c r="BA14">
-        <v>50</v>
-      </c>
-      <c r="BB14">
-        <v>12.5</v>
-      </c>
-      <c r="BC14">
-        <v>15</v>
-      </c>
-      <c r="BD14">
-        <v>26</v>
-      </c>
-      <c r="BE14">
-        <v>85</v>
-      </c>
-      <c r="BF14">
-        <v>8</v>
-      </c>
-      <c r="BG14">
-        <v>65</v>
-      </c>
-      <c r="BH14">
-        <v>3.55</v>
-      </c>
-      <c r="BI14">
-        <v>2.8</v>
-      </c>
-      <c r="BJ14">
-        <v>11.5</v>
-      </c>
-      <c r="BK14">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BL14">
-        <v>1000</v>
-      </c>
-      <c r="BM14">
-        <v>1.01</v>
-      </c>
-      <c r="BN14">
-        <v>4.1</v>
-      </c>
-      <c r="BO14">
-        <v>3.15</v>
-      </c>
-      <c r="BP14">
-        <v>10.5</v>
-      </c>
-      <c r="BQ14">
-        <v>7.6</v>
-      </c>
-      <c r="BR14">
-        <v>27</v>
-      </c>
-      <c r="BS14">
-        <v>19</v>
-      </c>
-      <c r="BT14">
-        <v>10.5</v>
-      </c>
-      <c r="BU14">
-        <v>7.6</v>
-      </c>
-      <c r="BV14">
-        <v>1000</v>
-      </c>
-      <c r="BW14">
-        <v>44</v>
-      </c>
-      <c r="BX14">
-        <v>1000</v>
-      </c>
-      <c r="BY14">
-        <v>48</v>
-      </c>
-      <c r="BZ14">
-        <v>20</v>
-      </c>
-      <c r="CA14">
-        <v>14</v>
-      </c>
-      <c r="CB14" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
